--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G21">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G38">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G39">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G45">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G66">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G68">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G69">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G70">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G80">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G81">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G82">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G83">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G84">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G85">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G99">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G100">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G101">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G122">

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G38">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G39">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G99">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G100">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G101">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G123">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G124">

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G38">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G39">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G62">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G63">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G123">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G125">

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU135"/>
+  <dimension ref="A1:AU128"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5646,22 +5646,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G33">
@@ -5809,22 +5809,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G34">
@@ -5972,22 +5972,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G35">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G38">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Omonia 29is Maiou</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G39">
@@ -6782,12 +6782,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Omonia 29is Maiou</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G40">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>2026-09-18 13:00:00</t>
+          <t>2026-09-18 13:30:00</t>
         </is>
       </c>
     </row>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G42">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G44">
@@ -7597,12 +7597,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G45">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>2026-09-18 13:30:00</t>
+          <t>2026-09-18 14:00:00</t>
         </is>
       </c>
     </row>
@@ -7765,22 +7765,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G46">
@@ -7928,22 +7928,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="G47">
@@ -8091,22 +8091,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G48">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G49">
@@ -8417,22 +8417,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Muğlaspor</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G50">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Muğlaspor</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G51">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G52">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G53">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G54">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Honvéd</t>
         </is>
       </c>
       <c r="G55">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>2026-09-18 14:00:00</t>
+          <t>2026-09-18 14:30:00</t>
         </is>
       </c>
     </row>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Honvéd</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G56">
@@ -9558,7 +9558,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G57">
@@ -9721,22 +9721,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G59">
@@ -10047,22 +10047,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G60">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G61">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G62">
@@ -10531,12 +10531,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G63">
@@ -10682,7 +10682,7 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>2026-09-18 14:30:00</t>
+          <t>2026-09-18 15:00:00</t>
         </is>
       </c>
     </row>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G64">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G65">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G66">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G68">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G69">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G70">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G71">
@@ -12003,7 +12003,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Deportivo Alavés W</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G72">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Deportivo Alavés W</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G73">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G74">
@@ -12492,7 +12492,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O75">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P75">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -12655,7 +12655,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O76">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P76">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -12818,7 +12818,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G77">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G78">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G79">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G80">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G81">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G82">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G83">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G84">
@@ -14117,12 +14117,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G85">
@@ -14268,7 +14268,7 @@
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>2026-09-18 15:00:00</t>
+          <t>2026-09-18 15:15:00</t>
         </is>
       </c>
     </row>
@@ -14280,12 +14280,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G86">
@@ -14431,7 +14431,7 @@
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>2026-09-18 15:15:00</t>
+          <t>2026-09-18 15:30:00</t>
         </is>
       </c>
     </row>
@@ -14448,7 +14448,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G87">
@@ -14611,7 +14611,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G88">
@@ -14774,7 +14774,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G89">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G90">
@@ -15100,7 +15100,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G91">
@@ -15258,12 +15258,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G92">
@@ -15409,7 +15409,7 @@
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>2026-09-18 15:30:00</t>
+          <t>2026-09-18 15:45:00</t>
         </is>
       </c>
     </row>
@@ -15426,7 +15426,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G93">
@@ -15589,22 +15589,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G94">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G95">
@@ -15915,7 +15915,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G96">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G97">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G98">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G99">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G100">
@@ -16730,22 +16730,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G101">
@@ -16893,7 +16893,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G102">
@@ -17051,12 +17051,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G103">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:00</t>
+          <t>2026-09-18 16:00:00</t>
         </is>
       </c>
     </row>
@@ -17219,7 +17219,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="G104">
@@ -17382,22 +17382,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G105">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G106">
@@ -17708,22 +17708,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G107">
@@ -17871,7 +17871,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G108">
@@ -18029,12 +18029,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G109">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>2026-09-18 16:00:00</t>
+          <t>2026-09-18 17:00:00</t>
         </is>
       </c>
     </row>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G110">
@@ -18355,27 +18355,27 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G111">
@@ -18506,7 +18506,7 @@
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>2026-09-18 17:00:00</t>
+          <t>2026-09-18 19:30:00</t>
         </is>
       </c>
     </row>
@@ -18518,12 +18518,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G112">
@@ -18669,7 +18669,7 @@
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>2026-09-18 19:30:00</t>
+          <t>2026-09-18 20:00:00</t>
         </is>
       </c>
     </row>
@@ -18681,12 +18681,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G113">
@@ -18832,7 +18832,7 @@
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>2026-09-18 20:00:00</t>
+          <t>2026-09-18 20:30:00</t>
         </is>
       </c>
     </row>
@@ -18849,7 +18849,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G114">
@@ -19007,27 +19007,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G115">
@@ -19158,7 +19158,7 @@
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>2026-09-18 20:30:00</t>
+          <t>2026-09-18 21:00:00</t>
         </is>
       </c>
     </row>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G116">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="G117">
@@ -19501,7 +19501,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G118">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G120">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G123">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G124">
@@ -20642,7 +20642,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G126">
@@ -20968,22 +20968,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G127">
@@ -21126,27 +21126,27 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Kalamata</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G128">
@@ -21276,1147 +21276,6 @@
         <v>0</v>
       </c>
       <c r="AU128" t="inlineStr">
-        <is>
-          <t>2026-09-18 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Greece Super League</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>OFI</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>Asteras Tripolis</t>
-        </is>
-      </c>
-      <c r="G129">
-        <v>0</v>
-      </c>
-      <c r="H129">
-        <v>0</v>
-      </c>
-      <c r="I129">
-        <v>0</v>
-      </c>
-      <c r="J129">
-        <v>0</v>
-      </c>
-      <c r="K129">
-        <v>0</v>
-      </c>
-      <c r="L129">
-        <v>0</v>
-      </c>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N129">
-        <v>0</v>
-      </c>
-      <c r="O129">
-        <v>0</v>
-      </c>
-      <c r="P129">
-        <v>0</v>
-      </c>
-      <c r="Q129">
-        <v>0</v>
-      </c>
-      <c r="R129">
-        <v>0</v>
-      </c>
-      <c r="S129">
-        <v>0</v>
-      </c>
-      <c r="T129">
-        <v>0</v>
-      </c>
-      <c r="U129">
-        <v>0</v>
-      </c>
-      <c r="V129">
-        <v>0</v>
-      </c>
-      <c r="W129">
-        <v>0</v>
-      </c>
-      <c r="X129">
-        <v>0</v>
-      </c>
-      <c r="Y129">
-        <v>0</v>
-      </c>
-      <c r="Z129">
-        <v>0</v>
-      </c>
-      <c r="AA129">
-        <v>0</v>
-      </c>
-      <c r="AB129">
-        <v>0</v>
-      </c>
-      <c r="AC129">
-        <v>0</v>
-      </c>
-      <c r="AD129">
-        <v>0</v>
-      </c>
-      <c r="AE129">
-        <v>0</v>
-      </c>
-      <c r="AF129">
-        <v>0</v>
-      </c>
-      <c r="AG129">
-        <v>0</v>
-      </c>
-      <c r="AH129" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI129" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ129">
-        <v>0</v>
-      </c>
-      <c r="AK129">
-        <v>0</v>
-      </c>
-      <c r="AL129">
-        <v>0</v>
-      </c>
-      <c r="AM129">
-        <v>-1</v>
-      </c>
-      <c r="AN129">
-        <v>-1</v>
-      </c>
-      <c r="AO129">
-        <v>-1</v>
-      </c>
-      <c r="AP129">
-        <v>-1</v>
-      </c>
-      <c r="AQ129">
-        <v>0</v>
-      </c>
-      <c r="AR129">
-        <v>0</v>
-      </c>
-      <c r="AS129">
-        <v>0</v>
-      </c>
-      <c r="AT129">
-        <v>0</v>
-      </c>
-      <c r="AU129" t="inlineStr">
-        <is>
-          <t>2026-09-18 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Greece Super League</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>Volos NFC</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>AEK Athens</t>
-        </is>
-      </c>
-      <c r="G130">
-        <v>0</v>
-      </c>
-      <c r="H130">
-        <v>0</v>
-      </c>
-      <c r="I130">
-        <v>0</v>
-      </c>
-      <c r="J130">
-        <v>0</v>
-      </c>
-      <c r="K130">
-        <v>0</v>
-      </c>
-      <c r="L130">
-        <v>0</v>
-      </c>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N130">
-        <v>0</v>
-      </c>
-      <c r="O130">
-        <v>0</v>
-      </c>
-      <c r="P130">
-        <v>0</v>
-      </c>
-      <c r="Q130">
-        <v>0</v>
-      </c>
-      <c r="R130">
-        <v>0</v>
-      </c>
-      <c r="S130">
-        <v>0</v>
-      </c>
-      <c r="T130">
-        <v>0</v>
-      </c>
-      <c r="U130">
-        <v>0</v>
-      </c>
-      <c r="V130">
-        <v>0</v>
-      </c>
-      <c r="W130">
-        <v>0</v>
-      </c>
-      <c r="X130">
-        <v>0</v>
-      </c>
-      <c r="Y130">
-        <v>0</v>
-      </c>
-      <c r="Z130">
-        <v>0</v>
-      </c>
-      <c r="AA130">
-        <v>0</v>
-      </c>
-      <c r="AB130">
-        <v>0</v>
-      </c>
-      <c r="AC130">
-        <v>0</v>
-      </c>
-      <c r="AD130">
-        <v>0</v>
-      </c>
-      <c r="AE130">
-        <v>0</v>
-      </c>
-      <c r="AF130">
-        <v>0</v>
-      </c>
-      <c r="AG130">
-        <v>0</v>
-      </c>
-      <c r="AH130" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI130" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ130">
-        <v>0</v>
-      </c>
-      <c r="AK130">
-        <v>0</v>
-      </c>
-      <c r="AL130">
-        <v>0</v>
-      </c>
-      <c r="AM130">
-        <v>-1</v>
-      </c>
-      <c r="AN130">
-        <v>-1</v>
-      </c>
-      <c r="AO130">
-        <v>-1</v>
-      </c>
-      <c r="AP130">
-        <v>-1</v>
-      </c>
-      <c r="AQ130">
-        <v>0</v>
-      </c>
-      <c r="AR130">
-        <v>0</v>
-      </c>
-      <c r="AS130">
-        <v>0</v>
-      </c>
-      <c r="AT130">
-        <v>0</v>
-      </c>
-      <c r="AU130" t="inlineStr">
-        <is>
-          <t>2026-09-18 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Greece Super League</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>Levadiakos</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>Olympiakos Piraeus</t>
-        </is>
-      </c>
-      <c r="G131">
-        <v>0</v>
-      </c>
-      <c r="H131">
-        <v>0</v>
-      </c>
-      <c r="I131">
-        <v>0</v>
-      </c>
-      <c r="J131">
-        <v>0</v>
-      </c>
-      <c r="K131">
-        <v>0</v>
-      </c>
-      <c r="L131">
-        <v>0</v>
-      </c>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N131">
-        <v>0</v>
-      </c>
-      <c r="O131">
-        <v>0</v>
-      </c>
-      <c r="P131">
-        <v>0</v>
-      </c>
-      <c r="Q131">
-        <v>0</v>
-      </c>
-      <c r="R131">
-        <v>0</v>
-      </c>
-      <c r="S131">
-        <v>0</v>
-      </c>
-      <c r="T131">
-        <v>0</v>
-      </c>
-      <c r="U131">
-        <v>0</v>
-      </c>
-      <c r="V131">
-        <v>0</v>
-      </c>
-      <c r="W131">
-        <v>0</v>
-      </c>
-      <c r="X131">
-        <v>0</v>
-      </c>
-      <c r="Y131">
-        <v>0</v>
-      </c>
-      <c r="Z131">
-        <v>0</v>
-      </c>
-      <c r="AA131">
-        <v>0</v>
-      </c>
-      <c r="AB131">
-        <v>0</v>
-      </c>
-      <c r="AC131">
-        <v>0</v>
-      </c>
-      <c r="AD131">
-        <v>0</v>
-      </c>
-      <c r="AE131">
-        <v>0</v>
-      </c>
-      <c r="AF131">
-        <v>0</v>
-      </c>
-      <c r="AG131">
-        <v>0</v>
-      </c>
-      <c r="AH131" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI131" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ131">
-        <v>0</v>
-      </c>
-      <c r="AK131">
-        <v>0</v>
-      </c>
-      <c r="AL131">
-        <v>0</v>
-      </c>
-      <c r="AM131">
-        <v>-1</v>
-      </c>
-      <c r="AN131">
-        <v>-1</v>
-      </c>
-      <c r="AO131">
-        <v>-1</v>
-      </c>
-      <c r="AP131">
-        <v>-1</v>
-      </c>
-      <c r="AQ131">
-        <v>0</v>
-      </c>
-      <c r="AR131">
-        <v>0</v>
-      </c>
-      <c r="AS131">
-        <v>0</v>
-      </c>
-      <c r="AT131">
-        <v>0</v>
-      </c>
-      <c r="AU131" t="inlineStr">
-        <is>
-          <t>2026-09-18 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Greece Super League</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Panaitolikos</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>PAOK</t>
-        </is>
-      </c>
-      <c r="G132">
-        <v>0</v>
-      </c>
-      <c r="H132">
-        <v>0</v>
-      </c>
-      <c r="I132">
-        <v>0</v>
-      </c>
-      <c r="J132">
-        <v>0</v>
-      </c>
-      <c r="K132">
-        <v>0</v>
-      </c>
-      <c r="L132">
-        <v>0</v>
-      </c>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N132">
-        <v>0</v>
-      </c>
-      <c r="O132">
-        <v>0</v>
-      </c>
-      <c r="P132">
-        <v>0</v>
-      </c>
-      <c r="Q132">
-        <v>0</v>
-      </c>
-      <c r="R132">
-        <v>0</v>
-      </c>
-      <c r="S132">
-        <v>0</v>
-      </c>
-      <c r="T132">
-        <v>0</v>
-      </c>
-      <c r="U132">
-        <v>0</v>
-      </c>
-      <c r="V132">
-        <v>0</v>
-      </c>
-      <c r="W132">
-        <v>0</v>
-      </c>
-      <c r="X132">
-        <v>0</v>
-      </c>
-      <c r="Y132">
-        <v>0</v>
-      </c>
-      <c r="Z132">
-        <v>0</v>
-      </c>
-      <c r="AA132">
-        <v>0</v>
-      </c>
-      <c r="AB132">
-        <v>0</v>
-      </c>
-      <c r="AC132">
-        <v>0</v>
-      </c>
-      <c r="AD132">
-        <v>0</v>
-      </c>
-      <c r="AE132">
-        <v>0</v>
-      </c>
-      <c r="AF132">
-        <v>0</v>
-      </c>
-      <c r="AG132">
-        <v>0</v>
-      </c>
-      <c r="AH132" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI132" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ132">
-        <v>0</v>
-      </c>
-      <c r="AK132">
-        <v>0</v>
-      </c>
-      <c r="AL132">
-        <v>0</v>
-      </c>
-      <c r="AM132">
-        <v>-1</v>
-      </c>
-      <c r="AN132">
-        <v>-1</v>
-      </c>
-      <c r="AO132">
-        <v>-1</v>
-      </c>
-      <c r="AP132">
-        <v>-1</v>
-      </c>
-      <c r="AQ132">
-        <v>0</v>
-      </c>
-      <c r="AR132">
-        <v>0</v>
-      </c>
-      <c r="AS132">
-        <v>0</v>
-      </c>
-      <c r="AT132">
-        <v>0</v>
-      </c>
-      <c r="AU132" t="inlineStr">
-        <is>
-          <t>2026-09-18 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Croatia Druga HNL</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Karlovac 1919</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>Dubrava Zagreb</t>
-        </is>
-      </c>
-      <c r="G133">
-        <v>0</v>
-      </c>
-      <c r="H133">
-        <v>0</v>
-      </c>
-      <c r="I133">
-        <v>0</v>
-      </c>
-      <c r="J133">
-        <v>0</v>
-      </c>
-      <c r="K133">
-        <v>0</v>
-      </c>
-      <c r="L133">
-        <v>0</v>
-      </c>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N133">
-        <v>0</v>
-      </c>
-      <c r="O133">
-        <v>0</v>
-      </c>
-      <c r="P133">
-        <v>0</v>
-      </c>
-      <c r="Q133">
-        <v>0</v>
-      </c>
-      <c r="R133">
-        <v>0</v>
-      </c>
-      <c r="S133">
-        <v>0</v>
-      </c>
-      <c r="T133">
-        <v>0</v>
-      </c>
-      <c r="U133">
-        <v>0</v>
-      </c>
-      <c r="V133">
-        <v>0</v>
-      </c>
-      <c r="W133">
-        <v>0</v>
-      </c>
-      <c r="X133">
-        <v>0</v>
-      </c>
-      <c r="Y133">
-        <v>0</v>
-      </c>
-      <c r="Z133">
-        <v>0</v>
-      </c>
-      <c r="AA133">
-        <v>0</v>
-      </c>
-      <c r="AB133">
-        <v>0</v>
-      </c>
-      <c r="AC133">
-        <v>0</v>
-      </c>
-      <c r="AD133">
-        <v>0</v>
-      </c>
-      <c r="AE133">
-        <v>0</v>
-      </c>
-      <c r="AF133">
-        <v>0</v>
-      </c>
-      <c r="AG133">
-        <v>0</v>
-      </c>
-      <c r="AH133" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI133" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ133">
-        <v>0</v>
-      </c>
-      <c r="AK133">
-        <v>0</v>
-      </c>
-      <c r="AL133">
-        <v>0</v>
-      </c>
-      <c r="AM133">
-        <v>-1</v>
-      </c>
-      <c r="AN133">
-        <v>-1</v>
-      </c>
-      <c r="AO133">
-        <v>-1</v>
-      </c>
-      <c r="AP133">
-        <v>-1</v>
-      </c>
-      <c r="AQ133">
-        <v>0</v>
-      </c>
-      <c r="AR133">
-        <v>0</v>
-      </c>
-      <c r="AS133">
-        <v>0</v>
-      </c>
-      <c r="AT133">
-        <v>0</v>
-      </c>
-      <c r="AU133" t="inlineStr">
-        <is>
-          <t>2026-09-18 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>São Bernardo</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>Atlético GO</t>
-        </is>
-      </c>
-      <c r="G134">
-        <v>0</v>
-      </c>
-      <c r="H134">
-        <v>0</v>
-      </c>
-      <c r="I134">
-        <v>0</v>
-      </c>
-      <c r="J134">
-        <v>0</v>
-      </c>
-      <c r="K134">
-        <v>0</v>
-      </c>
-      <c r="L134">
-        <v>0</v>
-      </c>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N134">
-        <v>0</v>
-      </c>
-      <c r="O134">
-        <v>0</v>
-      </c>
-      <c r="P134">
-        <v>0</v>
-      </c>
-      <c r="Q134">
-        <v>0</v>
-      </c>
-      <c r="R134">
-        <v>0</v>
-      </c>
-      <c r="S134">
-        <v>0</v>
-      </c>
-      <c r="T134">
-        <v>0</v>
-      </c>
-      <c r="U134">
-        <v>0</v>
-      </c>
-      <c r="V134">
-        <v>0</v>
-      </c>
-      <c r="W134">
-        <v>0</v>
-      </c>
-      <c r="X134">
-        <v>0</v>
-      </c>
-      <c r="Y134">
-        <v>0</v>
-      </c>
-      <c r="Z134">
-        <v>0</v>
-      </c>
-      <c r="AA134">
-        <v>0</v>
-      </c>
-      <c r="AB134">
-        <v>0</v>
-      </c>
-      <c r="AC134">
-        <v>0</v>
-      </c>
-      <c r="AD134">
-        <v>0</v>
-      </c>
-      <c r="AE134">
-        <v>0</v>
-      </c>
-      <c r="AF134">
-        <v>0</v>
-      </c>
-      <c r="AG134">
-        <v>0</v>
-      </c>
-      <c r="AH134" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI134" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ134">
-        <v>0</v>
-      </c>
-      <c r="AK134">
-        <v>0</v>
-      </c>
-      <c r="AL134">
-        <v>0</v>
-      </c>
-      <c r="AM134">
-        <v>-1</v>
-      </c>
-      <c r="AN134">
-        <v>-1</v>
-      </c>
-      <c r="AO134">
-        <v>-1</v>
-      </c>
-      <c r="AP134">
-        <v>-1</v>
-      </c>
-      <c r="AQ134">
-        <v>0</v>
-      </c>
-      <c r="AR134">
-        <v>0</v>
-      </c>
-      <c r="AS134">
-        <v>0</v>
-      </c>
-      <c r="AT134">
-        <v>0</v>
-      </c>
-      <c r="AU134" t="inlineStr">
-        <is>
-          <t>2026-09-18 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>San Diego Wave</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>Kansas City</t>
-        </is>
-      </c>
-      <c r="G135">
-        <v>0</v>
-      </c>
-      <c r="H135">
-        <v>0</v>
-      </c>
-      <c r="I135">
-        <v>0</v>
-      </c>
-      <c r="J135">
-        <v>0</v>
-      </c>
-      <c r="K135">
-        <v>0</v>
-      </c>
-      <c r="L135">
-        <v>0</v>
-      </c>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N135">
-        <v>0</v>
-      </c>
-      <c r="O135">
-        <v>0</v>
-      </c>
-      <c r="P135">
-        <v>0</v>
-      </c>
-      <c r="Q135">
-        <v>0</v>
-      </c>
-      <c r="R135">
-        <v>0</v>
-      </c>
-      <c r="S135">
-        <v>0</v>
-      </c>
-      <c r="T135">
-        <v>0</v>
-      </c>
-      <c r="U135">
-        <v>0</v>
-      </c>
-      <c r="V135">
-        <v>0</v>
-      </c>
-      <c r="W135">
-        <v>0</v>
-      </c>
-      <c r="X135">
-        <v>0</v>
-      </c>
-      <c r="Y135">
-        <v>0</v>
-      </c>
-      <c r="Z135">
-        <v>0</v>
-      </c>
-      <c r="AA135">
-        <v>0</v>
-      </c>
-      <c r="AB135">
-        <v>0</v>
-      </c>
-      <c r="AC135">
-        <v>0</v>
-      </c>
-      <c r="AD135">
-        <v>0</v>
-      </c>
-      <c r="AE135">
-        <v>0</v>
-      </c>
-      <c r="AF135">
-        <v>0</v>
-      </c>
-      <c r="AG135">
-        <v>0</v>
-      </c>
-      <c r="AH135" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ135">
-        <v>0</v>
-      </c>
-      <c r="AK135">
-        <v>0</v>
-      </c>
-      <c r="AL135">
-        <v>0</v>
-      </c>
-      <c r="AM135">
-        <v>-1</v>
-      </c>
-      <c r="AN135">
-        <v>-1</v>
-      </c>
-      <c r="AO135">
-        <v>-1</v>
-      </c>
-      <c r="AP135">
-        <v>-1</v>
-      </c>
-      <c r="AQ135">
-        <v>0</v>
-      </c>
-      <c r="AR135">
-        <v>0</v>
-      </c>
-      <c r="AS135">
-        <v>0</v>
-      </c>
-      <c r="AT135">
-        <v>0</v>
-      </c>
-      <c r="AU135" t="inlineStr">
         <is>
           <t>2026-09-18 23:00:00</t>
         </is>

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G98">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G99">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G100">

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G68">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G69">

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL11">
         <v>0</v>

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -4882,55 +4882,55 @@
         <v>3.37</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5534,55 +5534,55 @@
         <v>0</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5697,55 +5697,55 @@
         <v>0</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>5.66</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9283,55 +9283,55 @@
         <v>0</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z55">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK55">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>6.79</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T57">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U57">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W57">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z57">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF57">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG57">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK57">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T64">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U64">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V64">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W64">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE64">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF64">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK64">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S66">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T66">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U66">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V66">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W66">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X66">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z66">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC66">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD66">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE66">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF66">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG66">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK66">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S67">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T67">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U67">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V67">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W67">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X67">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y67">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z67">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="AD67">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF67">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG67">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK67">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G68">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O69">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S69">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T69">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U69">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V69">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W69">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X69">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y69">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z69">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="AA69">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AD69">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE69">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF69">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG69">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK69">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -12217,55 +12217,55 @@
         <v>0</v>
       </c>
       <c r="Q73">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R73">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S73">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T73">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U73">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V73">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W73">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X73">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y73">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z73">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA73">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB73">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC73">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD73">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE73">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF73">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG73">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK73">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O76">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q76">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="R76">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="S76">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T76">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U76">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V76">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="W76">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X76">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y76">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z76">
-        <v>0</v>
+        <v>6.03</v>
       </c>
       <c r="AA76">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB76">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AC76">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD76">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE76">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF76">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG76">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK76">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O77">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P77">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q77">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="R77">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S77">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T77">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="U77">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V77">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W77">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X77">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y77">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z77">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA77">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB77">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC77">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD77">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE77">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF77">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG77">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK77">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O78">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P78">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="Q78">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="R78">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S78">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T78">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U78">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="V78">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W78">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y78">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z78">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA78">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AB78">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AC78">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD78">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE78">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF78">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG78">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK78">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q79">
         <v>0</v>
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q80">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R80">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S80">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T80">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U80">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="V80">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W80">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X80">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y80">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z80">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA80">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB80">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AC80">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD80">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE80">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF80">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG80">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK80">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S82">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T82">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U82">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V82">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="W82">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X82">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y82">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z82">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA82">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC82">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD82">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG82">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK82">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O84">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S84">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T84">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U84">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V84">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W84">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X84">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z84">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA84">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD84">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE84">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF84">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG84">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK84">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL84">
         <v>0</v>

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G19">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="O40">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P40">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q40">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="R40">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="S40">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T40">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U40">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V40">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W40">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y40">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z40">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA40">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB40">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AC40">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AD40">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE40">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF40">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG40">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AK40">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>3.75</v>
+        <v>2.41</v>
       </c>
       <c r="O42">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="P42">
-        <v>1.74</v>
+        <v>2.55</v>
       </c>
       <c r="Q42">
-        <v>4</v>
+        <v>3.03</v>
       </c>
       <c r="R42">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="S42">
         <v>1.25</v>
       </c>
       <c r="T42">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="U42">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="V42">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W42">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X42">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
+        <v>1.16</v>
+      </c>
+      <c r="Z42">
+        <v>4.2</v>
+      </c>
+      <c r="AA42">
+        <v>1.65</v>
+      </c>
+      <c r="AB42">
+        <v>2.21</v>
+      </c>
+      <c r="AC42">
+        <v>2.62</v>
+      </c>
+      <c r="AD42">
+        <v>1.46</v>
+      </c>
+      <c r="AE42">
         <v>1.13</v>
-      </c>
-      <c r="Z42">
-        <v>4.5</v>
-      </c>
-      <c r="AA42">
-        <v>1.58</v>
-      </c>
-      <c r="AB42">
-        <v>2.31</v>
-      </c>
-      <c r="AC42">
-        <v>2.35</v>
-      </c>
-      <c r="AD42">
-        <v>1.47</v>
-      </c>
-      <c r="AE42">
-        <v>1.16</v>
       </c>
       <c r="AF42">
         <v>1.55</v>
       </c>
       <c r="AG42">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="AK42">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7816,55 +7816,55 @@
         <v>0</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8142,55 +8142,55 @@
         <v>0</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G60">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G61">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G62">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="O64">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P64">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q64">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="R64">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S64">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T64">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="U64">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="V64">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W64">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y64">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z64">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AA64">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB64">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC64">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AD64">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE64">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF64">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AG64">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK64">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="O65">
-        <v>3.15</v>
+        <v>3.52</v>
       </c>
       <c r="P65">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="Q65">
-        <v>2.81</v>
+        <v>2.71</v>
       </c>
       <c r="R65">
-        <v>2.12</v>
+        <v>2.19</v>
       </c>
       <c r="S65">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="T65">
-        <v>2.62</v>
+        <v>3.22</v>
       </c>
       <c r="U65">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="V65">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="W65">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X65">
         <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="Z65">
-        <v>3.04</v>
+        <v>3.91</v>
       </c>
       <c r="AA65">
+        <v>1.72</v>
+      </c>
+      <c r="AB65">
         <v>2.08</v>
       </c>
-      <c r="AB65">
-        <v>1.72</v>
-      </c>
       <c r="AC65">
-        <v>3.54</v>
+        <v>2.93</v>
       </c>
       <c r="AD65">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="AE65">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF65">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="AG65">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AK65">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.76</v>
+        <v>2.2</v>
       </c>
       <c r="O66">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="P66">
-        <v>4.05</v>
+        <v>3.15</v>
       </c>
       <c r="Q66">
-        <v>2.29</v>
+        <v>2.81</v>
       </c>
       <c r="R66">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="S66">
+        <v>1.43</v>
+      </c>
+      <c r="T66">
+        <v>2.62</v>
+      </c>
+      <c r="U66">
+        <v>3.2</v>
+      </c>
+      <c r="V66">
         <v>1.3</v>
       </c>
-      <c r="T66">
-        <v>3.25</v>
-      </c>
-      <c r="U66">
-        <v>2.4</v>
-      </c>
-      <c r="V66">
-        <v>1.5</v>
-      </c>
       <c r="W66">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X66">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>1.15</v>
+        <v>1.37</v>
       </c>
       <c r="Z66">
-        <v>4.15</v>
+        <v>3.04</v>
       </c>
       <c r="AA66">
-        <v>1.65</v>
+        <v>2.08</v>
       </c>
       <c r="AB66">
-        <v>2.12</v>
+        <v>1.72</v>
       </c>
       <c r="AC66">
-        <v>2.85</v>
+        <v>3.54</v>
       </c>
       <c r="AD66">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="AE66">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AF66">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="AG66">
-        <v>2.15</v>
+        <v>1.86</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AK66">
-        <v>2.1</v>
+        <v>1.63</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.08</v>
+        <v>2.39</v>
       </c>
       <c r="O67">
-        <v>3.62</v>
+        <v>3.34</v>
       </c>
       <c r="P67">
-        <v>3.22</v>
+        <v>2.86</v>
       </c>
       <c r="Q67">
-        <v>2.61</v>
+        <v>2.93</v>
       </c>
       <c r="R67">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="S67">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T67">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="U67">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="V67">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="W67">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X67">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y67">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z67">
-        <v>3.62</v>
+        <v>3.84</v>
       </c>
       <c r="AA67">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AB67">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="AC67">
-        <v>3.26</v>
+        <v>2.71</v>
       </c>
       <c r="AD67">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE67">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF67">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AG67">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK67">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O68">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK68">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="O69">
-        <v>3.52</v>
+        <v>3.62</v>
       </c>
       <c r="P69">
-        <v>3.05</v>
+        <v>3.22</v>
       </c>
       <c r="Q69">
-        <v>2.71</v>
+        <v>2.61</v>
       </c>
       <c r="R69">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="S69">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T69">
-        <v>3.22</v>
+        <v>3.04</v>
       </c>
       <c r="U69">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="V69">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W69">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X69">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y69">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z69">
-        <v>3.91</v>
+        <v>3.62</v>
       </c>
       <c r="AA69">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AB69">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AC69">
-        <v>2.93</v>
+        <v>3.26</v>
       </c>
       <c r="AD69">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="AE69">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF69">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG69">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK69">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="O77">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="P77">
-        <v>5</v>
+        <v>4.17</v>
       </c>
       <c r="Q77">
-        <v>2.03</v>
+        <v>2.13</v>
       </c>
       <c r="R77">
         <v>2.49</v>
       </c>
       <c r="S77">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T77">
-        <v>3.78</v>
+        <v>3.68</v>
       </c>
       <c r="U77">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="V77">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="W77">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X77">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y77">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z77">
-        <v>5.45</v>
+        <v>5.3</v>
       </c>
       <c r="AA77">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="AB77">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="AC77">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="AD77">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AE77">
         <v>1.26</v>
       </c>
       <c r="AF77">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AG77">
-        <v>2.38</v>
+        <v>2.53</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK77">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.67</v>
+        <v>2.92</v>
       </c>
       <c r="O78">
-        <v>4.25</v>
+        <v>3.65</v>
       </c>
       <c r="P78">
-        <v>4.17</v>
+        <v>2.16</v>
       </c>
       <c r="Q78">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="R78">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="S78">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="T78">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="U78">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="V78">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="W78">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X78">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y78">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Z78">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA78">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AB78">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AC78">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD78">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE78">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AF78">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG78">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK78">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="O79">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="P79">
-        <v>2.16</v>
+        <v>1.99</v>
       </c>
       <c r="Q79">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R79">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S79">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T79">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U79">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="V79">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W79">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z79">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA79">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AC79">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD79">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE79">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF79">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG79">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK79">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="O80">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="P80">
-        <v>1.99</v>
+        <v>2.44</v>
       </c>
       <c r="Q80">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R80">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="S80">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="T80">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="U80">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="V80">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="W80">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X80">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y80">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z80">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA80">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB80">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AC80">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD80">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE80">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF80">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG80">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK80">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="O81">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="P81">
-        <v>2.44</v>
+        <v>2.11</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S81">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T81">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U81">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V81">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="W81">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X81">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y81">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z81">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA81">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC81">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD81">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG81">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK81">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.95</v>
+        <v>2.55</v>
       </c>
       <c r="O82">
-        <v>3.68</v>
+        <v>3.75</v>
       </c>
       <c r="P82">
-        <v>2.11</v>
+        <v>2.32</v>
       </c>
       <c r="Q82">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R82">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S82">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T82">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U82">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="V82">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="W82">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X82">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y82">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z82">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA82">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB82">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AC82">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD82">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE82">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AF82">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG82">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK82">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.55</v>
+        <v>1.57</v>
       </c>
       <c r="O83">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="P83">
-        <v>2.32</v>
+        <v>5</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S83">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T83">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="U83">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V83">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W83">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z83">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB83">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC83">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD83">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG83">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK83">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O94">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q94">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="R94">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S94">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T94">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U94">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V94">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W94">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X94">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y94">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z94">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA94">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB94">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC94">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AD94">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE94">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF94">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG94">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK94">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O95">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P95">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q95">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R95">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S95">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T95">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U95">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V95">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W95">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X95">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y95">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z95">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA95">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB95">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AC95">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AD95">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE95">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF95">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG95">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK95">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O96">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P96">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="Q96">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R96">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S96">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T96">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U96">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V96">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W96">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X96">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y96">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z96">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA96">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB96">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC96">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD96">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE96">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF96">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG96">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK96">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O97">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="Q97">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R97">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S97">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T97">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U97">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="V97">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W97">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X97">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y97">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z97">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AA97">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB97">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC97">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AD97">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE97">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF97">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG97">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK97">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O98">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q98">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R98">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S98">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T98">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U98">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V98">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W98">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y98">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z98">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA98">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB98">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC98">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD98">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE98">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF98">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG98">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK98">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O99">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P99">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q99">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R99">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S99">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T99">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U99">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V99">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W99">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y99">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z99">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA99">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB99">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC99">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD99">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE99">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF99">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG99">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK99">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O100">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P100">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q100">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="R100">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S100">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T100">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U100">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V100">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W100">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X100">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y100">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z100">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AA100">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB100">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC100">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD100">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE100">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF100">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG100">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK100">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O105">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P105">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q105">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="R105">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S105">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T105">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U105">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="V105">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W105">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X105">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y105">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z105">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AA105">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB105">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC105">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AD105">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE105">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF105">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG105">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK105">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O106">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P106">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="Q106">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="R106">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S106">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T106">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="U106">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="V106">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W106">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X106">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z106">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA106">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB106">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AC106">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD106">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE106">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF106">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG106">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK106">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AL106">
         <v>0</v>

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,80 +11067,80 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="O66">
-        <v>3.15</v>
+        <v>3.34</v>
       </c>
       <c r="P66">
-        <v>3.15</v>
+        <v>2.86</v>
       </c>
       <c r="Q66">
-        <v>2.81</v>
+        <v>2.93</v>
       </c>
       <c r="R66">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="S66">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="T66">
-        <v>2.62</v>
+        <v>3.02</v>
       </c>
       <c r="U66">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="V66">
+        <v>1.49</v>
+      </c>
+      <c r="W66">
+        <v>1.1</v>
+      </c>
+      <c r="X66">
+        <v>1</v>
+      </c>
+      <c r="Y66">
+        <v>1.25</v>
+      </c>
+      <c r="Z66">
+        <v>3.84</v>
+      </c>
+      <c r="AA66">
+        <v>1.76</v>
+      </c>
+      <c r="AB66">
+        <v>1.97</v>
+      </c>
+      <c r="AC66">
+        <v>2.71</v>
+      </c>
+      <c r="AD66">
+        <v>1.36</v>
+      </c>
+      <c r="AE66">
+        <v>1.14</v>
+      </c>
+      <c r="AF66">
+        <v>1.59</v>
+      </c>
+      <c r="AG66">
+        <v>2.21</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ66">
         <v>1.3</v>
       </c>
-      <c r="W66">
-        <v>1.07</v>
-      </c>
-      <c r="X66">
-        <v>1.02</v>
-      </c>
-      <c r="Y66">
-        <v>1.37</v>
-      </c>
-      <c r="Z66">
-        <v>3.04</v>
-      </c>
-      <c r="AA66">
-        <v>2.08</v>
-      </c>
-      <c r="AB66">
-        <v>1.72</v>
-      </c>
-      <c r="AC66">
-        <v>3.54</v>
-      </c>
-      <c r="AD66">
-        <v>1.22</v>
-      </c>
-      <c r="AE66">
-        <v>1.05</v>
-      </c>
-      <c r="AF66">
-        <v>1.82</v>
-      </c>
-      <c r="AG66">
-        <v>1.86</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ66">
-        <v>1.31</v>
-      </c>
       <c r="AK66">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,80 +11230,80 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.39</v>
+        <v>1.76</v>
       </c>
       <c r="O67">
-        <v>3.34</v>
+        <v>3.75</v>
       </c>
       <c r="P67">
-        <v>2.86</v>
+        <v>4.05</v>
       </c>
       <c r="Q67">
-        <v>2.93</v>
+        <v>2.29</v>
       </c>
       <c r="R67">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S67">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T67">
-        <v>3.02</v>
+        <v>3.25</v>
       </c>
       <c r="U67">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="V67">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W67">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X67">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y67">
+        <v>1.15</v>
+      </c>
+      <c r="Z67">
+        <v>4.15</v>
+      </c>
+      <c r="AA67">
+        <v>1.65</v>
+      </c>
+      <c r="AB67">
+        <v>2.12</v>
+      </c>
+      <c r="AC67">
+        <v>2.85</v>
+      </c>
+      <c r="AD67">
+        <v>1.41</v>
+      </c>
+      <c r="AE67">
+        <v>1.12</v>
+      </c>
+      <c r="AF67">
+        <v>1.65</v>
+      </c>
+      <c r="AG67">
+        <v>2.15</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ67">
         <v>1.25</v>
       </c>
-      <c r="Z67">
-        <v>3.84</v>
-      </c>
-      <c r="AA67">
-        <v>1.76</v>
-      </c>
-      <c r="AB67">
-        <v>1.97</v>
-      </c>
-      <c r="AC67">
-        <v>2.71</v>
-      </c>
-      <c r="AD67">
-        <v>1.36</v>
-      </c>
-      <c r="AE67">
-        <v>1.14</v>
-      </c>
-      <c r="AF67">
-        <v>1.59</v>
-      </c>
-      <c r="AG67">
-        <v>2.21</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ67">
-        <v>1.3</v>
-      </c>
       <c r="AK67">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.76</v>
+        <v>2.08</v>
       </c>
       <c r="O68">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="P68">
-        <v>4.05</v>
+        <v>3.22</v>
       </c>
       <c r="Q68">
-        <v>2.29</v>
+        <v>2.61</v>
       </c>
       <c r="R68">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="S68">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T68">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="U68">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="V68">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W68">
+        <v>1.07</v>
+      </c>
+      <c r="X68">
+        <v>1.03</v>
+      </c>
+      <c r="Y68">
+        <v>1.21</v>
+      </c>
+      <c r="Z68">
+        <v>3.62</v>
+      </c>
+      <c r="AA68">
+        <v>1.9</v>
+      </c>
+      <c r="AB68">
+        <v>1.92</v>
+      </c>
+      <c r="AC68">
+        <v>3.26</v>
+      </c>
+      <c r="AD68">
+        <v>1.32</v>
+      </c>
+      <c r="AE68">
         <v>1.08</v>
-      </c>
-      <c r="X68">
-        <v>1.01</v>
-      </c>
-      <c r="Y68">
-        <v>1.15</v>
-      </c>
-      <c r="Z68">
-        <v>4.15</v>
-      </c>
-      <c r="AA68">
-        <v>1.65</v>
-      </c>
-      <c r="AB68">
-        <v>2.12</v>
-      </c>
-      <c r="AC68">
-        <v>2.85</v>
-      </c>
-      <c r="AD68">
-        <v>1.41</v>
-      </c>
-      <c r="AE68">
-        <v>1.12</v>
       </c>
       <c r="AF68">
         <v>1.65</v>
       </c>
       <c r="AG68">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK68">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="O69">
-        <v>3.62</v>
+        <v>3.15</v>
       </c>
       <c r="P69">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="Q69">
-        <v>2.61</v>
+        <v>2.81</v>
       </c>
       <c r="R69">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="S69">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="T69">
-        <v>3.04</v>
+        <v>2.62</v>
       </c>
       <c r="U69">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="V69">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W69">
         <v>1.07</v>
       </c>
       <c r="X69">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y69">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="Z69">
-        <v>3.62</v>
+        <v>3.04</v>
       </c>
       <c r="AA69">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="AB69">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="AC69">
-        <v>3.26</v>
+        <v>3.54</v>
       </c>
       <c r="AD69">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AE69">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF69">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="AG69">
-        <v>2.11</v>
+        <v>1.86</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AK69">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AL69">
         <v>0</v>

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU128"/>
+  <dimension ref="A1:AU127"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X60">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE60">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF60">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK60">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T61">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U61">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V61">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W61">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z61">
-        <v>0</v>
+        <v>6.13</v>
       </c>
       <c r="AA61">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD61">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE61">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG61">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK61">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T62">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W62">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X62">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z62">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK62">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O85">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q85">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R85">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S85">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T85">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="U85">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V85">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W85">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X85">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y85">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z85">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA85">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB85">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AC85">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD85">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE85">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF85">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG85">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK85">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="O96">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="P96">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Q96">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="R96">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="S96">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T96">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U96">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V96">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W96">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X96">
         <v>1.02</v>
       </c>
       <c r="Y96">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z96">
-        <v>4.75</v>
+        <v>4.85</v>
       </c>
       <c r="AA96">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AB96">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC96">
-        <v>2.19</v>
+        <v>2.36</v>
       </c>
       <c r="AD96">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="AE96">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AF96">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AG96">
-        <v>2.21</v>
+        <v>2.04</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AK96">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,80 +16120,80 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.37</v>
+        <v>2.15</v>
       </c>
       <c r="O97">
-        <v>5</v>
+        <v>3.35</v>
       </c>
       <c r="P97">
-        <v>5.8</v>
+        <v>3.2</v>
       </c>
       <c r="Q97">
-        <v>1.83</v>
+        <v>2.78</v>
       </c>
       <c r="R97">
-        <v>2.6</v>
+        <v>2.24</v>
       </c>
       <c r="S97">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="T97">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="U97">
-        <v>2.24</v>
+        <v>2.75</v>
       </c>
       <c r="V97">
+        <v>1.4</v>
+      </c>
+      <c r="W97">
+        <v>1.08</v>
+      </c>
+      <c r="X97">
+        <v>1</v>
+      </c>
+      <c r="Y97">
+        <v>1.24</v>
+      </c>
+      <c r="Z97">
+        <v>3.34</v>
+      </c>
+      <c r="AA97">
+        <v>1.85</v>
+      </c>
+      <c r="AB97">
+        <v>1.85</v>
+      </c>
+      <c r="AC97">
+        <v>3.14</v>
+      </c>
+      <c r="AD97">
+        <v>1.3</v>
+      </c>
+      <c r="AE97">
+        <v>1.08</v>
+      </c>
+      <c r="AF97">
+        <v>1.67</v>
+      </c>
+      <c r="AG97">
+        <v>2.05</v>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ97">
+        <v>1.33</v>
+      </c>
+      <c r="AK97">
         <v>1.57</v>
-      </c>
-      <c r="W97">
-        <v>1.14</v>
-      </c>
-      <c r="X97">
-        <v>1.02</v>
-      </c>
-      <c r="Y97">
-        <v>1.11</v>
-      </c>
-      <c r="Z97">
-        <v>4.85</v>
-      </c>
-      <c r="AA97">
-        <v>1.56</v>
-      </c>
-      <c r="AB97">
-        <v>2.3</v>
-      </c>
-      <c r="AC97">
-        <v>2.36</v>
-      </c>
-      <c r="AD97">
-        <v>1.52</v>
-      </c>
-      <c r="AE97">
-        <v>1.21</v>
-      </c>
-      <c r="AF97">
-        <v>1.66</v>
-      </c>
-      <c r="AG97">
-        <v>2.04</v>
-      </c>
-      <c r="AH97" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI97" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ97">
-        <v>1.11</v>
-      </c>
-      <c r="AK97">
-        <v>2.6</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="O98">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P98">
+        <v>3.05</v>
+      </c>
+      <c r="Q98">
+        <v>2.7</v>
+      </c>
+      <c r="R98">
+        <v>2.3</v>
+      </c>
+      <c r="S98">
+        <v>1.3</v>
+      </c>
+      <c r="T98">
         <v>3.2</v>
       </c>
-      <c r="Q98">
-        <v>2.78</v>
-      </c>
-      <c r="R98">
-        <v>2.24</v>
-      </c>
-      <c r="S98">
-        <v>1.35</v>
-      </c>
-      <c r="T98">
-        <v>3.05</v>
-      </c>
       <c r="U98">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="V98">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W98">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X98">
         <v>1</v>
       </c>
       <c r="Y98">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z98">
-        <v>3.34</v>
+        <v>3.72</v>
       </c>
       <c r="AA98">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AB98">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="AC98">
-        <v>3.14</v>
+        <v>2.81</v>
       </c>
       <c r="AD98">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE98">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF98">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG98">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK98">
         <v>1.57</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.26</v>
+        <v>3.95</v>
       </c>
       <c r="O99">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="P99">
-        <v>3.05</v>
+        <v>1.79</v>
       </c>
       <c r="Q99">
-        <v>2.7</v>
+        <v>4.57</v>
       </c>
       <c r="R99">
         <v>2.3</v>
       </c>
       <c r="S99">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T99">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="U99">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="V99">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W99">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X99">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y99">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z99">
-        <v>3.72</v>
+        <v>3.76</v>
       </c>
       <c r="AA99">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AB99">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="AC99">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="AD99">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AE99">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF99">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG99">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK99">
-        <v>1.57</v>
+        <v>1.17</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>3.95</v>
+        <v>1.47</v>
       </c>
       <c r="O100">
+        <v>4.1</v>
+      </c>
+      <c r="P100">
+        <v>5.7</v>
+      </c>
+      <c r="Q100">
+        <v>2</v>
+      </c>
+      <c r="R100">
+        <v>2.35</v>
+      </c>
+      <c r="S100">
+        <v>1.22</v>
+      </c>
+      <c r="T100">
         <v>3.75</v>
       </c>
-      <c r="P100">
-        <v>1.79</v>
-      </c>
-      <c r="Q100">
-        <v>4.57</v>
-      </c>
-      <c r="R100">
-        <v>2.3</v>
-      </c>
-      <c r="S100">
-        <v>1.33</v>
-      </c>
-      <c r="T100">
-        <v>3.18</v>
-      </c>
       <c r="U100">
-        <v>2.66</v>
+        <v>2.2</v>
       </c>
       <c r="V100">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="W100">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="X100">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y100">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="Z100">
-        <v>3.76</v>
+        <v>4.75</v>
       </c>
       <c r="AA100">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AB100">
-        <v>1.96</v>
+        <v>2.35</v>
       </c>
       <c r="AC100">
-        <v>2.83</v>
+        <v>2.19</v>
       </c>
       <c r="AD100">
-        <v>1.37</v>
+        <v>1.63</v>
       </c>
       <c r="AE100">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AF100">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AG100">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK100">
-        <v>1.17</v>
+        <v>2.4</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G125">
@@ -20805,22 +20805,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G126">
@@ -20963,12 +20963,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G127">
@@ -21113,169 +21113,6 @@
         <v>0</v>
       </c>
       <c r="AU127" t="inlineStr">
-        <is>
-          <t>2026-09-18 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>San Diego Wave</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Kansas City</t>
-        </is>
-      </c>
-      <c r="G128">
-        <v>0</v>
-      </c>
-      <c r="H128">
-        <v>0</v>
-      </c>
-      <c r="I128">
-        <v>0</v>
-      </c>
-      <c r="J128">
-        <v>0</v>
-      </c>
-      <c r="K128">
-        <v>0</v>
-      </c>
-      <c r="L128">
-        <v>0</v>
-      </c>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N128">
-        <v>0</v>
-      </c>
-      <c r="O128">
-        <v>0</v>
-      </c>
-      <c r="P128">
-        <v>0</v>
-      </c>
-      <c r="Q128">
-        <v>0</v>
-      </c>
-      <c r="R128">
-        <v>0</v>
-      </c>
-      <c r="S128">
-        <v>0</v>
-      </c>
-      <c r="T128">
-        <v>0</v>
-      </c>
-      <c r="U128">
-        <v>0</v>
-      </c>
-      <c r="V128">
-        <v>0</v>
-      </c>
-      <c r="W128">
-        <v>0</v>
-      </c>
-      <c r="X128">
-        <v>0</v>
-      </c>
-      <c r="Y128">
-        <v>0</v>
-      </c>
-      <c r="Z128">
-        <v>0</v>
-      </c>
-      <c r="AA128">
-        <v>0</v>
-      </c>
-      <c r="AB128">
-        <v>0</v>
-      </c>
-      <c r="AC128">
-        <v>0</v>
-      </c>
-      <c r="AD128">
-        <v>0</v>
-      </c>
-      <c r="AE128">
-        <v>0</v>
-      </c>
-      <c r="AF128">
-        <v>0</v>
-      </c>
-      <c r="AG128">
-        <v>0</v>
-      </c>
-      <c r="AH128" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI128" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ128">
-        <v>0</v>
-      </c>
-      <c r="AK128">
-        <v>0</v>
-      </c>
-      <c r="AL128">
-        <v>0</v>
-      </c>
-      <c r="AM128">
-        <v>-1</v>
-      </c>
-      <c r="AN128">
-        <v>-1</v>
-      </c>
-      <c r="AO128">
-        <v>-1</v>
-      </c>
-      <c r="AP128">
-        <v>-1</v>
-      </c>
-      <c r="AQ128">
-        <v>0</v>
-      </c>
-      <c r="AR128">
-        <v>0</v>
-      </c>
-      <c r="AS128">
-        <v>0</v>
-      </c>
-      <c r="AT128">
-        <v>0</v>
-      </c>
-      <c r="AU128" t="inlineStr">
         <is>
           <t>2026-09-18 23:00:00</t>
         </is>

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -5860,25 +5860,25 @@
         <v>0</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X34">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>3.75</v>
+        <v>2.41</v>
       </c>
       <c r="O41">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="P41">
-        <v>1.74</v>
+        <v>2.55</v>
       </c>
       <c r="Q41">
-        <v>4</v>
+        <v>3.03</v>
       </c>
       <c r="R41">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="S41">
         <v>1.25</v>
       </c>
       <c r="T41">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="U41">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="V41">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W41">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X41">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
+        <v>1.16</v>
+      </c>
+      <c r="Z41">
+        <v>4.2</v>
+      </c>
+      <c r="AA41">
+        <v>1.65</v>
+      </c>
+      <c r="AB41">
+        <v>2.21</v>
+      </c>
+      <c r="AC41">
+        <v>2.62</v>
+      </c>
+      <c r="AD41">
+        <v>1.46</v>
+      </c>
+      <c r="AE41">
         <v>1.13</v>
-      </c>
-      <c r="Z41">
-        <v>4.5</v>
-      </c>
-      <c r="AA41">
-        <v>1.58</v>
-      </c>
-      <c r="AB41">
-        <v>2.31</v>
-      </c>
-      <c r="AC41">
-        <v>2.35</v>
-      </c>
-      <c r="AD41">
-        <v>1.47</v>
-      </c>
-      <c r="AE41">
-        <v>1.16</v>
       </c>
       <c r="AF41">
         <v>1.55</v>
       </c>
       <c r="AG41">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="AK41">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="O42">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P42">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q42">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="R42">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="S42">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T42">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U42">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V42">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W42">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X42">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y42">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z42">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA42">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB42">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AC42">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AD42">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE42">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF42">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG42">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AK42">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q46">
         <v>2.88</v>
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,31 +10089,31 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.89</v>
+        <v>2.35</v>
       </c>
       <c r="O60">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="P60">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q60">
-        <v>2.3</v>
+        <v>2.78</v>
       </c>
       <c r="R60">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="S60">
         <v>1.2</v>
       </c>
       <c r="T60">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="U60">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="V60">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="W60">
         <v>1.2</v>
@@ -10122,31 +10122,31 @@
         <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Z60">
-        <v>6.25</v>
+        <v>6.13</v>
       </c>
       <c r="AA60">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AB60">
         <v>2.86</v>
       </c>
       <c r="AC60">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AD60">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AE60">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AF60">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AG60">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK60">
-        <v>1.82</v>
+        <v>1.46</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.35</v>
+        <v>1.64</v>
       </c>
       <c r="O61">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="P61">
-        <v>2.4</v>
+        <v>4.4</v>
       </c>
       <c r="Q61">
-        <v>2.78</v>
+        <v>2.16</v>
       </c>
       <c r="R61">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="S61">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T61">
-        <v>4.33</v>
+        <v>3.28</v>
       </c>
       <c r="U61">
-        <v>2.04</v>
+        <v>2.28</v>
       </c>
       <c r="V61">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="W61">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X61">
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z61">
-        <v>6.13</v>
+        <v>4.61</v>
       </c>
       <c r="AA61">
-        <v>1.35</v>
+        <v>1.58</v>
       </c>
       <c r="AB61">
-        <v>2.86</v>
+        <v>2.32</v>
       </c>
       <c r="AC61">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AD61">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="AE61">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AF61">
-        <v>1.34</v>
+        <v>1.57</v>
       </c>
       <c r="AG61">
-        <v>2.95</v>
+        <v>2.25</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK61">
-        <v>1.46</v>
+        <v>1.99</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,80 +10415,80 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.64</v>
+        <v>1.89</v>
       </c>
       <c r="O62">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P62">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q62">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="R62">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="S62">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T62">
-        <v>3.28</v>
+        <v>4.5</v>
       </c>
       <c r="U62">
-        <v>2.28</v>
+        <v>1.99</v>
       </c>
       <c r="V62">
-        <v>1.56</v>
+        <v>1.72</v>
       </c>
       <c r="W62">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="Z62">
-        <v>4.61</v>
+        <v>6.25</v>
       </c>
       <c r="AA62">
-        <v>1.58</v>
+        <v>1.33</v>
       </c>
       <c r="AB62">
-        <v>2.32</v>
+        <v>2.86</v>
       </c>
       <c r="AC62">
-        <v>2.33</v>
+        <v>1.94</v>
       </c>
       <c r="AD62">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="AE62">
+        <v>1.33</v>
+      </c>
+      <c r="AF62">
+        <v>1.36</v>
+      </c>
+      <c r="AG62">
+        <v>2.85</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ62">
         <v>1.17</v>
       </c>
-      <c r="AF62">
-        <v>1.57</v>
-      </c>
-      <c r="AG62">
-        <v>2.25</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ62">
-        <v>1.25</v>
-      </c>
       <c r="AK62">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -11728,55 +11728,55 @@
         <v>1.84</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S70">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T70">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U70">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V70">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W70">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y70">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z70">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AC70">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD70">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE70">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF70">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG70">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK70">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -12543,55 +12543,55 @@
         <v>3.82</v>
       </c>
       <c r="Q75">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="R75">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S75">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T75">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U75">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V75">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W75">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X75">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y75">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z75">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA75">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC75">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD75">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE75">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF75">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG75">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK75">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O86">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S86">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T86">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U86">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V86">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W86">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X86">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z86">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD86">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG86">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK86">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q87">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R87">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S87">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T87">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U87">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V87">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W87">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X87">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z87">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="AA87">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB87">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC87">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD87">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE87">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF87">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG87">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK87">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14662,55 +14662,55 @@
         <v>0</v>
       </c>
       <c r="Q88">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="R88">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S88">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T88">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="U88">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V88">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W88">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X88">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y88">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z88">
-        <v>0</v>
+        <v>5.29</v>
       </c>
       <c r="AA88">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB88">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC88">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD88">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE88">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF88">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG88">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK88">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O89">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q89">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R89">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S89">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T89">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U89">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V89">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W89">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y89">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z89">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA89">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB89">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC89">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD89">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE89">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF89">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG89">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK89">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S90">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T90">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="U90">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V90">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W90">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X90">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y90">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z90">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA90">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB90">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC90">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD90">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE90">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF90">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG90">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK90">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="O91">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Q91">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="R91">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="S91">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="T91">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="U91">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V91">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="W91">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y91">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z91">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AA91">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB91">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AC91">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD91">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AE91">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF91">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG91">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK91">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O92">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q92">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R92">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S92">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T92">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U92">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V92">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W92">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y92">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z92">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA92">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB92">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC92">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD92">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE92">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF92">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG92">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK92">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O93">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P93">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q93">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R93">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S93">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T93">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="U93">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V93">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W93">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X93">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y93">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z93">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA93">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB93">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AC93">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD93">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE93">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF93">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG93">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK93">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O101">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P101">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q101">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R101">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S101">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T101">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U101">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="V101">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W101">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X101">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y101">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z101">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA101">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB101">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC101">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="AD101">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE101">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF101">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG101">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK101">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O102">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P102">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q103">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R103">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S103">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T103">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U103">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V103">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W103">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X103">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y103">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z103">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA103">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB103">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AC103">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD103">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE103">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF103">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG103">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AK103">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O107">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P107">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q107">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R107">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S107">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T107">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U107">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V107">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W107">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X107">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y107">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z107">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA107">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB107">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC107">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD107">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE107">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF107">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG107">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK107">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O108">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P108">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="Q108">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R108">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S108">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T108">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U108">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V108">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W108">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X108">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y108">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z108">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AA108">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB108">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC108">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AD108">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE108">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF108">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG108">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK108">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O114">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P114">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q114">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R114">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S114">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T114">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U114">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="V114">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W114">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X114">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y114">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z114">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA114">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB114">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC114">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD114">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE114">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF114">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG114">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AK114">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL114">
         <v>0</v>

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU127"/>
+  <dimension ref="A1:AU120"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -635,16 +635,16 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O2">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P2">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="Q2">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="R2">
         <v>1.99</v>
@@ -656,7 +656,7 @@
         <v>2.56</v>
       </c>
       <c r="U2">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="V2">
         <v>1.28</v>
@@ -668,7 +668,7 @@
         <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="Z2">
         <v>2.78</v>
@@ -677,7 +677,7 @@
         <v>2.17</v>
       </c>
       <c r="AB2">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AC2">
         <v>4.05</v>
@@ -686,13 +686,13 @@
         <v>1.16</v>
       </c>
       <c r="AE2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF2">
         <v>1.91</v>
       </c>
       <c r="AG2">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.66</v>
+        <v>1.33</v>
       </c>
       <c r="AK2">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.67</v>
+        <v>3.2</v>
       </c>
       <c r="O77">
-        <v>4.25</v>
+        <v>3.85</v>
       </c>
       <c r="P77">
-        <v>4.17</v>
+        <v>1.99</v>
       </c>
       <c r="Q77">
-        <v>2.13</v>
+        <v>3.51</v>
       </c>
       <c r="R77">
-        <v>2.49</v>
+        <v>2.66</v>
       </c>
       <c r="S77">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="T77">
-        <v>3.68</v>
+        <v>3.9</v>
       </c>
       <c r="U77">
-        <v>2.09</v>
+        <v>1.94</v>
       </c>
       <c r="V77">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="W77">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="X77">
         <v>1.01</v>
       </c>
       <c r="Y77">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z77">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="AA77">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AB77">
-        <v>2.59</v>
+        <v>2.83</v>
       </c>
       <c r="AC77">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="AD77">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AE77">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AF77">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AG77">
-        <v>2.53</v>
+        <v>2.9</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK77">
-        <v>2.1</v>
+        <v>1.31</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.92</v>
+        <v>2.5</v>
       </c>
       <c r="O78">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P78">
-        <v>2.16</v>
+        <v>2.44</v>
       </c>
       <c r="Q78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="O79">
-        <v>3.85</v>
+        <v>3.68</v>
       </c>
       <c r="P79">
-        <v>1.99</v>
+        <v>2.11</v>
       </c>
       <c r="Q79">
-        <v>3.51</v>
+        <v>3.1</v>
       </c>
       <c r="R79">
-        <v>2.66</v>
+        <v>2.33</v>
       </c>
       <c r="S79">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T79">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U79">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="V79">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="W79">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X79">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y79">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z79">
-        <v>7</v>
+        <v>5.3</v>
       </c>
       <c r="AA79">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AB79">
-        <v>2.83</v>
+        <v>2.6</v>
       </c>
       <c r="AC79">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="AD79">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AE79">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AF79">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG79">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK79">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="O80">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P80">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.95</v>
+        <v>1.57</v>
       </c>
       <c r="O81">
-        <v>3.68</v>
+        <v>4.4</v>
       </c>
       <c r="P81">
-        <v>2.11</v>
+        <v>5</v>
       </c>
       <c r="Q81">
-        <v>3.1</v>
+        <v>2.03</v>
       </c>
       <c r="R81">
-        <v>2.33</v>
+        <v>2.49</v>
       </c>
       <c r="S81">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T81">
-        <v>4</v>
+        <v>3.78</v>
       </c>
       <c r="U81">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="V81">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="W81">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X81">
         <v>1.02</v>
       </c>
       <c r="Y81">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z81">
-        <v>5.3</v>
+        <v>5.45</v>
       </c>
       <c r="AA81">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB81">
         <v>2.6</v>
       </c>
       <c r="AC81">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AD81">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AE81">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AF81">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AG81">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AK81">
-        <v>1.34</v>
+        <v>2.31</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="O82">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="P82">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S82">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T82">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U82">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V82">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W82">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X82">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z82">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA82">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC82">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD82">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG82">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK82">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="O83">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="P83">
-        <v>5</v>
+        <v>4.17</v>
       </c>
       <c r="Q83">
-        <v>2.03</v>
+        <v>2.13</v>
       </c>
       <c r="R83">
         <v>2.49</v>
       </c>
       <c r="S83">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T83">
-        <v>3.78</v>
+        <v>3.68</v>
       </c>
       <c r="U83">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="V83">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="W83">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X83">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z83">
-        <v>5.45</v>
+        <v>5.3</v>
       </c>
       <c r="AA83">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="AB83">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="AC83">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="AD83">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AE83">
         <v>1.26</v>
       </c>
       <c r="AF83">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AG83">
-        <v>2.38</v>
+        <v>2.53</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK83">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.63</v>
+        <v>2.92</v>
       </c>
       <c r="O84">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="P84">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="Q84">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R84">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S84">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T84">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U84">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V84">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W84">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X84">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y84">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z84">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA84">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB84">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AC84">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD84">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AE84">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF84">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG84">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK84">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -19501,7 +19501,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G118">
@@ -19664,22 +19664,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G119">
@@ -19822,27 +19822,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G120">
@@ -19972,1147 +19972,6 @@
         <v>0</v>
       </c>
       <c r="AU120" t="inlineStr">
-        <is>
-          <t>2026-09-18 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Serbia SuperLiga</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Železničar Pančevo</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>Čukarički</t>
-        </is>
-      </c>
-      <c r="G121">
-        <v>0</v>
-      </c>
-      <c r="H121">
-        <v>0</v>
-      </c>
-      <c r="I121">
-        <v>0</v>
-      </c>
-      <c r="J121">
-        <v>0</v>
-      </c>
-      <c r="K121">
-        <v>0</v>
-      </c>
-      <c r="L121">
-        <v>0</v>
-      </c>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N121">
-        <v>0</v>
-      </c>
-      <c r="O121">
-        <v>0</v>
-      </c>
-      <c r="P121">
-        <v>0</v>
-      </c>
-      <c r="Q121">
-        <v>0</v>
-      </c>
-      <c r="R121">
-        <v>0</v>
-      </c>
-      <c r="S121">
-        <v>0</v>
-      </c>
-      <c r="T121">
-        <v>0</v>
-      </c>
-      <c r="U121">
-        <v>0</v>
-      </c>
-      <c r="V121">
-        <v>0</v>
-      </c>
-      <c r="W121">
-        <v>0</v>
-      </c>
-      <c r="X121">
-        <v>0</v>
-      </c>
-      <c r="Y121">
-        <v>0</v>
-      </c>
-      <c r="Z121">
-        <v>0</v>
-      </c>
-      <c r="AA121">
-        <v>0</v>
-      </c>
-      <c r="AB121">
-        <v>0</v>
-      </c>
-      <c r="AC121">
-        <v>0</v>
-      </c>
-      <c r="AD121">
-        <v>0</v>
-      </c>
-      <c r="AE121">
-        <v>0</v>
-      </c>
-      <c r="AF121">
-        <v>0</v>
-      </c>
-      <c r="AG121">
-        <v>0</v>
-      </c>
-      <c r="AH121" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI121" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ121">
-        <v>0</v>
-      </c>
-      <c r="AK121">
-        <v>0</v>
-      </c>
-      <c r="AL121">
-        <v>0</v>
-      </c>
-      <c r="AM121">
-        <v>-1</v>
-      </c>
-      <c r="AN121">
-        <v>-1</v>
-      </c>
-      <c r="AO121">
-        <v>-1</v>
-      </c>
-      <c r="AP121">
-        <v>-1</v>
-      </c>
-      <c r="AQ121">
-        <v>0</v>
-      </c>
-      <c r="AR121">
-        <v>0</v>
-      </c>
-      <c r="AS121">
-        <v>0</v>
-      </c>
-      <c r="AT121">
-        <v>0</v>
-      </c>
-      <c r="AU121" t="inlineStr">
-        <is>
-          <t>2026-09-18 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Serbia SuperLiga</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>OFK Beograd</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>Radnički Kragujevac</t>
-        </is>
-      </c>
-      <c r="G122">
-        <v>0</v>
-      </c>
-      <c r="H122">
-        <v>0</v>
-      </c>
-      <c r="I122">
-        <v>0</v>
-      </c>
-      <c r="J122">
-        <v>0</v>
-      </c>
-      <c r="K122">
-        <v>0</v>
-      </c>
-      <c r="L122">
-        <v>0</v>
-      </c>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N122">
-        <v>0</v>
-      </c>
-      <c r="O122">
-        <v>0</v>
-      </c>
-      <c r="P122">
-        <v>0</v>
-      </c>
-      <c r="Q122">
-        <v>0</v>
-      </c>
-      <c r="R122">
-        <v>0</v>
-      </c>
-      <c r="S122">
-        <v>0</v>
-      </c>
-      <c r="T122">
-        <v>0</v>
-      </c>
-      <c r="U122">
-        <v>0</v>
-      </c>
-      <c r="V122">
-        <v>0</v>
-      </c>
-      <c r="W122">
-        <v>0</v>
-      </c>
-      <c r="X122">
-        <v>0</v>
-      </c>
-      <c r="Y122">
-        <v>0</v>
-      </c>
-      <c r="Z122">
-        <v>0</v>
-      </c>
-      <c r="AA122">
-        <v>0</v>
-      </c>
-      <c r="AB122">
-        <v>0</v>
-      </c>
-      <c r="AC122">
-        <v>0</v>
-      </c>
-      <c r="AD122">
-        <v>0</v>
-      </c>
-      <c r="AE122">
-        <v>0</v>
-      </c>
-      <c r="AF122">
-        <v>0</v>
-      </c>
-      <c r="AG122">
-        <v>0</v>
-      </c>
-      <c r="AH122" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI122" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ122">
-        <v>0</v>
-      </c>
-      <c r="AK122">
-        <v>0</v>
-      </c>
-      <c r="AL122">
-        <v>0</v>
-      </c>
-      <c r="AM122">
-        <v>-1</v>
-      </c>
-      <c r="AN122">
-        <v>-1</v>
-      </c>
-      <c r="AO122">
-        <v>-1</v>
-      </c>
-      <c r="AP122">
-        <v>-1</v>
-      </c>
-      <c r="AQ122">
-        <v>0</v>
-      </c>
-      <c r="AR122">
-        <v>0</v>
-      </c>
-      <c r="AS122">
-        <v>0</v>
-      </c>
-      <c r="AT122">
-        <v>0</v>
-      </c>
-      <c r="AU122" t="inlineStr">
-        <is>
-          <t>2026-09-18 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Serbia SuperLiga</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>Red Star Belgrade</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>Radnički Niš</t>
-        </is>
-      </c>
-      <c r="G123">
-        <v>0</v>
-      </c>
-      <c r="H123">
-        <v>0</v>
-      </c>
-      <c r="I123">
-        <v>0</v>
-      </c>
-      <c r="J123">
-        <v>0</v>
-      </c>
-      <c r="K123">
-        <v>0</v>
-      </c>
-      <c r="L123">
-        <v>0</v>
-      </c>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N123">
-        <v>0</v>
-      </c>
-      <c r="O123">
-        <v>0</v>
-      </c>
-      <c r="P123">
-        <v>0</v>
-      </c>
-      <c r="Q123">
-        <v>0</v>
-      </c>
-      <c r="R123">
-        <v>0</v>
-      </c>
-      <c r="S123">
-        <v>0</v>
-      </c>
-      <c r="T123">
-        <v>0</v>
-      </c>
-      <c r="U123">
-        <v>0</v>
-      </c>
-      <c r="V123">
-        <v>0</v>
-      </c>
-      <c r="W123">
-        <v>0</v>
-      </c>
-      <c r="X123">
-        <v>0</v>
-      </c>
-      <c r="Y123">
-        <v>0</v>
-      </c>
-      <c r="Z123">
-        <v>0</v>
-      </c>
-      <c r="AA123">
-        <v>0</v>
-      </c>
-      <c r="AB123">
-        <v>0</v>
-      </c>
-      <c r="AC123">
-        <v>0</v>
-      </c>
-      <c r="AD123">
-        <v>0</v>
-      </c>
-      <c r="AE123">
-        <v>0</v>
-      </c>
-      <c r="AF123">
-        <v>0</v>
-      </c>
-      <c r="AG123">
-        <v>0</v>
-      </c>
-      <c r="AH123" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI123" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ123">
-        <v>0</v>
-      </c>
-      <c r="AK123">
-        <v>0</v>
-      </c>
-      <c r="AL123">
-        <v>0</v>
-      </c>
-      <c r="AM123">
-        <v>-1</v>
-      </c>
-      <c r="AN123">
-        <v>-1</v>
-      </c>
-      <c r="AO123">
-        <v>-1</v>
-      </c>
-      <c r="AP123">
-        <v>-1</v>
-      </c>
-      <c r="AQ123">
-        <v>0</v>
-      </c>
-      <c r="AR123">
-        <v>0</v>
-      </c>
-      <c r="AS123">
-        <v>0</v>
-      </c>
-      <c r="AT123">
-        <v>0</v>
-      </c>
-      <c r="AU123" t="inlineStr">
-        <is>
-          <t>2026-09-18 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Serbia SuperLiga</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Radnik Surdulica</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>Partizan</t>
-        </is>
-      </c>
-      <c r="G124">
-        <v>0</v>
-      </c>
-      <c r="H124">
-        <v>0</v>
-      </c>
-      <c r="I124">
-        <v>0</v>
-      </c>
-      <c r="J124">
-        <v>0</v>
-      </c>
-      <c r="K124">
-        <v>0</v>
-      </c>
-      <c r="L124">
-        <v>0</v>
-      </c>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N124">
-        <v>0</v>
-      </c>
-      <c r="O124">
-        <v>0</v>
-      </c>
-      <c r="P124">
-        <v>0</v>
-      </c>
-      <c r="Q124">
-        <v>0</v>
-      </c>
-      <c r="R124">
-        <v>0</v>
-      </c>
-      <c r="S124">
-        <v>0</v>
-      </c>
-      <c r="T124">
-        <v>0</v>
-      </c>
-      <c r="U124">
-        <v>0</v>
-      </c>
-      <c r="V124">
-        <v>0</v>
-      </c>
-      <c r="W124">
-        <v>0</v>
-      </c>
-      <c r="X124">
-        <v>0</v>
-      </c>
-      <c r="Y124">
-        <v>0</v>
-      </c>
-      <c r="Z124">
-        <v>0</v>
-      </c>
-      <c r="AA124">
-        <v>0</v>
-      </c>
-      <c r="AB124">
-        <v>0</v>
-      </c>
-      <c r="AC124">
-        <v>0</v>
-      </c>
-      <c r="AD124">
-        <v>0</v>
-      </c>
-      <c r="AE124">
-        <v>0</v>
-      </c>
-      <c r="AF124">
-        <v>0</v>
-      </c>
-      <c r="AG124">
-        <v>0</v>
-      </c>
-      <c r="AH124" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI124" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ124">
-        <v>0</v>
-      </c>
-      <c r="AK124">
-        <v>0</v>
-      </c>
-      <c r="AL124">
-        <v>0</v>
-      </c>
-      <c r="AM124">
-        <v>-1</v>
-      </c>
-      <c r="AN124">
-        <v>-1</v>
-      </c>
-      <c r="AO124">
-        <v>-1</v>
-      </c>
-      <c r="AP124">
-        <v>-1</v>
-      </c>
-      <c r="AQ124">
-        <v>0</v>
-      </c>
-      <c r="AR124">
-        <v>0</v>
-      </c>
-      <c r="AS124">
-        <v>0</v>
-      </c>
-      <c r="AT124">
-        <v>0</v>
-      </c>
-      <c r="AU124" t="inlineStr">
-        <is>
-          <t>2026-09-18 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>FYR Macedonia First Football League</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>Bregalnica Štip</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>Skopje</t>
-        </is>
-      </c>
-      <c r="G125">
-        <v>0</v>
-      </c>
-      <c r="H125">
-        <v>0</v>
-      </c>
-      <c r="I125">
-        <v>0</v>
-      </c>
-      <c r="J125">
-        <v>0</v>
-      </c>
-      <c r="K125">
-        <v>0</v>
-      </c>
-      <c r="L125">
-        <v>0</v>
-      </c>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N125">
-        <v>0</v>
-      </c>
-      <c r="O125">
-        <v>0</v>
-      </c>
-      <c r="P125">
-        <v>0</v>
-      </c>
-      <c r="Q125">
-        <v>0</v>
-      </c>
-      <c r="R125">
-        <v>0</v>
-      </c>
-      <c r="S125">
-        <v>0</v>
-      </c>
-      <c r="T125">
-        <v>0</v>
-      </c>
-      <c r="U125">
-        <v>0</v>
-      </c>
-      <c r="V125">
-        <v>0</v>
-      </c>
-      <c r="W125">
-        <v>0</v>
-      </c>
-      <c r="X125">
-        <v>0</v>
-      </c>
-      <c r="Y125">
-        <v>0</v>
-      </c>
-      <c r="Z125">
-        <v>0</v>
-      </c>
-      <c r="AA125">
-        <v>0</v>
-      </c>
-      <c r="AB125">
-        <v>0</v>
-      </c>
-      <c r="AC125">
-        <v>0</v>
-      </c>
-      <c r="AD125">
-        <v>0</v>
-      </c>
-      <c r="AE125">
-        <v>0</v>
-      </c>
-      <c r="AF125">
-        <v>0</v>
-      </c>
-      <c r="AG125">
-        <v>0</v>
-      </c>
-      <c r="AH125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ125">
-        <v>0</v>
-      </c>
-      <c r="AK125">
-        <v>0</v>
-      </c>
-      <c r="AL125">
-        <v>0</v>
-      </c>
-      <c r="AM125">
-        <v>-1</v>
-      </c>
-      <c r="AN125">
-        <v>-1</v>
-      </c>
-      <c r="AO125">
-        <v>-1</v>
-      </c>
-      <c r="AP125">
-        <v>-1</v>
-      </c>
-      <c r="AQ125">
-        <v>0</v>
-      </c>
-      <c r="AR125">
-        <v>0</v>
-      </c>
-      <c r="AS125">
-        <v>0</v>
-      </c>
-      <c r="AT125">
-        <v>0</v>
-      </c>
-      <c r="AU125" t="inlineStr">
-        <is>
-          <t>2026-09-18 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>São Bernardo</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Atlético GO</t>
-        </is>
-      </c>
-      <c r="G126">
-        <v>0</v>
-      </c>
-      <c r="H126">
-        <v>0</v>
-      </c>
-      <c r="I126">
-        <v>0</v>
-      </c>
-      <c r="J126">
-        <v>0</v>
-      </c>
-      <c r="K126">
-        <v>0</v>
-      </c>
-      <c r="L126">
-        <v>0</v>
-      </c>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N126">
-        <v>0</v>
-      </c>
-      <c r="O126">
-        <v>0</v>
-      </c>
-      <c r="P126">
-        <v>0</v>
-      </c>
-      <c r="Q126">
-        <v>0</v>
-      </c>
-      <c r="R126">
-        <v>0</v>
-      </c>
-      <c r="S126">
-        <v>0</v>
-      </c>
-      <c r="T126">
-        <v>0</v>
-      </c>
-      <c r="U126">
-        <v>0</v>
-      </c>
-      <c r="V126">
-        <v>0</v>
-      </c>
-      <c r="W126">
-        <v>0</v>
-      </c>
-      <c r="X126">
-        <v>0</v>
-      </c>
-      <c r="Y126">
-        <v>0</v>
-      </c>
-      <c r="Z126">
-        <v>0</v>
-      </c>
-      <c r="AA126">
-        <v>0</v>
-      </c>
-      <c r="AB126">
-        <v>0</v>
-      </c>
-      <c r="AC126">
-        <v>0</v>
-      </c>
-      <c r="AD126">
-        <v>0</v>
-      </c>
-      <c r="AE126">
-        <v>0</v>
-      </c>
-      <c r="AF126">
-        <v>0</v>
-      </c>
-      <c r="AG126">
-        <v>0</v>
-      </c>
-      <c r="AH126" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI126" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ126">
-        <v>0</v>
-      </c>
-      <c r="AK126">
-        <v>0</v>
-      </c>
-      <c r="AL126">
-        <v>0</v>
-      </c>
-      <c r="AM126">
-        <v>-1</v>
-      </c>
-      <c r="AN126">
-        <v>-1</v>
-      </c>
-      <c r="AO126">
-        <v>-1</v>
-      </c>
-      <c r="AP126">
-        <v>-1</v>
-      </c>
-      <c r="AQ126">
-        <v>0</v>
-      </c>
-      <c r="AR126">
-        <v>0</v>
-      </c>
-      <c r="AS126">
-        <v>0</v>
-      </c>
-      <c r="AT126">
-        <v>0</v>
-      </c>
-      <c r="AU126" t="inlineStr">
-        <is>
-          <t>2026-09-18 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>San Diego Wave</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Kansas City</t>
-        </is>
-      </c>
-      <c r="G127">
-        <v>0</v>
-      </c>
-      <c r="H127">
-        <v>0</v>
-      </c>
-      <c r="I127">
-        <v>0</v>
-      </c>
-      <c r="J127">
-        <v>0</v>
-      </c>
-      <c r="K127">
-        <v>0</v>
-      </c>
-      <c r="L127">
-        <v>0</v>
-      </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N127">
-        <v>0</v>
-      </c>
-      <c r="O127">
-        <v>0</v>
-      </c>
-      <c r="P127">
-        <v>0</v>
-      </c>
-      <c r="Q127">
-        <v>0</v>
-      </c>
-      <c r="R127">
-        <v>0</v>
-      </c>
-      <c r="S127">
-        <v>0</v>
-      </c>
-      <c r="T127">
-        <v>0</v>
-      </c>
-      <c r="U127">
-        <v>0</v>
-      </c>
-      <c r="V127">
-        <v>0</v>
-      </c>
-      <c r="W127">
-        <v>0</v>
-      </c>
-      <c r="X127">
-        <v>0</v>
-      </c>
-      <c r="Y127">
-        <v>0</v>
-      </c>
-      <c r="Z127">
-        <v>0</v>
-      </c>
-      <c r="AA127">
-        <v>0</v>
-      </c>
-      <c r="AB127">
-        <v>0</v>
-      </c>
-      <c r="AC127">
-        <v>0</v>
-      </c>
-      <c r="AD127">
-        <v>0</v>
-      </c>
-      <c r="AE127">
-        <v>0</v>
-      </c>
-      <c r="AF127">
-        <v>0</v>
-      </c>
-      <c r="AG127">
-        <v>0</v>
-      </c>
-      <c r="AH127" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI127" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ127">
-        <v>0</v>
-      </c>
-      <c r="AK127">
-        <v>0</v>
-      </c>
-      <c r="AL127">
-        <v>0</v>
-      </c>
-      <c r="AM127">
-        <v>-1</v>
-      </c>
-      <c r="AN127">
-        <v>-1</v>
-      </c>
-      <c r="AO127">
-        <v>-1</v>
-      </c>
-      <c r="AP127">
-        <v>-1</v>
-      </c>
-      <c r="AQ127">
-        <v>0</v>
-      </c>
-      <c r="AR127">
-        <v>0</v>
-      </c>
-      <c r="AS127">
-        <v>0</v>
-      </c>
-      <c r="AT127">
-        <v>0</v>
-      </c>
-      <c r="AU127" t="inlineStr">
         <is>
           <t>2026-09-18 23:00:00</t>
         </is>

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -798,19 +798,19 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="O3">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P3">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="Q3">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="R3">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S3">
         <v>1.31</v>
@@ -825,16 +825,16 @@
         <v>1.47</v>
       </c>
       <c r="W3">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X3">
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="Z3">
-        <v>3.94</v>
+        <v>3.74</v>
       </c>
       <c r="AA3">
         <v>1.71</v>
@@ -846,16 +846,16 @@
         <v>2.7</v>
       </c>
       <c r="AD3">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE3">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF3">
         <v>1.68</v>
       </c>
       <c r="AG3">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK3">
         <v>2.2</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T64">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U64">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V64">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W64">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE64">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF64">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK64">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.19</v>
+        <v>2.39</v>
       </c>
       <c r="O65">
-        <v>3.52</v>
+        <v>3.34</v>
       </c>
       <c r="P65">
-        <v>3.05</v>
+        <v>2.86</v>
       </c>
       <c r="Q65">
-        <v>2.71</v>
+        <v>2.93</v>
       </c>
       <c r="R65">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="S65">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T65">
-        <v>3.22</v>
+        <v>3.02</v>
       </c>
       <c r="U65">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="V65">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="W65">
         <v>1.1</v>
       </c>
       <c r="X65">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y65">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z65">
-        <v>3.91</v>
+        <v>3.84</v>
       </c>
       <c r="AA65">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AB65">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="AC65">
-        <v>2.93</v>
+        <v>2.71</v>
       </c>
       <c r="AD65">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE65">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF65">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AG65">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK65">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,80 +11067,80 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.39</v>
+        <v>1.76</v>
       </c>
       <c r="O66">
-        <v>3.34</v>
+        <v>3.75</v>
       </c>
       <c r="P66">
-        <v>2.86</v>
+        <v>4.05</v>
       </c>
       <c r="Q66">
-        <v>2.93</v>
+        <v>2.29</v>
       </c>
       <c r="R66">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S66">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T66">
-        <v>3.02</v>
+        <v>3.25</v>
       </c>
       <c r="U66">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="V66">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W66">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X66">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y66">
+        <v>1.15</v>
+      </c>
+      <c r="Z66">
+        <v>4.15</v>
+      </c>
+      <c r="AA66">
+        <v>1.65</v>
+      </c>
+      <c r="AB66">
+        <v>2.12</v>
+      </c>
+      <c r="AC66">
+        <v>2.85</v>
+      </c>
+      <c r="AD66">
+        <v>1.41</v>
+      </c>
+      <c r="AE66">
+        <v>1.12</v>
+      </c>
+      <c r="AF66">
+        <v>1.65</v>
+      </c>
+      <c r="AG66">
+        <v>2.15</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ66">
         <v>1.25</v>
       </c>
-      <c r="Z66">
-        <v>3.84</v>
-      </c>
-      <c r="AA66">
-        <v>1.76</v>
-      </c>
-      <c r="AB66">
-        <v>1.97</v>
-      </c>
-      <c r="AC66">
-        <v>2.71</v>
-      </c>
-      <c r="AD66">
-        <v>1.36</v>
-      </c>
-      <c r="AE66">
-        <v>1.14</v>
-      </c>
-      <c r="AF66">
-        <v>1.59</v>
-      </c>
-      <c r="AG66">
-        <v>2.21</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ66">
-        <v>1.3</v>
-      </c>
       <c r="AK66">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.76</v>
+        <v>2.08</v>
       </c>
       <c r="O67">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="P67">
-        <v>4.05</v>
+        <v>3.22</v>
       </c>
       <c r="Q67">
-        <v>2.29</v>
+        <v>2.61</v>
       </c>
       <c r="R67">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="S67">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T67">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="U67">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="V67">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W67">
+        <v>1.07</v>
+      </c>
+      <c r="X67">
+        <v>1.03</v>
+      </c>
+      <c r="Y67">
+        <v>1.21</v>
+      </c>
+      <c r="Z67">
+        <v>3.62</v>
+      </c>
+      <c r="AA67">
+        <v>1.9</v>
+      </c>
+      <c r="AB67">
+        <v>1.92</v>
+      </c>
+      <c r="AC67">
+        <v>3.26</v>
+      </c>
+      <c r="AD67">
+        <v>1.32</v>
+      </c>
+      <c r="AE67">
         <v>1.08</v>
-      </c>
-      <c r="X67">
-        <v>1.01</v>
-      </c>
-      <c r="Y67">
-        <v>1.15</v>
-      </c>
-      <c r="Z67">
-        <v>4.15</v>
-      </c>
-      <c r="AA67">
-        <v>1.65</v>
-      </c>
-      <c r="AB67">
-        <v>2.12</v>
-      </c>
-      <c r="AC67">
-        <v>2.85</v>
-      </c>
-      <c r="AD67">
-        <v>1.41</v>
-      </c>
-      <c r="AE67">
-        <v>1.12</v>
       </c>
       <c r="AF67">
         <v>1.65</v>
       </c>
       <c r="AG67">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK67">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="O68">
-        <v>3.62</v>
+        <v>3.15</v>
       </c>
       <c r="P68">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="Q68">
-        <v>2.61</v>
+        <v>2.81</v>
       </c>
       <c r="R68">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="S68">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="T68">
-        <v>3.04</v>
+        <v>2.62</v>
       </c>
       <c r="U68">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="V68">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W68">
         <v>1.07</v>
       </c>
       <c r="X68">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y68">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="Z68">
-        <v>3.62</v>
+        <v>3.04</v>
       </c>
       <c r="AA68">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="AB68">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="AC68">
-        <v>3.26</v>
+        <v>3.54</v>
       </c>
       <c r="AD68">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AE68">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF68">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="AG68">
-        <v>2.11</v>
+        <v>1.86</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AK68">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O69">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P69">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q69">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="R69">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S69">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T69">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U69">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V69">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W69">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X69">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y69">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z69">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AA69">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB69">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC69">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AD69">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE69">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF69">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG69">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AK69">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL69">
         <v>0</v>

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -804,25 +804,25 @@
         <v>3.8</v>
       </c>
       <c r="P3">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q3">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="R3">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="S3">
         <v>1.31</v>
       </c>
       <c r="T3">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="U3">
-        <v>2.59</v>
+        <v>2.45</v>
       </c>
       <c r="V3">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W3">
         <v>1.11</v>
@@ -837,13 +837,13 @@
         <v>3.74</v>
       </c>
       <c r="AA3">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AB3">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AC3">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AD3">
         <v>1.36</v>
@@ -855,7 +855,7 @@
         <v>1.68</v>
       </c>
       <c r="AG3">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>1.18</v>
       </c>
       <c r="AK3">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1296,55 +1296,55 @@
         <v>3.22</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -2102,28 +2102,28 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="O11">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P11">
         <v>3.2</v>
       </c>
       <c r="Q11">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="R11">
         <v>1.98</v>
       </c>
       <c r="S11">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T11">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="U11">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="V11">
         <v>1.38</v>
@@ -2135,22 +2135,22 @@
         <v>1</v>
       </c>
       <c r="Y11">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z11">
-        <v>3.2</v>
+        <v>3.37</v>
       </c>
       <c r="AA11">
         <v>1.91</v>
       </c>
       <c r="AB11">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AC11">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AD11">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE11">
         <v>1.05</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AK11">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="O15">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P15">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="Q15">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="R15">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="S15">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="T15">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="U15">
-        <v>3.08</v>
+        <v>2.77</v>
       </c>
       <c r="V15">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="W15">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X15">
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z15">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="AA15">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AB15">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AC15">
         <v>3.58</v>
       </c>
       <c r="AD15">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AE15">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF15">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AG15">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AK15">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3089,55 +3089,55 @@
         <v>0</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3415,55 +3415,55 @@
         <v>0</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4556,55 +4556,55 @@
         <v>0</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4873,31 +4873,31 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="O28">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="P28">
-        <v>3.37</v>
+        <v>3.8</v>
       </c>
       <c r="Q28">
-        <v>2.43</v>
+        <v>2.29</v>
       </c>
       <c r="R28">
-        <v>2.09</v>
+        <v>2.21</v>
       </c>
       <c r="S28">
         <v>1.41</v>
       </c>
       <c r="T28">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="U28">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="V28">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W28">
         <v>1.05</v>
@@ -4906,31 +4906,31 @@
         <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z28">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AA28">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AB28">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AC28">
-        <v>3.34</v>
+        <v>3.48</v>
       </c>
       <c r="AD28">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AE28">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF28">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AG28">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AK28">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5045,55 +5045,55 @@
         <v>0</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>6.49</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T54">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U54">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V54">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK54">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.26</v>
+        <v>3.95</v>
       </c>
       <c r="O98">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="P98">
-        <v>3.05</v>
+        <v>1.79</v>
       </c>
       <c r="Q98">
-        <v>2.7</v>
+        <v>4.57</v>
       </c>
       <c r="R98">
         <v>2.3</v>
       </c>
       <c r="S98">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T98">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="U98">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="V98">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W98">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X98">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y98">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z98">
-        <v>3.72</v>
+        <v>3.76</v>
       </c>
       <c r="AA98">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AB98">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="AC98">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="AD98">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AE98">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF98">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG98">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK98">
-        <v>1.57</v>
+        <v>1.17</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>3.95</v>
+        <v>1.47</v>
       </c>
       <c r="O99">
+        <v>4.1</v>
+      </c>
+      <c r="P99">
+        <v>5.7</v>
+      </c>
+      <c r="Q99">
+        <v>2</v>
+      </c>
+      <c r="R99">
+        <v>2.35</v>
+      </c>
+      <c r="S99">
+        <v>1.22</v>
+      </c>
+      <c r="T99">
         <v>3.75</v>
       </c>
-      <c r="P99">
-        <v>1.79</v>
-      </c>
-      <c r="Q99">
-        <v>4.57</v>
-      </c>
-      <c r="R99">
-        <v>2.3</v>
-      </c>
-      <c r="S99">
-        <v>1.33</v>
-      </c>
-      <c r="T99">
-        <v>3.18</v>
-      </c>
       <c r="U99">
-        <v>2.66</v>
+        <v>2.2</v>
       </c>
       <c r="V99">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="W99">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="X99">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y99">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="Z99">
-        <v>3.76</v>
+        <v>4.75</v>
       </c>
       <c r="AA99">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AB99">
-        <v>1.96</v>
+        <v>2.35</v>
       </c>
       <c r="AC99">
-        <v>2.83</v>
+        <v>2.19</v>
       </c>
       <c r="AD99">
-        <v>1.37</v>
+        <v>1.63</v>
       </c>
       <c r="AE99">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AF99">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AG99">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK99">
-        <v>1.17</v>
+        <v>2.4</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.47</v>
+        <v>2.26</v>
       </c>
       <c r="O100">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="P100">
-        <v>5.7</v>
+        <v>3.05</v>
       </c>
       <c r="Q100">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="R100">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S100">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T100">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="U100">
-        <v>2.2</v>
+        <v>2.59</v>
       </c>
       <c r="V100">
+        <v>1.41</v>
+      </c>
+      <c r="W100">
+        <v>1.1</v>
+      </c>
+      <c r="X100">
+        <v>1</v>
+      </c>
+      <c r="Y100">
+        <v>1.2</v>
+      </c>
+      <c r="Z100">
+        <v>3.72</v>
+      </c>
+      <c r="AA100">
+        <v>1.76</v>
+      </c>
+      <c r="AB100">
+        <v>1.99</v>
+      </c>
+      <c r="AC100">
+        <v>2.81</v>
+      </c>
+      <c r="AD100">
+        <v>1.33</v>
+      </c>
+      <c r="AE100">
+        <v>1.09</v>
+      </c>
+      <c r="AF100">
         <v>1.62</v>
       </c>
-      <c r="W100">
-        <v>1.17</v>
-      </c>
-      <c r="X100">
-        <v>1.02</v>
-      </c>
-      <c r="Y100">
-        <v>1.12</v>
-      </c>
-      <c r="Z100">
-        <v>4.75</v>
-      </c>
-      <c r="AA100">
-        <v>1.5</v>
-      </c>
-      <c r="AB100">
-        <v>2.35</v>
-      </c>
-      <c r="AC100">
-        <v>2.19</v>
-      </c>
-      <c r="AD100">
-        <v>1.63</v>
-      </c>
-      <c r="AE100">
-        <v>1.22</v>
-      </c>
-      <c r="AF100">
-        <v>1.58</v>
-      </c>
       <c r="AG100">
-        <v>2.21</v>
+        <v>2.14</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AK100">
-        <v>2.4</v>
+        <v>1.57</v>
       </c>
       <c r="AL100">
         <v>0</v>

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -635,16 +635,16 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="O2">
-        <v>3.1</v>
+        <v>3.21</v>
       </c>
       <c r="P2">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="Q2">
-        <v>4.2</v>
+        <v>3.94</v>
       </c>
       <c r="R2">
         <v>1.99</v>
@@ -653,37 +653,37 @@
         <v>1.42</v>
       </c>
       <c r="T2">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="U2">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="V2">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W2">
         <v>1.01</v>
       </c>
       <c r="X2">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y2">
         <v>1.38</v>
       </c>
       <c r="Z2">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="AA2">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AB2">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AC2">
         <v>4.05</v>
       </c>
       <c r="AD2">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AE2">
         <v>1.04</v>
@@ -692,7 +692,7 @@
         <v>1.91</v>
       </c>
       <c r="AG2">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK2">
         <v>1.22</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="O9">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="P9">
         <v>4</v>
       </c>
       <c r="Q9">
-        <v>2.02</v>
+        <v>2.21</v>
       </c>
       <c r="R9">
-        <v>2.55</v>
+        <v>2.72</v>
       </c>
       <c r="S9">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T9">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="U9">
         <v>1.95</v>
       </c>
       <c r="V9">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="W9">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X9">
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z9">
-        <v>6.63</v>
+        <v>5.8</v>
       </c>
       <c r="AA9">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB9">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="AC9">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AD9">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AE9">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AF9">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AG9">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK9">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q17">
         <v>3.16</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q26">
         <v>4.7</v>
@@ -4885,52 +4885,52 @@
         <v>2.29</v>
       </c>
       <c r="R28">
-        <v>2.21</v>
+        <v>2.06</v>
       </c>
       <c r="S28">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="T28">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="U28">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="V28">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W28">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X28">
         <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z28">
         <v>3.25</v>
       </c>
       <c r="AA28">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="AB28">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="AC28">
-        <v>3.48</v>
+        <v>3.34</v>
       </c>
       <c r="AD28">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE28">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF28">
+        <v>1.83</v>
+      </c>
+      <c r="AG28">
         <v>1.86</v>
-      </c>
-      <c r="AG28">
-        <v>1.87</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>1.19</v>
       </c>
       <c r="AK28">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q34">
         <v>2.44</v>
@@ -5881,34 +5881,34 @@
         <v>1.12</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -7194,10 +7194,10 @@
         <v>0</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC42">
         <v>0</v>
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="O46">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="P46">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="Q46">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R46">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="S46">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="T46">
-        <v>3.3</v>
+        <v>3.11</v>
       </c>
       <c r="U46">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="V46">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="W46">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X46">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y46">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="Z46">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AA46">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AB46">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AC46">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AD46">
         <v>1.36</v>
       </c>
       <c r="AE46">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF46">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AG46">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK46">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8142,55 +8142,55 @@
         <v>0</v>
       </c>
       <c r="Q48">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="R48">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="S48">
         <v>1.22</v>
       </c>
       <c r="T48">
-        <v>3.7</v>
+        <v>3.32</v>
       </c>
       <c r="U48">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="V48">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W48">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X48">
         <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z48">
-        <v>5.45</v>
+        <v>4.65</v>
       </c>
       <c r="AA48">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AB48">
-        <v>2.39</v>
+        <v>2.33</v>
       </c>
       <c r="AC48">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="AD48">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AE48">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AF48">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AG48">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AK48">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O69">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S69">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T69">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U69">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V69">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W69">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X69">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y69">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z69">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA69">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD69">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE69">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF69">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG69">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK69">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -12534,34 +12534,34 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.03</v>
+        <v>1.73</v>
       </c>
       <c r="O75">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P75">
-        <v>3.82</v>
+        <v>4.33</v>
       </c>
       <c r="Q75">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="R75">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="S75">
         <v>1.44</v>
       </c>
       <c r="T75">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="U75">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="V75">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W75">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X75">
         <v>1.03</v>
@@ -12573,16 +12573,16 @@
         <v>2.7</v>
       </c>
       <c r="AA75">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="AB75">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AC75">
-        <v>4</v>
+        <v>4.19</v>
       </c>
       <c r="AD75">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AE75">
         <v>1.02</v>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK75">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12700,49 +12700,49 @@
         <v>1.63</v>
       </c>
       <c r="O76">
-        <v>3.85</v>
+        <v>4.15</v>
       </c>
       <c r="P76">
-        <v>4.6</v>
+        <v>4.15</v>
       </c>
       <c r="Q76">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="R76">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="S76">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T76">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="U76">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="V76">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W76">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X76">
         <v>1.02</v>
       </c>
       <c r="Y76">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z76">
         <v>6.03</v>
       </c>
       <c r="AA76">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AB76">
-        <v>2.74</v>
+        <v>2.52</v>
       </c>
       <c r="AC76">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AD76">
         <v>1.75</v>
@@ -12770,7 +12770,7 @@
         <v>1.25</v>
       </c>
       <c r="AK76">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12860,34 +12860,34 @@
         </is>
       </c>
       <c r="N77">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="O77">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P77">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="Q77">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="R77">
-        <v>2.66</v>
+        <v>2.45</v>
       </c>
       <c r="S77">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T77">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="U77">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="V77">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="W77">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X77">
         <v>1.01</v>
@@ -12896,25 +12896,25 @@
         <v>1.1</v>
       </c>
       <c r="Z77">
-        <v>7</v>
+        <v>6.36</v>
       </c>
       <c r="AA77">
         <v>1.33</v>
       </c>
       <c r="AB77">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="AC77">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="AD77">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AE77">
         <v>1.36</v>
       </c>
       <c r="AF77">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AG77">
         <v>2.9</v>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK77">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13026,61 +13026,61 @@
         <v>2.5</v>
       </c>
       <c r="O78">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P78">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="Q78">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R78">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S78">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T78">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U78">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V78">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W78">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y78">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z78">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="AA78">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB78">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC78">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AD78">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE78">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF78">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG78">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK78">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13186,19 +13186,19 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="O79">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="P79">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="Q79">
         <v>3.1</v>
       </c>
       <c r="R79">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="S79">
         <v>1.22</v>
@@ -13207,10 +13207,10 @@
         <v>4</v>
       </c>
       <c r="U79">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="V79">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="W79">
         <v>1.18</v>
@@ -13219,7 +13219,7 @@
         <v>1.02</v>
       </c>
       <c r="Y79">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Z79">
         <v>5.3</v>
@@ -13228,22 +13228,22 @@
         <v>1.44</v>
       </c>
       <c r="AB79">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AC79">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AD79">
         <v>1.68</v>
       </c>
       <c r="AE79">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF79">
         <v>1.4</v>
       </c>
       <c r="AG79">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.29</v>
+        <v>1.63</v>
       </c>
       <c r="AK79">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="O80">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P80">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="Q80">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="R80">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S80">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T80">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U80">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V80">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W80">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X80">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y80">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z80">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AA80">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB80">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AC80">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD80">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE80">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF80">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG80">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AK80">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13515,40 +13515,40 @@
         <v>1.57</v>
       </c>
       <c r="O81">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="P81">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="Q81">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="R81">
-        <v>2.49</v>
+        <v>2.44</v>
       </c>
       <c r="S81">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T81">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="U81">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="V81">
         <v>1.65</v>
       </c>
       <c r="W81">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X81">
         <v>1.02</v>
       </c>
       <c r="Y81">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z81">
-        <v>5.45</v>
+        <v>5.75</v>
       </c>
       <c r="AA81">
         <v>1.47</v>
@@ -13557,19 +13557,19 @@
         <v>2.6</v>
       </c>
       <c r="AC81">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AD81">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AE81">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF81">
         <v>1.5</v>
       </c>
       <c r="AG81">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AK81">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13675,28 +13675,28 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="O82">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P82">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q82">
-        <v>3.18</v>
+        <v>2.76</v>
       </c>
       <c r="R82">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="S82">
         <v>1.25</v>
       </c>
       <c r="T82">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U82">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="V82">
         <v>1.57</v>
@@ -13708,19 +13708,19 @@
         <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z82">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AA82">
         <v>1.57</v>
       </c>
       <c r="AB82">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="AC82">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="AD82">
         <v>1.47</v>
@@ -13729,7 +13729,7 @@
         <v>1.19</v>
       </c>
       <c r="AF82">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG82">
         <v>2.45</v>
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK82">
         <v>1.44</v>
@@ -13841,61 +13841,61 @@
         <v>1.67</v>
       </c>
       <c r="O83">
-        <v>4.25</v>
+        <v>3.9</v>
       </c>
       <c r="P83">
-        <v>4.17</v>
+        <v>3.8</v>
       </c>
       <c r="Q83">
-        <v>2.13</v>
+        <v>2.01</v>
       </c>
       <c r="R83">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="S83">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="T83">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="U83">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="V83">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="W83">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="X83">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y83">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z83">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AA83">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AB83">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="AC83">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AD83">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AE83">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF83">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AG83">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK83">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="O84">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P84">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S84">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T84">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U84">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V84">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W84">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X84">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y84">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z84">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA84">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD84">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE84">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF84">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG84">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AK84">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -15468,25 +15468,25 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="O93">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="P93">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="Q93">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="R93">
         <v>2.29</v>
       </c>
       <c r="S93">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T93">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
       <c r="U93">
         <v>2.32</v>
@@ -15495,19 +15495,19 @@
         <v>1.62</v>
       </c>
       <c r="W93">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X93">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y93">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z93">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AA93">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="AB93">
         <v>2.47</v>
@@ -15525,7 +15525,7 @@
         <v>1.5</v>
       </c>
       <c r="AG93">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AK93">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15957,7 +15957,7 @@
         </is>
       </c>
       <c r="N96">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="O96">
         <v>5</v>
@@ -15966,34 +15966,34 @@
         <v>5.8</v>
       </c>
       <c r="Q96">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="R96">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="S96">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T96">
-        <v>3.5</v>
+        <v>3.72</v>
       </c>
       <c r="U96">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="V96">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W96">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X96">
         <v>1.02</v>
       </c>
       <c r="Y96">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Z96">
-        <v>4.85</v>
+        <v>4.64</v>
       </c>
       <c r="AA96">
         <v>1.56</v>
@@ -16005,16 +16005,16 @@
         <v>2.36</v>
       </c>
       <c r="AD96">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AE96">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AF96">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG96">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK96">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="O97">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P97">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q97">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="R97">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="S97">
         <v>1.35</v>
       </c>
       <c r="T97">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="U97">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="V97">
         <v>1.4</v>
       </c>
       <c r="W97">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X97">
         <v>1</v>
       </c>
       <c r="Y97">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Z97">
-        <v>3.34</v>
+        <v>3.55</v>
       </c>
       <c r="AA97">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB97">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AC97">
-        <v>3.14</v>
+        <v>3.19</v>
       </c>
       <c r="AD97">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE97">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF97">
         <v>1.67</v>
       </c>
       <c r="AG97">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK97">
         <v>1.57</v>
@@ -16292,25 +16292,25 @@
         <v>1.79</v>
       </c>
       <c r="Q98">
-        <v>4.57</v>
+        <v>4.62</v>
       </c>
       <c r="R98">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="S98">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T98">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="U98">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="V98">
         <v>1.44</v>
       </c>
       <c r="W98">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X98">
         <v>1.03</v>
@@ -16322,25 +16322,25 @@
         <v>3.76</v>
       </c>
       <c r="AA98">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB98">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AC98">
-        <v>2.83</v>
+        <v>2.93</v>
       </c>
       <c r="AD98">
         <v>1.37</v>
       </c>
       <c r="AE98">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF98">
         <v>1.67</v>
       </c>
       <c r="AG98">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK98">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16446,7 +16446,7 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="O99">
         <v>4.1</v>
@@ -16455,10 +16455,10 @@
         <v>5.7</v>
       </c>
       <c r="Q99">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="R99">
-        <v>2.35</v>
+        <v>2.69</v>
       </c>
       <c r="S99">
         <v>1.22</v>
@@ -16485,25 +16485,25 @@
         <v>4.75</v>
       </c>
       <c r="AA99">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB99">
         <v>2.35</v>
       </c>
       <c r="AC99">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AD99">
         <v>1.63</v>
       </c>
       <c r="AE99">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AF99">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AG99">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16609,19 +16609,19 @@
         </is>
       </c>
       <c r="N100">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="O100">
         <v>3.25</v>
       </c>
       <c r="P100">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q100">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="R100">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="S100">
         <v>1.3</v>
@@ -16630,13 +16630,13 @@
         <v>3.2</v>
       </c>
       <c r="U100">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="V100">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W100">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X100">
         <v>1</v>
@@ -16648,10 +16648,10 @@
         <v>3.72</v>
       </c>
       <c r="AA100">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AB100">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="AC100">
         <v>2.81</v>
@@ -16663,10 +16663,10 @@
         <v>1.09</v>
       </c>
       <c r="AF100">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG100">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,7 +16679,7 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK100">
         <v>1.57</v>
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="O101">
-        <v>3.36</v>
+        <v>3.51</v>
       </c>
       <c r="P101">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="Q101">
-        <v>3.44</v>
+        <v>3.55</v>
       </c>
       <c r="R101">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="S101">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T101">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="U101">
-        <v>2.79</v>
+        <v>2.62</v>
       </c>
       <c r="V101">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W101">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X101">
         <v>1.01</v>
       </c>
       <c r="Y101">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Z101">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="AA101">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AB101">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="AC101">
-        <v>3.26</v>
+        <v>2.95</v>
       </c>
       <c r="AD101">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AE101">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF101">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG101">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.3</v>
+        <v>1.61</v>
       </c>
       <c r="AK101">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16974,10 +16974,10 @@
         <v>0</v>
       </c>
       <c r="AA102">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB102">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC102">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="O105">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="P105">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="Q105">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="R105">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="S105">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T105">
-        <v>3.3</v>
+        <v>3.56</v>
       </c>
       <c r="U105">
-        <v>2.57</v>
+        <v>2.24</v>
       </c>
       <c r="V105">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="W105">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X105">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y105">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z105">
-        <v>3.86</v>
+        <v>4.5</v>
       </c>
       <c r="AA105">
-        <v>1.75</v>
+        <v>1.59</v>
       </c>
       <c r="AB105">
-        <v>2.04</v>
+        <v>2.31</v>
       </c>
       <c r="AC105">
-        <v>2.72</v>
+        <v>2.34</v>
       </c>
       <c r="AD105">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AE105">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AF105">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AG105">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AK105">
-        <v>2.56</v>
+        <v>2.84</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="O106">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="P106">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="Q106">
+        <v>1.98</v>
+      </c>
+      <c r="R106">
+        <v>2.28</v>
+      </c>
+      <c r="S106">
+        <v>1.33</v>
+      </c>
+      <c r="T106">
+        <v>3.3</v>
+      </c>
+      <c r="U106">
+        <v>2.57</v>
+      </c>
+      <c r="V106">
+        <v>1.44</v>
+      </c>
+      <c r="W106">
+        <v>1.06</v>
+      </c>
+      <c r="X106">
+        <v>1.02</v>
+      </c>
+      <c r="Y106">
+        <v>1.18</v>
+      </c>
+      <c r="Z106">
+        <v>3.86</v>
+      </c>
+      <c r="AA106">
+        <v>1.75</v>
+      </c>
+      <c r="AB106">
+        <v>2.04</v>
+      </c>
+      <c r="AC106">
+        <v>2.72</v>
+      </c>
+      <c r="AD106">
+        <v>1.36</v>
+      </c>
+      <c r="AE106">
+        <v>1.1</v>
+      </c>
+      <c r="AF106">
         <v>1.87</v>
       </c>
-      <c r="R106">
-        <v>2.5</v>
-      </c>
-      <c r="S106">
-        <v>1.25</v>
-      </c>
-      <c r="T106">
-        <v>3.56</v>
-      </c>
-      <c r="U106">
-        <v>2.24</v>
-      </c>
-      <c r="V106">
-        <v>1.58</v>
-      </c>
-      <c r="W106">
-        <v>1.12</v>
-      </c>
-      <c r="X106">
-        <v>1.01</v>
-      </c>
-      <c r="Y106">
-        <v>1.14</v>
-      </c>
-      <c r="Z106">
-        <v>4.5</v>
-      </c>
-      <c r="AA106">
-        <v>1.59</v>
-      </c>
-      <c r="AB106">
-        <v>2.31</v>
-      </c>
-      <c r="AC106">
-        <v>2.34</v>
-      </c>
-      <c r="AD106">
-        <v>1.48</v>
-      </c>
-      <c r="AE106">
-        <v>1.16</v>
-      </c>
-      <c r="AF106">
-        <v>1.76</v>
-      </c>
       <c r="AG106">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AK106">
-        <v>2.84</v>
+        <v>2.56</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O112">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q112">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R112">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S112">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T112">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U112">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V112">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W112">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X112">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y112">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z112">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA112">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB112">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC112">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD112">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE112">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF112">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG112">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK112">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O117">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P117">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="Q117">
         <v>0</v>

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -5697,10 +5697,10 @@
         <v>0</v>
       </c>
       <c r="Q33">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="R33">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="S33">
         <v>1.3</v>
@@ -5709,7 +5709,7 @@
         <v>3.3</v>
       </c>
       <c r="U33">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V33">
         <v>1.5</v>
@@ -5718,34 +5718,34 @@
         <v>1.12</v>
       </c>
       <c r="X33">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
         <v>1.15</v>
       </c>
       <c r="Z33">
-        <v>4.36</v>
+        <v>4.25</v>
       </c>
       <c r="AA33">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AB33">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AC33">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="AD33">
         <v>1.44</v>
       </c>
       <c r="AE33">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF33">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG33">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK33">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,31 +10089,31 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.35</v>
+        <v>1.89</v>
       </c>
       <c r="O60">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="P60">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q60">
-        <v>2.78</v>
+        <v>2.3</v>
       </c>
       <c r="R60">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="S60">
         <v>1.2</v>
       </c>
       <c r="T60">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="U60">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="V60">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="W60">
         <v>1.2</v>
@@ -10122,31 +10122,31 @@
         <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="Z60">
-        <v>6.13</v>
+        <v>6.25</v>
       </c>
       <c r="AA60">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AB60">
         <v>2.86</v>
       </c>
       <c r="AC60">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AD60">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AE60">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AF60">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AG60">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK60">
-        <v>1.46</v>
+        <v>1.82</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.64</v>
+        <v>2.35</v>
       </c>
       <c r="O61">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="P61">
-        <v>4.4</v>
+        <v>2.4</v>
       </c>
       <c r="Q61">
-        <v>2.16</v>
+        <v>2.78</v>
       </c>
       <c r="R61">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="S61">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T61">
-        <v>3.28</v>
+        <v>4.33</v>
       </c>
       <c r="U61">
-        <v>2.28</v>
+        <v>2.04</v>
       </c>
       <c r="V61">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="W61">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X61">
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z61">
-        <v>4.61</v>
+        <v>6.13</v>
       </c>
       <c r="AA61">
-        <v>1.58</v>
+        <v>1.35</v>
       </c>
       <c r="AB61">
-        <v>2.32</v>
+        <v>2.86</v>
       </c>
       <c r="AC61">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AD61">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="AE61">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AF61">
-        <v>1.57</v>
+        <v>1.34</v>
       </c>
       <c r="AG61">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK61">
-        <v>1.99</v>
+        <v>1.46</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.89</v>
+        <v>1.64</v>
       </c>
       <c r="O62">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P62">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="Q62">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="R62">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="S62">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T62">
-        <v>4.5</v>
+        <v>3.28</v>
       </c>
       <c r="U62">
-        <v>1.99</v>
+        <v>2.28</v>
       </c>
       <c r="V62">
-        <v>1.72</v>
+        <v>1.56</v>
       </c>
       <c r="W62">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="Z62">
-        <v>6.25</v>
+        <v>4.61</v>
       </c>
       <c r="AA62">
-        <v>1.33</v>
+        <v>1.58</v>
       </c>
       <c r="AB62">
-        <v>2.86</v>
+        <v>2.32</v>
       </c>
       <c r="AC62">
-        <v>1.94</v>
+        <v>2.33</v>
       </c>
       <c r="AD62">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="AE62">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AF62">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AG62">
-        <v>2.85</v>
+        <v>2.25</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK62">
-        <v>1.82</v>
+        <v>1.99</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.19</v>
+        <v>2.37</v>
       </c>
       <c r="O64">
-        <v>3.52</v>
+        <v>3.1</v>
       </c>
       <c r="P64">
-        <v>3.05</v>
+        <v>3.17</v>
       </c>
       <c r="Q64">
-        <v>2.71</v>
+        <v>2.92</v>
       </c>
       <c r="R64">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="S64">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T64">
-        <v>3.22</v>
+        <v>2.67</v>
       </c>
       <c r="U64">
-        <v>2.5</v>
+        <v>2.82</v>
       </c>
       <c r="V64">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="W64">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X64">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y64">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="Z64">
-        <v>3.91</v>
+        <v>3.04</v>
       </c>
       <c r="AA64">
-        <v>1.72</v>
+        <v>2.02</v>
       </c>
       <c r="AB64">
-        <v>2.08</v>
+        <v>1.66</v>
       </c>
       <c r="AC64">
-        <v>2.93</v>
+        <v>3.85</v>
       </c>
       <c r="AD64">
-        <v>1.39</v>
+        <v>1.23</v>
       </c>
       <c r="AE64">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AF64">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="AG64">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AK64">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.39</v>
+        <v>2.2</v>
       </c>
       <c r="O65">
-        <v>3.34</v>
+        <v>3.46</v>
       </c>
       <c r="P65">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="Q65">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="R65">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S65">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T65">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="U65">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="V65">
         <v>1.49</v>
       </c>
       <c r="W65">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X65">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z65">
-        <v>3.84</v>
+        <v>3.91</v>
       </c>
       <c r="AA65">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AB65">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="AC65">
-        <v>2.71</v>
+        <v>2.9</v>
       </c>
       <c r="AD65">
         <v>1.36</v>
       </c>
       <c r="AE65">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF65">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AG65">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK65">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,80 +11067,80 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="O66">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="P66">
-        <v>4.05</v>
+        <v>2.75</v>
       </c>
       <c r="Q66">
+        <v>2.87</v>
+      </c>
+      <c r="R66">
         <v>2.29</v>
       </c>
-      <c r="R66">
-        <v>2.3</v>
-      </c>
       <c r="S66">
+        <v>1.36</v>
+      </c>
+      <c r="T66">
+        <v>3.1</v>
+      </c>
+      <c r="U66">
+        <v>2.42</v>
+      </c>
+      <c r="V66">
+        <v>1.48</v>
+      </c>
+      <c r="W66">
+        <v>1.1</v>
+      </c>
+      <c r="X66">
+        <v>1</v>
+      </c>
+      <c r="Y66">
+        <v>1.25</v>
+      </c>
+      <c r="Z66">
+        <v>3.86</v>
+      </c>
+      <c r="AA66">
+        <v>1.9</v>
+      </c>
+      <c r="AB66">
+        <v>1.9</v>
+      </c>
+      <c r="AC66">
+        <v>3.01</v>
+      </c>
+      <c r="AD66">
+        <v>1.37</v>
+      </c>
+      <c r="AE66">
+        <v>1.11</v>
+      </c>
+      <c r="AF66">
+        <v>1.67</v>
+      </c>
+      <c r="AG66">
+        <v>2.19</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ66">
         <v>1.3</v>
       </c>
-      <c r="T66">
-        <v>3.25</v>
-      </c>
-      <c r="U66">
-        <v>2.4</v>
-      </c>
-      <c r="V66">
-        <v>1.5</v>
-      </c>
-      <c r="W66">
-        <v>1.08</v>
-      </c>
-      <c r="X66">
-        <v>1.01</v>
-      </c>
-      <c r="Y66">
-        <v>1.15</v>
-      </c>
-      <c r="Z66">
-        <v>4.15</v>
-      </c>
-      <c r="AA66">
-        <v>1.65</v>
-      </c>
-      <c r="AB66">
-        <v>2.12</v>
-      </c>
-      <c r="AC66">
-        <v>2.85</v>
-      </c>
-      <c r="AD66">
-        <v>1.41</v>
-      </c>
-      <c r="AE66">
-        <v>1.12</v>
-      </c>
-      <c r="AF66">
-        <v>1.65</v>
-      </c>
-      <c r="AG66">
-        <v>2.15</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ66">
-        <v>1.25</v>
-      </c>
       <c r="AK66">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.08</v>
+        <v>1.75</v>
       </c>
       <c r="O67">
-        <v>3.62</v>
+        <v>3.78</v>
       </c>
       <c r="P67">
-        <v>3.22</v>
+        <v>4</v>
       </c>
       <c r="Q67">
-        <v>2.61</v>
+        <v>2.28</v>
       </c>
       <c r="R67">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="S67">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T67">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="U67">
-        <v>2.75</v>
+        <v>2.42</v>
       </c>
       <c r="V67">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W67">
         <v>1.07</v>
       </c>
       <c r="X67">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z67">
-        <v>3.62</v>
+        <v>4.1</v>
       </c>
       <c r="AA67">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="AB67">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="AC67">
-        <v>3.26</v>
+        <v>2.85</v>
       </c>
       <c r="AD67">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AE67">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF67">
         <v>1.65</v>
       </c>
       <c r="AG67">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK67">
-        <v>1.71</v>
+        <v>2.02</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="O68">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="P68">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="Q68">
-        <v>2.81</v>
+        <v>2.51</v>
       </c>
       <c r="R68">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="S68">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="T68">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="U68">
-        <v>3.2</v>
+        <v>2.63</v>
       </c>
       <c r="V68">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="W68">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X68">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y68">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="Z68">
-        <v>3.04</v>
+        <v>3.4</v>
       </c>
       <c r="AA68">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AB68">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC68">
-        <v>3.54</v>
+        <v>2.92</v>
       </c>
       <c r="AD68">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AE68">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF68">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AG68">
-        <v>1.86</v>
+        <v>2.09</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AK68">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="O69">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="P69">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="Q69">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="R69">
-        <v>2.14</v>
+        <v>2.03</v>
       </c>
       <c r="S69">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T69">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="U69">
         <v>3</v>
       </c>
       <c r="V69">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W69">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X69">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y69">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z69">
         <v>3.04</v>
       </c>
       <c r="AA69">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AB69">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC69">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AD69">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE69">
         <v>1.05</v>
       </c>
       <c r="AF69">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AG69">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK69">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11719,19 +11719,19 @@
         </is>
       </c>
       <c r="N70">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="O70">
         <v>3.5</v>
       </c>
       <c r="P70">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="Q70">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="R70">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="S70">
         <v>1.3</v>
@@ -11740,40 +11740,40 @@
         <v>3.2</v>
       </c>
       <c r="U70">
-        <v>2.62</v>
+        <v>2.43</v>
       </c>
       <c r="V70">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="W70">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X70">
         <v>1</v>
       </c>
       <c r="Y70">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z70">
-        <v>3.85</v>
+        <v>3.78</v>
       </c>
       <c r="AA70">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AB70">
-        <v>2.09</v>
+        <v>1.93</v>
       </c>
       <c r="AC70">
-        <v>2.59</v>
+        <v>2.95</v>
       </c>
       <c r="AD70">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AE70">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF70">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AG70">
         <v>2.15</v>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK70">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -14816,34 +14816,34 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O89">
         <v>3.6</v>
       </c>
       <c r="P89">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="Q89">
-        <v>2.88</v>
+        <v>2.59</v>
       </c>
       <c r="R89">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="S89">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T89">
         <v>3.2</v>
       </c>
       <c r="U89">
-        <v>2.44</v>
+        <v>2.63</v>
       </c>
       <c r="V89">
         <v>1.47</v>
       </c>
       <c r="W89">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X89">
         <v>1</v>
@@ -14852,28 +14852,28 @@
         <v>1.22</v>
       </c>
       <c r="Z89">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AA89">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AB89">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="AC89">
         <v>2.9</v>
       </c>
       <c r="AD89">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE89">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF89">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="AG89">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK89">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14985,34 +14985,34 @@
         <v>3.8</v>
       </c>
       <c r="P90">
-        <v>4.56</v>
+        <v>4.5</v>
       </c>
       <c r="Q90">
         <v>2.15</v>
       </c>
       <c r="R90">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="S90">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T90">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="U90">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="V90">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W90">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X90">
         <v>1.02</v>
       </c>
       <c r="Y90">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z90">
         <v>4.8</v>
@@ -15021,13 +15021,13 @@
         <v>1.54</v>
       </c>
       <c r="AB90">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="AC90">
         <v>2.43</v>
       </c>
       <c r="AD90">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AE90">
         <v>1.18</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,19 +15631,19 @@
         </is>
       </c>
       <c r="N94">
-        <v>1.69</v>
+        <v>2.2</v>
       </c>
       <c r="O94">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="P94">
-        <v>4.4</v>
+        <v>2.85</v>
       </c>
       <c r="Q94">
-        <v>2.21</v>
+        <v>2.8</v>
       </c>
       <c r="R94">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="S94">
         <v>1.3</v>
@@ -15652,43 +15652,43 @@
         <v>3.3</v>
       </c>
       <c r="U94">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="V94">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W94">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X94">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y94">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z94">
-        <v>3.88</v>
+        <v>3.78</v>
       </c>
       <c r="AA94">
         <v>1.72</v>
       </c>
       <c r="AB94">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AC94">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="AD94">
         <v>1.37</v>
       </c>
       <c r="AE94">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF94">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="AG94">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK94">
-        <v>2.13</v>
+        <v>1.62</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.27</v>
+        <v>1.7</v>
       </c>
       <c r="O95">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P95">
-        <v>2.85</v>
+        <v>4.05</v>
       </c>
       <c r="Q95">
-        <v>2.88</v>
+        <v>2.18</v>
       </c>
       <c r="R95">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="S95">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T95">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="U95">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="V95">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="W95">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X95">
         <v>1.02</v>
       </c>
       <c r="Y95">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z95">
-        <v>3.9</v>
+        <v>4.15</v>
       </c>
       <c r="AA95">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AB95">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="AC95">
-        <v>2.61</v>
+        <v>2.43</v>
       </c>
       <c r="AD95">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AE95">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF95">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AG95">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="AK95">
-        <v>1.59</v>
+        <v>2.2</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
+        <v>2.19</v>
+      </c>
+      <c r="O96">
+        <v>3.3</v>
+      </c>
+      <c r="P96">
+        <v>3.1</v>
+      </c>
+      <c r="Q96">
+        <v>2.76</v>
+      </c>
+      <c r="R96">
+        <v>2.23</v>
+      </c>
+      <c r="S96">
+        <v>1.35</v>
+      </c>
+      <c r="T96">
+        <v>2.84</v>
+      </c>
+      <c r="U96">
+        <v>2.62</v>
+      </c>
+      <c r="V96">
         <v>1.4</v>
       </c>
-      <c r="O96">
-        <v>5</v>
-      </c>
-      <c r="P96">
-        <v>5.8</v>
-      </c>
-      <c r="Q96">
-        <v>1.92</v>
-      </c>
-      <c r="R96">
-        <v>2.5</v>
-      </c>
-      <c r="S96">
-        <v>1.22</v>
-      </c>
-      <c r="T96">
-        <v>3.72</v>
-      </c>
-      <c r="U96">
-        <v>2.22</v>
-      </c>
-      <c r="V96">
-        <v>1.56</v>
-      </c>
       <c r="W96">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X96">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y96">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="Z96">
-        <v>4.64</v>
+        <v>3.55</v>
       </c>
       <c r="AA96">
-        <v>1.56</v>
+        <v>1.9</v>
       </c>
       <c r="AB96">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="AC96">
-        <v>2.36</v>
+        <v>3.19</v>
       </c>
       <c r="AD96">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="AE96">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="AF96">
         <v>1.67</v>
       </c>
       <c r="AG96">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AK96">
-        <v>2.61</v>
+        <v>1.57</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.19</v>
+        <v>1.4</v>
       </c>
       <c r="O97">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="P97">
-        <v>3.1</v>
+        <v>5.8</v>
       </c>
       <c r="Q97">
-        <v>2.76</v>
+        <v>1.92</v>
       </c>
       <c r="R97">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="S97">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="T97">
-        <v>2.84</v>
+        <v>3.72</v>
       </c>
       <c r="U97">
-        <v>2.62</v>
+        <v>2.22</v>
       </c>
       <c r="V97">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="W97">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X97">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y97">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="Z97">
-        <v>3.55</v>
+        <v>4.64</v>
       </c>
       <c r="AA97">
-        <v>1.9</v>
+        <v>1.56</v>
       </c>
       <c r="AB97">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="AC97">
-        <v>3.19</v>
+        <v>2.36</v>
       </c>
       <c r="AD97">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="AE97">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="AF97">
         <v>1.67</v>
       </c>
       <c r="AG97">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AK97">
-        <v>1.57</v>
+        <v>2.61</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -17098,34 +17098,34 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="O103">
         <v>3.8</v>
       </c>
       <c r="P103">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q103">
-        <v>2.99</v>
+        <v>3.25</v>
       </c>
       <c r="R103">
         <v>2.26</v>
       </c>
       <c r="S103">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T103">
         <v>3.9</v>
       </c>
       <c r="U103">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="V103">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="W103">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X103">
         <v>1.02</v>
@@ -17137,25 +17137,25 @@
         <v>5.3</v>
       </c>
       <c r="AA103">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AB103">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="AC103">
         <v>2.28</v>
       </c>
       <c r="AD103">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AE103">
         <v>1.23</v>
       </c>
       <c r="AF103">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AG103">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.67</v>
+        <v>1.3</v>
       </c>
       <c r="AK103">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="O105">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="P105">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="Q105">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="R105">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="S105">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T105">
-        <v>3.56</v>
+        <v>3.8</v>
       </c>
       <c r="U105">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="V105">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W105">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X105">
         <v>1.01</v>
       </c>
       <c r="Y105">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z105">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="AA105">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="AB105">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="AC105">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="AD105">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AE105">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF105">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AG105">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AK105">
-        <v>2.84</v>
+        <v>2.62</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="O106">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="P106">
-        <v>6</v>
+        <v>7.35</v>
       </c>
       <c r="Q106">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="R106">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="S106">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T106">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="U106">
-        <v>2.57</v>
+        <v>2.34</v>
       </c>
       <c r="V106">
+        <v>1.5</v>
+      </c>
+      <c r="W106">
+        <v>1.08</v>
+      </c>
+      <c r="X106">
+        <v>1.01</v>
+      </c>
+      <c r="Y106">
+        <v>1.14</v>
+      </c>
+      <c r="Z106">
+        <v>4.45</v>
+      </c>
+      <c r="AA106">
+        <v>1.6</v>
+      </c>
+      <c r="AB106">
+        <v>2.25</v>
+      </c>
+      <c r="AC106">
+        <v>2.42</v>
+      </c>
+      <c r="AD106">
         <v>1.44</v>
       </c>
-      <c r="W106">
-        <v>1.06</v>
-      </c>
-      <c r="X106">
-        <v>1.02</v>
-      </c>
-      <c r="Y106">
-        <v>1.18</v>
-      </c>
-      <c r="Z106">
-        <v>3.86</v>
-      </c>
-      <c r="AA106">
-        <v>1.75</v>
-      </c>
-      <c r="AB106">
-        <v>2.04</v>
-      </c>
-      <c r="AC106">
-        <v>2.72</v>
-      </c>
-      <c r="AD106">
-        <v>1.36</v>
-      </c>
       <c r="AE106">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF106">
         <v>1.87</v>
       </c>
       <c r="AG106">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AK106">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17753,37 +17753,37 @@
         <v>1.85</v>
       </c>
       <c r="O107">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="P107">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="Q107">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="R107">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S107">
         <v>1.4</v>
       </c>
       <c r="T107">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="U107">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="V107">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W107">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X107">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y107">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z107">
         <v>3.1</v>
@@ -17792,22 +17792,22 @@
         <v>1.94</v>
       </c>
       <c r="AB107">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AC107">
         <v>3.2</v>
       </c>
       <c r="AD107">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AE107">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF107">
         <v>1.75</v>
       </c>
       <c r="AG107">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>1.25</v>
       </c>
       <c r="AK107">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AL107">
         <v>0</v>

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="O2">
-        <v>3.21</v>
+        <v>3.1</v>
       </c>
       <c r="P2">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="Q2">
         <v>3.94</v>
@@ -650,13 +650,13 @@
         <v>1.99</v>
       </c>
       <c r="S2">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="T2">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="U2">
-        <v>2.95</v>
+        <v>3.18</v>
       </c>
       <c r="V2">
         <v>1.27</v>
@@ -665,25 +665,25 @@
         <v>1.01</v>
       </c>
       <c r="X2">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
         <v>1.38</v>
       </c>
       <c r="Z2">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AA2">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AB2">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AC2">
-        <v>4.05</v>
+        <v>4.33</v>
       </c>
       <c r="AD2">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE2">
         <v>1.04</v>
@@ -692,7 +692,7 @@
         <v>1.91</v>
       </c>
       <c r="AG2">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="O3">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P3">
         <v>4.5</v>
       </c>
       <c r="Q3">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="R3">
         <v>2.21</v>
       </c>
       <c r="S3">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T3">
         <v>2.94</v>
@@ -828,10 +828,10 @@
         <v>1.11</v>
       </c>
       <c r="X3">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z3">
         <v>3.74</v>
@@ -843,7 +843,7 @@
         <v>1.99</v>
       </c>
       <c r="AC3">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AD3">
         <v>1.36</v>
@@ -1302,16 +1302,16 @@
         <v>2.27</v>
       </c>
       <c r="S6">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T6">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="U6">
         <v>2.55</v>
       </c>
       <c r="V6">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W6">
         <v>1.09</v>
@@ -1360,7 +1360,7 @@
         <v>1.29</v>
       </c>
       <c r="AK6">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1782,58 +1782,58 @@
         <v>4.1</v>
       </c>
       <c r="P9">
-        <v>4</v>
+        <v>3.61</v>
       </c>
       <c r="Q9">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="R9">
-        <v>2.72</v>
+        <v>2.41</v>
       </c>
       <c r="S9">
         <v>1.2</v>
       </c>
       <c r="T9">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="U9">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="V9">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="W9">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X9">
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z9">
-        <v>5.8</v>
+        <v>6.33</v>
       </c>
       <c r="AA9">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AB9">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="AC9">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AD9">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AE9">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AF9">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AG9">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AK9">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2102,25 +2102,25 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O11">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P11">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="Q11">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="R11">
-        <v>1.98</v>
+        <v>2.19</v>
       </c>
       <c r="S11">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T11">
-        <v>2.77</v>
+        <v>2.93</v>
       </c>
       <c r="U11">
         <v>2.69</v>
@@ -2135,25 +2135,25 @@
         <v>1</v>
       </c>
       <c r="Y11">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z11">
         <v>3.37</v>
       </c>
       <c r="AA11">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="AB11">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AC11">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AD11">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE11">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF11">
         <v>1.7</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK11">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O13">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P13">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R13">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="S13">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T13">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U13">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V13">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W13">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X13">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y13">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z13">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA13">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AB13">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC13">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AD13">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE13">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF13">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG13">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK13">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2594,61 +2594,61 @@
         <v>1.33</v>
       </c>
       <c r="O14">
-        <v>4.6</v>
+        <v>4.95</v>
       </c>
       <c r="P14">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,7 +2754,7 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="O15">
         <v>3.25</v>
@@ -2763,25 +2763,25 @@
         <v>4</v>
       </c>
       <c r="Q15">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="R15">
         <v>2.1</v>
       </c>
       <c r="S15">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="T15">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="U15">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="V15">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="W15">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X15">
         <v>1.01</v>
@@ -2796,7 +2796,7 @@
         <v>2</v>
       </c>
       <c r="AB15">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AC15">
         <v>3.58</v>
@@ -2808,10 +2808,10 @@
         <v>1.05</v>
       </c>
       <c r="AF15">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG15">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>1.14</v>
       </c>
       <c r="AK15">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3089,22 +3089,22 @@
         <v>2.8</v>
       </c>
       <c r="Q17">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="R17">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="S17">
         <v>1.45</v>
       </c>
       <c r="T17">
-        <v>2.51</v>
+        <v>2.58</v>
       </c>
       <c r="U17">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="V17">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W17">
         <v>1.04</v>
@@ -3113,22 +3113,22 @@
         <v>1.04</v>
       </c>
       <c r="Y17">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Z17">
-        <v>2.66</v>
+        <v>2.79</v>
       </c>
       <c r="AA17">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="AB17">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AC17">
-        <v>3.96</v>
+        <v>4.28</v>
       </c>
       <c r="AD17">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE17">
         <v>1.02</v>
@@ -3137,7 +3137,7 @@
         <v>1.92</v>
       </c>
       <c r="AG17">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK17">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,28 +3243,28 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="O18">
-        <v>3.09</v>
+        <v>3.05</v>
       </c>
       <c r="P18">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="Q18">
-        <v>3.55</v>
+        <v>3.47</v>
       </c>
       <c r="R18">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="S18">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T18">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="U18">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="V18">
         <v>1.31</v>
@@ -3273,7 +3273,7 @@
         <v>1.02</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y18">
         <v>1.32</v>
@@ -3282,16 +3282,16 @@
         <v>2.88</v>
       </c>
       <c r="AA18">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="AB18">
         <v>1.71</v>
       </c>
       <c r="AC18">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="AD18">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE18">
         <v>1.03</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK18">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3415,22 +3415,22 @@
         <v>0</v>
       </c>
       <c r="Q19">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="R19">
-        <v>2.26</v>
+        <v>2.31</v>
       </c>
       <c r="S19">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T19">
-        <v>2.96</v>
+        <v>3.13</v>
       </c>
       <c r="U19">
         <v>2.53</v>
       </c>
       <c r="V19">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W19">
         <v>1.08</v>
@@ -3451,19 +3451,19 @@
         <v>1.98</v>
       </c>
       <c r="AC19">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="AD19">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE19">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF19">
-        <v>2.11</v>
+        <v>2.03</v>
       </c>
       <c r="AG19">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK19">
-        <v>2.99</v>
+        <v>2.89</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -4550,74 +4550,74 @@
         <v>4.1</v>
       </c>
       <c r="O26">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="P26">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q26">
-        <v>4.7</v>
+        <v>4.45</v>
       </c>
       <c r="R26">
-        <v>1.96</v>
+        <v>2.15</v>
       </c>
       <c r="S26">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="T26">
-        <v>2.42</v>
+        <v>2.82</v>
       </c>
       <c r="U26">
-        <v>3.32</v>
+        <v>3.02</v>
       </c>
       <c r="V26">
+        <v>1.32</v>
+      </c>
+      <c r="W26">
+        <v>1.03</v>
+      </c>
+      <c r="X26">
+        <v>1.04</v>
+      </c>
+      <c r="Y26">
+        <v>1.35</v>
+      </c>
+      <c r="Z26">
+        <v>2.92</v>
+      </c>
+      <c r="AA26">
+        <v>2.13</v>
+      </c>
+      <c r="AB26">
+        <v>1.73</v>
+      </c>
+      <c r="AC26">
+        <v>3.68</v>
+      </c>
+      <c r="AD26">
+        <v>1.2</v>
+      </c>
+      <c r="AE26">
+        <v>1.03</v>
+      </c>
+      <c r="AF26">
+        <v>1.92</v>
+      </c>
+      <c r="AG26">
+        <v>1.77</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26">
         <v>1.27</v>
-      </c>
-      <c r="W26">
-        <v>1.01</v>
-      </c>
-      <c r="X26">
-        <v>1.03</v>
-      </c>
-      <c r="Y26">
-        <v>1.39</v>
-      </c>
-      <c r="Z26">
-        <v>2.59</v>
-      </c>
-      <c r="AA26">
-        <v>2.37</v>
-      </c>
-      <c r="AB26">
-        <v>1.6</v>
-      </c>
-      <c r="AC26">
-        <v>4.3</v>
-      </c>
-      <c r="AD26">
-        <v>1.15</v>
-      </c>
-      <c r="AE26">
-        <v>1.01</v>
-      </c>
-      <c r="AF26">
-        <v>2.03</v>
-      </c>
-      <c r="AG26">
-        <v>1.7</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ26">
-        <v>1.32</v>
       </c>
       <c r="AK26">
         <v>1.25</v>
@@ -4885,10 +4885,10 @@
         <v>2.29</v>
       </c>
       <c r="R28">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S28">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T28">
         <v>2.7</v>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AK28">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5051,7 +5051,7 @@
         <v>2.06</v>
       </c>
       <c r="S29">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T29">
         <v>2.75</v>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK29">
         <v>1.88</v>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="O30">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P30">
         <v>3.85</v>
@@ -5211,19 +5211,19 @@
         <v>2.65</v>
       </c>
       <c r="R30">
-        <v>1.94</v>
+        <v>2.09</v>
       </c>
       <c r="S30">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T30">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="U30">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="V30">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W30">
         <v>1.04</v>
@@ -5232,16 +5232,16 @@
         <v>1.04</v>
       </c>
       <c r="Y30">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z30">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="AA30">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="AB30">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC30">
         <v>3.88</v>
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AK30">
         <v>1.76</v>
@@ -5534,55 +5534,55 @@
         <v>0</v>
       </c>
       <c r="Q32">
-        <v>2.63</v>
+        <v>2.69</v>
       </c>
       <c r="R32">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="S32">
         <v>1.26</v>
       </c>
       <c r="T32">
-        <v>3.32</v>
+        <v>3.24</v>
       </c>
       <c r="U32">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="V32">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W32">
         <v>1.11</v>
       </c>
       <c r="X32">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
         <v>1.18</v>
       </c>
       <c r="Z32">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AA32">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AB32">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="AC32">
-        <v>2.66</v>
+        <v>2.87</v>
       </c>
       <c r="AD32">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AE32">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF32">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG32">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>1.22</v>
       </c>
       <c r="AK32">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5700,7 +5700,7 @@
         <v>2.45</v>
       </c>
       <c r="R33">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S33">
         <v>1.3</v>
@@ -5727,13 +5727,13 @@
         <v>4.25</v>
       </c>
       <c r="AA33">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AB33">
         <v>2.23</v>
       </c>
       <c r="AC33">
-        <v>2.73</v>
+        <v>2.56</v>
       </c>
       <c r="AD33">
         <v>1.44</v>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5860,25 +5860,25 @@
         <v>3.1</v>
       </c>
       <c r="Q34">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="R34">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="S34">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T34">
-        <v>3.75</v>
+        <v>3.42</v>
       </c>
       <c r="U34">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="V34">
         <v>1.55</v>
       </c>
       <c r="W34">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X34">
         <v>1</v>
@@ -5890,7 +5890,7 @@
         <v>4.65</v>
       </c>
       <c r="AA34">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AB34">
         <v>2.37</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="O35">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="P35">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
+        <v>2.16</v>
+      </c>
+      <c r="O36">
         <v>3.4</v>
       </c>
-      <c r="O36">
-        <v>3.3</v>
-      </c>
       <c r="P36">
-        <v>2.06</v>
+        <v>3.1</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.35</v>
+        <v>3.4</v>
       </c>
       <c r="O37">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="P37">
-        <v>8</v>
+        <v>2.06</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.87</v>
+        <v>1.35</v>
       </c>
       <c r="O38">
-        <v>3.45</v>
+        <v>4.7</v>
       </c>
       <c r="P38">
-        <v>3.95</v>
+        <v>8</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6619,12 +6619,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Omonia 29is Maiou</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,80 +6666,80 @@
         </is>
       </c>
       <c r="N39">
-        <v>5.8</v>
+        <v>2.41</v>
       </c>
       <c r="O39">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="P39">
+        <v>2.55</v>
+      </c>
+      <c r="Q39">
+        <v>2.9</v>
+      </c>
+      <c r="R39">
+        <v>2.25</v>
+      </c>
+      <c r="S39">
+        <v>1.29</v>
+      </c>
+      <c r="T39">
+        <v>3.5</v>
+      </c>
+      <c r="U39">
+        <v>2.38</v>
+      </c>
+      <c r="V39">
         <v>1.53</v>
       </c>
-      <c r="Q39">
-        <v>6.49</v>
-      </c>
-      <c r="R39">
-        <v>2.28</v>
-      </c>
-      <c r="S39">
-        <v>1.33</v>
-      </c>
-      <c r="T39">
-        <v>3</v>
-      </c>
-      <c r="U39">
-        <v>2.75</v>
-      </c>
-      <c r="V39">
-        <v>1.4</v>
-      </c>
       <c r="W39">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y39">
+        <v>1.18</v>
+      </c>
+      <c r="Z39">
+        <v>4.5</v>
+      </c>
+      <c r="AA39">
+        <v>1.62</v>
+      </c>
+      <c r="AB39">
+        <v>2.19</v>
+      </c>
+      <c r="AC39">
+        <v>2.46</v>
+      </c>
+      <c r="AD39">
+        <v>1.43</v>
+      </c>
+      <c r="AE39">
+        <v>1.14</v>
+      </c>
+      <c r="AF39">
+        <v>1.51</v>
+      </c>
+      <c r="AG39">
+        <v>2.3</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39">
         <v>1.22</v>
       </c>
-      <c r="Z39">
-        <v>3.5</v>
-      </c>
-      <c r="AA39">
-        <v>1.85</v>
-      </c>
-      <c r="AB39">
-        <v>1.95</v>
-      </c>
-      <c r="AC39">
-        <v>3.04</v>
-      </c>
-      <c r="AD39">
-        <v>1.29</v>
-      </c>
-      <c r="AE39">
-        <v>1.07</v>
-      </c>
-      <c r="AF39">
-        <v>2</v>
-      </c>
-      <c r="AG39">
-        <v>1.73</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39">
-        <v>1.18</v>
-      </c>
       <c r="AK39">
-        <v>1.07</v>
+        <v>1.5</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>2026-09-18 13:00:00</t>
+          <t>2026-09-18 13:30:00</t>
         </is>
       </c>
     </row>
@@ -6829,7 +6829,7 @@
         </is>
       </c>
       <c r="N40">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O40">
         <v>3.9</v>
@@ -6841,7 +6841,7 @@
         <v>4</v>
       </c>
       <c r="R40">
-        <v>2.33</v>
+        <v>2.47</v>
       </c>
       <c r="S40">
         <v>1.25</v>
@@ -6853,13 +6853,13 @@
         <v>2.25</v>
       </c>
       <c r="V40">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W40">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X40">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
         <v>1.13</v>
@@ -6868,10 +6868,10 @@
         <v>4.5</v>
       </c>
       <c r="AA40">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AB40">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="AC40">
         <v>2.35</v>
@@ -6883,10 +6883,10 @@
         <v>1.16</v>
       </c>
       <c r="AF40">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AG40">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK40">
         <v>1.2</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="O41">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P41">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q41">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="R41">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="S41">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T41">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U41">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V41">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W41">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X41">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y41">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z41">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA41">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB41">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AC41">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AD41">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE41">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF41">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG41">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AK41">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA42">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AB42">
-        <v>2.15</v>
+        <v>2.48</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,34 +7318,34 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="O43">
-        <v>4.35</v>
+        <v>4.5</v>
       </c>
       <c r="P43">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q43">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="R43">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="S43">
         <v>1.2</v>
       </c>
       <c r="T43">
-        <v>3.92</v>
+        <v>3.8</v>
       </c>
       <c r="U43">
-        <v>2.17</v>
+        <v>2.06</v>
       </c>
       <c r="V43">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="W43">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X43">
         <v>1.02</v>
@@ -7354,28 +7354,28 @@
         <v>1.1</v>
       </c>
       <c r="Z43">
-        <v>5.15</v>
+        <v>5.05</v>
       </c>
       <c r="AA43">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AB43">
-        <v>2.54</v>
+        <v>2.69</v>
       </c>
       <c r="AC43">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AD43">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AE43">
         <v>1.24</v>
       </c>
       <c r="AF43">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AG43">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK43">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7434,12 +7434,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="O44">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="P44">
-        <v>2.45</v>
+        <v>2.95</v>
       </c>
       <c r="Q44">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="R44">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="S44">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="T44">
-        <v>3.42</v>
+        <v>2.56</v>
       </c>
       <c r="U44">
-        <v>2.21</v>
+        <v>2.78</v>
       </c>
       <c r="V44">
-        <v>1.62</v>
+        <v>1.37</v>
       </c>
       <c r="W44">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X44">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="Z44">
-        <v>5.25</v>
+        <v>3.13</v>
       </c>
       <c r="AA44">
-        <v>1.46</v>
+        <v>1.98</v>
       </c>
       <c r="AB44">
-        <v>2.39</v>
+        <v>1.74</v>
       </c>
       <c r="AC44">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="AD44">
-        <v>1.62</v>
+        <v>1.22</v>
       </c>
       <c r="AE44">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AF44">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="AG44">
-        <v>2.58</v>
+        <v>1.9</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AK44">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>2026-09-18 13:30:00</t>
+          <t>2026-09-18 14:00:00</t>
         </is>
       </c>
     </row>
@@ -7602,22 +7602,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O45">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="P45">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="Q45">
-        <v>3.07</v>
+        <v>2.97</v>
       </c>
       <c r="R45">
-        <v>2.17</v>
+        <v>2.02</v>
       </c>
       <c r="S45">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="T45">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="U45">
-        <v>3.06</v>
+        <v>2.7</v>
       </c>
       <c r="V45">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W45">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X45">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="Z45">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AA45">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="AB45">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="AC45">
-        <v>3.69</v>
+        <v>3.09</v>
       </c>
       <c r="AD45">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AE45">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AF45">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AG45">
-        <v>1.93</v>
+        <v>2.11</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK45">
         <v>1.53</v>
@@ -7765,22 +7765,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="O46">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="P46">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="Q46">
-        <v>2.9</v>
+        <v>2.34</v>
       </c>
       <c r="R46">
-        <v>2.27</v>
+        <v>2.36</v>
       </c>
       <c r="S46">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="T46">
-        <v>3.11</v>
+        <v>3.75</v>
       </c>
       <c r="U46">
-        <v>2.73</v>
+        <v>2.18</v>
       </c>
       <c r="V46">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="W46">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X46">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="Z46">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="AA46">
-        <v>1.82</v>
+        <v>1.46</v>
       </c>
       <c r="AB46">
-        <v>1.93</v>
+        <v>2.38</v>
       </c>
       <c r="AC46">
-        <v>2.92</v>
+        <v>2.22</v>
       </c>
       <c r="AD46">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="AE46">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AF46">
-        <v>1.64</v>
+        <v>1.46</v>
       </c>
       <c r="AG46">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AK46">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7928,22 +7928,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,80 +7970,80 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O47">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P47">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q47">
-        <v>2.36</v>
+        <v>2.08</v>
       </c>
       <c r="R47">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="S47">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T47">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U47">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="V47">
         <v>1.62</v>
       </c>
       <c r="W47">
+        <v>1.13</v>
+      </c>
+      <c r="X47">
+        <v>1.02</v>
+      </c>
+      <c r="Y47">
         <v>1.12</v>
       </c>
-      <c r="X47">
-        <v>1.01</v>
-      </c>
-      <c r="Y47">
-        <v>1.11</v>
-      </c>
       <c r="Z47">
-        <v>4.9</v>
+        <v>4.65</v>
       </c>
       <c r="AA47">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AB47">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="AC47">
+        <v>2.27</v>
+      </c>
+      <c r="AD47">
+        <v>1.62</v>
+      </c>
+      <c r="AE47">
+        <v>1.24</v>
+      </c>
+      <c r="AF47">
+        <v>1.55</v>
+      </c>
+      <c r="AG47">
+        <v>2.3</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ47">
+        <v>1.23</v>
+      </c>
+      <c r="AK47">
         <v>2.25</v>
-      </c>
-      <c r="AD47">
-        <v>1.57</v>
-      </c>
-      <c r="AE47">
-        <v>1.19</v>
-      </c>
-      <c r="AF47">
-        <v>1.46</v>
-      </c>
-      <c r="AG47">
-        <v>2.45</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ47">
-        <v>1.19</v>
-      </c>
-      <c r="AK47">
-        <v>1.77</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G48">
@@ -8142,55 +8142,55 @@
         <v>0</v>
       </c>
       <c r="Q48">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="R48">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S48">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T48">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="U48">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="V48">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="W48">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X48">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y48">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z48">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AA48">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AB48">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AC48">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AD48">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE48">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AF48">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG48">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK48">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8254,22 +8254,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Muğlaspor</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8417,7 +8417,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Muğlaspor</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="O50">
-        <v>2.95</v>
+        <v>3.9</v>
       </c>
       <c r="P50">
-        <v>2.36</v>
+        <v>3.6</v>
       </c>
       <c r="Q50">
-        <v>4.32</v>
+        <v>2.35</v>
       </c>
       <c r="R50">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="S50">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="T50">
-        <v>2.33</v>
+        <v>4</v>
       </c>
       <c r="U50">
-        <v>3.03</v>
+        <v>2.05</v>
       </c>
       <c r="V50">
-        <v>1.32</v>
+        <v>1.66</v>
       </c>
       <c r="W50">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="X50">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="Z50">
-        <v>2.92</v>
+        <v>5</v>
       </c>
       <c r="AA50">
-        <v>2.04</v>
+        <v>1.43</v>
       </c>
       <c r="AB50">
-        <v>1.69</v>
+        <v>2.61</v>
       </c>
       <c r="AC50">
-        <v>3.34</v>
+        <v>2.15</v>
       </c>
       <c r="AD50">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="AE50">
-        <v>1.05</v>
+        <v>1.23</v>
       </c>
       <c r="AF50">
-        <v>1.76</v>
+        <v>1.44</v>
       </c>
       <c r="AG50">
-        <v>1.94</v>
+        <v>2.55</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="AK50">
-        <v>1.25</v>
+        <v>1.84</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8580,7 +8580,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
+        <v>4.2</v>
+      </c>
+      <c r="O51">
+        <v>3.35</v>
+      </c>
+      <c r="P51">
+        <v>1.83</v>
+      </c>
+      <c r="Q51">
+        <v>4.32</v>
+      </c>
+      <c r="R51">
+        <v>1.99</v>
+      </c>
+      <c r="S51">
+        <v>1.39</v>
+      </c>
+      <c r="T51">
+        <v>2.71</v>
+      </c>
+      <c r="U51">
+        <v>2.8</v>
+      </c>
+      <c r="V51">
+        <v>1.36</v>
+      </c>
+      <c r="W51">
+        <v>1.07</v>
+      </c>
+      <c r="X51">
+        <v>1.02</v>
+      </c>
+      <c r="Y51">
+        <v>1.33</v>
+      </c>
+      <c r="Z51">
+        <v>3.14</v>
+      </c>
+      <c r="AA51">
+        <v>2.05</v>
+      </c>
+      <c r="AB51">
         <v>1.71</v>
       </c>
-      <c r="O51">
-        <v>4.2</v>
-      </c>
-      <c r="P51">
-        <v>4.21</v>
-      </c>
-      <c r="Q51">
-        <v>2.15</v>
-      </c>
-      <c r="R51">
-        <v>2.67</v>
-      </c>
-      <c r="S51">
-        <v>1.22</v>
-      </c>
-      <c r="T51">
-        <v>3.66</v>
-      </c>
-      <c r="U51">
-        <v>2.06</v>
-      </c>
-      <c r="V51">
-        <v>1.66</v>
-      </c>
-      <c r="W51">
-        <v>1.15</v>
-      </c>
-      <c r="X51">
-        <v>1.01</v>
-      </c>
-      <c r="Y51">
-        <v>1.14</v>
-      </c>
-      <c r="Z51">
-        <v>5.66</v>
-      </c>
-      <c r="AA51">
-        <v>1.41</v>
-      </c>
-      <c r="AB51">
-        <v>2.63</v>
-      </c>
       <c r="AC51">
-        <v>2.13</v>
+        <v>3.5</v>
       </c>
       <c r="AD51">
-        <v>1.69</v>
+        <v>1.27</v>
       </c>
       <c r="AE51">
-        <v>1.28</v>
+        <v>1.04</v>
       </c>
       <c r="AF51">
-        <v>1.46</v>
+        <v>1.85</v>
       </c>
       <c r="AG51">
-        <v>2.49</v>
+        <v>1.83</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK51">
-        <v>2.05</v>
+        <v>1.18</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8743,7 +8743,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O52">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P52">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q52">
-        <v>5.24</v>
+        <v>0</v>
       </c>
       <c r="R52">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S52">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T52">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="U52">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="V52">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W52">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X52">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y52">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z52">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="AA52">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB52">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC52">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="AD52">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE52">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF52">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG52">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK52">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8906,7 +8906,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U53">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z53">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA53">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AD53">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF53">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG53">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK53">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Omonia 29is Maiou</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.37</v>
+        <v>6.4</v>
       </c>
       <c r="O54">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="P54">
-        <v>7.6</v>
+        <v>1.45</v>
       </c>
       <c r="Q54">
-        <v>1.8</v>
+        <v>6.5</v>
       </c>
       <c r="R54">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S54">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T54">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="U54">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V54">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="W54">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X54">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y54">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z54">
-        <v>3.86</v>
+        <v>3.5</v>
       </c>
       <c r="AA54">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="AB54">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AC54">
-        <v>2.7</v>
+        <v>2.97</v>
       </c>
       <c r="AD54">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE54">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF54">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AG54">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK54">
-        <v>3.12</v>
+        <v>1.06</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9286,7 +9286,7 @@
         <v>2.5</v>
       </c>
       <c r="R55">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S55">
         <v>1.29</v>
@@ -9295,34 +9295,34 @@
         <v>3.4</v>
       </c>
       <c r="U55">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="V55">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W55">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X55">
         <v>1.01</v>
       </c>
       <c r="Y55">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z55">
-        <v>4.44</v>
+        <v>4</v>
       </c>
       <c r="AA55">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AB55">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AC55">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="AD55">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AE55">
         <v>1.14</v>
@@ -9331,7 +9331,7 @@
         <v>1.54</v>
       </c>
       <c r="AG55">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK55">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="O57">
-        <v>4.85</v>
+        <v>5.15</v>
       </c>
       <c r="P57">
-        <v>6.79</v>
+        <v>7.09</v>
       </c>
       <c r="Q57">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="R57">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="S57">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="T57">
-        <v>3.9</v>
+        <v>4.25</v>
       </c>
       <c r="U57">
-        <v>2.07</v>
+        <v>1.97</v>
       </c>
       <c r="V57">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="W57">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X57">
         <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z57">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AA57">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="AB57">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="AC57">
-        <v>2.18</v>
+        <v>2.03</v>
       </c>
       <c r="AD57">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AE57">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AF57">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG57">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AK57">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -10095,52 +10095,52 @@
         <v>4</v>
       </c>
       <c r="P60">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q60">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="R60">
-        <v>2.48</v>
+        <v>2.65</v>
       </c>
       <c r="S60">
         <v>1.2</v>
       </c>
       <c r="T60">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="U60">
         <v>1.99</v>
       </c>
       <c r="V60">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="W60">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X60">
         <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Z60">
-        <v>6.25</v>
+        <v>6.15</v>
       </c>
       <c r="AA60">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AB60">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="AC60">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AD60">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AE60">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AF60">
         <v>1.36</v>
@@ -10162,7 +10162,7 @@
         <v>1.17</v>
       </c>
       <c r="AK60">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,7 +10252,7 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.35</v>
+        <v>2.42</v>
       </c>
       <c r="O61">
         <v>3.85</v>
@@ -10261,25 +10261,25 @@
         <v>2.4</v>
       </c>
       <c r="Q61">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="R61">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="S61">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="T61">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="U61">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V61">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="W61">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X61">
         <v>1.01</v>
@@ -10291,16 +10291,16 @@
         <v>6.13</v>
       </c>
       <c r="AA61">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AB61">
         <v>2.86</v>
       </c>
       <c r="AC61">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AD61">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AE61">
         <v>1.28</v>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK61">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10421,28 +10421,28 @@
         <v>3.9</v>
       </c>
       <c r="P62">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Q62">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="R62">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="S62">
         <v>1.25</v>
       </c>
       <c r="T62">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="U62">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="V62">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W62">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X62">
         <v>1.01</v>
@@ -10460,19 +10460,19 @@
         <v>2.32</v>
       </c>
       <c r="AC62">
-        <v>2.33</v>
+        <v>2.44</v>
       </c>
       <c r="AD62">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AE62">
         <v>1.17</v>
       </c>
       <c r="AF62">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG62">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK62">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="O64">
         <v>3.1</v>
       </c>
       <c r="P64">
-        <v>3.17</v>
+        <v>2.7</v>
       </c>
       <c r="Q64">
         <v>2.92</v>
@@ -10762,7 +10762,7 @@
         <v>2.67</v>
       </c>
       <c r="U64">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="V64">
         <v>1.35</v>
@@ -10771,19 +10771,19 @@
         <v>1.07</v>
       </c>
       <c r="X64">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y64">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z64">
         <v>3.04</v>
       </c>
       <c r="AA64">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AB64">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC64">
         <v>3.85</v>
@@ -10795,10 +10795,10 @@
         <v>1.05</v>
       </c>
       <c r="AF64">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AG64">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AK64">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10904,34 +10904,34 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="O65">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="P65">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="Q65">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R65">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="S65">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T65">
-        <v>3.3</v>
+        <v>2.82</v>
       </c>
       <c r="U65">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="V65">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W65">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X65">
         <v>1.02</v>
@@ -10940,28 +10940,28 @@
         <v>1.22</v>
       </c>
       <c r="Z65">
-        <v>3.91</v>
+        <v>3.86</v>
       </c>
       <c r="AA65">
         <v>1.73</v>
       </c>
       <c r="AB65">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="AC65">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="AD65">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE65">
         <v>1.11</v>
       </c>
       <c r="AF65">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG65">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -11067,31 +11067,31 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="O66">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P66">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="Q66">
-        <v>2.87</v>
+        <v>2.56</v>
       </c>
       <c r="R66">
         <v>2.29</v>
       </c>
       <c r="S66">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T66">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="U66">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="V66">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W66">
         <v>1.1</v>
@@ -11106,16 +11106,16 @@
         <v>3.86</v>
       </c>
       <c r="AA66">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AB66">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AC66">
-        <v>3.01</v>
+        <v>2.7</v>
       </c>
       <c r="AD66">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE66">
         <v>1.11</v>
@@ -11124,7 +11124,7 @@
         <v>1.67</v>
       </c>
       <c r="AG66">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK66">
         <v>1.53</v>
@@ -11233,13 +11233,13 @@
         <v>1.75</v>
       </c>
       <c r="O67">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="P67">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="Q67">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R67">
         <v>2.19</v>
@@ -11254,7 +11254,7 @@
         <v>2.42</v>
       </c>
       <c r="V67">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W67">
         <v>1.07</v>
@@ -11263,25 +11263,25 @@
         <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z67">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="AA67">
         <v>1.64</v>
       </c>
       <c r="AB67">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AC67">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="AD67">
         <v>1.4</v>
       </c>
       <c r="AE67">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF67">
         <v>1.65</v>
@@ -11300,7 +11300,7 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AK67">
         <v>2.02</v>
@@ -11393,10 +11393,10 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="O68">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P68">
         <v>3.45</v>
@@ -11405,13 +11405,13 @@
         <v>2.51</v>
       </c>
       <c r="R68">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="S68">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="T68">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="U68">
         <v>2.63</v>
@@ -11432,10 +11432,10 @@
         <v>3.4</v>
       </c>
       <c r="AA68">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="AB68">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AC68">
         <v>2.92</v>
@@ -11447,10 +11447,10 @@
         <v>1.08</v>
       </c>
       <c r="AF68">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG68">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK68">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11559,10 +11559,10 @@
         <v>2.15</v>
       </c>
       <c r="O69">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="P69">
-        <v>3</v>
+        <v>3.23</v>
       </c>
       <c r="Q69">
         <v>2.83</v>
@@ -11571,7 +11571,7 @@
         <v>2.03</v>
       </c>
       <c r="S69">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T69">
         <v>2.7</v>
@@ -11580,10 +11580,10 @@
         <v>3</v>
       </c>
       <c r="V69">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W69">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X69">
         <v>1.02</v>
@@ -11592,16 +11592,16 @@
         <v>1.31</v>
       </c>
       <c r="Z69">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="AA69">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AB69">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AC69">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AD69">
         <v>1.22</v>
@@ -11610,7 +11610,7 @@
         <v>1.05</v>
       </c>
       <c r="AF69">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG69">
         <v>1.88</v>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK69">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11719,31 +11719,31 @@
         </is>
       </c>
       <c r="N70">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="O70">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P70">
         <v>1.98</v>
       </c>
       <c r="Q70">
-        <v>3.7</v>
+        <v>4.11</v>
       </c>
       <c r="R70">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="S70">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T70">
         <v>3.2</v>
       </c>
       <c r="U70">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="V70">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W70">
         <v>1.08</v>
@@ -11761,7 +11761,7 @@
         <v>1.79</v>
       </c>
       <c r="AB70">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AC70">
         <v>2.95</v>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK70">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -12217,25 +12217,25 @@
         <v>0</v>
       </c>
       <c r="Q73">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="R73">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="S73">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T73">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="U73">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="V73">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="W73">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X73">
         <v>1.02</v>
@@ -12247,10 +12247,10 @@
         <v>4.1</v>
       </c>
       <c r="AA73">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AB73">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AC73">
         <v>2.52</v>
@@ -12262,10 +12262,10 @@
         <v>1.13</v>
       </c>
       <c r="AF73">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG73">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK73">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="O75">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P75">
-        <v>4.33</v>
+        <v>3.71</v>
       </c>
       <c r="Q75">
         <v>2.25</v>
@@ -12697,19 +12697,19 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="O76">
-        <v>4.15</v>
+        <v>3.85</v>
       </c>
       <c r="P76">
-        <v>4.15</v>
+        <v>4.78</v>
       </c>
       <c r="Q76">
         <v>2.15</v>
       </c>
       <c r="R76">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="S76">
         <v>1.22</v>
@@ -12730,13 +12730,13 @@
         <v>1.02</v>
       </c>
       <c r="Y76">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z76">
-        <v>6.03</v>
+        <v>6</v>
       </c>
       <c r="AA76">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AB76">
         <v>2.52</v>
@@ -12745,16 +12745,16 @@
         <v>2.02</v>
       </c>
       <c r="AD76">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AE76">
         <v>1.26</v>
       </c>
       <c r="AF76">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG76">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK76">
         <v>2.19</v>
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="O77">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="P77">
         <v>1.95</v>
       </c>
       <c r="Q77">
-        <v>3.5</v>
+        <v>2.91</v>
       </c>
       <c r="R77">
-        <v>2.45</v>
+        <v>2.86</v>
       </c>
       <c r="S77">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T77">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="U77">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V77">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="W77">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="X77">
         <v>1.01</v>
       </c>
       <c r="Y77">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Z77">
-        <v>6.36</v>
+        <v>8</v>
       </c>
       <c r="AA77">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AB77">
-        <v>2.87</v>
+        <v>3.58</v>
       </c>
       <c r="AC77">
-        <v>1.98</v>
+        <v>1.64</v>
       </c>
       <c r="AD77">
-        <v>1.84</v>
+        <v>2.08</v>
       </c>
       <c r="AE77">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AF77">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AG77">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK77">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13023,19 +13023,19 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="O78">
         <v>3.5</v>
       </c>
       <c r="P78">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q78">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="R78">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="S78">
         <v>1.22</v>
@@ -13044,10 +13044,10 @@
         <v>3.9</v>
       </c>
       <c r="U78">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V78">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W78">
         <v>1.18</v>
@@ -13059,28 +13059,28 @@
         <v>1.09</v>
       </c>
       <c r="Z78">
-        <v>5.26</v>
+        <v>5.4</v>
       </c>
       <c r="AA78">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB78">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="AC78">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AD78">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AE78">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF78">
         <v>1.4</v>
       </c>
       <c r="AG78">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13192,13 +13192,13 @@
         <v>3.6</v>
       </c>
       <c r="P79">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="Q79">
-        <v>3.1</v>
+        <v>3.48</v>
       </c>
       <c r="R79">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S79">
         <v>1.22</v>
@@ -13210,7 +13210,7 @@
         <v>2.1</v>
       </c>
       <c r="V79">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="W79">
         <v>1.18</v>
@@ -13228,13 +13228,13 @@
         <v>1.44</v>
       </c>
       <c r="AB79">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="AC79">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="AD79">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AE79">
         <v>1.25</v>
@@ -13259,7 +13259,7 @@
         <v>1.63</v>
       </c>
       <c r="AK79">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13349,22 +13349,22 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="O80">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P80">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q80">
-        <v>3.03</v>
+        <v>2.96</v>
       </c>
       <c r="R80">
-        <v>2.45</v>
+        <v>2.71</v>
       </c>
       <c r="S80">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="T80">
         <v>4.4</v>
@@ -13376,7 +13376,7 @@
         <v>1.8</v>
       </c>
       <c r="W80">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X80">
         <v>1.01</v>
@@ -13385,13 +13385,13 @@
         <v>1.05</v>
       </c>
       <c r="Z80">
-        <v>6.55</v>
+        <v>6.6</v>
       </c>
       <c r="AA80">
         <v>1.33</v>
       </c>
       <c r="AB80">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="AC80">
         <v>1.82</v>
@@ -13400,7 +13400,7 @@
         <v>1.91</v>
       </c>
       <c r="AE80">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AF80">
         <v>1.33</v>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AK80">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13518,13 +13518,13 @@
         <v>4</v>
       </c>
       <c r="P81">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="Q81">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="R81">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="S81">
         <v>1.22</v>
@@ -13533,10 +13533,10 @@
         <v>3.8</v>
       </c>
       <c r="U81">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="V81">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W81">
         <v>1.17</v>
@@ -13554,7 +13554,7 @@
         <v>1.47</v>
       </c>
       <c r="AB81">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="AC81">
         <v>2.17</v>
@@ -13582,7 +13582,7 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AK81">
         <v>2.25</v>
@@ -13675,19 +13675,19 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O82">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P82">
         <v>2.4</v>
       </c>
       <c r="Q82">
-        <v>2.76</v>
+        <v>2.98</v>
       </c>
       <c r="R82">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="S82">
         <v>1.25</v>
@@ -13696,7 +13696,7 @@
         <v>3.5</v>
       </c>
       <c r="U82">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="V82">
         <v>1.57</v>
@@ -13708,19 +13708,19 @@
         <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z82">
         <v>4.4</v>
       </c>
       <c r="AA82">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB82">
+        <v>2.2</v>
+      </c>
+      <c r="AC82">
         <v>2.35</v>
-      </c>
-      <c r="AC82">
-        <v>2.36</v>
       </c>
       <c r="AD82">
         <v>1.47</v>
@@ -13729,10 +13729,10 @@
         <v>1.19</v>
       </c>
       <c r="AF82">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AG82">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>1.25</v>
       </c>
       <c r="AK82">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13838,19 +13838,19 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="O83">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="P83">
         <v>3.8</v>
       </c>
       <c r="Q83">
-        <v>2.01</v>
+        <v>2.19</v>
       </c>
       <c r="R83">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="S83">
         <v>1.17</v>
@@ -13859,25 +13859,25 @@
         <v>4</v>
       </c>
       <c r="U83">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="V83">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="W83">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X83">
         <v>1.02</v>
       </c>
       <c r="Y83">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z83">
         <v>5.5</v>
       </c>
       <c r="AA83">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AB83">
         <v>2.65</v>
@@ -13895,7 +13895,7 @@
         <v>1.44</v>
       </c>
       <c r="AG83">
-        <v>2.63</v>
+        <v>2.58</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>1.2</v>
       </c>
       <c r="AK83">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14010,25 +14010,25 @@
         <v>2.1</v>
       </c>
       <c r="Q84">
-        <v>3.47</v>
+        <v>3.44</v>
       </c>
       <c r="R84">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="S84">
         <v>1.22</v>
       </c>
       <c r="T84">
-        <v>3.32</v>
+        <v>3.48</v>
       </c>
       <c r="U84">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V84">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W84">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X84">
         <v>1.02</v>
@@ -14037,28 +14037,28 @@
         <v>1.11</v>
       </c>
       <c r="Z84">
-        <v>5.25</v>
+        <v>4.95</v>
       </c>
       <c r="AA84">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AB84">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="AC84">
         <v>2.18</v>
       </c>
       <c r="AD84">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AE84">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AF84">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG84">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AK84">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14167,28 +14167,28 @@
         <v>2.2</v>
       </c>
       <c r="O85">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P85">
         <v>2.7</v>
       </c>
       <c r="Q85">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="R85">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="S85">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T85">
-        <v>3.74</v>
+        <v>4</v>
       </c>
       <c r="U85">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="V85">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="W85">
         <v>1.14</v>
@@ -14197,22 +14197,22 @@
         <v>1.02</v>
       </c>
       <c r="Y85">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z85">
         <v>5.2</v>
       </c>
       <c r="AA85">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AB85">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="AC85">
         <v>2.17</v>
       </c>
       <c r="AD85">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AE85">
         <v>1.21</v>
@@ -14221,7 +14221,7 @@
         <v>1.4</v>
       </c>
       <c r="AG85">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>1.22</v>
       </c>
       <c r="AK85">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14336,55 +14336,55 @@
         <v>2.9</v>
       </c>
       <c r="Q86">
-        <v>2.92</v>
+        <v>2.58</v>
       </c>
       <c r="R86">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="S86">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T86">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="U86">
-        <v>2.73</v>
+        <v>2.66</v>
       </c>
       <c r="V86">
         <v>1.4</v>
       </c>
       <c r="W86">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X86">
         <v>1.02</v>
       </c>
       <c r="Y86">
+        <v>1.29</v>
+      </c>
+      <c r="Z86">
+        <v>3.3</v>
+      </c>
+      <c r="AA86">
+        <v>1.9</v>
+      </c>
+      <c r="AB86">
+        <v>1.78</v>
+      </c>
+      <c r="AC86">
+        <v>3.56</v>
+      </c>
+      <c r="AD86">
         <v>1.28</v>
       </c>
-      <c r="Z86">
-        <v>3.08</v>
-      </c>
-      <c r="AA86">
-        <v>1.99</v>
-      </c>
-      <c r="AB86">
-        <v>1.79</v>
-      </c>
-      <c r="AC86">
-        <v>3.3</v>
-      </c>
-      <c r="AD86">
-        <v>1.27</v>
-      </c>
       <c r="AE86">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF86">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AG86">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AK86">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14490,34 +14490,34 @@
         </is>
       </c>
       <c r="N87">
+        <v>3.1</v>
+      </c>
+      <c r="O87">
         <v>3.2</v>
       </c>
-      <c r="O87">
-        <v>3.15</v>
-      </c>
       <c r="P87">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="Q87">
-        <v>3.94</v>
+        <v>4.1</v>
       </c>
       <c r="R87">
         <v>2</v>
       </c>
       <c r="S87">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T87">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="U87">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="V87">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W87">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X87">
         <v>1.01</v>
@@ -14526,7 +14526,7 @@
         <v>1.28</v>
       </c>
       <c r="Z87">
-        <v>3.21</v>
+        <v>3.08</v>
       </c>
       <c r="AA87">
         <v>2.05</v>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK87">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14662,25 +14662,25 @@
         <v>0</v>
       </c>
       <c r="Q88">
-        <v>2.07</v>
+        <v>1.91</v>
       </c>
       <c r="R88">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
       <c r="S88">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T88">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="U88">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="V88">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W88">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X88">
         <v>1.02</v>
@@ -14689,16 +14689,16 @@
         <v>1.14</v>
       </c>
       <c r="Z88">
-        <v>5.29</v>
+        <v>5</v>
       </c>
       <c r="AA88">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AB88">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AC88">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AD88">
         <v>1.61</v>
@@ -14707,10 +14707,10 @@
         <v>1.2</v>
       </c>
       <c r="AF88">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG88">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14726,7 +14726,7 @@
         <v>1.17</v>
       </c>
       <c r="AK88">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14819,22 +14819,22 @@
         <v>2.2</v>
       </c>
       <c r="O89">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P89">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="Q89">
-        <v>2.59</v>
+        <v>2.83</v>
       </c>
       <c r="R89">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="S89">
         <v>1.3</v>
       </c>
       <c r="T89">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
       <c r="U89">
         <v>2.63</v>
@@ -14855,16 +14855,16 @@
         <v>3.8</v>
       </c>
       <c r="AA89">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AB89">
         <v>2.03</v>
       </c>
       <c r="AC89">
-        <v>2.9</v>
+        <v>2.66</v>
       </c>
       <c r="AD89">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AE89">
         <v>1.12</v>
@@ -14873,7 +14873,7 @@
         <v>1.67</v>
       </c>
       <c r="AG89">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK89">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14982,31 +14982,31 @@
         <v>1.65</v>
       </c>
       <c r="O90">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="P90">
         <v>4.5</v>
       </c>
       <c r="Q90">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="R90">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="S90">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T90">
-        <v>3.8</v>
+        <v>3.48</v>
       </c>
       <c r="U90">
         <v>2.17</v>
       </c>
       <c r="V90">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="W90">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X90">
         <v>1.02</v>
@@ -15049,7 +15049,7 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK90">
         <v>2.15</v>
@@ -15142,34 +15142,34 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="O91">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P91">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q91">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="R91">
         <v>4.1</v>
       </c>
       <c r="S91">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="T91">
-        <v>6.7</v>
+        <v>6</v>
       </c>
       <c r="U91">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="V91">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="W91">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="X91">
         <v>1</v>
@@ -15181,25 +15181,25 @@
         <v>15.5</v>
       </c>
       <c r="AA91">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AB91">
-        <v>5.15</v>
+        <v>5.5</v>
       </c>
       <c r="AC91">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AD91">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="AE91">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AF91">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG91">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK91">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15311,43 +15311,43 @@
         <v>3.4</v>
       </c>
       <c r="P92">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="Q92">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R92">
         <v>2.18</v>
       </c>
       <c r="S92">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T92">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U92">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="V92">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W92">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X92">
         <v>1</v>
       </c>
       <c r="Y92">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z92">
-        <v>4</v>
+        <v>4.45</v>
       </c>
       <c r="AA92">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AB92">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AC92">
         <v>2.49</v>
@@ -15362,7 +15362,7 @@
         <v>1.53</v>
       </c>
       <c r="AG92">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK92">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15471,31 +15471,31 @@
         <v>2.15</v>
       </c>
       <c r="O93">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="P93">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="Q93">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="R93">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="S93">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T93">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="U93">
         <v>2.32</v>
       </c>
       <c r="V93">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="W93">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="X93">
         <v>1.02</v>
@@ -15507,10 +15507,10 @@
         <v>4.6</v>
       </c>
       <c r="AA93">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AB93">
-        <v>2.47</v>
+        <v>2.33</v>
       </c>
       <c r="AC93">
         <v>2.4</v>
@@ -15519,13 +15519,13 @@
         <v>1.61</v>
       </c>
       <c r="AE93">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AF93">
         <v>1.5</v>
       </c>
       <c r="AG93">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="AK93">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15637,25 +15637,25 @@
         <v>3.3</v>
       </c>
       <c r="P94">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="Q94">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="R94">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="S94">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T94">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="U94">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V94">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W94">
         <v>1.08</v>
@@ -15676,19 +15676,19 @@
         <v>2.05</v>
       </c>
       <c r="AC94">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AD94">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE94">
         <v>1.12</v>
       </c>
       <c r="AF94">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AG94">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK94">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15794,61 +15794,61 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="O95">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P95">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="Q95">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="R95">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="S95">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T95">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="U95">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="V95">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="W95">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X95">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y95">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z95">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="AA95">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AB95">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="AC95">
-        <v>2.43</v>
+        <v>2.56</v>
       </c>
       <c r="AD95">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE95">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF95">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG95">
         <v>2.25</v>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AK95">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15957,7 +15957,7 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="O96">
         <v>3.3</v>
@@ -15969,10 +15969,10 @@
         <v>2.76</v>
       </c>
       <c r="R96">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="S96">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T96">
         <v>2.84</v>
@@ -15990,10 +15990,10 @@
         <v>1</v>
       </c>
       <c r="Y96">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z96">
-        <v>3.55</v>
+        <v>3.34</v>
       </c>
       <c r="AA96">
         <v>1.9</v>
@@ -16030,7 +16030,7 @@
         <v>1.25</v>
       </c>
       <c r="AK96">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16126,16 +16126,16 @@
         <v>5</v>
       </c>
       <c r="P97">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="Q97">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="R97">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="S97">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T97">
         <v>3.72</v>
@@ -16153,13 +16153,13 @@
         <v>1.02</v>
       </c>
       <c r="Y97">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z97">
         <v>4.64</v>
       </c>
       <c r="AA97">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AB97">
         <v>2.3</v>
@@ -16177,7 +16177,7 @@
         <v>1.67</v>
       </c>
       <c r="AG97">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="O98">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P98">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q98">
         <v>4.62</v>
@@ -16298,13 +16298,13 @@
         <v>2.17</v>
       </c>
       <c r="S98">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T98">
         <v>3.1</v>
       </c>
       <c r="U98">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="V98">
         <v>1.44</v>
@@ -16325,7 +16325,7 @@
         <v>1.73</v>
       </c>
       <c r="AB98">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC98">
         <v>2.93</v>
@@ -16340,7 +16340,7 @@
         <v>1.67</v>
       </c>
       <c r="AG98">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.2</v>
+        <v>1.91</v>
       </c>
       <c r="AK98">
         <v>1.16</v>
@@ -16455,10 +16455,10 @@
         <v>5.7</v>
       </c>
       <c r="Q99">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="R99">
-        <v>2.69</v>
+        <v>2.35</v>
       </c>
       <c r="S99">
         <v>1.22</v>
@@ -16473,7 +16473,7 @@
         <v>1.62</v>
       </c>
       <c r="W99">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X99">
         <v>1.02</v>
@@ -16491,19 +16491,19 @@
         <v>2.35</v>
       </c>
       <c r="AC99">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="AD99">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AE99">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AF99">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AG99">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK99">
         <v>2.4</v>
@@ -16618,16 +16618,16 @@
         <v>3.1</v>
       </c>
       <c r="Q100">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="R100">
-        <v>2.29</v>
+        <v>2.05</v>
       </c>
       <c r="S100">
         <v>1.3</v>
       </c>
       <c r="T100">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="U100">
         <v>2.57</v>
@@ -16682,7 +16682,7 @@
         <v>1.33</v>
       </c>
       <c r="AK100">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16772,22 +16772,22 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.63</v>
+        <v>2.87</v>
       </c>
       <c r="O101">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="P101">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="Q101">
-        <v>3.55</v>
+        <v>3.47</v>
       </c>
       <c r="R101">
         <v>2.15</v>
       </c>
       <c r="S101">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T101">
         <v>2.94</v>
@@ -16799,37 +16799,37 @@
         <v>1.44</v>
       </c>
       <c r="W101">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X101">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y101">
         <v>1.27</v>
       </c>
       <c r="Z101">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="AA101">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AB101">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AC101">
         <v>2.95</v>
       </c>
       <c r="AD101">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE101">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF101">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AG101">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="O102">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P102">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -17098,34 +17098,34 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="O103">
         <v>3.8</v>
       </c>
       <c r="P103">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="Q103">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="R103">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="S103">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T103">
-        <v>3.9</v>
+        <v>3.84</v>
       </c>
       <c r="U103">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="V103">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="W103">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X103">
         <v>1.02</v>
@@ -17140,13 +17140,13 @@
         <v>1.5</v>
       </c>
       <c r="AB103">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="AC103">
         <v>2.28</v>
       </c>
       <c r="AD103">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AE103">
         <v>1.23</v>
@@ -17155,7 +17155,7 @@
         <v>1.44</v>
       </c>
       <c r="AG103">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.3</v>
+        <v>1.68</v>
       </c>
       <c r="AK103">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17424,31 +17424,31 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="O105">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="P105">
-        <v>5.6</v>
+        <v>5.75</v>
       </c>
       <c r="Q105">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="R105">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="S105">
         <v>1.23</v>
       </c>
       <c r="T105">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="U105">
-        <v>2.21</v>
+        <v>2.34</v>
       </c>
       <c r="V105">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W105">
         <v>1.13</v>
@@ -17466,7 +17466,7 @@
         <v>1.51</v>
       </c>
       <c r="AB105">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="AC105">
         <v>2.38</v>
@@ -17475,10 +17475,10 @@
         <v>1.54</v>
       </c>
       <c r="AE105">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AF105">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="AG105">
         <v>1.9</v>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AK105">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17587,34 +17587,34 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="O106">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="P106">
-        <v>7.35</v>
+        <v>7</v>
       </c>
       <c r="Q106">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="R106">
         <v>2.5</v>
       </c>
       <c r="S106">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T106">
         <v>3.32</v>
       </c>
       <c r="U106">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="V106">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="W106">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X106">
         <v>1.01</v>
@@ -17641,10 +17641,10 @@
         <v>1.14</v>
       </c>
       <c r="AF106">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AG106">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AK106">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17756,19 +17756,19 @@
         <v>3.46</v>
       </c>
       <c r="P107">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="Q107">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="R107">
         <v>2.1</v>
       </c>
       <c r="S107">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T107">
-        <v>2.89</v>
+        <v>2.79</v>
       </c>
       <c r="U107">
         <v>2.88</v>
@@ -17777,7 +17777,7 @@
         <v>1.4</v>
       </c>
       <c r="W107">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X107">
         <v>1.03</v>
@@ -17795,7 +17795,7 @@
         <v>1.85</v>
       </c>
       <c r="AC107">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="AD107">
         <v>1.32</v>
@@ -17804,7 +17804,7 @@
         <v>1.07</v>
       </c>
       <c r="AF107">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG107">
         <v>1.95</v>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK107">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17913,16 +17913,16 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="O108">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P108">
-        <v>3.67</v>
+        <v>4</v>
       </c>
       <c r="Q108">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="R108">
         <v>2.12</v>
@@ -17931,10 +17931,10 @@
         <v>1.33</v>
       </c>
       <c r="T108">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="U108">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="V108">
         <v>1.44</v>
@@ -17946,22 +17946,22 @@
         <v>1.03</v>
       </c>
       <c r="Y108">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="Z108">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="AA108">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AB108">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AC108">
-        <v>2.99</v>
+        <v>2.93</v>
       </c>
       <c r="AD108">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AE108">
         <v>1.08</v>
@@ -17970,7 +17970,7 @@
         <v>1.71</v>
       </c>
       <c r="AG108">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AK108">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O111">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="P111">
-        <v>0</v>
+        <v>5.79</v>
       </c>
       <c r="Q111">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="R111">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S111">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T111">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U111">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V111">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W111">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X111">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y111">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z111">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AA111">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB111">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC111">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD111">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE111">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF111">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG111">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK111">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18574,22 +18574,22 @@
         <v>4.5</v>
       </c>
       <c r="Q112">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R112">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="S112">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T112">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U112">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="V112">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="W112">
         <v>1.18</v>
@@ -18619,10 +18619,10 @@
         <v>1.25</v>
       </c>
       <c r="AF112">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG112">
-        <v>2.53</v>
+        <v>2.48</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>1.16</v>
       </c>
       <c r="AK112">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O113">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="P113">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q113">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="R113">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S113">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T113">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U113">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V113">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W113">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X113">
         <v>0</v>
       </c>
       <c r="Y113">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z113">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA113">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB113">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC113">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AD113">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE113">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF113">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG113">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK113">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="O114">
         <v>3.1</v>
       </c>
       <c r="P114">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q114">
-        <v>3.25</v>
+        <v>3.59</v>
       </c>
       <c r="R114">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S114">
+        <v>1.39</v>
+      </c>
+      <c r="T114">
+        <v>2.71</v>
+      </c>
+      <c r="U114">
+        <v>2.9</v>
+      </c>
+      <c r="V114">
         <v>1.36</v>
-      </c>
-      <c r="T114">
-        <v>2.88</v>
-      </c>
-      <c r="U114">
-        <v>3.09</v>
-      </c>
-      <c r="V114">
-        <v>1.33</v>
       </c>
       <c r="W114">
         <v>1.05</v>
       </c>
       <c r="X114">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y114">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z114">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="AA114">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="AB114">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AC114">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="AD114">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AE114">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF114">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AG114">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AK114">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="O117">
         <v>3.25</v>
       </c>
       <c r="P117">
-        <v>3.59</v>
+        <v>3.7</v>
       </c>
       <c r="Q117">
         <v>0</v>
@@ -19706,64 +19706,64 @@
         </is>
       </c>
       <c r="N119">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O119">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P119">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q119">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R119">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S119">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T119">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U119">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V119">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W119">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X119">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y119">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z119">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA119">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB119">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC119">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD119">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE119">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF119">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG119">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK119">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL119">
         <v>0</v>

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -4873,34 +4873,34 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="O28">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P28">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Q28">
-        <v>2.29</v>
+        <v>2.44</v>
       </c>
       <c r="R28">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="S28">
+        <v>1.4</v>
+      </c>
+      <c r="T28">
+        <v>2.89</v>
+      </c>
+      <c r="U28">
+        <v>2.98</v>
+      </c>
+      <c r="V28">
         <v>1.36</v>
       </c>
-      <c r="T28">
-        <v>2.7</v>
-      </c>
-      <c r="U28">
-        <v>2.8</v>
-      </c>
-      <c r="V28">
-        <v>1.35</v>
-      </c>
       <c r="W28">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X28">
         <v>1.01</v>
@@ -4909,16 +4909,16 @@
         <v>1.28</v>
       </c>
       <c r="Z28">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="AA28">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AB28">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AC28">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AD28">
         <v>1.24</v>
@@ -4927,7 +4927,7 @@
         <v>1.05</v>
       </c>
       <c r="AF28">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AG28">
         <v>1.86</v>
@@ -4946,7 +4946,7 @@
         <v>1.26</v>
       </c>
       <c r="AK28">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.26</v>
+        <v>1.75</v>
       </c>
       <c r="O65">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P65">
-        <v>2.87</v>
+        <v>4.6</v>
       </c>
       <c r="Q65">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="R65">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="S65">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T65">
-        <v>2.82</v>
+        <v>3.25</v>
       </c>
       <c r="U65">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="V65">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W65">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X65">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="Z65">
-        <v>3.86</v>
+        <v>4.25</v>
       </c>
       <c r="AA65">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AB65">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="AC65">
-        <v>2.93</v>
+        <v>2.75</v>
       </c>
       <c r="AD65">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE65">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF65">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG65">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AK65">
-        <v>1.55</v>
+        <v>2.02</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="O66">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P66">
+        <v>3.45</v>
+      </c>
+      <c r="Q66">
+        <v>2.51</v>
+      </c>
+      <c r="R66">
+        <v>2.26</v>
+      </c>
+      <c r="S66">
+        <v>1.39</v>
+      </c>
+      <c r="T66">
         <v>3</v>
       </c>
-      <c r="Q66">
-        <v>2.56</v>
-      </c>
-      <c r="R66">
-        <v>2.29</v>
-      </c>
-      <c r="S66">
-        <v>1.37</v>
-      </c>
-      <c r="T66">
-        <v>2.78</v>
-      </c>
       <c r="U66">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V66">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W66">
         <v>1.1</v>
       </c>
       <c r="X66">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y66">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z66">
-        <v>3.86</v>
+        <v>3.4</v>
       </c>
       <c r="AA66">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AB66">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AC66">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="AD66">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AE66">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF66">
         <v>1.67</v>
       </c>
       <c r="AG66">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AK66">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.75</v>
+        <v>2.26</v>
       </c>
       <c r="O67">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P67">
-        <v>4.6</v>
+        <v>2.87</v>
       </c>
       <c r="Q67">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="R67">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="S67">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T67">
-        <v>3.25</v>
+        <v>2.82</v>
       </c>
       <c r="U67">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="V67">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W67">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X67">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="Z67">
-        <v>4.25</v>
+        <v>3.86</v>
       </c>
       <c r="AA67">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AB67">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="AC67">
-        <v>2.75</v>
+        <v>2.93</v>
       </c>
       <c r="AD67">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE67">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF67">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG67">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AK67">
-        <v>2.02</v>
+        <v>1.55</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="O68">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P68">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="Q68">
-        <v>2.51</v>
+        <v>2.56</v>
       </c>
       <c r="R68">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="S68">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="T68">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="U68">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V68">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W68">
         <v>1.1</v>
       </c>
       <c r="X68">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y68">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z68">
-        <v>3.4</v>
+        <v>3.86</v>
       </c>
       <c r="AA68">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AB68">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="AC68">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="AD68">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AE68">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF68">
         <v>1.67</v>
       </c>
       <c r="AG68">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK68">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -12534,34 +12534,34 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="O75">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="P75">
         <v>3.71</v>
       </c>
       <c r="Q75">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="R75">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S75">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T75">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="U75">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="V75">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="W75">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X75">
         <v>1.03</v>
@@ -12573,16 +12573,16 @@
         <v>2.7</v>
       </c>
       <c r="AA75">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AB75">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AC75">
-        <v>4.19</v>
+        <v>4</v>
       </c>
       <c r="AD75">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AE75">
         <v>1.02</v>
@@ -12591,7 +12591,7 @@
         <v>2.06</v>
       </c>
       <c r="AG75">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK75">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.95</v>
+        <v>1.66</v>
       </c>
       <c r="O77">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="P77">
-        <v>1.95</v>
+        <v>3.8</v>
       </c>
       <c r="Q77">
-        <v>2.91</v>
+        <v>2.19</v>
       </c>
       <c r="R77">
-        <v>2.86</v>
+        <v>2.5</v>
       </c>
       <c r="S77">
         <v>1.17</v>
       </c>
       <c r="T77">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="U77">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="V77">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="W77">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="X77">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y77">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Z77">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="AA77">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AB77">
-        <v>3.58</v>
+        <v>2.65</v>
       </c>
       <c r="AC77">
-        <v>1.64</v>
+        <v>2.12</v>
       </c>
       <c r="AD77">
-        <v>2.08</v>
+        <v>1.7</v>
       </c>
       <c r="AE77">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AF77">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AG77">
-        <v>3.5</v>
+        <v>2.58</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK77">
-        <v>1.35</v>
+        <v>2.03</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,65 +13023,65 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.46</v>
+        <v>2.95</v>
       </c>
       <c r="O78">
+        <v>4</v>
+      </c>
+      <c r="P78">
+        <v>1.95</v>
+      </c>
+      <c r="Q78">
+        <v>2.91</v>
+      </c>
+      <c r="R78">
+        <v>2.86</v>
+      </c>
+      <c r="S78">
+        <v>1.17</v>
+      </c>
+      <c r="T78">
+        <v>4.8</v>
+      </c>
+      <c r="U78">
+        <v>2</v>
+      </c>
+      <c r="V78">
+        <v>1.91</v>
+      </c>
+      <c r="W78">
+        <v>1.29</v>
+      </c>
+      <c r="X78">
+        <v>1.01</v>
+      </c>
+      <c r="Y78">
+        <v>1.05</v>
+      </c>
+      <c r="Z78">
+        <v>8</v>
+      </c>
+      <c r="AA78">
+        <v>1.3</v>
+      </c>
+      <c r="AB78">
+        <v>3.58</v>
+      </c>
+      <c r="AC78">
+        <v>1.64</v>
+      </c>
+      <c r="AD78">
+        <v>2.08</v>
+      </c>
+      <c r="AE78">
+        <v>1.5</v>
+      </c>
+      <c r="AF78">
+        <v>1.25</v>
+      </c>
+      <c r="AG78">
         <v>3.5</v>
       </c>
-      <c r="P78">
-        <v>2.5</v>
-      </c>
-      <c r="Q78">
-        <v>2.89</v>
-      </c>
-      <c r="R78">
-        <v>2.52</v>
-      </c>
-      <c r="S78">
-        <v>1.22</v>
-      </c>
-      <c r="T78">
-        <v>3.9</v>
-      </c>
-      <c r="U78">
-        <v>2.16</v>
-      </c>
-      <c r="V78">
-        <v>1.66</v>
-      </c>
-      <c r="W78">
-        <v>1.18</v>
-      </c>
-      <c r="X78">
-        <v>1.02</v>
-      </c>
-      <c r="Y78">
-        <v>1.09</v>
-      </c>
-      <c r="Z78">
-        <v>5.4</v>
-      </c>
-      <c r="AA78">
-        <v>1.47</v>
-      </c>
-      <c r="AB78">
-        <v>2.57</v>
-      </c>
-      <c r="AC78">
-        <v>2.15</v>
-      </c>
-      <c r="AD78">
-        <v>1.68</v>
-      </c>
-      <c r="AE78">
-        <v>1.25</v>
-      </c>
-      <c r="AF78">
-        <v>1.4</v>
-      </c>
-      <c r="AG78">
-        <v>2.75</v>
-      </c>
       <c r="AH78" t="inlineStr">
         <is>
           <t>[]</t>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK78">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,31 +13186,31 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.7</v>
+        <v>2.46</v>
       </c>
       <c r="O79">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P79">
-        <v>2.01</v>
+        <v>2.5</v>
       </c>
       <c r="Q79">
-        <v>3.48</v>
+        <v>2.89</v>
       </c>
       <c r="R79">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="S79">
         <v>1.22</v>
       </c>
       <c r="T79">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U79">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="V79">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="W79">
         <v>1.18</v>
@@ -13222,19 +13222,19 @@
         <v>1.09</v>
       </c>
       <c r="Z79">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AA79">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB79">
-        <v>2.52</v>
+        <v>2.57</v>
       </c>
       <c r="AC79">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AD79">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AE79">
         <v>1.25</v>
@@ -13243,7 +13243,7 @@
         <v>1.4</v>
       </c>
       <c r="AG79">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.63</v>
+        <v>1.22</v>
       </c>
       <c r="AK79">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="O80">
         <v>3.6</v>
       </c>
       <c r="P80">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="Q80">
-        <v>2.96</v>
+        <v>3.48</v>
       </c>
       <c r="R80">
-        <v>2.71</v>
+        <v>2.45</v>
       </c>
       <c r="S80">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="T80">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="U80">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="V80">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="W80">
+        <v>1.18</v>
+      </c>
+      <c r="X80">
+        <v>1.02</v>
+      </c>
+      <c r="Y80">
+        <v>1.09</v>
+      </c>
+      <c r="Z80">
+        <v>5.3</v>
+      </c>
+      <c r="AA80">
+        <v>1.44</v>
+      </c>
+      <c r="AB80">
+        <v>2.52</v>
+      </c>
+      <c r="AC80">
+        <v>2.11</v>
+      </c>
+      <c r="AD80">
+        <v>1.67</v>
+      </c>
+      <c r="AE80">
         <v>1.25</v>
       </c>
-      <c r="X80">
-        <v>1.01</v>
-      </c>
-      <c r="Y80">
-        <v>1.05</v>
-      </c>
-      <c r="Z80">
-        <v>6.6</v>
-      </c>
-      <c r="AA80">
-        <v>1.33</v>
-      </c>
-      <c r="AB80">
-        <v>3.05</v>
-      </c>
-      <c r="AC80">
-        <v>1.82</v>
-      </c>
-      <c r="AD80">
-        <v>1.91</v>
-      </c>
-      <c r="AE80">
-        <v>1.36</v>
-      </c>
       <c r="AF80">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AG80">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="AK80">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.57</v>
+        <v>2.6</v>
       </c>
       <c r="O81">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="P81">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="Q81">
-        <v>2.1</v>
+        <v>2.96</v>
       </c>
       <c r="R81">
-        <v>2.38</v>
+        <v>2.71</v>
       </c>
       <c r="S81">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="T81">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="U81">
-        <v>2.17</v>
+        <v>1.91</v>
       </c>
       <c r="V81">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="W81">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X81">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Z81">
-        <v>5.75</v>
+        <v>6.6</v>
       </c>
       <c r="AA81">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AB81">
-        <v>2.46</v>
+        <v>3.05</v>
       </c>
       <c r="AC81">
-        <v>2.17</v>
+        <v>1.82</v>
       </c>
       <c r="AD81">
-        <v>1.63</v>
+        <v>1.91</v>
       </c>
       <c r="AE81">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AF81">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AG81">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.18</v>
+        <v>1.54</v>
       </c>
       <c r="AK81">
-        <v>2.25</v>
+        <v>1.44</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,80 +13675,80 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="O82">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P82">
+        <v>4.8</v>
+      </c>
+      <c r="Q82">
+        <v>2.1</v>
+      </c>
+      <c r="R82">
+        <v>2.38</v>
+      </c>
+      <c r="S82">
+        <v>1.22</v>
+      </c>
+      <c r="T82">
+        <v>3.8</v>
+      </c>
+      <c r="U82">
+        <v>2.17</v>
+      </c>
+      <c r="V82">
+        <v>1.67</v>
+      </c>
+      <c r="W82">
+        <v>1.17</v>
+      </c>
+      <c r="X82">
+        <v>1.02</v>
+      </c>
+      <c r="Y82">
+        <v>1.11</v>
+      </c>
+      <c r="Z82">
+        <v>5.75</v>
+      </c>
+      <c r="AA82">
+        <v>1.47</v>
+      </c>
+      <c r="AB82">
+        <v>2.46</v>
+      </c>
+      <c r="AC82">
+        <v>2.17</v>
+      </c>
+      <c r="AD82">
+        <v>1.63</v>
+      </c>
+      <c r="AE82">
+        <v>1.25</v>
+      </c>
+      <c r="AF82">
+        <v>1.5</v>
+      </c>
+      <c r="AG82">
         <v>2.4</v>
       </c>
-      <c r="Q82">
-        <v>2.98</v>
-      </c>
-      <c r="R82">
-        <v>2.23</v>
-      </c>
-      <c r="S82">
-        <v>1.25</v>
-      </c>
-      <c r="T82">
-        <v>3.5</v>
-      </c>
-      <c r="U82">
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ82">
+        <v>1.18</v>
+      </c>
+      <c r="AK82">
         <v>2.25</v>
-      </c>
-      <c r="V82">
-        <v>1.57</v>
-      </c>
-      <c r="W82">
-        <v>1.14</v>
-      </c>
-      <c r="X82">
-        <v>1.01</v>
-      </c>
-      <c r="Y82">
-        <v>1.17</v>
-      </c>
-      <c r="Z82">
-        <v>4.4</v>
-      </c>
-      <c r="AA82">
-        <v>1.6</v>
-      </c>
-      <c r="AB82">
-        <v>2.2</v>
-      </c>
-      <c r="AC82">
-        <v>2.35</v>
-      </c>
-      <c r="AD82">
-        <v>1.47</v>
-      </c>
-      <c r="AE82">
-        <v>1.19</v>
-      </c>
-      <c r="AF82">
-        <v>1.48</v>
-      </c>
-      <c r="AG82">
-        <v>2.43</v>
-      </c>
-      <c r="AH82" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI82" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ82">
-        <v>1.25</v>
-      </c>
-      <c r="AK82">
-        <v>1.47</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,80 +13838,80 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.66</v>
+        <v>2.5</v>
       </c>
       <c r="O83">
-        <v>4.05</v>
+        <v>3.5</v>
       </c>
       <c r="P83">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="Q83">
-        <v>2.19</v>
+        <v>2.98</v>
       </c>
       <c r="R83">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="S83">
+        <v>1.25</v>
+      </c>
+      <c r="T83">
+        <v>3.5</v>
+      </c>
+      <c r="U83">
+        <v>2.25</v>
+      </c>
+      <c r="V83">
+        <v>1.57</v>
+      </c>
+      <c r="W83">
+        <v>1.14</v>
+      </c>
+      <c r="X83">
+        <v>1.01</v>
+      </c>
+      <c r="Y83">
         <v>1.17</v>
       </c>
-      <c r="T83">
-        <v>4</v>
-      </c>
-      <c r="U83">
-        <v>2.11</v>
-      </c>
-      <c r="V83">
-        <v>1.72</v>
-      </c>
-      <c r="W83">
-        <v>1.15</v>
-      </c>
-      <c r="X83">
-        <v>1.02</v>
-      </c>
-      <c r="Y83">
-        <v>1.09</v>
-      </c>
       <c r="Z83">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA83">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AB83">
-        <v>2.65</v>
+        <v>2.2</v>
       </c>
       <c r="AC83">
-        <v>2.12</v>
+        <v>2.35</v>
       </c>
       <c r="AD83">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="AE83">
+        <v>1.19</v>
+      </c>
+      <c r="AF83">
+        <v>1.48</v>
+      </c>
+      <c r="AG83">
+        <v>2.43</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ83">
         <v>1.25</v>
       </c>
-      <c r="AF83">
-        <v>1.44</v>
-      </c>
-      <c r="AG83">
-        <v>2.58</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ83">
-        <v>1.2</v>
-      </c>
       <c r="AK83">
-        <v>2.03</v>
+        <v>1.47</v>
       </c>
       <c r="AL83">
         <v>0</v>

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -635,25 +635,25 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="O2">
-        <v>3.1</v>
+        <v>3.21</v>
       </c>
       <c r="P2">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="Q2">
-        <v>3.94</v>
+        <v>4.38</v>
       </c>
       <c r="R2">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="S2">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="T2">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="U2">
         <v>3.18</v>
@@ -668,10 +668,10 @@
         <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="Z2">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="AA2">
         <v>2.17</v>
@@ -680,19 +680,19 @@
         <v>1.61</v>
       </c>
       <c r="AC2">
-        <v>4.33</v>
+        <v>4.05</v>
       </c>
       <c r="AD2">
         <v>1.17</v>
       </c>
       <c r="AE2">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF2">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AG2">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK2">
         <v>1.22</v>
@@ -804,34 +804,34 @@
         <v>3.7</v>
       </c>
       <c r="P3">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="Q3">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="R3">
         <v>2.21</v>
       </c>
       <c r="S3">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T3">
         <v>2.94</v>
       </c>
       <c r="U3">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="V3">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W3">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X3">
         <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z3">
         <v>3.74</v>
@@ -843,7 +843,7 @@
         <v>1.99</v>
       </c>
       <c r="AC3">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AD3">
         <v>1.36</v>
@@ -855,7 +855,7 @@
         <v>1.68</v>
       </c>
       <c r="AG3">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1287,31 +1287,31 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="O6">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="P6">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="Q6">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="R6">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="S6">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T6">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="U6">
         <v>2.55</v>
       </c>
       <c r="V6">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W6">
         <v>1.09</v>
@@ -1329,7 +1329,7 @@
         <v>1.86</v>
       </c>
       <c r="AB6">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AC6">
         <v>3</v>
@@ -1360,7 +1360,7 @@
         <v>1.29</v>
       </c>
       <c r="AK6">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -2102,25 +2102,25 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="O11">
+        <v>3.2</v>
+      </c>
+      <c r="P11">
         <v>3.1</v>
       </c>
-      <c r="P11">
-        <v>3.15</v>
-      </c>
       <c r="Q11">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="R11">
-        <v>2.19</v>
+        <v>1.98</v>
       </c>
       <c r="S11">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T11">
-        <v>2.93</v>
+        <v>2.77</v>
       </c>
       <c r="U11">
         <v>2.69</v>
@@ -2138,13 +2138,13 @@
         <v>1.26</v>
       </c>
       <c r="Z11">
-        <v>3.37</v>
+        <v>3.2</v>
       </c>
       <c r="AA11">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AB11">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AC11">
         <v>3.2</v>
@@ -2153,13 +2153,13 @@
         <v>1.26</v>
       </c>
       <c r="AE11">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF11">
         <v>1.7</v>
       </c>
       <c r="AG11">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK11">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,19 +2265,19 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="O12">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="P12">
-        <v>3.02</v>
+        <v>2.95</v>
       </c>
       <c r="Q12">
         <v>3</v>
       </c>
       <c r="R12">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="S12">
         <v>1.41</v>
@@ -2307,7 +2307,7 @@
         <v>2.11</v>
       </c>
       <c r="AB12">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC12">
         <v>3.6</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2591,52 +2591,52 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="O14">
-        <v>4.95</v>
+        <v>4.6</v>
       </c>
       <c r="P14">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="Q14">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="R14">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="S14">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="T14">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="U14">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="V14">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="W14">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X14">
         <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z14">
-        <v>4.05</v>
+        <v>3.92</v>
       </c>
       <c r="AA14">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AB14">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AC14">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AD14">
         <v>1.38</v>
@@ -2648,7 +2648,7 @@
         <v>1.95</v>
       </c>
       <c r="AG14">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK14">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,7 +2754,7 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="O15">
         <v>3.25</v>
@@ -2763,37 +2763,37 @@
         <v>4</v>
       </c>
       <c r="Q15">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="R15">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="S15">
         <v>1.37</v>
       </c>
       <c r="T15">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="U15">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="V15">
         <v>1.34</v>
       </c>
       <c r="W15">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X15">
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z15">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="AA15">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AB15">
         <v>1.68</v>
@@ -2805,13 +2805,13 @@
         <v>1.21</v>
       </c>
       <c r="AE15">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF15">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG15">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AK15">
         <v>1.9</v>
@@ -3080,25 +3080,25 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="O17">
         <v>3.1</v>
       </c>
       <c r="P17">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="Q17">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="R17">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="S17">
         <v>1.45</v>
       </c>
       <c r="T17">
-        <v>2.58</v>
+        <v>2.51</v>
       </c>
       <c r="U17">
         <v>3.08</v>
@@ -3116,28 +3116,28 @@
         <v>1.38</v>
       </c>
       <c r="Z17">
-        <v>2.79</v>
+        <v>2.62</v>
       </c>
       <c r="AA17">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AB17">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AC17">
-        <v>4.28</v>
+        <v>4.05</v>
       </c>
       <c r="AD17">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE17">
         <v>1.02</v>
       </c>
       <c r="AF17">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AG17">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>1.36</v>
       </c>
       <c r="AK17">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,28 +3243,28 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="O18">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P18">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q18">
-        <v>3.47</v>
+        <v>3.54</v>
       </c>
       <c r="R18">
-        <v>2.11</v>
+        <v>1.94</v>
       </c>
       <c r="S18">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="T18">
         <v>2.5</v>
       </c>
       <c r="U18">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="V18">
         <v>1.31</v>
@@ -3282,7 +3282,7 @@
         <v>2.88</v>
       </c>
       <c r="AA18">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="AB18">
         <v>1.71</v>
@@ -3316,7 +3316,7 @@
         <v>1.36</v>
       </c>
       <c r="AK18">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3415,22 +3415,22 @@
         <v>0</v>
       </c>
       <c r="Q19">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="R19">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="S19">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="T19">
-        <v>3.13</v>
+        <v>3.08</v>
       </c>
       <c r="U19">
-        <v>2.53</v>
+        <v>2.48</v>
       </c>
       <c r="V19">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="W19">
         <v>1.08</v>
@@ -3439,31 +3439,31 @@
         <v>1</v>
       </c>
       <c r="Y19">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z19">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AA19">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AB19">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AC19">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AD19">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE19">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF19">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AG19">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>1.19</v>
       </c>
       <c r="AK19">
-        <v>2.89</v>
+        <v>2.82</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,7 +4058,7 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="O23">
         <v>3.2</v>
@@ -4073,10 +4073,10 @@
         <v>1.94</v>
       </c>
       <c r="S23">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T23">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="U23">
         <v>3</v>
@@ -4085,7 +4085,7 @@
         <v>1.33</v>
       </c>
       <c r="W23">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X23">
         <v>1.04</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AK23">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="N26">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="O26">
         <v>3.45</v>
@@ -4556,22 +4556,22 @@
         <v>1.75</v>
       </c>
       <c r="Q26">
-        <v>4.45</v>
+        <v>4.6</v>
       </c>
       <c r="R26">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="S26">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T26">
         <v>2.82</v>
       </c>
       <c r="U26">
-        <v>3.02</v>
+        <v>3.11</v>
       </c>
       <c r="V26">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W26">
         <v>1.03</v>
@@ -4580,16 +4580,16 @@
         <v>1.04</v>
       </c>
       <c r="Y26">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="Z26">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AA26">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AB26">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AC26">
         <v>3.68</v>
@@ -4604,7 +4604,7 @@
         <v>1.92</v>
       </c>
       <c r="AG26">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK26">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5045,13 +5045,13 @@
         <v>0</v>
       </c>
       <c r="Q29">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R29">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S29">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T29">
         <v>2.75</v>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AK29">
         <v>1.88</v>
@@ -5199,31 +5199,31 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="O30">
         <v>3.2</v>
       </c>
       <c r="P30">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="Q30">
         <v>2.65</v>
       </c>
       <c r="R30">
-        <v>2.09</v>
+        <v>1.94</v>
       </c>
       <c r="S30">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T30">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="U30">
-        <v>3.32</v>
+        <v>3.02</v>
       </c>
       <c r="V30">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W30">
         <v>1.04</v>
@@ -5232,31 +5232,31 @@
         <v>1.04</v>
       </c>
       <c r="Y30">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z30">
-        <v>2.87</v>
+        <v>2.66</v>
       </c>
       <c r="AA30">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="AB30">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AC30">
-        <v>3.88</v>
+        <v>4.13</v>
       </c>
       <c r="AD30">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AE30">
         <v>1.03</v>
       </c>
       <c r="AF30">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AG30">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>1.34</v>
       </c>
       <c r="AK30">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5534,55 +5534,55 @@
         <v>0</v>
       </c>
       <c r="Q32">
-        <v>2.69</v>
+        <v>2.48</v>
       </c>
       <c r="R32">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="S32">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="T32">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="U32">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="V32">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W32">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X32">
         <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z32">
-        <v>3.85</v>
+        <v>3.76</v>
       </c>
       <c r="AA32">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AB32">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AC32">
-        <v>2.87</v>
+        <v>2.74</v>
       </c>
       <c r="AD32">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AE32">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF32">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AG32">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>1.22</v>
       </c>
       <c r="AK32">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5697,25 +5697,25 @@
         <v>0</v>
       </c>
       <c r="Q33">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="R33">
         <v>2.3</v>
       </c>
       <c r="S33">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T33">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="U33">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V33">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W33">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X33">
         <v>1.03</v>
@@ -5724,28 +5724,28 @@
         <v>1.15</v>
       </c>
       <c r="Z33">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="AA33">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB33">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AC33">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="AD33">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AE33">
         <v>1.12</v>
       </c>
       <c r="AF33">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG33">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK33">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="O35">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="P35">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.16</v>
+        <v>3.05</v>
       </c>
       <c r="O36">
         <v>3.4</v>
       </c>
       <c r="P36">
-        <v>3.1</v>
+        <v>2.19</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.4</v>
+        <v>2.05</v>
       </c>
       <c r="O37">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P37">
-        <v>2.06</v>
+        <v>3.2</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="O38">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="P38">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6681,34 +6681,34 @@
         <v>2.25</v>
       </c>
       <c r="S39">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T39">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="U39">
         <v>2.38</v>
       </c>
       <c r="V39">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W39">
         <v>1.09</v>
       </c>
       <c r="X39">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z39">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="AA39">
         <v>1.62</v>
       </c>
       <c r="AB39">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AC39">
         <v>2.46</v>
@@ -6723,7 +6723,7 @@
         <v>1.51</v>
       </c>
       <c r="AG39">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK39">
         <v>1.5</v>
@@ -6835,13 +6835,13 @@
         <v>3.9</v>
       </c>
       <c r="P40">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="Q40">
-        <v>4</v>
+        <v>4.22</v>
       </c>
       <c r="R40">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="S40">
         <v>1.25</v>
@@ -6850,19 +6850,19 @@
         <v>3.5</v>
       </c>
       <c r="U40">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="V40">
         <v>1.55</v>
       </c>
       <c r="W40">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z40">
         <v>4.5</v>
@@ -6871,7 +6871,7 @@
         <v>1.57</v>
       </c>
       <c r="AB40">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="AC40">
         <v>2.35</v>
@@ -6902,7 +6902,7 @@
         <v>1.21</v>
       </c>
       <c r="AK40">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.7</v>
+        <v>2.43</v>
       </c>
       <c r="O42">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="P42">
-        <v>2.41</v>
+        <v>2.18</v>
       </c>
       <c r="Q42">
-        <v>3.1</v>
+        <v>2.77</v>
       </c>
       <c r="R42">
         <v>2.32</v>
       </c>
       <c r="S42">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="T42">
-        <v>4</v>
+        <v>3.48</v>
       </c>
       <c r="U42">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="V42">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="W42">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X42">
         <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z42">
-        <v>4.95</v>
+        <v>5.2</v>
       </c>
       <c r="AA42">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AB42">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="AC42">
         <v>2.08</v>
       </c>
       <c r="AD42">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AE42">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AF42">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AG42">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.57</v>
+        <v>1.26</v>
       </c>
       <c r="AK42">
         <v>1.44</v>
@@ -7318,22 +7318,22 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="O43">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="P43">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Q43">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="R43">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="S43">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T43">
         <v>3.8</v>
@@ -7342,7 +7342,7 @@
         <v>2.06</v>
       </c>
       <c r="V43">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="W43">
         <v>1.17</v>
@@ -7354,28 +7354,28 @@
         <v>1.1</v>
       </c>
       <c r="Z43">
-        <v>5.05</v>
+        <v>5.1</v>
       </c>
       <c r="AA43">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AB43">
-        <v>2.69</v>
+        <v>2.6</v>
       </c>
       <c r="AC43">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="AD43">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AE43">
         <v>1.24</v>
       </c>
       <c r="AF43">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AG43">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK43">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,16 +7481,16 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="O44">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P44">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="Q44">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="R44">
         <v>2.05</v>
@@ -7499,31 +7499,31 @@
         <v>1.37</v>
       </c>
       <c r="T44">
-        <v>2.56</v>
+        <v>2.79</v>
       </c>
       <c r="U44">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="V44">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W44">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X44">
         <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="Z44">
-        <v>3.13</v>
+        <v>3.04</v>
       </c>
       <c r="AA44">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="AB44">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AC44">
         <v>3.5</v>
@@ -7535,10 +7535,10 @@
         <v>1.04</v>
       </c>
       <c r="AF44">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG44">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="AK44">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,22 +7644,22 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="O45">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="P45">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="Q45">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="R45">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="S45">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T45">
         <v>2.78</v>
@@ -7677,31 +7677,31 @@
         <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z45">
         <v>3.5</v>
       </c>
       <c r="AA45">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AB45">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AC45">
         <v>3.09</v>
       </c>
       <c r="AD45">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE45">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF45">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG45">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7807,16 +7807,16 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="O46">
         <v>3.7</v>
       </c>
       <c r="P46">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q46">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R46">
         <v>2.36</v>
@@ -7825,7 +7825,7 @@
         <v>1.22</v>
       </c>
       <c r="T46">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U46">
         <v>2.18</v>
@@ -7834,7 +7834,7 @@
         <v>1.58</v>
       </c>
       <c r="W46">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X46">
         <v>1.01</v>
@@ -7979,7 +7979,7 @@
         <v>0</v>
       </c>
       <c r="Q47">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="R47">
         <v>2.38</v>
@@ -7988,16 +7988,16 @@
         <v>1.25</v>
       </c>
       <c r="T47">
-        <v>3.6</v>
+        <v>3.32</v>
       </c>
       <c r="U47">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="V47">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="W47">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X47">
         <v>1.02</v>
@@ -8009,19 +8009,19 @@
         <v>4.65</v>
       </c>
       <c r="AA47">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AB47">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="AC47">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
       <c r="AD47">
         <v>1.62</v>
       </c>
       <c r="AE47">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AF47">
         <v>1.55</v>
@@ -8043,7 +8043,7 @@
         <v>1.23</v>
       </c>
       <c r="AK47">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
+        <v>3</v>
+      </c>
+      <c r="O49">
         <v>2.9</v>
-      </c>
-      <c r="O49">
-        <v>3</v>
       </c>
       <c r="P49">
         <v>2.25</v>
       </c>
       <c r="Q49">
-        <v>3.75</v>
+        <v>4.27</v>
       </c>
       <c r="R49">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S49">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="T49">
-        <v>2.8</v>
+        <v>2.32</v>
       </c>
       <c r="U49">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="V49">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W49">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X49">
         <v>1.04</v>
       </c>
       <c r="Y49">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z49">
-        <v>2.97</v>
+        <v>3.29</v>
       </c>
       <c r="AA49">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AB49">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AC49">
-        <v>3.8</v>
+        <v>3.34</v>
       </c>
       <c r="AD49">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE49">
         <v>1.05</v>
       </c>
       <c r="AF49">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AG49">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8462,61 +8462,61 @@
         <v>1.8</v>
       </c>
       <c r="O50">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P50">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q50">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="R50">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="S50">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="T50">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="U50">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="V50">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="W50">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X50">
         <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z50">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AA50">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AB50">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="AC50">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AD50">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AE50">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AF50">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AG50">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK50">
         <v>1.84</v>
@@ -8622,19 +8622,19 @@
         </is>
       </c>
       <c r="N51">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="O51">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P51">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="Q51">
-        <v>4.32</v>
+        <v>5.19</v>
       </c>
       <c r="R51">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="S51">
         <v>1.39</v>
@@ -8643,43 +8643,43 @@
         <v>2.71</v>
       </c>
       <c r="U51">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="V51">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W51">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X51">
         <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z51">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="AA51">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AB51">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AC51">
         <v>3.5</v>
       </c>
       <c r="AD51">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE51">
         <v>1.04</v>
       </c>
       <c r="AF51">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AG51">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK51">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8957,22 +8957,22 @@
         <v>8.4</v>
       </c>
       <c r="Q53">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="R53">
         <v>2.35</v>
       </c>
       <c r="S53">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T53">
-        <v>3.25</v>
+        <v>3.02</v>
       </c>
       <c r="U53">
         <v>2.5</v>
       </c>
       <c r="V53">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W53">
         <v>1.11</v>
@@ -8990,7 +8990,7 @@
         <v>1.72</v>
       </c>
       <c r="AB53">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AC53">
         <v>2.69</v>
@@ -9002,7 +9002,7 @@
         <v>1.11</v>
       </c>
       <c r="AF53">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AG53">
         <v>1.67</v>
@@ -9021,7 +9021,7 @@
         <v>1.14</v>
       </c>
       <c r="AK53">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9120,16 +9120,16 @@
         <v>1.45</v>
       </c>
       <c r="Q54">
-        <v>6.5</v>
+        <v>7.43</v>
       </c>
       <c r="R54">
         <v>2.3</v>
       </c>
       <c r="S54">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T54">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="U54">
         <v>2.63</v>
@@ -9138,7 +9138,7 @@
         <v>1.41</v>
       </c>
       <c r="W54">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X54">
         <v>1</v>
@@ -9150,10 +9150,10 @@
         <v>3.5</v>
       </c>
       <c r="AA54">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AB54">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC54">
         <v>2.97</v>
@@ -9165,10 +9165,10 @@
         <v>1.07</v>
       </c>
       <c r="AF54">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="AG54">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK54">
         <v>1.06</v>
@@ -9283,25 +9283,25 @@
         <v>0</v>
       </c>
       <c r="Q55">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="R55">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="S55">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="T55">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="U55">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="V55">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="W55">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X55">
         <v>1.01</v>
@@ -9313,7 +9313,7 @@
         <v>4</v>
       </c>
       <c r="AA55">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AB55">
         <v>2.1</v>
@@ -9322,7 +9322,7 @@
         <v>2.49</v>
       </c>
       <c r="AD55">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AE55">
         <v>1.14</v>
@@ -9331,7 +9331,7 @@
         <v>1.54</v>
       </c>
       <c r="AG55">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK55">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="O57">
-        <v>5.15</v>
+        <v>5.05</v>
       </c>
       <c r="P57">
-        <v>7.09</v>
+        <v>7.08</v>
       </c>
       <c r="Q57">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="R57">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="S57">
         <v>1.16</v>
       </c>
       <c r="T57">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="U57">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="V57">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="W57">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X57">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y57">
         <v>1.08</v>
       </c>
       <c r="Z57">
-        <v>6</v>
+        <v>5.55</v>
       </c>
       <c r="AA57">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AB57">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AC57">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AD57">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AE57">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AF57">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AG57">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AK57">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -10095,19 +10095,19 @@
         <v>4</v>
       </c>
       <c r="P60">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="Q60">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="R60">
-        <v>2.65</v>
+        <v>2.42</v>
       </c>
       <c r="S60">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T60">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="U60">
         <v>1.99</v>
@@ -10122,7 +10122,7 @@
         <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="Z60">
         <v>6.15</v>
@@ -10137,7 +10137,7 @@
         <v>2</v>
       </c>
       <c r="AD60">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AE60">
         <v>1.28</v>
@@ -10258,7 +10258,7 @@
         <v>3.85</v>
       </c>
       <c r="P61">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q61">
         <v>2.79</v>
@@ -10273,7 +10273,7 @@
         <v>4.25</v>
       </c>
       <c r="U61">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="V61">
         <v>1.74</v>
@@ -10285,13 +10285,13 @@
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z61">
-        <v>6.13</v>
+        <v>5.8</v>
       </c>
       <c r="AA61">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AB61">
         <v>2.86</v>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK61">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="O62">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P62">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Q62">
         <v>2.2</v>
@@ -10430,16 +10430,16 @@
         <v>2.32</v>
       </c>
       <c r="S62">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T62">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="U62">
         <v>2.25</v>
       </c>
       <c r="V62">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="W62">
         <v>1.11</v>
@@ -10451,16 +10451,16 @@
         <v>1.14</v>
       </c>
       <c r="Z62">
-        <v>4.61</v>
+        <v>4.35</v>
       </c>
       <c r="AA62">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AB62">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="AC62">
-        <v>2.44</v>
+        <v>2.33</v>
       </c>
       <c r="AD62">
         <v>1.48</v>
@@ -10472,7 +10472,7 @@
         <v>1.56</v>
       </c>
       <c r="AG62">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK62">
         <v>1.97</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.45</v>
+        <v>1.96</v>
       </c>
       <c r="O64">
-        <v>3.1</v>
+        <v>3.23</v>
       </c>
       <c r="P64">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="Q64">
-        <v>2.92</v>
+        <v>2.67</v>
       </c>
       <c r="R64">
         <v>2.14</v>
       </c>
       <c r="S64">
+        <v>1.35</v>
+      </c>
+      <c r="T64">
+        <v>2.88</v>
+      </c>
+      <c r="U64">
+        <v>2.67</v>
+      </c>
+      <c r="V64">
         <v>1.4</v>
       </c>
-      <c r="T64">
-        <v>2.67</v>
-      </c>
-      <c r="U64">
-        <v>3</v>
-      </c>
-      <c r="V64">
-        <v>1.35</v>
-      </c>
       <c r="W64">
+        <v>1.05</v>
+      </c>
+      <c r="X64">
+        <v>1.01</v>
+      </c>
+      <c r="Y64">
+        <v>1.28</v>
+      </c>
+      <c r="Z64">
+        <v>3.58</v>
+      </c>
+      <c r="AA64">
+        <v>1.94</v>
+      </c>
+      <c r="AB64">
+        <v>1.9</v>
+      </c>
+      <c r="AC64">
+        <v>3.04</v>
+      </c>
+      <c r="AD64">
+        <v>1.29</v>
+      </c>
+      <c r="AE64">
         <v>1.07</v>
       </c>
-      <c r="X64">
-        <v>1.02</v>
-      </c>
-      <c r="Y64">
-        <v>1.29</v>
-      </c>
-      <c r="Z64">
-        <v>3.04</v>
-      </c>
-      <c r="AA64">
-        <v>2.03</v>
-      </c>
-      <c r="AB64">
-        <v>1.7</v>
-      </c>
-      <c r="AC64">
-        <v>3.85</v>
-      </c>
-      <c r="AD64">
-        <v>1.23</v>
-      </c>
-      <c r="AE64">
-        <v>1.05</v>
-      </c>
       <c r="AF64">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="AG64">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK64">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="O65">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="P65">
-        <v>4.6</v>
+        <v>2.68</v>
       </c>
       <c r="Q65">
-        <v>2.3</v>
+        <v>2.93</v>
       </c>
       <c r="R65">
-        <v>2.19</v>
+        <v>1.98</v>
       </c>
       <c r="S65">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T65">
-        <v>3.25</v>
+        <v>2.67</v>
       </c>
       <c r="U65">
-        <v>2.42</v>
+        <v>2.82</v>
       </c>
       <c r="V65">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="W65">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X65">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="Z65">
-        <v>4.25</v>
+        <v>3.04</v>
       </c>
       <c r="AA65">
-        <v>1.64</v>
+        <v>2.15</v>
       </c>
       <c r="AB65">
-        <v>2.02</v>
+        <v>1.66</v>
       </c>
       <c r="AC65">
-        <v>2.75</v>
+        <v>3.42</v>
       </c>
       <c r="AD65">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="AE65">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AF65">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AG65">
-        <v>2.16</v>
+        <v>1.93</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="AK65">
-        <v>2.02</v>
+        <v>1.6</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
+        <v>1.75</v>
+      </c>
+      <c r="O66">
+        <v>3.35</v>
+      </c>
+      <c r="P66">
+        <v>3.25</v>
+      </c>
+      <c r="Q66">
+        <v>2.32</v>
+      </c>
+      <c r="R66">
+        <v>2.21</v>
+      </c>
+      <c r="S66">
+        <v>1.31</v>
+      </c>
+      <c r="T66">
+        <v>3.08</v>
+      </c>
+      <c r="U66">
+        <v>2.52</v>
+      </c>
+      <c r="V66">
+        <v>1.44</v>
+      </c>
+      <c r="W66">
+        <v>1.06</v>
+      </c>
+      <c r="X66">
+        <v>1.02</v>
+      </c>
+      <c r="Y66">
+        <v>1.17</v>
+      </c>
+      <c r="Z66">
+        <v>3.95</v>
+      </c>
+      <c r="AA66">
+        <v>1.71</v>
+      </c>
+      <c r="AB66">
         <v>2.1</v>
       </c>
-      <c r="O66">
-        <v>3.5</v>
-      </c>
-      <c r="P66">
-        <v>3.45</v>
-      </c>
-      <c r="Q66">
-        <v>2.51</v>
-      </c>
-      <c r="R66">
-        <v>2.26</v>
-      </c>
-      <c r="S66">
-        <v>1.39</v>
-      </c>
-      <c r="T66">
-        <v>3</v>
-      </c>
-      <c r="U66">
-        <v>2.63</v>
-      </c>
-      <c r="V66">
-        <v>1.41</v>
-      </c>
-      <c r="W66">
+      <c r="AC66">
+        <v>2.69</v>
+      </c>
+      <c r="AD66">
+        <v>1.36</v>
+      </c>
+      <c r="AE66">
         <v>1.1</v>
       </c>
-      <c r="X66">
-        <v>1.03</v>
-      </c>
-      <c r="Y66">
-        <v>1.29</v>
-      </c>
-      <c r="Z66">
-        <v>3.4</v>
-      </c>
-      <c r="AA66">
-        <v>1.82</v>
-      </c>
-      <c r="AB66">
-        <v>1.92</v>
-      </c>
-      <c r="AC66">
-        <v>2.92</v>
-      </c>
-      <c r="AD66">
-        <v>1.29</v>
-      </c>
-      <c r="AE66">
-        <v>1.08</v>
-      </c>
       <c r="AF66">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG66">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK66">
-        <v>1.65</v>
+        <v>1.99</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11236,25 +11236,25 @@
         <v>3.5</v>
       </c>
       <c r="P67">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="Q67">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="R67">
         <v>2.17</v>
       </c>
       <c r="S67">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T67">
-        <v>2.82</v>
+        <v>3.14</v>
       </c>
       <c r="U67">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="V67">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W67">
         <v>1.09</v>
@@ -11263,19 +11263,19 @@
         <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z67">
         <v>3.86</v>
       </c>
       <c r="AA67">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AB67">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AC67">
-        <v>2.93</v>
+        <v>2.66</v>
       </c>
       <c r="AD67">
         <v>1.37</v>
@@ -11284,10 +11284,10 @@
         <v>1.11</v>
       </c>
       <c r="AF67">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AG67">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK67">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,31 +11393,31 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="O68">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P68">
-        <v>3</v>
+        <v>2.52</v>
       </c>
       <c r="Q68">
         <v>2.56</v>
       </c>
       <c r="R68">
-        <v>2.29</v>
+        <v>2.11</v>
       </c>
       <c r="S68">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T68">
-        <v>2.78</v>
+        <v>2.97</v>
       </c>
       <c r="U68">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="V68">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W68">
         <v>1.1</v>
@@ -11429,13 +11429,13 @@
         <v>1.25</v>
       </c>
       <c r="Z68">
-        <v>3.86</v>
+        <v>3.58</v>
       </c>
       <c r="AA68">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AB68">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AC68">
         <v>2.7</v>
@@ -11447,10 +11447,10 @@
         <v>1.11</v>
       </c>
       <c r="AF68">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AG68">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AK68">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="O69">
-        <v>3.24</v>
+        <v>3.03</v>
       </c>
       <c r="P69">
-        <v>3.23</v>
+        <v>2.65</v>
       </c>
       <c r="Q69">
         <v>2.83</v>
@@ -11571,34 +11571,34 @@
         <v>2.03</v>
       </c>
       <c r="S69">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T69">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="U69">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="V69">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W69">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X69">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y69">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="Z69">
         <v>2.92</v>
       </c>
       <c r="AA69">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AB69">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AC69">
         <v>3.5</v>
@@ -11610,7 +11610,7 @@
         <v>1.05</v>
       </c>
       <c r="AF69">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AG69">
         <v>1.88</v>
@@ -11629,7 +11629,7 @@
         <v>1.31</v>
       </c>
       <c r="AK69">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="O70">
         <v>3.3</v>
       </c>
       <c r="P70">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="Q70">
         <v>4.11</v>
       </c>
       <c r="R70">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="S70">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T70">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="U70">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="V70">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W70">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X70">
         <v>1</v>
       </c>
       <c r="Y70">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z70">
-        <v>3.78</v>
+        <v>3.84</v>
       </c>
       <c r="AA70">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="AB70">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AC70">
-        <v>2.95</v>
+        <v>2.59</v>
       </c>
       <c r="AD70">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AE70">
         <v>1.12</v>
       </c>
       <c r="AF70">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG70">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -12217,25 +12217,25 @@
         <v>0</v>
       </c>
       <c r="Q73">
-        <v>2.66</v>
+        <v>2.59</v>
       </c>
       <c r="R73">
         <v>2.2</v>
       </c>
       <c r="S73">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T73">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="U73">
         <v>2.34</v>
       </c>
       <c r="V73">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="W73">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X73">
         <v>1.02</v>
@@ -12262,10 +12262,10 @@
         <v>1.13</v>
       </c>
       <c r="AF73">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG73">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK73">
         <v>1.57</v>
@@ -12697,34 +12697,34 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="O76">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="P76">
-        <v>4.78</v>
+        <v>4.7</v>
       </c>
       <c r="Q76">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="R76">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="S76">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T76">
-        <v>3.48</v>
+        <v>4</v>
       </c>
       <c r="U76">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="V76">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="W76">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X76">
         <v>1.02</v>
@@ -12736,10 +12736,10 @@
         <v>6</v>
       </c>
       <c r="AA76">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AB76">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="AC76">
         <v>2.02</v>
@@ -12748,10 +12748,10 @@
         <v>1.68</v>
       </c>
       <c r="AE76">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF76">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AG76">
         <v>2.55</v>
@@ -12770,7 +12770,7 @@
         <v>1.17</v>
       </c>
       <c r="AK76">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12860,10 +12860,10 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="O77">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="P77">
         <v>3.8</v>
@@ -12872,37 +12872,37 @@
         <v>2.19</v>
       </c>
       <c r="R77">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="S77">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T77">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="U77">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="V77">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="W77">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X77">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y77">
         <v>1.09</v>
       </c>
       <c r="Z77">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="AA77">
         <v>1.4</v>
       </c>
       <c r="AB77">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AC77">
         <v>2.12</v>
@@ -12911,13 +12911,13 @@
         <v>1.7</v>
       </c>
       <c r="AE77">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF77">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AG77">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK77">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13023,34 +13023,34 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="O78">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P78">
         <v>1.95</v>
       </c>
       <c r="Q78">
-        <v>2.91</v>
+        <v>3.62</v>
       </c>
       <c r="R78">
-        <v>2.86</v>
+        <v>2.45</v>
       </c>
       <c r="S78">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T78">
-        <v>4.8</v>
+        <v>3.98</v>
       </c>
       <c r="U78">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="V78">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="W78">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="X78">
         <v>1.01</v>
@@ -13059,28 +13059,28 @@
         <v>1.05</v>
       </c>
       <c r="Z78">
-        <v>8</v>
+        <v>6.45</v>
       </c>
       <c r="AA78">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AB78">
-        <v>3.58</v>
+        <v>2.97</v>
       </c>
       <c r="AC78">
-        <v>1.64</v>
+        <v>1.88</v>
       </c>
       <c r="AD78">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="AE78">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="AF78">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AG78">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK78">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13186,34 +13186,34 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="O79">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P79">
         <v>2.5</v>
       </c>
       <c r="Q79">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="R79">
-        <v>2.52</v>
+        <v>2.28</v>
       </c>
       <c r="S79">
         <v>1.22</v>
       </c>
       <c r="T79">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="U79">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V79">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="W79">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="X79">
         <v>1.02</v>
@@ -13222,22 +13222,22 @@
         <v>1.09</v>
       </c>
       <c r="Z79">
-        <v>5.4</v>
+        <v>5.35</v>
       </c>
       <c r="AA79">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AB79">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AC79">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AD79">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AE79">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF79">
         <v>1.4</v>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK79">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13349,25 +13349,25 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="O80">
         <v>3.6</v>
       </c>
       <c r="P80">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="Q80">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="R80">
-        <v>2.45</v>
+        <v>2.54</v>
       </c>
       <c r="S80">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T80">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U80">
         <v>2.1</v>
@@ -13376,7 +13376,7 @@
         <v>1.69</v>
       </c>
       <c r="W80">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X80">
         <v>1.02</v>
@@ -13385,13 +13385,13 @@
         <v>1.09</v>
       </c>
       <c r="Z80">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AA80">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB80">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="AC80">
         <v>2.11</v>
@@ -13400,13 +13400,13 @@
         <v>1.67</v>
       </c>
       <c r="AE80">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF80">
         <v>1.4</v>
       </c>
       <c r="AG80">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.63</v>
+        <v>1.24</v>
       </c>
       <c r="AK80">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13521,25 +13521,25 @@
         <v>2.2</v>
       </c>
       <c r="Q81">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="R81">
-        <v>2.71</v>
+        <v>2.43</v>
       </c>
       <c r="S81">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="T81">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="U81">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="V81">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="W81">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X81">
         <v>1.01</v>
@@ -13548,28 +13548,28 @@
         <v>1.05</v>
       </c>
       <c r="Z81">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AA81">
         <v>1.33</v>
       </c>
       <c r="AB81">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="AC81">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AD81">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AE81">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AF81">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AG81">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.54</v>
+        <v>1.25</v>
       </c>
       <c r="AK81">
         <v>1.44</v>
@@ -13675,16 +13675,16 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="O82">
         <v>4</v>
       </c>
       <c r="P82">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="Q82">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R82">
         <v>2.38</v>
@@ -13693,31 +13693,31 @@
         <v>1.22</v>
       </c>
       <c r="T82">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="U82">
         <v>2.17</v>
       </c>
       <c r="V82">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="W82">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X82">
         <v>1.02</v>
       </c>
       <c r="Y82">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z82">
-        <v>5.75</v>
+        <v>5.3</v>
       </c>
       <c r="AA82">
         <v>1.47</v>
       </c>
       <c r="AB82">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="AC82">
         <v>2.17</v>
@@ -13726,13 +13726,13 @@
         <v>1.63</v>
       </c>
       <c r="AE82">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF82">
         <v>1.5</v>
       </c>
       <c r="AG82">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK82">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="O83">
-        <v>3.5</v>
+        <v>3.72</v>
       </c>
       <c r="P83">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="Q83">
         <v>2.98</v>
@@ -13853,25 +13853,25 @@
         <v>2.23</v>
       </c>
       <c r="S83">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T83">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="U83">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V83">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W83">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X83">
         <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z83">
         <v>4.4</v>
@@ -13880,7 +13880,7 @@
         <v>1.6</v>
       </c>
       <c r="AB83">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AC83">
         <v>2.35</v>
@@ -13889,13 +13889,13 @@
         <v>1.47</v>
       </c>
       <c r="AE83">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AF83">
         <v>1.48</v>
       </c>
       <c r="AG83">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,7 +13908,7 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK83">
         <v>1.47</v>
@@ -14010,22 +14010,22 @@
         <v>2.1</v>
       </c>
       <c r="Q84">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="R84">
         <v>2.34</v>
       </c>
       <c r="S84">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T84">
         <v>3.48</v>
       </c>
       <c r="U84">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="V84">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W84">
         <v>1.14</v>
@@ -14040,19 +14040,19 @@
         <v>4.95</v>
       </c>
       <c r="AA84">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AB84">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="AC84">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="AD84">
         <v>1.64</v>
       </c>
       <c r="AE84">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AF84">
         <v>1.44</v>
@@ -14071,7 +14071,7 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.65</v>
+        <v>1.23</v>
       </c>
       <c r="AK84">
         <v>1.34</v>
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="O85">
         <v>3.7</v>
       </c>
       <c r="P85">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="Q85">
         <v>2.74</v>
@@ -14179,16 +14179,16 @@
         <v>2.27</v>
       </c>
       <c r="S85">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="T85">
-        <v>4</v>
+        <v>3.74</v>
       </c>
       <c r="U85">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="V85">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W85">
         <v>1.14</v>
@@ -14221,7 +14221,7 @@
         <v>1.4</v>
       </c>
       <c r="AG85">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,7 +14234,7 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK85">
         <v>1.53</v>
@@ -14336,43 +14336,43 @@
         <v>2.9</v>
       </c>
       <c r="Q86">
-        <v>2.58</v>
+        <v>2.93</v>
       </c>
       <c r="R86">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="S86">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T86">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U86">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="V86">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W86">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X86">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y86">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z86">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA86">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB86">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AC86">
-        <v>3.56</v>
+        <v>3.05</v>
       </c>
       <c r="AD86">
         <v>1.28</v>
@@ -14490,7 +14490,7 @@
         </is>
       </c>
       <c r="N87">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O87">
         <v>3.2</v>
@@ -14499,7 +14499,7 @@
         <v>2.05</v>
       </c>
       <c r="Q87">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="R87">
         <v>2</v>
@@ -14508,16 +14508,16 @@
         <v>1.39</v>
       </c>
       <c r="T87">
-        <v>2.8</v>
+        <v>2.61</v>
       </c>
       <c r="U87">
         <v>2.89</v>
       </c>
       <c r="V87">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W87">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X87">
         <v>1.01</v>
@@ -14662,25 +14662,25 @@
         <v>0</v>
       </c>
       <c r="Q88">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="R88">
         <v>2.32</v>
       </c>
       <c r="S88">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T88">
-        <v>3.75</v>
+        <v>3.48</v>
       </c>
       <c r="U88">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="V88">
         <v>1.64</v>
       </c>
       <c r="W88">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X88">
         <v>1.02</v>
@@ -14698,10 +14698,10 @@
         <v>2.38</v>
       </c>
       <c r="AC88">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="AD88">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AE88">
         <v>1.2</v>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK88">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14816,49 +14816,49 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="O89">
-        <v>3.3</v>
+        <v>3.53</v>
       </c>
       <c r="P89">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="Q89">
         <v>2.83</v>
       </c>
       <c r="R89">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="S89">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T89">
-        <v>2.86</v>
+        <v>3.08</v>
       </c>
       <c r="U89">
-        <v>2.63</v>
+        <v>2.47</v>
       </c>
       <c r="V89">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W89">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X89">
         <v>1</v>
       </c>
       <c r="Y89">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z89">
         <v>3.8</v>
       </c>
       <c r="AA89">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AB89">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AC89">
         <v>2.66</v>
@@ -14870,10 +14870,10 @@
         <v>1.12</v>
       </c>
       <c r="AF89">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AG89">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>1.29</v>
       </c>
       <c r="AK89">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14982,16 +14982,16 @@
         <v>1.65</v>
       </c>
       <c r="O90">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="P90">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="Q90">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="R90">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="S90">
         <v>1.23</v>
@@ -15000,10 +15000,10 @@
         <v>3.48</v>
       </c>
       <c r="U90">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="V90">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="W90">
         <v>1.14</v>
@@ -15015,13 +15015,13 @@
         <v>1.14</v>
       </c>
       <c r="Z90">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="AA90">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="AB90">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="AC90">
         <v>2.43</v>
@@ -15036,7 +15036,7 @@
         <v>1.57</v>
       </c>
       <c r="AG90">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15052,7 +15052,7 @@
         <v>1.19</v>
       </c>
       <c r="AK90">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15142,34 +15142,34 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="O91">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P91">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="Q91">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="R91">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="S91">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="T91">
-        <v>6</v>
+        <v>7.08</v>
       </c>
       <c r="U91">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="V91">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="W91">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="X91">
         <v>1</v>
@@ -15178,28 +15178,28 @@
         <v>1.03</v>
       </c>
       <c r="Z91">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AA91">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AB91">
         <v>5.5</v>
       </c>
       <c r="AC91">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AD91">
-        <v>3.05</v>
+        <v>2.93</v>
       </c>
       <c r="AE91">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="AF91">
         <v>1.8</v>
       </c>
       <c r="AG91">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK91">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15308,22 +15308,22 @@
         <v>2.75</v>
       </c>
       <c r="O92">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P92">
         <v>2.34</v>
       </c>
       <c r="Q92">
-        <v>3.25</v>
+        <v>3.36</v>
       </c>
       <c r="R92">
         <v>2.18</v>
       </c>
       <c r="S92">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T92">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="U92">
         <v>2.23</v>
@@ -15332,37 +15332,37 @@
         <v>1.53</v>
       </c>
       <c r="W92">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X92">
         <v>1</v>
       </c>
       <c r="Y92">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z92">
-        <v>4.45</v>
+        <v>3.98</v>
       </c>
       <c r="AA92">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AB92">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC92">
         <v>2.49</v>
       </c>
       <c r="AD92">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE92">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF92">
         <v>1.53</v>
       </c>
       <c r="AG92">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15378,7 +15378,7 @@
         <v>1.23</v>
       </c>
       <c r="AK92">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15468,37 +15468,37 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="O93">
-        <v>3.7</v>
+        <v>3.78</v>
       </c>
       <c r="P93">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="Q93">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="R93">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S93">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T93">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="U93">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V93">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="W93">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X93">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y93">
         <v>1.13</v>
@@ -15510,19 +15510,19 @@
         <v>1.57</v>
       </c>
       <c r="AB93">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="AC93">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AD93">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AE93">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF93">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG93">
         <v>2.53</v>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="AK93">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="O101">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="P101">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q101">
-        <v>3.47</v>
+        <v>3.4</v>
       </c>
       <c r="R101">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="S101">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T101">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="U101">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="V101">
         <v>1.44</v>
       </c>
       <c r="W101">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X101">
         <v>1</v>
       </c>
       <c r="Y101">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z101">
         <v>3.7</v>
       </c>
       <c r="AA101">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AB101">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AC101">
-        <v>2.95</v>
+        <v>3.07</v>
       </c>
       <c r="AD101">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AE101">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF101">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG101">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AK101">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="O102">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P102">
-        <v>4.14</v>
+        <v>3.63</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O104">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q104">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R104">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S104">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T104">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U104">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="V104">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W104">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X104">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y104">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z104">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA104">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB104">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC104">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD104">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE104">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF104">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG104">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK104">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17756,10 +17756,10 @@
         <v>3.46</v>
       </c>
       <c r="P107">
-        <v>4.2</v>
+        <v>4.28</v>
       </c>
       <c r="Q107">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="R107">
         <v>2.1</v>
@@ -17777,53 +17777,53 @@
         <v>1.4</v>
       </c>
       <c r="W107">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X107">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y107">
         <v>1.26</v>
       </c>
       <c r="Z107">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AA107">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AB107">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC107">
-        <v>3.24</v>
+        <v>3.14</v>
       </c>
       <c r="AD107">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE107">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF107">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG107">
+        <v>1.96</v>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ107">
+        <v>1.34</v>
+      </c>
+      <c r="AK107">
         <v>1.95</v>
-      </c>
-      <c r="AH107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ107">
-        <v>1.23</v>
-      </c>
-      <c r="AK107">
-        <v>1.91</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="O108">
         <v>3.6</v>
       </c>
       <c r="P108">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="Q108">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="R108">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="S108">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T108">
-        <v>3.1</v>
+        <v>2.72</v>
       </c>
       <c r="U108">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="V108">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W108">
         <v>1.05</v>
       </c>
       <c r="X108">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y108">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="Z108">
         <v>3.42</v>
       </c>
       <c r="AA108">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB108">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AC108">
-        <v>2.93</v>
+        <v>2.97</v>
       </c>
       <c r="AD108">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AE108">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF108">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG108">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AK108">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18402,43 +18402,43 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="O111">
-        <v>3.99</v>
+        <v>4.1</v>
       </c>
       <c r="P111">
-        <v>5.79</v>
+        <v>6.2</v>
       </c>
       <c r="Q111">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="R111">
         <v>2.2</v>
       </c>
       <c r="S111">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T111">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U111">
-        <v>2.78</v>
+        <v>2.67</v>
       </c>
       <c r="V111">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W111">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X111">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y111">
         <v>1.24</v>
       </c>
       <c r="Z111">
-        <v>3.64</v>
+        <v>3.34</v>
       </c>
       <c r="AA111">
         <v>1.89</v>
@@ -18475,7 +18475,7 @@
         <v>1.08</v>
       </c>
       <c r="AK111">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18891,16 +18891,16 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="O114">
         <v>3.1</v>
       </c>
       <c r="P114">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q114">
-        <v>3.59</v>
+        <v>3.48</v>
       </c>
       <c r="R114">
         <v>2</v>
@@ -18918,22 +18918,22 @@
         <v>1.36</v>
       </c>
       <c r="W114">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X114">
         <v>1.02</v>
       </c>
       <c r="Y114">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z114">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AA114">
         <v>2.3</v>
       </c>
       <c r="AB114">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AC114">
         <v>3.68</v>
@@ -18948,7 +18948,7 @@
         <v>1.82</v>
       </c>
       <c r="AG114">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -19709,10 +19709,10 @@
         <v>2.3</v>
       </c>
       <c r="O119">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P119">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="Q119">
         <v>3</v>
@@ -19721,10 +19721,10 @@
         <v>1.96</v>
       </c>
       <c r="S119">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T119">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="U119">
         <v>2.96</v>
@@ -19733,7 +19733,7 @@
         <v>1.33</v>
       </c>
       <c r="W119">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X119">
         <v>1.02</v>
@@ -19742,13 +19742,13 @@
         <v>1.31</v>
       </c>
       <c r="Z119">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AA119">
         <v>2.08</v>
       </c>
       <c r="AB119">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AC119">
         <v>3.5</v>
@@ -19779,7 +19779,7 @@
         <v>1.32</v>
       </c>
       <c r="AK119">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL119">
         <v>0</v>

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU120"/>
+  <dimension ref="A1:AU118"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="O9">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P9">
-        <v>3.61</v>
+        <v>4</v>
       </c>
       <c r="Q9">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="R9">
-        <v>2.41</v>
+        <v>2.65</v>
       </c>
       <c r="S9">
         <v>1.2</v>
       </c>
       <c r="T9">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="U9">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="V9">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="W9">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X9">
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z9">
-        <v>6.33</v>
+        <v>6.5</v>
       </c>
       <c r="AA9">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AB9">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="AC9">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AD9">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AE9">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AF9">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AG9">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK9">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -4882,28 +4882,28 @@
         <v>3.7</v>
       </c>
       <c r="Q28">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="R28">
         <v>2.07</v>
       </c>
       <c r="S28">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T28">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="U28">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="V28">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W28">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
         <v>1.28</v>
@@ -4918,7 +4918,7 @@
         <v>1.75</v>
       </c>
       <c r="AC28">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AD28">
         <v>1.24</v>
@@ -4946,7 +4946,7 @@
         <v>1.26</v>
       </c>
       <c r="AK28">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5706,7 +5706,7 @@
         <v>1.25</v>
       </c>
       <c r="T33">
-        <v>3.46</v>
+        <v>3.3</v>
       </c>
       <c r="U33">
         <v>2.5</v>
@@ -5715,7 +5715,7 @@
         <v>1.52</v>
       </c>
       <c r="W33">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X33">
         <v>1.03</v>
@@ -5745,7 +5745,7 @@
         <v>1.58</v>
       </c>
       <c r="AG33">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
         <v>1.83</v>
@@ -5851,7 +5851,7 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="O34">
         <v>3.6</v>
@@ -5860,13 +5860,13 @@
         <v>3.1</v>
       </c>
       <c r="Q34">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="R34">
         <v>2.4</v>
       </c>
       <c r="S34">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T34">
         <v>3.42</v>
@@ -5878,7 +5878,7 @@
         <v>1.55</v>
       </c>
       <c r="W34">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X34">
         <v>1</v>
@@ -5908,7 +5908,7 @@
         <v>1.48</v>
       </c>
       <c r="AG34">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK34">
         <v>1.7</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.69</v>
+        <v>3.05</v>
       </c>
       <c r="O35">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P35">
-        <v>4.5</v>
+        <v>2.19</v>
       </c>
       <c r="Q35">
-        <v>2.2</v>
+        <v>3.74</v>
       </c>
       <c r="R35">
-        <v>2.21</v>
+        <v>2.09</v>
       </c>
       <c r="S35">
+        <v>1.33</v>
+      </c>
+      <c r="T35">
+        <v>3</v>
+      </c>
+      <c r="U35">
+        <v>2.68</v>
+      </c>
+      <c r="V35">
+        <v>1.37</v>
+      </c>
+      <c r="W35">
+        <v>1.05</v>
+      </c>
+      <c r="X35">
+        <v>1.01</v>
+      </c>
+      <c r="Y35">
+        <v>1.25</v>
+      </c>
+      <c r="Z35">
+        <v>3.28</v>
+      </c>
+      <c r="AA35">
+        <v>1.85</v>
+      </c>
+      <c r="AB35">
+        <v>1.82</v>
+      </c>
+      <c r="AC35">
+        <v>3.08</v>
+      </c>
+      <c r="AD35">
         <v>1.28</v>
       </c>
-      <c r="T35">
-        <v>3.12</v>
-      </c>
-      <c r="U35">
-        <v>2.34</v>
-      </c>
-      <c r="V35">
-        <v>1.48</v>
-      </c>
-      <c r="W35">
-        <v>1.08</v>
-      </c>
-      <c r="X35">
-        <v>1.02</v>
-      </c>
-      <c r="Y35">
-        <v>1.14</v>
-      </c>
-      <c r="Z35">
-        <v>4.35</v>
-      </c>
-      <c r="AA35">
-        <v>1.59</v>
-      </c>
-      <c r="AB35">
-        <v>2.17</v>
-      </c>
-      <c r="AC35">
-        <v>2.43</v>
-      </c>
-      <c r="AD35">
-        <v>1.44</v>
-      </c>
       <c r="AE35">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AF35">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="AG35">
-        <v>2.19</v>
+        <v>2.02</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AK35">
-        <v>2</v>
+        <v>1.29</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,65 +6177,65 @@
         </is>
       </c>
       <c r="N36">
-        <v>3.05</v>
+        <v>1.69</v>
       </c>
       <c r="O36">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="P36">
+        <v>4.5</v>
+      </c>
+      <c r="Q36">
+        <v>2.2</v>
+      </c>
+      <c r="R36">
+        <v>2.21</v>
+      </c>
+      <c r="S36">
+        <v>1.28</v>
+      </c>
+      <c r="T36">
+        <v>3.12</v>
+      </c>
+      <c r="U36">
+        <v>2.34</v>
+      </c>
+      <c r="V36">
+        <v>1.48</v>
+      </c>
+      <c r="W36">
+        <v>1.08</v>
+      </c>
+      <c r="X36">
+        <v>1.02</v>
+      </c>
+      <c r="Y36">
+        <v>1.14</v>
+      </c>
+      <c r="Z36">
+        <v>4.35</v>
+      </c>
+      <c r="AA36">
+        <v>1.59</v>
+      </c>
+      <c r="AB36">
+        <v>2.17</v>
+      </c>
+      <c r="AC36">
+        <v>2.43</v>
+      </c>
+      <c r="AD36">
+        <v>1.44</v>
+      </c>
+      <c r="AE36">
+        <v>1.14</v>
+      </c>
+      <c r="AF36">
+        <v>1.58</v>
+      </c>
+      <c r="AG36">
         <v>2.19</v>
       </c>
-      <c r="Q36">
-        <v>3.74</v>
-      </c>
-      <c r="R36">
-        <v>2.09</v>
-      </c>
-      <c r="S36">
-        <v>1.33</v>
-      </c>
-      <c r="T36">
-        <v>3</v>
-      </c>
-      <c r="U36">
-        <v>2.68</v>
-      </c>
-      <c r="V36">
-        <v>1.37</v>
-      </c>
-      <c r="W36">
-        <v>1.05</v>
-      </c>
-      <c r="X36">
-        <v>1.01</v>
-      </c>
-      <c r="Y36">
-        <v>1.25</v>
-      </c>
-      <c r="Z36">
-        <v>3.28</v>
-      </c>
-      <c r="AA36">
-        <v>1.85</v>
-      </c>
-      <c r="AB36">
-        <v>1.82</v>
-      </c>
-      <c r="AC36">
-        <v>3.08</v>
-      </c>
-      <c r="AD36">
-        <v>1.28</v>
-      </c>
-      <c r="AE36">
-        <v>1.07</v>
-      </c>
-      <c r="AF36">
-        <v>1.68</v>
-      </c>
-      <c r="AG36">
-        <v>2.02</v>
-      </c>
       <c r="AH36" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AK36">
-        <v>1.29</v>
+        <v>2</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -7659,16 +7659,16 @@
         <v>2.03</v>
       </c>
       <c r="S45">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T45">
         <v>2.78</v>
       </c>
       <c r="U45">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="V45">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W45">
         <v>1.04</v>
@@ -7677,7 +7677,7 @@
         <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z45">
         <v>3.5</v>
@@ -7689,10 +7689,10 @@
         <v>2</v>
       </c>
       <c r="AC45">
-        <v>3.09</v>
+        <v>2.97</v>
       </c>
       <c r="AD45">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AE45">
         <v>1.07</v>
@@ -7979,10 +7979,10 @@
         <v>0</v>
       </c>
       <c r="Q47">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="R47">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S47">
         <v>1.25</v>
@@ -7991,13 +7991,13 @@
         <v>3.32</v>
       </c>
       <c r="U47">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="V47">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W47">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X47">
         <v>1.02</v>
@@ -8006,19 +8006,19 @@
         <v>1.12</v>
       </c>
       <c r="Z47">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="AA47">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AB47">
         <v>2.4</v>
       </c>
       <c r="AC47">
-        <v>2.21</v>
+        <v>2.33</v>
       </c>
       <c r="AD47">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AE47">
         <v>1.21</v>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AK47">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -10536,7 +10536,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10617,10 +10617,10 @@
         <v>0</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC63">
         <v>0</v>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O64">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="P64">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q64">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="R64">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S64">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T64">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U64">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="V64">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W64">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X64">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y64">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z64">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA64">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB64">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC64">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AD64">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE64">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF64">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG64">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK64">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
+        <v>1.96</v>
+      </c>
+      <c r="O65">
+        <v>3.25</v>
+      </c>
+      <c r="P65">
+        <v>3.1</v>
+      </c>
+      <c r="Q65">
+        <v>2.74</v>
+      </c>
+      <c r="R65">
         <v>2.1</v>
       </c>
-      <c r="O65">
-        <v>3.05</v>
-      </c>
-      <c r="P65">
-        <v>2.68</v>
-      </c>
-      <c r="Q65">
-        <v>2.93</v>
-      </c>
-      <c r="R65">
-        <v>1.98</v>
-      </c>
       <c r="S65">
+        <v>1.39</v>
+      </c>
+      <c r="T65">
+        <v>2.92</v>
+      </c>
+      <c r="U65">
+        <v>2.67</v>
+      </c>
+      <c r="V65">
         <v>1.4</v>
-      </c>
-      <c r="T65">
-        <v>2.67</v>
-      </c>
-      <c r="U65">
-        <v>2.82</v>
-      </c>
-      <c r="V65">
-        <v>1.36</v>
       </c>
       <c r="W65">
         <v>1.05</v>
       </c>
       <c r="X65">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z65">
-        <v>3.04</v>
+        <v>3.48</v>
       </c>
       <c r="AA65">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AB65">
-        <v>1.66</v>
+        <v>1.91</v>
       </c>
       <c r="AC65">
-        <v>3.42</v>
+        <v>2.97</v>
       </c>
       <c r="AD65">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AE65">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF65">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG65">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AK65">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.75</v>
+        <v>2.26</v>
       </c>
       <c r="O66">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P66">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q66">
-        <v>2.32</v>
+        <v>2.92</v>
       </c>
       <c r="R66">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="S66">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="T66">
-        <v>3.08</v>
+        <v>2.67</v>
       </c>
       <c r="U66">
-        <v>2.52</v>
+        <v>2.91</v>
       </c>
       <c r="V66">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="W66">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X66">
         <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="Z66">
-        <v>3.95</v>
+        <v>3.04</v>
       </c>
       <c r="AA66">
-        <v>1.71</v>
+        <v>2.15</v>
       </c>
       <c r="AB66">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AC66">
-        <v>2.69</v>
+        <v>3.42</v>
       </c>
       <c r="AD66">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AE66">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF66">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AG66">
-        <v>2.11</v>
+        <v>1.93</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AK66">
-        <v>1.99</v>
+        <v>1.6</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.26</v>
+        <v>1.75</v>
       </c>
       <c r="O67">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P67">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="Q67">
-        <v>2.56</v>
+        <v>2.32</v>
       </c>
       <c r="R67">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="S67">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T67">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="U67">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="V67">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="W67">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X67">
         <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z67">
-        <v>3.86</v>
+        <v>3.82</v>
       </c>
       <c r="AA67">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AB67">
         <v>2</v>
       </c>
       <c r="AC67">
-        <v>2.66</v>
+        <v>3.1</v>
       </c>
       <c r="AD67">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE67">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF67">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AG67">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK67">
-        <v>1.63</v>
+        <v>1.95</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="O68">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P68">
-        <v>2.52</v>
+        <v>3</v>
       </c>
       <c r="Q68">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="R68">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="S68">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T68">
-        <v>2.97</v>
+        <v>3.14</v>
       </c>
       <c r="U68">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V68">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W68">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X68">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y68">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z68">
-        <v>3.58</v>
+        <v>3.91</v>
       </c>
       <c r="AA68">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AB68">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AC68">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AD68">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE68">
         <v>1.11</v>
       </c>
       <c r="AF68">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AG68">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AK68">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.12</v>
+        <v>2.31</v>
       </c>
       <c r="O69">
-        <v>3.03</v>
+        <v>3.34</v>
       </c>
       <c r="P69">
-        <v>2.65</v>
+        <v>2.52</v>
       </c>
       <c r="Q69">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="R69">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="S69">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="T69">
-        <v>2.6</v>
+        <v>2.97</v>
       </c>
       <c r="U69">
-        <v>2.96</v>
+        <v>2.5</v>
       </c>
       <c r="V69">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="W69">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X69">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y69">
+        <v>1.25</v>
+      </c>
+      <c r="Z69">
+        <v>3.68</v>
+      </c>
+      <c r="AA69">
+        <v>1.85</v>
+      </c>
+      <c r="AB69">
+        <v>1.95</v>
+      </c>
+      <c r="AC69">
+        <v>3.02</v>
+      </c>
+      <c r="AD69">
         <v>1.37</v>
       </c>
-      <c r="Z69">
-        <v>2.92</v>
-      </c>
-      <c r="AA69">
-        <v>2.15</v>
-      </c>
-      <c r="AB69">
-        <v>1.66</v>
-      </c>
-      <c r="AC69">
-        <v>3.5</v>
-      </c>
-      <c r="AD69">
-        <v>1.22</v>
-      </c>
       <c r="AE69">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AF69">
-        <v>1.82</v>
+        <v>1.59</v>
       </c>
       <c r="AG69">
-        <v>1.88</v>
+        <v>2.21</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AK69">
         <v>1.62</v>
@@ -11677,7 +11677,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="O70">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="P70">
-        <v>1.91</v>
+        <v>3.15</v>
       </c>
       <c r="Q70">
-        <v>4.11</v>
+        <v>2.83</v>
       </c>
       <c r="R70">
-        <v>2.23</v>
+        <v>2.03</v>
       </c>
       <c r="S70">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="T70">
-        <v>3.12</v>
+        <v>2.6</v>
       </c>
       <c r="U70">
-        <v>2.42</v>
+        <v>2.96</v>
       </c>
       <c r="V70">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="W70">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X70">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="Z70">
-        <v>3.84</v>
+        <v>2.92</v>
       </c>
       <c r="AA70">
-        <v>1.69</v>
+        <v>2.06</v>
       </c>
       <c r="AB70">
-        <v>2.08</v>
+        <v>1.66</v>
       </c>
       <c r="AC70">
-        <v>2.59</v>
+        <v>3.98</v>
       </c>
       <c r="AD70">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="AE70">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AF70">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AG70">
-        <v>2.19</v>
+        <v>1.85</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK70">
-        <v>1.26</v>
+        <v>1.55</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11840,7 +11840,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q71">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="R71">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S71">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T71">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U71">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V71">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W71">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y71">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z71">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA71">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB71">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC71">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD71">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE71">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF71">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG71">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK71">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12003,7 +12003,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Deportivo Alavés W</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G72">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Deportivo Alavés W</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G73">
@@ -12217,55 +12217,55 @@
         <v>0</v>
       </c>
       <c r="Q73">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="R73">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S73">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T73">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="U73">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="V73">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W73">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X73">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y73">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z73">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA73">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB73">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AC73">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AD73">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE73">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF73">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG73">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK73">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G74">
@@ -12380,55 +12380,55 @@
         <v>0</v>
       </c>
       <c r="Q74">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S74">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T74">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U74">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V74">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W74">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X74">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y74">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z74">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA74">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AC74">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD74">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE74">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF74">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG74">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK74">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12492,7 +12492,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O75">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P75">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="Q75">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="R75">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S75">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="T75">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U75">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="V75">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W75">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X75">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y75">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z75">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA75">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB75">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC75">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD75">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE75">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF75">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AG75">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK75">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12655,7 +12655,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="O76">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="P76">
-        <v>4.7</v>
+        <v>3.71</v>
       </c>
       <c r="Q76">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="R76">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="S76">
-        <v>1.2</v>
+        <v>1.48</v>
       </c>
       <c r="T76">
+        <v>2.41</v>
+      </c>
+      <c r="U76">
+        <v>3.22</v>
+      </c>
+      <c r="V76">
+        <v>1.29</v>
+      </c>
+      <c r="W76">
+        <v>1.03</v>
+      </c>
+      <c r="X76">
+        <v>1.03</v>
+      </c>
+      <c r="Y76">
+        <v>1.36</v>
+      </c>
+      <c r="Z76">
+        <v>2.7</v>
+      </c>
+      <c r="AA76">
+        <v>2.3</v>
+      </c>
+      <c r="AB76">
+        <v>1.6</v>
+      </c>
+      <c r="AC76">
         <v>4</v>
       </c>
-      <c r="U76">
-        <v>2.03</v>
-      </c>
-      <c r="V76">
-        <v>1.73</v>
-      </c>
-      <c r="W76">
+      <c r="AD76">
         <v>1.17</v>
       </c>
-      <c r="X76">
+      <c r="AE76">
         <v>1.02</v>
       </c>
-      <c r="Y76">
-        <v>1.1</v>
-      </c>
-      <c r="Z76">
-        <v>6</v>
-      </c>
-      <c r="AA76">
-        <v>1.4</v>
-      </c>
-      <c r="AB76">
-        <v>2.7</v>
-      </c>
-      <c r="AC76">
-        <v>2.02</v>
-      </c>
-      <c r="AD76">
-        <v>1.68</v>
-      </c>
-      <c r="AE76">
-        <v>1.25</v>
-      </c>
       <c r="AF76">
-        <v>1.47</v>
+        <v>2.08</v>
       </c>
       <c r="AG76">
-        <v>2.55</v>
+        <v>1.67</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK76">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12818,7 +12818,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,43 +12860,43 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="O77">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="P77">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="Q77">
-        <v>2.19</v>
+        <v>2.11</v>
       </c>
       <c r="R77">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="S77">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T77">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="U77">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="V77">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="W77">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X77">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y77">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z77">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="AA77">
         <v>1.4</v>
@@ -12905,19 +12905,19 @@
         <v>2.7</v>
       </c>
       <c r="AC77">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="AD77">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AE77">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF77">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AG77">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK77">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.9</v>
+        <v>1.67</v>
       </c>
       <c r="O78">
+        <v>3.9</v>
+      </c>
+      <c r="P78">
         <v>3.8</v>
       </c>
-      <c r="P78">
-        <v>1.95</v>
-      </c>
       <c r="Q78">
-        <v>3.62</v>
+        <v>2.19</v>
       </c>
       <c r="R78">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="S78">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="T78">
-        <v>3.98</v>
+        <v>3.55</v>
       </c>
       <c r="U78">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="V78">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="W78">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X78">
         <v>1.01</v>
       </c>
       <c r="Y78">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Z78">
-        <v>6.45</v>
+        <v>5.25</v>
       </c>
       <c r="AA78">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AB78">
-        <v>2.97</v>
+        <v>2.7</v>
       </c>
       <c r="AC78">
-        <v>1.88</v>
+        <v>2.12</v>
       </c>
       <c r="AD78">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AE78">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AF78">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="AG78">
-        <v>3.1</v>
+        <v>2.56</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK78">
-        <v>1.31</v>
+        <v>2.04</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,80 +13186,80 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="O79">
         <v>3.8</v>
       </c>
       <c r="P79">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="Q79">
-        <v>2.92</v>
+        <v>3.62</v>
       </c>
       <c r="R79">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="S79">
+        <v>1.18</v>
+      </c>
+      <c r="T79">
+        <v>3.98</v>
+      </c>
+      <c r="U79">
+        <v>1.93</v>
+      </c>
+      <c r="V79">
+        <v>1.88</v>
+      </c>
+      <c r="W79">
+        <v>1.19</v>
+      </c>
+      <c r="X79">
+        <v>1.01</v>
+      </c>
+      <c r="Y79">
+        <v>1.05</v>
+      </c>
+      <c r="Z79">
+        <v>6.45</v>
+      </c>
+      <c r="AA79">
+        <v>1.33</v>
+      </c>
+      <c r="AB79">
+        <v>2.97</v>
+      </c>
+      <c r="AC79">
+        <v>1.88</v>
+      </c>
+      <c r="AD79">
+        <v>1.9</v>
+      </c>
+      <c r="AE79">
+        <v>1.34</v>
+      </c>
+      <c r="AF79">
+        <v>1.32</v>
+      </c>
+      <c r="AG79">
+        <v>3.1</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ79">
         <v>1.22</v>
       </c>
-      <c r="T79">
-        <v>3.55</v>
-      </c>
-      <c r="U79">
-        <v>2.14</v>
-      </c>
-      <c r="V79">
-        <v>1.64</v>
-      </c>
-      <c r="W79">
-        <v>1.12</v>
-      </c>
-      <c r="X79">
-        <v>1.02</v>
-      </c>
-      <c r="Y79">
-        <v>1.09</v>
-      </c>
-      <c r="Z79">
-        <v>5.35</v>
-      </c>
-      <c r="AA79">
-        <v>1.5</v>
-      </c>
-      <c r="AB79">
-        <v>2.5</v>
-      </c>
-      <c r="AC79">
-        <v>2.14</v>
-      </c>
-      <c r="AD79">
-        <v>1.65</v>
-      </c>
-      <c r="AE79">
-        <v>1.22</v>
-      </c>
-      <c r="AF79">
-        <v>1.4</v>
-      </c>
-      <c r="AG79">
-        <v>2.75</v>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ79">
-        <v>1.25</v>
-      </c>
       <c r="AK79">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,34 +13349,34 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="O80">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P80">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="Q80">
-        <v>3.5</v>
+        <v>2.92</v>
       </c>
       <c r="R80">
-        <v>2.54</v>
+        <v>2.28</v>
       </c>
       <c r="S80">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T80">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="U80">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="V80">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="W80">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="X80">
         <v>1.02</v>
@@ -13385,28 +13385,28 @@
         <v>1.09</v>
       </c>
       <c r="Z80">
-        <v>5.25</v>
+        <v>5.35</v>
       </c>
       <c r="AA80">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AB80">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AC80">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="AD80">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AE80">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AF80">
         <v>1.4</v>
       </c>
       <c r="AG80">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK80">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,80 +13512,80 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="O81">
         <v>3.6</v>
       </c>
       <c r="P81">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q81">
-        <v>3.02</v>
+        <v>3.5</v>
       </c>
       <c r="R81">
-        <v>2.43</v>
+        <v>2.54</v>
       </c>
       <c r="S81">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T81">
-        <v>4.35</v>
+        <v>3.8</v>
       </c>
       <c r="U81">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="V81">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="W81">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="X81">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y81">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Z81">
-        <v>6.4</v>
+        <v>5.25</v>
       </c>
       <c r="AA81">
+        <v>1.47</v>
+      </c>
+      <c r="AB81">
+        <v>2.6</v>
+      </c>
+      <c r="AC81">
+        <v>2.11</v>
+      </c>
+      <c r="AD81">
+        <v>1.67</v>
+      </c>
+      <c r="AE81">
+        <v>1.24</v>
+      </c>
+      <c r="AF81">
+        <v>1.4</v>
+      </c>
+      <c r="AG81">
+        <v>2.73</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ81">
+        <v>1.24</v>
+      </c>
+      <c r="AK81">
         <v>1.33</v>
-      </c>
-      <c r="AB81">
-        <v>2.97</v>
-      </c>
-      <c r="AC81">
-        <v>1.85</v>
-      </c>
-      <c r="AD81">
-        <v>1.88</v>
-      </c>
-      <c r="AE81">
-        <v>1.39</v>
-      </c>
-      <c r="AF81">
-        <v>1.31</v>
-      </c>
-      <c r="AG81">
-        <v>3.14</v>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI81" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ81">
-        <v>1.25</v>
-      </c>
-      <c r="AK81">
-        <v>1.44</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="O82">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="P82">
-        <v>4.33</v>
+        <v>2.2</v>
       </c>
       <c r="Q82">
-        <v>2.12</v>
+        <v>3.02</v>
       </c>
       <c r="R82">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="S82">
+        <v>1.18</v>
+      </c>
+      <c r="T82">
+        <v>4.35</v>
+      </c>
+      <c r="U82">
+        <v>1.85</v>
+      </c>
+      <c r="V82">
+        <v>1.85</v>
+      </c>
+      <c r="W82">
         <v>1.22</v>
       </c>
-      <c r="T82">
-        <v>3.55</v>
-      </c>
-      <c r="U82">
-        <v>2.17</v>
-      </c>
-      <c r="V82">
-        <v>1.62</v>
-      </c>
-      <c r="W82">
-        <v>1.12</v>
-      </c>
       <c r="X82">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="Z82">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="AA82">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AB82">
-        <v>2.6</v>
+        <v>2.97</v>
       </c>
       <c r="AC82">
-        <v>2.17</v>
+        <v>1.85</v>
       </c>
       <c r="AD82">
-        <v>1.63</v>
+        <v>1.88</v>
       </c>
       <c r="AE82">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="AF82">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="AG82">
-        <v>2.42</v>
+        <v>3.14</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK82">
-        <v>2.18</v>
+        <v>1.44</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.32</v>
+        <v>1.6</v>
       </c>
       <c r="O83">
-        <v>3.72</v>
+        <v>4</v>
       </c>
       <c r="P83">
-        <v>2.35</v>
+        <v>4.33</v>
       </c>
       <c r="Q83">
-        <v>2.98</v>
+        <v>2.12</v>
       </c>
       <c r="R83">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="S83">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="T83">
-        <v>3.24</v>
+        <v>3.55</v>
       </c>
       <c r="U83">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="V83">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="W83">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X83">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y83">
         <v>1.14</v>
       </c>
       <c r="Z83">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="AA83">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AB83">
-        <v>2.27</v>
+        <v>2.6</v>
       </c>
       <c r="AC83">
-        <v>2.35</v>
+        <v>2.17</v>
       </c>
       <c r="AD83">
-        <v>1.47</v>
+        <v>1.63</v>
       </c>
       <c r="AE83">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AF83">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AG83">
-        <v>2.47</v>
+        <v>2.42</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK83">
-        <v>1.47</v>
+        <v>2.18</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.8</v>
+        <v>2.32</v>
       </c>
       <c r="O84">
-        <v>3.5</v>
+        <v>3.72</v>
       </c>
       <c r="P84">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="Q84">
-        <v>3.5</v>
+        <v>2.98</v>
       </c>
       <c r="R84">
-        <v>2.34</v>
+        <v>2.23</v>
       </c>
       <c r="S84">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="T84">
-        <v>3.48</v>
+        <v>3.24</v>
       </c>
       <c r="U84">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="V84">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="W84">
+        <v>1.1</v>
+      </c>
+      <c r="X84">
+        <v>1.01</v>
+      </c>
+      <c r="Y84">
         <v>1.14</v>
       </c>
-      <c r="X84">
-        <v>1.02</v>
-      </c>
-      <c r="Y84">
-        <v>1.11</v>
-      </c>
       <c r="Z84">
-        <v>4.95</v>
+        <v>4.4</v>
       </c>
       <c r="AA84">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AB84">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AC84">
-        <v>2.16</v>
+        <v>2.35</v>
       </c>
       <c r="AD84">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="AE84">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AF84">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AG84">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK84">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14117,12 +14117,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,31 +14164,31 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.24</v>
+        <v>2.8</v>
       </c>
       <c r="O85">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P85">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="Q85">
-        <v>2.74</v>
+        <v>3.5</v>
       </c>
       <c r="R85">
-        <v>2.27</v>
+        <v>2.34</v>
       </c>
       <c r="S85">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="T85">
-        <v>3.74</v>
+        <v>3.48</v>
       </c>
       <c r="U85">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="V85">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W85">
         <v>1.14</v>
@@ -14197,31 +14197,31 @@
         <v>1.02</v>
       </c>
       <c r="Y85">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z85">
-        <v>5.2</v>
+        <v>4.95</v>
       </c>
       <c r="AA85">
+        <v>1.43</v>
+      </c>
+      <c r="AB85">
+        <v>2.4</v>
+      </c>
+      <c r="AC85">
+        <v>2.16</v>
+      </c>
+      <c r="AD85">
+        <v>1.64</v>
+      </c>
+      <c r="AE85">
+        <v>1.27</v>
+      </c>
+      <c r="AF85">
         <v>1.44</v>
       </c>
-      <c r="AB85">
-        <v>2.43</v>
-      </c>
-      <c r="AC85">
-        <v>2.17</v>
-      </c>
-      <c r="AD85">
-        <v>1.59</v>
-      </c>
-      <c r="AE85">
-        <v>1.21</v>
-      </c>
-      <c r="AF85">
-        <v>1.4</v>
-      </c>
       <c r="AG85">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AK85">
-        <v>1.53</v>
+        <v>1.34</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14268,7 +14268,7 @@
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>2026-09-18 15:15:00</t>
+          <t>2026-09-18 15:00:00</t>
         </is>
       </c>
     </row>
@@ -14280,12 +14280,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="O86">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="P86">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="Q86">
-        <v>2.93</v>
+        <v>2.74</v>
       </c>
       <c r="R86">
-        <v>2.04</v>
+        <v>2.27</v>
       </c>
       <c r="S86">
-        <v>1.38</v>
+        <v>1.19</v>
       </c>
       <c r="T86">
-        <v>2.75</v>
+        <v>3.74</v>
       </c>
       <c r="U86">
-        <v>2.64</v>
+        <v>2.08</v>
       </c>
       <c r="V86">
-        <v>1.41</v>
+        <v>1.64</v>
       </c>
       <c r="W86">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X86">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="Z86">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="AA86">
-        <v>2.05</v>
+        <v>1.44</v>
       </c>
       <c r="AB86">
-        <v>1.75</v>
+        <v>2.43</v>
       </c>
       <c r="AC86">
-        <v>3.05</v>
+        <v>2.17</v>
       </c>
       <c r="AD86">
-        <v>1.28</v>
+        <v>1.59</v>
       </c>
       <c r="AE86">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AF86">
-        <v>1.69</v>
+        <v>1.4</v>
       </c>
       <c r="AG86">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AK86">
         <v>1.53</v>
@@ -14431,7 +14431,7 @@
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>2026-09-18 15:30:00</t>
+          <t>2026-09-18 15:15:00</t>
         </is>
       </c>
     </row>
@@ -14448,7 +14448,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,43 +14490,43 @@
         </is>
       </c>
       <c r="N87">
-        <v>3.25</v>
+        <v>2.2</v>
       </c>
       <c r="O87">
+        <v>3.1</v>
+      </c>
+      <c r="P87">
+        <v>2.9</v>
+      </c>
+      <c r="Q87">
+        <v>2.93</v>
+      </c>
+      <c r="R87">
+        <v>2.04</v>
+      </c>
+      <c r="S87">
+        <v>1.38</v>
+      </c>
+      <c r="T87">
+        <v>2.75</v>
+      </c>
+      <c r="U87">
+        <v>2.64</v>
+      </c>
+      <c r="V87">
+        <v>1.41</v>
+      </c>
+      <c r="W87">
+        <v>1.08</v>
+      </c>
+      <c r="X87">
+        <v>1.03</v>
+      </c>
+      <c r="Y87">
+        <v>1.26</v>
+      </c>
+      <c r="Z87">
         <v>3.2</v>
-      </c>
-      <c r="P87">
-        <v>2.05</v>
-      </c>
-      <c r="Q87">
-        <v>3.6</v>
-      </c>
-      <c r="R87">
-        <v>2</v>
-      </c>
-      <c r="S87">
-        <v>1.39</v>
-      </c>
-      <c r="T87">
-        <v>2.61</v>
-      </c>
-      <c r="U87">
-        <v>2.89</v>
-      </c>
-      <c r="V87">
-        <v>1.32</v>
-      </c>
-      <c r="W87">
-        <v>1.02</v>
-      </c>
-      <c r="X87">
-        <v>1.01</v>
-      </c>
-      <c r="Y87">
-        <v>1.28</v>
-      </c>
-      <c r="Z87">
-        <v>3.08</v>
       </c>
       <c r="AA87">
         <v>2.05</v>
@@ -14535,19 +14535,19 @@
         <v>1.75</v>
       </c>
       <c r="AC87">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="AD87">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE87">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF87">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="AG87">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK87">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14611,7 +14611,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O88">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q88">
-        <v>2.08</v>
+        <v>4.1</v>
       </c>
       <c r="R88">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="S88">
-        <v>1.23</v>
+        <v>1.39</v>
       </c>
       <c r="T88">
-        <v>3.48</v>
+        <v>2.61</v>
       </c>
       <c r="U88">
-        <v>2.14</v>
+        <v>2.89</v>
       </c>
       <c r="V88">
-        <v>1.64</v>
+        <v>1.32</v>
       </c>
       <c r="W88">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="X88">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y88">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="Z88">
-        <v>5</v>
+        <v>3.08</v>
       </c>
       <c r="AA88">
-        <v>1.46</v>
+        <v>2.05</v>
       </c>
       <c r="AB88">
-        <v>2.38</v>
+        <v>1.75</v>
       </c>
       <c r="AC88">
-        <v>2.23</v>
+        <v>3.5</v>
       </c>
       <c r="AD88">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="AE88">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="AF88">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="AG88">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.19</v>
+        <v>1.57</v>
       </c>
       <c r="AK88">
-        <v>2.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14774,7 +14774,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,80 +14816,80 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O89">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="P89">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Q89">
-        <v>2.83</v>
+        <v>2.08</v>
       </c>
       <c r="R89">
+        <v>2.32</v>
+      </c>
+      <c r="S89">
+        <v>1.23</v>
+      </c>
+      <c r="T89">
+        <v>3.48</v>
+      </c>
+      <c r="U89">
         <v>2.14</v>
       </c>
-      <c r="S89">
-        <v>1.31</v>
-      </c>
-      <c r="T89">
-        <v>3.08</v>
-      </c>
-      <c r="U89">
-        <v>2.47</v>
-      </c>
       <c r="V89">
+        <v>1.64</v>
+      </c>
+      <c r="W89">
+        <v>1.14</v>
+      </c>
+      <c r="X89">
+        <v>1.02</v>
+      </c>
+      <c r="Y89">
+        <v>1.14</v>
+      </c>
+      <c r="Z89">
+        <v>5</v>
+      </c>
+      <c r="AA89">
         <v>1.46</v>
       </c>
-      <c r="W89">
-        <v>1.08</v>
-      </c>
-      <c r="X89">
-        <v>1</v>
-      </c>
-      <c r="Y89">
+      <c r="AB89">
+        <v>2.38</v>
+      </c>
+      <c r="AC89">
+        <v>2.23</v>
+      </c>
+      <c r="AD89">
+        <v>1.6</v>
+      </c>
+      <c r="AE89">
+        <v>1.2</v>
+      </c>
+      <c r="AF89">
+        <v>1.55</v>
+      </c>
+      <c r="AG89">
+        <v>2.3</v>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ89">
         <v>1.19</v>
       </c>
-      <c r="Z89">
-        <v>3.8</v>
-      </c>
-      <c r="AA89">
-        <v>1.8</v>
-      </c>
-      <c r="AB89">
-        <v>2</v>
-      </c>
-      <c r="AC89">
-        <v>2.66</v>
-      </c>
-      <c r="AD89">
-        <v>1.37</v>
-      </c>
-      <c r="AE89">
-        <v>1.12</v>
-      </c>
-      <c r="AF89">
-        <v>1.58</v>
-      </c>
-      <c r="AG89">
-        <v>2.23</v>
-      </c>
-      <c r="AH89" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI89" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ89">
-        <v>1.29</v>
-      </c>
       <c r="AK89">
-        <v>1.59</v>
+        <v>2.3</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="O90">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="P90">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="Q90">
-        <v>2.15</v>
+        <v>2.88</v>
       </c>
       <c r="R90">
-        <v>2.31</v>
+        <v>2.22</v>
       </c>
       <c r="S90">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="T90">
-        <v>3.48</v>
+        <v>3.08</v>
       </c>
       <c r="U90">
-        <v>2.19</v>
+        <v>2.47</v>
       </c>
       <c r="V90">
-        <v>1.61</v>
+        <v>1.46</v>
       </c>
       <c r="W90">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X90">
         <v>1.02</v>
       </c>
       <c r="Y90">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Z90">
-        <v>4.45</v>
+        <v>3.93</v>
       </c>
       <c r="AA90">
-        <v>1.51</v>
+        <v>1.8</v>
       </c>
       <c r="AB90">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="AC90">
-        <v>2.43</v>
+        <v>3.04</v>
       </c>
       <c r="AD90">
-        <v>1.56</v>
+        <v>1.37</v>
       </c>
       <c r="AE90">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AF90">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG90">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AK90">
-        <v>2.14</v>
+        <v>1.54</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15100,7 +15100,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.04</v>
+        <v>1.65</v>
       </c>
       <c r="O91">
-        <v>16</v>
+        <v>3.8</v>
       </c>
       <c r="P91">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="Q91">
-        <v>1.25</v>
+        <v>2.15</v>
       </c>
       <c r="R91">
-        <v>4.7</v>
+        <v>2.36</v>
       </c>
       <c r="S91">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="T91">
-        <v>7.08</v>
+        <v>3.48</v>
       </c>
       <c r="U91">
-        <v>1.49</v>
+        <v>2.19</v>
       </c>
       <c r="V91">
-        <v>2.56</v>
+        <v>1.61</v>
       </c>
       <c r="W91">
-        <v>1.52</v>
+        <v>1.14</v>
       </c>
       <c r="X91">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y91">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="Z91">
-        <v>16.5</v>
+        <v>4.45</v>
       </c>
       <c r="AA91">
-        <v>1.14</v>
+        <v>1.57</v>
       </c>
       <c r="AB91">
-        <v>5.5</v>
+        <v>2.35</v>
       </c>
       <c r="AC91">
-        <v>1.33</v>
+        <v>2.36</v>
       </c>
       <c r="AD91">
-        <v>2.93</v>
+        <v>1.54</v>
       </c>
       <c r="AE91">
-        <v>2.02</v>
+        <v>1.21</v>
       </c>
       <c r="AF91">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AG91">
-        <v>1.9</v>
+        <v>2.26</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.02</v>
+        <v>1.19</v>
       </c>
       <c r="AK91">
-        <v>11.5</v>
+        <v>2.14</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15258,12 +15258,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.75</v>
+        <v>1.04</v>
       </c>
       <c r="O92">
-        <v>3.45</v>
+        <v>16</v>
       </c>
       <c r="P92">
-        <v>2.34</v>
+        <v>30</v>
       </c>
       <c r="Q92">
-        <v>3.36</v>
+        <v>1.25</v>
       </c>
       <c r="R92">
-        <v>2.18</v>
+        <v>4.7</v>
       </c>
       <c r="S92">
-        <v>1.27</v>
+        <v>1.09</v>
       </c>
       <c r="T92">
-        <v>3.18</v>
+        <v>7.08</v>
       </c>
       <c r="U92">
-        <v>2.23</v>
+        <v>1.49</v>
       </c>
       <c r="V92">
-        <v>1.53</v>
+        <v>2.56</v>
       </c>
       <c r="W92">
-        <v>1.11</v>
+        <v>1.52</v>
       </c>
       <c r="X92">
         <v>1</v>
       </c>
       <c r="Y92">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="Z92">
-        <v>3.98</v>
+        <v>16.5</v>
       </c>
       <c r="AA92">
-        <v>1.66</v>
+        <v>1.14</v>
       </c>
       <c r="AB92">
-        <v>2.15</v>
+        <v>5.5</v>
       </c>
       <c r="AC92">
-        <v>2.49</v>
+        <v>1.33</v>
       </c>
       <c r="AD92">
-        <v>1.42</v>
+        <v>2.93</v>
       </c>
       <c r="AE92">
-        <v>1.16</v>
+        <v>2.02</v>
       </c>
       <c r="AF92">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AG92">
-        <v>2.32</v>
+        <v>1.9</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.23</v>
+        <v>1.02</v>
       </c>
       <c r="AK92">
-        <v>1.36</v>
+        <v>11.5</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15409,7 +15409,7 @@
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:00</t>
+          <t>2026-09-18 15:30:00</t>
         </is>
       </c>
     </row>
@@ -15426,7 +15426,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="O93">
-        <v>3.78</v>
+        <v>3.45</v>
       </c>
       <c r="P93">
-        <v>2.88</v>
+        <v>2.34</v>
       </c>
       <c r="Q93">
-        <v>2.55</v>
+        <v>3.36</v>
       </c>
       <c r="R93">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="S93">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T93">
-        <v>3.38</v>
+        <v>3.18</v>
       </c>
       <c r="U93">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="V93">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="W93">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X93">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y93">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z93">
-        <v>4.6</v>
+        <v>3.98</v>
       </c>
       <c r="AA93">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AB93">
-        <v>2.37</v>
+        <v>2.15</v>
       </c>
       <c r="AC93">
-        <v>2.42</v>
+        <v>2.49</v>
       </c>
       <c r="AD93">
-        <v>1.66</v>
+        <v>1.42</v>
       </c>
       <c r="AE93">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AF93">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AG93">
-        <v>2.53</v>
+        <v>2.32</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="AK93">
-        <v>1.81</v>
+        <v>1.36</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15589,22 +15589,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="O94">
-        <v>3.3</v>
+        <v>3.78</v>
       </c>
       <c r="P94">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="Q94">
-        <v>2.81</v>
+        <v>2.55</v>
       </c>
       <c r="R94">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S94">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="T94">
-        <v>3.02</v>
+        <v>3.38</v>
       </c>
       <c r="U94">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="V94">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="W94">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X94">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y94">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="Z94">
-        <v>3.78</v>
+        <v>4.6</v>
       </c>
       <c r="AA94">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AB94">
-        <v>2.05</v>
+        <v>2.37</v>
       </c>
       <c r="AC94">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="AD94">
-        <v>1.38</v>
+        <v>1.66</v>
       </c>
       <c r="AE94">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AF94">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="AG94">
-        <v>2.23</v>
+        <v>2.53</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AK94">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="O95">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P95">
+        <v>2.8</v>
+      </c>
+      <c r="Q95">
+        <v>2.8</v>
+      </c>
+      <c r="R95">
+        <v>2.18</v>
+      </c>
+      <c r="S95">
+        <v>1.32</v>
+      </c>
+      <c r="T95">
+        <v>3.2</v>
+      </c>
+      <c r="U95">
+        <v>2.47</v>
+      </c>
+      <c r="V95">
+        <v>1.46</v>
+      </c>
+      <c r="W95">
+        <v>1.08</v>
+      </c>
+      <c r="X95">
+        <v>1</v>
+      </c>
+      <c r="Y95">
+        <v>1.19</v>
+      </c>
+      <c r="Z95">
         <v>3.8</v>
       </c>
-      <c r="Q95">
-        <v>2.38</v>
-      </c>
-      <c r="R95">
-        <v>2.22</v>
-      </c>
-      <c r="S95">
-        <v>1.31</v>
-      </c>
-      <c r="T95">
-        <v>3.22</v>
-      </c>
-      <c r="U95">
-        <v>2.56</v>
-      </c>
-      <c r="V95">
-        <v>1.51</v>
-      </c>
-      <c r="W95">
-        <v>1.1</v>
-      </c>
-      <c r="X95">
-        <v>1.03</v>
-      </c>
-      <c r="Y95">
-        <v>1.17</v>
-      </c>
-      <c r="Z95">
-        <v>4</v>
-      </c>
       <c r="AA95">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AB95">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="AC95">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="AD95">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE95">
         <v>1.12</v>
       </c>
       <c r="AF95">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG95">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK95">
-        <v>1.9</v>
+        <v>1.58</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15915,7 +15915,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,80 +15957,80 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="O96">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P96">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="Q96">
-        <v>2.76</v>
+        <v>2.41</v>
       </c>
       <c r="R96">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S96">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T96">
-        <v>2.84</v>
+        <v>3.14</v>
       </c>
       <c r="U96">
+        <v>2.38</v>
+      </c>
+      <c r="V96">
+        <v>1.5</v>
+      </c>
+      <c r="W96">
+        <v>1.1</v>
+      </c>
+      <c r="X96">
+        <v>1.03</v>
+      </c>
+      <c r="Y96">
+        <v>1.18</v>
+      </c>
+      <c r="Z96">
+        <v>3.9</v>
+      </c>
+      <c r="AA96">
+        <v>1.7</v>
+      </c>
+      <c r="AB96">
+        <v>2.1</v>
+      </c>
+      <c r="AC96">
         <v>2.62</v>
       </c>
-      <c r="V96">
-        <v>1.4</v>
-      </c>
-      <c r="W96">
-        <v>1.07</v>
-      </c>
-      <c r="X96">
-        <v>1</v>
-      </c>
-      <c r="Y96">
-        <v>1.24</v>
-      </c>
-      <c r="Z96">
-        <v>3.34</v>
-      </c>
-      <c r="AA96">
-        <v>1.9</v>
-      </c>
-      <c r="AB96">
+      <c r="AD96">
+        <v>1.38</v>
+      </c>
+      <c r="AE96">
+        <v>1.16</v>
+      </c>
+      <c r="AF96">
+        <v>1.6</v>
+      </c>
+      <c r="AG96">
+        <v>2.16</v>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ96">
+        <v>1.26</v>
+      </c>
+      <c r="AK96">
         <v>1.88</v>
-      </c>
-      <c r="AC96">
-        <v>3.19</v>
-      </c>
-      <c r="AD96">
-        <v>1.32</v>
-      </c>
-      <c r="AE96">
-        <v>1.07</v>
-      </c>
-      <c r="AF96">
-        <v>1.67</v>
-      </c>
-      <c r="AG96">
-        <v>2.02</v>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ96">
-        <v>1.25</v>
-      </c>
-      <c r="AK96">
-        <v>1.55</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
+        <v>2.19</v>
+      </c>
+      <c r="O97">
+        <v>3.3</v>
+      </c>
+      <c r="P97">
+        <v>3.1</v>
+      </c>
+      <c r="Q97">
+        <v>2.78</v>
+      </c>
+      <c r="R97">
+        <v>2.05</v>
+      </c>
+      <c r="S97">
+        <v>1.33</v>
+      </c>
+      <c r="T97">
+        <v>2.84</v>
+      </c>
+      <c r="U97">
+        <v>2.82</v>
+      </c>
+      <c r="V97">
         <v>1.4</v>
       </c>
-      <c r="O97">
-        <v>5</v>
-      </c>
-      <c r="P97">
-        <v>6</v>
-      </c>
-      <c r="Q97">
-        <v>1.83</v>
-      </c>
-      <c r="R97">
-        <v>2.57</v>
-      </c>
-      <c r="S97">
-        <v>1.2</v>
-      </c>
-      <c r="T97">
-        <v>3.72</v>
-      </c>
-      <c r="U97">
-        <v>2.22</v>
-      </c>
-      <c r="V97">
-        <v>1.56</v>
-      </c>
       <c r="W97">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X97">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y97">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="Z97">
-        <v>4.64</v>
+        <v>3.34</v>
       </c>
       <c r="AA97">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AB97">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="AC97">
-        <v>2.36</v>
+        <v>3.05</v>
       </c>
       <c r="AD97">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="AE97">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="AF97">
         <v>1.67</v>
       </c>
       <c r="AG97">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AK97">
-        <v>2.61</v>
+        <v>1.62</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>3.8</v>
+        <v>1.47</v>
       </c>
       <c r="O98">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="P98">
-        <v>1.78</v>
+        <v>5.4</v>
       </c>
       <c r="Q98">
-        <v>4.62</v>
+        <v>1.98</v>
       </c>
       <c r="R98">
+        <v>2.5</v>
+      </c>
+      <c r="S98">
+        <v>1.22</v>
+      </c>
+      <c r="T98">
+        <v>3.75</v>
+      </c>
+      <c r="U98">
+        <v>2.1</v>
+      </c>
+      <c r="V98">
+        <v>1.63</v>
+      </c>
+      <c r="W98">
+        <v>1.15</v>
+      </c>
+      <c r="X98">
+        <v>1.02</v>
+      </c>
+      <c r="Y98">
+        <v>1.15</v>
+      </c>
+      <c r="Z98">
+        <v>4.75</v>
+      </c>
+      <c r="AA98">
+        <v>1.46</v>
+      </c>
+      <c r="AB98">
+        <v>2.55</v>
+      </c>
+      <c r="AC98">
         <v>2.17</v>
       </c>
-      <c r="S98">
-        <v>1.3</v>
-      </c>
-      <c r="T98">
-        <v>3.1</v>
-      </c>
-      <c r="U98">
-        <v>2.66</v>
-      </c>
-      <c r="V98">
-        <v>1.44</v>
-      </c>
-      <c r="W98">
-        <v>1.11</v>
-      </c>
-      <c r="X98">
-        <v>1.03</v>
-      </c>
-      <c r="Y98">
-        <v>1.19</v>
-      </c>
-      <c r="Z98">
-        <v>3.76</v>
-      </c>
-      <c r="AA98">
-        <v>1.73</v>
-      </c>
-      <c r="AB98">
-        <v>2</v>
-      </c>
-      <c r="AC98">
-        <v>2.93</v>
-      </c>
       <c r="AD98">
-        <v>1.37</v>
+        <v>1.59</v>
       </c>
       <c r="AE98">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AF98">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AG98">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.91</v>
+        <v>1.07</v>
       </c>
       <c r="AK98">
-        <v>1.16</v>
+        <v>2.34</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,19 +16446,19 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.51</v>
+        <v>1.37</v>
       </c>
       <c r="O99">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="P99">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Q99">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="R99">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="S99">
         <v>1.22</v>
@@ -16467,10 +16467,10 @@
         <v>3.75</v>
       </c>
       <c r="U99">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V99">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W99">
         <v>1.14</v>
@@ -16479,31 +16479,31 @@
         <v>1.02</v>
       </c>
       <c r="Y99">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Z99">
-        <v>4.75</v>
+        <v>4.64</v>
       </c>
       <c r="AA99">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AB99">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AC99">
-        <v>2.17</v>
+        <v>2.33</v>
       </c>
       <c r="AD99">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="AE99">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AF99">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AG99">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AK99">
-        <v>2.4</v>
+        <v>2.61</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,52 +16609,52 @@
         </is>
       </c>
       <c r="N100">
-        <v>2.21</v>
+        <v>3.8</v>
       </c>
       <c r="O100">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="P100">
-        <v>3.1</v>
+        <v>1.78</v>
       </c>
       <c r="Q100">
-        <v>2.7</v>
+        <v>4.57</v>
       </c>
       <c r="R100">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="S100">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T100">
-        <v>2.83</v>
+        <v>2.94</v>
       </c>
       <c r="U100">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="V100">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W100">
         <v>1.05</v>
       </c>
       <c r="X100">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y100">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z100">
-        <v>3.72</v>
+        <v>3.76</v>
       </c>
       <c r="AA100">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB100">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AC100">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="AD100">
         <v>1.33</v>
@@ -16663,10 +16663,10 @@
         <v>1.09</v>
       </c>
       <c r="AF100">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG100">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AK100">
-        <v>1.6</v>
+        <v>1.16</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16730,22 +16730,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,61 +16772,61 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.9</v>
+        <v>2.21</v>
       </c>
       <c r="O101">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="P101">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q101">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="R101">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="S101">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T101">
-        <v>2.99</v>
+        <v>2.83</v>
       </c>
       <c r="U101">
-        <v>2.66</v>
+        <v>2.57</v>
       </c>
       <c r="V101">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W101">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X101">
         <v>1</v>
       </c>
       <c r="Y101">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z101">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="AA101">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AB101">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AC101">
-        <v>3.07</v>
+        <v>2.81</v>
       </c>
       <c r="AD101">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE101">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF101">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG101">
         <v>2.18</v>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AK101">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16893,7 +16893,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.84</v>
+        <v>2.9</v>
       </c>
       <c r="O102">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="P102">
-        <v>3.63</v>
+        <v>2.3</v>
       </c>
       <c r="Q102">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R102">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S102">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T102">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U102">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V102">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W102">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X102">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y102">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z102">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA102">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="AB102">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AC102">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AD102">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE102">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF102">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG102">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AK102">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17051,12 +17051,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.95</v>
+        <v>1.84</v>
       </c>
       <c r="O103">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="P103">
-        <v>2.31</v>
+        <v>3.63</v>
       </c>
       <c r="Q103">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R103">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S103">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="T103">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="U103">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="V103">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="W103">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X103">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y103">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Z103">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA103">
-        <v>1.5</v>
+        <v>2.05</v>
       </c>
       <c r="AB103">
-        <v>2.63</v>
+        <v>1.75</v>
       </c>
       <c r="AC103">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD103">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE103">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AF103">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG103">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AK103">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17202,7 +17202,7 @@
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>2026-09-18 16:00:00</t>
+          <t>2026-09-18 15:45:00</t>
         </is>
       </c>
     </row>
@@ -17219,7 +17219,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,80 +17261,80 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.97</v>
+        <v>2.55</v>
       </c>
       <c r="O104">
-        <v>3.15</v>
+        <v>3.83</v>
       </c>
       <c r="P104">
-        <v>3.9</v>
+        <v>2.25</v>
       </c>
       <c r="Q104">
-        <v>2.65</v>
+        <v>3.07</v>
       </c>
       <c r="R104">
-        <v>1.93</v>
+        <v>2.37</v>
       </c>
       <c r="S104">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="T104">
-        <v>2.42</v>
+        <v>3.94</v>
       </c>
       <c r="U104">
-        <v>3.06</v>
+        <v>2.2</v>
       </c>
       <c r="V104">
+        <v>1.69</v>
+      </c>
+      <c r="W104">
+        <v>1.18</v>
+      </c>
+      <c r="X104">
+        <v>1.01</v>
+      </c>
+      <c r="Y104">
+        <v>1.08</v>
+      </c>
+      <c r="Z104">
+        <v>5.5</v>
+      </c>
+      <c r="AA104">
+        <v>1.42</v>
+      </c>
+      <c r="AB104">
+        <v>2.61</v>
+      </c>
+      <c r="AC104">
+        <v>2.23</v>
+      </c>
+      <c r="AD104">
+        <v>1.76</v>
+      </c>
+      <c r="AE104">
+        <v>1.25</v>
+      </c>
+      <c r="AF104">
+        <v>1.39</v>
+      </c>
+      <c r="AG104">
+        <v>2.81</v>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ104">
         <v>1.29</v>
       </c>
-      <c r="W104">
-        <v>1.04</v>
-      </c>
-      <c r="X104">
-        <v>1.05</v>
-      </c>
-      <c r="Y104">
-        <v>1.41</v>
-      </c>
-      <c r="Z104">
-        <v>2.52</v>
-      </c>
-      <c r="AA104">
-        <v>2.37</v>
-      </c>
-      <c r="AB104">
-        <v>1.53</v>
-      </c>
-      <c r="AC104">
-        <v>4.25</v>
-      </c>
-      <c r="AD104">
-        <v>1.15</v>
-      </c>
-      <c r="AE104">
-        <v>1.02</v>
-      </c>
-      <c r="AF104">
-        <v>2.02</v>
-      </c>
-      <c r="AG104">
-        <v>1.69</v>
-      </c>
-      <c r="AH104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ104">
-        <v>1.27</v>
-      </c>
       <c r="AK104">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17382,22 +17382,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.4</v>
+        <v>1.97</v>
       </c>
       <c r="O105">
-        <v>4.33</v>
+        <v>3.15</v>
       </c>
       <c r="P105">
-        <v>5.75</v>
+        <v>3.9</v>
       </c>
       <c r="Q105">
-        <v>1.83</v>
+        <v>2.65</v>
       </c>
       <c r="R105">
-        <v>2.6</v>
+        <v>1.93</v>
       </c>
       <c r="S105">
-        <v>1.23</v>
+        <v>1.45</v>
       </c>
       <c r="T105">
-        <v>3.5</v>
+        <v>2.42</v>
       </c>
       <c r="U105">
-        <v>2.34</v>
+        <v>3.06</v>
       </c>
       <c r="V105">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="W105">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="X105">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y105">
-        <v>1.13</v>
+        <v>1.41</v>
       </c>
       <c r="Z105">
-        <v>4.55</v>
+        <v>2.52</v>
       </c>
       <c r="AA105">
-        <v>1.51</v>
+        <v>2.37</v>
       </c>
       <c r="AB105">
-        <v>2.26</v>
+        <v>1.53</v>
       </c>
       <c r="AC105">
-        <v>2.38</v>
+        <v>4.25</v>
       </c>
       <c r="AD105">
-        <v>1.54</v>
+        <v>1.15</v>
       </c>
       <c r="AE105">
-        <v>1.21</v>
+        <v>1.02</v>
       </c>
       <c r="AF105">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="AG105">
-        <v>1.9</v>
+        <v>1.69</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AK105">
-        <v>2.8</v>
+        <v>1.67</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="O106">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="P106">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="Q106">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="R106">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="S106">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="T106">
-        <v>3.32</v>
+        <v>3.48</v>
       </c>
       <c r="U106">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="V106">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="W106">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X106">
         <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z106">
-        <v>4.45</v>
+        <v>4.55</v>
       </c>
       <c r="AA106">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB106">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AC106">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="AD106">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AE106">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF106">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AG106">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK106">
-        <v>3.2</v>
+        <v>2.64</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17708,22 +17708,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,65 +17750,65 @@
         </is>
       </c>
       <c r="N107">
+        <v>1.4</v>
+      </c>
+      <c r="O107">
+        <v>4.33</v>
+      </c>
+      <c r="P107">
+        <v>6.5</v>
+      </c>
+      <c r="Q107">
+        <v>1.88</v>
+      </c>
+      <c r="R107">
+        <v>2.5</v>
+      </c>
+      <c r="S107">
+        <v>1.31</v>
+      </c>
+      <c r="T107">
+        <v>3.08</v>
+      </c>
+      <c r="U107">
+        <v>2.39</v>
+      </c>
+      <c r="V107">
+        <v>1.49</v>
+      </c>
+      <c r="W107">
+        <v>1.08</v>
+      </c>
+      <c r="X107">
+        <v>1.02</v>
+      </c>
+      <c r="Y107">
+        <v>1.15</v>
+      </c>
+      <c r="Z107">
+        <v>4.3</v>
+      </c>
+      <c r="AA107">
+        <v>1.62</v>
+      </c>
+      <c r="AB107">
+        <v>2.21</v>
+      </c>
+      <c r="AC107">
+        <v>2.33</v>
+      </c>
+      <c r="AD107">
+        <v>1.44</v>
+      </c>
+      <c r="AE107">
+        <v>1.14</v>
+      </c>
+      <c r="AF107">
+        <v>1.84</v>
+      </c>
+      <c r="AG107">
         <v>1.85</v>
       </c>
-      <c r="O107">
-        <v>3.46</v>
-      </c>
-      <c r="P107">
-        <v>4.28</v>
-      </c>
-      <c r="Q107">
-        <v>2.51</v>
-      </c>
-      <c r="R107">
-        <v>2.1</v>
-      </c>
-      <c r="S107">
-        <v>1.42</v>
-      </c>
-      <c r="T107">
-        <v>2.79</v>
-      </c>
-      <c r="U107">
-        <v>2.88</v>
-      </c>
-      <c r="V107">
-        <v>1.4</v>
-      </c>
-      <c r="W107">
-        <v>1.05</v>
-      </c>
-      <c r="X107">
-        <v>1</v>
-      </c>
-      <c r="Y107">
-        <v>1.26</v>
-      </c>
-      <c r="Z107">
-        <v>3.4</v>
-      </c>
-      <c r="AA107">
-        <v>1.9</v>
-      </c>
-      <c r="AB107">
-        <v>1.9</v>
-      </c>
-      <c r="AC107">
-        <v>3.14</v>
-      </c>
-      <c r="AD107">
-        <v>1.3</v>
-      </c>
-      <c r="AE107">
-        <v>1.06</v>
-      </c>
-      <c r="AF107">
-        <v>1.77</v>
-      </c>
-      <c r="AG107">
-        <v>1.96</v>
-      </c>
       <c r="AH107" t="inlineStr">
         <is>
           <t>[]</t>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="AK107">
-        <v>1.95</v>
+        <v>2.91</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17871,7 +17871,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,43 +17913,43 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="O108">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P108">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="Q108">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="R108">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="S108">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T108">
-        <v>2.72</v>
+        <v>2.79</v>
       </c>
       <c r="U108">
-        <v>2.67</v>
+        <v>2.88</v>
       </c>
       <c r="V108">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W108">
         <v>1.05</v>
       </c>
       <c r="X108">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y108">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z108">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="AA108">
         <v>1.9</v>
@@ -17958,19 +17958,19 @@
         <v>1.9</v>
       </c>
       <c r="AC108">
-        <v>2.97</v>
+        <v>3.14</v>
       </c>
       <c r="AD108">
         <v>1.3</v>
       </c>
       <c r="AE108">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF108">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AG108">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AK108">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18029,12 +18029,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q109">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R109">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S109">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T109">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U109">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="V109">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W109">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X109">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y109">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z109">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA109">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB109">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC109">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AD109">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE109">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF109">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG109">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK109">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18180,7 +18180,7 @@
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>2026-09-18 17:00:00</t>
+          <t>2026-09-18 16:00:00</t>
         </is>
       </c>
     </row>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G110">
@@ -18355,27 +18355,27 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="O111">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P111">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="Q111">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R111">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S111">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T111">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U111">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="V111">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W111">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X111">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y111">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z111">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AA111">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB111">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC111">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AD111">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE111">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF111">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG111">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK111">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18506,7 +18506,7 @@
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>2026-09-18 19:30:00</t>
+          <t>2026-09-18 17:00:00</t>
         </is>
       </c>
     </row>
@@ -18518,12 +18518,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,81 +18565,81 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
       <c r="O112">
         <v>4.1</v>
       </c>
       <c r="P112">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="Q112">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="R112">
+        <v>2.2</v>
+      </c>
+      <c r="S112">
+        <v>1.35</v>
+      </c>
+      <c r="T112">
+        <v>2.88</v>
+      </c>
+      <c r="U112">
+        <v>2.67</v>
+      </c>
+      <c r="V112">
+        <v>1.4</v>
+      </c>
+      <c r="W112">
+        <v>1.06</v>
+      </c>
+      <c r="X112">
+        <v>1.01</v>
+      </c>
+      <c r="Y112">
+        <v>1.24</v>
+      </c>
+      <c r="Z112">
+        <v>3.34</v>
+      </c>
+      <c r="AA112">
+        <v>1.89</v>
+      </c>
+      <c r="AB112">
+        <v>1.93</v>
+      </c>
+      <c r="AC112">
+        <v>3.04</v>
+      </c>
+      <c r="AD112">
+        <v>1.29</v>
+      </c>
+      <c r="AE112">
+        <v>1.07</v>
+      </c>
+      <c r="AF112">
+        <v>1.93</v>
+      </c>
+      <c r="AG112">
+        <v>1.78</v>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ112">
+        <v>1.08</v>
+      </c>
+      <c r="AK112">
         <v>2.39</v>
       </c>
-      <c r="S112">
-        <v>1.22</v>
-      </c>
-      <c r="T112">
-        <v>4</v>
-      </c>
-      <c r="U112">
-        <v>2.05</v>
-      </c>
-      <c r="V112">
-        <v>1.7</v>
-      </c>
-      <c r="W112">
-        <v>1.18</v>
-      </c>
-      <c r="X112">
-        <v>1.02</v>
-      </c>
-      <c r="Y112">
-        <v>1.09</v>
-      </c>
-      <c r="Z112">
-        <v>5.35</v>
-      </c>
-      <c r="AA112">
-        <v>1.4</v>
-      </c>
-      <c r="AB112">
-        <v>2.56</v>
-      </c>
-      <c r="AC112">
-        <v>2.05</v>
-      </c>
-      <c r="AD112">
-        <v>1.66</v>
-      </c>
-      <c r="AE112">
-        <v>1.25</v>
-      </c>
-      <c r="AF112">
-        <v>1.44</v>
-      </c>
-      <c r="AG112">
-        <v>2.48</v>
-      </c>
-      <c r="AH112" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI112" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ112">
-        <v>1.16</v>
-      </c>
-      <c r="AK112">
-        <v>2.2</v>
-      </c>
       <c r="AL112">
         <v>0</v>
       </c>
@@ -18669,7 +18669,7 @@
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>2026-09-18 20:00:00</t>
+          <t>2026-09-18 19:30:00</t>
         </is>
       </c>
     </row>
@@ -18681,12 +18681,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,61 +18728,61 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="O113">
-        <v>4.12</v>
+        <v>4.1</v>
       </c>
       <c r="P113">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="Q113">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="R113">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="S113">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T113">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="U113">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="V113">
+        <v>1.68</v>
+      </c>
+      <c r="W113">
+        <v>1.18</v>
+      </c>
+      <c r="X113">
+        <v>1.02</v>
+      </c>
+      <c r="Y113">
+        <v>1.09</v>
+      </c>
+      <c r="Z113">
+        <v>5.35</v>
+      </c>
+      <c r="AA113">
+        <v>1.44</v>
+      </c>
+      <c r="AB113">
+        <v>2.7</v>
+      </c>
+      <c r="AC113">
+        <v>2.05</v>
+      </c>
+      <c r="AD113">
         <v>1.66</v>
-      </c>
-      <c r="W113">
-        <v>1.15</v>
-      </c>
-      <c r="X113">
-        <v>0</v>
-      </c>
-      <c r="Y113">
-        <v>1.11</v>
-      </c>
-      <c r="Z113">
-        <v>5.75</v>
-      </c>
-      <c r="AA113">
-        <v>1.41</v>
-      </c>
-      <c r="AB113">
-        <v>2.63</v>
-      </c>
-      <c r="AC113">
-        <v>2.07</v>
-      </c>
-      <c r="AD113">
-        <v>1.7</v>
       </c>
       <c r="AE113">
         <v>1.25</v>
       </c>
       <c r="AF113">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AG113">
         <v>2.53</v>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK113">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18832,7 +18832,7 @@
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>2026-09-18 20:30:00</t>
+          <t>2026-09-18 20:00:00</t>
         </is>
       </c>
     </row>
@@ -18849,7 +18849,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,80 +18891,80 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.75</v>
+        <v>1.75</v>
       </c>
       <c r="O114">
-        <v>3.1</v>
+        <v>4.12</v>
       </c>
       <c r="P114">
-        <v>2.45</v>
+        <v>4</v>
       </c>
       <c r="Q114">
-        <v>3.48</v>
+        <v>2.13</v>
       </c>
       <c r="R114">
+        <v>2.5</v>
+      </c>
+      <c r="S114">
+        <v>1.22</v>
+      </c>
+      <c r="T114">
+        <v>4.1</v>
+      </c>
+      <c r="U114">
+        <v>2.08</v>
+      </c>
+      <c r="V114">
+        <v>1.66</v>
+      </c>
+      <c r="W114">
+        <v>1.15</v>
+      </c>
+      <c r="X114">
+        <v>0</v>
+      </c>
+      <c r="Y114">
+        <v>1.11</v>
+      </c>
+      <c r="Z114">
+        <v>5.75</v>
+      </c>
+      <c r="AA114">
+        <v>1.41</v>
+      </c>
+      <c r="AB114">
+        <v>2.63</v>
+      </c>
+      <c r="AC114">
+        <v>2.07</v>
+      </c>
+      <c r="AD114">
+        <v>1.7</v>
+      </c>
+      <c r="AE114">
+        <v>1.25</v>
+      </c>
+      <c r="AF114">
+        <v>1.44</v>
+      </c>
+      <c r="AG114">
+        <v>2.53</v>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ114">
+        <v>1.22</v>
+      </c>
+      <c r="AK114">
         <v>2</v>
-      </c>
-      <c r="S114">
-        <v>1.39</v>
-      </c>
-      <c r="T114">
-        <v>2.71</v>
-      </c>
-      <c r="U114">
-        <v>2.9</v>
-      </c>
-      <c r="V114">
-        <v>1.36</v>
-      </c>
-      <c r="W114">
-        <v>1.07</v>
-      </c>
-      <c r="X114">
-        <v>1.02</v>
-      </c>
-      <c r="Y114">
-        <v>1.36</v>
-      </c>
-      <c r="Z114">
-        <v>2.9</v>
-      </c>
-      <c r="AA114">
-        <v>2.3</v>
-      </c>
-      <c r="AB114">
-        <v>1.6</v>
-      </c>
-      <c r="AC114">
-        <v>3.68</v>
-      </c>
-      <c r="AD114">
-        <v>1.2</v>
-      </c>
-      <c r="AE114">
-        <v>1.03</v>
-      </c>
-      <c r="AF114">
-        <v>1.82</v>
-      </c>
-      <c r="AG114">
-        <v>1.88</v>
-      </c>
-      <c r="AH114" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI114" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ114">
-        <v>1.33</v>
-      </c>
-      <c r="AK114">
-        <v>1.4</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19007,27 +19007,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O115">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P115">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q115">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R115">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S115">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T115">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U115">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V115">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W115">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X115">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y115">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z115">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA115">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB115">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC115">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AD115">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE115">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF115">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG115">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK115">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19158,7 +19158,7 @@
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>2026-09-18 21:00:00</t>
+          <t>2026-09-18 20:30:00</t>
         </is>
       </c>
     </row>
@@ -19175,7 +19175,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G116">
@@ -19338,22 +19338,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="O117">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P117">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="Q117">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R117">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S117">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T117">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U117">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V117">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W117">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X117">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y117">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z117">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA117">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB117">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC117">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD117">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE117">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF117">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG117">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK117">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19496,27 +19496,27 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G118">
@@ -19552,55 +19552,55 @@
         <v>0</v>
       </c>
       <c r="Q118">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="R118">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S118">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T118">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U118">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V118">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W118">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X118">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y118">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z118">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA118">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB118">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC118">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD118">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE118">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF118">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG118">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK118">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19646,332 +19646,6 @@
         <v>0</v>
       </c>
       <c r="AU118" t="inlineStr">
-        <is>
-          <t>2026-09-18 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>São Bernardo</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>Atlético GO</t>
-        </is>
-      </c>
-      <c r="G119">
-        <v>0</v>
-      </c>
-      <c r="H119">
-        <v>0</v>
-      </c>
-      <c r="I119">
-        <v>0</v>
-      </c>
-      <c r="J119">
-        <v>0</v>
-      </c>
-      <c r="K119">
-        <v>0</v>
-      </c>
-      <c r="L119">
-        <v>0</v>
-      </c>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N119">
-        <v>2.3</v>
-      </c>
-      <c r="O119">
-        <v>3.1</v>
-      </c>
-      <c r="P119">
-        <v>2.9</v>
-      </c>
-      <c r="Q119">
-        <v>3</v>
-      </c>
-      <c r="R119">
-        <v>1.96</v>
-      </c>
-      <c r="S119">
-        <v>1.44</v>
-      </c>
-      <c r="T119">
-        <v>2.53</v>
-      </c>
-      <c r="U119">
-        <v>2.96</v>
-      </c>
-      <c r="V119">
-        <v>1.33</v>
-      </c>
-      <c r="W119">
-        <v>1.03</v>
-      </c>
-      <c r="X119">
-        <v>1.02</v>
-      </c>
-      <c r="Y119">
-        <v>1.31</v>
-      </c>
-      <c r="Z119">
-        <v>3.1</v>
-      </c>
-      <c r="AA119">
-        <v>2.08</v>
-      </c>
-      <c r="AB119">
-        <v>1.72</v>
-      </c>
-      <c r="AC119">
-        <v>3.5</v>
-      </c>
-      <c r="AD119">
-        <v>1.22</v>
-      </c>
-      <c r="AE119">
-        <v>1.04</v>
-      </c>
-      <c r="AF119">
-        <v>1.81</v>
-      </c>
-      <c r="AG119">
-        <v>1.9</v>
-      </c>
-      <c r="AH119" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI119" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ119">
-        <v>1.32</v>
-      </c>
-      <c r="AK119">
-        <v>1.53</v>
-      </c>
-      <c r="AL119">
-        <v>0</v>
-      </c>
-      <c r="AM119">
-        <v>-1</v>
-      </c>
-      <c r="AN119">
-        <v>-1</v>
-      </c>
-      <c r="AO119">
-        <v>-1</v>
-      </c>
-      <c r="AP119">
-        <v>-1</v>
-      </c>
-      <c r="AQ119">
-        <v>0</v>
-      </c>
-      <c r="AR119">
-        <v>0</v>
-      </c>
-      <c r="AS119">
-        <v>0</v>
-      </c>
-      <c r="AT119">
-        <v>0</v>
-      </c>
-      <c r="AU119" t="inlineStr">
-        <is>
-          <t>2026-09-18 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>San Diego Wave</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>Kansas City</t>
-        </is>
-      </c>
-      <c r="G120">
-        <v>0</v>
-      </c>
-      <c r="H120">
-        <v>0</v>
-      </c>
-      <c r="I120">
-        <v>0</v>
-      </c>
-      <c r="J120">
-        <v>0</v>
-      </c>
-      <c r="K120">
-        <v>0</v>
-      </c>
-      <c r="L120">
-        <v>0</v>
-      </c>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N120">
-        <v>0</v>
-      </c>
-      <c r="O120">
-        <v>0</v>
-      </c>
-      <c r="P120">
-        <v>0</v>
-      </c>
-      <c r="Q120">
-        <v>0</v>
-      </c>
-      <c r="R120">
-        <v>0</v>
-      </c>
-      <c r="S120">
-        <v>0</v>
-      </c>
-      <c r="T120">
-        <v>0</v>
-      </c>
-      <c r="U120">
-        <v>0</v>
-      </c>
-      <c r="V120">
-        <v>0</v>
-      </c>
-      <c r="W120">
-        <v>0</v>
-      </c>
-      <c r="X120">
-        <v>0</v>
-      </c>
-      <c r="Y120">
-        <v>0</v>
-      </c>
-      <c r="Z120">
-        <v>0</v>
-      </c>
-      <c r="AA120">
-        <v>0</v>
-      </c>
-      <c r="AB120">
-        <v>0</v>
-      </c>
-      <c r="AC120">
-        <v>0</v>
-      </c>
-      <c r="AD120">
-        <v>0</v>
-      </c>
-      <c r="AE120">
-        <v>0</v>
-      </c>
-      <c r="AF120">
-        <v>0</v>
-      </c>
-      <c r="AG120">
-        <v>0</v>
-      </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI120" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ120">
-        <v>0</v>
-      </c>
-      <c r="AK120">
-        <v>0</v>
-      </c>
-      <c r="AL120">
-        <v>0</v>
-      </c>
-      <c r="AM120">
-        <v>-1</v>
-      </c>
-      <c r="AN120">
-        <v>-1</v>
-      </c>
-      <c r="AO120">
-        <v>-1</v>
-      </c>
-      <c r="AP120">
-        <v>-1</v>
-      </c>
-      <c r="AQ120">
-        <v>0</v>
-      </c>
-      <c r="AR120">
-        <v>0</v>
-      </c>
-      <c r="AS120">
-        <v>0</v>
-      </c>
-      <c r="AT120">
-        <v>0</v>
-      </c>
-      <c r="AU120" t="inlineStr">
         <is>
           <t>2026-09-18 23:00:00</t>
         </is>

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,65 +11067,65 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.26</v>
+        <v>1.75</v>
       </c>
       <c r="O66">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P66">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="Q66">
-        <v>2.92</v>
+        <v>2.32</v>
       </c>
       <c r="R66">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="S66">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="T66">
-        <v>2.67</v>
+        <v>3.08</v>
       </c>
       <c r="U66">
-        <v>2.91</v>
+        <v>2.5</v>
       </c>
       <c r="V66">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="W66">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X66">
         <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="Z66">
-        <v>3.04</v>
+        <v>3.82</v>
       </c>
       <c r="AA66">
+        <v>1.7</v>
+      </c>
+      <c r="AB66">
+        <v>2</v>
+      </c>
+      <c r="AC66">
+        <v>3.1</v>
+      </c>
+      <c r="AD66">
+        <v>1.36</v>
+      </c>
+      <c r="AE66">
+        <v>1.1</v>
+      </c>
+      <c r="AF66">
+        <v>1.64</v>
+      </c>
+      <c r="AG66">
         <v>2.15</v>
       </c>
-      <c r="AB66">
-        <v>1.67</v>
-      </c>
-      <c r="AC66">
-        <v>3.42</v>
-      </c>
-      <c r="AD66">
-        <v>1.23</v>
-      </c>
-      <c r="AE66">
-        <v>1.05</v>
-      </c>
-      <c r="AF66">
-        <v>1.78</v>
-      </c>
-      <c r="AG66">
-        <v>1.93</v>
-      </c>
       <c r="AH66" t="inlineStr">
         <is>
           <t>[]</t>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AK66">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.75</v>
+        <v>2.26</v>
       </c>
       <c r="O67">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P67">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q67">
-        <v>2.32</v>
+        <v>2.92</v>
       </c>
       <c r="R67">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="S67">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="T67">
-        <v>3.08</v>
+        <v>2.67</v>
       </c>
       <c r="U67">
-        <v>2.5</v>
+        <v>2.91</v>
       </c>
       <c r="V67">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="W67">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X67">
         <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="Z67">
-        <v>3.82</v>
+        <v>3.04</v>
       </c>
       <c r="AA67">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="AB67">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AC67">
-        <v>3.1</v>
+        <v>3.42</v>
       </c>
       <c r="AD67">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AE67">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF67">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="AG67">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK67">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="O112">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="P112">
-        <v>6.2</v>
+        <v>5.75</v>
       </c>
       <c r="Q112">
         <v>2.05</v>
@@ -18580,28 +18580,28 @@
         <v>2.2</v>
       </c>
       <c r="S112">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T112">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U112">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="V112">
         <v>1.4</v>
       </c>
       <c r="W112">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X112">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y112">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Z112">
-        <v>3.34</v>
+        <v>3.64</v>
       </c>
       <c r="AA112">
         <v>1.89</v>
@@ -18616,7 +18616,7 @@
         <v>1.29</v>
       </c>
       <c r="AE112">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF112">
         <v>1.93</v>
@@ -18638,7 +18638,7 @@
         <v>1.08</v>
       </c>
       <c r="AK112">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18737,22 +18737,22 @@
         <v>4.5</v>
       </c>
       <c r="Q113">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R113">
         <v>2.39</v>
       </c>
       <c r="S113">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T113">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U113">
         <v>2.02</v>
       </c>
       <c r="V113">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="W113">
         <v>1.18</v>
@@ -18767,10 +18767,10 @@
         <v>5.35</v>
       </c>
       <c r="AA113">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB113">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="AC113">
         <v>2.05</v>
@@ -18798,7 +18798,7 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AK113">
         <v>2.03</v>
@@ -19069,10 +19069,10 @@
         <v>2</v>
       </c>
       <c r="S115">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T115">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="U115">
         <v>2.9</v>
@@ -19093,10 +19093,10 @@
         <v>2.9</v>
       </c>
       <c r="AA115">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AB115">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AC115">
         <v>3.68</v>
@@ -19111,7 +19111,7 @@
         <v>1.82</v>
       </c>
       <c r="AG115">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19401,13 +19401,13 @@
         <v>2.53</v>
       </c>
       <c r="U117">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="V117">
         <v>1.33</v>
       </c>
       <c r="W117">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X117">
         <v>1.02</v>
@@ -19416,13 +19416,13 @@
         <v>1.31</v>
       </c>
       <c r="Z117">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AA117">
         <v>2.08</v>
       </c>
       <c r="AB117">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AC117">
         <v>3.5</v>
@@ -19450,7 +19450,7 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AK117">
         <v>1.53</v>

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU118"/>
+  <dimension ref="A1:AU117"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,16 +798,16 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="O3">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P3">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="Q3">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="R3">
         <v>2.21</v>
@@ -831,19 +831,19 @@
         <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="Z3">
-        <v>3.74</v>
+        <v>3.94</v>
       </c>
       <c r="AA3">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AB3">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AC3">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AD3">
         <v>1.36</v>
@@ -2102,16 +2102,16 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="O11">
         <v>3.2</v>
       </c>
       <c r="P11">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="Q11">
-        <v>2.84</v>
+        <v>2.53</v>
       </c>
       <c r="R11">
         <v>1.98</v>
@@ -2141,25 +2141,25 @@
         <v>3.2</v>
       </c>
       <c r="AA11">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB11">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AC11">
-        <v>3.2</v>
+        <v>3.33</v>
       </c>
       <c r="AD11">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE11">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF11">
         <v>1.7</v>
       </c>
       <c r="AG11">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK11">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -8963,7 +8963,7 @@
         <v>2.35</v>
       </c>
       <c r="S53">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T53">
         <v>3.02</v>
@@ -8972,7 +8972,7 @@
         <v>2.5</v>
       </c>
       <c r="V53">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W53">
         <v>1.11</v>
@@ -8987,10 +8987,10 @@
         <v>3.88</v>
       </c>
       <c r="AA53">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AB53">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AC53">
         <v>2.69</v>
@@ -9002,10 +9002,10 @@
         <v>1.11</v>
       </c>
       <c r="AF53">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AG53">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9120,7 +9120,7 @@
         <v>1.45</v>
       </c>
       <c r="Q54">
-        <v>7.43</v>
+        <v>7.2</v>
       </c>
       <c r="R54">
         <v>2.3</v>
@@ -9132,10 +9132,10 @@
         <v>2.92</v>
       </c>
       <c r="U54">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="V54">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W54">
         <v>1.09</v>
@@ -9150,10 +9150,10 @@
         <v>3.5</v>
       </c>
       <c r="AA54">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB54">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC54">
         <v>2.97</v>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK54">
         <v>1.06</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,16 +16283,16 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="O98">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="P98">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="Q98">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="R98">
         <v>2.5</v>
@@ -16304,43 +16304,43 @@
         <v>3.75</v>
       </c>
       <c r="U98">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="V98">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="W98">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X98">
         <v>1.02</v>
       </c>
       <c r="Y98">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z98">
-        <v>4.75</v>
+        <v>4.64</v>
       </c>
       <c r="AA98">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AB98">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AC98">
-        <v>2.17</v>
+        <v>2.33</v>
       </c>
       <c r="AD98">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="AE98">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AF98">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="AG98">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AK98">
-        <v>2.34</v>
+        <v>2.61</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,16 +16446,16 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="O99">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="P99">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="Q99">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="R99">
         <v>2.5</v>
@@ -16467,43 +16467,43 @@
         <v>3.75</v>
       </c>
       <c r="U99">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="V99">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="W99">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X99">
         <v>1.02</v>
       </c>
       <c r="Y99">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z99">
-        <v>4.64</v>
+        <v>4.75</v>
       </c>
       <c r="AA99">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AB99">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AC99">
-        <v>2.33</v>
+        <v>2.17</v>
       </c>
       <c r="AD99">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="AE99">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AF99">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AG99">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AK99">
-        <v>2.61</v>
+        <v>2.34</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -19175,22 +19175,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O116">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P116">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q116">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R116">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S116">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T116">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U116">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V116">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W116">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X116">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y116">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z116">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA116">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB116">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC116">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD116">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE116">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF116">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG116">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK116">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19333,12 +19333,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
+        <v>0</v>
+      </c>
+      <c r="O117">
+        <v>0</v>
+      </c>
+      <c r="P117">
+        <v>0</v>
+      </c>
+      <c r="Q117">
+        <v>2.59</v>
+      </c>
+      <c r="R117">
         <v>2.3</v>
       </c>
-      <c r="O117">
-        <v>3.1</v>
-      </c>
-      <c r="P117">
-        <v>2.9</v>
-      </c>
-      <c r="Q117">
-        <v>3</v>
-      </c>
-      <c r="R117">
-        <v>1.96</v>
-      </c>
       <c r="S117">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="T117">
-        <v>2.53</v>
+        <v>3.24</v>
       </c>
       <c r="U117">
-        <v>3.15</v>
+        <v>2.45</v>
       </c>
       <c r="V117">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="W117">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X117">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y117">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="Z117">
-        <v>3.08</v>
+        <v>3.95</v>
       </c>
       <c r="AA117">
+        <v>1.64</v>
+      </c>
+      <c r="AB117">
         <v>2.08</v>
       </c>
-      <c r="AB117">
-        <v>1.69</v>
-      </c>
       <c r="AC117">
-        <v>3.5</v>
+        <v>2.56</v>
       </c>
       <c r="AD117">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AE117">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AF117">
-        <v>1.81</v>
+        <v>1.54</v>
       </c>
       <c r="AG117">
-        <v>1.9</v>
+        <v>2.22</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AK117">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19483,169 +19483,6 @@
         <v>0</v>
       </c>
       <c r="AU117" t="inlineStr">
-        <is>
-          <t>2026-09-18 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>San Diego Wave</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>Kansas City</t>
-        </is>
-      </c>
-      <c r="G118">
-        <v>0</v>
-      </c>
-      <c r="H118">
-        <v>0</v>
-      </c>
-      <c r="I118">
-        <v>0</v>
-      </c>
-      <c r="J118">
-        <v>0</v>
-      </c>
-      <c r="K118">
-        <v>0</v>
-      </c>
-      <c r="L118">
-        <v>0</v>
-      </c>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N118">
-        <v>0</v>
-      </c>
-      <c r="O118">
-        <v>0</v>
-      </c>
-      <c r="P118">
-        <v>0</v>
-      </c>
-      <c r="Q118">
-        <v>2.59</v>
-      </c>
-      <c r="R118">
-        <v>2.3</v>
-      </c>
-      <c r="S118">
-        <v>1.26</v>
-      </c>
-      <c r="T118">
-        <v>3.24</v>
-      </c>
-      <c r="U118">
-        <v>2.45</v>
-      </c>
-      <c r="V118">
-        <v>1.51</v>
-      </c>
-      <c r="W118">
-        <v>1.1</v>
-      </c>
-      <c r="X118">
-        <v>1.03</v>
-      </c>
-      <c r="Y118">
-        <v>1.17</v>
-      </c>
-      <c r="Z118">
-        <v>3.95</v>
-      </c>
-      <c r="AA118">
-        <v>1.64</v>
-      </c>
-      <c r="AB118">
-        <v>2.08</v>
-      </c>
-      <c r="AC118">
-        <v>2.56</v>
-      </c>
-      <c r="AD118">
-        <v>1.4</v>
-      </c>
-      <c r="AE118">
-        <v>1.13</v>
-      </c>
-      <c r="AF118">
-        <v>1.54</v>
-      </c>
-      <c r="AG118">
-        <v>2.22</v>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI118" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ118">
-        <v>1.21</v>
-      </c>
-      <c r="AK118">
-        <v>1.59</v>
-      </c>
-      <c r="AL118">
-        <v>0</v>
-      </c>
-      <c r="AM118">
-        <v>-1</v>
-      </c>
-      <c r="AN118">
-        <v>-1</v>
-      </c>
-      <c r="AO118">
-        <v>-1</v>
-      </c>
-      <c r="AP118">
-        <v>-1</v>
-      </c>
-      <c r="AQ118">
-        <v>0</v>
-      </c>
-      <c r="AR118">
-        <v>0</v>
-      </c>
-      <c r="AS118">
-        <v>0</v>
-      </c>
-      <c r="AT118">
-        <v>0</v>
-      </c>
-      <c r="AU118" t="inlineStr">
         <is>
           <t>2026-09-18 23:00:00</t>
         </is>

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="O2">
-        <v>3.21</v>
+        <v>3.1</v>
       </c>
       <c r="P2">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="Q2">
-        <v>4.38</v>
+        <v>4.32</v>
       </c>
       <c r="R2">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="S2">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T2">
-        <v>2.51</v>
+        <v>2.63</v>
       </c>
       <c r="U2">
-        <v>3.18</v>
+        <v>2.96</v>
       </c>
       <c r="V2">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W2">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X2">
         <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="Z2">
-        <v>2.78</v>
+        <v>2.89</v>
       </c>
       <c r="AA2">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AB2">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC2">
-        <v>4.05</v>
+        <v>4.33</v>
       </c>
       <c r="AD2">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE2">
         <v>1.01</v>
       </c>
       <c r="AF2">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AG2">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="AK2">
         <v>1.22</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="O6">
+        <v>3.51</v>
+      </c>
+      <c r="P6">
         <v>3.3</v>
-      </c>
-      <c r="P6">
-        <v>3.15</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -1302,65 +1302,65 @@
         <v>2.2</v>
       </c>
       <c r="S6">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T6">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="U6">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="V6">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W6">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X6">
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z6">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AA6">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AB6">
         <v>2</v>
       </c>
       <c r="AC6">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AD6">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE6">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF6">
+        <v>1.64</v>
+      </c>
+      <c r="AG6">
+        <v>2.07</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6">
+        <v>1.27</v>
+      </c>
+      <c r="AK6">
         <v>1.7</v>
-      </c>
-      <c r="AG6">
-        <v>2.05</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6">
-        <v>1.29</v>
-      </c>
-      <c r="AK6">
-        <v>1.64</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1797,10 +1797,10 @@
         <v>4</v>
       </c>
       <c r="U9">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="V9">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W9">
         <v>1.2</v>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="O12">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P12">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="Q12">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="R12">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="S12">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="T12">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="U12">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="V12">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W12">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X12">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="Z12">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AA12">
-        <v>2.11</v>
+        <v>1.96</v>
       </c>
       <c r="AB12">
         <v>1.75</v>
       </c>
       <c r="AC12">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="AD12">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE12">
         <v>1.04</v>
       </c>
       <c r="AF12">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AG12">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK12">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.63</v>
+        <v>2.29</v>
       </c>
       <c r="O13">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="P13">
-        <v>2.58</v>
+        <v>3.02</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2467,10 +2467,10 @@
         <v>0</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC13">
         <v>0</v>
@@ -2591,19 +2591,19 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="O14">
         <v>4.6</v>
       </c>
       <c r="P14">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Q14">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="R14">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="S14">
         <v>1.28</v>
@@ -2612,31 +2612,31 @@
         <v>3.22</v>
       </c>
       <c r="U14">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="V14">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="W14">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X14">
         <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z14">
         <v>3.92</v>
       </c>
       <c r="AA14">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AB14">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AC14">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AD14">
         <v>1.38</v>
@@ -2664,7 +2664,7 @@
         <v>1.14</v>
       </c>
       <c r="AK14">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2757,19 +2757,19 @@
         <v>1.8</v>
       </c>
       <c r="O15">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P15">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="Q15">
         <v>2.43</v>
       </c>
       <c r="R15">
-        <v>2.01</v>
+        <v>2.18</v>
       </c>
       <c r="S15">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T15">
         <v>2.69</v>
@@ -2778,34 +2778,34 @@
         <v>2.81</v>
       </c>
       <c r="V15">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W15">
         <v>1.04</v>
       </c>
       <c r="X15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y15">
         <v>1.29</v>
       </c>
       <c r="Z15">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="AA15">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AB15">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AC15">
-        <v>3.58</v>
+        <v>3.63</v>
       </c>
       <c r="AD15">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE15">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF15">
         <v>1.87</v>
@@ -2827,7 +2827,7 @@
         <v>1.23</v>
       </c>
       <c r="AK15">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3080,16 +3080,16 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="O17">
         <v>3.1</v>
       </c>
       <c r="P17">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="Q17">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="R17">
         <v>1.94</v>
@@ -3119,16 +3119,16 @@
         <v>2.62</v>
       </c>
       <c r="AA17">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AB17">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AC17">
-        <v>4.05</v>
+        <v>4.26</v>
       </c>
       <c r="AD17">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE17">
         <v>1.02</v>
@@ -3243,16 +3243,16 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="O18">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P18">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q18">
-        <v>3.54</v>
+        <v>3.57</v>
       </c>
       <c r="R18">
         <v>1.94</v>
@@ -3264,10 +3264,10 @@
         <v>2.5</v>
       </c>
       <c r="U18">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="V18">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W18">
         <v>1.02</v>
@@ -3276,16 +3276,16 @@
         <v>1.03</v>
       </c>
       <c r="Y18">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Z18">
-        <v>2.88</v>
+        <v>3.09</v>
       </c>
       <c r="AA18">
         <v>2.14</v>
       </c>
       <c r="AB18">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AC18">
         <v>3.58</v>
@@ -3316,7 +3316,7 @@
         <v>1.36</v>
       </c>
       <c r="AK18">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3418,13 +3418,13 @@
         <v>1.87</v>
       </c>
       <c r="R19">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="S19">
         <v>1.31</v>
       </c>
       <c r="T19">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="U19">
         <v>2.48</v>
@@ -3448,13 +3448,13 @@
         <v>1.84</v>
       </c>
       <c r="AB19">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AC19">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="AD19">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE19">
         <v>1.09</v>
@@ -3479,7 +3479,7 @@
         <v>1.19</v>
       </c>
       <c r="AK19">
-        <v>2.82</v>
+        <v>2.89</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3904,10 +3904,10 @@
         <v>3.4</v>
       </c>
       <c r="Q22">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="R22">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="S22">
         <v>1.36</v>
@@ -3925,19 +3925,19 @@
         <v>1.05</v>
       </c>
       <c r="X22">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y22">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z22">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="AA22">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AB22">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AC22">
         <v>3.34</v>
@@ -3946,7 +3946,7 @@
         <v>1.24</v>
       </c>
       <c r="AE22">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF22">
         <v>1.78</v>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK22">
         <v>1.61</v>
@@ -4058,52 +4058,52 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="O23">
-        <v>3.2</v>
+        <v>3.31</v>
       </c>
       <c r="P23">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="Q23">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="R23">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="S23">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T23">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="U23">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="V23">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W23">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X23">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z23">
-        <v>2.85</v>
+        <v>2.97</v>
       </c>
       <c r="AA23">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AB23">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC23">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AD23">
         <v>1.22</v>
@@ -4112,10 +4112,10 @@
         <v>1.04</v>
       </c>
       <c r="AF23">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AG23">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK23">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4230,25 +4230,25 @@
         <v>3.4</v>
       </c>
       <c r="Q24">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="R24">
         <v>1.99</v>
       </c>
       <c r="S24">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T24">
         <v>2.69</v>
       </c>
       <c r="U24">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="V24">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W24">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X24">
         <v>1.03</v>
@@ -4260,19 +4260,19 @@
         <v>2.92</v>
       </c>
       <c r="AA24">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AB24">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AC24">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="AD24">
         <v>1.19</v>
       </c>
       <c r="AE24">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF24">
         <v>1.83</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK24">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4550,25 +4550,25 @@
         <v>3.8</v>
       </c>
       <c r="O26">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P26">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q26">
-        <v>4.6</v>
+        <v>5.03</v>
       </c>
       <c r="R26">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="S26">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T26">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="U26">
-        <v>3.11</v>
+        <v>2.92</v>
       </c>
       <c r="V26">
         <v>1.34</v>
@@ -4577,34 +4577,34 @@
         <v>1.03</v>
       </c>
       <c r="X26">
+        <v>1</v>
+      </c>
+      <c r="Y26">
+        <v>1.28</v>
+      </c>
+      <c r="Z26">
+        <v>3.05</v>
+      </c>
+      <c r="AA26">
+        <v>2.04</v>
+      </c>
+      <c r="AB26">
+        <v>1.78</v>
+      </c>
+      <c r="AC26">
+        <v>3.63</v>
+      </c>
+      <c r="AD26">
+        <v>1.22</v>
+      </c>
+      <c r="AE26">
         <v>1.04</v>
       </c>
-      <c r="Y26">
-        <v>1.3</v>
-      </c>
-      <c r="Z26">
-        <v>2.97</v>
-      </c>
-      <c r="AA26">
-        <v>2.1</v>
-      </c>
-      <c r="AB26">
-        <v>1.72</v>
-      </c>
-      <c r="AC26">
-        <v>3.68</v>
-      </c>
-      <c r="AD26">
-        <v>1.2</v>
-      </c>
-      <c r="AE26">
-        <v>1.03</v>
-      </c>
       <c r="AF26">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AG26">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK26">
         <v>1.22</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4749,10 +4749,10 @@
         <v>0</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC27">
         <v>0</v>
@@ -4888,16 +4888,16 @@
         <v>2.07</v>
       </c>
       <c r="S28">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T28">
         <v>2.7</v>
       </c>
       <c r="U28">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="V28">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W28">
         <v>1.03</v>
@@ -4906,22 +4906,22 @@
         <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z28">
         <v>3.08</v>
       </c>
       <c r="AA28">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB28">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC28">
         <v>3.34</v>
       </c>
       <c r="AD28">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AE28">
         <v>1.05</v>
@@ -4930,7 +4930,7 @@
         <v>1.84</v>
       </c>
       <c r="AG28">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>1.26</v>
       </c>
       <c r="AK28">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5045,55 +5045,55 @@
         <v>0</v>
       </c>
       <c r="Q29">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="R29">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="S29">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T29">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="U29">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="V29">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W29">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X29">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y29">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z29">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AA29">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="AB29">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AC29">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD29">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AE29">
         <v>1.06</v>
       </c>
       <c r="AF29">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AG29">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK29">
-        <v>1.88</v>
+        <v>2.04</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.01</v>
+        <v>1.92</v>
       </c>
       <c r="O30">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P30">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="Q30">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="R30">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="S30">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T30">
-        <v>2.62</v>
+        <v>2.51</v>
       </c>
       <c r="U30">
-        <v>3.02</v>
+        <v>2.97</v>
       </c>
       <c r="V30">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W30">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X30">
         <v>1.04</v>
       </c>
       <c r="Y30">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z30">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AA30">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="AB30">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AC30">
-        <v>4.13</v>
+        <v>4.06</v>
       </c>
       <c r="AD30">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE30">
         <v>1.03</v>
       </c>
       <c r="AF30">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AG30">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>1.34</v>
       </c>
       <c r="AK30">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="Q32">
-        <v>2.48</v>
+        <v>2.59</v>
       </c>
       <c r="R32">
         <v>2.2</v>
       </c>
       <c r="S32">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="T32">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="U32">
         <v>2.34</v>
@@ -5558,25 +5558,25 @@
         <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z32">
-        <v>3.76</v>
+        <v>3.98</v>
       </c>
       <c r="AA32">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AB32">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AC32">
         <v>2.74</v>
       </c>
       <c r="AD32">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AE32">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF32">
         <v>1.6</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q33">
         <v>2.4</v>
@@ -5709,10 +5709,10 @@
         <v>3.3</v>
       </c>
       <c r="U33">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="V33">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W33">
         <v>1.11</v>
@@ -5721,28 +5721,28 @@
         <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z33">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="AA33">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AB33">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="AC33">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="AD33">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE33">
         <v>1.12</v>
       </c>
       <c r="AF33">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG33">
         <v>2.25</v>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK33">
         <v>1.83</v>
@@ -6023,25 +6023,25 @@
         <v>2.19</v>
       </c>
       <c r="Q35">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="R35">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="S35">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T35">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="U35">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="V35">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W35">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X35">
         <v>1.01</v>
@@ -6053,25 +6053,25 @@
         <v>3.28</v>
       </c>
       <c r="AA35">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AB35">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AC35">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="AD35">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE35">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF35">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG35">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.23</v>
+        <v>1.54</v>
       </c>
       <c r="AK35">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6186,16 +6186,16 @@
         <v>4.5</v>
       </c>
       <c r="Q36">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R36">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="S36">
         <v>1.28</v>
       </c>
       <c r="T36">
-        <v>3.12</v>
+        <v>3.5</v>
       </c>
       <c r="U36">
         <v>2.34</v>
@@ -6210,32 +6210,32 @@
         <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z36">
-        <v>4.35</v>
+        <v>4.3</v>
       </c>
       <c r="AA36">
+        <v>1.6</v>
+      </c>
+      <c r="AB36">
+        <v>2.15</v>
+      </c>
+      <c r="AC36">
+        <v>2.46</v>
+      </c>
+      <c r="AD36">
+        <v>1.43</v>
+      </c>
+      <c r="AE36">
+        <v>1.13</v>
+      </c>
+      <c r="AF36">
         <v>1.59</v>
       </c>
-      <c r="AB36">
+      <c r="AG36">
         <v>2.17</v>
       </c>
-      <c r="AC36">
-        <v>2.43</v>
-      </c>
-      <c r="AD36">
-        <v>1.44</v>
-      </c>
-      <c r="AE36">
-        <v>1.14</v>
-      </c>
-      <c r="AF36">
-        <v>1.58</v>
-      </c>
-      <c r="AG36">
-        <v>2.19</v>
-      </c>
       <c r="AH36" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK36">
         <v>2</v>
@@ -6349,22 +6349,22 @@
         <v>3.2</v>
       </c>
       <c r="Q37">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="R37">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="S37">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T37">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="U37">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="V37">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="W37">
         <v>1.12</v>
@@ -6376,28 +6376,28 @@
         <v>1.12</v>
       </c>
       <c r="Z37">
-        <v>4.75</v>
+        <v>4.65</v>
       </c>
       <c r="AA37">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AB37">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="AC37">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="AD37">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AE37">
         <v>1.16</v>
       </c>
       <c r="AF37">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AG37">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK37">
         <v>1.61</v>
@@ -6512,52 +6512,52 @@
         <v>7.8</v>
       </c>
       <c r="Q38">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="R38">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
       <c r="S38">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T38">
-        <v>3.72</v>
+        <v>3.58</v>
       </c>
       <c r="U38">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="V38">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W38">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X38">
         <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z38">
-        <v>5.75</v>
+        <v>5.55</v>
       </c>
       <c r="AA38">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AB38">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="AC38">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="AD38">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AE38">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF38">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AG38">
         <v>2.08</v>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AK38">
-        <v>3.06</v>
+        <v>2.94</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,34 +6666,34 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="O39">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P39">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q39">
         <v>2.9</v>
       </c>
       <c r="R39">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="S39">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T39">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="U39">
         <v>2.38</v>
       </c>
       <c r="V39">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W39">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X39">
         <v>1.02</v>
@@ -6708,7 +6708,7 @@
         <v>1.62</v>
       </c>
       <c r="AB39">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AC39">
         <v>2.46</v>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AK39">
         <v>1.5</v>
@@ -6829,10 +6829,10 @@
         </is>
       </c>
       <c r="N40">
+        <v>3.6</v>
+      </c>
+      <c r="O40">
         <v>3.7</v>
-      </c>
-      <c r="O40">
-        <v>3.9</v>
       </c>
       <c r="P40">
         <v>1.81</v>
@@ -6841,52 +6841,52 @@
         <v>4.22</v>
       </c>
       <c r="R40">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="S40">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T40">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U40">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="V40">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W40">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X40">
         <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z40">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="AA40">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AB40">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AC40">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AD40">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AE40">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AF40">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AG40">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.21</v>
+        <v>1.94</v>
       </c>
       <c r="AK40">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7001,34 +7001,34 @@
         <v>0</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA41">
         <v>1.66</v>
@@ -7037,19 +7037,19 @@
         <v>2.15</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7164,22 +7164,22 @@
         <v>2.18</v>
       </c>
       <c r="Q42">
-        <v>2.77</v>
+        <v>3.33</v>
       </c>
       <c r="R42">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="S42">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T42">
-        <v>3.48</v>
+        <v>4</v>
       </c>
       <c r="U42">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V42">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W42">
         <v>1.15</v>
@@ -7188,22 +7188,22 @@
         <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z42">
-        <v>5.2</v>
+        <v>6.13</v>
       </c>
       <c r="AA42">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AB42">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="AC42">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AD42">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AE42">
         <v>1.26</v>
@@ -7228,7 +7228,7 @@
         <v>1.26</v>
       </c>
       <c r="AK42">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,19 +7318,19 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="O43">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="P43">
-        <v>4.4</v>
+        <v>4.65</v>
       </c>
       <c r="Q43">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R43">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="S43">
         <v>1.19</v>
@@ -7339,13 +7339,13 @@
         <v>3.8</v>
       </c>
       <c r="U43">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="V43">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="W43">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X43">
         <v>1.02</v>
@@ -7354,28 +7354,28 @@
         <v>1.1</v>
       </c>
       <c r="Z43">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AA43">
+        <v>1.4</v>
+      </c>
+      <c r="AB43">
+        <v>2.56</v>
+      </c>
+      <c r="AC43">
+        <v>2.08</v>
+      </c>
+      <c r="AD43">
+        <v>1.7</v>
+      </c>
+      <c r="AE43">
+        <v>1.25</v>
+      </c>
+      <c r="AF43">
         <v>1.47</v>
       </c>
-      <c r="AB43">
-        <v>2.6</v>
-      </c>
-      <c r="AC43">
-        <v>2.12</v>
-      </c>
-      <c r="AD43">
-        <v>1.67</v>
-      </c>
-      <c r="AE43">
-        <v>1.24</v>
-      </c>
-      <c r="AF43">
-        <v>1.51</v>
-      </c>
       <c r="AG43">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK43">
-        <v>2.29</v>
+        <v>2.18</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,52 +7481,52 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.41</v>
+        <v>2.37</v>
       </c>
       <c r="O44">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="P44">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="Q44">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="R44">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="S44">
         <v>1.37</v>
       </c>
       <c r="T44">
-        <v>2.79</v>
+        <v>2.56</v>
       </c>
       <c r="U44">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
       <c r="V44">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W44">
         <v>1.05</v>
       </c>
       <c r="X44">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y44">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="Z44">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="AA44">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="AB44">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AC44">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AD44">
         <v>1.22</v>
@@ -7538,7 +7538,7 @@
         <v>1.78</v>
       </c>
       <c r="AG44">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="O46">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P46">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q46">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="R46">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="S46">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T46">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="U46">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V46">
+        <v>1.57</v>
+      </c>
+      <c r="W46">
+        <v>1.1</v>
+      </c>
+      <c r="X46">
+        <v>1.02</v>
+      </c>
+      <c r="Y46">
+        <v>1.12</v>
+      </c>
+      <c r="Z46">
+        <v>4.8</v>
+      </c>
+      <c r="AA46">
+        <v>1.48</v>
+      </c>
+      <c r="AB46">
+        <v>2.44</v>
+      </c>
+      <c r="AC46">
+        <v>2.31</v>
+      </c>
+      <c r="AD46">
         <v>1.58</v>
       </c>
-      <c r="W46">
-        <v>1.12</v>
-      </c>
-      <c r="X46">
-        <v>1.01</v>
-      </c>
-      <c r="Y46">
-        <v>1.11</v>
-      </c>
-      <c r="Z46">
-        <v>4.9</v>
-      </c>
-      <c r="AA46">
-        <v>1.46</v>
-      </c>
-      <c r="AB46">
-        <v>2.38</v>
-      </c>
-      <c r="AC46">
-        <v>2.22</v>
-      </c>
-      <c r="AD46">
-        <v>1.56</v>
-      </c>
       <c r="AE46">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AF46">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AG46">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AK46">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8296,31 +8296,31 @@
         </is>
       </c>
       <c r="N49">
+        <v>2.95</v>
+      </c>
+      <c r="O49">
         <v>3</v>
-      </c>
-      <c r="O49">
-        <v>2.9</v>
       </c>
       <c r="P49">
         <v>2.25</v>
       </c>
       <c r="Q49">
-        <v>4.27</v>
+        <v>3.79</v>
       </c>
       <c r="R49">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="S49">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="T49">
-        <v>2.32</v>
+        <v>2.83</v>
       </c>
       <c r="U49">
-        <v>2.89</v>
+        <v>3.03</v>
       </c>
       <c r="V49">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W49">
         <v>1.03</v>
@@ -8329,31 +8329,31 @@
         <v>1.04</v>
       </c>
       <c r="Y49">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z49">
-        <v>3.29</v>
+        <v>2.97</v>
       </c>
       <c r="AA49">
         <v>2.02</v>
       </c>
       <c r="AB49">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AC49">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="AD49">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE49">
         <v>1.05</v>
       </c>
       <c r="AF49">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AG49">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="AK49">
         <v>1.25</v>
@@ -8462,28 +8462,28 @@
         <v>1.8</v>
       </c>
       <c r="O50">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P50">
         <v>3.5</v>
       </c>
       <c r="Q50">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="R50">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="S50">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="T50">
         <v>3.4</v>
       </c>
       <c r="U50">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="V50">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W50">
         <v>1.13</v>
@@ -8498,10 +8498,10 @@
         <v>4.75</v>
       </c>
       <c r="AA50">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB50">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AC50">
         <v>2.25</v>
@@ -8510,13 +8510,13 @@
         <v>1.6</v>
       </c>
       <c r="AE50">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF50">
         <v>1.47</v>
       </c>
       <c r="AG50">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK50">
         <v>1.84</v>
@@ -8622,49 +8622,49 @@
         </is>
       </c>
       <c r="N51">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O51">
         <v>3.25</v>
       </c>
       <c r="P51">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q51">
         <v>5.19</v>
       </c>
       <c r="R51">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="S51">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="T51">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="U51">
         <v>2.79</v>
       </c>
       <c r="V51">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="W51">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X51">
         <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z51">
-        <v>2.97</v>
+        <v>3.14</v>
       </c>
       <c r="AA51">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AB51">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AC51">
         <v>3.5</v>
@@ -8679,7 +8679,7 @@
         <v>1.89</v>
       </c>
       <c r="AG51">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK51">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -9283,19 +9283,19 @@
         <v>0</v>
       </c>
       <c r="Q55">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="R55">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="S55">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T55">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="U55">
-        <v>2.27</v>
+        <v>2.48</v>
       </c>
       <c r="V55">
         <v>1.51</v>
@@ -9304,34 +9304,34 @@
         <v>1.11</v>
       </c>
       <c r="X55">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y55">
+        <v>1.19</v>
+      </c>
+      <c r="Z55">
+        <v>4.41</v>
+      </c>
+      <c r="AA55">
+        <v>1.67</v>
+      </c>
+      <c r="AB55">
+        <v>2.08</v>
+      </c>
+      <c r="AC55">
+        <v>2.52</v>
+      </c>
+      <c r="AD55">
+        <v>1.41</v>
+      </c>
+      <c r="AE55">
         <v>1.17</v>
       </c>
-      <c r="Z55">
-        <v>4</v>
-      </c>
-      <c r="AA55">
-        <v>1.63</v>
-      </c>
-      <c r="AB55">
-        <v>2.1</v>
-      </c>
-      <c r="AC55">
-        <v>2.49</v>
-      </c>
-      <c r="AD55">
-        <v>1.42</v>
-      </c>
-      <c r="AE55">
-        <v>1.14</v>
-      </c>
       <c r="AF55">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AG55">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>1.22</v>
       </c>
       <c r="AK55">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>5.44</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T56">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U56">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V56">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z56">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF56">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG56">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK56">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9600,7 +9600,7 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="O57">
         <v>5.05</v>
@@ -9609,10 +9609,10 @@
         <v>7.08</v>
       </c>
       <c r="Q57">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="R57">
-        <v>2.66</v>
+        <v>2.51</v>
       </c>
       <c r="S57">
         <v>1.16</v>
@@ -9621,37 +9621,37 @@
         <v>4.2</v>
       </c>
       <c r="U57">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V57">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W57">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X57">
         <v>1.01</v>
       </c>
       <c r="Y57">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z57">
-        <v>5.55</v>
+        <v>6.07</v>
       </c>
       <c r="AA57">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB57">
-        <v>2.7</v>
+        <v>2.89</v>
       </c>
       <c r="AC57">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AD57">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AE57">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AF57">
         <v>1.61</v>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AK57">
         <v>2.95</v>
@@ -10089,25 +10089,25 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="O60">
         <v>4</v>
       </c>
       <c r="P60">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q60">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R60">
         <v>2.42</v>
       </c>
       <c r="S60">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T60">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="U60">
         <v>1.99</v>
@@ -10128,13 +10128,13 @@
         <v>6.15</v>
       </c>
       <c r="AA60">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="AB60">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="AC60">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AD60">
         <v>1.75</v>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK60">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,19 +10252,19 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="O61">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="P61">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="Q61">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="R61">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="S61">
         <v>1.15</v>
@@ -10288,13 +10288,13 @@
         <v>1.07</v>
       </c>
       <c r="Z61">
-        <v>5.8</v>
+        <v>5.85</v>
       </c>
       <c r="AA61">
         <v>1.35</v>
       </c>
       <c r="AB61">
-        <v>2.86</v>
+        <v>2.74</v>
       </c>
       <c r="AC61">
         <v>1.95</v>
@@ -10306,10 +10306,10 @@
         <v>1.28</v>
       </c>
       <c r="AF61">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AG61">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>1.18</v>
       </c>
       <c r="AK61">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,31 +10415,31 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="O62">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P62">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="Q62">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="R62">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="S62">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T62">
-        <v>3.24</v>
+        <v>3.6</v>
       </c>
       <c r="U62">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="V62">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="W62">
         <v>1.11</v>
@@ -10448,10 +10448,10 @@
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z62">
-        <v>4.35</v>
+        <v>4.61</v>
       </c>
       <c r="AA62">
         <v>1.55</v>
@@ -10460,7 +10460,7 @@
         <v>2.24</v>
       </c>
       <c r="AC62">
-        <v>2.33</v>
+        <v>2.44</v>
       </c>
       <c r="AD62">
         <v>1.48</v>
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="O63">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="P63">
-        <v>3.74</v>
+        <v>3.61</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10925,7 +10925,7 @@
         <v>2.92</v>
       </c>
       <c r="U65">
-        <v>2.67</v>
+        <v>2.86</v>
       </c>
       <c r="V65">
         <v>1.4</v>
@@ -10937,16 +10937,16 @@
         <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z65">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="AA65">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AB65">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC65">
         <v>2.97</v>
@@ -10955,7 +10955,7 @@
         <v>1.3</v>
       </c>
       <c r="AE65">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF65">
         <v>1.75</v>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK65">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11073,13 +11073,13 @@
         <v>3.35</v>
       </c>
       <c r="P66">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="Q66">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="R66">
-        <v>2.21</v>
+        <v>2.33</v>
       </c>
       <c r="S66">
         <v>1.31</v>
@@ -11088,10 +11088,10 @@
         <v>3.08</v>
       </c>
       <c r="U66">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="V66">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W66">
         <v>1.06</v>
@@ -11100,13 +11100,13 @@
         <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z66">
         <v>3.82</v>
       </c>
       <c r="AA66">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB66">
         <v>2</v>
@@ -11124,7 +11124,7 @@
         <v>1.64</v>
       </c>
       <c r="AG66">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>1.25</v>
       </c>
       <c r="AK66">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="O67">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="P67">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q67">
         <v>2.92</v>
@@ -11245,19 +11245,19 @@
         <v>2</v>
       </c>
       <c r="S67">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T67">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="U67">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="V67">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W67">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X67">
         <v>1.02</v>
@@ -11269,10 +11269,10 @@
         <v>3.04</v>
       </c>
       <c r="AA67">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AB67">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AC67">
         <v>3.42</v>
@@ -11393,19 +11393,19 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="O68">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P68">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
       </c>
       <c r="R68">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="S68">
         <v>1.3</v>
@@ -11417,7 +11417,7 @@
         <v>2.4</v>
       </c>
       <c r="V68">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="W68">
         <v>1.09</v>
@@ -11426,7 +11426,7 @@
         <v>1.02</v>
       </c>
       <c r="Y68">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="Z68">
         <v>3.91</v>
@@ -11438,13 +11438,13 @@
         <v>2.02</v>
       </c>
       <c r="AC68">
-        <v>2.66</v>
+        <v>2.93</v>
       </c>
       <c r="AD68">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AE68">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF68">
         <v>1.58</v>
@@ -11556,7 +11556,7 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="O69">
         <v>3.34</v>
@@ -11565,7 +11565,7 @@
         <v>2.52</v>
       </c>
       <c r="Q69">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="R69">
         <v>2.08</v>
@@ -11574,19 +11574,19 @@
         <v>1.33</v>
       </c>
       <c r="T69">
-        <v>2.97</v>
+        <v>3.15</v>
       </c>
       <c r="U69">
         <v>2.5</v>
       </c>
       <c r="V69">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W69">
         <v>1.1</v>
       </c>
       <c r="X69">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y69">
         <v>1.25</v>
@@ -11601,16 +11601,16 @@
         <v>1.95</v>
       </c>
       <c r="AC69">
-        <v>3.02</v>
+        <v>2.7</v>
       </c>
       <c r="AD69">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE69">
         <v>1.14</v>
       </c>
       <c r="AF69">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AG69">
         <v>2.21</v>
@@ -11719,16 +11719,16 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O70">
-        <v>3.15</v>
+        <v>3.03</v>
       </c>
       <c r="P70">
-        <v>3.15</v>
+        <v>2.65</v>
       </c>
       <c r="Q70">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="R70">
         <v>2.03</v>
@@ -11737,13 +11737,13 @@
         <v>1.42</v>
       </c>
       <c r="T70">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="U70">
-        <v>2.96</v>
+        <v>2.89</v>
       </c>
       <c r="V70">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W70">
         <v>1.03</v>
@@ -11755,7 +11755,7 @@
         <v>1.31</v>
       </c>
       <c r="Z70">
-        <v>2.92</v>
+        <v>3.04</v>
       </c>
       <c r="AA70">
         <v>2.06</v>
@@ -11770,7 +11770,7 @@
         <v>1.22</v>
       </c>
       <c r="AE70">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF70">
         <v>1.85</v>
@@ -11882,55 +11882,55 @@
         </is>
       </c>
       <c r="N71">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="O71">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P71">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="Q71">
-        <v>4.11</v>
+        <v>3.75</v>
       </c>
       <c r="R71">
-        <v>2.23</v>
+        <v>2.08</v>
       </c>
       <c r="S71">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T71">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="U71">
-        <v>2.42</v>
+        <v>2.63</v>
       </c>
       <c r="V71">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W71">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X71">
         <v>1</v>
       </c>
       <c r="Y71">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z71">
-        <v>3.84</v>
+        <v>3.9</v>
       </c>
       <c r="AA71">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AB71">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="AC71">
         <v>2.59</v>
       </c>
       <c r="AD71">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AE71">
         <v>1.12</v>
@@ -11939,7 +11939,7 @@
         <v>1.6</v>
       </c>
       <c r="AG71">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
+        <v>1.78</v>
+      </c>
+      <c r="AK71">
         <v>1.25</v>
-      </c>
-      <c r="AK71">
-        <v>1.26</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12380,22 +12380,22 @@
         <v>0</v>
       </c>
       <c r="Q74">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="R74">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="S74">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T74">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="U74">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="V74">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="W74">
         <v>1.09</v>
@@ -12407,22 +12407,22 @@
         <v>1.16</v>
       </c>
       <c r="Z74">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="AA74">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AB74">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
       <c r="AC74">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="AD74">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AE74">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AF74">
         <v>1.53</v>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK74">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12543,55 +12543,55 @@
         <v>0</v>
       </c>
       <c r="Q75">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R75">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S75">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T75">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U75">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V75">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W75">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X75">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y75">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z75">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA75">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC75">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD75">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE75">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF75">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG75">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK75">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12697,10 +12697,10 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="O76">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P76">
         <v>3.71</v>
@@ -12709,49 +12709,49 @@
         <v>2.3</v>
       </c>
       <c r="R76">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="S76">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="T76">
-        <v>2.41</v>
+        <v>2.47</v>
       </c>
       <c r="U76">
-        <v>3.22</v>
+        <v>2.93</v>
       </c>
       <c r="V76">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W76">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X76">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y76">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="Z76">
-        <v>2.7</v>
+        <v>2.89</v>
       </c>
       <c r="AA76">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AB76">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC76">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AD76">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE76">
         <v>1.02</v>
       </c>
       <c r="AF76">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AG76">
         <v>1.67</v>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AK76">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="O77">
-        <v>4.4</v>
+        <v>4.08</v>
       </c>
       <c r="P77">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="Q77">
         <v>2.11</v>
@@ -12875,13 +12875,13 @@
         <v>2.38</v>
       </c>
       <c r="S77">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="T77">
         <v>4</v>
       </c>
       <c r="U77">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="V77">
         <v>1.73</v>
@@ -12905,10 +12905,10 @@
         <v>2.7</v>
       </c>
       <c r="AC77">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AD77">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AE77">
         <v>1.25</v>
@@ -12930,7 +12930,7 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AK77">
         <v>2.22</v>
@@ -13029,13 +13029,13 @@
         <v>3.9</v>
       </c>
       <c r="P78">
-        <v>3.8</v>
+        <v>3.92</v>
       </c>
       <c r="Q78">
-        <v>2.19</v>
+        <v>2.01</v>
       </c>
       <c r="R78">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="S78">
         <v>1.22</v>
@@ -13044,7 +13044,7 @@
         <v>3.55</v>
       </c>
       <c r="U78">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="V78">
         <v>1.7</v>
@@ -13065,7 +13065,7 @@
         <v>1.4</v>
       </c>
       <c r="AB78">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AC78">
         <v>2.12</v>
@@ -13093,7 +13093,7 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK78">
         <v>2.04</v>
@@ -13195,52 +13195,52 @@
         <v>1.95</v>
       </c>
       <c r="Q79">
-        <v>3.62</v>
+        <v>3.56</v>
       </c>
       <c r="R79">
         <v>2.45</v>
       </c>
       <c r="S79">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T79">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="U79">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="V79">
         <v>1.88</v>
       </c>
       <c r="W79">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="X79">
         <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z79">
-        <v>6.45</v>
+        <v>7.5</v>
       </c>
       <c r="AA79">
         <v>1.33</v>
       </c>
       <c r="AB79">
-        <v>2.97</v>
+        <v>3.4</v>
       </c>
       <c r="AC79">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AD79">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AE79">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AF79">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AG79">
         <v>3.1</v>
@@ -13259,7 +13259,7 @@
         <v>1.22</v>
       </c>
       <c r="AK79">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13349,31 +13349,31 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.6</v>
+        <v>2.21</v>
       </c>
       <c r="O80">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P80">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="Q80">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="R80">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="S80">
         <v>1.22</v>
       </c>
       <c r="T80">
-        <v>3.55</v>
+        <v>3.48</v>
       </c>
       <c r="U80">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V80">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W80">
         <v>1.12</v>
@@ -13385,19 +13385,19 @@
         <v>1.09</v>
       </c>
       <c r="Z80">
-        <v>5.35</v>
+        <v>5.3</v>
       </c>
       <c r="AA80">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB80">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AC80">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AD80">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AE80">
         <v>1.22</v>
@@ -13422,7 +13422,7 @@
         <v>1.25</v>
       </c>
       <c r="AK80">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13512,19 +13512,19 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="O81">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P81">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="Q81">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R81">
-        <v>2.54</v>
+        <v>2.35</v>
       </c>
       <c r="S81">
         <v>1.2</v>
@@ -13536,10 +13536,10 @@
         <v>2.1</v>
       </c>
       <c r="V81">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="W81">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X81">
         <v>1.02</v>
@@ -13551,10 +13551,10 @@
         <v>5.25</v>
       </c>
       <c r="AA81">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AB81">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="AC81">
         <v>2.11</v>
@@ -13563,13 +13563,13 @@
         <v>1.67</v>
       </c>
       <c r="AE81">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AF81">
         <v>1.4</v>
       </c>
       <c r="AG81">
-        <v>2.73</v>
+        <v>2.68</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.24</v>
+        <v>1.64</v>
       </c>
       <c r="AK81">
         <v>1.33</v>
@@ -13675,16 +13675,16 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O82">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P82">
         <v>2.2</v>
       </c>
       <c r="Q82">
-        <v>3.02</v>
+        <v>2.7</v>
       </c>
       <c r="R82">
         <v>2.43</v>
@@ -13693,13 +13693,13 @@
         <v>1.18</v>
       </c>
       <c r="T82">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="U82">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="V82">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="W82">
         <v>1.22</v>
@@ -13847,16 +13847,16 @@
         <v>4.33</v>
       </c>
       <c r="Q83">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R83">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S83">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T83">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="U83">
         <v>2.17</v>
@@ -13865,28 +13865,28 @@
         <v>1.62</v>
       </c>
       <c r="W83">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X83">
         <v>1.02</v>
       </c>
       <c r="Y83">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Z83">
         <v>5.3</v>
       </c>
       <c r="AA83">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AB83">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="AC83">
         <v>2.17</v>
       </c>
       <c r="AD83">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AE83">
         <v>1.22</v>
@@ -13911,7 +13911,7 @@
         <v>1.2</v>
       </c>
       <c r="AK83">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="O84">
         <v>3.72</v>
       </c>
       <c r="P84">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="Q84">
         <v>2.98</v>
@@ -14025,7 +14025,7 @@
         <v>2.3</v>
       </c>
       <c r="V84">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W84">
         <v>1.1</v>
@@ -14037,10 +14037,10 @@
         <v>1.14</v>
       </c>
       <c r="Z84">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA84">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB84">
         <v>2.27</v>
@@ -14049,7 +14049,7 @@
         <v>2.35</v>
       </c>
       <c r="AD84">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="AE84">
         <v>1.16</v>
@@ -14173,19 +14173,19 @@
         <v>2.1</v>
       </c>
       <c r="Q85">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="R85">
-        <v>2.34</v>
+        <v>2.53</v>
       </c>
       <c r="S85">
         <v>1.23</v>
       </c>
       <c r="T85">
-        <v>3.48</v>
+        <v>3.8</v>
       </c>
       <c r="U85">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="V85">
         <v>1.65</v>
@@ -14206,7 +14206,7 @@
         <v>1.43</v>
       </c>
       <c r="AB85">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="AC85">
         <v>2.16</v>
@@ -14215,7 +14215,7 @@
         <v>1.64</v>
       </c>
       <c r="AE85">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AF85">
         <v>1.44</v>
@@ -14330,7 +14330,7 @@
         <v>2.24</v>
       </c>
       <c r="O86">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P86">
         <v>2.75</v>
@@ -14348,7 +14348,7 @@
         <v>3.74</v>
       </c>
       <c r="U86">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="V86">
         <v>1.64</v>
@@ -14372,19 +14372,19 @@
         <v>2.43</v>
       </c>
       <c r="AC86">
-        <v>2.17</v>
+        <v>2.24</v>
       </c>
       <c r="AD86">
         <v>1.59</v>
       </c>
       <c r="AE86">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AF86">
         <v>1.4</v>
       </c>
       <c r="AG86">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="AK86">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="O87">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P87">
+        <v>3</v>
+      </c>
+      <c r="Q87">
+        <v>2.88</v>
+      </c>
+      <c r="R87">
+        <v>2.1</v>
+      </c>
+      <c r="S87">
+        <v>1.37</v>
+      </c>
+      <c r="T87">
+        <v>2.79</v>
+      </c>
+      <c r="U87">
         <v>2.9</v>
-      </c>
-      <c r="Q87">
-        <v>2.93</v>
-      </c>
-      <c r="R87">
-        <v>2.04</v>
-      </c>
-      <c r="S87">
-        <v>1.38</v>
-      </c>
-      <c r="T87">
-        <v>2.75</v>
-      </c>
-      <c r="U87">
-        <v>2.64</v>
       </c>
       <c r="V87">
         <v>1.41</v>
       </c>
       <c r="W87">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X87">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y87">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="Z87">
         <v>3.2</v>
       </c>
       <c r="AA87">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AB87">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AC87">
-        <v>3.05</v>
+        <v>3.51</v>
       </c>
       <c r="AD87">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE87">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF87">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AG87">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,7 +14560,7 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AK87">
         <v>1.53</v>
@@ -14674,7 +14674,7 @@
         <v>2.61</v>
       </c>
       <c r="U88">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="V88">
         <v>1.32</v>
@@ -14683,10 +14683,10 @@
         <v>1.02</v>
       </c>
       <c r="X88">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z88">
         <v>3.08</v>
@@ -14701,7 +14701,7 @@
         <v>3.5</v>
       </c>
       <c r="AD88">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE88">
         <v>1.04</v>
@@ -14723,7 +14723,7 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AK88">
         <v>1.25</v>
@@ -14825,22 +14825,22 @@
         <v>0</v>
       </c>
       <c r="Q89">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="R89">
-        <v>2.32</v>
+        <v>2.63</v>
       </c>
       <c r="S89">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T89">
-        <v>3.48</v>
+        <v>3.56</v>
       </c>
       <c r="U89">
         <v>2.14</v>
       </c>
       <c r="V89">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="W89">
         <v>1.14</v>
@@ -14858,7 +14858,7 @@
         <v>1.46</v>
       </c>
       <c r="AB89">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="AC89">
         <v>2.23</v>
@@ -14886,7 +14886,7 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK89">
         <v>2.3</v>
@@ -14982,10 +14982,10 @@
         <v>2.25</v>
       </c>
       <c r="O90">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P90">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="Q90">
         <v>2.88</v>
@@ -14994,10 +14994,10 @@
         <v>2.22</v>
       </c>
       <c r="S90">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="T90">
-        <v>3.08</v>
+        <v>2.85</v>
       </c>
       <c r="U90">
         <v>2.47</v>
@@ -15006,7 +15006,7 @@
         <v>1.46</v>
       </c>
       <c r="W90">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X90">
         <v>1.02</v>
@@ -15015,16 +15015,16 @@
         <v>1.22</v>
       </c>
       <c r="Z90">
-        <v>3.93</v>
+        <v>3.8</v>
       </c>
       <c r="AA90">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AB90">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AC90">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="AD90">
         <v>1.37</v>
@@ -15036,7 +15036,7 @@
         <v>1.58</v>
       </c>
       <c r="AG90">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK90">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15148,19 +15148,19 @@
         <v>3.8</v>
       </c>
       <c r="P91">
-        <v>4</v>
+        <v>4.53</v>
       </c>
       <c r="Q91">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="R91">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="S91">
         <v>1.23</v>
       </c>
       <c r="T91">
-        <v>3.48</v>
+        <v>3.7</v>
       </c>
       <c r="U91">
         <v>2.19</v>
@@ -15169,7 +15169,7 @@
         <v>1.61</v>
       </c>
       <c r="W91">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X91">
         <v>1.02</v>
@@ -15178,13 +15178,13 @@
         <v>1.14</v>
       </c>
       <c r="Z91">
-        <v>4.45</v>
+        <v>4.94</v>
       </c>
       <c r="AA91">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AB91">
-        <v>2.35</v>
+        <v>2.26</v>
       </c>
       <c r="AC91">
         <v>2.36</v>
@@ -15193,7 +15193,7 @@
         <v>1.54</v>
       </c>
       <c r="AE91">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AF91">
         <v>1.57</v>
@@ -15215,7 +15215,7 @@
         <v>1.19</v>
       </c>
       <c r="AK91">
-        <v>2.14</v>
+        <v>2.03</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15305,34 +15305,34 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="O92">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="P92">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="Q92">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="R92">
-        <v>4.7</v>
+        <v>3.87</v>
       </c>
       <c r="S92">
         <v>1.09</v>
       </c>
       <c r="T92">
-        <v>7.08</v>
+        <v>6.7</v>
       </c>
       <c r="U92">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="V92">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="W92">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X92">
         <v>1</v>
@@ -15347,19 +15347,19 @@
         <v>1.14</v>
       </c>
       <c r="AB92">
-        <v>5.5</v>
+        <v>5.65</v>
       </c>
       <c r="AC92">
         <v>1.33</v>
       </c>
       <c r="AD92">
-        <v>2.93</v>
+        <v>2.82</v>
       </c>
       <c r="AE92">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="AF92">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AG92">
         <v>1.9</v>
@@ -15378,7 +15378,7 @@
         <v>1.02</v>
       </c>
       <c r="AK92">
-        <v>11.5</v>
+        <v>10.75</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15468,22 +15468,22 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="O93">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="P93">
         <v>2.34</v>
       </c>
       <c r="Q93">
-        <v>3.36</v>
+        <v>2.96</v>
       </c>
       <c r="R93">
         <v>2.18</v>
       </c>
       <c r="S93">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T93">
         <v>3.18</v>
@@ -15507,19 +15507,19 @@
         <v>3.98</v>
       </c>
       <c r="AA93">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AB93">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC93">
-        <v>2.49</v>
+        <v>2.69</v>
       </c>
       <c r="AD93">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE93">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AF93">
         <v>1.53</v>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK93">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="O94">
-        <v>3.78</v>
+        <v>3.65</v>
       </c>
       <c r="P94">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="Q94">
         <v>2.55</v>
@@ -15646,10 +15646,10 @@
         <v>2.3</v>
       </c>
       <c r="S94">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T94">
-        <v>3.38</v>
+        <v>3.9</v>
       </c>
       <c r="U94">
         <v>2.3</v>
@@ -15661,7 +15661,7 @@
         <v>1.14</v>
       </c>
       <c r="X94">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y94">
         <v>1.13</v>
@@ -15670,16 +15670,16 @@
         <v>4.6</v>
       </c>
       <c r="AA94">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AB94">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="AC94">
         <v>2.42</v>
       </c>
       <c r="AD94">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AE94">
         <v>1.22</v>
@@ -15704,7 +15704,7 @@
         <v>1.34</v>
       </c>
       <c r="AK94">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -16120,10 +16120,10 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="O97">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P97">
         <v>3.1</v>
@@ -16141,7 +16141,7 @@
         <v>2.84</v>
       </c>
       <c r="U97">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="V97">
         <v>1.4</v>
@@ -16159,10 +16159,10 @@
         <v>3.34</v>
       </c>
       <c r="AA97">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AB97">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC97">
         <v>3.05</v>
@@ -16171,13 +16171,13 @@
         <v>1.28</v>
       </c>
       <c r="AE97">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF97">
         <v>1.67</v>
       </c>
       <c r="AG97">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK97">
         <v>1.62</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,19 +16283,19 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="O98">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="P98">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="Q98">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="R98">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="S98">
         <v>1.22</v>
@@ -16304,59 +16304,59 @@
         <v>3.75</v>
       </c>
       <c r="U98">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="V98">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W98">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X98">
         <v>1.02</v>
       </c>
       <c r="Y98">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z98">
-        <v>4.64</v>
+        <v>4.75</v>
       </c>
       <c r="AA98">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AB98">
+        <v>2.55</v>
+      </c>
+      <c r="AC98">
+        <v>2.17</v>
+      </c>
+      <c r="AD98">
+        <v>1.59</v>
+      </c>
+      <c r="AE98">
+        <v>1.22</v>
+      </c>
+      <c r="AF98">
+        <v>1.58</v>
+      </c>
+      <c r="AG98">
+        <v>2.17</v>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ98">
+        <v>1.07</v>
+      </c>
+      <c r="AK98">
         <v>2.4</v>
-      </c>
-      <c r="AC98">
-        <v>2.33</v>
-      </c>
-      <c r="AD98">
-        <v>1.51</v>
-      </c>
-      <c r="AE98">
-        <v>1.16</v>
-      </c>
-      <c r="AF98">
-        <v>1.67</v>
-      </c>
-      <c r="AG98">
-        <v>2.06</v>
-      </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI98" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ98">
-        <v>1.1</v>
-      </c>
-      <c r="AK98">
-        <v>2.61</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="O99">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="P99">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="Q99">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="R99">
         <v>2.5</v>
       </c>
       <c r="S99">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T99">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="U99">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="V99">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="W99">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X99">
         <v>1.02</v>
       </c>
       <c r="Y99">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z99">
-        <v>4.75</v>
+        <v>4.64</v>
       </c>
       <c r="AA99">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AB99">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AC99">
-        <v>2.17</v>
+        <v>2.33</v>
       </c>
       <c r="AD99">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="AE99">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AF99">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="AG99">
-        <v>2.19</v>
+        <v>2.04</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AK99">
-        <v>2.34</v>
+        <v>2.58</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16618,19 +16618,19 @@
         <v>1.78</v>
       </c>
       <c r="Q100">
-        <v>4.57</v>
+        <v>4.54</v>
       </c>
       <c r="R100">
-        <v>2.17</v>
+        <v>2.33</v>
       </c>
       <c r="S100">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T100">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="U100">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="V100">
         <v>1.44</v>
@@ -16642,16 +16642,16 @@
         <v>1.03</v>
       </c>
       <c r="Y100">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z100">
-        <v>3.76</v>
+        <v>3.77</v>
       </c>
       <c r="AA100">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB100">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC100">
         <v>2.83</v>
@@ -16666,7 +16666,7 @@
         <v>1.67</v>
       </c>
       <c r="AG100">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="O101">
         <v>3.3</v>
       </c>
       <c r="P101">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="Q101">
         <v>2.8</v>
@@ -16787,13 +16787,13 @@
         <v>2.05</v>
       </c>
       <c r="S101">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T101">
-        <v>2.83</v>
+        <v>3.2</v>
       </c>
       <c r="U101">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="V101">
         <v>1.4</v>
@@ -16811,10 +16811,10 @@
         <v>3.72</v>
       </c>
       <c r="AA101">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB101">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC101">
         <v>2.81</v>
@@ -16829,7 +16829,7 @@
         <v>1.6</v>
       </c>
       <c r="AG101">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>1.25</v>
       </c>
       <c r="AK101">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16938,10 +16938,10 @@
         <v>2.9</v>
       </c>
       <c r="O102">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="P102">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="Q102">
         <v>3.4</v>
@@ -16953,28 +16953,28 @@
         <v>1.36</v>
       </c>
       <c r="T102">
-        <v>2.99</v>
+        <v>3.17</v>
       </c>
       <c r="U102">
         <v>2.66</v>
       </c>
       <c r="V102">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W102">
         <v>1.06</v>
       </c>
       <c r="X102">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y102">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z102">
         <v>3.7</v>
       </c>
       <c r="AA102">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AB102">
         <v>2.07</v>
@@ -16986,7 +16986,7 @@
         <v>1.34</v>
       </c>
       <c r="AE102">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF102">
         <v>1.62</v>
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="O103">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P103">
-        <v>3.63</v>
+        <v>4</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.55</v>
+        <v>2.71</v>
       </c>
       <c r="O104">
-        <v>3.83</v>
+        <v>3.84</v>
       </c>
       <c r="P104">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="Q104">
         <v>3.07</v>
@@ -17279,37 +17279,37 @@
         <v>1.22</v>
       </c>
       <c r="T104">
-        <v>3.94</v>
+        <v>4.1</v>
       </c>
       <c r="U104">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="V104">
         <v>1.69</v>
       </c>
       <c r="W104">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X104">
         <v>1.01</v>
       </c>
       <c r="Y104">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z104">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AA104">
         <v>1.42</v>
       </c>
       <c r="AB104">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="AC104">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AD104">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="AE104">
         <v>1.25</v>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AK104">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17433,22 +17433,22 @@
         <v>3.9</v>
       </c>
       <c r="Q105">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="R105">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="S105">
         <v>1.45</v>
       </c>
       <c r="T105">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="U105">
-        <v>3.06</v>
+        <v>3.12</v>
       </c>
       <c r="V105">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W105">
         <v>1.04</v>
@@ -17463,10 +17463,10 @@
         <v>2.52</v>
       </c>
       <c r="AA105">
-        <v>2.37</v>
+        <v>2.31</v>
       </c>
       <c r="AB105">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AC105">
         <v>4.25</v>
@@ -17475,13 +17475,13 @@
         <v>1.15</v>
       </c>
       <c r="AE105">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF105">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AG105">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK105">
         <v>1.67</v>
@@ -17913,7 +17913,7 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="O108">
         <v>3.5</v>
@@ -17928,10 +17928,10 @@
         <v>2.07</v>
       </c>
       <c r="S108">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T108">
-        <v>2.79</v>
+        <v>2.89</v>
       </c>
       <c r="U108">
         <v>2.88</v>
@@ -17940,34 +17940,34 @@
         <v>1.4</v>
       </c>
       <c r="W108">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X108">
         <v>1</v>
       </c>
       <c r="Y108">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z108">
-        <v>3.4</v>
+        <v>3.68</v>
       </c>
       <c r="AA108">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AB108">
         <v>1.9</v>
       </c>
       <c r="AC108">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AD108">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE108">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF108">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG108">
         <v>1.95</v>
@@ -18085,19 +18085,19 @@
         <v>3.8</v>
       </c>
       <c r="Q109">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="R109">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S109">
         <v>1.3</v>
       </c>
       <c r="T109">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="U109">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="V109">
         <v>1.44</v>
@@ -18106,34 +18106,34 @@
         <v>1.1</v>
       </c>
       <c r="X109">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y109">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z109">
-        <v>3.42</v>
+        <v>3.8</v>
       </c>
       <c r="AA109">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AB109">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AC109">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="AD109">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AE109">
         <v>1.08</v>
       </c>
       <c r="AF109">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG109">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AK109">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18574,16 +18574,16 @@
         <v>5.75</v>
       </c>
       <c r="Q112">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="R112">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S112">
         <v>1.33</v>
       </c>
       <c r="T112">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="U112">
         <v>2.75</v>
@@ -18595,34 +18595,34 @@
         <v>1.07</v>
       </c>
       <c r="X112">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y112">
         <v>1.27</v>
       </c>
       <c r="Z112">
-        <v>3.64</v>
+        <v>3.69</v>
       </c>
       <c r="AA112">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AB112">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AC112">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AD112">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE112">
         <v>1.08</v>
       </c>
       <c r="AF112">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AG112">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>1.08</v>
       </c>
       <c r="AK112">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18752,7 +18752,7 @@
         <v>2.02</v>
       </c>
       <c r="V113">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="W113">
         <v>1.18</v>
@@ -18767,10 +18767,10 @@
         <v>5.35</v>
       </c>
       <c r="AA113">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB113">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="AC113">
         <v>2.05</v>
@@ -18785,7 +18785,7 @@
         <v>1.45</v>
       </c>
       <c r="AG113">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>1.2</v>
       </c>
       <c r="AK113">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -19054,25 +19054,25 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="O115">
         <v>3.1</v>
       </c>
       <c r="P115">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="Q115">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="R115">
         <v>2</v>
       </c>
       <c r="S115">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T115">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="U115">
         <v>2.9</v>
@@ -19084,25 +19084,25 @@
         <v>1.07</v>
       </c>
       <c r="X115">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y115">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z115">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AA115">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="AB115">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AC115">
-        <v>3.68</v>
+        <v>3.79</v>
       </c>
       <c r="AD115">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE115">
         <v>1.03</v>
@@ -19238,13 +19238,13 @@
         <v>2.53</v>
       </c>
       <c r="U116">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="V116">
         <v>1.33</v>
       </c>
       <c r="W116">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X116">
         <v>1.02</v>
@@ -19253,22 +19253,22 @@
         <v>1.31</v>
       </c>
       <c r="Z116">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AA116">
         <v>2.08</v>
       </c>
       <c r="AB116">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AC116">
-        <v>3.5</v>
+        <v>3.83</v>
       </c>
       <c r="AD116">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE116">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF116">
         <v>1.81</v>

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G75">
@@ -12543,25 +12543,25 @@
         <v>0</v>
       </c>
       <c r="Q75">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="R75">
-        <v>2.22</v>
+        <v>2.42</v>
       </c>
       <c r="S75">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T75">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="U75">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="V75">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W75">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X75">
         <v>1.02</v>
@@ -12570,28 +12570,28 @@
         <v>1.16</v>
       </c>
       <c r="Z75">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="AA75">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AB75">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AC75">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="AD75">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AE75">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AF75">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AG75">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK75">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G76">
@@ -12706,25 +12706,25 @@
         <v>0</v>
       </c>
       <c r="Q76">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="R76">
-        <v>2.42</v>
+        <v>2.22</v>
       </c>
       <c r="S76">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T76">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="U76">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="V76">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W76">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X76">
         <v>1.02</v>
@@ -12733,28 +12733,28 @@
         <v>1.16</v>
       </c>
       <c r="Z76">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="AA76">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AB76">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AC76">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="AD76">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AE76">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AF76">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AG76">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK76">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,80 +16283,80 @@
         </is>
       </c>
       <c r="N98">
+        <v>1.47</v>
+      </c>
+      <c r="O98">
+        <v>4.1</v>
+      </c>
+      <c r="P98">
+        <v>5.4</v>
+      </c>
+      <c r="Q98">
+        <v>1.99</v>
+      </c>
+      <c r="R98">
+        <v>2.35</v>
+      </c>
+      <c r="S98">
+        <v>1.22</v>
+      </c>
+      <c r="T98">
+        <v>3.75</v>
+      </c>
+      <c r="U98">
         <v>2.1</v>
       </c>
-      <c r="O98">
-        <v>3.2</v>
-      </c>
-      <c r="P98">
-        <v>3.1</v>
-      </c>
-      <c r="Q98">
-        <v>2.78</v>
-      </c>
-      <c r="R98">
-        <v>2.05</v>
-      </c>
-      <c r="S98">
-        <v>1.33</v>
-      </c>
-      <c r="T98">
-        <v>2.84</v>
-      </c>
-      <c r="U98">
-        <v>2.58</v>
-      </c>
       <c r="V98">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="W98">
+        <v>1.17</v>
+      </c>
+      <c r="X98">
+        <v>1.02</v>
+      </c>
+      <c r="Y98">
+        <v>1.15</v>
+      </c>
+      <c r="Z98">
+        <v>4.75</v>
+      </c>
+      <c r="AA98">
+        <v>1.46</v>
+      </c>
+      <c r="AB98">
+        <v>2.55</v>
+      </c>
+      <c r="AC98">
+        <v>2.17</v>
+      </c>
+      <c r="AD98">
+        <v>1.59</v>
+      </c>
+      <c r="AE98">
+        <v>1.22</v>
+      </c>
+      <c r="AF98">
+        <v>1.58</v>
+      </c>
+      <c r="AG98">
+        <v>2.17</v>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ98">
         <v>1.07</v>
       </c>
-      <c r="X98">
-        <v>1</v>
-      </c>
-      <c r="Y98">
-        <v>1.24</v>
-      </c>
-      <c r="Z98">
-        <v>3.34</v>
-      </c>
-      <c r="AA98">
-        <v>1.87</v>
-      </c>
-      <c r="AB98">
-        <v>1.9</v>
-      </c>
-      <c r="AC98">
-        <v>3.05</v>
-      </c>
-      <c r="AD98">
-        <v>1.28</v>
-      </c>
-      <c r="AE98">
-        <v>1.11</v>
-      </c>
-      <c r="AF98">
-        <v>1.67</v>
-      </c>
-      <c r="AG98">
-        <v>2.02</v>
-      </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI98" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ98">
-        <v>1.28</v>
-      </c>
       <c r="AK98">
-        <v>1.62</v>
+        <v>2.4</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,80 +16609,80 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.47</v>
+        <v>2.1</v>
       </c>
       <c r="O100">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="P100">
-        <v>5.4</v>
+        <v>3.1</v>
       </c>
       <c r="Q100">
-        <v>1.99</v>
+        <v>2.78</v>
       </c>
       <c r="R100">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="S100">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="T100">
-        <v>3.75</v>
+        <v>2.84</v>
       </c>
       <c r="U100">
-        <v>2.1</v>
+        <v>2.58</v>
       </c>
       <c r="V100">
+        <v>1.4</v>
+      </c>
+      <c r="W100">
+        <v>1.07</v>
+      </c>
+      <c r="X100">
+        <v>1</v>
+      </c>
+      <c r="Y100">
+        <v>1.24</v>
+      </c>
+      <c r="Z100">
+        <v>3.34</v>
+      </c>
+      <c r="AA100">
+        <v>1.87</v>
+      </c>
+      <c r="AB100">
+        <v>1.9</v>
+      </c>
+      <c r="AC100">
+        <v>3.05</v>
+      </c>
+      <c r="AD100">
+        <v>1.28</v>
+      </c>
+      <c r="AE100">
+        <v>1.11</v>
+      </c>
+      <c r="AF100">
+        <v>1.67</v>
+      </c>
+      <c r="AG100">
+        <v>2.02</v>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ100">
+        <v>1.28</v>
+      </c>
+      <c r="AK100">
         <v>1.62</v>
-      </c>
-      <c r="W100">
-        <v>1.17</v>
-      </c>
-      <c r="X100">
-        <v>1.02</v>
-      </c>
-      <c r="Y100">
-        <v>1.15</v>
-      </c>
-      <c r="Z100">
-        <v>4.75</v>
-      </c>
-      <c r="AA100">
-        <v>1.46</v>
-      </c>
-      <c r="AB100">
-        <v>2.55</v>
-      </c>
-      <c r="AC100">
-        <v>2.17</v>
-      </c>
-      <c r="AD100">
-        <v>1.59</v>
-      </c>
-      <c r="AE100">
-        <v>1.22</v>
-      </c>
-      <c r="AF100">
-        <v>1.58</v>
-      </c>
-      <c r="AG100">
-        <v>2.17</v>
-      </c>
-      <c r="AH100" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI100" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ100">
-        <v>1.07</v>
-      </c>
-      <c r="AK100">
-        <v>2.4</v>
       </c>
       <c r="AL100">
         <v>0</v>

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -804,28 +804,28 @@
         <v>3.8</v>
       </c>
       <c r="P3">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q3">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="R3">
         <v>2.21</v>
       </c>
       <c r="S3">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T3">
         <v>3.25</v>
       </c>
       <c r="U3">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="V3">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W3">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X3">
         <v>1.01</v>
@@ -846,13 +846,13 @@
         <v>2.69</v>
       </c>
       <c r="AD3">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE3">
         <v>1.11</v>
       </c>
       <c r="AF3">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG3">
         <v>2.02</v>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="O11">
         <v>3.2</v>
@@ -2111,13 +2111,13 @@
         <v>3.05</v>
       </c>
       <c r="Q11">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="R11">
         <v>1.98</v>
       </c>
       <c r="S11">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T11">
         <v>2.93</v>
@@ -2126,10 +2126,10 @@
         <v>2.88</v>
       </c>
       <c r="V11">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W11">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X11">
         <v>1</v>
@@ -2141,10 +2141,10 @@
         <v>3.2</v>
       </c>
       <c r="AA11">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB11">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC11">
         <v>3.33</v>
@@ -2175,7 +2175,7 @@
         <v>1.26</v>
       </c>
       <c r="AK11">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -3080,19 +3080,19 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.45</v>
+        <v>2.21</v>
       </c>
       <c r="O17">
         <v>3.1</v>
       </c>
       <c r="P17">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="Q17">
         <v>2.99</v>
       </c>
       <c r="R17">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="S17">
         <v>1.45</v>
@@ -3119,10 +3119,10 @@
         <v>2.62</v>
       </c>
       <c r="AA17">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="AB17">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AC17">
         <v>4.26</v>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AK17">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3249,10 +3249,10 @@
         <v>3.05</v>
       </c>
       <c r="P18">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="Q18">
-        <v>3.57</v>
+        <v>3.75</v>
       </c>
       <c r="R18">
         <v>1.94</v>
@@ -3279,7 +3279,7 @@
         <v>1.34</v>
       </c>
       <c r="Z18">
-        <v>3.09</v>
+        <v>2.88</v>
       </c>
       <c r="AA18">
         <v>2.14</v>
@@ -3415,22 +3415,22 @@
         <v>0</v>
       </c>
       <c r="Q19">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="R19">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="S19">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T19">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="U19">
-        <v>2.48</v>
+        <v>2.68</v>
       </c>
       <c r="V19">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W19">
         <v>1.08</v>
@@ -3439,31 +3439,31 @@
         <v>1</v>
       </c>
       <c r="Y19">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z19">
-        <v>3.58</v>
+        <v>3.78</v>
       </c>
       <c r="AA19">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AB19">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AC19">
-        <v>2.99</v>
+        <v>2.83</v>
       </c>
       <c r="AD19">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE19">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF19">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AG19">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK19">
-        <v>2.89</v>
+        <v>2.97</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="O27">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P27">
         <v>1.74</v>
       </c>
       <c r="Q27">
-        <v>5.03</v>
+        <v>5.14</v>
       </c>
       <c r="R27">
-        <v>2.21</v>
+        <v>2.26</v>
       </c>
       <c r="S27">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T27">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="U27">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="V27">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W27">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X27">
         <v>1</v>
       </c>
       <c r="Y27">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z27">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AA27">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AB27">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AC27">
-        <v>3.63</v>
+        <v>3.52</v>
       </c>
       <c r="AD27">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE27">
         <v>1.04</v>
       </c>
       <c r="AF27">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AG27">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK27">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="O28">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P28">
         <v>2.5</v>
@@ -5362,28 +5362,28 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="O31">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P31">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="Q31">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="R31">
         <v>2.1</v>
       </c>
       <c r="S31">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T31">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="U31">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="V31">
         <v>1.33</v>
@@ -5401,7 +5401,7 @@
         <v>2.7</v>
       </c>
       <c r="AA31">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
       <c r="AB31">
         <v>1.62</v>
@@ -5419,7 +5419,7 @@
         <v>1.97</v>
       </c>
       <c r="AG31">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AK31">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -9111,25 +9111,25 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="O54">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="P54">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q54">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="R54">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="S54">
         <v>1.29</v>
       </c>
       <c r="T54">
-        <v>3.02</v>
+        <v>2.95</v>
       </c>
       <c r="U54">
         <v>2.5</v>
@@ -9147,28 +9147,28 @@
         <v>1.18</v>
       </c>
       <c r="Z54">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="AA54">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AB54">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AC54">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="AD54">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE54">
         <v>1.11</v>
       </c>
       <c r="AF54">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AG54">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AK54">
-        <v>3.24</v>
+        <v>3.12</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9295,7 +9295,7 @@
         <v>2.92</v>
       </c>
       <c r="U55">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="V55">
         <v>1.4</v>
@@ -9328,10 +9328,10 @@
         <v>1.07</v>
       </c>
       <c r="AF55">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AG55">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="O57">
-        <v>3.48</v>
+        <v>3.55</v>
       </c>
       <c r="P57">
-        <v>5.44</v>
+        <v>5.2</v>
       </c>
       <c r="Q57">
         <v>2.16</v>
@@ -9618,16 +9618,16 @@
         <v>1.36</v>
       </c>
       <c r="T57">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="U57">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="V57">
         <v>1.36</v>
       </c>
       <c r="W57">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X57">
         <v>1.02</v>
@@ -9657,7 +9657,7 @@
         <v>1.96</v>
       </c>
       <c r="AG57">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK57">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -10252,7 +10252,7 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="O61">
         <v>4</v>
@@ -10261,10 +10261,10 @@
         <v>3.35</v>
       </c>
       <c r="Q61">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="R61">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="S61">
         <v>1.17</v>
@@ -10273,10 +10273,10 @@
         <v>3.94</v>
       </c>
       <c r="U61">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="V61">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="W61">
         <v>1.15</v>
@@ -10288,19 +10288,19 @@
         <v>1.06</v>
       </c>
       <c r="Z61">
-        <v>6.15</v>
+        <v>6.06</v>
       </c>
       <c r="AA61">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AB61">
-        <v>2.86</v>
+        <v>2.81</v>
       </c>
       <c r="AC61">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AD61">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AE61">
         <v>1.28</v>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK61">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10454,13 +10454,13 @@
         <v>5.85</v>
       </c>
       <c r="AA62">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AB62">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="AC62">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AD62">
         <v>1.73</v>
@@ -10469,10 +10469,10 @@
         <v>1.28</v>
       </c>
       <c r="AF62">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AG62">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK62">
         <v>1.45</v>
@@ -10590,19 +10590,19 @@
         <v>2.16</v>
       </c>
       <c r="R63">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="S63">
         <v>1.25</v>
       </c>
       <c r="T63">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U63">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="V63">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="W63">
         <v>1.11</v>
@@ -10611,10 +10611,10 @@
         <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z63">
-        <v>4.61</v>
+        <v>4.4</v>
       </c>
       <c r="AA63">
         <v>1.55</v>
@@ -10651,7 +10651,7 @@
         <v>1.17</v>
       </c>
       <c r="AK63">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -12217,55 +12217,55 @@
         <v>0</v>
       </c>
       <c r="Q73">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R73">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S73">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T73">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U73">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="V73">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W73">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X73">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y73">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z73">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA73">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB73">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC73">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AD73">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE73">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF73">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG73">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK73">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -14499,19 +14499,19 @@
         <v>2.75</v>
       </c>
       <c r="Q87">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="R87">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="S87">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T87">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="U87">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="V87">
         <v>1.64</v>
@@ -14535,7 +14535,7 @@
         <v>2.43</v>
       </c>
       <c r="AC87">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="AD87">
         <v>1.59</v>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="AK87">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="O98">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="P98">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="Q98">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="R98">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="S98">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T98">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="U98">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="V98">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W98">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X98">
         <v>1.02</v>
       </c>
       <c r="Y98">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z98">
-        <v>4.75</v>
+        <v>4.64</v>
       </c>
       <c r="AA98">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AB98">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AC98">
-        <v>2.17</v>
+        <v>2.33</v>
       </c>
       <c r="AD98">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="AE98">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AF98">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AG98">
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AK98">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.37</v>
+        <v>2.1</v>
       </c>
       <c r="O99">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="P99">
-        <v>5.8</v>
+        <v>3.1</v>
       </c>
       <c r="Q99">
-        <v>1.86</v>
+        <v>2.78</v>
       </c>
       <c r="R99">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="S99">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="T99">
-        <v>3.72</v>
+        <v>2.84</v>
       </c>
       <c r="U99">
-        <v>2.22</v>
+        <v>2.58</v>
       </c>
       <c r="V99">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="W99">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X99">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y99">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="Z99">
-        <v>4.64</v>
+        <v>3.34</v>
       </c>
       <c r="AA99">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="AB99">
-        <v>2.45</v>
+        <v>1.9</v>
       </c>
       <c r="AC99">
-        <v>2.33</v>
+        <v>3.05</v>
       </c>
       <c r="AD99">
-        <v>1.51</v>
+        <v>1.28</v>
       </c>
       <c r="AE99">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AF99">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG99">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.06</v>
+        <v>1.28</v>
       </c>
       <c r="AK99">
-        <v>2.58</v>
+        <v>1.62</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,80 +16609,80 @@
         </is>
       </c>
       <c r="N100">
+        <v>1.47</v>
+      </c>
+      <c r="O100">
+        <v>4.1</v>
+      </c>
+      <c r="P100">
+        <v>5.4</v>
+      </c>
+      <c r="Q100">
+        <v>1.99</v>
+      </c>
+      <c r="R100">
+        <v>2.35</v>
+      </c>
+      <c r="S100">
+        <v>1.22</v>
+      </c>
+      <c r="T100">
+        <v>3.75</v>
+      </c>
+      <c r="U100">
         <v>2.1</v>
       </c>
-      <c r="O100">
-        <v>3.2</v>
-      </c>
-      <c r="P100">
-        <v>3.1</v>
-      </c>
-      <c r="Q100">
-        <v>2.78</v>
-      </c>
-      <c r="R100">
-        <v>2.05</v>
-      </c>
-      <c r="S100">
-        <v>1.33</v>
-      </c>
-      <c r="T100">
-        <v>2.84</v>
-      </c>
-      <c r="U100">
-        <v>2.58</v>
-      </c>
       <c r="V100">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="W100">
+        <v>1.17</v>
+      </c>
+      <c r="X100">
+        <v>1.02</v>
+      </c>
+      <c r="Y100">
+        <v>1.15</v>
+      </c>
+      <c r="Z100">
+        <v>4.75</v>
+      </c>
+      <c r="AA100">
+        <v>1.46</v>
+      </c>
+      <c r="AB100">
+        <v>2.55</v>
+      </c>
+      <c r="AC100">
+        <v>2.17</v>
+      </c>
+      <c r="AD100">
+        <v>1.59</v>
+      </c>
+      <c r="AE100">
+        <v>1.22</v>
+      </c>
+      <c r="AF100">
+        <v>1.58</v>
+      </c>
+      <c r="AG100">
+        <v>2.17</v>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ100">
         <v>1.07</v>
       </c>
-      <c r="X100">
-        <v>1</v>
-      </c>
-      <c r="Y100">
-        <v>1.24</v>
-      </c>
-      <c r="Z100">
-        <v>3.34</v>
-      </c>
-      <c r="AA100">
-        <v>1.87</v>
-      </c>
-      <c r="AB100">
-        <v>1.9</v>
-      </c>
-      <c r="AC100">
-        <v>3.05</v>
-      </c>
-      <c r="AD100">
-        <v>1.28</v>
-      </c>
-      <c r="AE100">
-        <v>1.11</v>
-      </c>
-      <c r="AF100">
-        <v>1.67</v>
-      </c>
-      <c r="AG100">
-        <v>2.02</v>
-      </c>
-      <c r="AH100" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI100" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ100">
-        <v>1.28</v>
-      </c>
       <c r="AK100">
-        <v>1.62</v>
+        <v>2.4</v>
       </c>
       <c r="AL100">
         <v>0</v>

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -653,10 +653,10 @@
         <v>1.4</v>
       </c>
       <c r="T2">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U2">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="V2">
         <v>1.3</v>
@@ -665,10 +665,10 @@
         <v>1.06</v>
       </c>
       <c r="X2">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y2">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="Z2">
         <v>2.89</v>
@@ -680,10 +680,10 @@
         <v>1.65</v>
       </c>
       <c r="AC2">
-        <v>4.33</v>
+        <v>4.05</v>
       </c>
       <c r="AD2">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AE2">
         <v>1.01</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="AK2">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="O6">
         <v>3.51</v>
       </c>
       <c r="P6">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -1326,16 +1326,16 @@
         <v>3.58</v>
       </c>
       <c r="AA6">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AB6">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC6">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AD6">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AE6">
         <v>1.08</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK6">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1776,19 +1776,19 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="O9">
         <v>4.2</v>
       </c>
       <c r="P9">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="Q9">
         <v>2.3</v>
       </c>
       <c r="R9">
-        <v>2.65</v>
+        <v>2.51</v>
       </c>
       <c r="S9">
         <v>1.2</v>
@@ -1824,7 +1824,7 @@
         <v>1.96</v>
       </c>
       <c r="AD9">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AE9">
         <v>1.33</v>
@@ -1948,55 +1948,55 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="O12">
         <v>3.2</v>
@@ -2280,49 +2280,49 @@
         <v>2.04</v>
       </c>
       <c r="S12">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T12">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="U12">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V12">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W12">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Z12">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="AA12">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="AB12">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AC12">
-        <v>3.34</v>
+        <v>3.14</v>
       </c>
       <c r="AD12">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AE12">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF12">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG12">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK12">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="O13">
         <v>3.36</v>
       </c>
       <c r="P13">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2597,7 +2597,7 @@
         <v>4.6</v>
       </c>
       <c r="P14">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="Q14">
         <v>1.8</v>
@@ -2606,16 +2606,16 @@
         <v>2.5</v>
       </c>
       <c r="S14">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T14">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="U14">
         <v>2.53</v>
       </c>
       <c r="V14">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="W14">
         <v>1.12</v>
@@ -2624,16 +2624,16 @@
         <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z14">
-        <v>3.92</v>
+        <v>4.1</v>
       </c>
       <c r="AA14">
         <v>1.67</v>
       </c>
       <c r="AB14">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="AC14">
         <v>2.62</v>
@@ -2642,13 +2642,13 @@
         <v>1.38</v>
       </c>
       <c r="AE14">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF14">
         <v>1.95</v>
       </c>
       <c r="AG14">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AK14">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2763,10 +2763,10 @@
         <v>4.15</v>
       </c>
       <c r="Q15">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="R15">
-        <v>2.18</v>
+        <v>2.01</v>
       </c>
       <c r="S15">
         <v>1.4</v>
@@ -2778,10 +2778,10 @@
         <v>2.81</v>
       </c>
       <c r="V15">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W15">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X15">
         <v>1.04</v>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK15">
         <v>1.85</v>
@@ -3080,19 +3080,19 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.21</v>
+        <v>2.06</v>
       </c>
       <c r="O17">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P17">
-        <v>2.87</v>
+        <v>3.15</v>
       </c>
       <c r="Q17">
-        <v>2.99</v>
+        <v>2.78</v>
       </c>
       <c r="R17">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="S17">
         <v>1.45</v>
@@ -3101,10 +3101,10 @@
         <v>2.51</v>
       </c>
       <c r="U17">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="V17">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W17">
         <v>1.04</v>
@@ -3119,13 +3119,13 @@
         <v>2.62</v>
       </c>
       <c r="AA17">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AB17">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AC17">
-        <v>4.26</v>
+        <v>4.22</v>
       </c>
       <c r="AD17">
         <v>1.2</v>
@@ -3134,10 +3134,10 @@
         <v>1.02</v>
       </c>
       <c r="AF17">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AG17">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AK17">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3249,7 +3249,7 @@
         <v>3.05</v>
       </c>
       <c r="P18">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="Q18">
         <v>3.75</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q19">
         <v>1.85</v>
@@ -3457,7 +3457,7 @@
         <v>1.33</v>
       </c>
       <c r="AE19">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF19">
         <v>2.03</v>
@@ -3895,16 +3895,16 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="O22">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P22">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="Q22">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="R22">
         <v>2.1</v>
@@ -3925,7 +3925,7 @@
         <v>1.05</v>
       </c>
       <c r="X22">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
         <v>1.29</v>
@@ -3934,7 +3934,7 @@
         <v>3.04</v>
       </c>
       <c r="AA22">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AB22">
         <v>1.72</v>
@@ -3946,7 +3946,7 @@
         <v>1.24</v>
       </c>
       <c r="AE22">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF22">
         <v>1.78</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK22">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4076,13 +4076,13 @@
         <v>1.4</v>
       </c>
       <c r="T23">
-        <v>2.75</v>
+        <v>2.57</v>
       </c>
       <c r="U23">
         <v>2.89</v>
       </c>
       <c r="V23">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W23">
         <v>1.03</v>
@@ -4097,10 +4097,10 @@
         <v>2.97</v>
       </c>
       <c r="AA23">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB23">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AC23">
         <v>3.5</v>
@@ -4115,7 +4115,7 @@
         <v>1.8</v>
       </c>
       <c r="AG23">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK23">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="O24">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P24">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="Q24">
         <v>2.69</v>
@@ -4236,7 +4236,7 @@
         <v>1.99</v>
       </c>
       <c r="S24">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T24">
         <v>2.69</v>
@@ -4248,16 +4248,16 @@
         <v>1.3</v>
       </c>
       <c r="W24">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X24">
         <v>1.03</v>
       </c>
       <c r="Y24">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z24">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AA24">
         <v>2.15</v>
@@ -4272,7 +4272,7 @@
         <v>1.19</v>
       </c>
       <c r="AE24">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF24">
         <v>1.83</v>
@@ -5039,7 +5039,7 @@
         <v>1.85</v>
       </c>
       <c r="O29">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P29">
         <v>3.7</v>
@@ -5057,10 +5057,10 @@
         <v>2.7</v>
       </c>
       <c r="U29">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="V29">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W29">
         <v>1.03</v>
@@ -5069,22 +5069,22 @@
         <v>1.03</v>
       </c>
       <c r="Y29">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z29">
         <v>3.08</v>
       </c>
       <c r="AA29">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB29">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AC29">
         <v>3.34</v>
       </c>
       <c r="AD29">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AE29">
         <v>1.05</v>
@@ -5093,7 +5093,7 @@
         <v>1.84</v>
       </c>
       <c r="AG29">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK29">
         <v>1.87</v>
@@ -5208,10 +5208,10 @@
         <v>0</v>
       </c>
       <c r="Q30">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="R30">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="S30">
         <v>1.36</v>
@@ -5253,10 +5253,10 @@
         <v>1.06</v>
       </c>
       <c r="AF30">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG30">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK30">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5700,22 +5700,22 @@
         <v>2.59</v>
       </c>
       <c r="R33">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="S33">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="T33">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="U33">
-        <v>2.34</v>
+        <v>2.45</v>
       </c>
       <c r="V33">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W33">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X33">
         <v>1.03</v>
@@ -5745,7 +5745,7 @@
         <v>1.6</v>
       </c>
       <c r="AG33">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK33">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,16 +5851,16 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="O34">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P34">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="Q34">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R34">
         <v>2.3</v>
@@ -5872,10 +5872,10 @@
         <v>3.3</v>
       </c>
       <c r="U34">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="V34">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W34">
         <v>1.11</v>
@@ -5887,13 +5887,13 @@
         <v>1.18</v>
       </c>
       <c r="Z34">
-        <v>4.25</v>
+        <v>4.38</v>
       </c>
       <c r="AA34">
         <v>1.64</v>
       </c>
       <c r="AB34">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AC34">
         <v>2.56</v>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK34">
         <v>1.83</v>
@@ -6023,13 +6023,13 @@
         <v>3.1</v>
       </c>
       <c r="Q35">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="R35">
         <v>2.4</v>
       </c>
       <c r="S35">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="T35">
         <v>3.75</v>
@@ -6047,10 +6047,10 @@
         <v>1</v>
       </c>
       <c r="Y35">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z35">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="AA35">
         <v>1.52</v>
@@ -6059,19 +6059,19 @@
         <v>2.45</v>
       </c>
       <c r="AC35">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AD35">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AE35">
         <v>1.17</v>
       </c>
       <c r="AF35">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AG35">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AK35">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6198,7 +6198,7 @@
         <v>2.76</v>
       </c>
       <c r="U36">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="V36">
         <v>1.4</v>
@@ -6216,7 +6216,7 @@
         <v>3.28</v>
       </c>
       <c r="AA36">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AB36">
         <v>1.9</v>
@@ -6234,7 +6234,7 @@
         <v>1.67</v>
       </c>
       <c r="AG36">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>4.5</v>
       </c>
       <c r="Q37">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="R37">
         <v>2.4</v>
@@ -6361,10 +6361,10 @@
         <v>3.5</v>
       </c>
       <c r="U37">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="V37">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="W37">
         <v>1.08</v>
@@ -6397,7 +6397,7 @@
         <v>1.59</v>
       </c>
       <c r="AG37">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK37">
         <v>2</v>
@@ -6512,10 +6512,10 @@
         <v>3.2</v>
       </c>
       <c r="Q38">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="R38">
-        <v>2.38</v>
+        <v>2.21</v>
       </c>
       <c r="S38">
         <v>1.25</v>
@@ -6527,7 +6527,7 @@
         <v>2.17</v>
       </c>
       <c r="V38">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W38">
         <v>1.12</v>
@@ -6542,10 +6542,10 @@
         <v>4.65</v>
       </c>
       <c r="AA38">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AB38">
-        <v>2.45</v>
+        <v>2.27</v>
       </c>
       <c r="AC38">
         <v>2.33</v>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK38">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6675,7 +6675,7 @@
         <v>7.8</v>
       </c>
       <c r="Q39">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="R39">
         <v>2.49</v>
@@ -6684,16 +6684,16 @@
         <v>1.21</v>
       </c>
       <c r="T39">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="U39">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="V39">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="W39">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X39">
         <v>1.02</v>
@@ -6720,10 +6720,10 @@
         <v>1.25</v>
       </c>
       <c r="AF39">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AG39">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AK39">
         <v>2.94</v>
@@ -6838,7 +6838,7 @@
         <v>2.5</v>
       </c>
       <c r="Q40">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="R40">
         <v>2.39</v>
@@ -6847,46 +6847,46 @@
         <v>1.25</v>
       </c>
       <c r="T40">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U40">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="V40">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="W40">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X40">
         <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z40">
-        <v>4.25</v>
+        <v>4.53</v>
       </c>
       <c r="AA40">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AB40">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="AC40">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="AD40">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AE40">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF40">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AG40">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="AK40">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6998,7 +6998,7 @@
         <v>3.7</v>
       </c>
       <c r="P41">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="Q41">
         <v>4.22</v>
@@ -7007,19 +7007,19 @@
         <v>2.47</v>
       </c>
       <c r="S41">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T41">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="U41">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="V41">
         <v>1.57</v>
       </c>
       <c r="W41">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X41">
         <v>1.01</v>
@@ -7028,7 +7028,7 @@
         <v>1.13</v>
       </c>
       <c r="Z41">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="AA41">
         <v>1.56</v>
@@ -7040,7 +7040,7 @@
         <v>2.33</v>
       </c>
       <c r="AD41">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AE41">
         <v>1.2</v>
@@ -7164,31 +7164,31 @@
         <v>0</v>
       </c>
       <c r="Q42">
-        <v>4.11</v>
+        <v>3.75</v>
       </c>
       <c r="R42">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S42">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T42">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="U42">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="V42">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W42">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X42">
         <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z42">
         <v>4.2</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK42">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,16 +7318,16 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="O43">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="P43">
         <v>2.18</v>
       </c>
       <c r="Q43">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="R43">
         <v>2.33</v>
@@ -7339,13 +7339,13 @@
         <v>4</v>
       </c>
       <c r="U43">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="V43">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W43">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X43">
         <v>1.02</v>
@@ -7354,28 +7354,28 @@
         <v>1.09</v>
       </c>
       <c r="Z43">
-        <v>6.13</v>
+        <v>5.25</v>
       </c>
       <c r="AA43">
         <v>1.45</v>
       </c>
       <c r="AB43">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="AC43">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AD43">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AE43">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AF43">
         <v>1.38</v>
       </c>
       <c r="AG43">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.26</v>
+        <v>1.58</v>
       </c>
       <c r="AK43">
         <v>1.4</v>
@@ -7487,25 +7487,25 @@
         <v>4</v>
       </c>
       <c r="P44">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="Q44">
         <v>2.04</v>
       </c>
       <c r="R44">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="S44">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T44">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U44">
         <v>2.02</v>
       </c>
       <c r="V44">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="W44">
         <v>1.18</v>
@@ -7523,7 +7523,7 @@
         <v>1.4</v>
       </c>
       <c r="AB44">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="AC44">
         <v>2.08</v>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK44">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7647,7 +7647,7 @@
         <v>2.37</v>
       </c>
       <c r="O45">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P45">
         <v>2.95</v>
@@ -7665,22 +7665,22 @@
         <v>2.56</v>
       </c>
       <c r="U45">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="V45">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W45">
         <v>1.05</v>
       </c>
       <c r="X45">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
         <v>1.33</v>
       </c>
       <c r="Z45">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="AA45">
         <v>1.98</v>
@@ -7689,16 +7689,16 @@
         <v>1.71</v>
       </c>
       <c r="AC45">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AD45">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE45">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF45">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG45">
         <v>1.95</v>
@@ -7807,19 +7807,19 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="O46">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P46">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="Q46">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="R46">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S46">
         <v>1.38</v>
@@ -7831,19 +7831,19 @@
         <v>2.62</v>
       </c>
       <c r="V46">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W46">
         <v>1.04</v>
       </c>
       <c r="X46">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y46">
         <v>1.22</v>
       </c>
       <c r="Z46">
-        <v>3.48</v>
+        <v>3.67</v>
       </c>
       <c r="AA46">
         <v>1.9</v>
@@ -7982,7 +7982,7 @@
         <v>2.5</v>
       </c>
       <c r="R47">
-        <v>2.26</v>
+        <v>2.49</v>
       </c>
       <c r="S47">
         <v>1.24</v>
@@ -7994,10 +7994,10 @@
         <v>2.2</v>
       </c>
       <c r="V47">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W47">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X47">
         <v>1.02</v>
@@ -8006,28 +8006,28 @@
         <v>1.12</v>
       </c>
       <c r="Z47">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AA47">
         <v>1.48</v>
       </c>
       <c r="AB47">
-        <v>2.44</v>
+        <v>2.02</v>
       </c>
       <c r="AC47">
-        <v>2.31</v>
+        <v>1.96</v>
       </c>
       <c r="AD47">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AE47">
         <v>1.23</v>
       </c>
       <c r="AF47">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG47">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AK47">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="O48">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="P48">
-        <v>4.5</v>
+        <v>5.05</v>
       </c>
       <c r="Q48">
         <v>2</v>
@@ -8154,7 +8154,7 @@
         <v>3.32</v>
       </c>
       <c r="U48">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="V48">
         <v>1.6</v>
@@ -8169,7 +8169,7 @@
         <v>1.12</v>
       </c>
       <c r="Z48">
-        <v>4.7</v>
+        <v>5.26</v>
       </c>
       <c r="AA48">
         <v>1.51</v>
@@ -8184,13 +8184,13 @@
         <v>1.57</v>
       </c>
       <c r="AE48">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AF48">
         <v>1.55</v>
       </c>
       <c r="AG48">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8299,55 +8299,55 @@
         <v>1.43</v>
       </c>
       <c r="O49">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="P49">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X49">
         <v>0</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF49">
         <v>0</v>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="O50">
         <v>3</v>
@@ -8468,19 +8468,19 @@
         <v>2.25</v>
       </c>
       <c r="Q50">
-        <v>3.79</v>
+        <v>3.81</v>
       </c>
       <c r="R50">
         <v>1.83</v>
       </c>
       <c r="S50">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="T50">
-        <v>2.83</v>
+        <v>2.34</v>
       </c>
       <c r="U50">
-        <v>3.03</v>
+        <v>2.8</v>
       </c>
       <c r="V50">
         <v>1.36</v>
@@ -8498,25 +8498,25 @@
         <v>2.97</v>
       </c>
       <c r="AA50">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="AB50">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AC50">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AD50">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE50">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF50">
         <v>1.8</v>
       </c>
       <c r="AG50">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AK50">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8649,7 +8649,7 @@
         <v>1.6</v>
       </c>
       <c r="W51">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="X51">
         <v>1.02</v>
@@ -8809,7 +8809,7 @@
         <v>2.79</v>
       </c>
       <c r="V52">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W52">
         <v>1.06</v>
@@ -8818,10 +8818,10 @@
         <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z52">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="AA52">
         <v>2.05</v>
@@ -8839,7 +8839,7 @@
         <v>1.04</v>
       </c>
       <c r="AF52">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AG52">
         <v>1.83</v>
@@ -9437,16 +9437,16 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q56">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="R56">
         <v>2.36</v>
@@ -9455,10 +9455,10 @@
         <v>1.28</v>
       </c>
       <c r="T56">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="U56">
-        <v>2.48</v>
+        <v>2.27</v>
       </c>
       <c r="V56">
         <v>1.51</v>
@@ -9470,10 +9470,10 @@
         <v>1</v>
       </c>
       <c r="Y56">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z56">
-        <v>4.41</v>
+        <v>3.94</v>
       </c>
       <c r="AA56">
         <v>1.67</v>
@@ -9488,7 +9488,7 @@
         <v>1.41</v>
       </c>
       <c r="AE56">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF56">
         <v>1.55</v>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK56">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9775,7 +9775,7 @@
         <v>1.84</v>
       </c>
       <c r="R58">
-        <v>2.88</v>
+        <v>2.51</v>
       </c>
       <c r="S58">
         <v>1.16</v>
@@ -9796,10 +9796,10 @@
         <v>1.01</v>
       </c>
       <c r="Y58">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z58">
-        <v>6.07</v>
+        <v>5.55</v>
       </c>
       <c r="AA58">
         <v>1.41</v>
@@ -9817,10 +9817,10 @@
         <v>1.26</v>
       </c>
       <c r="AF58">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AG58">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="O59">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="P59">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10098,55 +10098,55 @@
         <v>1.96</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X60">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE60">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF60">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AK60">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="O61">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="P61">
-        <v>3.35</v>
+        <v>2.4</v>
       </c>
       <c r="Q61">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="R61">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="S61">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T61">
-        <v>3.94</v>
+        <v>4.25</v>
       </c>
       <c r="U61">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V61">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="W61">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X61">
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z61">
-        <v>6.06</v>
+        <v>5.85</v>
       </c>
       <c r="AA61">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB61">
-        <v>2.81</v>
+        <v>2.86</v>
       </c>
       <c r="AC61">
         <v>2</v>
       </c>
       <c r="AD61">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AE61">
         <v>1.28</v>
       </c>
       <c r="AF61">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AG61">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK61">
-        <v>1.8</v>
+        <v>1.45</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="O62">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="P62">
-        <v>2.4</v>
+        <v>3.35</v>
       </c>
       <c r="Q62">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="R62">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="S62">
+        <v>1.17</v>
+      </c>
+      <c r="T62">
+        <v>3.94</v>
+      </c>
+      <c r="U62">
+        <v>1.95</v>
+      </c>
+      <c r="V62">
+        <v>1.71</v>
+      </c>
+      <c r="W62">
         <v>1.15</v>
-      </c>
-      <c r="T62">
-        <v>4.25</v>
-      </c>
-      <c r="U62">
-        <v>1.94</v>
-      </c>
-      <c r="V62">
-        <v>1.74</v>
-      </c>
-      <c r="W62">
-        <v>1.18</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z62">
-        <v>5.85</v>
+        <v>6.06</v>
       </c>
       <c r="AA62">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB62">
-        <v>2.86</v>
+        <v>2.81</v>
       </c>
       <c r="AC62">
         <v>2</v>
       </c>
       <c r="AD62">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AE62">
         <v>1.28</v>
       </c>
       <c r="AF62">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AG62">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK62">
-        <v>1.45</v>
+        <v>1.8</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10741,43 +10741,43 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="O64">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="P64">
-        <v>3.61</v>
+        <v>3.65</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T64">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U64">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V64">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W64">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA64">
         <v>2.05</v>
@@ -10786,19 +10786,19 @@
         <v>1.75</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE64">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF64">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK64">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -11070,10 +11070,10 @@
         <v>1.96</v>
       </c>
       <c r="O66">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P66">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q66">
         <v>2.74</v>
@@ -11094,7 +11094,7 @@
         <v>1.4</v>
       </c>
       <c r="W66">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X66">
         <v>1.01</v>
@@ -11115,10 +11115,10 @@
         <v>2.97</v>
       </c>
       <c r="AD66">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE66">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF66">
         <v>1.75</v>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AK66">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11233,7 +11233,7 @@
         <v>1.75</v>
       </c>
       <c r="O67">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P67">
         <v>3.9</v>
@@ -11245,10 +11245,10 @@
         <v>2.33</v>
       </c>
       <c r="S67">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T67">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="U67">
         <v>2.71</v>
@@ -11263,28 +11263,28 @@
         <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z67">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="AA67">
         <v>1.75</v>
       </c>
       <c r="AB67">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AC67">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AD67">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE67">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF67">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AG67">
         <v>2.05</v>
@@ -11393,7 +11393,7 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="O68">
         <v>3.05</v>
@@ -11420,10 +11420,10 @@
         <v>1.35</v>
       </c>
       <c r="W68">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X68">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y68">
         <v>1.29</v>
@@ -11435,7 +11435,7 @@
         <v>2.16</v>
       </c>
       <c r="AB68">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AC68">
         <v>3.42</v>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AK68">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11568,7 +11568,7 @@
         <v>2.75</v>
       </c>
       <c r="R69">
-        <v>2.08</v>
+        <v>2.31</v>
       </c>
       <c r="S69">
         <v>1.3</v>
@@ -11589,7 +11589,7 @@
         <v>1.02</v>
       </c>
       <c r="Y69">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="Z69">
         <v>3.91</v>
@@ -11719,19 +11719,19 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="O70">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="P70">
         <v>2.52</v>
       </c>
       <c r="Q70">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="R70">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="S70">
         <v>1.33</v>
@@ -11746,37 +11746,37 @@
         <v>1.44</v>
       </c>
       <c r="W70">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X70">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y70">
         <v>1.25</v>
       </c>
       <c r="Z70">
-        <v>3.68</v>
+        <v>3.85</v>
       </c>
       <c r="AA70">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AB70">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AC70">
         <v>2.7</v>
       </c>
       <c r="AD70">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE70">
         <v>1.14</v>
       </c>
       <c r="AF70">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG70">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11891,25 +11891,25 @@
         <v>2.65</v>
       </c>
       <c r="Q71">
-        <v>2.92</v>
+        <v>2.75</v>
       </c>
       <c r="R71">
         <v>2.03</v>
       </c>
       <c r="S71">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T71">
-        <v>2.48</v>
+        <v>2.69</v>
       </c>
       <c r="U71">
-        <v>2.89</v>
+        <v>3.2</v>
       </c>
       <c r="V71">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W71">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X71">
         <v>1.02</v>
@@ -11918,22 +11918,22 @@
         <v>1.31</v>
       </c>
       <c r="Z71">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="AA71">
         <v>2.06</v>
       </c>
       <c r="AB71">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC71">
-        <v>3.98</v>
+        <v>3.99</v>
       </c>
       <c r="AD71">
         <v>1.22</v>
       </c>
       <c r="AE71">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF71">
         <v>1.85</v>
@@ -12084,22 +12084,22 @@
         <v>3.9</v>
       </c>
       <c r="AA72">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AB72">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AC72">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AD72">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE72">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF72">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG72">
         <v>2.15</v>
@@ -12543,16 +12543,16 @@
         <v>0</v>
       </c>
       <c r="Q75">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R75">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="S75">
         <v>1.28</v>
       </c>
       <c r="T75">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="U75">
         <v>2.29</v>
@@ -12570,13 +12570,13 @@
         <v>1.16</v>
       </c>
       <c r="Z75">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="AA75">
         <v>1.61</v>
       </c>
       <c r="AB75">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AC75">
         <v>2.46</v>
@@ -12588,7 +12588,7 @@
         <v>1.14</v>
       </c>
       <c r="AF75">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AG75">
         <v>2.25</v>
@@ -12706,46 +12706,46 @@
         <v>0</v>
       </c>
       <c r="Q76">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="R76">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="S76">
         <v>1.29</v>
       </c>
       <c r="T76">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="U76">
         <v>2.32</v>
       </c>
       <c r="V76">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="W76">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X76">
         <v>1.02</v>
       </c>
       <c r="Y76">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="Z76">
         <v>4.15</v>
       </c>
       <c r="AA76">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AB76">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AC76">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="AD76">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AE76">
         <v>1.19</v>
@@ -12754,7 +12754,7 @@
         <v>1.53</v>
       </c>
       <c r="AG76">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AK76">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12878,10 +12878,10 @@
         <v>1.46</v>
       </c>
       <c r="T77">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="U77">
-        <v>2.93</v>
+        <v>3.2</v>
       </c>
       <c r="V77">
         <v>1.3</v>
@@ -12890,25 +12890,25 @@
         <v>1.05</v>
       </c>
       <c r="X77">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y77">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="Z77">
-        <v>2.89</v>
+        <v>2.74</v>
       </c>
       <c r="AA77">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AB77">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC77">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AD77">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE77">
         <v>1.02</v>
@@ -12917,7 +12917,7 @@
         <v>2.05</v>
       </c>
       <c r="AG77">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -13023,16 +13023,16 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="O78">
-        <v>4.08</v>
+        <v>4.2</v>
       </c>
       <c r="P78">
         <v>4.2</v>
       </c>
       <c r="Q78">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="R78">
         <v>2.38</v>
@@ -13065,22 +13065,22 @@
         <v>1.4</v>
       </c>
       <c r="AB78">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="AC78">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AD78">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AE78">
         <v>1.25</v>
       </c>
       <c r="AF78">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG78">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK78">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13198,13 +13198,13 @@
         <v>2.01</v>
       </c>
       <c r="R79">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="S79">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T79">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="U79">
         <v>2</v>
@@ -13243,7 +13243,7 @@
         <v>1.45</v>
       </c>
       <c r="AG79">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK79">
         <v>2.04</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="O80">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P80">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="Q80">
-        <v>3.56</v>
+        <v>2.7</v>
       </c>
       <c r="R80">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="S80">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T80">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="U80">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="V80">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="W80">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="X80">
         <v>1.01</v>
       </c>
       <c r="Y80">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z80">
-        <v>7.5</v>
+        <v>6.4</v>
       </c>
       <c r="AA80">
         <v>1.33</v>
       </c>
       <c r="AB80">
-        <v>3.4</v>
+        <v>2.97</v>
       </c>
       <c r="AC80">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AD80">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AE80">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AF80">
         <v>1.31</v>
       </c>
       <c r="AG80">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK80">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,80 +13512,80 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.21</v>
+        <v>2.9</v>
       </c>
       <c r="O81">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P81">
-        <v>2.41</v>
+        <v>1.95</v>
       </c>
       <c r="Q81">
-        <v>2.62</v>
+        <v>3.3</v>
       </c>
       <c r="R81">
-        <v>2.27</v>
+        <v>2.45</v>
       </c>
       <c r="S81">
+        <v>1.17</v>
+      </c>
+      <c r="T81">
+        <v>4.1</v>
+      </c>
+      <c r="U81">
+        <v>1.9</v>
+      </c>
+      <c r="V81">
+        <v>1.88</v>
+      </c>
+      <c r="W81">
+        <v>1.17</v>
+      </c>
+      <c r="X81">
+        <v>1.01</v>
+      </c>
+      <c r="Y81">
+        <v>1.06</v>
+      </c>
+      <c r="Z81">
+        <v>7.5</v>
+      </c>
+      <c r="AA81">
+        <v>1.33</v>
+      </c>
+      <c r="AB81">
+        <v>3.4</v>
+      </c>
+      <c r="AC81">
+        <v>1.79</v>
+      </c>
+      <c r="AD81">
+        <v>1.97</v>
+      </c>
+      <c r="AE81">
+        <v>1.37</v>
+      </c>
+      <c r="AF81">
+        <v>1.3</v>
+      </c>
+      <c r="AG81">
+        <v>3.1</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ81">
         <v>1.22</v>
       </c>
-      <c r="T81">
-        <v>3.48</v>
-      </c>
-      <c r="U81">
-        <v>2.16</v>
-      </c>
-      <c r="V81">
-        <v>1.63</v>
-      </c>
-      <c r="W81">
-        <v>1.12</v>
-      </c>
-      <c r="X81">
-        <v>1.02</v>
-      </c>
-      <c r="Y81">
-        <v>1.09</v>
-      </c>
-      <c r="Z81">
-        <v>5.3</v>
-      </c>
-      <c r="AA81">
-        <v>1.47</v>
-      </c>
-      <c r="AB81">
-        <v>2.6</v>
-      </c>
-      <c r="AC81">
-        <v>2.16</v>
-      </c>
-      <c r="AD81">
-        <v>1.64</v>
-      </c>
-      <c r="AE81">
-        <v>1.22</v>
-      </c>
-      <c r="AF81">
-        <v>1.4</v>
-      </c>
-      <c r="AG81">
-        <v>2.75</v>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI81" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ81">
-        <v>1.25</v>
-      </c>
       <c r="AK81">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,34 +13675,34 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.82</v>
+        <v>2.21</v>
       </c>
       <c r="O82">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P82">
-        <v>2.03</v>
+        <v>2.4</v>
       </c>
       <c r="Q82">
-        <v>3.4</v>
+        <v>2.87</v>
       </c>
       <c r="R82">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="S82">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T82">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="U82">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="V82">
         <v>1.65</v>
       </c>
       <c r="W82">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X82">
         <v>1.02</v>
@@ -13711,19 +13711,19 @@
         <v>1.09</v>
       </c>
       <c r="Z82">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="AA82">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AB82">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="AC82">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="AD82">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AE82">
         <v>1.27</v>
@@ -13732,7 +13732,7 @@
         <v>1.4</v>
       </c>
       <c r="AG82">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="AK82">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,80 +13838,80 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.5</v>
+        <v>2.82</v>
       </c>
       <c r="O83">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="P83">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="Q83">
-        <v>2.7</v>
+        <v>2.94</v>
       </c>
       <c r="R83">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="S83">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T83">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="U83">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="V83">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="W83">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="X83">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y83">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Z83">
-        <v>6.4</v>
+        <v>5.25</v>
       </c>
       <c r="AA83">
+        <v>1.47</v>
+      </c>
+      <c r="AB83">
+        <v>2.6</v>
+      </c>
+      <c r="AC83">
+        <v>2.11</v>
+      </c>
+      <c r="AD83">
+        <v>1.67</v>
+      </c>
+      <c r="AE83">
+        <v>1.24</v>
+      </c>
+      <c r="AF83">
+        <v>1.4</v>
+      </c>
+      <c r="AG83">
+        <v>2.73</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ83">
+        <v>1.64</v>
+      </c>
+      <c r="AK83">
         <v>1.33</v>
-      </c>
-      <c r="AB83">
-        <v>2.97</v>
-      </c>
-      <c r="AC83">
-        <v>1.85</v>
-      </c>
-      <c r="AD83">
-        <v>1.88</v>
-      </c>
-      <c r="AE83">
-        <v>1.39</v>
-      </c>
-      <c r="AF83">
-        <v>1.31</v>
-      </c>
-      <c r="AG83">
-        <v>3.14</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ83">
-        <v>1.25</v>
-      </c>
-      <c r="AK83">
-        <v>1.44</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14010,22 +14010,22 @@
         <v>4.33</v>
       </c>
       <c r="Q84">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="R84">
         <v>2.5</v>
       </c>
       <c r="S84">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T84">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U84">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="V84">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="W84">
         <v>1.14</v>
@@ -14040,25 +14040,25 @@
         <v>5.3</v>
       </c>
       <c r="AA84">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AB84">
         <v>2.46</v>
       </c>
       <c r="AC84">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AD84">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AE84">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF84">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AG84">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
         <v>1.2</v>
       </c>
       <c r="AK84">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14173,10 +14173,10 @@
         <v>2.5</v>
       </c>
       <c r="Q85">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="R85">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S85">
         <v>1.28</v>
@@ -14188,7 +14188,7 @@
         <v>2.3</v>
       </c>
       <c r="V85">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W85">
         <v>1.1</v>
@@ -14212,7 +14212,7 @@
         <v>2.35</v>
       </c>
       <c r="AD85">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AE85">
         <v>1.16</v>
@@ -14221,7 +14221,7 @@
         <v>1.48</v>
       </c>
       <c r="AG85">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>1.3</v>
       </c>
       <c r="AK85">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14336,10 +14336,10 @@
         <v>2.1</v>
       </c>
       <c r="Q86">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="R86">
-        <v>2.53</v>
+        <v>2.34</v>
       </c>
       <c r="S86">
         <v>1.23</v>
@@ -14369,10 +14369,10 @@
         <v>1.43</v>
       </c>
       <c r="AB86">
-        <v>2.46</v>
+        <v>2.63</v>
       </c>
       <c r="AC86">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AD86">
         <v>1.64</v>
@@ -14384,7 +14384,7 @@
         <v>1.44</v>
       </c>
       <c r="AG86">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK86">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14653,7 +14653,7 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="O88">
         <v>3.25</v>
@@ -14668,10 +14668,10 @@
         <v>2.1</v>
       </c>
       <c r="S88">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T88">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="U88">
         <v>2.9</v>
@@ -14680,37 +14680,37 @@
         <v>1.41</v>
       </c>
       <c r="W88">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X88">
         <v>1.02</v>
       </c>
       <c r="Y88">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="Z88">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="AA88">
         <v>1.92</v>
       </c>
       <c r="AB88">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AC88">
-        <v>3.51</v>
+        <v>3.05</v>
       </c>
       <c r="AD88">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE88">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF88">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AG88">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14831,28 +14831,28 @@
         <v>2</v>
       </c>
       <c r="S89">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="T89">
-        <v>2.61</v>
+        <v>2.56</v>
       </c>
       <c r="U89">
         <v>2.88</v>
       </c>
       <c r="V89">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W89">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X89">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y89">
         <v>1.33</v>
       </c>
       <c r="Z89">
-        <v>3.08</v>
+        <v>3.21</v>
       </c>
       <c r="AA89">
         <v>2.05</v>
@@ -14988,10 +14988,10 @@
         <v>0</v>
       </c>
       <c r="Q90">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="R90">
-        <v>2.63</v>
+        <v>2.32</v>
       </c>
       <c r="S90">
         <v>1.22</v>
@@ -15003,7 +15003,7 @@
         <v>2.14</v>
       </c>
       <c r="V90">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W90">
         <v>1.14</v>
@@ -15012,31 +15012,31 @@
         <v>1.02</v>
       </c>
       <c r="Y90">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z90">
-        <v>5</v>
+        <v>5.29</v>
       </c>
       <c r="AA90">
         <v>1.46</v>
       </c>
       <c r="AB90">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="AC90">
         <v>2.23</v>
       </c>
       <c r="AD90">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AE90">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AF90">
         <v>1.55</v>
       </c>
       <c r="AG90">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15142,10 +15142,10 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="O91">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P91">
         <v>2.83</v>
@@ -15157,13 +15157,13 @@
         <v>2.22</v>
       </c>
       <c r="S91">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="T91">
-        <v>2.85</v>
+        <v>3.18</v>
       </c>
       <c r="U91">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="V91">
         <v>1.46</v>
@@ -15178,13 +15178,13 @@
         <v>1.22</v>
       </c>
       <c r="Z91">
-        <v>3.8</v>
+        <v>3.93</v>
       </c>
       <c r="AA91">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="AB91">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="AC91">
         <v>2.9</v>
@@ -15199,7 +15199,7 @@
         <v>1.58</v>
       </c>
       <c r="AG91">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK91">
         <v>1.56</v>
@@ -15314,7 +15314,7 @@
         <v>4.53</v>
       </c>
       <c r="Q92">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="R92">
         <v>2.38</v>
@@ -15323,7 +15323,7 @@
         <v>1.23</v>
       </c>
       <c r="T92">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="U92">
         <v>2.19</v>
@@ -15332,7 +15332,7 @@
         <v>1.61</v>
       </c>
       <c r="W92">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X92">
         <v>1.02</v>
@@ -15341,10 +15341,10 @@
         <v>1.14</v>
       </c>
       <c r="Z92">
-        <v>4.94</v>
+        <v>4.5</v>
       </c>
       <c r="AA92">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AB92">
         <v>2.26</v>
@@ -15362,7 +15362,7 @@
         <v>1.57</v>
       </c>
       <c r="AG92">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AK92">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15477,7 +15477,7 @@
         <v>19</v>
       </c>
       <c r="Q93">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="R93">
         <v>3.87</v>
@@ -15513,13 +15513,13 @@
         <v>5.65</v>
       </c>
       <c r="AC93">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AD93">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="AE93">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AF93">
         <v>1.82</v>
@@ -15541,7 +15541,7 @@
         <v>1.02</v>
       </c>
       <c r="AK93">
-        <v>10.75</v>
+        <v>9</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15640,25 +15640,25 @@
         <v>2.34</v>
       </c>
       <c r="Q94">
-        <v>2.96</v>
+        <v>3.36</v>
       </c>
       <c r="R94">
         <v>2.18</v>
       </c>
       <c r="S94">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T94">
         <v>3.18</v>
       </c>
       <c r="U94">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="V94">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W94">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X94">
         <v>1</v>
@@ -15673,13 +15673,13 @@
         <v>1.63</v>
       </c>
       <c r="AB94">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AC94">
         <v>2.69</v>
       </c>
       <c r="AD94">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE94">
         <v>1.14</v>
@@ -15704,7 +15704,7 @@
         <v>1.25</v>
       </c>
       <c r="AK94">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15800,7 +15800,7 @@
         <v>3.65</v>
       </c>
       <c r="P95">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="Q95">
         <v>2.55</v>
@@ -15812,7 +15812,7 @@
         <v>1.25</v>
       </c>
       <c r="T95">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="U95">
         <v>2.3</v>
@@ -15821,7 +15821,7 @@
         <v>1.62</v>
       </c>
       <c r="W95">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X95">
         <v>1.02</v>
@@ -15839,7 +15839,7 @@
         <v>2.35</v>
       </c>
       <c r="AC95">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="AD95">
         <v>1.62</v>
@@ -15966,10 +15966,10 @@
         <v>2.8</v>
       </c>
       <c r="Q96">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="R96">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="S96">
         <v>1.29</v>
@@ -15990,47 +15990,47 @@
         <v>1</v>
       </c>
       <c r="Y96">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z96">
-        <v>3.8</v>
+        <v>3.98</v>
       </c>
       <c r="AA96">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB96">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC96">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="AD96">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AE96">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF96">
+        <v>1.54</v>
+      </c>
+      <c r="AG96">
+        <v>2.28</v>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ96">
+        <v>1.27</v>
+      </c>
+      <c r="AK96">
         <v>1.57</v>
-      </c>
-      <c r="AG96">
-        <v>2.22</v>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ96">
-        <v>1.28</v>
-      </c>
-      <c r="AK96">
-        <v>1.58</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16120,7 +16120,7 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="O97">
         <v>3.65</v>
@@ -16153,19 +16153,19 @@
         <v>1.03</v>
       </c>
       <c r="Y97">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="Z97">
-        <v>4.06</v>
+        <v>3.92</v>
       </c>
       <c r="AA97">
         <v>1.71</v>
       </c>
       <c r="AB97">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AC97">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AD97">
         <v>1.43</v>
@@ -16177,7 +16177,7 @@
         <v>1.6</v>
       </c>
       <c r="AG97">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,80 +16283,80 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.37</v>
+        <v>3.8</v>
       </c>
       <c r="O98">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="P98">
-        <v>5.8</v>
+        <v>1.78</v>
       </c>
       <c r="Q98">
-        <v>1.86</v>
+        <v>4.2</v>
       </c>
       <c r="R98">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="S98">
+        <v>1.33</v>
+      </c>
+      <c r="T98">
+        <v>3.2</v>
+      </c>
+      <c r="U98">
+        <v>2.54</v>
+      </c>
+      <c r="V98">
+        <v>1.44</v>
+      </c>
+      <c r="W98">
+        <v>1.05</v>
+      </c>
+      <c r="X98">
+        <v>1.03</v>
+      </c>
+      <c r="Y98">
+        <v>1.19</v>
+      </c>
+      <c r="Z98">
+        <v>3.77</v>
+      </c>
+      <c r="AA98">
+        <v>1.75</v>
+      </c>
+      <c r="AB98">
+        <v>2.05</v>
+      </c>
+      <c r="AC98">
+        <v>2.83</v>
+      </c>
+      <c r="AD98">
+        <v>1.33</v>
+      </c>
+      <c r="AE98">
+        <v>1.09</v>
+      </c>
+      <c r="AF98">
+        <v>1.67</v>
+      </c>
+      <c r="AG98">
+        <v>2.06</v>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ98">
         <v>1.2</v>
       </c>
-      <c r="T98">
-        <v>3.72</v>
-      </c>
-      <c r="U98">
-        <v>2.22</v>
-      </c>
-      <c r="V98">
-        <v>1.57</v>
-      </c>
-      <c r="W98">
-        <v>1.1</v>
-      </c>
-      <c r="X98">
-        <v>1.02</v>
-      </c>
-      <c r="Y98">
+      <c r="AK98">
         <v>1.17</v>
-      </c>
-      <c r="Z98">
-        <v>4.64</v>
-      </c>
-      <c r="AA98">
-        <v>1.53</v>
-      </c>
-      <c r="AB98">
-        <v>2.45</v>
-      </c>
-      <c r="AC98">
-        <v>2.33</v>
-      </c>
-      <c r="AD98">
-        <v>1.51</v>
-      </c>
-      <c r="AE98">
-        <v>1.21</v>
-      </c>
-      <c r="AF98">
-        <v>1.66</v>
-      </c>
-      <c r="AG98">
-        <v>2.04</v>
-      </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI98" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ98">
-        <v>1.06</v>
-      </c>
-      <c r="AK98">
-        <v>2.58</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.1</v>
+        <v>1.37</v>
       </c>
       <c r="O99">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="P99">
-        <v>3.1</v>
+        <v>5.8</v>
       </c>
       <c r="Q99">
-        <v>2.78</v>
+        <v>1.85</v>
       </c>
       <c r="R99">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="S99">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="T99">
-        <v>2.84</v>
+        <v>3.72</v>
       </c>
       <c r="U99">
-        <v>2.58</v>
+        <v>2.22</v>
       </c>
       <c r="V99">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="W99">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X99">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y99">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="Z99">
-        <v>3.34</v>
+        <v>4.85</v>
       </c>
       <c r="AA99">
-        <v>1.87</v>
+        <v>1.53</v>
       </c>
       <c r="AB99">
-        <v>1.9</v>
+        <v>2.45</v>
       </c>
       <c r="AC99">
-        <v>3.05</v>
+        <v>2.33</v>
       </c>
       <c r="AD99">
-        <v>1.28</v>
+        <v>1.51</v>
       </c>
       <c r="AE99">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AF99">
         <v>1.67</v>
       </c>
       <c r="AG99">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.28</v>
+        <v>1.06</v>
       </c>
       <c r="AK99">
-        <v>1.62</v>
+        <v>2.58</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,80 +16609,80 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.47</v>
+        <v>2.1</v>
       </c>
       <c r="O100">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="P100">
-        <v>5.4</v>
+        <v>3.1</v>
       </c>
       <c r="Q100">
-        <v>1.99</v>
+        <v>2.78</v>
       </c>
       <c r="R100">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="S100">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="T100">
-        <v>3.75</v>
+        <v>2.84</v>
       </c>
       <c r="U100">
-        <v>2.1</v>
+        <v>2.58</v>
       </c>
       <c r="V100">
+        <v>1.4</v>
+      </c>
+      <c r="W100">
+        <v>1.07</v>
+      </c>
+      <c r="X100">
+        <v>1</v>
+      </c>
+      <c r="Y100">
+        <v>1.24</v>
+      </c>
+      <c r="Z100">
+        <v>3.34</v>
+      </c>
+      <c r="AA100">
+        <v>1.87</v>
+      </c>
+      <c r="AB100">
+        <v>1.9</v>
+      </c>
+      <c r="AC100">
+        <v>3.04</v>
+      </c>
+      <c r="AD100">
+        <v>1.29</v>
+      </c>
+      <c r="AE100">
+        <v>1.07</v>
+      </c>
+      <c r="AF100">
+        <v>1.67</v>
+      </c>
+      <c r="AG100">
+        <v>2.05</v>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ100">
+        <v>1.25</v>
+      </c>
+      <c r="AK100">
         <v>1.62</v>
-      </c>
-      <c r="W100">
-        <v>1.17</v>
-      </c>
-      <c r="X100">
-        <v>1.02</v>
-      </c>
-      <c r="Y100">
-        <v>1.15</v>
-      </c>
-      <c r="Z100">
-        <v>4.75</v>
-      </c>
-      <c r="AA100">
-        <v>1.46</v>
-      </c>
-      <c r="AB100">
-        <v>2.55</v>
-      </c>
-      <c r="AC100">
-        <v>2.17</v>
-      </c>
-      <c r="AD100">
-        <v>1.59</v>
-      </c>
-      <c r="AE100">
-        <v>1.22</v>
-      </c>
-      <c r="AF100">
-        <v>1.58</v>
-      </c>
-      <c r="AG100">
-        <v>2.17</v>
-      </c>
-      <c r="AH100" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI100" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ100">
-        <v>1.07</v>
-      </c>
-      <c r="AK100">
-        <v>2.4</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>3.8</v>
+        <v>1.47</v>
       </c>
       <c r="O101">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="P101">
-        <v>1.78</v>
+        <v>5.4</v>
       </c>
       <c r="Q101">
-        <v>4.54</v>
+        <v>1.98</v>
       </c>
       <c r="R101">
-        <v>2.33</v>
+        <v>2.69</v>
       </c>
       <c r="S101">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="T101">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="U101">
-        <v>2.66</v>
+        <v>2.1</v>
       </c>
       <c r="V101">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="W101">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="X101">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y101">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z101">
-        <v>3.77</v>
+        <v>4.75</v>
       </c>
       <c r="AA101">
-        <v>1.75</v>
+        <v>1.46</v>
       </c>
       <c r="AB101">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="AC101">
-        <v>2.83</v>
+        <v>2.15</v>
       </c>
       <c r="AD101">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AE101">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AF101">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AG101">
-        <v>2.03</v>
+        <v>2.17</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AK101">
-        <v>1.16</v>
+        <v>2.5</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -17005,7 +17005,7 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK102">
         <v>1.6</v>
@@ -17098,7 +17098,7 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="O103">
         <v>3.42</v>
@@ -17110,16 +17110,16 @@
         <v>3.4</v>
       </c>
       <c r="R103">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="S103">
         <v>1.36</v>
       </c>
       <c r="T103">
-        <v>3.17</v>
+        <v>2.8</v>
       </c>
       <c r="U103">
-        <v>2.66</v>
+        <v>2.51</v>
       </c>
       <c r="V103">
         <v>1.45</v>
@@ -17128,7 +17128,7 @@
         <v>1.06</v>
       </c>
       <c r="X103">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y103">
         <v>1.25</v>
@@ -17137,10 +17137,10 @@
         <v>3.7</v>
       </c>
       <c r="AA103">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AB103">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AC103">
         <v>3.07</v>
@@ -17149,10 +17149,10 @@
         <v>1.34</v>
       </c>
       <c r="AE103">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF103">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG103">
         <v>2.18</v>
@@ -17171,7 +17171,7 @@
         <v>1.62</v>
       </c>
       <c r="AK103">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17427,10 +17427,10 @@
         <v>2.71</v>
       </c>
       <c r="O105">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="P105">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q105">
         <v>3.07</v>
@@ -17442,40 +17442,40 @@
         <v>1.22</v>
       </c>
       <c r="T105">
-        <v>4.1</v>
+        <v>3.94</v>
       </c>
       <c r="U105">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="V105">
         <v>1.69</v>
       </c>
       <c r="W105">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X105">
         <v>1.01</v>
       </c>
       <c r="Y105">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z105">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AA105">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AB105">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="AC105">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AD105">
         <v>1.62</v>
       </c>
       <c r="AE105">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AF105">
         <v>1.39</v>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.21</v>
+        <v>1.66</v>
       </c>
       <c r="AK105">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17596,16 +17596,16 @@
         <v>3.9</v>
       </c>
       <c r="Q106">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="R106">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="S106">
         <v>1.45</v>
       </c>
       <c r="T106">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="U106">
         <v>3.12</v>
@@ -17614,16 +17614,16 @@
         <v>1.28</v>
       </c>
       <c r="W106">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X106">
         <v>1.05</v>
       </c>
       <c r="Y106">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Z106">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="AA106">
         <v>2.31</v>
@@ -17632,7 +17632,7 @@
         <v>1.52</v>
       </c>
       <c r="AC106">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="AD106">
         <v>1.15</v>
@@ -17753,10 +17753,10 @@
         <v>1.4</v>
       </c>
       <c r="O107">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="P107">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Q107">
         <v>1.83</v>
@@ -17765,10 +17765,10 @@
         <v>2.6</v>
       </c>
       <c r="S107">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T107">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="U107">
         <v>2.25</v>
@@ -17777,7 +17777,7 @@
         <v>1.57</v>
       </c>
       <c r="W107">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X107">
         <v>1.01</v>
@@ -17786,13 +17786,13 @@
         <v>1.18</v>
       </c>
       <c r="Z107">
-        <v>4.73</v>
+        <v>4.6</v>
       </c>
       <c r="AA107">
         <v>1.57</v>
       </c>
       <c r="AB107">
-        <v>2.39</v>
+        <v>2.26</v>
       </c>
       <c r="AC107">
         <v>2.45</v>
@@ -17807,7 +17807,7 @@
         <v>1.67</v>
       </c>
       <c r="AG107">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>1.17</v>
       </c>
       <c r="AK107">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17919,7 +17919,7 @@
         <v>4.2</v>
       </c>
       <c r="P108">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="Q108">
         <v>1.94</v>
@@ -17934,43 +17934,43 @@
         <v>3.08</v>
       </c>
       <c r="U108">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="V108">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="W108">
         <v>1.07</v>
       </c>
       <c r="X108">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y108">
         <v>1.16</v>
       </c>
       <c r="Z108">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="AA108">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB108">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="AC108">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="AD108">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AE108">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF108">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AG108">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>1.19</v>
       </c>
       <c r="AK108">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="O109">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P109">
         <v>4.2</v>
       </c>
       <c r="Q109">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="R109">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="S109">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T109">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="U109">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="V109">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W109">
         <v>1.06</v>
       </c>
       <c r="X109">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y109">
         <v>1.28</v>
       </c>
       <c r="Z109">
-        <v>3.68</v>
+        <v>3.25</v>
       </c>
       <c r="AA109">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AB109">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AC109">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AD109">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE109">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF109">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG109">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AK109">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18245,10 +18245,10 @@
         <v>3.6</v>
       </c>
       <c r="P110">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="Q110">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="R110">
         <v>2.2</v>
@@ -18257,7 +18257,7 @@
         <v>1.3</v>
       </c>
       <c r="T110">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="U110">
         <v>2.63</v>
@@ -18275,28 +18275,28 @@
         <v>1.26</v>
       </c>
       <c r="Z110">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="AA110">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AB110">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AC110">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AD110">
         <v>1.37</v>
       </c>
       <c r="AE110">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF110">
         <v>1.7</v>
       </c>
       <c r="AG110">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>1.2</v>
       </c>
       <c r="AK110">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18565,22 +18565,22 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="O112">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P112">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="Q112">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="R112">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S112">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T112">
         <v>2.77</v>
@@ -18601,10 +18601,10 @@
         <v>1.27</v>
       </c>
       <c r="Z112">
-        <v>3.69</v>
+        <v>3.68</v>
       </c>
       <c r="AA112">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AB112">
         <v>1.94</v>
@@ -18616,7 +18616,7 @@
         <v>1.3</v>
       </c>
       <c r="AE112">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF112">
         <v>1.94</v>
@@ -18737,10 +18737,10 @@
         <v>4.5</v>
       </c>
       <c r="Q113">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="R113">
-        <v>2.39</v>
+        <v>2.6</v>
       </c>
       <c r="S113">
         <v>1.21</v>
@@ -18752,7 +18752,7 @@
         <v>2.02</v>
       </c>
       <c r="V113">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="W113">
         <v>1.18</v>
@@ -18767,10 +18767,10 @@
         <v>5.35</v>
       </c>
       <c r="AA113">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB113">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="AC113">
         <v>2.05</v>
@@ -18785,7 +18785,7 @@
         <v>1.45</v>
       </c>
       <c r="AG113">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>1.2</v>
       </c>
       <c r="AK113">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -19054,25 +19054,25 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="O115">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P115">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="Q115">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R115">
         <v>2</v>
       </c>
       <c r="S115">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T115">
-        <v>2.71</v>
+        <v>2.56</v>
       </c>
       <c r="U115">
         <v>2.9</v>
@@ -19099,19 +19099,19 @@
         <v>1.67</v>
       </c>
       <c r="AC115">
-        <v>3.79</v>
+        <v>3.58</v>
       </c>
       <c r="AD115">
         <v>1.22</v>
       </c>
       <c r="AE115">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF115">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AG115">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AK115">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19217,10 +19217,10 @@
         </is>
       </c>
       <c r="N116">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O116">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P116">
         <v>2.9</v>
@@ -19238,43 +19238,43 @@
         <v>2.53</v>
       </c>
       <c r="U116">
-        <v>2.96</v>
+        <v>2.82</v>
       </c>
       <c r="V116">
         <v>1.33</v>
       </c>
       <c r="W116">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X116">
         <v>1.02</v>
       </c>
       <c r="Y116">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="Z116">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AA116">
         <v>2.08</v>
       </c>
       <c r="AB116">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AC116">
-        <v>3.83</v>
+        <v>3.5</v>
       </c>
       <c r="AD116">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE116">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF116">
         <v>1.81</v>
       </c>
       <c r="AG116">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19290,7 +19290,7 @@
         <v>1.33</v>
       </c>
       <c r="AK116">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O117">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P117">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q117">
         <v>0</v>
@@ -19552,10 +19552,10 @@
         <v>0</v>
       </c>
       <c r="Q118">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="R118">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="S118">
         <v>1.3</v>
@@ -19585,13 +19585,13 @@
         <v>1.76</v>
       </c>
       <c r="AB118">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="AC118">
-        <v>2.89</v>
+        <v>2.74</v>
       </c>
       <c r="AD118">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AE118">
         <v>1.13</v>
@@ -19600,7 +19600,7 @@
         <v>1.6</v>
       </c>
       <c r="AG118">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>3.8</v>
+        <v>1.37</v>
       </c>
       <c r="O98">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="P98">
-        <v>1.78</v>
+        <v>5.8</v>
       </c>
       <c r="Q98">
-        <v>4.2</v>
+        <v>1.85</v>
       </c>
       <c r="R98">
+        <v>2.5</v>
+      </c>
+      <c r="S98">
+        <v>1.2</v>
+      </c>
+      <c r="T98">
+        <v>3.72</v>
+      </c>
+      <c r="U98">
+        <v>2.22</v>
+      </c>
+      <c r="V98">
+        <v>1.57</v>
+      </c>
+      <c r="W98">
+        <v>1.1</v>
+      </c>
+      <c r="X98">
+        <v>1.02</v>
+      </c>
+      <c r="Y98">
+        <v>1.11</v>
+      </c>
+      <c r="Z98">
+        <v>4.85</v>
+      </c>
+      <c r="AA98">
+        <v>1.53</v>
+      </c>
+      <c r="AB98">
+        <v>2.45</v>
+      </c>
+      <c r="AC98">
         <v>2.33</v>
       </c>
-      <c r="S98">
-        <v>1.33</v>
-      </c>
-      <c r="T98">
-        <v>3.2</v>
-      </c>
-      <c r="U98">
-        <v>2.54</v>
-      </c>
-      <c r="V98">
-        <v>1.44</v>
-      </c>
-      <c r="W98">
-        <v>1.05</v>
-      </c>
-      <c r="X98">
-        <v>1.03</v>
-      </c>
-      <c r="Y98">
-        <v>1.19</v>
-      </c>
-      <c r="Z98">
-        <v>3.77</v>
-      </c>
-      <c r="AA98">
-        <v>1.75</v>
-      </c>
-      <c r="AB98">
-        <v>2.05</v>
-      </c>
-      <c r="AC98">
-        <v>2.83</v>
-      </c>
       <c r="AD98">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="AE98">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="AF98">
         <v>1.67</v>
       </c>
       <c r="AG98">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AK98">
-        <v>1.17</v>
+        <v>2.58</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.37</v>
+        <v>3.8</v>
       </c>
       <c r="O99">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="P99">
-        <v>5.8</v>
+        <v>1.78</v>
       </c>
       <c r="Q99">
-        <v>1.85</v>
+        <v>4.2</v>
       </c>
       <c r="R99">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="S99">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="T99">
-        <v>3.72</v>
+        <v>3.2</v>
       </c>
       <c r="U99">
-        <v>2.22</v>
+        <v>2.54</v>
       </c>
       <c r="V99">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="W99">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X99">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y99">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="Z99">
-        <v>4.85</v>
+        <v>3.77</v>
       </c>
       <c r="AA99">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AB99">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="AC99">
-        <v>2.33</v>
+        <v>2.83</v>
       </c>
       <c r="AD99">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="AE99">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="AF99">
         <v>1.67</v>
       </c>
       <c r="AG99">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AK99">
-        <v>2.58</v>
+        <v>1.17</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -18580,10 +18580,10 @@
         <v>2.25</v>
       </c>
       <c r="S112">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T112">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="U112">
         <v>2.75</v>
@@ -18595,34 +18595,34 @@
         <v>1.07</v>
       </c>
       <c r="X112">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y112">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z112">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="AA112">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB112">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="AC112">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="AD112">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE112">
         <v>1.07</v>
       </c>
       <c r="AF112">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AG112">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18764,7 +18764,7 @@
         <v>1.09</v>
       </c>
       <c r="Z113">
-        <v>5.35</v>
+        <v>5.4</v>
       </c>
       <c r="AA113">
         <v>1.4</v>
@@ -19290,7 +19290,7 @@
         <v>1.33</v>
       </c>
       <c r="AK116">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL116">
         <v>0</v>

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.37</v>
+        <v>3.8</v>
       </c>
       <c r="O98">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="P98">
-        <v>5.8</v>
+        <v>1.78</v>
       </c>
       <c r="Q98">
-        <v>1.85</v>
+        <v>4.2</v>
       </c>
       <c r="R98">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="S98">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="T98">
-        <v>3.72</v>
+        <v>3.2</v>
       </c>
       <c r="U98">
-        <v>2.22</v>
+        <v>2.54</v>
       </c>
       <c r="V98">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="W98">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X98">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y98">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="Z98">
-        <v>4.85</v>
+        <v>3.77</v>
       </c>
       <c r="AA98">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AB98">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="AC98">
-        <v>2.33</v>
+        <v>2.83</v>
       </c>
       <c r="AD98">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="AE98">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="AF98">
         <v>1.67</v>
       </c>
       <c r="AG98">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AK98">
-        <v>2.58</v>
+        <v>1.17</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>3.8</v>
+        <v>1.37</v>
       </c>
       <c r="O99">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="P99">
-        <v>1.78</v>
+        <v>5.8</v>
       </c>
       <c r="Q99">
-        <v>4.2</v>
+        <v>1.85</v>
       </c>
       <c r="R99">
+        <v>2.5</v>
+      </c>
+      <c r="S99">
+        <v>1.2</v>
+      </c>
+      <c r="T99">
+        <v>3.72</v>
+      </c>
+      <c r="U99">
+        <v>2.22</v>
+      </c>
+      <c r="V99">
+        <v>1.57</v>
+      </c>
+      <c r="W99">
+        <v>1.1</v>
+      </c>
+      <c r="X99">
+        <v>1.02</v>
+      </c>
+      <c r="Y99">
+        <v>1.11</v>
+      </c>
+      <c r="Z99">
+        <v>4.85</v>
+      </c>
+      <c r="AA99">
+        <v>1.53</v>
+      </c>
+      <c r="AB99">
+        <v>2.45</v>
+      </c>
+      <c r="AC99">
         <v>2.33</v>
       </c>
-      <c r="S99">
-        <v>1.33</v>
-      </c>
-      <c r="T99">
-        <v>3.2</v>
-      </c>
-      <c r="U99">
-        <v>2.54</v>
-      </c>
-      <c r="V99">
-        <v>1.44</v>
-      </c>
-      <c r="W99">
-        <v>1.05</v>
-      </c>
-      <c r="X99">
-        <v>1.03</v>
-      </c>
-      <c r="Y99">
-        <v>1.19</v>
-      </c>
-      <c r="Z99">
-        <v>3.77</v>
-      </c>
-      <c r="AA99">
-        <v>1.75</v>
-      </c>
-      <c r="AB99">
-        <v>2.05</v>
-      </c>
-      <c r="AC99">
-        <v>2.83</v>
-      </c>
       <c r="AD99">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="AE99">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="AF99">
         <v>1.67</v>
       </c>
       <c r="AG99">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AK99">
-        <v>1.17</v>
+        <v>2.58</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -18737,16 +18737,16 @@
         <v>4.5</v>
       </c>
       <c r="Q113">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R113">
-        <v>2.6</v>
+        <v>2.39</v>
       </c>
       <c r="S113">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T113">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U113">
         <v>2.02</v>
@@ -18773,10 +18773,10 @@
         <v>2.56</v>
       </c>
       <c r="AC113">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AD113">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AE113">
         <v>1.25</v>

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="O3">
         <v>3.8</v>
@@ -807,7 +807,7 @@
         <v>4.5</v>
       </c>
       <c r="Q3">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="R3">
         <v>2.21</v>
@@ -825,7 +825,7 @@
         <v>1.44</v>
       </c>
       <c r="W3">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X3">
         <v>1.01</v>
@@ -834,19 +834,19 @@
         <v>1.23</v>
       </c>
       <c r="Z3">
-        <v>3.94</v>
+        <v>3.98</v>
       </c>
       <c r="AA3">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AB3">
         <v>2.05</v>
       </c>
       <c r="AC3">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="AD3">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE3">
         <v>1.11</v>
@@ -855,7 +855,7 @@
         <v>1.67</v>
       </c>
       <c r="AG3">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q10">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="R10">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="S10">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="T10">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="U10">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="V10">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W10">
         <v>1.06</v>
       </c>
       <c r="X10">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
         <v>1.28</v>
       </c>
       <c r="Z10">
+        <v>2.63</v>
+      </c>
+      <c r="AA10">
+        <v>1.9</v>
+      </c>
+      <c r="AB10">
+        <v>1.8</v>
+      </c>
+      <c r="AC10">
         <v>3.08</v>
       </c>
-      <c r="AA10">
-        <v>1.96</v>
-      </c>
-      <c r="AB10">
-        <v>1.72</v>
-      </c>
-      <c r="AC10">
-        <v>3.28</v>
-      </c>
       <c r="AD10">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE10">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF10">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AG10">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>1.36</v>
       </c>
       <c r="AK10">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2105,10 +2105,10 @@
         <v>2.15</v>
       </c>
       <c r="O11">
-        <v>3.2</v>
+        <v>3.06</v>
       </c>
       <c r="P11">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="Q11">
         <v>2.83</v>
@@ -2117,19 +2117,19 @@
         <v>1.98</v>
       </c>
       <c r="S11">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T11">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="U11">
         <v>2.88</v>
       </c>
       <c r="V11">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W11">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X11">
         <v>1</v>
@@ -2141,16 +2141,16 @@
         <v>3.2</v>
       </c>
       <c r="AA11">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB11">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC11">
-        <v>3.33</v>
+        <v>3.35</v>
       </c>
       <c r="AD11">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE11">
         <v>1.1</v>
@@ -2757,77 +2757,77 @@
         <v>1.8</v>
       </c>
       <c r="O15">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P15">
         <v>4.15</v>
       </c>
       <c r="Q15">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="R15">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="S15">
         <v>1.4</v>
       </c>
       <c r="T15">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="U15">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="V15">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W15">
         <v>1.08</v>
       </c>
       <c r="X15">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z15">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AA15">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="AB15">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="AC15">
-        <v>3.63</v>
+        <v>3.47</v>
       </c>
       <c r="AD15">
+        <v>1.25</v>
+      </c>
+      <c r="AE15">
+        <v>1.06</v>
+      </c>
+      <c r="AF15">
+        <v>1.83</v>
+      </c>
+      <c r="AG15">
+        <v>1.86</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15">
         <v>1.22</v>
       </c>
-      <c r="AE15">
-        <v>1.05</v>
-      </c>
-      <c r="AF15">
+      <c r="AK15">
         <v>1.87</v>
-      </c>
-      <c r="AG15">
-        <v>1.82</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15">
-        <v>1.2</v>
-      </c>
-      <c r="AK15">
-        <v>1.85</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -4260,7 +4260,7 @@
         <v>2.88</v>
       </c>
       <c r="AA24">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AB24">
         <v>1.64</v>
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>2.55</v>
       </c>
       <c r="O28">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P28">
         <v>2.5</v>
@@ -5039,7 +5039,7 @@
         <v>1.85</v>
       </c>
       <c r="O29">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P29">
         <v>3.7</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5745,7 +5745,7 @@
         <v>1.6</v>
       </c>
       <c r="AG33">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK33">
         <v>1.64</v>
@@ -6177,19 +6177,19 @@
         </is>
       </c>
       <c r="N36">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="O36">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P36">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="Q36">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="R36">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S36">
         <v>1.35</v>
@@ -6201,37 +6201,37 @@
         <v>2.64</v>
       </c>
       <c r="V36">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W36">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X36">
         <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z36">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AA36">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AB36">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC36">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AD36">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE36">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF36">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AG36">
         <v>2</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.54</v>
+        <v>1.22</v>
       </c>
       <c r="AK36">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="O37">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P37">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="Q37">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R37">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S37">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T37">
-        <v>3.5</v>
+        <v>2.99</v>
       </c>
       <c r="U37">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="V37">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="W37">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X37">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y37">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z37">
-        <v>4.3</v>
+        <v>3.98</v>
       </c>
       <c r="AA37">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AB37">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="AC37">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="AD37">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AE37">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF37">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="AG37">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK37">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,16 +6503,16 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="O38">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P38">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q38">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="R38">
         <v>2.21</v>
@@ -6524,43 +6524,43 @@
         <v>3.5</v>
       </c>
       <c r="U38">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="V38">
         <v>1.57</v>
       </c>
       <c r="W38">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X38">
         <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z38">
-        <v>4.65</v>
+        <v>4.4</v>
       </c>
       <c r="AA38">
+        <v>1.58</v>
+      </c>
+      <c r="AB38">
+        <v>2.18</v>
+      </c>
+      <c r="AC38">
+        <v>2.43</v>
+      </c>
+      <c r="AD38">
+        <v>1.44</v>
+      </c>
+      <c r="AE38">
+        <v>1.14</v>
+      </c>
+      <c r="AF38">
         <v>1.53</v>
       </c>
-      <c r="AB38">
-        <v>2.27</v>
-      </c>
-      <c r="AC38">
-        <v>2.33</v>
-      </c>
-      <c r="AD38">
-        <v>1.48</v>
-      </c>
-      <c r="AE38">
-        <v>1.16</v>
-      </c>
-      <c r="AF38">
-        <v>1.5</v>
-      </c>
       <c r="AG38">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>1.22</v>
       </c>
       <c r="AK38">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,31 +6666,31 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="O39">
         <v>5.6</v>
       </c>
       <c r="P39">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="Q39">
         <v>1.67</v>
       </c>
       <c r="R39">
-        <v>2.49</v>
+        <v>2.59</v>
       </c>
       <c r="S39">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="T39">
         <v>4</v>
       </c>
       <c r="U39">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="V39">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="W39">
         <v>1.17</v>
@@ -6702,7 +6702,7 @@
         <v>1.08</v>
       </c>
       <c r="Z39">
-        <v>5.55</v>
+        <v>5.65</v>
       </c>
       <c r="AA39">
         <v>1.4</v>
@@ -6711,19 +6711,19 @@
         <v>2.88</v>
       </c>
       <c r="AC39">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AD39">
+        <v>1.66</v>
+      </c>
+      <c r="AE39">
+        <v>1.24</v>
+      </c>
+      <c r="AF39">
         <v>1.68</v>
       </c>
-      <c r="AE39">
-        <v>1.25</v>
-      </c>
-      <c r="AF39">
-        <v>1.64</v>
-      </c>
       <c r="AG39">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>1.05</v>
       </c>
       <c r="AK39">
-        <v>2.94</v>
+        <v>3.12</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -8468,7 +8468,7 @@
         <v>2.25</v>
       </c>
       <c r="Q50">
-        <v>3.81</v>
+        <v>3.79</v>
       </c>
       <c r="R50">
         <v>1.83</v>
@@ -8498,10 +8498,10 @@
         <v>2.97</v>
       </c>
       <c r="AA50">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="AB50">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC50">
         <v>3.6</v>
@@ -8510,13 +8510,13 @@
         <v>1.25</v>
       </c>
       <c r="AE50">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF50">
         <v>1.8</v>
       </c>
       <c r="AG50">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>1.8</v>
       </c>
       <c r="O51">
-        <v>3.8</v>
+        <v>3.52</v>
       </c>
       <c r="P51">
         <v>3.5</v>
@@ -8676,10 +8676,10 @@
         <v>1.22</v>
       </c>
       <c r="AF51">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AG51">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>1.22</v>
       </c>
       <c r="AK51">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8839,7 +8839,7 @@
         <v>1.04</v>
       </c>
       <c r="AF52">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AG52">
         <v>1.83</v>
@@ -9111,65 +9111,65 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="O54">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="P54">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Q54">
-        <v>1.82</v>
+        <v>1.71</v>
       </c>
       <c r="R54">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="S54">
         <v>1.29</v>
       </c>
       <c r="T54">
-        <v>2.95</v>
+        <v>3.12</v>
       </c>
       <c r="U54">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="V54">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W54">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X54">
         <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z54">
-        <v>3.86</v>
+        <v>4.15</v>
       </c>
       <c r="AA54">
+        <v>1.65</v>
+      </c>
+      <c r="AB54">
+        <v>2.07</v>
+      </c>
+      <c r="AC54">
+        <v>2.52</v>
+      </c>
+      <c r="AD54">
+        <v>1.41</v>
+      </c>
+      <c r="AE54">
+        <v>1.13</v>
+      </c>
+      <c r="AF54">
+        <v>2.1</v>
+      </c>
+      <c r="AG54">
         <v>1.67</v>
       </c>
-      <c r="AB54">
-        <v>2.15</v>
-      </c>
-      <c r="AC54">
-        <v>2.62</v>
-      </c>
-      <c r="AD54">
-        <v>1.38</v>
-      </c>
-      <c r="AE54">
-        <v>1.11</v>
-      </c>
-      <c r="AF54">
-        <v>2.08</v>
-      </c>
-      <c r="AG54">
-        <v>1.65</v>
-      </c>
       <c r="AH54" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AK54">
-        <v>3.12</v>
+        <v>3.6</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9274,61 +9274,61 @@
         </is>
       </c>
       <c r="N55">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="O55">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="P55">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="Q55">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="R55">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S55">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T55">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="U55">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="V55">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W55">
+        <v>1.11</v>
+      </c>
+      <c r="X55">
+        <v>1.02</v>
+      </c>
+      <c r="Y55">
+        <v>1.2</v>
+      </c>
+      <c r="Z55">
+        <v>3.75</v>
+      </c>
+      <c r="AA55">
+        <v>1.76</v>
+      </c>
+      <c r="AB55">
+        <v>1.98</v>
+      </c>
+      <c r="AC55">
+        <v>2.83</v>
+      </c>
+      <c r="AD55">
+        <v>1.33</v>
+      </c>
+      <c r="AE55">
         <v>1.09</v>
       </c>
-      <c r="X55">
-        <v>1</v>
-      </c>
-      <c r="Y55">
-        <v>1.22</v>
-      </c>
-      <c r="Z55">
-        <v>3.5</v>
-      </c>
-      <c r="AA55">
-        <v>1.83</v>
-      </c>
-      <c r="AB55">
-        <v>1.9</v>
-      </c>
-      <c r="AC55">
-        <v>2.97</v>
-      </c>
-      <c r="AD55">
-        <v>1.3</v>
-      </c>
-      <c r="AE55">
-        <v>1.07</v>
-      </c>
       <c r="AF55">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG55">
         <v>1.67</v>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK55">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9600,16 +9600,16 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="O57">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="P57">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="Q57">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="R57">
         <v>2.06</v>
@@ -9639,10 +9639,10 @@
         <v>3.05</v>
       </c>
       <c r="AA57">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AB57">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC57">
         <v>3.34</v>
@@ -9654,10 +9654,10 @@
         <v>1.05</v>
       </c>
       <c r="AF57">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AG57">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -10285,22 +10285,22 @@
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z61">
         <v>5.85</v>
       </c>
       <c r="AA61">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AB61">
         <v>2.86</v>
       </c>
       <c r="AC61">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AD61">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AE61">
         <v>1.28</v>
@@ -10415,7 +10415,7 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="O62">
         <v>4</v>
@@ -10430,49 +10430,49 @@
         <v>2.62</v>
       </c>
       <c r="S62">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="T62">
-        <v>3.94</v>
+        <v>4.1</v>
       </c>
       <c r="U62">
         <v>1.95</v>
       </c>
       <c r="V62">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="W62">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z62">
         <v>6.06</v>
       </c>
       <c r="AA62">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AB62">
-        <v>2.81</v>
+        <v>2.92</v>
       </c>
       <c r="AC62">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AD62">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AE62">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AF62">
         <v>1.36</v>
       </c>
       <c r="AG62">
-        <v>2.85</v>
+        <v>2.93</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK62">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,7 +10578,7 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="O63">
         <v>3.9</v>
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -12223,7 +12223,7 @@
         <v>2.63</v>
       </c>
       <c r="S73">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T73">
         <v>3.8</v>
@@ -12232,7 +12232,7 @@
         <v>2.24</v>
       </c>
       <c r="V73">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="W73">
         <v>1.14</v>
@@ -12253,7 +12253,7 @@
         <v>2.45</v>
       </c>
       <c r="AC73">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="AD73">
         <v>1.55</v>
@@ -12262,7 +12262,7 @@
         <v>1.17</v>
       </c>
       <c r="AF73">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AG73">
         <v>1.91</v>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AK73">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12872,7 +12872,7 @@
         <v>2.3</v>
       </c>
       <c r="R77">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="S77">
         <v>1.46</v>
@@ -12899,10 +12899,10 @@
         <v>2.74</v>
       </c>
       <c r="AA77">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AB77">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AC77">
         <v>3.9</v>
@@ -13032,16 +13032,16 @@
         <v>4.2</v>
       </c>
       <c r="Q78">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="R78">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="S78">
         <v>1.23</v>
       </c>
       <c r="T78">
-        <v>4</v>
+        <v>3.48</v>
       </c>
       <c r="U78">
         <v>2</v>
@@ -13068,19 +13068,19 @@
         <v>2.56</v>
       </c>
       <c r="AC78">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AD78">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AE78">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF78">
         <v>1.44</v>
       </c>
       <c r="AG78">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK78">
         <v>2.23</v>
@@ -13192,10 +13192,10 @@
         <v>3.9</v>
       </c>
       <c r="P79">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="Q79">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="R79">
         <v>2.42</v>
@@ -13204,13 +13204,13 @@
         <v>1.17</v>
       </c>
       <c r="T79">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="U79">
         <v>2</v>
       </c>
       <c r="V79">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="W79">
         <v>1.2</v>
@@ -13256,7 +13256,7 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK79">
         <v>2.04</v>
@@ -13406,7 +13406,7 @@
         <v>1.31</v>
       </c>
       <c r="AG80">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13515,7 +13515,7 @@
         <v>2.9</v>
       </c>
       <c r="O81">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P81">
         <v>1.95</v>
@@ -13524,7 +13524,7 @@
         <v>3.3</v>
       </c>
       <c r="R81">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="S81">
         <v>1.17</v>
@@ -13539,7 +13539,7 @@
         <v>1.88</v>
       </c>
       <c r="W81">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X81">
         <v>1.01</v>
@@ -13569,7 +13569,7 @@
         <v>1.3</v>
       </c>
       <c r="AG81">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13702,16 +13702,16 @@
         <v>1.65</v>
       </c>
       <c r="W82">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X82">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z82">
-        <v>5.3</v>
+        <v>5.45</v>
       </c>
       <c r="AA82">
         <v>1.47</v>
@@ -13720,19 +13720,19 @@
         <v>2.6</v>
       </c>
       <c r="AC82">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="AD82">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AE82">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AF82">
         <v>1.4</v>
       </c>
       <c r="AG82">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13841,16 +13841,16 @@
         <v>2.82</v>
       </c>
       <c r="O83">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="P83">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="Q83">
-        <v>2.94</v>
+        <v>3.26</v>
       </c>
       <c r="R83">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="S83">
         <v>1.2</v>
@@ -14001,19 +14001,19 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="O84">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P84">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="Q84">
         <v>2.09</v>
       </c>
       <c r="R84">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="S84">
         <v>1.22</v>
@@ -14022,22 +14022,22 @@
         <v>3.8</v>
       </c>
       <c r="U84">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="V84">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="W84">
         <v>1.14</v>
       </c>
       <c r="X84">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Z84">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AA84">
         <v>1.47</v>
@@ -14046,7 +14046,7 @@
         <v>2.46</v>
       </c>
       <c r="AC84">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AD84">
         <v>1.63</v>
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O85">
         <v>3.72</v>
       </c>
       <c r="P85">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="Q85">
         <v>3</v>
@@ -14400,7 +14400,7 @@
         <v>1.22</v>
       </c>
       <c r="AK86">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="O87">
         <v>3.6</v>
       </c>
       <c r="P87">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q87">
         <v>2.73</v>
@@ -14526,7 +14526,7 @@
         <v>1.1</v>
       </c>
       <c r="Z87">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AA87">
         <v>1.44</v>
@@ -14668,7 +14668,7 @@
         <v>2.1</v>
       </c>
       <c r="S88">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T88">
         <v>2.75</v>
@@ -14689,7 +14689,7 @@
         <v>1.26</v>
       </c>
       <c r="Z88">
-        <v>3.45</v>
+        <v>3.46</v>
       </c>
       <c r="AA88">
         <v>1.92</v>
@@ -14726,7 +14726,7 @@
         <v>1.31</v>
       </c>
       <c r="AK88">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -15471,7 +15471,7 @@
         <v>1.09</v>
       </c>
       <c r="O93">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P93">
         <v>19</v>
@@ -15480,7 +15480,7 @@
         <v>1.24</v>
       </c>
       <c r="R93">
-        <v>3.87</v>
+        <v>4.04</v>
       </c>
       <c r="S93">
         <v>1.09</v>
@@ -15489,13 +15489,13 @@
         <v>6.7</v>
       </c>
       <c r="U93">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="V93">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="W93">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="X93">
         <v>1</v>
@@ -15507,10 +15507,10 @@
         <v>16.5</v>
       </c>
       <c r="AA93">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AB93">
-        <v>5.65</v>
+        <v>5.8</v>
       </c>
       <c r="AC93">
         <v>1.36</v>
@@ -15522,10 +15522,10 @@
         <v>1.9</v>
       </c>
       <c r="AF93">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG93">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15637,7 +15637,7 @@
         <v>3.35</v>
       </c>
       <c r="P94">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q94">
         <v>3.36</v>
@@ -15649,7 +15649,7 @@
         <v>1.3</v>
       </c>
       <c r="T94">
-        <v>3.18</v>
+        <v>3.24</v>
       </c>
       <c r="U94">
         <v>2.4</v>
@@ -15661,25 +15661,25 @@
         <v>1.12</v>
       </c>
       <c r="X94">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y94">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z94">
-        <v>3.98</v>
+        <v>4.5</v>
       </c>
       <c r="AA94">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AB94">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AC94">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="AD94">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE94">
         <v>1.14</v>
@@ -15688,7 +15688,7 @@
         <v>1.53</v>
       </c>
       <c r="AG94">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="O99">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="P99">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="Q99">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="R99">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="S99">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T99">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="U99">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="V99">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="W99">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X99">
         <v>1.02</v>
       </c>
       <c r="Y99">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z99">
-        <v>4.85</v>
+        <v>4.75</v>
       </c>
       <c r="AA99">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AB99">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AC99">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AD99">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="AE99">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF99">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AG99">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK99">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,58 +16609,58 @@
         </is>
       </c>
       <c r="N100">
-        <v>2.1</v>
+        <v>1.37</v>
       </c>
       <c r="O100">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="P100">
-        <v>3.1</v>
+        <v>5.8</v>
       </c>
       <c r="Q100">
-        <v>2.78</v>
+        <v>1.85</v>
       </c>
       <c r="R100">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="S100">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="T100">
-        <v>2.84</v>
+        <v>3.72</v>
       </c>
       <c r="U100">
-        <v>2.58</v>
+        <v>2.22</v>
       </c>
       <c r="V100">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="W100">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X100">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y100">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="Z100">
-        <v>3.34</v>
+        <v>4.85</v>
       </c>
       <c r="AA100">
-        <v>1.87</v>
+        <v>1.53</v>
       </c>
       <c r="AB100">
-        <v>1.9</v>
+        <v>2.45</v>
       </c>
       <c r="AC100">
-        <v>3.04</v>
+        <v>2.33</v>
       </c>
       <c r="AD100">
-        <v>1.29</v>
+        <v>1.51</v>
       </c>
       <c r="AE100">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="AF100">
         <v>1.67</v>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AK100">
-        <v>1.62</v>
+        <v>2.58</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>1.47</v>
+        <v>2.1</v>
       </c>
       <c r="O101">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="P101">
-        <v>5.4</v>
+        <v>3.1</v>
       </c>
       <c r="Q101">
-        <v>1.98</v>
+        <v>2.78</v>
       </c>
       <c r="R101">
-        <v>2.69</v>
+        <v>2.05</v>
       </c>
       <c r="S101">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="T101">
-        <v>3.75</v>
+        <v>2.84</v>
       </c>
       <c r="U101">
-        <v>2.1</v>
+        <v>2.58</v>
       </c>
       <c r="V101">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="W101">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="X101">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y101">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="Z101">
-        <v>4.75</v>
+        <v>3.34</v>
       </c>
       <c r="AA101">
-        <v>1.46</v>
+        <v>1.87</v>
       </c>
       <c r="AB101">
-        <v>2.55</v>
+        <v>1.9</v>
       </c>
       <c r="AC101">
-        <v>2.15</v>
+        <v>3.04</v>
       </c>
       <c r="AD101">
-        <v>1.6</v>
+        <v>1.29</v>
       </c>
       <c r="AE101">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="AF101">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AG101">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AK101">
-        <v>2.5</v>
+        <v>1.62</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -17116,7 +17116,7 @@
         <v>1.36</v>
       </c>
       <c r="T103">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="U103">
         <v>2.51</v>
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="O106">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="P106">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q106">
-        <v>2.67</v>
+        <v>2.56</v>
       </c>
       <c r="R106">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="S106">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T106">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="U106">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="V106">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W106">
         <v>1.03</v>
       </c>
       <c r="X106">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y106">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="Z106">
-        <v>2.49</v>
+        <v>2.62</v>
       </c>
       <c r="AA106">
-        <v>2.31</v>
+        <v>2.22</v>
       </c>
       <c r="AB106">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="AC106">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AD106">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE106">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF106">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AG106">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK106">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O111">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P111">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q111">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R111">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="S111">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T111">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="U111">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="V111">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W111">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X111">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y111">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z111">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AA111">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AB111">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC111">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD111">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE111">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF111">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG111">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK111">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -19555,7 +19555,7 @@
         <v>2.63</v>
       </c>
       <c r="R118">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="S118">
         <v>1.3</v>
@@ -19582,7 +19582,7 @@
         <v>3.58</v>
       </c>
       <c r="AA118">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AB118">
         <v>1.96</v>
@@ -19600,7 +19600,7 @@
         <v>1.6</v>
       </c>
       <c r="AG118">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -653,13 +653,13 @@
         <v>1.4</v>
       </c>
       <c r="T2">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U2">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="V2">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W2">
         <v>1.06</v>
@@ -671,10 +671,10 @@
         <v>1.34</v>
       </c>
       <c r="Z2">
-        <v>2.89</v>
+        <v>2.78</v>
       </c>
       <c r="AA2">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AB2">
         <v>1.65</v>
@@ -683,7 +683,7 @@
         <v>4.05</v>
       </c>
       <c r="AD2">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AE2">
         <v>1.01</v>
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="O4">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P4">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="Q4">
-        <v>4.2</v>
+        <v>4.53</v>
       </c>
       <c r="R4">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="S4">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T4">
-        <v>2.81</v>
+        <v>3.2</v>
       </c>
       <c r="U4">
-        <v>2.71</v>
+        <v>2.63</v>
       </c>
       <c r="V4">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W4">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X4">
         <v>1.04</v>
       </c>
       <c r="Y4">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Z4">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AA4">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AB4">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AC4">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AD4">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE4">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF4">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG4">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.74</v>
+        <v>1.22</v>
       </c>
       <c r="AK4">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.99</v>
+        <v>1.89</v>
       </c>
       <c r="O5">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P5">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="Q5">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="R5">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="S5">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T5">
         <v>2.88</v>
       </c>
       <c r="U5">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="V5">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="W5">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X5">
         <v>1.01</v>
       </c>
       <c r="Y5">
+        <v>1.27</v>
+      </c>
+      <c r="Z5">
+        <v>3.14</v>
+      </c>
+      <c r="AA5">
+        <v>1.99</v>
+      </c>
+      <c r="AB5">
+        <v>1.75</v>
+      </c>
+      <c r="AC5">
+        <v>3.2</v>
+      </c>
+      <c r="AD5">
         <v>1.26</v>
-      </c>
-      <c r="Z5">
-        <v>3.2</v>
-      </c>
-      <c r="AA5">
-        <v>1.89</v>
-      </c>
-      <c r="AB5">
-        <v>1.78</v>
-      </c>
-      <c r="AC5">
-        <v>3.14</v>
-      </c>
-      <c r="AD5">
-        <v>1.27</v>
       </c>
       <c r="AE5">
         <v>1.06</v>
       </c>
       <c r="AF5">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG5">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AK5">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1332,10 +1332,10 @@
         <v>1.95</v>
       </c>
       <c r="AC6">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AD6">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AE6">
         <v>1.08</v>
@@ -1450,34 +1450,34 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="O7">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P7">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="Q7">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="R7">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="S7">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T7">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="U7">
-        <v>2.65</v>
+        <v>2.86</v>
       </c>
       <c r="V7">
         <v>1.38</v>
       </c>
       <c r="W7">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X7">
         <v>1.02</v>
@@ -1489,10 +1489,10 @@
         <v>3.08</v>
       </c>
       <c r="AA7">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AB7">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC7">
         <v>3.2</v>
@@ -1504,10 +1504,10 @@
         <v>1.06</v>
       </c>
       <c r="AF7">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AG7">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK7">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="O12">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P12">
         <v>3</v>
@@ -2277,10 +2277,10 @@
         <v>2.8</v>
       </c>
       <c r="R12">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="S12">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T12">
         <v>3</v>
@@ -2304,7 +2304,7 @@
         <v>3.34</v>
       </c>
       <c r="AA12">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AB12">
         <v>1.9</v>
@@ -2313,7 +2313,7 @@
         <v>3.14</v>
       </c>
       <c r="AD12">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AE12">
         <v>1.06</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK12">
         <v>1.57</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="O13">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
       <c r="P13">
-        <v>3.08</v>
+        <v>3.03</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2612,7 +2612,7 @@
         <v>3.25</v>
       </c>
       <c r="U14">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="V14">
         <v>1.46</v>
@@ -3080,25 +3080,25 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="O17">
         <v>3.15</v>
       </c>
       <c r="P17">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q17">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="R17">
         <v>2.06</v>
       </c>
       <c r="S17">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T17">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="U17">
         <v>3.02</v>
@@ -3125,10 +3125,10 @@
         <v>1.63</v>
       </c>
       <c r="AC17">
-        <v>4.22</v>
+        <v>4.26</v>
       </c>
       <c r="AD17">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE17">
         <v>1.02</v>
@@ -3153,7 +3153,7 @@
         <v>1.34</v>
       </c>
       <c r="AK17">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3252,7 +3252,7 @@
         <v>2.4</v>
       </c>
       <c r="Q18">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="R18">
         <v>1.94</v>
@@ -3276,7 +3276,7 @@
         <v>1.03</v>
       </c>
       <c r="Y18">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z18">
         <v>2.88</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="O19">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="P19">
-        <v>7.5</v>
+        <v>6.2</v>
       </c>
       <c r="Q19">
         <v>1.85</v>
@@ -3424,10 +3424,10 @@
         <v>1.33</v>
       </c>
       <c r="T19">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="U19">
-        <v>2.68</v>
+        <v>2.48</v>
       </c>
       <c r="V19">
         <v>1.44</v>
@@ -3439,22 +3439,22 @@
         <v>1</v>
       </c>
       <c r="Y19">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z19">
-        <v>3.78</v>
+        <v>3.81</v>
       </c>
       <c r="AA19">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AB19">
         <v>2</v>
       </c>
       <c r="AC19">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AD19">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE19">
         <v>1.09</v>
@@ -3479,7 +3479,7 @@
         <v>1.18</v>
       </c>
       <c r="AK19">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -4061,10 +4061,10 @@
         <v>2.18</v>
       </c>
       <c r="O23">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="P23">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="Q23">
         <v>2.76</v>
@@ -4079,7 +4079,7 @@
         <v>2.57</v>
       </c>
       <c r="U23">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="V23">
         <v>1.33</v>
@@ -4112,10 +4112,10 @@
         <v>1.04</v>
       </c>
       <c r="AF23">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG23">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>1.91</v>
       </c>
       <c r="O31">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P31">
         <v>3.45</v>
@@ -5374,7 +5374,7 @@
         <v>2.55</v>
       </c>
       <c r="R31">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="S31">
         <v>1.44</v>
@@ -5419,7 +5419,7 @@
         <v>1.97</v>
       </c>
       <c r="AG31">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AK31">
         <v>1.8</v>
@@ -5851,31 +5851,31 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="O34">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="P34">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="Q34">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="R34">
         <v>2.3</v>
       </c>
       <c r="S34">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T34">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U34">
         <v>2.4</v>
       </c>
       <c r="V34">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="W34">
         <v>1.11</v>
@@ -5884,25 +5884,25 @@
         <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z34">
-        <v>4.38</v>
+        <v>4.72</v>
       </c>
       <c r="AA34">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="AB34">
-        <v>2.14</v>
+        <v>2.27</v>
       </c>
       <c r="AC34">
-        <v>2.56</v>
+        <v>2.43</v>
       </c>
       <c r="AD34">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE34">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF34">
         <v>1.57</v>
@@ -6023,46 +6023,46 @@
         <v>3.1</v>
       </c>
       <c r="Q35">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="R35">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S35">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T35">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U35">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="V35">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W35">
         <v>1.14</v>
       </c>
       <c r="X35">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z35">
-        <v>4.65</v>
+        <v>4.55</v>
       </c>
       <c r="AA35">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AB35">
         <v>2.45</v>
       </c>
       <c r="AC35">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AD35">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AE35">
         <v>1.17</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK35">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6847,7 +6847,7 @@
         <v>1.25</v>
       </c>
       <c r="T40">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U40">
         <v>2.34</v>
@@ -6877,16 +6877,16 @@
         <v>2.43</v>
       </c>
       <c r="AD40">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AE40">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF40">
         <v>1.55</v>
       </c>
       <c r="AG40">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6992,16 +6992,16 @@
         </is>
       </c>
       <c r="N41">
+        <v>3.7</v>
+      </c>
+      <c r="O41">
         <v>3.6</v>
       </c>
-      <c r="O41">
-        <v>3.7</v>
-      </c>
       <c r="P41">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Q41">
-        <v>4.22</v>
+        <v>4.15</v>
       </c>
       <c r="R41">
         <v>2.47</v>
@@ -7031,19 +7031,19 @@
         <v>4.6</v>
       </c>
       <c r="AA41">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AB41">
         <v>2.33</v>
       </c>
       <c r="AC41">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AD41">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AE41">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AF41">
         <v>1.55</v>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.94</v>
+        <v>1.2</v>
       </c>
       <c r="AK41">
         <v>1.2</v>
@@ -7188,7 +7188,7 @@
         <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z42">
         <v>4.2</v>
@@ -7200,10 +7200,10 @@
         <v>2.15</v>
       </c>
       <c r="AC42">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="AD42">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE42">
         <v>1.12</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,22 +7318,22 @@
         </is>
       </c>
       <c r="N43">
+        <v>1.59</v>
+      </c>
+      <c r="O43">
+        <v>4</v>
+      </c>
+      <c r="P43">
+        <v>4.48</v>
+      </c>
+      <c r="Q43">
+        <v>1.93</v>
+      </c>
+      <c r="R43">
         <v>2.45</v>
       </c>
-      <c r="O43">
-        <v>3.85</v>
-      </c>
-      <c r="P43">
-        <v>2.18</v>
-      </c>
-      <c r="Q43">
-        <v>3.32</v>
-      </c>
-      <c r="R43">
-        <v>2.33</v>
-      </c>
       <c r="S43">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T43">
         <v>4</v>
@@ -7342,40 +7342,40 @@
         <v>2.04</v>
       </c>
       <c r="V43">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="W43">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X43">
         <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z43">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="AA43">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AB43">
         <v>2.88</v>
       </c>
       <c r="AC43">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="AD43">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AE43">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AF43">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AG43">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.58</v>
+        <v>1.13</v>
       </c>
       <c r="AK43">
-        <v>1.4</v>
+        <v>2.38</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.62</v>
+        <v>2.45</v>
       </c>
       <c r="O44">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="P44">
-        <v>4.7</v>
+        <v>2.18</v>
       </c>
       <c r="Q44">
-        <v>2.04</v>
+        <v>3.38</v>
       </c>
       <c r="R44">
-        <v>2.47</v>
+        <v>2.33</v>
       </c>
       <c r="S44">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T44">
         <v>4</v>
       </c>
       <c r="U44">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V44">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="W44">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X44">
         <v>1.02</v>
       </c>
       <c r="Y44">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z44">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AA44">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AB44">
         <v>2.88</v>
       </c>
       <c r="AC44">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AD44">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AE44">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF44">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AG44">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.14</v>
+        <v>1.6</v>
       </c>
       <c r="AK44">
-        <v>2.38</v>
+        <v>1.39</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7647,7 +7647,7 @@
         <v>2.37</v>
       </c>
       <c r="O45">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="P45">
         <v>2.95</v>
@@ -7674,7 +7674,7 @@
         <v>1.05</v>
       </c>
       <c r="X45">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y45">
         <v>1.33</v>
@@ -7695,10 +7695,10 @@
         <v>1.22</v>
       </c>
       <c r="AE45">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF45">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG45">
         <v>1.95</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AK45">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="O47">
         <v>3.75</v>
       </c>
       <c r="P47">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q47">
         <v>2.5</v>
@@ -8015,7 +8015,7 @@
         <v>2.02</v>
       </c>
       <c r="AC47">
-        <v>1.96</v>
+        <v>2.32</v>
       </c>
       <c r="AD47">
         <v>1.55</v>
@@ -8027,7 +8027,7 @@
         <v>1.44</v>
       </c>
       <c r="AG47">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="O48">
-        <v>4.05</v>
+        <v>4.3</v>
       </c>
       <c r="P48">
-        <v>5.05</v>
+        <v>4.45</v>
       </c>
       <c r="Q48">
         <v>2</v>
@@ -8305,7 +8305,7 @@
         <v>5.8</v>
       </c>
       <c r="Q49">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="R49">
         <v>2.5</v>
@@ -9437,10 +9437,10 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="O56">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P56">
         <v>2.9</v>
@@ -9763,34 +9763,34 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="O58">
-        <v>5.05</v>
+        <v>5.2</v>
       </c>
       <c r="P58">
-        <v>7.08</v>
+        <v>7.28</v>
       </c>
       <c r="Q58">
         <v>1.84</v>
       </c>
       <c r="R58">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="S58">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="T58">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="U58">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="V58">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="W58">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X58">
         <v>1.01</v>
@@ -9799,22 +9799,22 @@
         <v>1.08</v>
       </c>
       <c r="Z58">
-        <v>5.55</v>
+        <v>5.7</v>
       </c>
       <c r="AA58">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AB58">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AC58">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AD58">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AE58">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AF58">
         <v>1.61</v>
@@ -9836,7 +9836,7 @@
         <v>1.15</v>
       </c>
       <c r="AK58">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9926,37 +9926,37 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="O59">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="P59">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="Q59">
         <v>1.55</v>
       </c>
       <c r="R59">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="S59">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T59">
         <v>3.58</v>
       </c>
       <c r="U59">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="V59">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="W59">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X59">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y59">
         <v>1.1</v>
@@ -9965,10 +9965,10 @@
         <v>6.5</v>
       </c>
       <c r="AA59">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AB59">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AC59">
         <v>2.12</v>
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="O60">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="P60">
-        <v>1.96</v>
+        <v>1.72</v>
       </c>
       <c r="Q60">
-        <v>3.98</v>
+        <v>4.2</v>
       </c>
       <c r="R60">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S60">
         <v>1.25</v>
       </c>
       <c r="T60">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="U60">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V60">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W60">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X60">
         <v>1.01</v>
       </c>
       <c r="Y60">
+        <v>1.16</v>
+      </c>
+      <c r="Z60">
+        <v>4.5</v>
+      </c>
+      <c r="AA60">
+        <v>1.61</v>
+      </c>
+      <c r="AB60">
+        <v>2.25</v>
+      </c>
+      <c r="AC60">
+        <v>2.51</v>
+      </c>
+      <c r="AD60">
+        <v>1.48</v>
+      </c>
+      <c r="AE60">
         <v>1.15</v>
       </c>
-      <c r="Z60">
-        <v>4.3</v>
-      </c>
-      <c r="AA60">
-        <v>1.56</v>
-      </c>
-      <c r="AB60">
-        <v>2.38</v>
-      </c>
-      <c r="AC60">
-        <v>2.38</v>
-      </c>
-      <c r="AD60">
-        <v>1.46</v>
-      </c>
-      <c r="AE60">
-        <v>1.16</v>
-      </c>
       <c r="AF60">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG60">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.77</v>
+        <v>1.17</v>
       </c>
       <c r="AK60">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10744,10 +10744,10 @@
         <v>1.93</v>
       </c>
       <c r="O64">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P64">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="Q64">
         <v>2.5</v>
@@ -10792,13 +10792,13 @@
         <v>1.23</v>
       </c>
       <c r="AE64">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF64">
         <v>1.8</v>
       </c>
       <c r="AG64">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -11100,22 +11100,22 @@
         <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z66">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="AA66">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AB66">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC66">
         <v>2.97</v>
       </c>
       <c r="AD66">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE66">
         <v>1.08</v>
@@ -11140,7 +11140,7 @@
         <v>1.31</v>
       </c>
       <c r="AK66">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="O67">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="P67">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="Q67">
-        <v>2.38</v>
+        <v>2.92</v>
       </c>
       <c r="R67">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="S67">
+        <v>1.45</v>
+      </c>
+      <c r="T67">
+        <v>2.5</v>
+      </c>
+      <c r="U67">
+        <v>2.86</v>
+      </c>
+      <c r="V67">
+        <v>1.35</v>
+      </c>
+      <c r="W67">
+        <v>1.05</v>
+      </c>
+      <c r="X67">
+        <v>1.04</v>
+      </c>
+      <c r="Y67">
         <v>1.29</v>
       </c>
-      <c r="T67">
-        <v>3.3</v>
-      </c>
-      <c r="U67">
-        <v>2.71</v>
-      </c>
-      <c r="V67">
-        <v>1.44</v>
-      </c>
-      <c r="W67">
-        <v>1.06</v>
-      </c>
-      <c r="X67">
-        <v>1.02</v>
-      </c>
-      <c r="Y67">
-        <v>1.17</v>
-      </c>
       <c r="Z67">
-        <v>3.84</v>
+        <v>3.04</v>
       </c>
       <c r="AA67">
-        <v>1.75</v>
+        <v>2.16</v>
       </c>
       <c r="AB67">
-        <v>2.01</v>
+        <v>1.66</v>
       </c>
       <c r="AC67">
-        <v>3.08</v>
+        <v>3.42</v>
       </c>
       <c r="AD67">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="AE67">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AF67">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AG67">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK67">
-        <v>1.97</v>
+        <v>1.57</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="O68">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="P68">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="Q68">
-        <v>2.92</v>
+        <v>2.39</v>
       </c>
       <c r="R68">
+        <v>2.2</v>
+      </c>
+      <c r="S68">
+        <v>1.29</v>
+      </c>
+      <c r="T68">
+        <v>3.08</v>
+      </c>
+      <c r="U68">
+        <v>2.71</v>
+      </c>
+      <c r="V68">
+        <v>1.44</v>
+      </c>
+      <c r="W68">
+        <v>1.06</v>
+      </c>
+      <c r="X68">
+        <v>1.02</v>
+      </c>
+      <c r="Y68">
+        <v>1.17</v>
+      </c>
+      <c r="Z68">
+        <v>3.83</v>
+      </c>
+      <c r="AA68">
+        <v>1.75</v>
+      </c>
+      <c r="AB68">
         <v>2</v>
       </c>
-      <c r="S68">
-        <v>1.45</v>
-      </c>
-      <c r="T68">
-        <v>2.5</v>
-      </c>
-      <c r="U68">
-        <v>2.86</v>
-      </c>
-      <c r="V68">
-        <v>1.35</v>
-      </c>
-      <c r="W68">
-        <v>1.05</v>
-      </c>
-      <c r="X68">
-        <v>1.04</v>
-      </c>
-      <c r="Y68">
-        <v>1.29</v>
-      </c>
-      <c r="Z68">
-        <v>3.04</v>
-      </c>
-      <c r="AA68">
-        <v>2.16</v>
-      </c>
-      <c r="AB68">
-        <v>1.67</v>
-      </c>
       <c r="AC68">
-        <v>3.42</v>
+        <v>3.09</v>
       </c>
       <c r="AD68">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AE68">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF68">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AG68">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK68">
-        <v>1.57</v>
+        <v>1.97</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11568,7 +11568,7 @@
         <v>2.75</v>
       </c>
       <c r="R69">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="S69">
         <v>1.3</v>
@@ -11610,7 +11610,7 @@
         <v>1.15</v>
       </c>
       <c r="AF69">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AG69">
         <v>2.2</v>
@@ -12057,7 +12057,7 @@
         <v>3.75</v>
       </c>
       <c r="R72">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="S72">
         <v>1.31</v>
@@ -12543,10 +12543,10 @@
         <v>0</v>
       </c>
       <c r="Q75">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R75">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="S75">
         <v>1.28</v>
@@ -12579,16 +12579,16 @@
         <v>2.13</v>
       </c>
       <c r="AC75">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="AD75">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AE75">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF75">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AG75">
         <v>2.25</v>
@@ -12607,7 +12607,7 @@
         <v>1.2</v>
       </c>
       <c r="AK75">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12715,7 +12715,7 @@
         <v>1.29</v>
       </c>
       <c r="T76">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U76">
         <v>2.32</v>
@@ -14997,13 +14997,13 @@
         <v>1.22</v>
       </c>
       <c r="T90">
-        <v>3.56</v>
+        <v>3.48</v>
       </c>
       <c r="U90">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V90">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W90">
         <v>1.14</v>
@@ -15015,10 +15015,10 @@
         <v>1.1</v>
       </c>
       <c r="Z90">
-        <v>5.29</v>
+        <v>5.5</v>
       </c>
       <c r="AA90">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="AB90">
         <v>2.38</v>
@@ -15027,7 +15027,7 @@
         <v>2.23</v>
       </c>
       <c r="AD90">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AE90">
         <v>1.23</v>
@@ -15036,7 +15036,7 @@
         <v>1.55</v>
       </c>
       <c r="AG90">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK90">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15148,13 +15148,13 @@
         <v>3.45</v>
       </c>
       <c r="P91">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
       </c>
       <c r="R91">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="S91">
         <v>1.31</v>
@@ -15178,13 +15178,13 @@
         <v>1.22</v>
       </c>
       <c r="Z91">
-        <v>3.93</v>
+        <v>3.9</v>
       </c>
       <c r="AA91">
         <v>1.82</v>
       </c>
       <c r="AB91">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AC91">
         <v>2.9</v>
@@ -15215,7 +15215,7 @@
         <v>1.27</v>
       </c>
       <c r="AK91">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15344,7 +15344,7 @@
         <v>4.5</v>
       </c>
       <c r="AA92">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AB92">
         <v>2.26</v>
@@ -15794,22 +15794,22 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="O95">
-        <v>3.65</v>
+        <v>3.42</v>
       </c>
       <c r="P95">
-        <v>3.15</v>
+        <v>3.06</v>
       </c>
       <c r="Q95">
         <v>2.55</v>
       </c>
       <c r="R95">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="S95">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T95">
         <v>3.8</v>
@@ -15821,7 +15821,7 @@
         <v>1.62</v>
       </c>
       <c r="W95">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="X95">
         <v>1.02</v>
@@ -15833,10 +15833,10 @@
         <v>4.6</v>
       </c>
       <c r="AA95">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="AB95">
-        <v>2.35</v>
+        <v>2.49</v>
       </c>
       <c r="AC95">
         <v>2.38</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>3.8</v>
+        <v>1.47</v>
       </c>
       <c r="O98">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="P98">
-        <v>1.78</v>
+        <v>5.4</v>
       </c>
       <c r="Q98">
-        <v>4.2</v>
+        <v>1.98</v>
       </c>
       <c r="R98">
-        <v>2.33</v>
+        <v>2.69</v>
       </c>
       <c r="S98">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="T98">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="U98">
-        <v>2.54</v>
+        <v>2.1</v>
       </c>
       <c r="V98">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="W98">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="X98">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y98">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z98">
-        <v>3.77</v>
+        <v>4.75</v>
       </c>
       <c r="AA98">
-        <v>1.75</v>
+        <v>1.46</v>
       </c>
       <c r="AB98">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="AC98">
-        <v>2.83</v>
+        <v>2.15</v>
       </c>
       <c r="AD98">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AE98">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AF98">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AG98">
-        <v>2.06</v>
+        <v>2.17</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AK98">
-        <v>1.17</v>
+        <v>2.5</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="O99">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="P99">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="Q99">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="R99">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="S99">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T99">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="U99">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="V99">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="W99">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X99">
         <v>1.02</v>
       </c>
       <c r="Y99">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z99">
-        <v>4.75</v>
+        <v>4.85</v>
       </c>
       <c r="AA99">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AB99">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AC99">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="AD99">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="AE99">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AF99">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AG99">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AK99">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.37</v>
+        <v>3.8</v>
       </c>
       <c r="O100">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="P100">
-        <v>5.8</v>
+        <v>1.78</v>
       </c>
       <c r="Q100">
-        <v>1.85</v>
+        <v>4.2</v>
       </c>
       <c r="R100">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="S100">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="T100">
-        <v>3.72</v>
+        <v>3.2</v>
       </c>
       <c r="U100">
-        <v>2.22</v>
+        <v>2.54</v>
       </c>
       <c r="V100">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="W100">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X100">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y100">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="Z100">
-        <v>4.85</v>
+        <v>3.77</v>
       </c>
       <c r="AA100">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AB100">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="AC100">
-        <v>2.33</v>
+        <v>2.83</v>
       </c>
       <c r="AD100">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="AE100">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="AF100">
         <v>1.67</v>
       </c>
       <c r="AG100">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AK100">
-        <v>2.58</v>
+        <v>1.17</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -17424,16 +17424,16 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.71</v>
+        <v>2.56</v>
       </c>
       <c r="O105">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="P105">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="Q105">
-        <v>3.07</v>
+        <v>2.97</v>
       </c>
       <c r="R105">
         <v>2.37</v>
@@ -17445,7 +17445,7 @@
         <v>3.94</v>
       </c>
       <c r="U105">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="V105">
         <v>1.69</v>
@@ -17472,10 +17472,10 @@
         <v>2.08</v>
       </c>
       <c r="AD105">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AE105">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AF105">
         <v>1.39</v>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AK105">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="O109">
         <v>3.6</v>
@@ -18085,19 +18085,19 @@
         <v>4.2</v>
       </c>
       <c r="Q109">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="R109">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="S109">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T109">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="U109">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="V109">
         <v>1.44</v>
@@ -18109,16 +18109,16 @@
         <v>1.01</v>
       </c>
       <c r="Y109">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z109">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AA109">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="AB109">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="AC109">
         <v>3.1</v>
@@ -18146,7 +18146,7 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK109">
         <v>1.91</v>
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="O110">
         <v>3.6</v>
       </c>
       <c r="P110">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="Q110">
         <v>2.42</v>
@@ -18275,13 +18275,13 @@
         <v>1.26</v>
       </c>
       <c r="Z110">
-        <v>3.82</v>
+        <v>3.5</v>
       </c>
       <c r="AA110">
         <v>1.78</v>
       </c>
       <c r="AB110">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AC110">
         <v>2.88</v>
@@ -18580,10 +18580,10 @@
         <v>2.25</v>
       </c>
       <c r="S112">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T112">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="U112">
         <v>2.75</v>
@@ -18619,10 +18619,10 @@
         <v>1.07</v>
       </c>
       <c r="AF112">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AG112">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18728,10 +18728,10 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="O113">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P113">
         <v>4.5</v>
@@ -18743,10 +18743,10 @@
         <v>2.39</v>
       </c>
       <c r="S113">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T113">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U113">
         <v>2.02</v>
@@ -18782,10 +18782,10 @@
         <v>1.25</v>
       </c>
       <c r="AF113">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG113">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,7 +18798,7 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK113">
         <v>2.2</v>
@@ -19072,7 +19072,7 @@
         <v>1.4</v>
       </c>
       <c r="T115">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="U115">
         <v>2.9</v>
@@ -19229,7 +19229,7 @@
         <v>3</v>
       </c>
       <c r="R116">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="S116">
         <v>1.44</v>
@@ -19238,7 +19238,7 @@
         <v>2.53</v>
       </c>
       <c r="U116">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="V116">
         <v>1.33</v>
@@ -19259,7 +19259,7 @@
         <v>2.08</v>
       </c>
       <c r="AB116">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AC116">
         <v>3.5</v>
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="O117">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="P117">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="Q117">
         <v>0</v>
@@ -19419,10 +19419,10 @@
         <v>0</v>
       </c>
       <c r="AA117">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB117">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC117">
         <v>0</v>

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -819,16 +819,16 @@
         <v>3.25</v>
       </c>
       <c r="U3">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="V3">
         <v>1.44</v>
       </c>
       <c r="W3">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X3">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y3">
         <v>1.23</v>
@@ -855,7 +855,7 @@
         <v>1.67</v>
       </c>
       <c r="AG3">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1776,19 +1776,19 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="O9">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P9">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q9">
         <v>2.3</v>
       </c>
       <c r="R9">
-        <v>2.51</v>
+        <v>2.57</v>
       </c>
       <c r="S9">
         <v>1.2</v>
@@ -1797,10 +1797,10 @@
         <v>4</v>
       </c>
       <c r="U9">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="V9">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="W9">
         <v>1.2</v>
@@ -1809,31 +1809,31 @@
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z9">
         <v>6.5</v>
       </c>
       <c r="AA9">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AB9">
-        <v>2.98</v>
+        <v>3.3</v>
       </c>
       <c r="AC9">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="AD9">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AE9">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF9">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AG9">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -2105,13 +2105,13 @@
         <v>2.15</v>
       </c>
       <c r="O11">
-        <v>3.06</v>
+        <v>3.2</v>
       </c>
       <c r="P11">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q11">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="R11">
         <v>1.98</v>
@@ -2175,7 +2175,7 @@
         <v>1.26</v>
       </c>
       <c r="AK11">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2754,16 +2754,16 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="O15">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P15">
         <v>4.15</v>
       </c>
       <c r="Q15">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="R15">
         <v>2.05</v>
@@ -2799,7 +2799,7 @@
         <v>1.74</v>
       </c>
       <c r="AC15">
-        <v>3.47</v>
+        <v>3.44</v>
       </c>
       <c r="AD15">
         <v>1.25</v>
@@ -2811,7 +2811,7 @@
         <v>1.83</v>
       </c>
       <c r="AG15">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         <v>1.22</v>
       </c>
       <c r="Z46">
-        <v>3.67</v>
+        <v>3.48</v>
       </c>
       <c r="AA46">
         <v>1.9</v>
@@ -7855,7 +7855,7 @@
         <v>2.97</v>
       </c>
       <c r="AD46">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE46">
         <v>1.07</v>
@@ -8468,7 +8468,7 @@
         <v>2.25</v>
       </c>
       <c r="Q50">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="R50">
         <v>1.83</v>
@@ -8498,7 +8498,7 @@
         <v>2.97</v>
       </c>
       <c r="AA50">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="AB50">
         <v>1.75</v>
@@ -8532,7 +8532,7 @@
         <v>1.57</v>
       </c>
       <c r="AK50">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.35</v>
+        <v>1.89</v>
       </c>
       <c r="O61">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="P61">
-        <v>2.4</v>
+        <v>3.35</v>
       </c>
       <c r="Q61">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="R61">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="S61">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="T61">
-        <v>4.25</v>
+        <v>4.1</v>
       </c>
       <c r="U61">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V61">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W61">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X61">
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Z61">
-        <v>5.85</v>
+        <v>6.06</v>
       </c>
       <c r="AA61">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AB61">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="AC61">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AD61">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AE61">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AF61">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AG61">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK61">
-        <v>1.45</v>
+        <v>1.81</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.89</v>
+        <v>2.35</v>
       </c>
       <c r="O62">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="P62">
-        <v>3.35</v>
+        <v>2.4</v>
       </c>
       <c r="Q62">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="R62">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="S62">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="T62">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="U62">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V62">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="W62">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z62">
-        <v>6.06</v>
+        <v>5.85</v>
       </c>
       <c r="AA62">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AB62">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="AC62">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AD62">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AE62">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AF62">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AG62">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK62">
-        <v>1.81</v>
+        <v>1.45</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="O66">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="P66">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q66">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="R66">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S66">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="T66">
-        <v>2.92</v>
+        <v>2.5</v>
       </c>
       <c r="U66">
         <v>2.86</v>
       </c>
       <c r="V66">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W66">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X66">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y66">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="Z66">
-        <v>3.48</v>
+        <v>3.04</v>
       </c>
       <c r="AA66">
-        <v>1.83</v>
+        <v>2.16</v>
       </c>
       <c r="AB66">
-        <v>1.91</v>
+        <v>1.66</v>
       </c>
       <c r="AC66">
-        <v>2.97</v>
+        <v>3.42</v>
       </c>
       <c r="AD66">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AE66">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF66">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG66">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AK66">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,28 +11230,28 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O67">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="P67">
-        <v>3.25</v>
+        <v>2.65</v>
       </c>
       <c r="Q67">
-        <v>2.92</v>
+        <v>2.75</v>
       </c>
       <c r="R67">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="S67">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="T67">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="U67">
-        <v>2.86</v>
+        <v>3.2</v>
       </c>
       <c r="V67">
         <v>1.35</v>
@@ -11260,34 +11260,34 @@
         <v>1.05</v>
       </c>
       <c r="X67">
+        <v>1.02</v>
+      </c>
+      <c r="Y67">
+        <v>1.31</v>
+      </c>
+      <c r="Z67">
+        <v>3.03</v>
+      </c>
+      <c r="AA67">
+        <v>2.06</v>
+      </c>
+      <c r="AB67">
+        <v>1.67</v>
+      </c>
+      <c r="AC67">
+        <v>3.99</v>
+      </c>
+      <c r="AD67">
+        <v>1.22</v>
+      </c>
+      <c r="AE67">
         <v>1.04</v>
       </c>
-      <c r="Y67">
-        <v>1.29</v>
-      </c>
-      <c r="Z67">
-        <v>3.04</v>
-      </c>
-      <c r="AA67">
-        <v>2.16</v>
-      </c>
-      <c r="AB67">
-        <v>1.66</v>
-      </c>
-      <c r="AC67">
-        <v>3.42</v>
-      </c>
-      <c r="AD67">
-        <v>1.23</v>
-      </c>
-      <c r="AE67">
-        <v>1.05</v>
-      </c>
       <c r="AF67">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AG67">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>1.29</v>
       </c>
       <c r="AK67">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
+        <v>1.96</v>
+      </c>
+      <c r="O68">
+        <v>3.2</v>
+      </c>
+      <c r="P68">
+        <v>3.2</v>
+      </c>
+      <c r="Q68">
+        <v>2.74</v>
+      </c>
+      <c r="R68">
+        <v>2.1</v>
+      </c>
+      <c r="S68">
+        <v>1.39</v>
+      </c>
+      <c r="T68">
+        <v>2.92</v>
+      </c>
+      <c r="U68">
+        <v>2.86</v>
+      </c>
+      <c r="V68">
+        <v>1.4</v>
+      </c>
+      <c r="W68">
+        <v>1.07</v>
+      </c>
+      <c r="X68">
+        <v>1.01</v>
+      </c>
+      <c r="Y68">
+        <v>1.22</v>
+      </c>
+      <c r="Z68">
+        <v>3.48</v>
+      </c>
+      <c r="AA68">
+        <v>1.83</v>
+      </c>
+      <c r="AB68">
+        <v>1.91</v>
+      </c>
+      <c r="AC68">
+        <v>2.97</v>
+      </c>
+      <c r="AD68">
+        <v>1.3</v>
+      </c>
+      <c r="AE68">
+        <v>1.08</v>
+      </c>
+      <c r="AF68">
         <v>1.75</v>
       </c>
-      <c r="O68">
-        <v>3.4</v>
-      </c>
-      <c r="P68">
-        <v>3.9</v>
-      </c>
-      <c r="Q68">
-        <v>2.39</v>
-      </c>
-      <c r="R68">
-        <v>2.2</v>
-      </c>
-      <c r="S68">
-        <v>1.29</v>
-      </c>
-      <c r="T68">
-        <v>3.08</v>
-      </c>
-      <c r="U68">
-        <v>2.71</v>
-      </c>
-      <c r="V68">
-        <v>1.44</v>
-      </c>
-      <c r="W68">
-        <v>1.06</v>
-      </c>
-      <c r="X68">
-        <v>1.02</v>
-      </c>
-      <c r="Y68">
-        <v>1.17</v>
-      </c>
-      <c r="Z68">
-        <v>3.83</v>
-      </c>
-      <c r="AA68">
-        <v>1.75</v>
-      </c>
-      <c r="AB68">
-        <v>2</v>
-      </c>
-      <c r="AC68">
-        <v>3.09</v>
-      </c>
-      <c r="AD68">
-        <v>1.36</v>
-      </c>
-      <c r="AE68">
-        <v>1.11</v>
-      </c>
-      <c r="AF68">
-        <v>1.65</v>
-      </c>
       <c r="AG68">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AK68">
-        <v>1.97</v>
+        <v>1.64</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,80 +11556,80 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="O69">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="P69">
-        <v>2.87</v>
+        <v>2.52</v>
       </c>
       <c r="Q69">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R69">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="S69">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T69">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="U69">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V69">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W69">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X69">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y69">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z69">
-        <v>3.91</v>
+        <v>3.85</v>
       </c>
       <c r="AA69">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AB69">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AC69">
-        <v>2.93</v>
+        <v>2.7</v>
       </c>
       <c r="AD69">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AE69">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF69">
+        <v>1.67</v>
+      </c>
+      <c r="AG69">
+        <v>2.1</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ69">
+        <v>1.26</v>
+      </c>
+      <c r="AK69">
         <v>1.62</v>
-      </c>
-      <c r="AG69">
-        <v>2.2</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ69">
-        <v>1.34</v>
-      </c>
-      <c r="AK69">
-        <v>1.67</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,80 +11719,80 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="O70">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="P70">
-        <v>2.52</v>
+        <v>3.9</v>
       </c>
       <c r="Q70">
-        <v>2.8</v>
+        <v>2.39</v>
       </c>
       <c r="R70">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="S70">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T70">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="U70">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="V70">
         <v>1.44</v>
       </c>
       <c r="W70">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X70">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y70">
+        <v>1.17</v>
+      </c>
+      <c r="Z70">
+        <v>3.83</v>
+      </c>
+      <c r="AA70">
+        <v>1.75</v>
+      </c>
+      <c r="AB70">
+        <v>2</v>
+      </c>
+      <c r="AC70">
+        <v>3.09</v>
+      </c>
+      <c r="AD70">
+        <v>1.36</v>
+      </c>
+      <c r="AE70">
+        <v>1.11</v>
+      </c>
+      <c r="AF70">
+        <v>1.65</v>
+      </c>
+      <c r="AG70">
+        <v>2.05</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ70">
         <v>1.25</v>
       </c>
-      <c r="Z70">
-        <v>3.85</v>
-      </c>
-      <c r="AA70">
-        <v>1.84</v>
-      </c>
-      <c r="AB70">
-        <v>2.01</v>
-      </c>
-      <c r="AC70">
-        <v>2.7</v>
-      </c>
-      <c r="AD70">
-        <v>1.33</v>
-      </c>
-      <c r="AE70">
-        <v>1.14</v>
-      </c>
-      <c r="AF70">
-        <v>1.67</v>
-      </c>
-      <c r="AG70">
-        <v>2.1</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ70">
-        <v>1.26</v>
-      </c>
       <c r="AK70">
-        <v>1.62</v>
+        <v>1.97</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G71">
@@ -11885,77 +11885,77 @@
         <v>2.15</v>
       </c>
       <c r="O71">
-        <v>3.03</v>
+        <v>3.3</v>
       </c>
       <c r="P71">
-        <v>2.65</v>
+        <v>2.87</v>
       </c>
       <c r="Q71">
         <v>2.75</v>
       </c>
       <c r="R71">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="S71">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="T71">
-        <v>2.69</v>
+        <v>3.14</v>
       </c>
       <c r="U71">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="V71">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="W71">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X71">
         <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="Z71">
-        <v>3.03</v>
+        <v>3.91</v>
       </c>
       <c r="AA71">
-        <v>2.06</v>
+        <v>1.73</v>
       </c>
       <c r="AB71">
+        <v>2.02</v>
+      </c>
+      <c r="AC71">
+        <v>2.93</v>
+      </c>
+      <c r="AD71">
+        <v>1.39</v>
+      </c>
+      <c r="AE71">
+        <v>1.15</v>
+      </c>
+      <c r="AF71">
+        <v>1.62</v>
+      </c>
+      <c r="AG71">
+        <v>2.2</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ71">
+        <v>1.34</v>
+      </c>
+      <c r="AK71">
         <v>1.67</v>
-      </c>
-      <c r="AC71">
-        <v>3.99</v>
-      </c>
-      <c r="AD71">
-        <v>1.22</v>
-      </c>
-      <c r="AE71">
-        <v>1.04</v>
-      </c>
-      <c r="AF71">
-        <v>1.85</v>
-      </c>
-      <c r="AG71">
-        <v>1.85</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ71">
-        <v>1.29</v>
-      </c>
-      <c r="AK71">
-        <v>1.55</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -15978,13 +15978,13 @@
         <v>3.2</v>
       </c>
       <c r="U96">
-        <v>2.54</v>
+        <v>2.49</v>
       </c>
       <c r="V96">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="W96">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X96">
         <v>1</v>
@@ -15993,10 +15993,10 @@
         <v>1.17</v>
       </c>
       <c r="Z96">
-        <v>3.98</v>
+        <v>3.94</v>
       </c>
       <c r="AA96">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB96">
         <v>2.1</v>
@@ -16008,13 +16008,13 @@
         <v>1.41</v>
       </c>
       <c r="AE96">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF96">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AG96">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AK96">
         <v>1.57</v>
@@ -16120,7 +16120,7 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="O97">
         <v>3.65</v>
@@ -16129,10 +16129,10 @@
         <v>3.7</v>
       </c>
       <c r="Q97">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R97">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="S97">
         <v>1.28</v>
@@ -16162,7 +16162,7 @@
         <v>1.71</v>
       </c>
       <c r="AB97">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AC97">
         <v>2.62</v>
@@ -16193,7 +16193,7 @@
         <v>1.25</v>
       </c>
       <c r="AK97">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="O98">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="P98">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="Q98">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="R98">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="S98">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T98">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="U98">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="V98">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="W98">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X98">
         <v>1.02</v>
       </c>
       <c r="Y98">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z98">
-        <v>4.75</v>
+        <v>4.85</v>
       </c>
       <c r="AA98">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AB98">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AC98">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="AD98">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="AE98">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AF98">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AG98">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AK98">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.37</v>
+        <v>3.8</v>
       </c>
       <c r="O99">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="P99">
-        <v>5.8</v>
+        <v>1.78</v>
       </c>
       <c r="Q99">
-        <v>1.85</v>
+        <v>4.2</v>
       </c>
       <c r="R99">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="S99">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="T99">
-        <v>3.72</v>
+        <v>3.2</v>
       </c>
       <c r="U99">
-        <v>2.22</v>
+        <v>2.54</v>
       </c>
       <c r="V99">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="W99">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X99">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y99">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="Z99">
-        <v>4.85</v>
+        <v>3.77</v>
       </c>
       <c r="AA99">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AB99">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="AC99">
-        <v>2.33</v>
+        <v>2.83</v>
       </c>
       <c r="AD99">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="AE99">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="AF99">
         <v>1.67</v>
       </c>
       <c r="AG99">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AK99">
-        <v>2.58</v>
+        <v>1.16</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="O100">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P100">
-        <v>1.78</v>
+        <v>3.1</v>
       </c>
       <c r="Q100">
-        <v>4.2</v>
+        <v>2.78</v>
       </c>
       <c r="R100">
-        <v>2.33</v>
+        <v>2.05</v>
       </c>
       <c r="S100">
         <v>1.33</v>
       </c>
       <c r="T100">
-        <v>3.2</v>
+        <v>2.84</v>
       </c>
       <c r="U100">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="V100">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W100">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X100">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y100">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="Z100">
-        <v>3.77</v>
+        <v>3.34</v>
       </c>
       <c r="AA100">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AB100">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AC100">
-        <v>2.83</v>
+        <v>3.04</v>
       </c>
       <c r="AD100">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE100">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF100">
         <v>1.67</v>
       </c>
       <c r="AG100">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK100">
-        <v>1.17</v>
+        <v>1.62</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,80 +16772,80 @@
         </is>
       </c>
       <c r="N101">
+        <v>1.47</v>
+      </c>
+      <c r="O101">
+        <v>4.1</v>
+      </c>
+      <c r="P101">
+        <v>5.4</v>
+      </c>
+      <c r="Q101">
+        <v>1.98</v>
+      </c>
+      <c r="R101">
+        <v>2.69</v>
+      </c>
+      <c r="S101">
+        <v>1.22</v>
+      </c>
+      <c r="T101">
+        <v>3.75</v>
+      </c>
+      <c r="U101">
         <v>2.1</v>
       </c>
-      <c r="O101">
-        <v>3.2</v>
-      </c>
-      <c r="P101">
-        <v>3.1</v>
-      </c>
-      <c r="Q101">
-        <v>2.78</v>
-      </c>
-      <c r="R101">
-        <v>2.05</v>
-      </c>
-      <c r="S101">
-        <v>1.33</v>
-      </c>
-      <c r="T101">
-        <v>2.84</v>
-      </c>
-      <c r="U101">
-        <v>2.58</v>
-      </c>
       <c r="V101">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="W101">
+        <v>1.14</v>
+      </c>
+      <c r="X101">
+        <v>1.02</v>
+      </c>
+      <c r="Y101">
+        <v>1.15</v>
+      </c>
+      <c r="Z101">
+        <v>4.8</v>
+      </c>
+      <c r="AA101">
+        <v>1.46</v>
+      </c>
+      <c r="AB101">
+        <v>2.55</v>
+      </c>
+      <c r="AC101">
+        <v>2.15</v>
+      </c>
+      <c r="AD101">
+        <v>1.6</v>
+      </c>
+      <c r="AE101">
+        <v>1.22</v>
+      </c>
+      <c r="AF101">
+        <v>1.58</v>
+      </c>
+      <c r="AG101">
+        <v>2.17</v>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ101">
         <v>1.07</v>
       </c>
-      <c r="X101">
-        <v>1</v>
-      </c>
-      <c r="Y101">
-        <v>1.24</v>
-      </c>
-      <c r="Z101">
-        <v>3.34</v>
-      </c>
-      <c r="AA101">
-        <v>1.87</v>
-      </c>
-      <c r="AB101">
-        <v>1.9</v>
-      </c>
-      <c r="AC101">
-        <v>3.04</v>
-      </c>
-      <c r="AD101">
-        <v>1.29</v>
-      </c>
-      <c r="AE101">
-        <v>1.07</v>
-      </c>
-      <c r="AF101">
-        <v>1.67</v>
-      </c>
-      <c r="AG101">
-        <v>2.05</v>
-      </c>
-      <c r="AH101" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI101" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ101">
-        <v>1.25</v>
-      </c>
       <c r="AK101">
-        <v>1.62</v>
+        <v>2.33</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -17753,10 +17753,10 @@
         <v>1.4</v>
       </c>
       <c r="O107">
-        <v>4.25</v>
+        <v>4.06</v>
       </c>
       <c r="P107">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="Q107">
         <v>1.83</v>
@@ -17765,7 +17765,7 @@
         <v>2.6</v>
       </c>
       <c r="S107">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T107">
         <v>3.5</v>
@@ -17777,37 +17777,37 @@
         <v>1.57</v>
       </c>
       <c r="W107">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X107">
         <v>1.01</v>
       </c>
       <c r="Y107">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z107">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AA107">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AB107">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AC107">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AD107">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AE107">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF107">
         <v>1.67</v>
       </c>
       <c r="AG107">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17913,16 +17913,16 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="O108">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="P108">
         <v>6</v>
       </c>
       <c r="Q108">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="R108">
         <v>2.5</v>
@@ -17934,10 +17934,10 @@
         <v>3.08</v>
       </c>
       <c r="U108">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="V108">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W108">
         <v>1.07</v>
@@ -17949,25 +17949,25 @@
         <v>1.16</v>
       </c>
       <c r="Z108">
-        <v>4.1</v>
+        <v>3.74</v>
       </c>
       <c r="AA108">
         <v>1.7</v>
       </c>
       <c r="AB108">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="AC108">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="AD108">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE108">
         <v>1.12</v>
       </c>
       <c r="AF108">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG108">
         <v>1.9</v>
@@ -17986,7 +17986,7 @@
         <v>1.19</v>
       </c>
       <c r="AK108">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="O109">
         <v>3.6</v>
@@ -18085,7 +18085,7 @@
         <v>4.2</v>
       </c>
       <c r="Q109">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="R109">
         <v>2.12</v>

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.89</v>
+        <v>2.35</v>
       </c>
       <c r="O61">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="P61">
-        <v>3.35</v>
+        <v>2.4</v>
       </c>
       <c r="Q61">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="R61">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="S61">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="T61">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="U61">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V61">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="W61">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X61">
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z61">
-        <v>6.06</v>
+        <v>5.85</v>
       </c>
       <c r="AA61">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AB61">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="AC61">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AD61">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AE61">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AF61">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AG61">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK61">
-        <v>1.81</v>
+        <v>1.45</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.35</v>
+        <v>1.89</v>
       </c>
       <c r="O62">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="P62">
-        <v>2.4</v>
+        <v>3.35</v>
       </c>
       <c r="Q62">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="R62">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="S62">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="T62">
-        <v>4.25</v>
+        <v>4.1</v>
       </c>
       <c r="U62">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V62">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W62">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Z62">
-        <v>5.85</v>
+        <v>6.06</v>
       </c>
       <c r="AA62">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AB62">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="AC62">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AD62">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AE62">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AF62">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AG62">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK62">
-        <v>1.45</v>
+        <v>1.81</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
+        <v>1.96</v>
+      </c>
+      <c r="O66">
+        <v>3.2</v>
+      </c>
+      <c r="P66">
+        <v>3.2</v>
+      </c>
+      <c r="Q66">
+        <v>2.74</v>
+      </c>
+      <c r="R66">
         <v>2.1</v>
       </c>
-      <c r="O66">
-        <v>3.05</v>
-      </c>
-      <c r="P66">
-        <v>3.25</v>
-      </c>
-      <c r="Q66">
+      <c r="S66">
+        <v>1.39</v>
+      </c>
+      <c r="T66">
         <v>2.92</v>
-      </c>
-      <c r="R66">
-        <v>2</v>
-      </c>
-      <c r="S66">
-        <v>1.45</v>
-      </c>
-      <c r="T66">
-        <v>2.5</v>
       </c>
       <c r="U66">
         <v>2.86</v>
       </c>
       <c r="V66">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W66">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X66">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z66">
-        <v>3.04</v>
+        <v>3.48</v>
       </c>
       <c r="AA66">
-        <v>2.16</v>
+        <v>1.83</v>
       </c>
       <c r="AB66">
-        <v>1.66</v>
+        <v>1.91</v>
       </c>
       <c r="AC66">
-        <v>3.42</v>
+        <v>2.97</v>
       </c>
       <c r="AD66">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AE66">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF66">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG66">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AK66">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="O67">
-        <v>3.03</v>
+        <v>3.4</v>
       </c>
       <c r="P67">
-        <v>2.65</v>
+        <v>3.9</v>
       </c>
       <c r="Q67">
-        <v>2.75</v>
+        <v>2.39</v>
       </c>
       <c r="R67">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="S67">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="T67">
-        <v>2.69</v>
+        <v>3.08</v>
       </c>
       <c r="U67">
-        <v>3.2</v>
+        <v>2.71</v>
       </c>
       <c r="V67">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W67">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X67">
         <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="Z67">
-        <v>3.03</v>
+        <v>3.83</v>
       </c>
       <c r="AA67">
-        <v>2.06</v>
+        <v>1.75</v>
       </c>
       <c r="AB67">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AC67">
-        <v>3.99</v>
+        <v>3.09</v>
       </c>
       <c r="AD67">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AE67">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF67">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AG67">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK67">
-        <v>1.55</v>
+        <v>1.97</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.96</v>
+        <v>2.15</v>
       </c>
       <c r="O68">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P68">
-        <v>3.2</v>
+        <v>2.87</v>
       </c>
       <c r="Q68">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="R68">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S68">
+        <v>1.3</v>
+      </c>
+      <c r="T68">
+        <v>3.14</v>
+      </c>
+      <c r="U68">
+        <v>2.4</v>
+      </c>
+      <c r="V68">
+        <v>1.46</v>
+      </c>
+      <c r="W68">
+        <v>1.09</v>
+      </c>
+      <c r="X68">
+        <v>1.02</v>
+      </c>
+      <c r="Y68">
+        <v>1.18</v>
+      </c>
+      <c r="Z68">
+        <v>3.91</v>
+      </c>
+      <c r="AA68">
+        <v>1.73</v>
+      </c>
+      <c r="AB68">
+        <v>2.02</v>
+      </c>
+      <c r="AC68">
+        <v>2.93</v>
+      </c>
+      <c r="AD68">
         <v>1.39</v>
       </c>
-      <c r="T68">
-        <v>2.92</v>
-      </c>
-      <c r="U68">
-        <v>2.86</v>
-      </c>
-      <c r="V68">
-        <v>1.4</v>
-      </c>
-      <c r="W68">
-        <v>1.07</v>
-      </c>
-      <c r="X68">
-        <v>1.01</v>
-      </c>
-      <c r="Y68">
-        <v>1.22</v>
-      </c>
-      <c r="Z68">
-        <v>3.48</v>
-      </c>
-      <c r="AA68">
-        <v>1.83</v>
-      </c>
-      <c r="AB68">
-        <v>1.91</v>
-      </c>
-      <c r="AC68">
-        <v>2.97</v>
-      </c>
-      <c r="AD68">
-        <v>1.3</v>
-      </c>
       <c r="AE68">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF68">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG68">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AK68">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="O69">
-        <v>3.32</v>
+        <v>3.05</v>
       </c>
       <c r="P69">
-        <v>2.52</v>
+        <v>3.25</v>
       </c>
       <c r="Q69">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="R69">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="S69">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="T69">
-        <v>3.15</v>
+        <v>2.5</v>
       </c>
       <c r="U69">
-        <v>2.5</v>
+        <v>2.86</v>
       </c>
       <c r="V69">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="W69">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X69">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y69">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z69">
-        <v>3.85</v>
+        <v>3.04</v>
       </c>
       <c r="AA69">
-        <v>1.84</v>
+        <v>2.16</v>
       </c>
       <c r="AB69">
-        <v>2.01</v>
+        <v>1.66</v>
       </c>
       <c r="AC69">
-        <v>2.7</v>
+        <v>3.42</v>
       </c>
       <c r="AD69">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AE69">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AF69">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AG69">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK69">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.75</v>
+        <v>2.33</v>
       </c>
       <c r="O70">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="P70">
-        <v>3.9</v>
+        <v>2.52</v>
       </c>
       <c r="Q70">
-        <v>2.39</v>
+        <v>2.8</v>
       </c>
       <c r="R70">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S70">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T70">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="U70">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="V70">
         <v>1.44</v>
       </c>
       <c r="W70">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X70">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y70">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z70">
-        <v>3.83</v>
+        <v>3.85</v>
       </c>
       <c r="AA70">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AB70">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AC70">
-        <v>3.09</v>
+        <v>2.7</v>
       </c>
       <c r="AD70">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE70">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF70">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG70">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK70">
-        <v>1.97</v>
+        <v>1.62</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G71">
@@ -11885,61 +11885,61 @@
         <v>2.15</v>
       </c>
       <c r="O71">
-        <v>3.3</v>
+        <v>3.03</v>
       </c>
       <c r="P71">
-        <v>2.87</v>
+        <v>2.65</v>
       </c>
       <c r="Q71">
         <v>2.75</v>
       </c>
       <c r="R71">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="S71">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="T71">
-        <v>3.14</v>
+        <v>2.69</v>
       </c>
       <c r="U71">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="V71">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="W71">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X71">
         <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="Z71">
-        <v>3.91</v>
+        <v>3.03</v>
       </c>
       <c r="AA71">
-        <v>1.73</v>
+        <v>2.06</v>
       </c>
       <c r="AB71">
-        <v>2.02</v>
+        <v>1.67</v>
       </c>
       <c r="AC71">
-        <v>2.93</v>
+        <v>3.99</v>
       </c>
       <c r="AD71">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="AE71">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="AF71">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AG71">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AK71">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,80 +16446,80 @@
         </is>
       </c>
       <c r="N99">
-        <v>3.8</v>
+        <v>1.47</v>
       </c>
       <c r="O99">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="P99">
-        <v>1.78</v>
+        <v>5.4</v>
       </c>
       <c r="Q99">
-        <v>4.2</v>
+        <v>1.98</v>
       </c>
       <c r="R99">
+        <v>2.69</v>
+      </c>
+      <c r="S99">
+        <v>1.22</v>
+      </c>
+      <c r="T99">
+        <v>3.75</v>
+      </c>
+      <c r="U99">
+        <v>2.1</v>
+      </c>
+      <c r="V99">
+        <v>1.62</v>
+      </c>
+      <c r="W99">
+        <v>1.14</v>
+      </c>
+      <c r="X99">
+        <v>1.02</v>
+      </c>
+      <c r="Y99">
+        <v>1.15</v>
+      </c>
+      <c r="Z99">
+        <v>4.8</v>
+      </c>
+      <c r="AA99">
+        <v>1.46</v>
+      </c>
+      <c r="AB99">
+        <v>2.55</v>
+      </c>
+      <c r="AC99">
+        <v>2.15</v>
+      </c>
+      <c r="AD99">
+        <v>1.6</v>
+      </c>
+      <c r="AE99">
+        <v>1.22</v>
+      </c>
+      <c r="AF99">
+        <v>1.58</v>
+      </c>
+      <c r="AG99">
+        <v>2.17</v>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ99">
+        <v>1.07</v>
+      </c>
+      <c r="AK99">
         <v>2.33</v>
-      </c>
-      <c r="S99">
-        <v>1.33</v>
-      </c>
-      <c r="T99">
-        <v>3.2</v>
-      </c>
-      <c r="U99">
-        <v>2.54</v>
-      </c>
-      <c r="V99">
-        <v>1.44</v>
-      </c>
-      <c r="W99">
-        <v>1.05</v>
-      </c>
-      <c r="X99">
-        <v>1.03</v>
-      </c>
-      <c r="Y99">
-        <v>1.19</v>
-      </c>
-      <c r="Z99">
-        <v>3.77</v>
-      </c>
-      <c r="AA99">
-        <v>1.75</v>
-      </c>
-      <c r="AB99">
-        <v>2.05</v>
-      </c>
-      <c r="AC99">
-        <v>2.83</v>
-      </c>
-      <c r="AD99">
-        <v>1.33</v>
-      </c>
-      <c r="AE99">
-        <v>1.09</v>
-      </c>
-      <c r="AF99">
-        <v>1.67</v>
-      </c>
-      <c r="AG99">
-        <v>2.06</v>
-      </c>
-      <c r="AH99" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI99" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ99">
-        <v>1.2</v>
-      </c>
-      <c r="AK99">
-        <v>1.16</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="O100">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="P100">
-        <v>3.1</v>
+        <v>1.78</v>
       </c>
       <c r="Q100">
-        <v>2.78</v>
+        <v>4.2</v>
       </c>
       <c r="R100">
-        <v>2.05</v>
+        <v>2.33</v>
       </c>
       <c r="S100">
         <v>1.33</v>
       </c>
       <c r="T100">
-        <v>2.84</v>
+        <v>3.2</v>
       </c>
       <c r="U100">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="V100">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W100">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X100">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y100">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="Z100">
-        <v>3.34</v>
+        <v>3.77</v>
       </c>
       <c r="AA100">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AB100">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AC100">
-        <v>3.04</v>
+        <v>2.83</v>
       </c>
       <c r="AD100">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE100">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF100">
         <v>1.67</v>
       </c>
       <c r="AG100">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK100">
-        <v>1.62</v>
+        <v>1.16</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,80 +16772,80 @@
         </is>
       </c>
       <c r="N101">
-        <v>1.47</v>
+        <v>2.1</v>
       </c>
       <c r="O101">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="P101">
-        <v>5.4</v>
+        <v>3.1</v>
       </c>
       <c r="Q101">
-        <v>1.98</v>
+        <v>2.78</v>
       </c>
       <c r="R101">
-        <v>2.69</v>
+        <v>2.05</v>
       </c>
       <c r="S101">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="T101">
-        <v>3.75</v>
+        <v>2.84</v>
       </c>
       <c r="U101">
-        <v>2.1</v>
+        <v>2.58</v>
       </c>
       <c r="V101">
+        <v>1.4</v>
+      </c>
+      <c r="W101">
+        <v>1.07</v>
+      </c>
+      <c r="X101">
+        <v>1</v>
+      </c>
+      <c r="Y101">
+        <v>1.24</v>
+      </c>
+      <c r="Z101">
+        <v>3.34</v>
+      </c>
+      <c r="AA101">
+        <v>1.87</v>
+      </c>
+      <c r="AB101">
+        <v>1.9</v>
+      </c>
+      <c r="AC101">
+        <v>3.04</v>
+      </c>
+      <c r="AD101">
+        <v>1.29</v>
+      </c>
+      <c r="AE101">
+        <v>1.07</v>
+      </c>
+      <c r="AF101">
+        <v>1.67</v>
+      </c>
+      <c r="AG101">
+        <v>2.05</v>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ101">
+        <v>1.25</v>
+      </c>
+      <c r="AK101">
         <v>1.62</v>
-      </c>
-      <c r="W101">
-        <v>1.14</v>
-      </c>
-      <c r="X101">
-        <v>1.02</v>
-      </c>
-      <c r="Y101">
-        <v>1.15</v>
-      </c>
-      <c r="Z101">
-        <v>4.8</v>
-      </c>
-      <c r="AA101">
-        <v>1.46</v>
-      </c>
-      <c r="AB101">
-        <v>2.55</v>
-      </c>
-      <c r="AC101">
-        <v>2.15</v>
-      </c>
-      <c r="AD101">
-        <v>1.6</v>
-      </c>
-      <c r="AE101">
-        <v>1.22</v>
-      </c>
-      <c r="AF101">
-        <v>1.58</v>
-      </c>
-      <c r="AG101">
-        <v>2.17</v>
-      </c>
-      <c r="AH101" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI101" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ101">
-        <v>1.07</v>
-      </c>
-      <c r="AK101">
-        <v>2.33</v>
       </c>
       <c r="AL101">
         <v>0</v>

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -798,55 +798,55 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="O3">
         <v>3.8</v>
       </c>
       <c r="P3">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="Q3">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="R3">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="S3">
         <v>1.3</v>
       </c>
       <c r="T3">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U3">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="V3">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W3">
         <v>1.11</v>
       </c>
       <c r="X3">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z3">
-        <v>3.98</v>
+        <v>3.93</v>
       </c>
       <c r="AA3">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AB3">
         <v>2.05</v>
       </c>
       <c r="AC3">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AD3">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AE3">
         <v>1.11</v>
@@ -855,7 +855,7 @@
         <v>1.67</v>
       </c>
       <c r="AG3">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>1.25</v>
       </c>
       <c r="AK3">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="O6">
-        <v>3.51</v>
+        <v>3.4</v>
       </c>
       <c r="P6">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="Q6">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="R6">
         <v>2.2</v>
       </c>
       <c r="S6">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T6">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="U6">
-        <v>2.48</v>
+        <v>2.61</v>
       </c>
       <c r="V6">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="W6">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y6">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z6">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="AA6">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB6">
         <v>1.95</v>
       </c>
       <c r="AC6">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="AD6">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AE6">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF6">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AG6">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK6">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC8">
         <v>0</v>
@@ -2102,31 +2102,31 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O11">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="P11">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Q11">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="R11">
         <v>1.98</v>
       </c>
       <c r="S11">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T11">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="U11">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="V11">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="W11">
         <v>1.05</v>
@@ -2135,25 +2135,25 @@
         <v>1</v>
       </c>
       <c r="Y11">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z11">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AA11">
         <v>1.95</v>
       </c>
       <c r="AB11">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AC11">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="AD11">
         <v>1.31</v>
       </c>
       <c r="AE11">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF11">
         <v>1.7</v>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="O12">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="P12">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q12">
         <v>2.8</v>
       </c>
       <c r="R12">
-        <v>2.09</v>
+        <v>1.98</v>
       </c>
       <c r="S12">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="T12">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U12">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="V12">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W12">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X12">
         <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z12">
-        <v>3.34</v>
+        <v>3.08</v>
       </c>
       <c r="AA12">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AB12">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AC12">
-        <v>3.14</v>
+        <v>3.42</v>
       </c>
       <c r="AD12">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AE12">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF12">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG12">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK12">
         <v>1.57</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="O13">
-        <v>3.38</v>
+        <v>3</v>
       </c>
       <c r="P13">
-        <v>3.03</v>
+        <v>2.9</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2467,10 +2467,10 @@
         <v>0</v>
       </c>
       <c r="AA13">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB13">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC13">
         <v>0</v>
@@ -3080,16 +3080,16 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.04</v>
+        <v>2.45</v>
       </c>
       <c r="O17">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P17">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="Q17">
-        <v>2.76</v>
+        <v>2.71</v>
       </c>
       <c r="R17">
         <v>2.06</v>
@@ -3098,7 +3098,7 @@
         <v>1.44</v>
       </c>
       <c r="T17">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="U17">
         <v>3.02</v>
@@ -3125,7 +3125,7 @@
         <v>1.63</v>
       </c>
       <c r="AC17">
-        <v>4.26</v>
+        <v>4.24</v>
       </c>
       <c r="AD17">
         <v>1.21</v>
@@ -3134,10 +3134,10 @@
         <v>1.02</v>
       </c>
       <c r="AF17">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AG17">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>1.34</v>
       </c>
       <c r="AK17">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3249,13 +3249,13 @@
         <v>3.05</v>
       </c>
       <c r="P18">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q18">
-        <v>3.72</v>
+        <v>3.61</v>
       </c>
       <c r="R18">
-        <v>1.94</v>
+        <v>2.11</v>
       </c>
       <c r="S18">
         <v>1.45</v>
@@ -3276,7 +3276,7 @@
         <v>1.03</v>
       </c>
       <c r="Y18">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="Z18">
         <v>2.88</v>
@@ -3288,7 +3288,7 @@
         <v>1.72</v>
       </c>
       <c r="AC18">
-        <v>3.58</v>
+        <v>3.79</v>
       </c>
       <c r="AD18">
         <v>1.21</v>
@@ -3316,7 +3316,7 @@
         <v>1.36</v>
       </c>
       <c r="AK18">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="O19">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="P19">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="Q19">
         <v>1.85</v>
@@ -3424,13 +3424,13 @@
         <v>1.33</v>
       </c>
       <c r="T19">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="U19">
-        <v>2.48</v>
+        <v>2.68</v>
       </c>
       <c r="V19">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W19">
         <v>1.08</v>
@@ -3439,31 +3439,31 @@
         <v>1</v>
       </c>
       <c r="Y19">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z19">
-        <v>3.81</v>
+        <v>3.58</v>
       </c>
       <c r="AA19">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AB19">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AC19">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AD19">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE19">
         <v>1.09</v>
       </c>
       <c r="AF19">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AG19">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>1.18</v>
       </c>
       <c r="AK19">
-        <v>3.02</v>
+        <v>2.97</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -4058,19 +4058,19 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="O23">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
       <c r="P23">
-        <v>3.29</v>
+        <v>3.02</v>
       </c>
       <c r="Q23">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="R23">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="S23">
         <v>1.4</v>
@@ -4082,40 +4082,40 @@
         <v>2.94</v>
       </c>
       <c r="V23">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W23">
         <v>1.03</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Z23">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AA23">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AB23">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AC23">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AD23">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE23">
         <v>1.04</v>
       </c>
       <c r="AF23">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AG23">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O27">
         <v>3.6</v>
@@ -4719,43 +4719,43 @@
         <v>1.74</v>
       </c>
       <c r="Q27">
-        <v>5.14</v>
+        <v>5.16</v>
       </c>
       <c r="R27">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="S27">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T27">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="U27">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="V27">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W27">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X27">
         <v>1</v>
       </c>
       <c r="Y27">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z27">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="AA27">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AB27">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC27">
-        <v>3.52</v>
+        <v>3.62</v>
       </c>
       <c r="AD27">
         <v>1.27</v>
@@ -4764,10 +4764,10 @@
         <v>1.04</v>
       </c>
       <c r="AF27">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AG27">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -5208,16 +5208,16 @@
         <v>0</v>
       </c>
       <c r="Q30">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R30">
         <v>2.13</v>
       </c>
       <c r="S30">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T30">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="U30">
         <v>2.76</v>
@@ -5238,10 +5238,10 @@
         <v>3.2</v>
       </c>
       <c r="AA30">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AB30">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AC30">
         <v>3.2</v>
@@ -5250,13 +5250,13 @@
         <v>1.26</v>
       </c>
       <c r="AE30">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF30">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG30">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK30">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,34 +5362,34 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="O31">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P31">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="Q31">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="R31">
         <v>1.97</v>
       </c>
       <c r="S31">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T31">
         <v>2.54</v>
       </c>
       <c r="U31">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="V31">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W31">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X31">
         <v>1.04</v>
@@ -5404,13 +5404,13 @@
         <v>2.21</v>
       </c>
       <c r="AB31">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AC31">
-        <v>4.06</v>
+        <v>4.12</v>
       </c>
       <c r="AD31">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE31">
         <v>1.03</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK31">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,22 +7318,22 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.59</v>
+        <v>2.45</v>
       </c>
       <c r="O43">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="P43">
-        <v>4.48</v>
+        <v>2.18</v>
       </c>
       <c r="Q43">
-        <v>1.93</v>
+        <v>3.38</v>
       </c>
       <c r="R43">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="S43">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T43">
         <v>4</v>
@@ -7342,40 +7342,40 @@
         <v>2.04</v>
       </c>
       <c r="V43">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="W43">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X43">
         <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z43">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AA43">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AB43">
         <v>2.88</v>
       </c>
       <c r="AC43">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AD43">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AE43">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF43">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AG43">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.13</v>
+        <v>1.6</v>
       </c>
       <c r="AK43">
-        <v>2.38</v>
+        <v>1.39</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,22 +7481,22 @@
         </is>
       </c>
       <c r="N44">
+        <v>1.59</v>
+      </c>
+      <c r="O44">
+        <v>4</v>
+      </c>
+      <c r="P44">
+        <v>4.48</v>
+      </c>
+      <c r="Q44">
+        <v>1.93</v>
+      </c>
+      <c r="R44">
         <v>2.45</v>
       </c>
-      <c r="O44">
-        <v>3.85</v>
-      </c>
-      <c r="P44">
-        <v>2.18</v>
-      </c>
-      <c r="Q44">
-        <v>3.38</v>
-      </c>
-      <c r="R44">
-        <v>2.33</v>
-      </c>
       <c r="S44">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T44">
         <v>4</v>
@@ -7505,40 +7505,40 @@
         <v>2.04</v>
       </c>
       <c r="V44">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="W44">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X44">
         <v>1.02</v>
       </c>
       <c r="Y44">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z44">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AA44">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AB44">
         <v>2.88</v>
       </c>
       <c r="AC44">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AD44">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AE44">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF44">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AG44">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.6</v>
+        <v>1.13</v>
       </c>
       <c r="AK44">
-        <v>1.39</v>
+        <v>2.38</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.27</v>
+        <v>1.43</v>
       </c>
       <c r="O54">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="P54">
-        <v>10</v>
+        <v>6.25</v>
       </c>
       <c r="Q54">
-        <v>1.71</v>
+        <v>1.94</v>
       </c>
       <c r="R54">
-        <v>2.42</v>
+        <v>2.37</v>
       </c>
       <c r="S54">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T54">
-        <v>3.12</v>
+        <v>2.92</v>
       </c>
       <c r="U54">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="V54">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="W54">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X54">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y54">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="Z54">
-        <v>4.15</v>
+        <v>3.8</v>
       </c>
       <c r="AA54">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB54">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AC54">
-        <v>2.52</v>
+        <v>2.88</v>
       </c>
       <c r="AD54">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AE54">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF54">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AG54">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AK54">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="O55">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="P55">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="Q55">
-        <v>7.6</v>
+        <v>6.35</v>
       </c>
       <c r="R55">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S55">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="T55">
-        <v>3.05</v>
+        <v>2.87</v>
       </c>
       <c r="U55">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="V55">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W55">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X55">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y55">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z55">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="AA55">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AB55">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AC55">
-        <v>2.83</v>
+        <v>2.97</v>
       </c>
       <c r="AD55">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE55">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF55">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG55">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AK55">
         <v>1.07</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.35</v>
+        <v>1.89</v>
       </c>
       <c r="O61">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="P61">
-        <v>2.4</v>
+        <v>3.35</v>
       </c>
       <c r="Q61">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="R61">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="S61">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="T61">
-        <v>4.25</v>
+        <v>4.1</v>
       </c>
       <c r="U61">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V61">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W61">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X61">
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Z61">
-        <v>5.85</v>
+        <v>6.06</v>
       </c>
       <c r="AA61">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AB61">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="AC61">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AD61">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AE61">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AF61">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AG61">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK61">
-        <v>1.45</v>
+        <v>1.81</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.89</v>
+        <v>2.35</v>
       </c>
       <c r="O62">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="P62">
-        <v>3.35</v>
+        <v>2.4</v>
       </c>
       <c r="Q62">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="R62">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="S62">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="T62">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="U62">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V62">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="W62">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z62">
-        <v>6.06</v>
+        <v>5.85</v>
       </c>
       <c r="AA62">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AB62">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="AC62">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AD62">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AE62">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AF62">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AG62">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK62">
-        <v>1.81</v>
+        <v>1.45</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.75</v>
+        <v>2.33</v>
       </c>
       <c r="O67">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="P67">
-        <v>3.9</v>
+        <v>2.52</v>
       </c>
       <c r="Q67">
-        <v>2.39</v>
+        <v>2.8</v>
       </c>
       <c r="R67">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S67">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T67">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="U67">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="V67">
         <v>1.44</v>
       </c>
       <c r="W67">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X67">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y67">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z67">
-        <v>3.83</v>
+        <v>3.85</v>
       </c>
       <c r="AA67">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AB67">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AC67">
-        <v>3.09</v>
+        <v>2.7</v>
       </c>
       <c r="AD67">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE67">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF67">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG67">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK67">
-        <v>1.97</v>
+        <v>1.62</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,80 +11719,80 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="O70">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="P70">
-        <v>2.52</v>
+        <v>3.9</v>
       </c>
       <c r="Q70">
-        <v>2.8</v>
+        <v>2.39</v>
       </c>
       <c r="R70">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="S70">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T70">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="U70">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="V70">
         <v>1.44</v>
       </c>
       <c r="W70">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X70">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y70">
+        <v>1.17</v>
+      </c>
+      <c r="Z70">
+        <v>3.83</v>
+      </c>
+      <c r="AA70">
+        <v>1.75</v>
+      </c>
+      <c r="AB70">
+        <v>2</v>
+      </c>
+      <c r="AC70">
+        <v>3.09</v>
+      </c>
+      <c r="AD70">
+        <v>1.36</v>
+      </c>
+      <c r="AE70">
+        <v>1.11</v>
+      </c>
+      <c r="AF70">
+        <v>1.65</v>
+      </c>
+      <c r="AG70">
+        <v>2.05</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ70">
         <v>1.25</v>
       </c>
-      <c r="Z70">
-        <v>3.85</v>
-      </c>
-      <c r="AA70">
-        <v>1.84</v>
-      </c>
-      <c r="AB70">
-        <v>2.01</v>
-      </c>
-      <c r="AC70">
-        <v>2.7</v>
-      </c>
-      <c r="AD70">
-        <v>1.33</v>
-      </c>
-      <c r="AE70">
-        <v>1.14</v>
-      </c>
-      <c r="AF70">
-        <v>1.67</v>
-      </c>
-      <c r="AG70">
-        <v>2.1</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ70">
-        <v>1.26</v>
-      </c>
       <c r="AK70">
-        <v>1.62</v>
+        <v>1.97</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="O100">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P100">
-        <v>1.78</v>
+        <v>3.1</v>
       </c>
       <c r="Q100">
-        <v>4.2</v>
+        <v>2.78</v>
       </c>
       <c r="R100">
-        <v>2.33</v>
+        <v>2.05</v>
       </c>
       <c r="S100">
         <v>1.33</v>
       </c>
       <c r="T100">
-        <v>3.2</v>
+        <v>2.84</v>
       </c>
       <c r="U100">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="V100">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W100">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X100">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y100">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="Z100">
-        <v>3.77</v>
+        <v>3.34</v>
       </c>
       <c r="AA100">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AB100">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AC100">
-        <v>2.83</v>
+        <v>3.04</v>
       </c>
       <c r="AD100">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE100">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF100">
         <v>1.67</v>
       </c>
       <c r="AG100">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK100">
-        <v>1.16</v>
+        <v>1.62</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="O101">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="P101">
-        <v>3.1</v>
+        <v>1.78</v>
       </c>
       <c r="Q101">
-        <v>2.78</v>
+        <v>4.2</v>
       </c>
       <c r="R101">
-        <v>2.05</v>
+        <v>2.33</v>
       </c>
       <c r="S101">
         <v>1.33</v>
       </c>
       <c r="T101">
-        <v>2.84</v>
+        <v>3.2</v>
       </c>
       <c r="U101">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="V101">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W101">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X101">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y101">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="Z101">
-        <v>3.34</v>
+        <v>3.77</v>
       </c>
       <c r="AA101">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AB101">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AC101">
-        <v>3.04</v>
+        <v>2.83</v>
       </c>
       <c r="AD101">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE101">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF101">
         <v>1.67</v>
       </c>
       <c r="AG101">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK101">
-        <v>1.62</v>
+        <v>1.16</v>
       </c>
       <c r="AL101">
         <v>0</v>

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -644,7 +644,7 @@
         <v>2</v>
       </c>
       <c r="Q2">
-        <v>4.32</v>
+        <v>4.36</v>
       </c>
       <c r="R2">
         <v>2</v>
@@ -653,10 +653,10 @@
         <v>1.4</v>
       </c>
       <c r="T2">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="U2">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="V2">
         <v>1.33</v>
@@ -671,19 +671,19 @@
         <v>1.34</v>
       </c>
       <c r="Z2">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="AA2">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="AB2">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC2">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="AD2">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AE2">
         <v>1.01</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK2">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="O4">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P4">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="Q4">
         <v>4.53</v>
@@ -976,19 +976,19 @@
         <v>2.16</v>
       </c>
       <c r="S4">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T4">
-        <v>3.2</v>
+        <v>2.93</v>
       </c>
       <c r="U4">
-        <v>2.63</v>
+        <v>2.57</v>
       </c>
       <c r="V4">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W4">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X4">
         <v>1.04</v>
@@ -1000,10 +1000,10 @@
         <v>3.58</v>
       </c>
       <c r="AA4">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB4">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AC4">
         <v>3.1</v>
@@ -1018,7 +1018,7 @@
         <v>1.68</v>
       </c>
       <c r="AG4">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
+        <v>1.3</v>
+      </c>
+      <c r="AK4">
         <v>1.22</v>
-      </c>
-      <c r="AK4">
-        <v>1.2</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="O5">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P5">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="Q5">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="R5">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="S5">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="T5">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="U5">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="V5">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="W5">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X5">
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="Z5">
-        <v>3.14</v>
+        <v>3.58</v>
       </c>
       <c r="AA5">
-        <v>1.99</v>
+        <v>1.78</v>
       </c>
       <c r="AB5">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AC5">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="AD5">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AE5">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF5">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AG5">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AK5">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1450,58 +1450,58 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="O7">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P7">
-        <v>3.55</v>
+        <v>3.39</v>
       </c>
       <c r="Q7">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="R7">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="S7">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T7">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="U7">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="V7">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W7">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y7">
         <v>1.28</v>
       </c>
       <c r="Z7">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AA7">
         <v>1.94</v>
       </c>
       <c r="AB7">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AC7">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AD7">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE7">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF7">
         <v>1.75</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AK7">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="O9">
         <v>4</v>
@@ -1788,7 +1788,7 @@
         <v>2.3</v>
       </c>
       <c r="R9">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="S9">
         <v>1.2</v>
@@ -1797,10 +1797,10 @@
         <v>4</v>
       </c>
       <c r="U9">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V9">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="W9">
         <v>1.2</v>
@@ -1809,31 +1809,31 @@
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z9">
         <v>6.5</v>
       </c>
       <c r="AA9">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AB9">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="AC9">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AD9">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AE9">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AF9">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AG9">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1948,40 +1948,40 @@
         <v>3.01</v>
       </c>
       <c r="Q10">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R10">
-        <v>2.15</v>
+        <v>1.84</v>
       </c>
       <c r="S10">
         <v>1.36</v>
       </c>
       <c r="T10">
-        <v>2.44</v>
+        <v>2.91</v>
       </c>
       <c r="U10">
         <v>2.8</v>
       </c>
       <c r="V10">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="W10">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z10">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AA10">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB10">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AC10">
         <v>3.08</v>
@@ -1993,10 +1993,10 @@
         <v>1.06</v>
       </c>
       <c r="AF10">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG10">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.36</v>
+        <v>1.1</v>
       </c>
       <c r="AK10">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2606,16 +2606,16 @@
         <v>2.5</v>
       </c>
       <c r="S14">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T14">
         <v>3.25</v>
       </c>
       <c r="U14">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="V14">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="W14">
         <v>1.12</v>
@@ -2627,10 +2627,10 @@
         <v>1.17</v>
       </c>
       <c r="Z14">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AA14">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB14">
         <v>2.04</v>
@@ -2642,13 +2642,13 @@
         <v>1.38</v>
       </c>
       <c r="AE14">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF14">
         <v>1.95</v>
       </c>
       <c r="AG14">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2763,10 +2763,10 @@
         <v>4.15</v>
       </c>
       <c r="Q15">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="R15">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S15">
         <v>1.4</v>
@@ -2784,22 +2784,22 @@
         <v>1.08</v>
       </c>
       <c r="X15">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y15">
         <v>1.27</v>
       </c>
       <c r="Z15">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="AA15">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AB15">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AC15">
-        <v>3.44</v>
+        <v>3.47</v>
       </c>
       <c r="AD15">
         <v>1.25</v>
@@ -2811,7 +2811,7 @@
         <v>1.83</v>
       </c>
       <c r="AG15">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>5.4</v>
+        <v>6.42</v>
       </c>
       <c r="O16">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="P16">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="Q16">
-        <v>5.75</v>
+        <v>7</v>
       </c>
       <c r="R16">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S16">
         <v>1.37</v>
       </c>
       <c r="T16">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="U16">
-        <v>2.53</v>
+        <v>2.88</v>
       </c>
       <c r="V16">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W16">
         <v>1.06</v>
       </c>
       <c r="X16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z16">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="AA16">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="AB16">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC16">
         <v>3.4</v>
       </c>
       <c r="AD16">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE16">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF16">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AG16">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.3</v>
+        <v>2.45</v>
       </c>
       <c r="AK16">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,25 +3080,25 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="O17">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P17">
-        <v>3.35</v>
+        <v>2.5</v>
       </c>
       <c r="Q17">
-        <v>2.71</v>
+        <v>3.61</v>
       </c>
       <c r="R17">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="S17">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T17">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="U17">
         <v>3.02</v>
@@ -3107,37 +3107,37 @@
         <v>1.32</v>
       </c>
       <c r="W17">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X17">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="Z17">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AA17">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AB17">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="AC17">
-        <v>4.24</v>
+        <v>3.79</v>
       </c>
       <c r="AD17">
         <v>1.21</v>
       </c>
       <c r="AE17">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF17">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AG17">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AK17">
-        <v>1.71</v>
+        <v>1.35</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,25 +3243,25 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="O18">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P18">
-        <v>2.5</v>
+        <v>3.35</v>
       </c>
       <c r="Q18">
-        <v>3.61</v>
+        <v>2.71</v>
       </c>
       <c r="R18">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="S18">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T18">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="U18">
         <v>3.02</v>
@@ -3270,37 +3270,37 @@
         <v>1.32</v>
       </c>
       <c r="W18">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X18">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y18">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="Z18">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AA18">
-        <v>2.14</v>
+        <v>2.31</v>
       </c>
       <c r="AB18">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="AC18">
-        <v>3.79</v>
+        <v>4.24</v>
       </c>
       <c r="AD18">
         <v>1.21</v>
       </c>
       <c r="AE18">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF18">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AG18">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AK18">
-        <v>1.35</v>
+        <v>1.71</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>16.04</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3771,10 +3771,10 @@
         <v>0</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AC21">
         <v>0</v>
@@ -3895,16 +3895,16 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="O22">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P22">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="Q22">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="R22">
         <v>2.1</v>
@@ -3913,7 +3913,7 @@
         <v>1.36</v>
       </c>
       <c r="T22">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="U22">
         <v>2.73</v>
@@ -3925,34 +3925,34 @@
         <v>1.05</v>
       </c>
       <c r="X22">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y22">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z22">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AA22">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AB22">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC22">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AD22">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE22">
         <v>1.05</v>
       </c>
       <c r="AF22">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AG22">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4230,22 +4230,22 @@
         <v>3.45</v>
       </c>
       <c r="Q24">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="R24">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="S24">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T24">
-        <v>2.69</v>
+        <v>2.58</v>
       </c>
       <c r="U24">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="V24">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W24">
         <v>1.04</v>
@@ -4257,16 +4257,16 @@
         <v>1.32</v>
       </c>
       <c r="Z24">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="AA24">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="AB24">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="AC24">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AD24">
         <v>1.19</v>
@@ -4275,10 +4275,10 @@
         <v>1.04</v>
       </c>
       <c r="AF24">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AG24">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4384,25 +4384,25 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O25">
         <v>3</v>
       </c>
       <c r="P25">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="Q25">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="R25">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="S25">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="T25">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="U25">
         <v>3.24</v>
@@ -4411,7 +4411,7 @@
         <v>1.26</v>
       </c>
       <c r="W25">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X25">
         <v>1.04</v>
@@ -4420,7 +4420,7 @@
         <v>1.38</v>
       </c>
       <c r="Z25">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AA25">
         <v>2.24</v>
@@ -4429,19 +4429,19 @@
         <v>1.55</v>
       </c>
       <c r="AC25">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="AD25">
         <v>1.16</v>
       </c>
       <c r="AE25">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF25">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG25">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK25">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,52 +4547,52 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.96</v>
+        <v>2.7</v>
       </c>
       <c r="O26">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="P26">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="Q26">
-        <v>3.97</v>
+        <v>3.61</v>
       </c>
       <c r="R26">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="S26">
         <v>1.44</v>
       </c>
       <c r="T26">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="U26">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="V26">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W26">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X26">
         <v>1.04</v>
       </c>
       <c r="Y26">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="Z26">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="AA26">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="AB26">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AC26">
-        <v>4.65</v>
+        <v>4.75</v>
       </c>
       <c r="AD26">
         <v>1.12</v>
@@ -4601,10 +4601,10 @@
         <v>1</v>
       </c>
       <c r="AF26">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AG26">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.59</v>
+        <v>1.33</v>
       </c>
       <c r="AK26">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.55</v>
+        <v>3.06</v>
       </c>
       <c r="O28">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="P28">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -5036,16 +5036,16 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="O29">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P29">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="Q29">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="R29">
         <v>2.07</v>
@@ -5060,7 +5060,7 @@
         <v>2.8</v>
       </c>
       <c r="V29">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W29">
         <v>1.03</v>
@@ -5084,7 +5084,7 @@
         <v>3.34</v>
       </c>
       <c r="AD29">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE29">
         <v>1.05</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK29">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q30">
         <v>2.22</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="O32">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="P32">
-        <v>16</v>
+        <v>11.64</v>
       </c>
       <c r="Q32">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="R32">
-        <v>2.68</v>
+        <v>2.94</v>
       </c>
       <c r="S32">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="T32">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="U32">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="V32">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="W32">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X32">
         <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z32">
-        <v>5.75</v>
+        <v>6.05</v>
       </c>
       <c r="AA32">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AB32">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="AC32">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AD32">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AE32">
         <v>1.33</v>
       </c>
       <c r="AF32">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AG32">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AK32">
-        <v>4.55</v>
+        <v>5.3</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q33">
         <v>2.59</v>
@@ -5712,7 +5712,7 @@
         <v>2.45</v>
       </c>
       <c r="V33">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W33">
         <v>1.11</v>
@@ -5724,7 +5724,7 @@
         <v>1.22</v>
       </c>
       <c r="Z33">
-        <v>3.98</v>
+        <v>4.07</v>
       </c>
       <c r="AA33">
         <v>1.75</v>
@@ -5733,19 +5733,19 @@
         <v>2.05</v>
       </c>
       <c r="AC33">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AD33">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE33">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF33">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AG33">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="O34">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="P34">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="Q34">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="R34">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S34">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="T34">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U34">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="V34">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W34">
         <v>1.11</v>
       </c>
       <c r="X34">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z34">
-        <v>4.72</v>
+        <v>5</v>
       </c>
       <c r="AA34">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AB34">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AC34">
-        <v>2.43</v>
+        <v>2.51</v>
       </c>
       <c r="AD34">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AE34">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF34">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG34">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="O35">
         <v>3.6</v>
       </c>
       <c r="P35">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q35">
-        <v>2.63</v>
+        <v>2.52</v>
       </c>
       <c r="R35">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="S35">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T35">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="U35">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="V35">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="W35">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X35">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z35">
-        <v>4.55</v>
+        <v>4.9</v>
       </c>
       <c r="AA35">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB35">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="AC35">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="AD35">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="AE35">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF35">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG35">
-        <v>2.42</v>
+        <v>2.51</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AK35">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="N36">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="O36">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P36">
         <v>2</v>
@@ -6219,7 +6219,7 @@
         <v>1.82</v>
       </c>
       <c r="AB36">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC36">
         <v>2.97</v>
@@ -6228,7 +6228,7 @@
         <v>1.3</v>
       </c>
       <c r="AE36">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF36">
         <v>1.69</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.22</v>
+        <v>1.7</v>
       </c>
       <c r="AK36">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,31 +6340,31 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="O37">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P37">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="Q37">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="R37">
         <v>2.3</v>
       </c>
       <c r="S37">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T37">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="U37">
         <v>2.45</v>
       </c>
       <c r="V37">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W37">
         <v>1.06</v>
@@ -6376,28 +6376,28 @@
         <v>1.17</v>
       </c>
       <c r="Z37">
-        <v>3.98</v>
+        <v>3.95</v>
       </c>
       <c r="AA37">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AB37">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AC37">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AD37">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AE37">
         <v>1.11</v>
       </c>
       <c r="AF37">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AG37">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK37">
         <v>2.05</v>
@@ -6503,19 +6503,19 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="O38">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P38">
         <v>3.25</v>
       </c>
       <c r="Q38">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="R38">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="S38">
         <v>1.25</v>
@@ -6524,13 +6524,13 @@
         <v>3.5</v>
       </c>
       <c r="U38">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="V38">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W38">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X38">
         <v>1.01</v>
@@ -6539,13 +6539,13 @@
         <v>1.14</v>
       </c>
       <c r="Z38">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA38">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AB38">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="AC38">
         <v>2.43</v>
@@ -6554,13 +6554,13 @@
         <v>1.44</v>
       </c>
       <c r="AE38">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF38">
         <v>1.53</v>
       </c>
       <c r="AG38">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>1.22</v>
       </c>
       <c r="AK38">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="O39">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="P39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q39">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="R39">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="S39">
         <v>1.19</v>
       </c>
       <c r="T39">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="U39">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V39">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="W39">
         <v>1.17</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
         <v>1.08</v>
       </c>
       <c r="Z39">
-        <v>5.65</v>
+        <v>6</v>
       </c>
       <c r="AA39">
         <v>1.4</v>
       </c>
       <c r="AB39">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AC39">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AD39">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AE39">
         <v>1.24</v>
       </c>
       <c r="AF39">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AG39">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AK39">
-        <v>3.12</v>
+        <v>2.8</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="O40">
         <v>3.6</v>
       </c>
       <c r="P40">
-        <v>2.5</v>
+        <v>1.88</v>
       </c>
       <c r="Q40">
-        <v>2.88</v>
+        <v>3.66</v>
       </c>
       <c r="R40">
-        <v>2.39</v>
+        <v>2.46</v>
       </c>
       <c r="S40">
         <v>1.25</v>
       </c>
       <c r="T40">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="U40">
+        <v>2.31</v>
+      </c>
+      <c r="V40">
+        <v>1.57</v>
+      </c>
+      <c r="W40">
+        <v>1.14</v>
+      </c>
+      <c r="X40">
+        <v>1.01</v>
+      </c>
+      <c r="Y40">
+        <v>1.13</v>
+      </c>
+      <c r="Z40">
+        <v>4.66</v>
+      </c>
+      <c r="AA40">
+        <v>1.57</v>
+      </c>
+      <c r="AB40">
         <v>2.34</v>
       </c>
-      <c r="V40">
-        <v>1.51</v>
-      </c>
-      <c r="W40">
-        <v>1.09</v>
-      </c>
-      <c r="X40">
-        <v>1.02</v>
-      </c>
-      <c r="Y40">
+      <c r="AC40">
+        <v>2.44</v>
+      </c>
+      <c r="AD40">
+        <v>1.5</v>
+      </c>
+      <c r="AE40">
         <v>1.18</v>
-      </c>
-      <c r="Z40">
-        <v>4.53</v>
-      </c>
-      <c r="AA40">
-        <v>1.61</v>
-      </c>
-      <c r="AB40">
-        <v>2.3</v>
-      </c>
-      <c r="AC40">
-        <v>2.43</v>
-      </c>
-      <c r="AD40">
-        <v>1.44</v>
-      </c>
-      <c r="AE40">
-        <v>1.14</v>
       </c>
       <c r="AF40">
         <v>1.55</v>
       </c>
       <c r="AG40">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK40">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,58 +6992,58 @@
         </is>
       </c>
       <c r="N41">
-        <v>3.7</v>
+        <v>2.47</v>
       </c>
       <c r="O41">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P41">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="Q41">
-        <v>4.15</v>
+        <v>2.88</v>
       </c>
       <c r="R41">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="S41">
         <v>1.25</v>
       </c>
       <c r="T41">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="U41">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="V41">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="W41">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X41">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z41">
-        <v>4.6</v>
+        <v>4.59</v>
       </c>
       <c r="AA41">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AB41">
-        <v>2.33</v>
+        <v>2.21</v>
       </c>
       <c r="AC41">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="AD41">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AE41">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF41">
         <v>1.55</v>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK41">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q42">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="R42">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="S42">
         <v>1.29</v>
       </c>
       <c r="T42">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U42">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V42">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W42">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X42">
         <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="Z42">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AA42">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB42">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AC42">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="AD42">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AE42">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF42">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG42">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK42">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7327,10 +7327,10 @@
         <v>2.18</v>
       </c>
       <c r="Q43">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="R43">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="S43">
         <v>1.22</v>
@@ -7339,13 +7339,13 @@
         <v>4</v>
       </c>
       <c r="U43">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V43">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W43">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X43">
         <v>1.02</v>
@@ -7360,22 +7360,22 @@
         <v>1.45</v>
       </c>
       <c r="AB43">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AC43">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AD43">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AE43">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AF43">
         <v>1.38</v>
       </c>
       <c r="AG43">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>1.6</v>
       </c>
       <c r="AK43">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>4</v>
       </c>
       <c r="P44">
-        <v>4.48</v>
+        <v>4.65</v>
       </c>
       <c r="Q44">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="R44">
         <v>2.45</v>
@@ -7517,13 +7517,13 @@
         <v>1.1</v>
       </c>
       <c r="Z44">
-        <v>5.1</v>
+        <v>5.15</v>
       </c>
       <c r="AA44">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AB44">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AC44">
         <v>2.11</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AK44">
         <v>2.38</v>
@@ -7647,58 +7647,58 @@
         <v>2.37</v>
       </c>
       <c r="O45">
-        <v>3.06</v>
+        <v>3.3</v>
       </c>
       <c r="P45">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
       </c>
       <c r="R45">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="S45">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="T45">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="U45">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="V45">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W45">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X45">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y45">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="Z45">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AA45">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="AB45">
+        <v>1.79</v>
+      </c>
+      <c r="AC45">
+        <v>3.4</v>
+      </c>
+      <c r="AD45">
+        <v>1.29</v>
+      </c>
+      <c r="AE45">
+        <v>1.06</v>
+      </c>
+      <c r="AF45">
         <v>1.71</v>
-      </c>
-      <c r="AC45">
-        <v>3.5</v>
-      </c>
-      <c r="AD45">
-        <v>1.22</v>
-      </c>
-      <c r="AE45">
-        <v>1.08</v>
-      </c>
-      <c r="AF45">
-        <v>1.78</v>
       </c>
       <c r="AG45">
         <v>1.95</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AK45">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -8015,13 +8015,13 @@
         <v>2.02</v>
       </c>
       <c r="AC47">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="AD47">
         <v>1.55</v>
       </c>
       <c r="AE47">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AF47">
         <v>1.44</v>
@@ -8468,22 +8468,22 @@
         <v>2.25</v>
       </c>
       <c r="Q50">
-        <v>3.84</v>
+        <v>3.79</v>
       </c>
       <c r="R50">
         <v>1.83</v>
       </c>
       <c r="S50">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="T50">
         <v>2.34</v>
       </c>
       <c r="U50">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="V50">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W50">
         <v>1.03</v>
@@ -8510,13 +8510,13 @@
         <v>1.25</v>
       </c>
       <c r="AE50">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF50">
         <v>1.8</v>
       </c>
       <c r="AG50">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AK50">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="O51">
-        <v>3.52</v>
+        <v>3.85</v>
       </c>
       <c r="P51">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="Q51">
         <v>2.35</v>
@@ -8640,16 +8640,16 @@
         <v>1.2</v>
       </c>
       <c r="T51">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="U51">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="V51">
         <v>1.6</v>
       </c>
       <c r="W51">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X51">
         <v>1.02</v>
@@ -8664,7 +8664,7 @@
         <v>1.47</v>
       </c>
       <c r="AB51">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="AC51">
         <v>2.25</v>
@@ -8679,7 +8679,7 @@
         <v>1.48</v>
       </c>
       <c r="AG51">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8803,13 +8803,13 @@
         <v>1.41</v>
       </c>
       <c r="T52">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="U52">
         <v>2.79</v>
       </c>
       <c r="V52">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W52">
         <v>1.06</v>
@@ -8818,31 +8818,31 @@
         <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z52">
-        <v>2.97</v>
+        <v>3.22</v>
       </c>
       <c r="AA52">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AB52">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AC52">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AD52">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE52">
         <v>1.04</v>
       </c>
       <c r="AF52">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AG52">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U53">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z53">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AA53">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD53">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF53">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG53">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK53">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9437,25 +9437,25 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O56">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P56">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Q56">
         <v>2.66</v>
       </c>
       <c r="R56">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="S56">
         <v>1.28</v>
       </c>
       <c r="T56">
-        <v>3.12</v>
+        <v>3.5</v>
       </c>
       <c r="U56">
         <v>2.27</v>
@@ -9476,7 +9476,7 @@
         <v>3.94</v>
       </c>
       <c r="AA56">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AB56">
         <v>2.08</v>
@@ -9488,13 +9488,13 @@
         <v>1.41</v>
       </c>
       <c r="AE56">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AF56">
         <v>1.55</v>
       </c>
       <c r="AG56">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="O57">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="P57">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="Q57">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="R57">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="S57">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T57">
-        <v>2.88</v>
+        <v>2.61</v>
       </c>
       <c r="U57">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="V57">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W57">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X57">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y57">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z57">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="AA57">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AB57">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AC57">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AD57">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE57">
         <v>1.05</v>
       </c>
       <c r="AF57">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AG57">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK57">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9766,10 +9766,10 @@
         <v>1.36</v>
       </c>
       <c r="O58">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="P58">
-        <v>7.28</v>
+        <v>7.38</v>
       </c>
       <c r="Q58">
         <v>1.84</v>
@@ -9781,46 +9781,46 @@
         <v>1.15</v>
       </c>
       <c r="T58">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="U58">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="V58">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="W58">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X58">
         <v>1.01</v>
       </c>
       <c r="Y58">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z58">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AA58">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AB58">
-        <v>2.7</v>
+        <v>3.02</v>
       </c>
       <c r="AC58">
         <v>2.05</v>
       </c>
       <c r="AD58">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AE58">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AF58">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AG58">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
         <v>11</v>
       </c>
       <c r="Q59">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R59">
         <v>3</v>
@@ -9944,10 +9944,10 @@
         <v>1.22</v>
       </c>
       <c r="T59">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="U59">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="V59">
         <v>1.67</v>
@@ -9962,7 +9962,7 @@
         <v>1.1</v>
       </c>
       <c r="Z59">
-        <v>6.5</v>
+        <v>5.1</v>
       </c>
       <c r="AA59">
         <v>1.44</v>
@@ -9971,19 +9971,19 @@
         <v>2.62</v>
       </c>
       <c r="AC59">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AD59">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AE59">
         <v>1.25</v>
       </c>
       <c r="AF59">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AG59">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AK59">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10095,13 +10095,13 @@
         <v>3.85</v>
       </c>
       <c r="P60">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="Q60">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="R60">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="S60">
         <v>1.25</v>
@@ -10110,37 +10110,37 @@
         <v>3.4</v>
       </c>
       <c r="U60">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V60">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W60">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X60">
         <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z60">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AA60">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AB60">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AC60">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="AD60">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AE60">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF60">
         <v>1.57</v>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK60">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.89</v>
+        <v>2.35</v>
       </c>
       <c r="O61">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="P61">
-        <v>3.35</v>
+        <v>2.4</v>
       </c>
       <c r="Q61">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="R61">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="S61">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="T61">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="U61">
         <v>1.95</v>
       </c>
       <c r="V61">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="W61">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X61">
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Z61">
-        <v>6.06</v>
+        <v>5.75</v>
       </c>
       <c r="AA61">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AB61">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="AC61">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AD61">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AE61">
         <v>1.32</v>
       </c>
       <c r="AF61">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AG61">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK61">
-        <v>1.81</v>
+        <v>1.44</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.35</v>
+        <v>1.84</v>
       </c>
       <c r="O62">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="P62">
-        <v>2.4</v>
+        <v>3.35</v>
       </c>
       <c r="Q62">
-        <v>2.7</v>
+        <v>2.31</v>
       </c>
       <c r="R62">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="S62">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T62">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="U62">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V62">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="W62">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Z62">
-        <v>5.85</v>
+        <v>6.46</v>
       </c>
       <c r="AA62">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AB62">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="AC62">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AD62">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AE62">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AF62">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AG62">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK62">
-        <v>1.45</v>
+        <v>1.8</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>1.71</v>
       </c>
       <c r="O63">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P63">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Q63">
         <v>2.16</v>
@@ -10596,16 +10596,16 @@
         <v>1.25</v>
       </c>
       <c r="T63">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="U63">
         <v>2.25</v>
       </c>
       <c r="V63">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="W63">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X63">
         <v>1.01</v>
@@ -10614,16 +10614,16 @@
         <v>1.14</v>
       </c>
       <c r="Z63">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="AA63">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AB63">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="AC63">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="AD63">
         <v>1.48</v>
@@ -10750,55 +10750,55 @@
         <v>3.85</v>
       </c>
       <c r="Q64">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R64">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S64">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T64">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U64">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="V64">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W64">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X64">
         <v>1.02</v>
       </c>
       <c r="Y64">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z64">
-        <v>3.08</v>
+        <v>2.5</v>
       </c>
       <c r="AA64">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AB64">
         <v>1.75</v>
       </c>
       <c r="AC64">
-        <v>3.42</v>
+        <v>2.8</v>
       </c>
       <c r="AD64">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE64">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF64">
         <v>1.8</v>
       </c>
       <c r="AG64">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK64">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="O65">
         <v>4.2</v>
       </c>
       <c r="P65">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="Q65">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="R65">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="S65">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T65">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="U65">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="V65">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W65">
         <v>1.06</v>
       </c>
       <c r="X65">
+        <v>1.03</v>
+      </c>
+      <c r="Y65">
+        <v>1.36</v>
+      </c>
+      <c r="Z65">
+        <v>2.98</v>
+      </c>
+      <c r="AA65">
+        <v>2.05</v>
+      </c>
+      <c r="AB65">
+        <v>1.66</v>
+      </c>
+      <c r="AC65">
+        <v>3.58</v>
+      </c>
+      <c r="AD65">
+        <v>1.21</v>
+      </c>
+      <c r="AE65">
         <v>1.04</v>
       </c>
-      <c r="Y65">
-        <v>1.35</v>
-      </c>
-      <c r="Z65">
-        <v>2.74</v>
-      </c>
-      <c r="AA65">
-        <v>2.11</v>
-      </c>
-      <c r="AB65">
-        <v>1.62</v>
-      </c>
-      <c r="AC65">
-        <v>3.72</v>
-      </c>
-      <c r="AD65">
-        <v>1.2</v>
-      </c>
-      <c r="AE65">
-        <v>1.03</v>
-      </c>
       <c r="AF65">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AG65">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK65">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="O66">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="P66">
-        <v>3.2</v>
+        <v>2.78</v>
       </c>
       <c r="Q66">
         <v>2.74</v>
@@ -11088,34 +11088,34 @@
         <v>2.92</v>
       </c>
       <c r="U66">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="V66">
         <v>1.4</v>
       </c>
       <c r="W66">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X66">
         <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z66">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="AA66">
         <v>1.83</v>
       </c>
       <c r="AB66">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AC66">
         <v>2.97</v>
       </c>
       <c r="AD66">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE66">
         <v>1.08</v>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AK66">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11230,25 +11230,25 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="O67">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="P67">
         <v>2.52</v>
       </c>
       <c r="Q67">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="R67">
         <v>2.12</v>
       </c>
       <c r="S67">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T67">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="U67">
         <v>2.5</v>
@@ -11260,22 +11260,22 @@
         <v>1.07</v>
       </c>
       <c r="X67">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y67">
         <v>1.25</v>
       </c>
       <c r="Z67">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AA67">
-        <v>1.84</v>
+        <v>1.74</v>
       </c>
       <c r="AB67">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AC67">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AD67">
         <v>1.33</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O68">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="P68">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
       </c>
       <c r="R68">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="S68">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="T68">
-        <v>3.14</v>
+        <v>2.71</v>
       </c>
       <c r="U68">
-        <v>2.4</v>
+        <v>2.87</v>
       </c>
       <c r="V68">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="W68">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X68">
         <v>1.02</v>
       </c>
       <c r="Y68">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="Z68">
-        <v>3.91</v>
+        <v>3.05</v>
       </c>
       <c r="AA68">
-        <v>1.73</v>
+        <v>2.06</v>
       </c>
       <c r="AB68">
-        <v>2.02</v>
+        <v>1.67</v>
       </c>
       <c r="AC68">
-        <v>2.93</v>
+        <v>4.03</v>
       </c>
       <c r="AD68">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="AE68">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AF68">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AG68">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AK68">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="O69">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="P69">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="Q69">
-        <v>2.92</v>
+        <v>2.81</v>
       </c>
       <c r="R69">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="S69">
+        <v>1.31</v>
+      </c>
+      <c r="T69">
+        <v>3.08</v>
+      </c>
+      <c r="U69">
+        <v>2.42</v>
+      </c>
+      <c r="V69">
         <v>1.45</v>
       </c>
-      <c r="T69">
-        <v>2.5</v>
-      </c>
-      <c r="U69">
-        <v>2.86</v>
-      </c>
-      <c r="V69">
-        <v>1.35</v>
-      </c>
       <c r="W69">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X69">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y69">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="Z69">
-        <v>3.04</v>
+        <v>3.84</v>
       </c>
       <c r="AA69">
-        <v>2.16</v>
+        <v>1.77</v>
       </c>
       <c r="AB69">
-        <v>1.66</v>
+        <v>1.99</v>
       </c>
       <c r="AC69">
-        <v>3.42</v>
+        <v>3.03</v>
       </c>
       <c r="AD69">
-        <v>1.23</v>
+        <v>1.38</v>
       </c>
       <c r="AE69">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AF69">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AG69">
-        <v>1.93</v>
+        <v>2.18</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AK69">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11728,19 +11728,19 @@
         <v>3.9</v>
       </c>
       <c r="Q70">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="R70">
         <v>2.2</v>
       </c>
       <c r="S70">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T70">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="U70">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="V70">
         <v>1.44</v>
@@ -11752,28 +11752,28 @@
         <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z70">
-        <v>3.83</v>
+        <v>3.86</v>
       </c>
       <c r="AA70">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB70">
         <v>2</v>
       </c>
       <c r="AC70">
-        <v>3.09</v>
+        <v>3.13</v>
       </c>
       <c r="AD70">
         <v>1.36</v>
       </c>
       <c r="AE70">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF70">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG70">
         <v>2.05</v>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK70">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="O71">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="P71">
-        <v>2.65</v>
+        <v>3.25</v>
       </c>
       <c r="Q71">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
       <c r="R71">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="S71">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T71">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="U71">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
       <c r="V71">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W71">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X71">
         <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="Z71">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="AA71">
-        <v>2.06</v>
+        <v>2.17</v>
       </c>
       <c r="AB71">
         <v>1.67</v>
       </c>
       <c r="AC71">
-        <v>3.99</v>
+        <v>3.42</v>
       </c>
       <c r="AD71">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE71">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF71">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AG71">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>1.29</v>
       </c>
       <c r="AK71">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12045,10 +12045,10 @@
         </is>
       </c>
       <c r="N72">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="O72">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P72">
         <v>2.02</v>
@@ -12060,10 +12060,10 @@
         <v>2.11</v>
       </c>
       <c r="S72">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T72">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="U72">
         <v>2.63</v>
@@ -12075,31 +12075,31 @@
         <v>1.08</v>
       </c>
       <c r="X72">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y72">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z72">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AA72">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AB72">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AC72">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AD72">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE72">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF72">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG72">
         <v>2.15</v>
@@ -12226,22 +12226,22 @@
         <v>1.22</v>
       </c>
       <c r="T73">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="U73">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="V73">
         <v>1.6</v>
       </c>
       <c r="W73">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X73">
         <v>1.02</v>
       </c>
       <c r="Y73">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z73">
         <v>5</v>
@@ -12253,16 +12253,16 @@
         <v>2.45</v>
       </c>
       <c r="AC73">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="AD73">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AE73">
         <v>1.17</v>
       </c>
       <c r="AF73">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AG73">
         <v>1.91</v>
@@ -12281,7 +12281,7 @@
         <v>1.06</v>
       </c>
       <c r="AK73">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12380,55 +12380,55 @@
         <v>0</v>
       </c>
       <c r="Q74">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="S74">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="T74">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U74">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V74">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="W74">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X74">
         <v>0</v>
       </c>
       <c r="Y74">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z74">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AA74">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AC74">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AD74">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AE74">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AF74">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AG74">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,7 +12441,7 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK74">
         <v>0</v>
@@ -12543,25 +12543,25 @@
         <v>0</v>
       </c>
       <c r="Q75">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R75">
-        <v>2.42</v>
+        <v>2.22</v>
       </c>
       <c r="S75">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T75">
         <v>3.25</v>
       </c>
       <c r="U75">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="V75">
         <v>1.5</v>
       </c>
       <c r="W75">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X75">
         <v>1.02</v>
@@ -12570,7 +12570,7 @@
         <v>1.16</v>
       </c>
       <c r="Z75">
-        <v>4.05</v>
+        <v>4.5</v>
       </c>
       <c r="AA75">
         <v>1.61</v>
@@ -12579,35 +12579,35 @@
         <v>2.13</v>
       </c>
       <c r="AC75">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="AD75">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AE75">
+        <v>1.14</v>
+      </c>
+      <c r="AF75">
+        <v>1.55</v>
+      </c>
+      <c r="AG75">
+        <v>2.3</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ75">
         <v>1.18</v>
       </c>
-      <c r="AF75">
-        <v>1.56</v>
-      </c>
-      <c r="AG75">
-        <v>2.25</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ75">
-        <v>1.2</v>
-      </c>
       <c r="AK75">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12715,7 +12715,7 @@
         <v>1.29</v>
       </c>
       <c r="T76">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U76">
         <v>2.32</v>
@@ -12733,19 +12733,19 @@
         <v>1.19</v>
       </c>
       <c r="Z76">
-        <v>4.15</v>
+        <v>4.4</v>
       </c>
       <c r="AA76">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AB76">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AC76">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="AD76">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AE76">
         <v>1.19</v>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK76">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="O77">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P77">
-        <v>3.71</v>
+        <v>5.35</v>
       </c>
       <c r="Q77">
         <v>2.3</v>
@@ -12878,10 +12878,10 @@
         <v>1.46</v>
       </c>
       <c r="T77">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="U77">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="V77">
         <v>1.3</v>
@@ -12896,19 +12896,19 @@
         <v>1.35</v>
       </c>
       <c r="Z77">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="AA77">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="AB77">
         <v>1.63</v>
       </c>
       <c r="AC77">
-        <v>3.9</v>
+        <v>4.16</v>
       </c>
       <c r="AD77">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE77">
         <v>1.02</v>
@@ -13023,10 +13023,10 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="O78">
-        <v>4.2</v>
+        <v>4.35</v>
       </c>
       <c r="P78">
         <v>4.2</v>
@@ -13038,10 +13038,10 @@
         <v>2.39</v>
       </c>
       <c r="S78">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T78">
-        <v>3.48</v>
+        <v>4</v>
       </c>
       <c r="U78">
         <v>2</v>
@@ -13056,22 +13056,22 @@
         <v>1.02</v>
       </c>
       <c r="Y78">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z78">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="AA78">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB78">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="AC78">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AD78">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AE78">
         <v>1.29</v>
@@ -13080,7 +13080,7 @@
         <v>1.44</v>
       </c>
       <c r="AG78">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AK78">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13189,61 +13189,61 @@
         <v>1.67</v>
       </c>
       <c r="O79">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P79">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="Q79">
         <v>2.04</v>
       </c>
       <c r="R79">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="S79">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T79">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="U79">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="V79">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="W79">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X79">
         <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Z79">
-        <v>5.25</v>
+        <v>6.53</v>
       </c>
       <c r="AA79">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AB79">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="AC79">
-        <v>2.12</v>
+        <v>1.91</v>
       </c>
       <c r="AD79">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AE79">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AF79">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AG79">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK79">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13349,19 +13349,19 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="O80">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P80">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q80">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="R80">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="S80">
         <v>1.18</v>
@@ -13385,10 +13385,10 @@
         <v>1.05</v>
       </c>
       <c r="Z80">
-        <v>6.4</v>
+        <v>6.45</v>
       </c>
       <c r="AA80">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB80">
         <v>2.97</v>
@@ -13400,7 +13400,7 @@
         <v>1.88</v>
       </c>
       <c r="AE80">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AF80">
         <v>1.31</v>
@@ -13422,7 +13422,7 @@
         <v>1.25</v>
       </c>
       <c r="AK80">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13533,10 +13533,10 @@
         <v>4.1</v>
       </c>
       <c r="U81">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="V81">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="W81">
         <v>1.25</v>
@@ -13545,28 +13545,28 @@
         <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z81">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AA81">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AB81">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AC81">
         <v>1.79</v>
       </c>
       <c r="AD81">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AE81">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AF81">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AG81">
         <v>3.4</v>
@@ -13681,25 +13681,25 @@
         <v>3.6</v>
       </c>
       <c r="P82">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q82">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="R82">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S82">
         <v>1.22</v>
       </c>
       <c r="T82">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U82">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="V82">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W82">
         <v>1.13</v>
@@ -13711,22 +13711,22 @@
         <v>1.08</v>
       </c>
       <c r="Z82">
-        <v>5.45</v>
+        <v>5.55</v>
       </c>
       <c r="AA82">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB82">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AC82">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="AD82">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AE82">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AF82">
         <v>1.4</v>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AK82">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13838,19 +13838,19 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="O83">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="P83">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="Q83">
-        <v>3.26</v>
+        <v>3.06</v>
       </c>
       <c r="R83">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="S83">
         <v>1.2</v>
@@ -13862,7 +13862,7 @@
         <v>2.1</v>
       </c>
       <c r="V83">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="W83">
         <v>1.16</v>
@@ -13874,16 +13874,16 @@
         <v>1.09</v>
       </c>
       <c r="Z83">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="AA83">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AB83">
         <v>2.6</v>
       </c>
       <c r="AC83">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="AD83">
         <v>1.67</v>
@@ -13895,7 +13895,7 @@
         <v>1.4</v>
       </c>
       <c r="AG83">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AK83">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14001,31 +14001,31 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="O84">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P84">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="Q84">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="R84">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="S84">
         <v>1.22</v>
       </c>
       <c r="T84">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="U84">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="V84">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="W84">
         <v>1.14</v>
@@ -14034,7 +14034,7 @@
         <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z84">
         <v>5.5</v>
@@ -14046,13 +14046,13 @@
         <v>2.46</v>
       </c>
       <c r="AC84">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="AD84">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AE84">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF84">
         <v>1.49</v>
@@ -14074,7 +14074,7 @@
         <v>1.2</v>
       </c>
       <c r="AK84">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14170,58 +14170,58 @@
         <v>3.72</v>
       </c>
       <c r="P85">
-        <v>2.41</v>
+        <v>2.47</v>
       </c>
       <c r="Q85">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="R85">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S85">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T85">
-        <v>3.24</v>
+        <v>3.32</v>
       </c>
       <c r="U85">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="V85">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W85">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X85">
         <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z85">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AA85">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB85">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AC85">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="AD85">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AE85">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF85">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AG85">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>1.3</v>
       </c>
       <c r="AK85">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14327,22 +14327,22 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="O86">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P86">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="Q86">
         <v>3.5</v>
       </c>
       <c r="R86">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="S86">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T86">
         <v>3.8</v>
@@ -14354,28 +14354,28 @@
         <v>1.65</v>
       </c>
       <c r="W86">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X86">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z86">
-        <v>4.95</v>
+        <v>6.5</v>
       </c>
       <c r="AA86">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AB86">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AC86">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AD86">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AE86">
         <v>1.25</v>
@@ -14384,7 +14384,7 @@
         <v>1.44</v>
       </c>
       <c r="AG86">
-        <v>2.61</v>
+        <v>2.69</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>1.22</v>
       </c>
       <c r="AK86">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14490,31 +14490,31 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="O87">
         <v>3.6</v>
       </c>
       <c r="P87">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="Q87">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="R87">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S87">
         <v>1.2</v>
       </c>
       <c r="T87">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="U87">
         <v>2.08</v>
       </c>
       <c r="V87">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W87">
         <v>1.14</v>
@@ -14526,7 +14526,7 @@
         <v>1.1</v>
       </c>
       <c r="Z87">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AA87">
         <v>1.44</v>
@@ -14535,10 +14535,10 @@
         <v>2.43</v>
       </c>
       <c r="AC87">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AD87">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AE87">
         <v>1.26</v>
@@ -14563,7 +14563,7 @@
         <v>1.21</v>
       </c>
       <c r="AK87">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14653,7 +14653,7 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="O88">
         <v>3.25</v>
@@ -14668,19 +14668,19 @@
         <v>2.1</v>
       </c>
       <c r="S88">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T88">
         <v>2.75</v>
       </c>
       <c r="U88">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="V88">
         <v>1.41</v>
       </c>
       <c r="W88">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X88">
         <v>1.02</v>
@@ -14689,28 +14689,28 @@
         <v>1.26</v>
       </c>
       <c r="Z88">
-        <v>3.46</v>
+        <v>3.49</v>
       </c>
       <c r="AA88">
         <v>1.92</v>
       </c>
       <c r="AB88">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AC88">
         <v>3.05</v>
       </c>
       <c r="AD88">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE88">
         <v>1.08</v>
       </c>
       <c r="AF88">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AG88">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14825,55 +14825,55 @@
         <v>2.05</v>
       </c>
       <c r="Q89">
-        <v>4.1</v>
+        <v>4.16</v>
       </c>
       <c r="R89">
         <v>2</v>
       </c>
       <c r="S89">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="T89">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="U89">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V89">
         <v>1.36</v>
       </c>
       <c r="W89">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X89">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y89">
         <v>1.33</v>
       </c>
       <c r="Z89">
-        <v>3.21</v>
+        <v>3.1</v>
       </c>
       <c r="AA89">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AB89">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC89">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="AD89">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE89">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF89">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AG89">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,7 +14886,7 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK89">
         <v>1.25</v>
@@ -14979,65 +14979,65 @@
         </is>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q90">
         <v>1.91</v>
       </c>
       <c r="R90">
-        <v>2.32</v>
+        <v>2.69</v>
       </c>
       <c r="S90">
         <v>1.22</v>
       </c>
       <c r="T90">
-        <v>3.48</v>
+        <v>3.75</v>
       </c>
       <c r="U90">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="V90">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W90">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X90">
         <v>1.02</v>
       </c>
       <c r="Y90">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z90">
-        <v>5.5</v>
+        <v>5.76</v>
       </c>
       <c r="AA90">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AB90">
+        <v>2.49</v>
+      </c>
+      <c r="AC90">
+        <v>2.14</v>
+      </c>
+      <c r="AD90">
+        <v>1.68</v>
+      </c>
+      <c r="AE90">
+        <v>1.26</v>
+      </c>
+      <c r="AF90">
+        <v>1.53</v>
+      </c>
+      <c r="AG90">
         <v>2.38</v>
       </c>
-      <c r="AC90">
-        <v>2.23</v>
-      </c>
-      <c r="AD90">
-        <v>1.6</v>
-      </c>
-      <c r="AE90">
-        <v>1.23</v>
-      </c>
-      <c r="AF90">
-        <v>1.55</v>
-      </c>
-      <c r="AG90">
-        <v>2.25</v>
-      </c>
       <c r="AH90" t="inlineStr">
         <is>
           <t>[]</t>
@@ -15049,7 +15049,7 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK90">
         <v>2.4</v>
@@ -15145,61 +15145,61 @@
         <v>2.35</v>
       </c>
       <c r="O91">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P91">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
       </c>
       <c r="R91">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="S91">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="T91">
-        <v>3.18</v>
+        <v>3.24</v>
       </c>
       <c r="U91">
-        <v>2.62</v>
+        <v>2.34</v>
       </c>
       <c r="V91">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="W91">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X91">
         <v>1.02</v>
       </c>
       <c r="Y91">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z91">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AA91">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AB91">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC91">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AD91">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AE91">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF91">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="AG91">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK91">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15305,58 +15305,58 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="O92">
         <v>3.8</v>
       </c>
       <c r="P92">
-        <v>4.53</v>
+        <v>4</v>
       </c>
       <c r="Q92">
         <v>2.1</v>
       </c>
       <c r="R92">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="S92">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T92">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U92">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="V92">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="W92">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X92">
         <v>1.02</v>
       </c>
       <c r="Y92">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z92">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AA92">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AB92">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="AC92">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AD92">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AE92">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF92">
         <v>1.57</v>
@@ -15375,7 +15375,7 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AK92">
         <v>2.15</v>
@@ -15468,19 +15468,19 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="O93">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P93">
         <v>19</v>
       </c>
       <c r="Q93">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="R93">
-        <v>4.04</v>
+        <v>4.08</v>
       </c>
       <c r="S93">
         <v>1.09</v>
@@ -15489,13 +15489,13 @@
         <v>6.7</v>
       </c>
       <c r="U93">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="V93">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="W93">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X93">
         <v>1</v>
@@ -15504,22 +15504,22 @@
         <v>1.03</v>
       </c>
       <c r="Z93">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AA93">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AB93">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AC93">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AD93">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="AE93">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AF93">
         <v>1.83</v>
@@ -15538,7 +15538,7 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AK93">
         <v>9</v>
@@ -15637,7 +15637,7 @@
         <v>3.35</v>
       </c>
       <c r="P94">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="Q94">
         <v>3.36</v>
@@ -15649,7 +15649,7 @@
         <v>1.3</v>
       </c>
       <c r="T94">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="U94">
         <v>2.4</v>
@@ -15661,25 +15661,25 @@
         <v>1.12</v>
       </c>
       <c r="X94">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y94">
         <v>1.2</v>
       </c>
       <c r="Z94">
-        <v>4.5</v>
+        <v>3.98</v>
       </c>
       <c r="AA94">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AB94">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AC94">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="AD94">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AE94">
         <v>1.14</v>
@@ -15688,7 +15688,7 @@
         <v>1.53</v>
       </c>
       <c r="AG94">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,7 +15701,7 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AK94">
         <v>1.36</v>
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="O95">
-        <v>3.42</v>
+        <v>3.65</v>
       </c>
       <c r="P95">
-        <v>3.06</v>
+        <v>3.15</v>
       </c>
       <c r="Q95">
         <v>2.55</v>
@@ -15824,7 +15824,7 @@
         <v>1.13</v>
       </c>
       <c r="X95">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y95">
         <v>1.13</v>
@@ -15833,13 +15833,13 @@
         <v>4.6</v>
       </c>
       <c r="AA95">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AB95">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="AC95">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AD95">
         <v>1.62</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.37</v>
+        <v>3.8</v>
       </c>
       <c r="O98">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="P98">
-        <v>5.8</v>
+        <v>1.78</v>
       </c>
       <c r="Q98">
-        <v>1.83</v>
+        <v>4.4</v>
       </c>
       <c r="R98">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="S98">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="T98">
-        <v>3.72</v>
+        <v>3.2</v>
       </c>
       <c r="U98">
-        <v>2.22</v>
+        <v>2.54</v>
       </c>
       <c r="V98">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="W98">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X98">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y98">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="Z98">
-        <v>4.85</v>
+        <v>3.79</v>
       </c>
       <c r="AA98">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AB98">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="AC98">
-        <v>2.33</v>
+        <v>2.83</v>
       </c>
       <c r="AD98">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="AE98">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AF98">
         <v>1.67</v>
       </c>
       <c r="AG98">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="AK98">
-        <v>2.58</v>
+        <v>1.16</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,80 +16446,80 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.47</v>
+        <v>2.24</v>
       </c>
       <c r="O99">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="P99">
-        <v>5.4</v>
+        <v>3.1</v>
       </c>
       <c r="Q99">
-        <v>1.98</v>
+        <v>2.81</v>
       </c>
       <c r="R99">
-        <v>2.69</v>
+        <v>2.03</v>
       </c>
       <c r="S99">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="T99">
-        <v>3.75</v>
+        <v>2.77</v>
       </c>
       <c r="U99">
-        <v>2.1</v>
+        <v>2.61</v>
       </c>
       <c r="V99">
+        <v>1.39</v>
+      </c>
+      <c r="W99">
+        <v>1.07</v>
+      </c>
+      <c r="X99">
+        <v>1.01</v>
+      </c>
+      <c r="Y99">
+        <v>1.25</v>
+      </c>
+      <c r="Z99">
+        <v>3.49</v>
+      </c>
+      <c r="AA99">
+        <v>1.9</v>
+      </c>
+      <c r="AB99">
+        <v>1.87</v>
+      </c>
+      <c r="AC99">
+        <v>3.37</v>
+      </c>
+      <c r="AD99">
+        <v>1.3</v>
+      </c>
+      <c r="AE99">
+        <v>1.1</v>
+      </c>
+      <c r="AF99">
+        <v>1.69</v>
+      </c>
+      <c r="AG99">
+        <v>2</v>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ99">
+        <v>1.25</v>
+      </c>
+      <c r="AK99">
         <v>1.62</v>
-      </c>
-      <c r="W99">
-        <v>1.14</v>
-      </c>
-      <c r="X99">
-        <v>1.02</v>
-      </c>
-      <c r="Y99">
-        <v>1.15</v>
-      </c>
-      <c r="Z99">
-        <v>4.8</v>
-      </c>
-      <c r="AA99">
-        <v>1.46</v>
-      </c>
-      <c r="AB99">
-        <v>2.55</v>
-      </c>
-      <c r="AC99">
-        <v>2.15</v>
-      </c>
-      <c r="AD99">
-        <v>1.6</v>
-      </c>
-      <c r="AE99">
-        <v>1.22</v>
-      </c>
-      <c r="AF99">
-        <v>1.58</v>
-      </c>
-      <c r="AG99">
-        <v>2.17</v>
-      </c>
-      <c r="AH99" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI99" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ99">
-        <v>1.07</v>
-      </c>
-      <c r="AK99">
-        <v>2.33</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,65 +16609,65 @@
         </is>
       </c>
       <c r="N100">
+        <v>2.15</v>
+      </c>
+      <c r="O100">
+        <v>3.25</v>
+      </c>
+      <c r="P100">
+        <v>3.05</v>
+      </c>
+      <c r="Q100">
+        <v>2.64</v>
+      </c>
+      <c r="R100">
+        <v>2.08</v>
+      </c>
+      <c r="S100">
+        <v>1.35</v>
+      </c>
+      <c r="T100">
+        <v>2.76</v>
+      </c>
+      <c r="U100">
+        <v>2.63</v>
+      </c>
+      <c r="V100">
+        <v>1.44</v>
+      </c>
+      <c r="W100">
+        <v>1.05</v>
+      </c>
+      <c r="X100">
+        <v>1.01</v>
+      </c>
+      <c r="Y100">
+        <v>1.21</v>
+      </c>
+      <c r="Z100">
+        <v>3.58</v>
+      </c>
+      <c r="AA100">
+        <v>1.8</v>
+      </c>
+      <c r="AB100">
+        <v>2</v>
+      </c>
+      <c r="AC100">
+        <v>2.88</v>
+      </c>
+      <c r="AD100">
+        <v>1.32</v>
+      </c>
+      <c r="AE100">
+        <v>1.08</v>
+      </c>
+      <c r="AF100">
+        <v>1.62</v>
+      </c>
+      <c r="AG100">
         <v>2.1</v>
       </c>
-      <c r="O100">
-        <v>3.2</v>
-      </c>
-      <c r="P100">
-        <v>3.1</v>
-      </c>
-      <c r="Q100">
-        <v>2.78</v>
-      </c>
-      <c r="R100">
-        <v>2.05</v>
-      </c>
-      <c r="S100">
-        <v>1.33</v>
-      </c>
-      <c r="T100">
-        <v>2.84</v>
-      </c>
-      <c r="U100">
-        <v>2.58</v>
-      </c>
-      <c r="V100">
-        <v>1.4</v>
-      </c>
-      <c r="W100">
-        <v>1.07</v>
-      </c>
-      <c r="X100">
-        <v>1</v>
-      </c>
-      <c r="Y100">
-        <v>1.24</v>
-      </c>
-      <c r="Z100">
-        <v>3.34</v>
-      </c>
-      <c r="AA100">
-        <v>1.87</v>
-      </c>
-      <c r="AB100">
-        <v>1.9</v>
-      </c>
-      <c r="AC100">
-        <v>3.04</v>
-      </c>
-      <c r="AD100">
-        <v>1.29</v>
-      </c>
-      <c r="AE100">
-        <v>1.07</v>
-      </c>
-      <c r="AF100">
-        <v>1.67</v>
-      </c>
-      <c r="AG100">
-        <v>2.05</v>
-      </c>
       <c r="AH100" t="inlineStr">
         <is>
           <t>[]</t>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK100">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>3.8</v>
+        <v>1.41</v>
       </c>
       <c r="O101">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="P101">
-        <v>1.78</v>
+        <v>5.5</v>
       </c>
       <c r="Q101">
-        <v>4.2</v>
+        <v>1.86</v>
       </c>
       <c r="R101">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="S101">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="T101">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="U101">
-        <v>2.54</v>
+        <v>2.17</v>
       </c>
       <c r="V101">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="W101">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X101">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y101">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z101">
-        <v>3.77</v>
+        <v>5.5</v>
       </c>
       <c r="AA101">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AB101">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="AC101">
-        <v>2.83</v>
+        <v>2.24</v>
       </c>
       <c r="AD101">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="AE101">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="AF101">
         <v>1.67</v>
       </c>
       <c r="AG101">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AK101">
-        <v>1.16</v>
+        <v>2.66</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.1</v>
+        <v>1.47</v>
       </c>
       <c r="O102">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="P102">
-        <v>2.9</v>
+        <v>5.4</v>
       </c>
       <c r="Q102">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="R102">
-        <v>2.05</v>
+        <v>2.66</v>
       </c>
       <c r="S102">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T102">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="U102">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="V102">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="W102">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="X102">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y102">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z102">
-        <v>3.72</v>
+        <v>4.7</v>
       </c>
       <c r="AA102">
-        <v>1.75</v>
+        <v>1.47</v>
       </c>
       <c r="AB102">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="AC102">
-        <v>2.81</v>
+        <v>2.18</v>
       </c>
       <c r="AD102">
-        <v>1.33</v>
+        <v>1.58</v>
       </c>
       <c r="AE102">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="AF102">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AG102">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="AK102">
-        <v>1.6</v>
+        <v>2.29</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17101,61 +17101,61 @@
         <v>3</v>
       </c>
       <c r="O103">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="P103">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="Q103">
         <v>3.4</v>
       </c>
       <c r="R103">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="S103">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T103">
-        <v>2.79</v>
+        <v>3.02</v>
       </c>
       <c r="U103">
-        <v>2.51</v>
+        <v>2.7</v>
       </c>
       <c r="V103">
         <v>1.45</v>
       </c>
       <c r="W103">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X103">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y103">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z103">
-        <v>3.7</v>
+        <v>3.88</v>
       </c>
       <c r="AA103">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AB103">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AC103">
-        <v>3.07</v>
+        <v>3.03</v>
       </c>
       <c r="AD103">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE103">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF103">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AG103">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AK103">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="O104">
-        <v>3.5</v>
+        <v>3.63</v>
       </c>
       <c r="P104">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -17300,10 +17300,10 @@
         <v>0</v>
       </c>
       <c r="AA104">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AB104">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC104">
         <v>0</v>
@@ -17424,13 +17424,13 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="O105">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="P105">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="Q105">
         <v>2.97</v>
@@ -17442,37 +17442,37 @@
         <v>1.22</v>
       </c>
       <c r="T105">
-        <v>3.94</v>
+        <v>3.96</v>
       </c>
       <c r="U105">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="V105">
         <v>1.69</v>
       </c>
       <c r="W105">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X105">
         <v>1.01</v>
       </c>
       <c r="Y105">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z105">
         <v>6</v>
       </c>
       <c r="AA105">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AB105">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AC105">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AD105">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AE105">
         <v>1.25</v>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.62</v>
+        <v>1.22</v>
       </c>
       <c r="AK105">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17587,16 +17587,16 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="O106">
         <v>3</v>
       </c>
       <c r="P106">
-        <v>3.8</v>
+        <v>3.99</v>
       </c>
       <c r="Q106">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="R106">
         <v>1.94</v>
@@ -17605,16 +17605,16 @@
         <v>1.44</v>
       </c>
       <c r="T106">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="U106">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="V106">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W106">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X106">
         <v>1.04</v>
@@ -17629,7 +17629,7 @@
         <v>2.22</v>
       </c>
       <c r="AB106">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AC106">
         <v>4</v>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK106">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -18076,10 +18076,10 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="O109">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P109">
         <v>4.2</v>
@@ -18088,13 +18088,13 @@
         <v>2.45</v>
       </c>
       <c r="R109">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="S109">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T109">
-        <v>2.73</v>
+        <v>2.76</v>
       </c>
       <c r="U109">
         <v>2.56</v>
@@ -18103,22 +18103,22 @@
         <v>1.44</v>
       </c>
       <c r="W109">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X109">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y109">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z109">
-        <v>3.3</v>
+        <v>3.72</v>
       </c>
       <c r="AA109">
+        <v>1.8</v>
+      </c>
+      <c r="AB109">
         <v>1.91</v>
-      </c>
-      <c r="AB109">
-        <v>2.03</v>
       </c>
       <c r="AC109">
         <v>3.1</v>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AK109">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18242,13 +18242,13 @@
         <v>1.85</v>
       </c>
       <c r="O110">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P110">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q110">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="R110">
         <v>2.2</v>
@@ -18257,7 +18257,7 @@
         <v>1.3</v>
       </c>
       <c r="T110">
-        <v>2.78</v>
+        <v>3.15</v>
       </c>
       <c r="U110">
         <v>2.63</v>
@@ -18272,31 +18272,31 @@
         <v>1.02</v>
       </c>
       <c r="Y110">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z110">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="AA110">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AB110">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AC110">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AD110">
         <v>1.37</v>
       </c>
       <c r="AE110">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF110">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AG110">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,7 +18309,7 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK110">
         <v>1.87</v>
@@ -18402,25 +18402,25 @@
         </is>
       </c>
       <c r="N111">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O111">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="P111">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q111">
-        <v>3.32</v>
+        <v>2.92</v>
       </c>
       <c r="R111">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="S111">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="T111">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="U111">
         <v>3.52</v>
@@ -18429,16 +18429,16 @@
         <v>1.22</v>
       </c>
       <c r="W111">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X111">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y111">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="Z111">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="AA111">
         <v>2.63</v>
@@ -18447,19 +18447,19 @@
         <v>1.47</v>
       </c>
       <c r="AC111">
-        <v>5.5</v>
+        <v>5.15</v>
       </c>
       <c r="AD111">
         <v>1.14</v>
       </c>
       <c r="AE111">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF111">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="AG111">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AK111">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18565,7 +18565,7 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="O112">
         <v>4</v>
@@ -18580,10 +18580,10 @@
         <v>2.25</v>
       </c>
       <c r="S112">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T112">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="U112">
         <v>2.75</v>
@@ -18592,7 +18592,7 @@
         <v>1.4</v>
       </c>
       <c r="W112">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X112">
         <v>1</v>
@@ -18601,13 +18601,13 @@
         <v>1.29</v>
       </c>
       <c r="Z112">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AA112">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AB112">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AC112">
         <v>3.08</v>
@@ -18619,10 +18619,10 @@
         <v>1.07</v>
       </c>
       <c r="AF112">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="AG112">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AK112">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18728,19 +18728,19 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="O113">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="P113">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="Q113">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="R113">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="S113">
         <v>1.21</v>
@@ -18767,16 +18767,16 @@
         <v>5.4</v>
       </c>
       <c r="AA113">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB113">
         <v>2.56</v>
       </c>
       <c r="AC113">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AD113">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AE113">
         <v>1.25</v>
@@ -18785,7 +18785,7 @@
         <v>1.44</v>
       </c>
       <c r="AG113">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>1.18</v>
       </c>
       <c r="AK113">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -19057,10 +19057,10 @@
         <v>2.8</v>
       </c>
       <c r="O115">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P115">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q115">
         <v>3.5</v>
@@ -19093,7 +19093,7 @@
         <v>3.1</v>
       </c>
       <c r="AA115">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="AB115">
         <v>1.67</v>
@@ -19217,19 +19217,19 @@
         </is>
       </c>
       <c r="N116">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="O116">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P116">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="Q116">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="R116">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="S116">
         <v>1.44</v>
@@ -19238,31 +19238,31 @@
         <v>2.53</v>
       </c>
       <c r="U116">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="V116">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W116">
         <v>1.05</v>
       </c>
       <c r="X116">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y116">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z116">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AA116">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="AB116">
         <v>1.67</v>
       </c>
       <c r="AC116">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AD116">
         <v>1.22</v>
@@ -19271,7 +19271,7 @@
         <v>1.04</v>
       </c>
       <c r="AF116">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="AG116">
         <v>1.87</v>
@@ -19290,7 +19290,7 @@
         <v>1.33</v>
       </c>
       <c r="AK116">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19380,10 +19380,10 @@
         </is>
       </c>
       <c r="N117">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="O117">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="P117">
         <v>3.7</v>
@@ -19552,71 +19552,71 @@
         <v>0</v>
       </c>
       <c r="Q118">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="R118">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="S118">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T118">
         <v>3.1</v>
       </c>
       <c r="U118">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="V118">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W118">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X118">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y118">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z118">
-        <v>3.58</v>
+        <v>3.76</v>
       </c>
       <c r="AA118">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AB118">
-        <v>1.96</v>
+        <v>2.01</v>
       </c>
       <c r="AC118">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="AD118">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE118">
         <v>1.13</v>
       </c>
       <c r="AF118">
+        <v>1.57</v>
+      </c>
+      <c r="AG118">
+        <v>2.15</v>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ118">
+        <v>1.32</v>
+      </c>
+      <c r="AK118">
         <v>1.6</v>
-      </c>
-      <c r="AG118">
-        <v>2.11</v>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI118" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ118">
-        <v>1.29</v>
-      </c>
-      <c r="AK118">
-        <v>1.65</v>
       </c>
       <c r="AL118">
         <v>0</v>

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -4393,7 +4393,7 @@
         <v>3.2</v>
       </c>
       <c r="Q25">
-        <v>2.78</v>
+        <v>2.73</v>
       </c>
       <c r="R25">
         <v>2.05</v>
@@ -4405,10 +4405,10 @@
         <v>2.34</v>
       </c>
       <c r="U25">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="V25">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W25">
         <v>1.06</v>
@@ -4417,19 +4417,19 @@
         <v>1.04</v>
       </c>
       <c r="Y25">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z25">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="AA25">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="AB25">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AC25">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="AD25">
         <v>1.16</v>
@@ -4438,7 +4438,7 @@
         <v>1.02</v>
       </c>
       <c r="AF25">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG25">
         <v>1.8</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK25">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="O26">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P26">
         <v>2.4</v>
       </c>
       <c r="Q26">
-        <v>3.61</v>
+        <v>3.72</v>
       </c>
       <c r="R26">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="S26">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T26">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="U26">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="V26">
         <v>1.25</v>
       </c>
       <c r="W26">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X26">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y26">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="Z26">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AA26">
-        <v>2.44</v>
+        <v>2.59</v>
       </c>
       <c r="AB26">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AC26">
-        <v>4.75</v>
+        <v>5.1</v>
       </c>
       <c r="AD26">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AE26">
         <v>1</v>
       </c>
       <c r="AF26">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AG26">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK26">
         <v>1.4</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.93</v>
+        <v>1.36</v>
       </c>
       <c r="O38">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="P38">
-        <v>3.25</v>
+        <v>7</v>
       </c>
       <c r="Q38">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="R38">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="S38">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="T38">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U38">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="V38">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="W38">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X38">
         <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z38">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="AA38">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="AB38">
-        <v>2.22</v>
+        <v>2.75</v>
       </c>
       <c r="AC38">
-        <v>2.43</v>
+        <v>2.12</v>
       </c>
       <c r="AD38">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AE38">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AF38">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG38">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AK38">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.36</v>
+        <v>1.93</v>
       </c>
       <c r="O39">
-        <v>5.2</v>
+        <v>3.6</v>
       </c>
       <c r="P39">
-        <v>7</v>
+        <v>3.25</v>
       </c>
       <c r="Q39">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="R39">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="S39">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="T39">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U39">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="V39">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="W39">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X39">
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z39">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="AA39">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="AB39">
-        <v>2.75</v>
+        <v>2.22</v>
       </c>
       <c r="AC39">
-        <v>2.12</v>
+        <v>2.43</v>
       </c>
       <c r="AD39">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AE39">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AF39">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG39">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="AK39">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,55 +6829,55 @@
         </is>
       </c>
       <c r="N40">
+        <v>2.47</v>
+      </c>
+      <c r="O40">
         <v>3.5</v>
       </c>
-      <c r="O40">
-        <v>3.6</v>
-      </c>
       <c r="P40">
-        <v>1.88</v>
+        <v>2.5</v>
       </c>
       <c r="Q40">
-        <v>3.66</v>
+        <v>2.88</v>
       </c>
       <c r="R40">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
       <c r="S40">
         <v>1.25</v>
       </c>
       <c r="T40">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="U40">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="V40">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="W40">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X40">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z40">
-        <v>4.66</v>
+        <v>4.59</v>
       </c>
       <c r="AA40">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AB40">
-        <v>2.34</v>
+        <v>2.21</v>
       </c>
       <c r="AC40">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="AD40">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AE40">
         <v>1.18</v>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK40">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,55 +6992,55 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.47</v>
+        <v>3.5</v>
       </c>
       <c r="O41">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P41">
-        <v>2.5</v>
+        <v>1.88</v>
       </c>
       <c r="Q41">
-        <v>2.88</v>
+        <v>3.66</v>
       </c>
       <c r="R41">
-        <v>2.39</v>
+        <v>2.46</v>
       </c>
       <c r="S41">
         <v>1.25</v>
       </c>
       <c r="T41">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="U41">
+        <v>2.31</v>
+      </c>
+      <c r="V41">
+        <v>1.57</v>
+      </c>
+      <c r="W41">
+        <v>1.14</v>
+      </c>
+      <c r="X41">
+        <v>1.01</v>
+      </c>
+      <c r="Y41">
+        <v>1.13</v>
+      </c>
+      <c r="Z41">
+        <v>4.66</v>
+      </c>
+      <c r="AA41">
+        <v>1.57</v>
+      </c>
+      <c r="AB41">
         <v>2.34</v>
       </c>
-      <c r="V41">
-        <v>1.51</v>
-      </c>
-      <c r="W41">
-        <v>1.09</v>
-      </c>
-      <c r="X41">
-        <v>1.02</v>
-      </c>
-      <c r="Y41">
-        <v>1.18</v>
-      </c>
-      <c r="Z41">
-        <v>4.59</v>
-      </c>
-      <c r="AA41">
-        <v>1.61</v>
-      </c>
-      <c r="AB41">
-        <v>2.21</v>
-      </c>
       <c r="AC41">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="AD41">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AE41">
         <v>1.18</v>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK41">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7807,25 +7807,25 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="O46">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="P46">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="Q46">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="R46">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="S46">
         <v>1.38</v>
       </c>
       <c r="T46">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="U46">
         <v>2.62</v>
@@ -7837,7 +7837,7 @@
         <v>1.04</v>
       </c>
       <c r="X46">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y46">
         <v>1.22</v>
@@ -7846,7 +7846,7 @@
         <v>3.48</v>
       </c>
       <c r="AA46">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB46">
         <v>1.9</v>
@@ -7855,16 +7855,16 @@
         <v>2.97</v>
       </c>
       <c r="AD46">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE46">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF46">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG46">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="O48">
         <v>4.3</v>
       </c>
       <c r="P48">
-        <v>4.45</v>
+        <v>4.75</v>
       </c>
       <c r="Q48">
         <v>2</v>
@@ -8148,13 +8148,13 @@
         <v>2.5</v>
       </c>
       <c r="S48">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T48">
         <v>3.32</v>
       </c>
       <c r="U48">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="V48">
         <v>1.6</v>
@@ -8169,7 +8169,7 @@
         <v>1.12</v>
       </c>
       <c r="Z48">
-        <v>5.26</v>
+        <v>5.36</v>
       </c>
       <c r="AA48">
         <v>1.51</v>
@@ -8178,13 +8178,13 @@
         <v>2.4</v>
       </c>
       <c r="AC48">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AD48">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AE48">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF48">
         <v>1.55</v>
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="O49">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="P49">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="Q49">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="R49">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="S49">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T49">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U49">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V49">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W49">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z49">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AA49">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AB49">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AC49">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AD49">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AE49">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="AK49">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -10913,7 +10913,7 @@
         <v>9</v>
       </c>
       <c r="Q65">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R65">
         <v>2.25</v>
@@ -10937,10 +10937,10 @@
         <v>1.03</v>
       </c>
       <c r="Y65">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z65">
-        <v>2.98</v>
+        <v>2.75</v>
       </c>
       <c r="AA65">
         <v>2.05</v>
@@ -10958,10 +10958,10 @@
         <v>1.04</v>
       </c>
       <c r="AF65">
-        <v>2.64</v>
+        <v>2.45</v>
       </c>
       <c r="AG65">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="O67">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="P67">
-        <v>2.52</v>
+        <v>3.25</v>
       </c>
       <c r="Q67">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="R67">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="S67">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="T67">
-        <v>3.18</v>
+        <v>2.5</v>
       </c>
       <c r="U67">
-        <v>2.5</v>
+        <v>2.86</v>
       </c>
       <c r="V67">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W67">
         <v>1.07</v>
       </c>
       <c r="X67">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z67">
-        <v>3.9</v>
+        <v>3.04</v>
       </c>
       <c r="AA67">
-        <v>1.74</v>
+        <v>2.17</v>
       </c>
       <c r="AB67">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
       <c r="AC67">
-        <v>2.66</v>
+        <v>3.42</v>
       </c>
       <c r="AD67">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AE67">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AF67">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AG67">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK67">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
+        <v>2.35</v>
+      </c>
+      <c r="O68">
+        <v>3.4</v>
+      </c>
+      <c r="P68">
+        <v>3</v>
+      </c>
+      <c r="Q68">
+        <v>2.81</v>
+      </c>
+      <c r="R68">
         <v>2.2</v>
       </c>
-      <c r="O68">
-        <v>3.15</v>
-      </c>
-      <c r="P68">
-        <v>2.9</v>
-      </c>
-      <c r="Q68">
-        <v>2.75</v>
-      </c>
-      <c r="R68">
-        <v>2.03</v>
-      </c>
       <c r="S68">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="T68">
-        <v>2.71</v>
+        <v>3.08</v>
       </c>
       <c r="U68">
-        <v>2.87</v>
+        <v>2.42</v>
       </c>
       <c r="V68">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="W68">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X68">
         <v>1.02</v>
       </c>
       <c r="Y68">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="Z68">
-        <v>3.05</v>
+        <v>3.84</v>
       </c>
       <c r="AA68">
-        <v>2.06</v>
+        <v>1.77</v>
       </c>
       <c r="AB68">
+        <v>1.99</v>
+      </c>
+      <c r="AC68">
+        <v>3.03</v>
+      </c>
+      <c r="AD68">
+        <v>1.38</v>
+      </c>
+      <c r="AE68">
+        <v>1.14</v>
+      </c>
+      <c r="AF68">
         <v>1.67</v>
       </c>
-      <c r="AC68">
-        <v>4.03</v>
-      </c>
-      <c r="AD68">
-        <v>1.22</v>
-      </c>
-      <c r="AE68">
-        <v>1.05</v>
-      </c>
-      <c r="AF68">
-        <v>1.85</v>
-      </c>
       <c r="AG68">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AK68">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,55 +11556,55 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="O69">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P69">
-        <v>3</v>
+        <v>2.52</v>
       </c>
       <c r="Q69">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="R69">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S69">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="T69">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="U69">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="V69">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W69">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X69">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y69">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z69">
-        <v>3.84</v>
+        <v>3.9</v>
       </c>
       <c r="AA69">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AB69">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AC69">
-        <v>3.03</v>
+        <v>2.66</v>
       </c>
       <c r="AD69">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE69">
         <v>1.14</v>
@@ -11613,7 +11613,7 @@
         <v>1.67</v>
       </c>
       <c r="AG69">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AK69">
         <v>1.62</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="O71">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="P71">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="Q71">
-        <v>2.92</v>
+        <v>2.75</v>
       </c>
       <c r="R71">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="S71">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T71">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="U71">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="V71">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W71">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X71">
         <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="Z71">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="AA71">
-        <v>2.17</v>
+        <v>2.06</v>
       </c>
       <c r="AB71">
         <v>1.67</v>
       </c>
       <c r="AC71">
-        <v>3.42</v>
+        <v>4.03</v>
       </c>
       <c r="AD71">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE71">
         <v>1.05</v>
       </c>
       <c r="AF71">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AG71">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK71">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G75">
@@ -12543,22 +12543,22 @@
         <v>0</v>
       </c>
       <c r="Q75">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="R75">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="S75">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T75">
         <v>3.25</v>
       </c>
       <c r="U75">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="V75">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W75">
         <v>1.12</v>
@@ -12567,28 +12567,28 @@
         <v>1.02</v>
       </c>
       <c r="Y75">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="Z75">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA75">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AB75">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="AC75">
-        <v>2.63</v>
+        <v>2.58</v>
       </c>
       <c r="AD75">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AE75">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AF75">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG75">
         <v>2.3</v>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK75">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G76">
@@ -12706,22 +12706,22 @@
         <v>0</v>
       </c>
       <c r="Q76">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="R76">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="S76">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T76">
         <v>3.25</v>
       </c>
       <c r="U76">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="V76">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W76">
         <v>1.12</v>
@@ -12730,28 +12730,28 @@
         <v>1.02</v>
       </c>
       <c r="Y76">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z76">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA76">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AB76">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="AC76">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="AD76">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AE76">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AF76">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG76">
         <v>2.3</v>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK76">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -14825,7 +14825,7 @@
         <v>2.05</v>
       </c>
       <c r="Q89">
-        <v>4.16</v>
+        <v>4.12</v>
       </c>
       <c r="R89">
         <v>2</v>
@@ -14861,19 +14861,19 @@
         <v>1.7</v>
       </c>
       <c r="AC89">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="AD89">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE89">
         <v>1.03</v>
       </c>
       <c r="AF89">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AG89">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,7 +14886,7 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK89">
         <v>1.25</v>
@@ -15178,19 +15178,19 @@
         <v>1.18</v>
       </c>
       <c r="Z91">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA91">
         <v>1.7</v>
       </c>
       <c r="AB91">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AC91">
         <v>2.7</v>
       </c>
       <c r="AD91">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE91">
         <v>1.15</v>
@@ -15957,19 +15957,19 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O96">
         <v>3.3</v>
       </c>
       <c r="P96">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q96">
         <v>2.78</v>
       </c>
       <c r="R96">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="S96">
         <v>1.29</v>
@@ -15978,13 +15978,13 @@
         <v>3.2</v>
       </c>
       <c r="U96">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="V96">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W96">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X96">
         <v>1</v>
@@ -15993,13 +15993,13 @@
         <v>1.17</v>
       </c>
       <c r="Z96">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="AA96">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB96">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC96">
         <v>2.52</v>
@@ -16011,10 +16011,10 @@
         <v>1.13</v>
       </c>
       <c r="AF96">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AG96">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AK96">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16120,7 +16120,7 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="O97">
         <v>3.65</v>
@@ -16129,10 +16129,10 @@
         <v>3.7</v>
       </c>
       <c r="Q97">
-        <v>2.44</v>
+        <v>2.33</v>
       </c>
       <c r="R97">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S97">
         <v>1.28</v>
@@ -16141,34 +16141,34 @@
         <v>3.22</v>
       </c>
       <c r="U97">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="V97">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W97">
         <v>1.11</v>
       </c>
       <c r="X97">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y97">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z97">
-        <v>3.92</v>
+        <v>3.95</v>
       </c>
       <c r="AA97">
         <v>1.71</v>
       </c>
       <c r="AB97">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AC97">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AD97">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE97">
         <v>1.16</v>
@@ -16193,7 +16193,7 @@
         <v>1.25</v>
       </c>
       <c r="AK97">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>3.8</v>
+        <v>1.41</v>
       </c>
       <c r="O98">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="P98">
-        <v>1.78</v>
+        <v>5.5</v>
       </c>
       <c r="Q98">
-        <v>4.4</v>
+        <v>1.86</v>
       </c>
       <c r="R98">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="S98">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="T98">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="U98">
-        <v>2.54</v>
+        <v>2.17</v>
       </c>
       <c r="V98">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="W98">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X98">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y98">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z98">
-        <v>3.79</v>
+        <v>5.5</v>
       </c>
       <c r="AA98">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AB98">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="AC98">
-        <v>2.83</v>
+        <v>2.24</v>
       </c>
       <c r="AD98">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="AE98">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AF98">
         <v>1.67</v>
       </c>
       <c r="AG98">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AK98">
-        <v>1.16</v>
+        <v>2.66</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,80 +16446,80 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.24</v>
+        <v>1.47</v>
       </c>
       <c r="O99">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="P99">
-        <v>3.1</v>
+        <v>5.4</v>
       </c>
       <c r="Q99">
-        <v>2.81</v>
+        <v>2</v>
       </c>
       <c r="R99">
-        <v>2.03</v>
+        <v>2.66</v>
       </c>
       <c r="S99">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="T99">
-        <v>2.77</v>
+        <v>3.8</v>
       </c>
       <c r="U99">
-        <v>2.61</v>
+        <v>2.2</v>
       </c>
       <c r="V99">
-        <v>1.39</v>
+        <v>1.62</v>
       </c>
       <c r="W99">
+        <v>1.15</v>
+      </c>
+      <c r="X99">
+        <v>1.02</v>
+      </c>
+      <c r="Y99">
+        <v>1.15</v>
+      </c>
+      <c r="Z99">
+        <v>4.7</v>
+      </c>
+      <c r="AA99">
+        <v>1.47</v>
+      </c>
+      <c r="AB99">
+        <v>2.55</v>
+      </c>
+      <c r="AC99">
+        <v>2.18</v>
+      </c>
+      <c r="AD99">
+        <v>1.58</v>
+      </c>
+      <c r="AE99">
+        <v>1.21</v>
+      </c>
+      <c r="AF99">
+        <v>1.55</v>
+      </c>
+      <c r="AG99">
+        <v>2.15</v>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ99">
         <v>1.07</v>
       </c>
-      <c r="X99">
-        <v>1.01</v>
-      </c>
-      <c r="Y99">
-        <v>1.25</v>
-      </c>
-      <c r="Z99">
-        <v>3.49</v>
-      </c>
-      <c r="AA99">
-        <v>1.9</v>
-      </c>
-      <c r="AB99">
-        <v>1.87</v>
-      </c>
-      <c r="AC99">
-        <v>3.37</v>
-      </c>
-      <c r="AD99">
-        <v>1.3</v>
-      </c>
-      <c r="AE99">
-        <v>1.1</v>
-      </c>
-      <c r="AF99">
-        <v>1.69</v>
-      </c>
-      <c r="AG99">
-        <v>2</v>
-      </c>
-      <c r="AH99" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI99" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ99">
-        <v>1.25</v>
-      </c>
       <c r="AK99">
-        <v>1.62</v>
+        <v>2.29</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>1.41</v>
+        <v>3.8</v>
       </c>
       <c r="O101">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="P101">
-        <v>5.5</v>
+        <v>1.78</v>
       </c>
       <c r="Q101">
-        <v>1.86</v>
+        <v>4.4</v>
       </c>
       <c r="R101">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="S101">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="T101">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="U101">
-        <v>2.17</v>
+        <v>2.54</v>
       </c>
       <c r="V101">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="W101">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X101">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y101">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="Z101">
-        <v>5.5</v>
+        <v>3.79</v>
       </c>
       <c r="AA101">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AB101">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="AC101">
-        <v>2.24</v>
+        <v>2.83</v>
       </c>
       <c r="AD101">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="AE101">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AF101">
         <v>1.67</v>
       </c>
       <c r="AG101">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="AK101">
-        <v>2.66</v>
+        <v>1.16</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,80 +16935,80 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.47</v>
+        <v>2.24</v>
       </c>
       <c r="O102">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="P102">
-        <v>5.4</v>
+        <v>3.1</v>
       </c>
       <c r="Q102">
+        <v>2.81</v>
+      </c>
+      <c r="R102">
+        <v>2.03</v>
+      </c>
+      <c r="S102">
+        <v>1.36</v>
+      </c>
+      <c r="T102">
+        <v>2.77</v>
+      </c>
+      <c r="U102">
+        <v>2.61</v>
+      </c>
+      <c r="V102">
+        <v>1.39</v>
+      </c>
+      <c r="W102">
+        <v>1.07</v>
+      </c>
+      <c r="X102">
+        <v>1.01</v>
+      </c>
+      <c r="Y102">
+        <v>1.25</v>
+      </c>
+      <c r="Z102">
+        <v>3.49</v>
+      </c>
+      <c r="AA102">
+        <v>1.9</v>
+      </c>
+      <c r="AB102">
+        <v>1.87</v>
+      </c>
+      <c r="AC102">
+        <v>3.37</v>
+      </c>
+      <c r="AD102">
+        <v>1.3</v>
+      </c>
+      <c r="AE102">
+        <v>1.1</v>
+      </c>
+      <c r="AF102">
+        <v>1.69</v>
+      </c>
+      <c r="AG102">
         <v>2</v>
       </c>
-      <c r="R102">
-        <v>2.66</v>
-      </c>
-      <c r="S102">
-        <v>1.22</v>
-      </c>
-      <c r="T102">
-        <v>3.8</v>
-      </c>
-      <c r="U102">
-        <v>2.2</v>
-      </c>
-      <c r="V102">
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ102">
+        <v>1.25</v>
+      </c>
+      <c r="AK102">
         <v>1.62</v>
-      </c>
-      <c r="W102">
-        <v>1.15</v>
-      </c>
-      <c r="X102">
-        <v>1.02</v>
-      </c>
-      <c r="Y102">
-        <v>1.15</v>
-      </c>
-      <c r="Z102">
-        <v>4.7</v>
-      </c>
-      <c r="AA102">
-        <v>1.47</v>
-      </c>
-      <c r="AB102">
-        <v>2.55</v>
-      </c>
-      <c r="AC102">
-        <v>2.18</v>
-      </c>
-      <c r="AD102">
-        <v>1.58</v>
-      </c>
-      <c r="AE102">
-        <v>1.21</v>
-      </c>
-      <c r="AF102">
-        <v>1.55</v>
-      </c>
-      <c r="AG102">
-        <v>2.15</v>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ102">
-        <v>1.07</v>
-      </c>
-      <c r="AK102">
-        <v>2.29</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17753,16 +17753,16 @@
         <v>1.4</v>
       </c>
       <c r="O107">
-        <v>4.06</v>
+        <v>4.15</v>
       </c>
       <c r="P107">
         <v>5.3</v>
       </c>
       <c r="Q107">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="R107">
-        <v>2.6</v>
+        <v>2.29</v>
       </c>
       <c r="S107">
         <v>1.25</v>
@@ -17771,7 +17771,7 @@
         <v>3.5</v>
       </c>
       <c r="U107">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="V107">
         <v>1.57</v>
@@ -17783,22 +17783,22 @@
         <v>1.01</v>
       </c>
       <c r="Y107">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z107">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AA107">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AB107">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AC107">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AD107">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AE107">
         <v>1.15</v>
@@ -17807,7 +17807,7 @@
         <v>1.67</v>
       </c>
       <c r="AG107">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK107">
-        <v>2.8</v>
+        <v>2.51</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17913,19 +17913,19 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="O108">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="P108">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="Q108">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="R108">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S108">
         <v>1.31</v>
@@ -17934,43 +17934,43 @@
         <v>3.08</v>
       </c>
       <c r="U108">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="V108">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="W108">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X108">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y108">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z108">
-        <v>3.74</v>
+        <v>4.05</v>
       </c>
       <c r="AA108">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AB108">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="AC108">
-        <v>2.41</v>
+        <v>2.53</v>
       </c>
       <c r="AD108">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AE108">
         <v>1.12</v>
       </c>
       <c r="AF108">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG108">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="AK108">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18085,10 +18085,10 @@
         <v>4.2</v>
       </c>
       <c r="Q109">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="R109">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="S109">
         <v>1.37</v>
@@ -18106,7 +18106,7 @@
         <v>1.1</v>
       </c>
       <c r="X109">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y109">
         <v>1.24</v>
@@ -18130,7 +18130,7 @@
         <v>1.13</v>
       </c>
       <c r="AF109">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AG109">
         <v>2</v>
@@ -18459,7 +18459,7 @@
         <v>2.17</v>
       </c>
       <c r="AG111">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18773,10 +18773,10 @@
         <v>2.56</v>
       </c>
       <c r="AC113">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AD113">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AE113">
         <v>1.25</v>

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,65 +6177,65 @@
         </is>
       </c>
       <c r="N36">
-        <v>3.2</v>
+        <v>1.76</v>
       </c>
       <c r="O36">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P36">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="Q36">
-        <v>3.75</v>
+        <v>2.26</v>
       </c>
       <c r="R36">
+        <v>2.3</v>
+      </c>
+      <c r="S36">
+        <v>1.31</v>
+      </c>
+      <c r="T36">
+        <v>2.94</v>
+      </c>
+      <c r="U36">
+        <v>2.45</v>
+      </c>
+      <c r="V36">
+        <v>1.5</v>
+      </c>
+      <c r="W36">
+        <v>1.06</v>
+      </c>
+      <c r="X36">
+        <v>1.03</v>
+      </c>
+      <c r="Y36">
+        <v>1.17</v>
+      </c>
+      <c r="Z36">
+        <v>3.95</v>
+      </c>
+      <c r="AA36">
+        <v>1.68</v>
+      </c>
+      <c r="AB36">
+        <v>2.02</v>
+      </c>
+      <c r="AC36">
+        <v>2.66</v>
+      </c>
+      <c r="AD36">
+        <v>1.37</v>
+      </c>
+      <c r="AE36">
+        <v>1.11</v>
+      </c>
+      <c r="AF36">
+        <v>1.67</v>
+      </c>
+      <c r="AG36">
         <v>2.1</v>
       </c>
-      <c r="S36">
-        <v>1.35</v>
-      </c>
-      <c r="T36">
-        <v>2.76</v>
-      </c>
-      <c r="U36">
-        <v>2.64</v>
-      </c>
-      <c r="V36">
-        <v>1.38</v>
-      </c>
-      <c r="W36">
-        <v>1.1</v>
-      </c>
-      <c r="X36">
-        <v>1.01</v>
-      </c>
-      <c r="Y36">
-        <v>1.24</v>
-      </c>
-      <c r="Z36">
-        <v>3.34</v>
-      </c>
-      <c r="AA36">
-        <v>1.82</v>
-      </c>
-      <c r="AB36">
-        <v>1.85</v>
-      </c>
-      <c r="AC36">
-        <v>2.97</v>
-      </c>
-      <c r="AD36">
-        <v>1.3</v>
-      </c>
-      <c r="AE36">
-        <v>1.08</v>
-      </c>
-      <c r="AF36">
-        <v>1.69</v>
-      </c>
-      <c r="AG36">
-        <v>2</v>
-      </c>
       <c r="AH36" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="AK36">
-        <v>1.29</v>
+        <v>2.05</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,80 +6340,80 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.76</v>
+        <v>1.36</v>
       </c>
       <c r="O37">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="P37">
-        <v>3.9</v>
+        <v>7</v>
       </c>
       <c r="Q37">
-        <v>2.26</v>
+        <v>1.8</v>
       </c>
       <c r="R37">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="S37">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="T37">
-        <v>2.94</v>
+        <v>3.75</v>
       </c>
       <c r="U37">
-        <v>2.45</v>
+        <v>2.04</v>
       </c>
       <c r="V37">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="W37">
+        <v>1.17</v>
+      </c>
+      <c r="X37">
+        <v>1.01</v>
+      </c>
+      <c r="Y37">
+        <v>1.08</v>
+      </c>
+      <c r="Z37">
+        <v>6</v>
+      </c>
+      <c r="AA37">
+        <v>1.4</v>
+      </c>
+      <c r="AB37">
+        <v>2.75</v>
+      </c>
+      <c r="AC37">
+        <v>2.12</v>
+      </c>
+      <c r="AD37">
+        <v>1.65</v>
+      </c>
+      <c r="AE37">
+        <v>1.24</v>
+      </c>
+      <c r="AF37">
+        <v>1.62</v>
+      </c>
+      <c r="AG37">
+        <v>2.2</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ37">
         <v>1.06</v>
       </c>
-      <c r="X37">
-        <v>1.03</v>
-      </c>
-      <c r="Y37">
-        <v>1.17</v>
-      </c>
-      <c r="Z37">
-        <v>3.95</v>
-      </c>
-      <c r="AA37">
-        <v>1.68</v>
-      </c>
-      <c r="AB37">
-        <v>2.02</v>
-      </c>
-      <c r="AC37">
-        <v>2.66</v>
-      </c>
-      <c r="AD37">
-        <v>1.37</v>
-      </c>
-      <c r="AE37">
-        <v>1.11</v>
-      </c>
-      <c r="AF37">
-        <v>1.67</v>
-      </c>
-      <c r="AG37">
-        <v>2.1</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ37">
-        <v>1.2</v>
-      </c>
       <c r="AK37">
-        <v>2.05</v>
+        <v>2.8</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.36</v>
+        <v>1.93</v>
       </c>
       <c r="O38">
-        <v>5.2</v>
+        <v>3.6</v>
       </c>
       <c r="P38">
-        <v>7</v>
+        <v>3.25</v>
       </c>
       <c r="Q38">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="R38">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="S38">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="T38">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U38">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="V38">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="W38">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X38">
         <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z38">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="AA38">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="AB38">
-        <v>2.75</v>
+        <v>2.22</v>
       </c>
       <c r="AC38">
-        <v>2.12</v>
+        <v>2.43</v>
       </c>
       <c r="AD38">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AE38">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AF38">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG38">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="AK38">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.93</v>
+        <v>3.2</v>
       </c>
       <c r="O39">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P39">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="Q39">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="R39">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S39">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="T39">
-        <v>3.5</v>
+        <v>2.76</v>
       </c>
       <c r="U39">
-        <v>2.3</v>
+        <v>2.64</v>
       </c>
       <c r="V39">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="W39">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X39">
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="Z39">
-        <v>4.6</v>
+        <v>3.34</v>
       </c>
       <c r="AA39">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="AB39">
-        <v>2.22</v>
+        <v>1.85</v>
       </c>
       <c r="AC39">
-        <v>2.43</v>
+        <v>2.97</v>
       </c>
       <c r="AD39">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AE39">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF39">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="AG39">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.22</v>
+        <v>1.7</v>
       </c>
       <c r="AK39">
-        <v>1.7</v>
+        <v>1.29</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="O67">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="P67">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="Q67">
-        <v>2.92</v>
+        <v>2.75</v>
       </c>
       <c r="R67">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="S67">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T67">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="U67">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="V67">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W67">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X67">
         <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="Z67">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="AA67">
-        <v>2.17</v>
+        <v>2.06</v>
       </c>
       <c r="AB67">
         <v>1.67</v>
       </c>
       <c r="AC67">
-        <v>3.42</v>
+        <v>4.03</v>
       </c>
       <c r="AD67">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE67">
         <v>1.05</v>
       </c>
       <c r="AF67">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AG67">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK67">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="O68">
         <v>3.4</v>
       </c>
       <c r="P68">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="Q68">
-        <v>2.81</v>
+        <v>2.43</v>
       </c>
       <c r="R68">
         <v>2.2</v>
       </c>
       <c r="S68">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T68">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="U68">
-        <v>2.42</v>
+        <v>2.74</v>
       </c>
       <c r="V68">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W68">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X68">
         <v>1.02</v>
       </c>
       <c r="Y68">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z68">
-        <v>3.84</v>
+        <v>3.86</v>
       </c>
       <c r="AA68">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AB68">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AC68">
-        <v>3.03</v>
+        <v>3.13</v>
       </c>
       <c r="AD68">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE68">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF68">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AG68">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AK68">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,55 +11556,55 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="O69">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P69">
-        <v>2.52</v>
+        <v>3</v>
       </c>
       <c r="Q69">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="R69">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="S69">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="T69">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="U69">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="V69">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W69">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X69">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y69">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z69">
-        <v>3.9</v>
+        <v>3.84</v>
       </c>
       <c r="AA69">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AB69">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AC69">
-        <v>2.66</v>
+        <v>3.03</v>
       </c>
       <c r="AD69">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE69">
         <v>1.14</v>
@@ -11613,7 +11613,7 @@
         <v>1.67</v>
       </c>
       <c r="AG69">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AK69">
         <v>1.62</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.75</v>
+        <v>2.32</v>
       </c>
       <c r="O70">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="P70">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="Q70">
-        <v>2.43</v>
+        <v>2.92</v>
       </c>
       <c r="R70">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="S70">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T70">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="U70">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="V70">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W70">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X70">
         <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="Z70">
-        <v>3.86</v>
+        <v>3.04</v>
       </c>
       <c r="AA70">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="AB70">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AC70">
-        <v>3.13</v>
+        <v>3.42</v>
       </c>
       <c r="AD70">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AE70">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF70">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="AG70">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK70">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="O71">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="P71">
-        <v>2.9</v>
+        <v>2.52</v>
       </c>
       <c r="Q71">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="R71">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="S71">
+        <v>1.34</v>
+      </c>
+      <c r="T71">
+        <v>3.18</v>
+      </c>
+      <c r="U71">
+        <v>2.5</v>
+      </c>
+      <c r="V71">
         <v>1.44</v>
       </c>
-      <c r="T71">
-        <v>2.71</v>
-      </c>
-      <c r="U71">
-        <v>2.87</v>
-      </c>
-      <c r="V71">
-        <v>1.35</v>
-      </c>
       <c r="W71">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X71">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y71">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="Z71">
-        <v>3.05</v>
+        <v>3.9</v>
       </c>
       <c r="AA71">
-        <v>2.06</v>
+        <v>1.74</v>
       </c>
       <c r="AB71">
+        <v>1.98</v>
+      </c>
+      <c r="AC71">
+        <v>2.66</v>
+      </c>
+      <c r="AD71">
+        <v>1.33</v>
+      </c>
+      <c r="AE71">
+        <v>1.14</v>
+      </c>
+      <c r="AF71">
         <v>1.67</v>
       </c>
-      <c r="AC71">
-        <v>4.03</v>
-      </c>
-      <c r="AD71">
-        <v>1.22</v>
-      </c>
-      <c r="AE71">
-        <v>1.05</v>
-      </c>
-      <c r="AF71">
-        <v>1.85</v>
-      </c>
       <c r="AG71">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK71">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,80 +13512,80 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="O81">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="P81">
-        <v>1.95</v>
+        <v>2.47</v>
       </c>
       <c r="Q81">
-        <v>3.3</v>
+        <v>2.72</v>
       </c>
       <c r="R81">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="S81">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="T81">
-        <v>4.1</v>
+        <v>3.32</v>
       </c>
       <c r="U81">
-        <v>1.97</v>
+        <v>2.27</v>
       </c>
       <c r="V81">
-        <v>1.93</v>
+        <v>1.57</v>
       </c>
       <c r="W81">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="X81">
         <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="Z81">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AA81">
+        <v>1.53</v>
+      </c>
+      <c r="AB81">
+        <v>2.33</v>
+      </c>
+      <c r="AC81">
+        <v>2.28</v>
+      </c>
+      <c r="AD81">
+        <v>1.5</v>
+      </c>
+      <c r="AE81">
+        <v>1.17</v>
+      </c>
+      <c r="AF81">
+        <v>1.46</v>
+      </c>
+      <c r="AG81">
+        <v>2.55</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ81">
         <v>1.3</v>
       </c>
-      <c r="AB81">
-        <v>3.5</v>
-      </c>
-      <c r="AC81">
-        <v>1.79</v>
-      </c>
-      <c r="AD81">
-        <v>1.98</v>
-      </c>
-      <c r="AE81">
-        <v>1.4</v>
-      </c>
-      <c r="AF81">
-        <v>1.33</v>
-      </c>
-      <c r="AG81">
-        <v>3.4</v>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI81" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ81">
-        <v>1.22</v>
-      </c>
       <c r="AK81">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.21</v>
+        <v>2.9</v>
       </c>
       <c r="O82">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P82">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="Q82">
-        <v>2.85</v>
+        <v>3.3</v>
       </c>
       <c r="R82">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="S82">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T82">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="U82">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="V82">
-        <v>1.66</v>
+        <v>1.93</v>
       </c>
       <c r="W82">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="X82">
         <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Z82">
-        <v>5.55</v>
+        <v>8</v>
       </c>
       <c r="AA82">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AB82">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="AC82">
-        <v>2.09</v>
+        <v>1.79</v>
       </c>
       <c r="AD82">
-        <v>1.68</v>
+        <v>1.98</v>
       </c>
       <c r="AE82">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AF82">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AG82">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK82">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>3</v>
+        <v>2.21</v>
       </c>
       <c r="O83">
         <v>3.6</v>
       </c>
       <c r="P83">
-        <v>2.07</v>
+        <v>2.5</v>
       </c>
       <c r="Q83">
-        <v>3.06</v>
+        <v>2.85</v>
       </c>
       <c r="R83">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="S83">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T83">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U83">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V83">
+        <v>1.66</v>
+      </c>
+      <c r="W83">
+        <v>1.13</v>
+      </c>
+      <c r="X83">
+        <v>1.01</v>
+      </c>
+      <c r="Y83">
+        <v>1.08</v>
+      </c>
+      <c r="Z83">
+        <v>5.55</v>
+      </c>
+      <c r="AA83">
+        <v>1.44</v>
+      </c>
+      <c r="AB83">
+        <v>2.7</v>
+      </c>
+      <c r="AC83">
+        <v>2.09</v>
+      </c>
+      <c r="AD83">
         <v>1.68</v>
       </c>
-      <c r="W83">
-        <v>1.16</v>
-      </c>
-      <c r="X83">
-        <v>1.02</v>
-      </c>
-      <c r="Y83">
-        <v>1.09</v>
-      </c>
-      <c r="Z83">
-        <v>5.3</v>
-      </c>
-      <c r="AA83">
-        <v>1.41</v>
-      </c>
-      <c r="AB83">
-        <v>2.6</v>
-      </c>
-      <c r="AC83">
-        <v>2.08</v>
-      </c>
-      <c r="AD83">
-        <v>1.67</v>
-      </c>
       <c r="AE83">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AF83">
         <v>1.4</v>
       </c>
       <c r="AG83">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="AK83">
-        <v>1.29</v>
+        <v>1.51</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.65</v>
+        <v>3</v>
       </c>
       <c r="O84">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="P84">
-        <v>4.33</v>
+        <v>2.07</v>
       </c>
       <c r="Q84">
-        <v>2.03</v>
+        <v>3.06</v>
       </c>
       <c r="R84">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="S84">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T84">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="U84">
         <v>2.1</v>
       </c>
       <c r="V84">
+        <v>1.68</v>
+      </c>
+      <c r="W84">
+        <v>1.16</v>
+      </c>
+      <c r="X84">
+        <v>1.02</v>
+      </c>
+      <c r="Y84">
+        <v>1.09</v>
+      </c>
+      <c r="Z84">
+        <v>5.3</v>
+      </c>
+      <c r="AA84">
+        <v>1.41</v>
+      </c>
+      <c r="AB84">
+        <v>2.6</v>
+      </c>
+      <c r="AC84">
+        <v>2.08</v>
+      </c>
+      <c r="AD84">
         <v>1.67</v>
       </c>
-      <c r="W84">
-        <v>1.14</v>
-      </c>
-      <c r="X84">
-        <v>1.01</v>
-      </c>
-      <c r="Y84">
-        <v>1.13</v>
-      </c>
-      <c r="Z84">
-        <v>5.5</v>
-      </c>
-      <c r="AA84">
-        <v>1.47</v>
-      </c>
-      <c r="AB84">
-        <v>2.46</v>
-      </c>
-      <c r="AC84">
-        <v>2.21</v>
-      </c>
-      <c r="AD84">
-        <v>1.65</v>
-      </c>
       <c r="AE84">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AF84">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="AG84">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.2</v>
+        <v>1.75</v>
       </c>
       <c r="AK84">
-        <v>2.25</v>
+        <v>1.29</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,34 +14164,34 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.4</v>
+        <v>1.65</v>
       </c>
       <c r="O85">
-        <v>3.72</v>
+        <v>4</v>
       </c>
       <c r="P85">
-        <v>2.47</v>
+        <v>4.33</v>
       </c>
       <c r="Q85">
-        <v>2.72</v>
+        <v>2.03</v>
       </c>
       <c r="R85">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S85">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T85">
-        <v>3.32</v>
+        <v>3.55</v>
       </c>
       <c r="U85">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="V85">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="W85">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X85">
         <v>1.01</v>
@@ -14200,28 +14200,28 @@
         <v>1.13</v>
       </c>
       <c r="Z85">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA85">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AB85">
-        <v>2.33</v>
+        <v>2.46</v>
       </c>
       <c r="AC85">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="AD85">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AE85">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AF85">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AG85">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK85">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.47</v>
+        <v>2.15</v>
       </c>
       <c r="O99">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="P99">
-        <v>5.4</v>
+        <v>3.05</v>
       </c>
       <c r="Q99">
+        <v>2.64</v>
+      </c>
+      <c r="R99">
+        <v>2.08</v>
+      </c>
+      <c r="S99">
+        <v>1.35</v>
+      </c>
+      <c r="T99">
+        <v>2.76</v>
+      </c>
+      <c r="U99">
+        <v>2.63</v>
+      </c>
+      <c r="V99">
+        <v>1.44</v>
+      </c>
+      <c r="W99">
+        <v>1.05</v>
+      </c>
+      <c r="X99">
+        <v>1.01</v>
+      </c>
+      <c r="Y99">
+        <v>1.21</v>
+      </c>
+      <c r="Z99">
+        <v>3.58</v>
+      </c>
+      <c r="AA99">
+        <v>1.8</v>
+      </c>
+      <c r="AB99">
         <v>2</v>
       </c>
-      <c r="R99">
-        <v>2.66</v>
-      </c>
-      <c r="S99">
-        <v>1.22</v>
-      </c>
-      <c r="T99">
-        <v>3.8</v>
-      </c>
-      <c r="U99">
-        <v>2.2</v>
-      </c>
-      <c r="V99">
+      <c r="AC99">
+        <v>2.88</v>
+      </c>
+      <c r="AD99">
+        <v>1.32</v>
+      </c>
+      <c r="AE99">
+        <v>1.08</v>
+      </c>
+      <c r="AF99">
         <v>1.62</v>
       </c>
-      <c r="W99">
-        <v>1.15</v>
-      </c>
-      <c r="X99">
-        <v>1.02</v>
-      </c>
-      <c r="Y99">
-        <v>1.15</v>
-      </c>
-      <c r="Z99">
-        <v>4.7</v>
-      </c>
-      <c r="AA99">
-        <v>1.47</v>
-      </c>
-      <c r="AB99">
-        <v>2.55</v>
-      </c>
-      <c r="AC99">
-        <v>2.18</v>
-      </c>
-      <c r="AD99">
-        <v>1.58</v>
-      </c>
-      <c r="AE99">
-        <v>1.21</v>
-      </c>
-      <c r="AF99">
-        <v>1.55</v>
-      </c>
       <c r="AG99">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.07</v>
+        <v>1.26</v>
       </c>
       <c r="AK99">
-        <v>2.29</v>
+        <v>1.6</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,65 +16609,65 @@
         </is>
       </c>
       <c r="N100">
+        <v>1.47</v>
+      </c>
+      <c r="O100">
+        <v>4.1</v>
+      </c>
+      <c r="P100">
+        <v>5.4</v>
+      </c>
+      <c r="Q100">
+        <v>2</v>
+      </c>
+      <c r="R100">
+        <v>2.66</v>
+      </c>
+      <c r="S100">
+        <v>1.22</v>
+      </c>
+      <c r="T100">
+        <v>3.8</v>
+      </c>
+      <c r="U100">
+        <v>2.2</v>
+      </c>
+      <c r="V100">
+        <v>1.62</v>
+      </c>
+      <c r="W100">
+        <v>1.15</v>
+      </c>
+      <c r="X100">
+        <v>1.02</v>
+      </c>
+      <c r="Y100">
+        <v>1.15</v>
+      </c>
+      <c r="Z100">
+        <v>4.7</v>
+      </c>
+      <c r="AA100">
+        <v>1.47</v>
+      </c>
+      <c r="AB100">
+        <v>2.55</v>
+      </c>
+      <c r="AC100">
+        <v>2.18</v>
+      </c>
+      <c r="AD100">
+        <v>1.58</v>
+      </c>
+      <c r="AE100">
+        <v>1.21</v>
+      </c>
+      <c r="AF100">
+        <v>1.55</v>
+      </c>
+      <c r="AG100">
         <v>2.15</v>
       </c>
-      <c r="O100">
-        <v>3.25</v>
-      </c>
-      <c r="P100">
-        <v>3.05</v>
-      </c>
-      <c r="Q100">
-        <v>2.64</v>
-      </c>
-      <c r="R100">
-        <v>2.08</v>
-      </c>
-      <c r="S100">
-        <v>1.35</v>
-      </c>
-      <c r="T100">
-        <v>2.76</v>
-      </c>
-      <c r="U100">
-        <v>2.63</v>
-      </c>
-      <c r="V100">
-        <v>1.44</v>
-      </c>
-      <c r="W100">
-        <v>1.05</v>
-      </c>
-      <c r="X100">
-        <v>1.01</v>
-      </c>
-      <c r="Y100">
-        <v>1.21</v>
-      </c>
-      <c r="Z100">
-        <v>3.58</v>
-      </c>
-      <c r="AA100">
-        <v>1.8</v>
-      </c>
-      <c r="AB100">
-        <v>2</v>
-      </c>
-      <c r="AC100">
-        <v>2.88</v>
-      </c>
-      <c r="AD100">
-        <v>1.32</v>
-      </c>
-      <c r="AE100">
-        <v>1.08</v>
-      </c>
-      <c r="AF100">
-        <v>1.62</v>
-      </c>
-      <c r="AG100">
-        <v>2.1</v>
-      </c>
       <c r="AH100" t="inlineStr">
         <is>
           <t>[]</t>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="AK100">
-        <v>1.6</v>
+        <v>2.29</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -18737,7 +18737,7 @@
         <v>4.3</v>
       </c>
       <c r="Q113">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="R113">
         <v>2.38</v>

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -798,19 +798,19 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="O3">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P3">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="Q3">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="R3">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="S3">
         <v>1.3</v>
@@ -819,43 +819,43 @@
         <v>3.2</v>
       </c>
       <c r="U3">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="V3">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W3">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X3">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z3">
-        <v>3.93</v>
+        <v>3.96</v>
       </c>
       <c r="AA3">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AB3">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC3">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="AD3">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE3">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF3">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AG3">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>1.25</v>
       </c>
       <c r="AK3">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="O8">
         <v>4</v>
       </c>
       <c r="P8">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -2102,52 +2102,52 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="O11">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="P11">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="Q11">
-        <v>2.81</v>
+        <v>2.58</v>
       </c>
       <c r="R11">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="S11">
         <v>1.36</v>
       </c>
       <c r="T11">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="U11">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="V11">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W11">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z11">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AA11">
         <v>1.95</v>
       </c>
       <c r="AB11">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AC11">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="AD11">
         <v>1.31</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK11">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -4405,10 +4405,10 @@
         <v>2.34</v>
       </c>
       <c r="U25">
-        <v>3.18</v>
+        <v>3.24</v>
       </c>
       <c r="V25">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W25">
         <v>1.06</v>
@@ -4417,7 +4417,7 @@
         <v>1.04</v>
       </c>
       <c r="Y25">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Z25">
         <v>2.81</v>
@@ -4429,7 +4429,7 @@
         <v>1.56</v>
       </c>
       <c r="AC25">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="AD25">
         <v>1.16</v>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AK25">
         <v>1.59</v>
@@ -4547,16 +4547,16 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="O26">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P26">
         <v>2.4</v>
       </c>
       <c r="Q26">
-        <v>3.72</v>
+        <v>3.51</v>
       </c>
       <c r="R26">
         <v>1.89</v>
@@ -4583,16 +4583,16 @@
         <v>1.58</v>
       </c>
       <c r="Z26">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="AA26">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AB26">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AC26">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AD26">
         <v>1.1</v>
@@ -4604,7 +4604,7 @@
         <v>2.15</v>
       </c>
       <c r="AG26">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>1.36</v>
       </c>
       <c r="AK26">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.36</v>
+        <v>1.93</v>
       </c>
       <c r="O37">
-        <v>5.2</v>
+        <v>3.6</v>
       </c>
       <c r="P37">
-        <v>7</v>
+        <v>3.25</v>
       </c>
       <c r="Q37">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="R37">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="S37">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="T37">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U37">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="V37">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="W37">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X37">
         <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z37">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="AA37">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="AB37">
-        <v>2.75</v>
+        <v>2.22</v>
       </c>
       <c r="AC37">
-        <v>2.12</v>
+        <v>2.43</v>
       </c>
       <c r="AD37">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AE37">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AF37">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG37">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="AK37">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.93</v>
+        <v>3.2</v>
       </c>
       <c r="O38">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P38">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="Q38">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="R38">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S38">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="T38">
-        <v>3.5</v>
+        <v>2.76</v>
       </c>
       <c r="U38">
-        <v>2.3</v>
+        <v>2.64</v>
       </c>
       <c r="V38">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="W38">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X38">
         <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="Z38">
-        <v>4.6</v>
+        <v>3.34</v>
       </c>
       <c r="AA38">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="AB38">
-        <v>2.22</v>
+        <v>1.85</v>
       </c>
       <c r="AC38">
-        <v>2.43</v>
+        <v>2.97</v>
       </c>
       <c r="AD38">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AE38">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF38">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="AG38">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.22</v>
+        <v>1.7</v>
       </c>
       <c r="AK38">
-        <v>1.7</v>
+        <v>1.29</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>3.2</v>
+        <v>1.36</v>
       </c>
       <c r="O39">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="P39">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Q39">
+        <v>1.8</v>
+      </c>
+      <c r="R39">
+        <v>2.63</v>
+      </c>
+      <c r="S39">
+        <v>1.19</v>
+      </c>
+      <c r="T39">
         <v>3.75</v>
       </c>
-      <c r="R39">
-        <v>2.1</v>
-      </c>
-      <c r="S39">
-        <v>1.35</v>
-      </c>
-      <c r="T39">
-        <v>2.76</v>
-      </c>
       <c r="U39">
-        <v>2.64</v>
+        <v>2.04</v>
       </c>
       <c r="V39">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="W39">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X39">
         <v>1.01</v>
       </c>
       <c r="Y39">
+        <v>1.08</v>
+      </c>
+      <c r="Z39">
+        <v>6</v>
+      </c>
+      <c r="AA39">
+        <v>1.4</v>
+      </c>
+      <c r="AB39">
+        <v>2.75</v>
+      </c>
+      <c r="AC39">
+        <v>2.12</v>
+      </c>
+      <c r="AD39">
+        <v>1.65</v>
+      </c>
+      <c r="AE39">
         <v>1.24</v>
       </c>
-      <c r="Z39">
-        <v>3.34</v>
-      </c>
-      <c r="AA39">
-        <v>1.82</v>
-      </c>
-      <c r="AB39">
-        <v>1.85</v>
-      </c>
-      <c r="AC39">
-        <v>2.97</v>
-      </c>
-      <c r="AD39">
-        <v>1.3</v>
-      </c>
-      <c r="AE39">
-        <v>1.08</v>
-      </c>
       <c r="AF39">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="AG39">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.7</v>
+        <v>1.06</v>
       </c>
       <c r="AK39">
-        <v>1.29</v>
+        <v>2.8</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
+        <v>1.59</v>
+      </c>
+      <c r="O43">
+        <v>4</v>
+      </c>
+      <c r="P43">
+        <v>4.65</v>
+      </c>
+      <c r="Q43">
+        <v>2</v>
+      </c>
+      <c r="R43">
         <v>2.45</v>
       </c>
-      <c r="O43">
-        <v>3.85</v>
-      </c>
-      <c r="P43">
-        <v>2.18</v>
-      </c>
-      <c r="Q43">
-        <v>3.36</v>
-      </c>
-      <c r="R43">
-        <v>2.34</v>
-      </c>
       <c r="S43">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T43">
         <v>4</v>
       </c>
       <c r="U43">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V43">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="W43">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X43">
         <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z43">
-        <v>5.3</v>
+        <v>5.15</v>
       </c>
       <c r="AA43">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AB43">
         <v>2.7</v>
       </c>
       <c r="AC43">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AD43">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AE43">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF43">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AG43">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.6</v>
+        <v>1.19</v>
       </c>
       <c r="AK43">
-        <v>1.4</v>
+        <v>2.38</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.59</v>
+        <v>2.45</v>
       </c>
       <c r="O44">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="P44">
-        <v>4.65</v>
+        <v>2.18</v>
       </c>
       <c r="Q44">
-        <v>2</v>
+        <v>3.36</v>
       </c>
       <c r="R44">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="S44">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T44">
         <v>4</v>
       </c>
       <c r="U44">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V44">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="W44">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X44">
         <v>1.02</v>
       </c>
       <c r="Y44">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z44">
-        <v>5.15</v>
+        <v>5.3</v>
       </c>
       <c r="AA44">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AB44">
         <v>2.7</v>
       </c>
       <c r="AC44">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AD44">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AE44">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF44">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AG44">
-        <v>2.5</v>
+        <v>2.81</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.19</v>
+        <v>1.6</v>
       </c>
       <c r="AK44">
-        <v>2.38</v>
+        <v>1.4</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="O54">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="P54">
         <v>6.25</v>
       </c>
       <c r="Q54">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="R54">
-        <v>2.37</v>
+        <v>2.44</v>
       </c>
       <c r="S54">
         <v>1.3</v>
       </c>
       <c r="T54">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="U54">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="V54">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W54">
         <v>1.1</v>
       </c>
       <c r="X54">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y54">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z54">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AA54">
+        <v>1.73</v>
+      </c>
+      <c r="AB54">
+        <v>1.98</v>
+      </c>
+      <c r="AC54">
+        <v>2.78</v>
+      </c>
+      <c r="AD54">
+        <v>1.37</v>
+      </c>
+      <c r="AE54">
+        <v>1.09</v>
+      </c>
+      <c r="AF54">
+        <v>1.95</v>
+      </c>
+      <c r="AG54">
         <v>1.8</v>
-      </c>
-      <c r="AB54">
-        <v>1.94</v>
-      </c>
-      <c r="AC54">
-        <v>2.88</v>
-      </c>
-      <c r="AD54">
-        <v>1.42</v>
-      </c>
-      <c r="AE54">
-        <v>1.08</v>
-      </c>
-      <c r="AF54">
-        <v>2</v>
-      </c>
-      <c r="AG54">
-        <v>1.75</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>1.05</v>
       </c>
       <c r="AK54">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9283,71 +9283,71 @@
         <v>1.5</v>
       </c>
       <c r="Q55">
-        <v>6.35</v>
+        <v>6.2</v>
       </c>
       <c r="R55">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S55">
+        <v>1.33</v>
+      </c>
+      <c r="T55">
+        <v>3.09</v>
+      </c>
+      <c r="U55">
+        <v>2.5</v>
+      </c>
+      <c r="V55">
+        <v>1.46</v>
+      </c>
+      <c r="W55">
+        <v>1.07</v>
+      </c>
+      <c r="X55">
+        <v>1.03</v>
+      </c>
+      <c r="Y55">
+        <v>1.19</v>
+      </c>
+      <c r="Z55">
+        <v>3.78</v>
+      </c>
+      <c r="AA55">
+        <v>1.75</v>
+      </c>
+      <c r="AB55">
+        <v>2</v>
+      </c>
+      <c r="AC55">
+        <v>2.74</v>
+      </c>
+      <c r="AD55">
         <v>1.35</v>
       </c>
-      <c r="T55">
-        <v>2.87</v>
-      </c>
-      <c r="U55">
-        <v>2.63</v>
-      </c>
-      <c r="V55">
-        <v>1.4</v>
-      </c>
-      <c r="W55">
-        <v>1.06</v>
-      </c>
-      <c r="X55">
-        <v>1</v>
-      </c>
-      <c r="Y55">
-        <v>1.22</v>
-      </c>
-      <c r="Z55">
-        <v>3.5</v>
-      </c>
-      <c r="AA55">
+      <c r="AE55">
+        <v>1.1</v>
+      </c>
+      <c r="AF55">
+        <v>1.8</v>
+      </c>
+      <c r="AG55">
         <v>1.83</v>
       </c>
-      <c r="AB55">
-        <v>1.95</v>
-      </c>
-      <c r="AC55">
-        <v>2.97</v>
-      </c>
-      <c r="AD55">
-        <v>1.3</v>
-      </c>
-      <c r="AE55">
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ55">
+        <v>1.19</v>
+      </c>
+      <c r="AK55">
         <v>1.08</v>
-      </c>
-      <c r="AF55">
-        <v>1.95</v>
-      </c>
-      <c r="AG55">
-        <v>1.77</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ55">
-        <v>1.21</v>
-      </c>
-      <c r="AK55">
-        <v>1.07</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -10913,55 +10913,55 @@
         <v>9</v>
       </c>
       <c r="Q65">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="R65">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S65">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T65">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="U65">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="V65">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W65">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X65">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y65">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z65">
         <v>2.75</v>
       </c>
       <c r="AA65">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="AB65">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC65">
-        <v>3.58</v>
+        <v>3.86</v>
       </c>
       <c r="AD65">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AE65">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF65">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="AG65">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>1.22</v>
       </c>
       <c r="AK65">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
+        <v>1.75</v>
+      </c>
+      <c r="O67">
+        <v>3.4</v>
+      </c>
+      <c r="P67">
+        <v>3.9</v>
+      </c>
+      <c r="Q67">
+        <v>2.43</v>
+      </c>
+      <c r="R67">
         <v>2.2</v>
       </c>
-      <c r="O67">
-        <v>3.15</v>
-      </c>
-      <c r="P67">
-        <v>2.9</v>
-      </c>
-      <c r="Q67">
-        <v>2.75</v>
-      </c>
-      <c r="R67">
-        <v>2.03</v>
-      </c>
       <c r="S67">
+        <v>1.33</v>
+      </c>
+      <c r="T67">
+        <v>3.1</v>
+      </c>
+      <c r="U67">
+        <v>2.74</v>
+      </c>
+      <c r="V67">
         <v>1.44</v>
       </c>
-      <c r="T67">
-        <v>2.71</v>
-      </c>
-      <c r="U67">
-        <v>2.87</v>
-      </c>
-      <c r="V67">
-        <v>1.35</v>
-      </c>
       <c r="W67">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X67">
         <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="Z67">
-        <v>3.05</v>
+        <v>3.86</v>
       </c>
       <c r="AA67">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="AB67">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AC67">
-        <v>4.03</v>
+        <v>3.13</v>
       </c>
       <c r="AD67">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AE67">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AF67">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="AG67">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK67">
-        <v>1.58</v>
+        <v>1.91</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.75</v>
+        <v>2.28</v>
       </c>
       <c r="O68">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P68">
-        <v>3.9</v>
+        <v>2.52</v>
       </c>
       <c r="Q68">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="R68">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S68">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T68">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="U68">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="V68">
         <v>1.44</v>
       </c>
       <c r="W68">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X68">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y68">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z68">
-        <v>3.86</v>
+        <v>3.9</v>
       </c>
       <c r="AA68">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AB68">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AC68">
-        <v>3.13</v>
+        <v>2.66</v>
       </c>
       <c r="AD68">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE68">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF68">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AG68">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>1.26</v>
       </c>
       <c r="AK68">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="O71">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="P71">
-        <v>2.52</v>
+        <v>2.9</v>
       </c>
       <c r="Q71">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="R71">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="S71">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="T71">
-        <v>3.18</v>
+        <v>2.71</v>
       </c>
       <c r="U71">
-        <v>2.5</v>
+        <v>2.87</v>
       </c>
       <c r="V71">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="W71">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X71">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="Z71">
-        <v>3.9</v>
+        <v>3.05</v>
       </c>
       <c r="AA71">
-        <v>1.74</v>
+        <v>2.06</v>
       </c>
       <c r="AB71">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
       <c r="AC71">
-        <v>2.66</v>
+        <v>4.03</v>
       </c>
       <c r="AD71">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AE71">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AF71">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AG71">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK71">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="O80">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="P80">
-        <v>2.15</v>
+        <v>2.47</v>
       </c>
       <c r="Q80">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="R80">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="S80">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="T80">
-        <v>4.4</v>
+        <v>3.32</v>
       </c>
       <c r="U80">
-        <v>1.91</v>
+        <v>2.27</v>
       </c>
       <c r="V80">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="W80">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="X80">
         <v>1.01</v>
       </c>
       <c r="Y80">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="Z80">
-        <v>6.45</v>
+        <v>5</v>
       </c>
       <c r="AA80">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AB80">
-        <v>2.97</v>
+        <v>2.33</v>
       </c>
       <c r="AC80">
-        <v>1.85</v>
+        <v>2.28</v>
       </c>
       <c r="AD80">
-        <v>1.88</v>
+        <v>1.5</v>
       </c>
       <c r="AE80">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AF80">
-        <v>1.31</v>
+        <v>1.46</v>
       </c>
       <c r="AG80">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK80">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="O81">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="P81">
-        <v>2.47</v>
+        <v>2.15</v>
       </c>
       <c r="Q81">
-        <v>2.72</v>
+        <v>2.9</v>
       </c>
       <c r="R81">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="S81">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="T81">
-        <v>3.32</v>
+        <v>4.4</v>
       </c>
       <c r="U81">
-        <v>2.27</v>
+        <v>1.91</v>
       </c>
       <c r="V81">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="W81">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="X81">
         <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="Z81">
-        <v>5</v>
+        <v>6.45</v>
       </c>
       <c r="AA81">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AB81">
-        <v>2.33</v>
+        <v>2.97</v>
       </c>
       <c r="AC81">
-        <v>2.28</v>
+        <v>1.85</v>
       </c>
       <c r="AD81">
-        <v>1.5</v>
+        <v>1.88</v>
       </c>
       <c r="AE81">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="AF81">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="AG81">
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK81">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -15969,7 +15969,7 @@
         <v>2.78</v>
       </c>
       <c r="R96">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="S96">
         <v>1.29</v>
@@ -15990,7 +15990,7 @@
         <v>1</v>
       </c>
       <c r="Y96">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z96">
         <v>3.92</v>
@@ -16011,10 +16011,10 @@
         <v>1.13</v>
       </c>
       <c r="AF96">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AG96">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16156,13 +16156,13 @@
         <v>1.17</v>
       </c>
       <c r="Z97">
-        <v>3.95</v>
+        <v>3.98</v>
       </c>
       <c r="AA97">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AB97">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AC97">
         <v>2.59</v>
@@ -16171,7 +16171,7 @@
         <v>1.44</v>
       </c>
       <c r="AE97">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF97">
         <v>1.6</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.41</v>
+        <v>3.8</v>
       </c>
       <c r="O98">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="P98">
-        <v>5.5</v>
+        <v>1.78</v>
       </c>
       <c r="Q98">
-        <v>1.86</v>
+        <v>4.4</v>
       </c>
       <c r="R98">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="S98">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="T98">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="U98">
-        <v>2.17</v>
+        <v>2.54</v>
       </c>
       <c r="V98">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="W98">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X98">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y98">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="Z98">
-        <v>5.5</v>
+        <v>3.79</v>
       </c>
       <c r="AA98">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AB98">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="AC98">
-        <v>2.24</v>
+        <v>2.83</v>
       </c>
       <c r="AD98">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="AE98">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AF98">
         <v>1.67</v>
       </c>
       <c r="AG98">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="AK98">
-        <v>2.66</v>
+        <v>1.16</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,80 +16446,80 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="O99">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P99">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q99">
-        <v>2.64</v>
+        <v>2.81</v>
       </c>
       <c r="R99">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="S99">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T99">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="U99">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="V99">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="W99">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X99">
         <v>1.01</v>
       </c>
       <c r="Y99">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z99">
-        <v>3.58</v>
+        <v>3.49</v>
       </c>
       <c r="AA99">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AB99">
+        <v>1.87</v>
+      </c>
+      <c r="AC99">
+        <v>3.37</v>
+      </c>
+      <c r="AD99">
+        <v>1.3</v>
+      </c>
+      <c r="AE99">
+        <v>1.1</v>
+      </c>
+      <c r="AF99">
+        <v>1.69</v>
+      </c>
+      <c r="AG99">
         <v>2</v>
       </c>
-      <c r="AC99">
-        <v>2.88</v>
-      </c>
-      <c r="AD99">
-        <v>1.32</v>
-      </c>
-      <c r="AE99">
-        <v>1.08</v>
-      </c>
-      <c r="AF99">
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ99">
+        <v>1.25</v>
+      </c>
+      <c r="AK99">
         <v>1.62</v>
-      </c>
-      <c r="AG99">
-        <v>2.1</v>
-      </c>
-      <c r="AH99" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI99" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ99">
-        <v>1.26</v>
-      </c>
-      <c r="AK99">
-        <v>1.6</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.47</v>
+        <v>2.15</v>
       </c>
       <c r="O100">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="P100">
-        <v>5.4</v>
+        <v>3.05</v>
       </c>
       <c r="Q100">
+        <v>2.64</v>
+      </c>
+      <c r="R100">
+        <v>2.08</v>
+      </c>
+      <c r="S100">
+        <v>1.35</v>
+      </c>
+      <c r="T100">
+        <v>2.76</v>
+      </c>
+      <c r="U100">
+        <v>2.63</v>
+      </c>
+      <c r="V100">
+        <v>1.44</v>
+      </c>
+      <c r="W100">
+        <v>1.05</v>
+      </c>
+      <c r="X100">
+        <v>1.01</v>
+      </c>
+      <c r="Y100">
+        <v>1.21</v>
+      </c>
+      <c r="Z100">
+        <v>3.58</v>
+      </c>
+      <c r="AA100">
+        <v>1.8</v>
+      </c>
+      <c r="AB100">
         <v>2</v>
       </c>
-      <c r="R100">
-        <v>2.66</v>
-      </c>
-      <c r="S100">
-        <v>1.22</v>
-      </c>
-      <c r="T100">
-        <v>3.8</v>
-      </c>
-      <c r="U100">
-        <v>2.2</v>
-      </c>
-      <c r="V100">
+      <c r="AC100">
+        <v>2.88</v>
+      </c>
+      <c r="AD100">
+        <v>1.32</v>
+      </c>
+      <c r="AE100">
+        <v>1.08</v>
+      </c>
+      <c r="AF100">
         <v>1.62</v>
       </c>
-      <c r="W100">
-        <v>1.15</v>
-      </c>
-      <c r="X100">
-        <v>1.02</v>
-      </c>
-      <c r="Y100">
-        <v>1.15</v>
-      </c>
-      <c r="Z100">
-        <v>4.7</v>
-      </c>
-      <c r="AA100">
-        <v>1.47</v>
-      </c>
-      <c r="AB100">
-        <v>2.55</v>
-      </c>
-      <c r="AC100">
-        <v>2.18</v>
-      </c>
-      <c r="AD100">
-        <v>1.58</v>
-      </c>
-      <c r="AE100">
-        <v>1.21</v>
-      </c>
-      <c r="AF100">
-        <v>1.55</v>
-      </c>
       <c r="AG100">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.07</v>
+        <v>1.26</v>
       </c>
       <c r="AK100">
-        <v>2.29</v>
+        <v>1.6</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>3.8</v>
+        <v>1.41</v>
       </c>
       <c r="O101">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="P101">
-        <v>1.78</v>
+        <v>5.5</v>
       </c>
       <c r="Q101">
-        <v>4.4</v>
+        <v>1.86</v>
       </c>
       <c r="R101">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="S101">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="T101">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="U101">
-        <v>2.54</v>
+        <v>2.17</v>
       </c>
       <c r="V101">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="W101">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X101">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y101">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z101">
-        <v>3.79</v>
+        <v>5.5</v>
       </c>
       <c r="AA101">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AB101">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="AC101">
-        <v>2.83</v>
+        <v>2.24</v>
       </c>
       <c r="AD101">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="AE101">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AF101">
         <v>1.67</v>
       </c>
       <c r="AG101">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AK101">
-        <v>1.16</v>
+        <v>2.66</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,80 +16935,80 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.24</v>
+        <v>1.47</v>
       </c>
       <c r="O102">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="P102">
-        <v>3.1</v>
+        <v>5.4</v>
       </c>
       <c r="Q102">
-        <v>2.81</v>
+        <v>2</v>
       </c>
       <c r="R102">
-        <v>2.03</v>
+        <v>2.66</v>
       </c>
       <c r="S102">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="T102">
-        <v>2.77</v>
+        <v>3.8</v>
       </c>
       <c r="U102">
-        <v>2.61</v>
+        <v>2.2</v>
       </c>
       <c r="V102">
-        <v>1.39</v>
+        <v>1.62</v>
       </c>
       <c r="W102">
+        <v>1.15</v>
+      </c>
+      <c r="X102">
+        <v>1.02</v>
+      </c>
+      <c r="Y102">
+        <v>1.15</v>
+      </c>
+      <c r="Z102">
+        <v>4.7</v>
+      </c>
+      <c r="AA102">
+        <v>1.47</v>
+      </c>
+      <c r="AB102">
+        <v>2.55</v>
+      </c>
+      <c r="AC102">
+        <v>2.18</v>
+      </c>
+      <c r="AD102">
+        <v>1.58</v>
+      </c>
+      <c r="AE102">
+        <v>1.21</v>
+      </c>
+      <c r="AF102">
+        <v>1.55</v>
+      </c>
+      <c r="AG102">
+        <v>2.15</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ102">
         <v>1.07</v>
       </c>
-      <c r="X102">
-        <v>1.01</v>
-      </c>
-      <c r="Y102">
-        <v>1.25</v>
-      </c>
-      <c r="Z102">
-        <v>3.49</v>
-      </c>
-      <c r="AA102">
-        <v>1.9</v>
-      </c>
-      <c r="AB102">
-        <v>1.87</v>
-      </c>
-      <c r="AC102">
-        <v>3.37</v>
-      </c>
-      <c r="AD102">
-        <v>1.3</v>
-      </c>
-      <c r="AE102">
-        <v>1.1</v>
-      </c>
-      <c r="AF102">
-        <v>1.69</v>
-      </c>
-      <c r="AG102">
-        <v>2</v>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ102">
-        <v>1.25</v>
-      </c>
       <c r="AK102">
-        <v>1.62</v>
+        <v>2.29</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17777,31 +17777,31 @@
         <v>1.57</v>
       </c>
       <c r="W107">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X107">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y107">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z107">
         <v>4.3</v>
       </c>
       <c r="AA107">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AB107">
         <v>2.15</v>
       </c>
       <c r="AC107">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="AD107">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AE107">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF107">
         <v>1.67</v>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK107">
-        <v>2.51</v>
+        <v>2.46</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17934,13 +17934,13 @@
         <v>3.08</v>
       </c>
       <c r="U108">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="V108">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W108">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X108">
         <v>1.02</v>
@@ -17949,7 +17949,7 @@
         <v>1.18</v>
       </c>
       <c r="Z108">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="AA108">
         <v>1.62</v>
@@ -17958,7 +17958,7 @@
         <v>2.11</v>
       </c>
       <c r="AC108">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="AD108">
         <v>1.39</v>
@@ -17983,7 +17983,7 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AK108">
         <v>2.6</v>
@@ -18432,7 +18432,7 @@
         <v>1.03</v>
       </c>
       <c r="X111">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y111">
         <v>1.51</v>
@@ -18441,10 +18441,10 @@
         <v>2.33</v>
       </c>
       <c r="AA111">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AB111">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AC111">
         <v>5.15</v>
@@ -18453,7 +18453,7 @@
         <v>1.14</v>
       </c>
       <c r="AE111">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF111">
         <v>2.17</v>
@@ -19552,7 +19552,7 @@
         <v>0</v>
       </c>
       <c r="Q118">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="R118">
         <v>2.19</v>
@@ -19561,7 +19561,7 @@
         <v>1.27</v>
       </c>
       <c r="T118">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U118">
         <v>2.32</v>
@@ -19579,10 +19579,10 @@
         <v>1.19</v>
       </c>
       <c r="Z118">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="AA118">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AB118">
         <v>2.01</v>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AK118">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AL118">
         <v>0</v>

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -615,45 +615,45 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
         <v>3.4</v>
       </c>
       <c r="O2">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P2">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q2">
-        <v>4.36</v>
+        <v>4.39</v>
       </c>
       <c r="R2">
         <v>2</v>
       </c>
       <c r="S2">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T2">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="U2">
         <v>3.25</v>
@@ -668,22 +668,22 @@
         <v>1.05</v>
       </c>
       <c r="Y2">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z2">
         <v>2.88</v>
       </c>
       <c r="AA2">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AB2">
         <v>1.6</v>
       </c>
       <c r="AC2">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AD2">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE2">
         <v>1.01</v>
@@ -701,41 +701,41 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13", "48", "79"]</t>
         </is>
       </c>
       <c r="AJ2">
+        <v>1.62</v>
+      </c>
+      <c r="AK2">
         <v>1.25</v>
       </c>
-      <c r="AK2">
-        <v>1.22</v>
-      </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="O4">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P4">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q4">
         <v>4.53</v>
@@ -988,7 +988,7 @@
         <v>1.42</v>
       </c>
       <c r="W4">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X4">
         <v>1.04</v>
@@ -1012,7 +1012,7 @@
         <v>1.36</v>
       </c>
       <c r="AE4">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF4">
         <v>1.68</v>
@@ -1133,10 +1133,10 @@
         <v>3.4</v>
       </c>
       <c r="Q5">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="R5">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="S5">
         <v>1.34</v>
@@ -1151,10 +1151,10 @@
         <v>1.4</v>
       </c>
       <c r="W5">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
         <v>1.21</v>
@@ -1178,10 +1178,10 @@
         <v>1.09</v>
       </c>
       <c r="AF5">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG5">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>1.18</v>
       </c>
       <c r="AK5">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="O6">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="P6">
-        <v>3.34</v>
+        <v>2.96</v>
       </c>
       <c r="Q6">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R6">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S6">
         <v>1.33</v>
       </c>
       <c r="T6">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="U6">
-        <v>2.61</v>
+        <v>2.8</v>
       </c>
       <c r="V6">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W6">
         <v>1.08</v>
       </c>
       <c r="X6">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z6">
-        <v>3.8</v>
+        <v>3.28</v>
       </c>
       <c r="AA6">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AB6">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC6">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="AD6">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE6">
         <v>1.1</v>
       </c>
       <c r="AF6">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG6">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>1.25</v>
       </c>
       <c r="AK6">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1459,22 +1459,22 @@
         <v>3.39</v>
       </c>
       <c r="Q7">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="R7">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="S7">
         <v>1.36</v>
       </c>
       <c r="T7">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="U7">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="V7">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W7">
         <v>1.06</v>
@@ -1483,25 +1483,25 @@
         <v>1.05</v>
       </c>
       <c r="Y7">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z7">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="AA7">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="AB7">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="AC7">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AD7">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE7">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF7">
         <v>1.75</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AK7">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1776,19 +1776,19 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="O9">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P9">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="Q9">
         <v>2.3</v>
       </c>
       <c r="R9">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="S9">
         <v>1.2</v>
@@ -1797,13 +1797,13 @@
         <v>4</v>
       </c>
       <c r="U9">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V9">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="W9">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X9">
         <v>1.01</v>
@@ -1818,10 +1818,10 @@
         <v>1.27</v>
       </c>
       <c r="AB9">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="AC9">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AD9">
         <v>2</v>
@@ -1951,22 +1951,22 @@
         <v>3.1</v>
       </c>
       <c r="R10">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="S10">
         <v>1.36</v>
       </c>
       <c r="T10">
-        <v>2.91</v>
+        <v>2.8</v>
       </c>
       <c r="U10">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="V10">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="W10">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X10">
         <v>1.03</v>
@@ -1975,22 +1975,22 @@
         <v>1.25</v>
       </c>
       <c r="Z10">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AA10">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB10">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AC10">
-        <v>3.08</v>
+        <v>3.28</v>
       </c>
       <c r="AD10">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE10">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF10">
         <v>1.6</v>
@@ -2012,7 +2012,7 @@
         <v>1.1</v>
       </c>
       <c r="AK10">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2268,25 +2268,25 @@
         <v>2.31</v>
       </c>
       <c r="O12">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="P12">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="Q12">
         <v>2.8</v>
       </c>
       <c r="R12">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="S12">
         <v>1.36</v>
       </c>
       <c r="T12">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="U12">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="V12">
         <v>1.36</v>
@@ -2295,34 +2295,34 @@
         <v>1.05</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y12">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z12">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AA12">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AB12">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC12">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AD12">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE12">
         <v>1.04</v>
       </c>
       <c r="AF12">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG12">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK12">
         <v>1.57</v>
@@ -2467,10 +2467,10 @@
         <v>0</v>
       </c>
       <c r="AA13">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB13">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC13">
         <v>0</v>
@@ -2597,19 +2597,19 @@
         <v>4.6</v>
       </c>
       <c r="P14">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Q14">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="R14">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S14">
         <v>1.28</v>
       </c>
       <c r="T14">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U14">
         <v>2.55</v>
@@ -2627,10 +2627,10 @@
         <v>1.17</v>
       </c>
       <c r="Z14">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AA14">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AB14">
         <v>2.04</v>
@@ -2642,7 +2642,7 @@
         <v>1.38</v>
       </c>
       <c r="AE14">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF14">
         <v>1.95</v>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK14">
         <v>3</v>
@@ -2763,7 +2763,7 @@
         <v>4.15</v>
       </c>
       <c r="Q15">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="R15">
         <v>2.1</v>
@@ -2772,7 +2772,7 @@
         <v>1.4</v>
       </c>
       <c r="T15">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="U15">
         <v>2.73</v>
@@ -2784,34 +2784,34 @@
         <v>1.08</v>
       </c>
       <c r="X15">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z15">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="AA15">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="AB15">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC15">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="AD15">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE15">
         <v>1.06</v>
       </c>
       <c r="AF15">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AG15">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK15">
         <v>1.87</v>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="N16">
-        <v>6.42</v>
+        <v>6.38</v>
       </c>
       <c r="O16">
         <v>4</v>
@@ -2926,22 +2926,22 @@
         <v>1.4</v>
       </c>
       <c r="Q16">
-        <v>7</v>
+        <v>6.34</v>
       </c>
       <c r="R16">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="S16">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T16">
         <v>2.9</v>
       </c>
       <c r="U16">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
       <c r="V16">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W16">
         <v>1.06</v>
@@ -2956,25 +2956,25 @@
         <v>3.28</v>
       </c>
       <c r="AA16">
+        <v>1.83</v>
+      </c>
+      <c r="AB16">
         <v>1.84</v>
       </c>
-      <c r="AB16">
-        <v>1.83</v>
-      </c>
       <c r="AC16">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AD16">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE16">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF16">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AG16">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>2.45</v>
       </c>
       <c r="AK16">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3086,13 +3086,13 @@
         <v>3.05</v>
       </c>
       <c r="P17">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="Q17">
-        <v>3.61</v>
+        <v>3.66</v>
       </c>
       <c r="R17">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="S17">
         <v>1.45</v>
@@ -3101,10 +3101,10 @@
         <v>2.5</v>
       </c>
       <c r="U17">
-        <v>3.02</v>
+        <v>3.17</v>
       </c>
       <c r="V17">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W17">
         <v>1.02</v>
@@ -3125,7 +3125,7 @@
         <v>1.72</v>
       </c>
       <c r="AC17">
-        <v>3.79</v>
+        <v>3.82</v>
       </c>
       <c r="AD17">
         <v>1.21</v>
@@ -3249,58 +3249,58 @@
         <v>3.1</v>
       </c>
       <c r="P18">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="Q18">
-        <v>2.71</v>
+        <v>2.65</v>
       </c>
       <c r="R18">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="S18">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T18">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="U18">
-        <v>3.02</v>
+        <v>2.97</v>
       </c>
       <c r="V18">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W18">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X18">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y18">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="Z18">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="AA18">
-        <v>2.31</v>
+        <v>2.23</v>
       </c>
       <c r="AB18">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AC18">
-        <v>4.24</v>
+        <v>4.03</v>
       </c>
       <c r="AD18">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AE18">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF18">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AG18">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AK18">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,31 +3406,31 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="O19">
-        <v>4.7</v>
+        <v>4.62</v>
       </c>
       <c r="P19">
-        <v>6.3</v>
+        <v>5.76</v>
       </c>
       <c r="Q19">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="R19">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="S19">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T19">
-        <v>3.21</v>
+        <v>3.08</v>
       </c>
       <c r="U19">
-        <v>2.68</v>
+        <v>2.73</v>
       </c>
       <c r="V19">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W19">
         <v>1.08</v>
@@ -3445,22 +3445,22 @@
         <v>3.58</v>
       </c>
       <c r="AA19">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AB19">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AC19">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AD19">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE19">
         <v>1.09</v>
       </c>
       <c r="AF19">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="AG19">
         <v>1.71</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK19">
-        <v>2.97</v>
+        <v>2.84</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3575,19 +3575,19 @@
         <v>3.3</v>
       </c>
       <c r="P20">
-        <v>2.93</v>
+        <v>3.15</v>
       </c>
       <c r="Q20">
         <v>2.8</v>
       </c>
       <c r="R20">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S20">
         <v>1.3</v>
       </c>
       <c r="T20">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U20">
         <v>2.44</v>
@@ -3596,7 +3596,7 @@
         <v>1.44</v>
       </c>
       <c r="W20">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X20">
         <v>1.01</v>
@@ -3608,10 +3608,10 @@
         <v>4</v>
       </c>
       <c r="AA20">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AB20">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AC20">
         <v>2.88</v>
@@ -3623,7 +3623,7 @@
         <v>1.11</v>
       </c>
       <c r="AF20">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG20">
         <v>2.15</v>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AK20">
         <v>1.56</v>
@@ -3771,10 +3771,10 @@
         <v>0</v>
       </c>
       <c r="AA21">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AB21">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="AC21">
         <v>0</v>
@@ -3904,7 +3904,7 @@
         <v>3.25</v>
       </c>
       <c r="Q22">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="R22">
         <v>2.1</v>
@@ -3913,13 +3913,13 @@
         <v>1.36</v>
       </c>
       <c r="T22">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="U22">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="V22">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W22">
         <v>1.05</v>
@@ -3931,16 +3931,16 @@
         <v>1.33</v>
       </c>
       <c r="Z22">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AA22">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="AB22">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC22">
-        <v>3.42</v>
+        <v>3.9</v>
       </c>
       <c r="AD22">
         <v>1.22</v>
@@ -3949,10 +3949,10 @@
         <v>1.05</v>
       </c>
       <c r="AF22">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AG22">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK22">
         <v>1.73</v>
@@ -4058,7 +4058,7 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="O23">
         <v>3.2</v>
@@ -4067,25 +4067,25 @@
         <v>3.02</v>
       </c>
       <c r="Q23">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="R23">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S23">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T23">
-        <v>2.57</v>
+        <v>2.51</v>
       </c>
       <c r="U23">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="V23">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W23">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X23">
         <v>1.02</v>
@@ -4094,10 +4094,10 @@
         <v>1.34</v>
       </c>
       <c r="Z23">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="AA23">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AB23">
         <v>1.7</v>
@@ -4106,32 +4106,32 @@
         <v>3.58</v>
       </c>
       <c r="AD23">
+        <v>1.21</v>
+      </c>
+      <c r="AE23">
+        <v>1.03</v>
+      </c>
+      <c r="AF23">
+        <v>1.83</v>
+      </c>
+      <c r="AG23">
+        <v>1.91</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
         <v>1.25</v>
       </c>
-      <c r="AE23">
-        <v>1.04</v>
-      </c>
-      <c r="AF23">
-        <v>1.81</v>
-      </c>
-      <c r="AG23">
-        <v>1.85</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23">
-        <v>1.29</v>
-      </c>
       <c r="AK23">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.07</v>
+        <v>1.97</v>
       </c>
       <c r="O24">
         <v>3.35</v>
       </c>
       <c r="P24">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="Q24">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="R24">
+        <v>1.96</v>
+      </c>
+      <c r="S24">
+        <v>1.39</v>
+      </c>
+      <c r="T24">
+        <v>2.61</v>
+      </c>
+      <c r="U24">
+        <v>3.2</v>
+      </c>
+      <c r="V24">
+        <v>1.3</v>
+      </c>
+      <c r="W24">
+        <v>1.03</v>
+      </c>
+      <c r="X24">
+        <v>1.05</v>
+      </c>
+      <c r="Y24">
+        <v>1.34</v>
+      </c>
+      <c r="Z24">
+        <v>2.78</v>
+      </c>
+      <c r="AA24">
+        <v>2.15</v>
+      </c>
+      <c r="AB24">
+        <v>1.6</v>
+      </c>
+      <c r="AC24">
+        <v>4</v>
+      </c>
+      <c r="AD24">
+        <v>1.17</v>
+      </c>
+      <c r="AE24">
+        <v>1.03</v>
+      </c>
+      <c r="AF24">
         <v>1.95</v>
       </c>
-      <c r="S24">
-        <v>1.4</v>
-      </c>
-      <c r="T24">
-        <v>2.58</v>
-      </c>
-      <c r="U24">
-        <v>3.3</v>
-      </c>
-      <c r="V24">
-        <v>1.29</v>
-      </c>
-      <c r="W24">
-        <v>1.04</v>
-      </c>
-      <c r="X24">
-        <v>1.03</v>
-      </c>
-      <c r="Y24">
-        <v>1.32</v>
-      </c>
-      <c r="Z24">
-        <v>2.74</v>
-      </c>
-      <c r="AA24">
-        <v>2.17</v>
-      </c>
-      <c r="AB24">
-        <v>1.59</v>
-      </c>
-      <c r="AC24">
-        <v>4.1</v>
-      </c>
-      <c r="AD24">
-        <v>1.19</v>
-      </c>
-      <c r="AE24">
-        <v>1.04</v>
-      </c>
-      <c r="AF24">
-        <v>1.9</v>
-      </c>
       <c r="AG24">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O25">
         <v>3</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="O26">
         <v>3.05</v>
@@ -4562,7 +4562,7 @@
         <v>1.89</v>
       </c>
       <c r="S26">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="T26">
         <v>2.26</v>
@@ -4583,16 +4583,16 @@
         <v>1.58</v>
       </c>
       <c r="Z26">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="AA26">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AB26">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AC26">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AD26">
         <v>1.1</v>
@@ -4604,7 +4604,7 @@
         <v>2.15</v>
       </c>
       <c r="AG26">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="N27">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="O27">
         <v>3.6</v>
@@ -4719,22 +4719,22 @@
         <v>1.74</v>
       </c>
       <c r="Q27">
-        <v>5.16</v>
+        <v>5.27</v>
       </c>
       <c r="R27">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="S27">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T27">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="U27">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="V27">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W27">
         <v>1.03</v>
@@ -4746,16 +4746,16 @@
         <v>1.28</v>
       </c>
       <c r="Z27">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="AA27">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="AB27">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC27">
-        <v>3.62</v>
+        <v>3.71</v>
       </c>
       <c r="AD27">
         <v>1.27</v>
@@ -4764,10 +4764,10 @@
         <v>1.04</v>
       </c>
       <c r="AF27">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AG27">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>3.06</v>
+        <v>3.45</v>
       </c>
       <c r="O28">
         <v>3.15</v>
       </c>
       <c r="P28">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -4912,10 +4912,10 @@
         <v>0</v>
       </c>
       <c r="AA28">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB28">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC28">
         <v>0</v>
@@ -5048,7 +5048,7 @@
         <v>2.45</v>
       </c>
       <c r="R29">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="S29">
         <v>1.36</v>
@@ -5057,7 +5057,7 @@
         <v>2.7</v>
       </c>
       <c r="U29">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="V29">
         <v>1.4</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK29">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="O30">
-        <v>3.7</v>
+        <v>4.18</v>
       </c>
       <c r="P30">
-        <v>4.6</v>
+        <v>6.25</v>
       </c>
       <c r="Q30">
-        <v>2.22</v>
+        <v>1.98</v>
       </c>
       <c r="R30">
-        <v>2.13</v>
+        <v>2.26</v>
       </c>
       <c r="S30">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="T30">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="U30">
-        <v>2.76</v>
+        <v>2.48</v>
       </c>
       <c r="V30">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="W30">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X30">
         <v>1</v>
       </c>
       <c r="Y30">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="Z30">
-        <v>3.2</v>
+        <v>3.78</v>
       </c>
       <c r="AA30">
-        <v>1.93</v>
+        <v>1.74</v>
       </c>
       <c r="AB30">
-        <v>1.79</v>
+        <v>1.99</v>
       </c>
       <c r="AC30">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="AD30">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AE30">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF30">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG30">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AK30">
-        <v>1.99</v>
+        <v>2.39</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,16 +5362,16 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="O31">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="P31">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="Q31">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="R31">
         <v>1.97</v>
@@ -5386,10 +5386,10 @@
         <v>2.97</v>
       </c>
       <c r="V31">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W31">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X31">
         <v>1.04</v>
@@ -5401,13 +5401,13 @@
         <v>2.7</v>
       </c>
       <c r="AA31">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AB31">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AC31">
-        <v>4.12</v>
+        <v>4.1</v>
       </c>
       <c r="AD31">
         <v>1.18</v>
@@ -5416,10 +5416,10 @@
         <v>1.03</v>
       </c>
       <c r="AF31">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AG31">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AK31">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5531,7 +5531,7 @@
         <v>8</v>
       </c>
       <c r="P32">
-        <v>11.64</v>
+        <v>13</v>
       </c>
       <c r="Q32">
         <v>1.44</v>
@@ -5543,13 +5543,13 @@
         <v>1.16</v>
       </c>
       <c r="T32">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="U32">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V32">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="W32">
         <v>1.2</v>
@@ -5561,28 +5561,28 @@
         <v>1.06</v>
       </c>
       <c r="Z32">
-        <v>6.05</v>
+        <v>6.2</v>
       </c>
       <c r="AA32">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AB32">
         <v>3.1</v>
       </c>
       <c r="AC32">
+        <v>1.83</v>
+      </c>
+      <c r="AD32">
         <v>1.84</v>
-      </c>
-      <c r="AD32">
-        <v>1.83</v>
       </c>
       <c r="AE32">
         <v>1.33</v>
       </c>
       <c r="AF32">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="AG32">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AK32">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,7 +5688,7 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="O33">
         <v>3.55</v>
@@ -5706,7 +5706,7 @@
         <v>1.26</v>
       </c>
       <c r="T33">
-        <v>3.24</v>
+        <v>3.29</v>
       </c>
       <c r="U33">
         <v>2.45</v>
@@ -5721,16 +5721,16 @@
         <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z33">
-        <v>4.07</v>
+        <v>4.11</v>
       </c>
       <c r="AA33">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB33">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC33">
         <v>2.7</v>
@@ -5739,7 +5739,7 @@
         <v>1.36</v>
       </c>
       <c r="AE33">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF33">
         <v>1.59</v>
@@ -5866,13 +5866,13 @@
         <v>2.38</v>
       </c>
       <c r="S34">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T34">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U34">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="V34">
         <v>1.57</v>
@@ -5896,13 +5896,13 @@
         <v>2.33</v>
       </c>
       <c r="AC34">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="AD34">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AE34">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF34">
         <v>1.53</v>
@@ -6035,16 +6035,16 @@
         <v>3.42</v>
       </c>
       <c r="U35">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="V35">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W35">
         <v>1.17</v>
       </c>
       <c r="X35">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
         <v>1.11</v>
@@ -6053,7 +6053,7 @@
         <v>4.9</v>
       </c>
       <c r="AA35">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AB35">
         <v>2.48</v>
@@ -6065,7 +6065,7 @@
         <v>1.56</v>
       </c>
       <c r="AE35">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF35">
         <v>1.44</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AK35">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6231,10 +6231,10 @@
         <v>1.11</v>
       </c>
       <c r="AF36">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG36">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6349,55 +6349,55 @@
         <v>3.25</v>
       </c>
       <c r="Q37">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="R37">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="S37">
         <v>1.25</v>
       </c>
       <c r="T37">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="U37">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="V37">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="W37">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X37">
         <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z37">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AA37">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AB37">
-        <v>2.22</v>
+        <v>2.35</v>
       </c>
       <c r="AC37">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="AD37">
+        <v>1.48</v>
+      </c>
+      <c r="AE37">
+        <v>1.18</v>
+      </c>
+      <c r="AF37">
         <v>1.44</v>
       </c>
-      <c r="AE37">
-        <v>1.15</v>
-      </c>
-      <c r="AF37">
-        <v>1.53</v>
-      </c>
       <c r="AG37">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>1.22</v>
       </c>
       <c r="AK37">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6539,7 +6539,7 @@
         <v>1.24</v>
       </c>
       <c r="Z38">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="AA38">
         <v>1.82</v>
@@ -6576,7 +6576,7 @@
         <v>1.7</v>
       </c>
       <c r="AK38">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,25 +6666,25 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="O39">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="P39">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="Q39">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="R39">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="S39">
         <v>1.19</v>
       </c>
       <c r="T39">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="U39">
         <v>2.04</v>
@@ -6693,7 +6693,7 @@
         <v>1.67</v>
       </c>
       <c r="W39">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X39">
         <v>1.01</v>
@@ -6714,16 +6714,16 @@
         <v>2.12</v>
       </c>
       <c r="AD39">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AE39">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF39">
         <v>1.62</v>
       </c>
       <c r="AG39">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>1.06</v>
       </c>
       <c r="AK39">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6832,7 +6832,7 @@
         <v>2.47</v>
       </c>
       <c r="O40">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P40">
         <v>2.5</v>
@@ -6841,10 +6841,10 @@
         <v>2.88</v>
       </c>
       <c r="R40">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="S40">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T40">
         <v>3.4</v>
@@ -6856,19 +6856,19 @@
         <v>1.51</v>
       </c>
       <c r="W40">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X40">
         <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z40">
-        <v>4.59</v>
+        <v>4.64</v>
       </c>
       <c r="AA40">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB40">
         <v>2.21</v>
@@ -6880,13 +6880,13 @@
         <v>1.49</v>
       </c>
       <c r="AE40">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF40">
         <v>1.55</v>
       </c>
       <c r="AG40">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>1.29</v>
       </c>
       <c r="AK40">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6998,13 +6998,13 @@
         <v>3.6</v>
       </c>
       <c r="P41">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="Q41">
-        <v>3.66</v>
+        <v>3.44</v>
       </c>
       <c r="R41">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="S41">
         <v>1.25</v>
@@ -7028,22 +7028,22 @@
         <v>1.13</v>
       </c>
       <c r="Z41">
-        <v>4.66</v>
+        <v>4.7</v>
       </c>
       <c r="AA41">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AB41">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AC41">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="AD41">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AE41">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AF41">
         <v>1.55</v>
@@ -7155,7 +7155,7 @@
         </is>
       </c>
       <c r="N42">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="O42">
         <v>3.5</v>
@@ -7167,52 +7167,52 @@
         <v>3.45</v>
       </c>
       <c r="R42">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="S42">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T42">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U42">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="V42">
         <v>1.53</v>
       </c>
       <c r="W42">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X42">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
         <v>1.19</v>
       </c>
       <c r="Z42">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA42">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AB42">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AC42">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="AD42">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AE42">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF42">
         <v>1.53</v>
       </c>
       <c r="AG42">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7330,19 +7330,19 @@
         <v>2</v>
       </c>
       <c r="R43">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="S43">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T43">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U43">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="V43">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="W43">
         <v>1.18</v>
@@ -7351,10 +7351,10 @@
         <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z43">
-        <v>5.15</v>
+        <v>5.3</v>
       </c>
       <c r="AA43">
         <v>1.44</v>
@@ -7363,16 +7363,16 @@
         <v>2.7</v>
       </c>
       <c r="AC43">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="AD43">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AE43">
         <v>1.25</v>
       </c>
       <c r="AF43">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AG43">
         <v>2.5</v>
@@ -7391,7 +7391,7 @@
         <v>1.19</v>
       </c>
       <c r="AK43">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7490,7 +7490,7 @@
         <v>2.18</v>
       </c>
       <c r="Q44">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="R44">
         <v>2.34</v>
@@ -7502,10 +7502,10 @@
         <v>4</v>
       </c>
       <c r="U44">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="V44">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W44">
         <v>1.15</v>
@@ -7520,10 +7520,10 @@
         <v>5.3</v>
       </c>
       <c r="AA44">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AB44">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AC44">
         <v>2.1</v>
@@ -7532,7 +7532,7 @@
         <v>1.73</v>
       </c>
       <c r="AE44">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AF44">
         <v>1.38</v>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AK44">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7656,25 +7656,25 @@
         <v>2.88</v>
       </c>
       <c r="R45">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="S45">
+        <v>1.4</v>
+      </c>
+      <c r="T45">
+        <v>2.64</v>
+      </c>
+      <c r="U45">
+        <v>2.71</v>
+      </c>
+      <c r="V45">
         <v>1.39</v>
-      </c>
-      <c r="T45">
-        <v>2.66</v>
-      </c>
-      <c r="U45">
-        <v>2.67</v>
-      </c>
-      <c r="V45">
-        <v>1.4</v>
       </c>
       <c r="W45">
         <v>1.06</v>
       </c>
       <c r="X45">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
         <v>1.26</v>
@@ -7683,10 +7683,10 @@
         <v>3.2</v>
       </c>
       <c r="AA45">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AB45">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AC45">
         <v>3.4</v>
@@ -7698,7 +7698,7 @@
         <v>1.06</v>
       </c>
       <c r="AF45">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AG45">
         <v>1.95</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AK45">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7813,7 +7813,7 @@
         <v>3.1</v>
       </c>
       <c r="P46">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="Q46">
         <v>2.7</v>
@@ -7837,22 +7837,22 @@
         <v>1.04</v>
       </c>
       <c r="X46">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z46">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="AA46">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AB46">
         <v>1.9</v>
       </c>
       <c r="AC46">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="AD46">
         <v>1.35</v>
@@ -7864,7 +7864,7 @@
         <v>1.67</v>
       </c>
       <c r="AG46">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7970,19 +7970,19 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="O47">
         <v>3.75</v>
       </c>
       <c r="P47">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Q47">
         <v>2.5</v>
       </c>
       <c r="R47">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="S47">
         <v>1.24</v>
@@ -7997,37 +7997,37 @@
         <v>1.62</v>
       </c>
       <c r="W47">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X47">
         <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z47">
-        <v>4.75</v>
+        <v>4.85</v>
       </c>
       <c r="AA47">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AB47">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="AC47">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AD47">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AE47">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AF47">
         <v>1.44</v>
       </c>
       <c r="AG47">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
         <v>1.12</v>
       </c>
       <c r="Z48">
-        <v>5.36</v>
+        <v>5</v>
       </c>
       <c r="AA48">
         <v>1.51</v>
@@ -8302,7 +8302,7 @@
         <v>4.5</v>
       </c>
       <c r="P49">
-        <v>6.4</v>
+        <v>6.25</v>
       </c>
       <c r="Q49">
         <v>1.73</v>
@@ -8341,19 +8341,19 @@
         <v>2.3</v>
       </c>
       <c r="AC49">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AD49">
         <v>1.53</v>
       </c>
       <c r="AE49">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AF49">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG49">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8459,16 +8459,16 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="O50">
         <v>3</v>
       </c>
       <c r="P50">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q50">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="R50">
         <v>1.83</v>
@@ -8510,13 +8510,13 @@
         <v>1.25</v>
       </c>
       <c r="AE50">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF50">
         <v>1.8</v>
       </c>
       <c r="AG50">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8625,13 +8625,13 @@
         <v>1.81</v>
       </c>
       <c r="O51">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="P51">
         <v>3.25</v>
       </c>
       <c r="Q51">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="R51">
         <v>2.4</v>
@@ -8649,7 +8649,7 @@
         <v>1.6</v>
       </c>
       <c r="W51">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X51">
         <v>1.02</v>
@@ -8679,7 +8679,7 @@
         <v>1.48</v>
       </c>
       <c r="AG51">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK51">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8788,10 +8788,10 @@
         <v>4</v>
       </c>
       <c r="O52">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P52">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Q52">
         <v>5.19</v>
@@ -8803,7 +8803,7 @@
         <v>1.41</v>
       </c>
       <c r="T52">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="U52">
         <v>2.79</v>
@@ -8821,7 +8821,7 @@
         <v>1.33</v>
       </c>
       <c r="Z52">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="AA52">
         <v>2.03</v>
@@ -8830,13 +8830,13 @@
         <v>1.72</v>
       </c>
       <c r="AC52">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="AD52">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE52">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF52">
         <v>1.88</v>
@@ -8858,7 +8858,7 @@
         <v>1.2</v>
       </c>
       <c r="AK52">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,19 +8948,19 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O53">
         <v>2.95</v>
       </c>
       <c r="P53">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q53">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="R53">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="S53">
         <v>1.44</v>
@@ -8969,25 +8969,25 @@
         <v>2.38</v>
       </c>
       <c r="U53">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="V53">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W53">
         <v>1.05</v>
       </c>
       <c r="X53">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y53">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Z53">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="AA53">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AB53">
         <v>1.48</v>
@@ -8999,7 +8999,7 @@
         <v>1.14</v>
       </c>
       <c r="AE53">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF53">
         <v>2</v>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AK53">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9449,13 +9449,13 @@
         <v>2.66</v>
       </c>
       <c r="R56">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="S56">
         <v>1.28</v>
       </c>
       <c r="T56">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="U56">
         <v>2.27</v>
@@ -9476,7 +9476,7 @@
         <v>3.94</v>
       </c>
       <c r="AA56">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AB56">
         <v>2.08</v>
@@ -9488,13 +9488,13 @@
         <v>1.41</v>
       </c>
       <c r="AE56">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF56">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG56">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK56">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9600,58 +9600,58 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="O57">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="P57">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="Q57">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="R57">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="S57">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="T57">
-        <v>2.61</v>
+        <v>2.84</v>
       </c>
       <c r="U57">
-        <v>2.73</v>
+        <v>2.64</v>
       </c>
       <c r="V57">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W57">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X57">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y57">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z57">
-        <v>3.04</v>
+        <v>3.28</v>
       </c>
       <c r="AA57">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AB57">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="AC57">
-        <v>3.42</v>
+        <v>3.08</v>
       </c>
       <c r="AD57">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AE57">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF57">
         <v>2.05</v>
@@ -9673,7 +9673,7 @@
         <v>1.2</v>
       </c>
       <c r="AK57">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="O58">
-        <v>5.25</v>
+        <v>5.45</v>
       </c>
       <c r="P58">
-        <v>7.38</v>
+        <v>7.75</v>
       </c>
       <c r="Q58">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="R58">
-        <v>2.53</v>
+        <v>2.67</v>
       </c>
       <c r="S58">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T58">
-        <v>4.33</v>
+        <v>4.45</v>
       </c>
       <c r="U58">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="V58">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="W58">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X58">
         <v>1.01</v>
       </c>
       <c r="Y58">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z58">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AA58">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AB58">
-        <v>3.02</v>
+        <v>3.12</v>
       </c>
       <c r="AC58">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AD58">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AE58">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AF58">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AG58">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>1.15</v>
       </c>
       <c r="AK58">
-        <v>3.05</v>
+        <v>3.22</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9932,13 +9932,13 @@
         <v>6.8</v>
       </c>
       <c r="P59">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q59">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="R59">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="S59">
         <v>1.22</v>
@@ -9980,7 +9980,7 @@
         <v>1.25</v>
       </c>
       <c r="AF59">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AG59">
         <v>1.67</v>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AK59">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10089,19 +10089,19 @@
         </is>
       </c>
       <c r="N60">
+        <v>3.6</v>
+      </c>
+      <c r="O60">
+        <v>3.8</v>
+      </c>
+      <c r="P60">
+        <v>1.8</v>
+      </c>
+      <c r="Q60">
         <v>3.9</v>
       </c>
-      <c r="O60">
-        <v>3.85</v>
-      </c>
-      <c r="P60">
-        <v>1.77</v>
-      </c>
-      <c r="Q60">
-        <v>4.1</v>
-      </c>
       <c r="R60">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="S60">
         <v>1.25</v>
@@ -10110,10 +10110,10 @@
         <v>3.4</v>
       </c>
       <c r="U60">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="V60">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W60">
         <v>1.1</v>
@@ -10122,31 +10122,31 @@
         <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z60">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="AA60">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AB60">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="AC60">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AD60">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AE60">
         <v>1.2</v>
       </c>
       <c r="AF60">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AG60">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK60">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10273,10 +10273,10 @@
         <v>4.2</v>
       </c>
       <c r="U61">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V61">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="W61">
         <v>1.18</v>
@@ -10285,25 +10285,25 @@
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z61">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="AA61">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AB61">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="AC61">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AD61">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AE61">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AF61">
         <v>1.35</v>
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK61">
         <v>1.44</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.84</v>
+        <v>1.65</v>
       </c>
       <c r="O62">
+        <v>3.7</v>
+      </c>
+      <c r="P62">
         <v>4</v>
       </c>
-      <c r="P62">
-        <v>3.35</v>
-      </c>
       <c r="Q62">
-        <v>2.31</v>
+        <v>2.18</v>
       </c>
       <c r="R62">
-        <v>2.62</v>
+        <v>2.32</v>
       </c>
       <c r="S62">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="T62">
-        <v>4</v>
+        <v>3.24</v>
       </c>
       <c r="U62">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="V62">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="W62">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="Z62">
-        <v>6.46</v>
+        <v>4.8</v>
       </c>
       <c r="AA62">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AB62">
-        <v>2.83</v>
+        <v>2.35</v>
       </c>
       <c r="AC62">
-        <v>1.89</v>
+        <v>2.47</v>
       </c>
       <c r="AD62">
-        <v>1.78</v>
+        <v>1.48</v>
       </c>
       <c r="AE62">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AF62">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="AG62">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>1.17</v>
       </c>
       <c r="AK62">
-        <v>1.8</v>
+        <v>1.99</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
       <c r="O63">
         <v>4</v>
       </c>
       <c r="P63">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q63">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="R63">
-        <v>2.32</v>
+        <v>2.62</v>
       </c>
       <c r="S63">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="T63">
-        <v>3.24</v>
+        <v>4</v>
       </c>
       <c r="U63">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="V63">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="W63">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X63">
         <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="Z63">
-        <v>4.35</v>
+        <v>6.57</v>
       </c>
       <c r="AA63">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AB63">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="AC63">
-        <v>2.46</v>
+        <v>1.89</v>
       </c>
       <c r="AD63">
-        <v>1.48</v>
+        <v>1.78</v>
       </c>
       <c r="AE63">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AF63">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="AG63">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
         <v>1.17</v>
       </c>
       <c r="AK63">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,34 +10741,34 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="O64">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P64">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="Q64">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R64">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S64">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T64">
         <v>2.8</v>
       </c>
       <c r="U64">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="V64">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W64">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X64">
         <v>1.02</v>
@@ -10777,10 +10777,10 @@
         <v>1.33</v>
       </c>
       <c r="Z64">
-        <v>2.5</v>
+        <v>3.09</v>
       </c>
       <c r="AA64">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="AB64">
         <v>1.75</v>
@@ -10795,7 +10795,7 @@
         <v>1.06</v>
       </c>
       <c r="AF64">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG64">
         <v>1.91</v>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK64">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10910,19 +10910,19 @@
         <v>4.2</v>
       </c>
       <c r="P65">
-        <v>9</v>
+        <v>8.44</v>
       </c>
       <c r="Q65">
         <v>1.94</v>
       </c>
       <c r="R65">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="S65">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T65">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="U65">
         <v>3</v>
@@ -10958,7 +10958,7 @@
         <v>1.03</v>
       </c>
       <c r="AF65">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="AG65">
         <v>1.4</v>
@@ -10974,7 +10974,7 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AK65">
         <v>2.9</v>
@@ -11076,19 +11076,19 @@
         <v>2.78</v>
       </c>
       <c r="Q66">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="R66">
         <v>2.1</v>
       </c>
       <c r="S66">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T66">
         <v>2.92</v>
       </c>
       <c r="U66">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="V66">
         <v>1.4</v>
@@ -11097,13 +11097,13 @@
         <v>1.05</v>
       </c>
       <c r="X66">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y66">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z66">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="AA66">
         <v>1.83</v>
@@ -11137,7 +11137,7 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AK66">
         <v>1.69</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,52 +11230,52 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.75</v>
+        <v>2.35</v>
       </c>
       <c r="O67">
         <v>3.4</v>
       </c>
       <c r="P67">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="Q67">
-        <v>2.43</v>
+        <v>2.9</v>
       </c>
       <c r="R67">
         <v>2.2</v>
       </c>
       <c r="S67">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T67">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="U67">
-        <v>2.74</v>
+        <v>2.45</v>
       </c>
       <c r="V67">
         <v>1.44</v>
       </c>
       <c r="W67">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X67">
         <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z67">
-        <v>3.86</v>
+        <v>3.76</v>
       </c>
       <c r="AA67">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AB67">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC67">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="AD67">
         <v>1.36</v>
@@ -11284,10 +11284,10 @@
         <v>1.13</v>
       </c>
       <c r="AF67">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AG67">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AK67">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="O68">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="P68">
-        <v>2.52</v>
+        <v>3</v>
       </c>
       <c r="Q68">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="R68">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="S68">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="T68">
-        <v>3.18</v>
+        <v>2.57</v>
       </c>
       <c r="U68">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="V68">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="W68">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X68">
+        <v>1.04</v>
+      </c>
+      <c r="Y68">
+        <v>1.37</v>
+      </c>
+      <c r="Z68">
+        <v>2.84</v>
+      </c>
+      <c r="AA68">
+        <v>2.23</v>
+      </c>
+      <c r="AB68">
+        <v>1.61</v>
+      </c>
+      <c r="AC68">
+        <v>4.55</v>
+      </c>
+      <c r="AD68">
+        <v>1.18</v>
+      </c>
+      <c r="AE68">
         <v>1.03</v>
       </c>
-      <c r="Y68">
-        <v>1.25</v>
-      </c>
-      <c r="Z68">
-        <v>3.9</v>
-      </c>
-      <c r="AA68">
-        <v>1.74</v>
-      </c>
-      <c r="AB68">
-        <v>1.98</v>
-      </c>
-      <c r="AC68">
-        <v>2.66</v>
-      </c>
-      <c r="AD68">
-        <v>1.33</v>
-      </c>
-      <c r="AE68">
-        <v>1.14</v>
-      </c>
       <c r="AF68">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AG68">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK68">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="O69">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="P69">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="Q69">
-        <v>2.81</v>
+        <v>2.95</v>
       </c>
       <c r="R69">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="S69">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="T69">
-        <v>3.08</v>
+        <v>2.51</v>
       </c>
       <c r="U69">
-        <v>2.42</v>
+        <v>2.86</v>
       </c>
       <c r="V69">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="W69">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X69">
         <v>1.02</v>
       </c>
       <c r="Y69">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="Z69">
-        <v>3.84</v>
+        <v>3.04</v>
       </c>
       <c r="AA69">
-        <v>1.77</v>
+        <v>2.18</v>
       </c>
       <c r="AB69">
-        <v>1.99</v>
+        <v>1.67</v>
       </c>
       <c r="AC69">
-        <v>3.03</v>
+        <v>3.42</v>
       </c>
       <c r="AD69">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="AE69">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AF69">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AG69">
-        <v>2.18</v>
+        <v>1.93</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AK69">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="O70">
-        <v>3.05</v>
+        <v>3.36</v>
       </c>
       <c r="P70">
-        <v>3.25</v>
+        <v>2.52</v>
       </c>
       <c r="Q70">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="R70">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="S70">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="T70">
+        <v>3.21</v>
+      </c>
+      <c r="U70">
         <v>2.5</v>
       </c>
-      <c r="U70">
-        <v>2.86</v>
-      </c>
       <c r="V70">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="W70">
         <v>1.07</v>
       </c>
       <c r="X70">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y70">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z70">
+        <v>3.94</v>
+      </c>
+      <c r="AA70">
+        <v>1.74</v>
+      </c>
+      <c r="AB70">
+        <v>1.98</v>
+      </c>
+      <c r="AC70">
         <v>3.04</v>
       </c>
-      <c r="AA70">
-        <v>2.17</v>
-      </c>
-      <c r="AB70">
-        <v>1.67</v>
-      </c>
-      <c r="AC70">
-        <v>3.42</v>
-      </c>
       <c r="AD70">
-        <v>1.23</v>
+        <v>1.39</v>
       </c>
       <c r="AE70">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AF70">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AG70">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK70">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
+        <v>1.75</v>
+      </c>
+      <c r="O71">
+        <v>3.4</v>
+      </c>
+      <c r="P71">
+        <v>3.82</v>
+      </c>
+      <c r="Q71">
+        <v>2.4</v>
+      </c>
+      <c r="R71">
         <v>2.2</v>
       </c>
-      <c r="O71">
-        <v>3.15</v>
-      </c>
-      <c r="P71">
-        <v>2.9</v>
-      </c>
-      <c r="Q71">
-        <v>2.75</v>
-      </c>
-      <c r="R71">
-        <v>2.03</v>
-      </c>
       <c r="S71">
+        <v>1.33</v>
+      </c>
+      <c r="T71">
+        <v>3.1</v>
+      </c>
+      <c r="U71">
+        <v>2.74</v>
+      </c>
+      <c r="V71">
         <v>1.44</v>
       </c>
-      <c r="T71">
-        <v>2.71</v>
-      </c>
-      <c r="U71">
-        <v>2.87</v>
-      </c>
-      <c r="V71">
-        <v>1.35</v>
-      </c>
       <c r="W71">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X71">
         <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="Z71">
-        <v>3.05</v>
+        <v>3.92</v>
       </c>
       <c r="AA71">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="AB71">
-        <v>1.67</v>
+        <v>2.01</v>
       </c>
       <c r="AC71">
-        <v>4.03</v>
+        <v>3.13</v>
       </c>
       <c r="AD71">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AE71">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AF71">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="AG71">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK71">
-        <v>1.58</v>
+        <v>1.93</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12087,7 +12087,7 @@
         <v>1.78</v>
       </c>
       <c r="AB72">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AC72">
         <v>2.7</v>
@@ -12253,7 +12253,7 @@
         <v>2.45</v>
       </c>
       <c r="AC73">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="AD73">
         <v>1.53</v>
@@ -12380,55 +12380,55 @@
         <v>0</v>
       </c>
       <c r="Q74">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="R74">
-        <v>4.8</v>
+        <v>4.65</v>
       </c>
       <c r="S74">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="T74">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="U74">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="V74">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="W74">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X74">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y74">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Z74">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA74">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AB74">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="AC74">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="AD74">
-        <v>2.59</v>
+        <v>2.42</v>
       </c>
       <c r="AE74">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AF74">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="AG74">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,7 +12441,7 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.04</v>
+        <v>7.1</v>
       </c>
       <c r="AK74">
         <v>0</v>
@@ -12546,7 +12546,7 @@
         <v>2.56</v>
       </c>
       <c r="R75">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="S75">
         <v>1.29</v>
@@ -12567,19 +12567,19 @@
         <v>1.02</v>
       </c>
       <c r="Y75">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z75">
-        <v>4.4</v>
+        <v>4.47</v>
       </c>
       <c r="AA75">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB75">
         <v>2.12</v>
       </c>
       <c r="AC75">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="AD75">
         <v>1.48</v>
@@ -12706,19 +12706,19 @@
         <v>0</v>
       </c>
       <c r="Q76">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R76">
         <v>2.22</v>
       </c>
       <c r="S76">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T76">
         <v>3.25</v>
       </c>
       <c r="U76">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="V76">
         <v>1.5</v>
@@ -12727,13 +12727,13 @@
         <v>1.12</v>
       </c>
       <c r="X76">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y76">
         <v>1.16</v>
       </c>
       <c r="Z76">
-        <v>4.5</v>
+        <v>4.05</v>
       </c>
       <c r="AA76">
         <v>1.61</v>
@@ -12872,16 +12872,16 @@
         <v>2.3</v>
       </c>
       <c r="R77">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S77">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T77">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="U77">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="V77">
         <v>1.3</v>
@@ -12890,34 +12890,34 @@
         <v>1.05</v>
       </c>
       <c r="X77">
+        <v>1.02</v>
+      </c>
+      <c r="Y77">
+        <v>1.33</v>
+      </c>
+      <c r="Z77">
+        <v>2.96</v>
+      </c>
+      <c r="AA77">
+        <v>2.07</v>
+      </c>
+      <c r="AB77">
+        <v>1.66</v>
+      </c>
+      <c r="AC77">
+        <v>4.1</v>
+      </c>
+      <c r="AD77">
+        <v>1.23</v>
+      </c>
+      <c r="AE77">
         <v>1.03</v>
-      </c>
-      <c r="Y77">
-        <v>1.35</v>
-      </c>
-      <c r="Z77">
-        <v>2.9</v>
-      </c>
-      <c r="AA77">
-        <v>2.12</v>
-      </c>
-      <c r="AB77">
-        <v>1.63</v>
-      </c>
-      <c r="AC77">
-        <v>4.16</v>
-      </c>
-      <c r="AD77">
-        <v>1.22</v>
-      </c>
-      <c r="AE77">
-        <v>1.02</v>
       </c>
       <c r="AF77">
         <v>2.05</v>
       </c>
       <c r="AG77">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK77">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13026,52 +13026,52 @@
         <v>1.65</v>
       </c>
       <c r="O78">
-        <v>4.35</v>
+        <v>4.5</v>
       </c>
       <c r="P78">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="Q78">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="R78">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="S78">
         <v>1.22</v>
       </c>
       <c r="T78">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="U78">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="V78">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="W78">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X78">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y78">
         <v>1.09</v>
       </c>
       <c r="Z78">
-        <v>5.3</v>
+        <v>5.35</v>
       </c>
       <c r="AA78">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB78">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AC78">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="AD78">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AE78">
         <v>1.29</v>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK78">
-        <v>2.21</v>
+        <v>2.31</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13198,7 +13198,7 @@
         <v>2.04</v>
       </c>
       <c r="R79">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="S79">
         <v>1.18</v>
@@ -13219,10 +13219,10 @@
         <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z79">
-        <v>6.53</v>
+        <v>6.63</v>
       </c>
       <c r="AA79">
         <v>1.33</v>
@@ -13231,13 +13231,13 @@
         <v>3.1</v>
       </c>
       <c r="AC79">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AD79">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AE79">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AF79">
         <v>1.38</v>
@@ -13259,7 +13259,7 @@
         <v>1.22</v>
       </c>
       <c r="AK79">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="O80">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="P80">
-        <v>2.47</v>
+        <v>2.1</v>
       </c>
       <c r="Q80">
-        <v>2.72</v>
+        <v>2.9</v>
       </c>
       <c r="R80">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="S80">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="T80">
-        <v>3.32</v>
+        <v>4.4</v>
       </c>
       <c r="U80">
-        <v>2.27</v>
+        <v>1.91</v>
       </c>
       <c r="V80">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="W80">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="X80">
         <v>1.01</v>
       </c>
       <c r="Y80">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="Z80">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="AA80">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AB80">
-        <v>2.33</v>
+        <v>2.97</v>
       </c>
       <c r="AC80">
-        <v>2.28</v>
+        <v>1.85</v>
       </c>
       <c r="AD80">
-        <v>1.5</v>
+        <v>1.88</v>
       </c>
       <c r="AE80">
-        <v>1.17</v>
+        <v>1.41</v>
       </c>
       <c r="AF80">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="AG80">
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK80">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,80 +13512,80 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="O81">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P81">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="Q81">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="R81">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="S81">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="T81">
-        <v>4.4</v>
+        <v>3.55</v>
       </c>
       <c r="U81">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="V81">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="W81">
+        <v>1.15</v>
+      </c>
+      <c r="X81">
+        <v>1.02</v>
+      </c>
+      <c r="Y81">
+        <v>1.09</v>
+      </c>
+      <c r="Z81">
+        <v>5.25</v>
+      </c>
+      <c r="AA81">
+        <v>1.4</v>
+      </c>
+      <c r="AB81">
+        <v>2.56</v>
+      </c>
+      <c r="AC81">
+        <v>2.03</v>
+      </c>
+      <c r="AD81">
+        <v>1.69</v>
+      </c>
+      <c r="AE81">
+        <v>1.25</v>
+      </c>
+      <c r="AF81">
+        <v>1.44</v>
+      </c>
+      <c r="AG81">
+        <v>2.69</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ81">
         <v>1.22</v>
       </c>
-      <c r="X81">
-        <v>1.01</v>
-      </c>
-      <c r="Y81">
-        <v>1.05</v>
-      </c>
-      <c r="Z81">
-        <v>6.45</v>
-      </c>
-      <c r="AA81">
-        <v>1.36</v>
-      </c>
-      <c r="AB81">
-        <v>2.97</v>
-      </c>
-      <c r="AC81">
-        <v>1.85</v>
-      </c>
-      <c r="AD81">
-        <v>1.88</v>
-      </c>
-      <c r="AE81">
-        <v>1.4</v>
-      </c>
-      <c r="AF81">
-        <v>1.31</v>
-      </c>
-      <c r="AG81">
-        <v>3.1</v>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI81" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ81">
-        <v>1.25</v>
-      </c>
       <c r="AK81">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,80 +13675,80 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.9</v>
+        <v>2.21</v>
       </c>
       <c r="O82">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P82">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="Q82">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="R82">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="S82">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T82">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="U82">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="V82">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="W82">
+        <v>1.13</v>
+      </c>
+      <c r="X82">
+        <v>1.02</v>
+      </c>
+      <c r="Y82">
+        <v>1.08</v>
+      </c>
+      <c r="Z82">
+        <v>5.55</v>
+      </c>
+      <c r="AA82">
+        <v>1.44</v>
+      </c>
+      <c r="AB82">
+        <v>2.7</v>
+      </c>
+      <c r="AC82">
+        <v>2.09</v>
+      </c>
+      <c r="AD82">
+        <v>1.68</v>
+      </c>
+      <c r="AE82">
+        <v>1.29</v>
+      </c>
+      <c r="AF82">
+        <v>1.4</v>
+      </c>
+      <c r="AG82">
+        <v>2.88</v>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ82">
         <v>1.25</v>
       </c>
-      <c r="X82">
-        <v>1.01</v>
-      </c>
-      <c r="Y82">
-        <v>1.05</v>
-      </c>
-      <c r="Z82">
-        <v>8</v>
-      </c>
-      <c r="AA82">
-        <v>1.3</v>
-      </c>
-      <c r="AB82">
-        <v>3.5</v>
-      </c>
-      <c r="AC82">
-        <v>1.79</v>
-      </c>
-      <c r="AD82">
-        <v>1.98</v>
-      </c>
-      <c r="AE82">
-        <v>1.4</v>
-      </c>
-      <c r="AF82">
-        <v>1.33</v>
-      </c>
-      <c r="AG82">
-        <v>3.4</v>
-      </c>
-      <c r="AH82" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI82" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ82">
-        <v>1.22</v>
-      </c>
       <c r="AK82">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="O83">
+        <v>3.72</v>
+      </c>
+      <c r="P83">
+        <v>2.55</v>
+      </c>
+      <c r="Q83">
+        <v>2.76</v>
+      </c>
+      <c r="R83">
+        <v>2.38</v>
+      </c>
+      <c r="S83">
+        <v>1.28</v>
+      </c>
+      <c r="T83">
         <v>3.6</v>
       </c>
-      <c r="P83">
-        <v>2.5</v>
-      </c>
-      <c r="Q83">
-        <v>2.85</v>
-      </c>
-      <c r="R83">
-        <v>2.3</v>
-      </c>
-      <c r="S83">
-        <v>1.22</v>
-      </c>
-      <c r="T83">
-        <v>4</v>
-      </c>
       <c r="U83">
-        <v>2.05</v>
+        <v>2.32</v>
       </c>
       <c r="V83">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="W83">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X83">
         <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z83">
-        <v>5.55</v>
+        <v>4.6</v>
       </c>
       <c r="AA83">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AB83">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="AC83">
-        <v>2.09</v>
+        <v>2.38</v>
       </c>
       <c r="AD83">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="AE83">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AF83">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AG83">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK83">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,80 +14001,80 @@
         </is>
       </c>
       <c r="N84">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="O84">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P84">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="Q84">
-        <v>3.06</v>
+        <v>3.3</v>
       </c>
       <c r="R84">
-        <v>2.31</v>
+        <v>2.62</v>
       </c>
       <c r="S84">
+        <v>1.17</v>
+      </c>
+      <c r="T84">
+        <v>4.1</v>
+      </c>
+      <c r="U84">
+        <v>1.98</v>
+      </c>
+      <c r="V84">
+        <v>1.93</v>
+      </c>
+      <c r="W84">
+        <v>1.25</v>
+      </c>
+      <c r="X84">
+        <v>1.01</v>
+      </c>
+      <c r="Y84">
+        <v>1.05</v>
+      </c>
+      <c r="Z84">
+        <v>8</v>
+      </c>
+      <c r="AA84">
+        <v>1.3</v>
+      </c>
+      <c r="AB84">
+        <v>3.5</v>
+      </c>
+      <c r="AC84">
+        <v>1.79</v>
+      </c>
+      <c r="AD84">
+        <v>1.99</v>
+      </c>
+      <c r="AE84">
+        <v>1.4</v>
+      </c>
+      <c r="AF84">
+        <v>1.33</v>
+      </c>
+      <c r="AG84">
+        <v>3.4</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ84">
         <v>1.2</v>
       </c>
-      <c r="T84">
-        <v>3.8</v>
-      </c>
-      <c r="U84">
-        <v>2.1</v>
-      </c>
-      <c r="V84">
-        <v>1.68</v>
-      </c>
-      <c r="W84">
-        <v>1.16</v>
-      </c>
-      <c r="X84">
-        <v>1.02</v>
-      </c>
-      <c r="Y84">
-        <v>1.09</v>
-      </c>
-      <c r="Z84">
-        <v>5.3</v>
-      </c>
-      <c r="AA84">
-        <v>1.41</v>
-      </c>
-      <c r="AB84">
-        <v>2.6</v>
-      </c>
-      <c r="AC84">
-        <v>2.08</v>
-      </c>
-      <c r="AD84">
-        <v>1.67</v>
-      </c>
-      <c r="AE84">
-        <v>1.24</v>
-      </c>
-      <c r="AF84">
-        <v>1.4</v>
-      </c>
-      <c r="AG84">
-        <v>2.7</v>
-      </c>
-      <c r="AH84" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI84" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ84">
-        <v>1.75</v>
-      </c>
       <c r="AK84">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,80 +14164,80 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.65</v>
+        <v>3.1</v>
       </c>
       <c r="O85">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P85">
-        <v>4.33</v>
+        <v>2.03</v>
       </c>
       <c r="Q85">
-        <v>2.03</v>
+        <v>3.18</v>
       </c>
       <c r="R85">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S85">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T85">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="U85">
         <v>2.1</v>
       </c>
       <c r="V85">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="W85">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X85">
         <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Z85">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AA85">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AB85">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="AC85">
-        <v>2.21</v>
+        <v>2.04</v>
       </c>
       <c r="AD85">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AE85">
+        <v>1.25</v>
+      </c>
+      <c r="AF85">
+        <v>1.4</v>
+      </c>
+      <c r="AG85">
+        <v>2.75</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ85">
+        <v>1.77</v>
+      </c>
+      <c r="AK85">
         <v>1.26</v>
-      </c>
-      <c r="AF85">
-        <v>1.49</v>
-      </c>
-      <c r="AG85">
-        <v>2.4</v>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI85" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ85">
-        <v>1.2</v>
-      </c>
-      <c r="AK85">
-        <v>2.25</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,16 +14327,16 @@
         </is>
       </c>
       <c r="N86">
-        <v>3.1</v>
+        <v>1.65</v>
       </c>
       <c r="O86">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="P86">
-        <v>1.91</v>
+        <v>4.33</v>
       </c>
       <c r="Q86">
-        <v>3.5</v>
+        <v>2.03</v>
       </c>
       <c r="R86">
         <v>2.5</v>
@@ -14351,40 +14351,40 @@
         <v>2.1</v>
       </c>
       <c r="V86">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W86">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X86">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z86">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="AA86">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AB86">
-        <v>2.75</v>
+        <v>2.49</v>
       </c>
       <c r="AC86">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="AD86">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AE86">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF86">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AG86">
-        <v>2.69</v>
+        <v>2.4</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK86">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14523,25 +14523,25 @@
         <v>1.02</v>
       </c>
       <c r="Y87">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z87">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="AA87">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AB87">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="AC87">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AD87">
         <v>1.6</v>
       </c>
       <c r="AE87">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AF87">
         <v>1.4</v>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK87">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14653,7 +14653,7 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O88">
         <v>3.25</v>
@@ -14662,7 +14662,7 @@
         <v>3</v>
       </c>
       <c r="Q88">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R88">
         <v>2.1</v>
@@ -14677,10 +14677,10 @@
         <v>2.75</v>
       </c>
       <c r="V88">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W88">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X88">
         <v>1.02</v>
@@ -14689,22 +14689,22 @@
         <v>1.26</v>
       </c>
       <c r="Z88">
-        <v>3.49</v>
+        <v>3.2</v>
       </c>
       <c r="AA88">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AB88">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AC88">
         <v>3.05</v>
       </c>
       <c r="AD88">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE88">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF88">
         <v>1.7</v>
@@ -14726,7 +14726,7 @@
         <v>1.31</v>
       </c>
       <c r="AK88">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14825,7 +14825,7 @@
         <v>2.05</v>
       </c>
       <c r="Q89">
-        <v>4.12</v>
+        <v>4.06</v>
       </c>
       <c r="R89">
         <v>2</v>
@@ -14852,13 +14852,13 @@
         <v>1.33</v>
       </c>
       <c r="Z89">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="AA89">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="AB89">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC89">
         <v>3.5</v>
@@ -14886,7 +14886,7 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK89">
         <v>1.25</v>
@@ -14979,31 +14979,31 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="O90">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="P90">
-        <v>4.6</v>
+        <v>5.21</v>
       </c>
       <c r="Q90">
         <v>1.91</v>
       </c>
       <c r="R90">
-        <v>2.69</v>
+        <v>2.74</v>
       </c>
       <c r="S90">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T90">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U90">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="V90">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="W90">
         <v>1.17</v>
@@ -15012,28 +15012,28 @@
         <v>1.02</v>
       </c>
       <c r="Y90">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z90">
-        <v>5.76</v>
+        <v>5.92</v>
       </c>
       <c r="AA90">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB90">
-        <v>2.49</v>
+        <v>2.62</v>
       </c>
       <c r="AC90">
-        <v>2.14</v>
+        <v>2.03</v>
       </c>
       <c r="AD90">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AE90">
         <v>1.26</v>
       </c>
       <c r="AF90">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AG90">
         <v>2.38</v>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK90">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15305,7 +15305,7 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="O92">
         <v>3.8</v>
@@ -15314,7 +15314,7 @@
         <v>4</v>
       </c>
       <c r="Q92">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="R92">
         <v>2.35</v>
@@ -15323,16 +15323,16 @@
         <v>1.25</v>
       </c>
       <c r="T92">
-        <v>3.6</v>
+        <v>3.46</v>
       </c>
       <c r="U92">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="V92">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W92">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X92">
         <v>1.02</v>
@@ -15341,7 +15341,7 @@
         <v>1.15</v>
       </c>
       <c r="Z92">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="AA92">
         <v>1.57</v>
@@ -15468,19 +15468,19 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="O93">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="P93">
         <v>19</v>
       </c>
       <c r="Q93">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="R93">
-        <v>4.08</v>
+        <v>4.24</v>
       </c>
       <c r="S93">
         <v>1.09</v>
@@ -15489,13 +15489,13 @@
         <v>6.7</v>
       </c>
       <c r="U93">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="V93">
-        <v>2.67</v>
+        <v>2.78</v>
       </c>
       <c r="W93">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="X93">
         <v>1</v>
@@ -15504,28 +15504,28 @@
         <v>1.03</v>
       </c>
       <c r="Z93">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA93">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AB93">
-        <v>5.9</v>
+        <v>6.25</v>
       </c>
       <c r="AC93">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AD93">
-        <v>3.14</v>
+        <v>3.26</v>
       </c>
       <c r="AE93">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AF93">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AG93">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>1.01</v>
       </c>
       <c r="AK93">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15640,7 +15640,7 @@
         <v>2.3</v>
       </c>
       <c r="Q94">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
       <c r="R94">
         <v>2.18</v>
@@ -15652,31 +15652,31 @@
         <v>3.18</v>
       </c>
       <c r="U94">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="V94">
         <v>1.5</v>
       </c>
       <c r="W94">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X94">
         <v>1</v>
       </c>
       <c r="Y94">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z94">
-        <v>3.98</v>
+        <v>3.96</v>
       </c>
       <c r="AA94">
         <v>1.64</v>
       </c>
       <c r="AB94">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AC94">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="AD94">
         <v>1.42</v>
@@ -15688,7 +15688,7 @@
         <v>1.53</v>
       </c>
       <c r="AG94">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,7 +15701,7 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="AK94">
         <v>1.36</v>
@@ -15794,16 +15794,16 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="O95">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="P95">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="Q95">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="R95">
         <v>2.45</v>
@@ -15812,46 +15812,46 @@
         <v>1.28</v>
       </c>
       <c r="T95">
-        <v>3.8</v>
+        <v>3.42</v>
       </c>
       <c r="U95">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="V95">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W95">
         <v>1.13</v>
       </c>
       <c r="X95">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y95">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z95">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AA95">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AB95">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AC95">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="AD95">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AE95">
         <v>1.22</v>
       </c>
       <c r="AF95">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AG95">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AK95">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>3.8</v>
+        <v>2.15</v>
       </c>
       <c r="O98">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="P98">
-        <v>1.78</v>
+        <v>3.05</v>
       </c>
       <c r="Q98">
-        <v>4.4</v>
+        <v>2.64</v>
       </c>
       <c r="R98">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="S98">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T98">
-        <v>3.2</v>
+        <v>2.76</v>
       </c>
       <c r="U98">
-        <v>2.54</v>
+        <v>2.63</v>
       </c>
       <c r="V98">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W98">
         <v>1.05</v>
       </c>
       <c r="X98">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y98">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z98">
-        <v>3.79</v>
+        <v>3.58</v>
       </c>
       <c r="AA98">
         <v>1.75</v>
       </c>
       <c r="AB98">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC98">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AD98">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE98">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF98">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG98">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AK98">
-        <v>1.16</v>
+        <v>1.6</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.24</v>
+        <v>3.8</v>
       </c>
       <c r="O99">
+        <v>3.7</v>
+      </c>
+      <c r="P99">
+        <v>1.78</v>
+      </c>
+      <c r="Q99">
+        <v>4.4</v>
+      </c>
+      <c r="R99">
+        <v>2.34</v>
+      </c>
+      <c r="S99">
+        <v>1.34</v>
+      </c>
+      <c r="T99">
         <v>3.2</v>
       </c>
-      <c r="P99">
-        <v>3.1</v>
-      </c>
-      <c r="Q99">
-        <v>2.81</v>
-      </c>
-      <c r="R99">
-        <v>2.03</v>
-      </c>
-      <c r="S99">
-        <v>1.36</v>
-      </c>
-      <c r="T99">
-        <v>2.77</v>
-      </c>
       <c r="U99">
-        <v>2.61</v>
+        <v>2.54</v>
       </c>
       <c r="V99">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W99">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X99">
         <v>1.01</v>
       </c>
       <c r="Y99">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z99">
-        <v>3.49</v>
+        <v>3.82</v>
       </c>
       <c r="AA99">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AB99">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AC99">
-        <v>3.37</v>
+        <v>2.83</v>
       </c>
       <c r="AD99">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE99">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF99">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AG99">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK99">
-        <v>1.62</v>
+        <v>1.16</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>2.15</v>
+        <v>1.43</v>
       </c>
       <c r="O100">
-        <v>3.25</v>
+        <v>4.7</v>
       </c>
       <c r="P100">
-        <v>3.05</v>
+        <v>5.5</v>
       </c>
       <c r="Q100">
-        <v>2.64</v>
+        <v>1.88</v>
       </c>
       <c r="R100">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="S100">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="T100">
-        <v>2.76</v>
+        <v>3.75</v>
       </c>
       <c r="U100">
-        <v>2.63</v>
+        <v>2.17</v>
       </c>
       <c r="V100">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="W100">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X100">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y100">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z100">
-        <v>3.58</v>
+        <v>5.5</v>
       </c>
       <c r="AA100">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AB100">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AC100">
-        <v>2.88</v>
+        <v>2.24</v>
       </c>
       <c r="AD100">
-        <v>1.32</v>
+        <v>1.55</v>
       </c>
       <c r="AE100">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="AF100">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AG100">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="AK100">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,80 +16772,80 @@
         </is>
       </c>
       <c r="N101">
-        <v>1.41</v>
+        <v>2.24</v>
       </c>
       <c r="O101">
-        <v>4.7</v>
+        <v>3.2</v>
       </c>
       <c r="P101">
-        <v>5.5</v>
+        <v>3.1</v>
       </c>
       <c r="Q101">
-        <v>1.86</v>
+        <v>2.81</v>
       </c>
       <c r="R101">
-        <v>2.6</v>
+        <v>2.03</v>
       </c>
       <c r="S101">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="T101">
-        <v>3.75</v>
+        <v>2.77</v>
       </c>
       <c r="U101">
-        <v>2.17</v>
+        <v>2.61</v>
       </c>
       <c r="V101">
+        <v>1.39</v>
+      </c>
+      <c r="W101">
+        <v>1.07</v>
+      </c>
+      <c r="X101">
+        <v>1.01</v>
+      </c>
+      <c r="Y101">
+        <v>1.25</v>
+      </c>
+      <c r="Z101">
+        <v>3.52</v>
+      </c>
+      <c r="AA101">
+        <v>1.85</v>
+      </c>
+      <c r="AB101">
+        <v>1.85</v>
+      </c>
+      <c r="AC101">
+        <v>3.4</v>
+      </c>
+      <c r="AD101">
+        <v>1.28</v>
+      </c>
+      <c r="AE101">
+        <v>1.11</v>
+      </c>
+      <c r="AF101">
+        <v>1.73</v>
+      </c>
+      <c r="AG101">
+        <v>2</v>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ101">
+        <v>1.25</v>
+      </c>
+      <c r="AK101">
         <v>1.62</v>
-      </c>
-      <c r="W101">
-        <v>1.11</v>
-      </c>
-      <c r="X101">
-        <v>1.02</v>
-      </c>
-      <c r="Y101">
-        <v>1.16</v>
-      </c>
-      <c r="Z101">
-        <v>5.5</v>
-      </c>
-      <c r="AA101">
-        <v>1.5</v>
-      </c>
-      <c r="AB101">
-        <v>2.55</v>
-      </c>
-      <c r="AC101">
-        <v>2.24</v>
-      </c>
-      <c r="AD101">
-        <v>1.55</v>
-      </c>
-      <c r="AE101">
-        <v>1.24</v>
-      </c>
-      <c r="AF101">
-        <v>1.67</v>
-      </c>
-      <c r="AG101">
-        <v>2.05</v>
-      </c>
-      <c r="AH101" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI101" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ101">
-        <v>1.06</v>
-      </c>
-      <c r="AK101">
-        <v>2.66</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16947,7 +16947,7 @@
         <v>2</v>
       </c>
       <c r="R102">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="S102">
         <v>1.22</v>
@@ -16959,31 +16959,31 @@
         <v>2.2</v>
       </c>
       <c r="V102">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W102">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X102">
         <v>1.02</v>
       </c>
       <c r="Y102">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z102">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AA102">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AB102">
         <v>2.55</v>
       </c>
       <c r="AC102">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="AD102">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AE102">
         <v>1.21</v>
@@ -16992,7 +16992,7 @@
         <v>1.55</v>
       </c>
       <c r="AG102">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AK102">
         <v>2.29</v>
@@ -17098,31 +17098,31 @@
         </is>
       </c>
       <c r="N103">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="O103">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P103">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="Q103">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R103">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="S103">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T103">
-        <v>3.02</v>
+        <v>3.12</v>
       </c>
       <c r="U103">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="V103">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W103">
         <v>1.08</v>
@@ -17131,31 +17131,31 @@
         <v>1.01</v>
       </c>
       <c r="Y103">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z103">
-        <v>3.88</v>
+        <v>4.05</v>
       </c>
       <c r="AA103">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AB103">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="AC103">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="AD103">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE103">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF103">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AG103">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AK103">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="O104">
-        <v>3.63</v>
+        <v>3.56</v>
       </c>
       <c r="P104">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -17424,19 +17424,19 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="O105">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P105">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="Q105">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="R105">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="S105">
         <v>1.22</v>
@@ -17448,10 +17448,10 @@
         <v>2.15</v>
       </c>
       <c r="V105">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="W105">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="X105">
         <v>1.01</v>
@@ -17469,7 +17469,7 @@
         <v>2.62</v>
       </c>
       <c r="AC105">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="AD105">
         <v>1.62</v>
@@ -17478,10 +17478,10 @@
         <v>1.25</v>
       </c>
       <c r="AF105">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AG105">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17596,7 +17596,7 @@
         <v>3.99</v>
       </c>
       <c r="Q106">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="R106">
         <v>1.94</v>
@@ -17614,7 +17614,7 @@
         <v>1.3</v>
       </c>
       <c r="W106">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X106">
         <v>1.04</v>
@@ -17629,7 +17629,7 @@
         <v>2.22</v>
       </c>
       <c r="AB106">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AC106">
         <v>4</v>
@@ -17657,7 +17657,7 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AK106">
         <v>1.75</v>
@@ -18076,28 +18076,28 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="O109">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P109">
         <v>4.2</v>
       </c>
       <c r="Q109">
-        <v>2.47</v>
+        <v>2.43</v>
       </c>
       <c r="R109">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="S109">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T109">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="U109">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="V109">
         <v>1.44</v>
@@ -18106,7 +18106,7 @@
         <v>1.1</v>
       </c>
       <c r="X109">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y109">
         <v>1.24</v>
@@ -18118,7 +18118,7 @@
         <v>1.8</v>
       </c>
       <c r="AB109">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AC109">
         <v>3.1</v>
@@ -18130,10 +18130,10 @@
         <v>1.13</v>
       </c>
       <c r="AF109">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AG109">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>1.33</v>
       </c>
       <c r="AK109">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18257,10 +18257,10 @@
         <v>1.3</v>
       </c>
       <c r="T110">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="U110">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="V110">
         <v>1.44</v>
@@ -18272,13 +18272,13 @@
         <v>1.02</v>
       </c>
       <c r="Y110">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z110">
         <v>3.48</v>
       </c>
       <c r="AA110">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AB110">
         <v>1.88</v>
@@ -18296,7 +18296,7 @@
         <v>1.72</v>
       </c>
       <c r="AG110">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18432,7 +18432,7 @@
         <v>1.03</v>
       </c>
       <c r="X111">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y111">
         <v>1.51</v>
@@ -18441,7 +18441,7 @@
         <v>2.33</v>
       </c>
       <c r="AA111">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="AB111">
         <v>1.44</v>
@@ -18450,7 +18450,7 @@
         <v>5.15</v>
       </c>
       <c r="AD111">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AE111">
         <v>1.01</v>
@@ -18459,7 +18459,7 @@
         <v>2.17</v>
       </c>
       <c r="AG111">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="O112">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P112">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q112">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="R112">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S112">
         <v>1.38</v>
       </c>
       <c r="T112">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="U112">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V112">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W112">
         <v>1.06</v>
       </c>
       <c r="X112">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y112">
         <v>1.29</v>
       </c>
       <c r="Z112">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AA112">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AB112">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC112">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="AD112">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE112">
         <v>1.07</v>
       </c>
       <c r="AF112">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="AG112">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AK112">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18731,13 +18731,13 @@
         <v>1.67</v>
       </c>
       <c r="O113">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P113">
         <v>4.3</v>
       </c>
       <c r="Q113">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R113">
         <v>2.38</v>
@@ -18746,13 +18746,13 @@
         <v>1.21</v>
       </c>
       <c r="T113">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U113">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="V113">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="W113">
         <v>1.18</v>
@@ -18764,28 +18764,28 @@
         <v>1.09</v>
       </c>
       <c r="Z113">
-        <v>5.4</v>
+        <v>5.25</v>
       </c>
       <c r="AA113">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB113">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="AC113">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AD113">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AE113">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF113">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AG113">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,7 +18798,7 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK113">
         <v>2.1</v>
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="O115">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P115">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q115">
         <v>3.5</v>
@@ -19075,10 +19075,10 @@
         <v>2.52</v>
       </c>
       <c r="U115">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="V115">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W115">
         <v>1.07</v>
@@ -19217,16 +19217,16 @@
         </is>
       </c>
       <c r="N116">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="O116">
+        <v>3.2</v>
+      </c>
+      <c r="P116">
+        <v>2.75</v>
+      </c>
+      <c r="Q116">
         <v>3.3</v>
-      </c>
-      <c r="P116">
-        <v>2.95</v>
-      </c>
-      <c r="Q116">
-        <v>2.81</v>
       </c>
       <c r="R116">
         <v>2.12</v>
@@ -19262,7 +19262,7 @@
         <v>1.67</v>
       </c>
       <c r="AC116">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AD116">
         <v>1.22</v>
@@ -19274,7 +19274,7 @@
         <v>1.87</v>
       </c>
       <c r="AG116">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19290,7 +19290,7 @@
         <v>1.33</v>
       </c>
       <c r="AK116">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19380,43 +19380,43 @@
         </is>
       </c>
       <c r="N117">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="O117">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="P117">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="Q117">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R117">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S117">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T117">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U117">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V117">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W117">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X117">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y117">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z117">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA117">
         <v>2.15</v>
@@ -19425,19 +19425,19 @@
         <v>1.66</v>
       </c>
       <c r="AC117">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD117">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE117">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF117">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG117">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK117">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL117">
         <v>0</v>

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -775,16 +775,16 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3">
         <v>0</v>
@@ -794,29 +794,29 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="O3">
         <v>3.85</v>
       </c>
       <c r="P3">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="Q3">
-        <v>2.12</v>
+        <v>2.19</v>
       </c>
       <c r="R3">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="S3">
         <v>1.3</v>
       </c>
       <c r="T3">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U3">
         <v>2.63</v>
@@ -828,77 +828,77 @@
         <v>1.08</v>
       </c>
       <c r="X3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z3">
-        <v>3.96</v>
+        <v>4.11</v>
       </c>
       <c r="AA3">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AB3">
         <v>2.07</v>
       </c>
       <c r="AC3">
-        <v>2.94</v>
+        <v>2.87</v>
       </c>
       <c r="AD3">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE3">
         <v>1.12</v>
       </c>
       <c r="AF3">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AG3">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["30"]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["6"]</t>
         </is>
       </c>
       <c r="AJ3">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK3">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O11">
         <v>3.2</v>
@@ -2111,19 +2111,19 @@
         <v>3.3</v>
       </c>
       <c r="Q11">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="R11">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="S11">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T11">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U11">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="V11">
         <v>1.39</v>
@@ -2141,22 +2141,22 @@
         <v>3.34</v>
       </c>
       <c r="AA11">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB11">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC11">
-        <v>3.36</v>
+        <v>3.33</v>
       </c>
       <c r="AD11">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE11">
         <v>1.11</v>
       </c>
       <c r="AF11">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AG11">
         <v>1.99</v>
@@ -2175,7 +2175,7 @@
         <v>1.24</v>
       </c>
       <c r="AK11">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.93</v>
+        <v>1.34</v>
       </c>
       <c r="O37">
-        <v>3.6</v>
+        <v>5.4</v>
       </c>
       <c r="P37">
-        <v>3.25</v>
+        <v>7.2</v>
       </c>
       <c r="Q37">
-        <v>2.46</v>
+        <v>1.75</v>
       </c>
       <c r="R37">
-        <v>2.24</v>
+        <v>2.7</v>
       </c>
       <c r="S37">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="T37">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="U37">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="V37">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="W37">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X37">
         <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Z37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA37">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AB37">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="AC37">
-        <v>2.33</v>
+        <v>2.12</v>
       </c>
       <c r="AD37">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="AE37">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AF37">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AG37">
-        <v>2.44</v>
+        <v>2.13</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AK37">
-        <v>1.69</v>
+        <v>2.92</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.34</v>
+        <v>1.93</v>
       </c>
       <c r="O39">
-        <v>5.4</v>
+        <v>3.6</v>
       </c>
       <c r="P39">
-        <v>7.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q39">
-        <v>1.75</v>
+        <v>2.46</v>
       </c>
       <c r="R39">
-        <v>2.7</v>
+        <v>2.24</v>
       </c>
       <c r="S39">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="T39">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="U39">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="V39">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="W39">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X39">
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Z39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA39">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AB39">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="AC39">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="AD39">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="AE39">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AF39">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AG39">
-        <v>2.13</v>
+        <v>2.44</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="AK39">
-        <v>2.92</v>
+        <v>1.69</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,34 +7318,34 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.59</v>
+        <v>2.45</v>
       </c>
       <c r="O43">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="P43">
-        <v>4.65</v>
+        <v>2.18</v>
       </c>
       <c r="Q43">
-        <v>2</v>
+        <v>3.42</v>
       </c>
       <c r="R43">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
       <c r="S43">
         <v>1.22</v>
       </c>
       <c r="T43">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U43">
         <v>2.01</v>
       </c>
       <c r="V43">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="W43">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X43">
         <v>1.02</v>
@@ -7357,25 +7357,25 @@
         <v>5.3</v>
       </c>
       <c r="AA43">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AB43">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AC43">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AD43">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AE43">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AF43">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AG43">
-        <v>2.5</v>
+        <v>2.81</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.19</v>
+        <v>1.62</v>
       </c>
       <c r="AK43">
-        <v>2.27</v>
+        <v>1.38</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,34 +7481,34 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.45</v>
+        <v>1.59</v>
       </c>
       <c r="O44">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="P44">
-        <v>2.18</v>
+        <v>4.65</v>
       </c>
       <c r="Q44">
-        <v>3.42</v>
+        <v>2</v>
       </c>
       <c r="R44">
-        <v>2.34</v>
+        <v>2.41</v>
       </c>
       <c r="S44">
         <v>1.22</v>
       </c>
       <c r="T44">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U44">
         <v>2.01</v>
       </c>
       <c r="V44">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="W44">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X44">
         <v>1.02</v>
@@ -7520,25 +7520,25 @@
         <v>5.3</v>
       </c>
       <c r="AA44">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AB44">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AC44">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AD44">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AE44">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AF44">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AG44">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.62</v>
+        <v>1.19</v>
       </c>
       <c r="AK44">
-        <v>1.38</v>
+        <v>2.27</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.35</v>
+        <v>1.65</v>
       </c>
       <c r="O61">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="P61">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="Q61">
-        <v>2.7</v>
+        <v>2.18</v>
       </c>
       <c r="R61">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="S61">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="T61">
-        <v>4.2</v>
+        <v>3.24</v>
       </c>
       <c r="U61">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="V61">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="W61">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X61">
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="Z61">
-        <v>6.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA61">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AB61">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="AC61">
-        <v>1.98</v>
+        <v>2.47</v>
       </c>
       <c r="AD61">
-        <v>1.68</v>
+        <v>1.48</v>
       </c>
       <c r="AE61">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AF61">
-        <v>1.35</v>
+        <v>1.56</v>
       </c>
       <c r="AG61">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK61">
-        <v>1.44</v>
+        <v>1.99</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.65</v>
+        <v>2.35</v>
       </c>
       <c r="O62">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="P62">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="Q62">
-        <v>2.18</v>
+        <v>2.7</v>
       </c>
       <c r="R62">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="S62">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="T62">
-        <v>3.24</v>
+        <v>4.2</v>
       </c>
       <c r="U62">
-        <v>2.25</v>
+        <v>1.96</v>
       </c>
       <c r="V62">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="W62">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="Z62">
-        <v>4.8</v>
+        <v>6.5</v>
       </c>
       <c r="AA62">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AB62">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="AC62">
-        <v>2.47</v>
+        <v>1.98</v>
       </c>
       <c r="AD62">
-        <v>1.48</v>
+        <v>1.68</v>
       </c>
       <c r="AE62">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AF62">
-        <v>1.56</v>
+        <v>1.35</v>
       </c>
       <c r="AG62">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK62">
-        <v>1.99</v>
+        <v>1.44</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="O67">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="P67">
         <v>3</v>
       </c>
       <c r="Q67">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="R67">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="S67">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="T67">
-        <v>3.08</v>
+        <v>2.57</v>
       </c>
       <c r="U67">
-        <v>2.45</v>
+        <v>2.95</v>
       </c>
       <c r="V67">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="W67">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X67">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y67">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="Z67">
-        <v>3.76</v>
+        <v>2.84</v>
       </c>
       <c r="AA67">
-        <v>1.78</v>
+        <v>2.23</v>
       </c>
       <c r="AB67">
+        <v>1.61</v>
+      </c>
+      <c r="AC67">
+        <v>4.55</v>
+      </c>
+      <c r="AD67">
+        <v>1.18</v>
+      </c>
+      <c r="AE67">
+        <v>1.03</v>
+      </c>
+      <c r="AF67">
         <v>1.95</v>
       </c>
-      <c r="AC67">
-        <v>3.15</v>
-      </c>
-      <c r="AD67">
-        <v>1.36</v>
-      </c>
-      <c r="AE67">
-        <v>1.13</v>
-      </c>
-      <c r="AF67">
-        <v>1.65</v>
-      </c>
       <c r="AG67">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AK67">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O68">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="P68">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="Q68">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="R68">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S68">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="T68">
-        <v>2.57</v>
+        <v>2.51</v>
       </c>
       <c r="U68">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="V68">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W68">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X68">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y68">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="Z68">
-        <v>2.84</v>
+        <v>3.04</v>
       </c>
       <c r="AA68">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="AB68">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AC68">
-        <v>4.55</v>
+        <v>3.42</v>
       </c>
       <c r="AD68">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AE68">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF68">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AG68">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK68">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="O69">
-        <v>3.05</v>
+        <v>3.36</v>
       </c>
       <c r="P69">
-        <v>3.25</v>
+        <v>2.52</v>
       </c>
       <c r="Q69">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="R69">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="S69">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="T69">
-        <v>2.51</v>
+        <v>3.21</v>
       </c>
       <c r="U69">
-        <v>2.86</v>
+        <v>2.5</v>
       </c>
       <c r="V69">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="W69">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X69">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y69">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z69">
+        <v>3.94</v>
+      </c>
+      <c r="AA69">
+        <v>1.74</v>
+      </c>
+      <c r="AB69">
+        <v>1.98</v>
+      </c>
+      <c r="AC69">
         <v>3.04</v>
       </c>
-      <c r="AA69">
-        <v>2.18</v>
-      </c>
-      <c r="AB69">
-        <v>1.67</v>
-      </c>
-      <c r="AC69">
-        <v>3.42</v>
-      </c>
       <c r="AD69">
-        <v>1.23</v>
+        <v>1.39</v>
       </c>
       <c r="AE69">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AF69">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AG69">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK69">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="O70">
-        <v>3.36</v>
+        <v>3.4</v>
       </c>
       <c r="P70">
-        <v>2.52</v>
+        <v>3</v>
       </c>
       <c r="Q70">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="R70">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="S70">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="T70">
-        <v>3.21</v>
+        <v>3.08</v>
       </c>
       <c r="U70">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V70">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W70">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X70">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z70">
-        <v>3.94</v>
+        <v>3.76</v>
       </c>
       <c r="AA70">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AB70">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AC70">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="AD70">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE70">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF70">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG70">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AK70">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G75">
@@ -12543,52 +12543,52 @@
         <v>0</v>
       </c>
       <c r="Q75">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="R75">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="S75">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T75">
         <v>3.25</v>
       </c>
       <c r="U75">
-        <v>2.32</v>
+        <v>2.46</v>
       </c>
       <c r="V75">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W75">
         <v>1.12</v>
       </c>
       <c r="X75">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y75">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z75">
-        <v>4.47</v>
+        <v>4.05</v>
       </c>
       <c r="AA75">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AB75">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="AC75">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AD75">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AE75">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AF75">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG75">
         <v>2.3</v>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK75">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G76">
@@ -12706,52 +12706,52 @@
         <v>0</v>
       </c>
       <c r="Q76">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="R76">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="S76">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T76">
         <v>3.25</v>
       </c>
       <c r="U76">
-        <v>2.46</v>
+        <v>2.32</v>
       </c>
       <c r="V76">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W76">
         <v>1.12</v>
       </c>
       <c r="X76">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y76">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z76">
-        <v>4.05</v>
+        <v>4.47</v>
       </c>
       <c r="AA76">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AB76">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="AC76">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AD76">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AE76">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AF76">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG76">
         <v>2.3</v>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK76">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,80 +13186,80 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.67</v>
+        <v>2.9</v>
       </c>
       <c r="O79">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P79">
-        <v>3.75</v>
+        <v>1.95</v>
       </c>
       <c r="Q79">
-        <v>2.04</v>
+        <v>3.3</v>
       </c>
       <c r="R79">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="S79">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T79">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="U79">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="V79">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="W79">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X79">
         <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z79">
-        <v>6.63</v>
+        <v>8</v>
       </c>
       <c r="AA79">
+        <v>1.3</v>
+      </c>
+      <c r="AB79">
+        <v>3.5</v>
+      </c>
+      <c r="AC79">
+        <v>1.79</v>
+      </c>
+      <c r="AD79">
+        <v>1.99</v>
+      </c>
+      <c r="AE79">
+        <v>1.4</v>
+      </c>
+      <c r="AF79">
         <v>1.33</v>
       </c>
-      <c r="AB79">
-        <v>3.1</v>
-      </c>
-      <c r="AC79">
-        <v>1.92</v>
-      </c>
-      <c r="AD79">
-        <v>1.9</v>
-      </c>
-      <c r="AE79">
+      <c r="AG79">
+        <v>3.4</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ79">
+        <v>1.2</v>
+      </c>
+      <c r="AK79">
         <v>1.33</v>
-      </c>
-      <c r="AF79">
-        <v>1.38</v>
-      </c>
-      <c r="AG79">
-        <v>2.76</v>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ79">
-        <v>1.22</v>
-      </c>
-      <c r="AK79">
-        <v>2.07</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.62</v>
+        <v>2.21</v>
       </c>
       <c r="O80">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P80">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="Q80">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="R80">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="S80">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="T80">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="U80">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="V80">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="W80">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="X80">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y80">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z80">
-        <v>7.5</v>
+        <v>5.55</v>
       </c>
       <c r="AA80">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AB80">
-        <v>2.97</v>
+        <v>2.7</v>
       </c>
       <c r="AC80">
-        <v>1.85</v>
+        <v>2.09</v>
       </c>
       <c r="AD80">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="AE80">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AF80">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AG80">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>1.25</v>
       </c>
       <c r="AK80">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.21</v>
+        <v>2.62</v>
       </c>
       <c r="O82">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P82">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="Q82">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="R82">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="S82">
+        <v>1.18</v>
+      </c>
+      <c r="T82">
+        <v>4.4</v>
+      </c>
+      <c r="U82">
+        <v>1.91</v>
+      </c>
+      <c r="V82">
+        <v>1.8</v>
+      </c>
+      <c r="W82">
         <v>1.22</v>
       </c>
-      <c r="T82">
-        <v>4</v>
-      </c>
-      <c r="U82">
-        <v>2.04</v>
-      </c>
-      <c r="V82">
-        <v>1.67</v>
-      </c>
-      <c r="W82">
-        <v>1.13</v>
-      </c>
       <c r="X82">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Z82">
-        <v>5.55</v>
+        <v>7.5</v>
       </c>
       <c r="AA82">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AB82">
-        <v>2.7</v>
+        <v>2.97</v>
       </c>
       <c r="AC82">
-        <v>2.09</v>
+        <v>1.85</v>
       </c>
       <c r="AD82">
-        <v>1.68</v>
+        <v>1.88</v>
       </c>
       <c r="AE82">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AF82">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AG82">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>1.25</v>
       </c>
       <c r="AK82">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.9</v>
+        <v>1.67</v>
       </c>
       <c r="O84">
+        <v>4</v>
+      </c>
+      <c r="P84">
         <v>3.75</v>
       </c>
-      <c r="P84">
-        <v>1.95</v>
-      </c>
       <c r="Q84">
-        <v>3.3</v>
+        <v>2.04</v>
       </c>
       <c r="R84">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="S84">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T84">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="U84">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="V84">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="W84">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X84">
         <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z84">
-        <v>8</v>
+        <v>6.63</v>
       </c>
       <c r="AA84">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AB84">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="AC84">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="AD84">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="AE84">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AF84">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AG84">
-        <v>3.4</v>
+        <v>2.76</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK84">
-        <v>1.33</v>
+        <v>2.07</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -15999,10 +15999,10 @@
         <v>1.7</v>
       </c>
       <c r="AB96">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC96">
-        <v>2.52</v>
+        <v>2.75</v>
       </c>
       <c r="AD96">
         <v>1.41</v>
@@ -16014,7 +16014,7 @@
         <v>1.55</v>
       </c>
       <c r="AG96">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16147,16 +16147,16 @@
         <v>1.51</v>
       </c>
       <c r="W97">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X97">
         <v>1.02</v>
       </c>
       <c r="Y97">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z97">
-        <v>3.98</v>
+        <v>4.16</v>
       </c>
       <c r="AA97">
         <v>1.72</v>
@@ -16177,7 +16177,7 @@
         <v>1.6</v>
       </c>
       <c r="AG97">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,65 +16446,65 @@
         </is>
       </c>
       <c r="N99">
-        <v>3.8</v>
+        <v>2.24</v>
       </c>
       <c r="O99">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P99">
-        <v>1.78</v>
+        <v>3.1</v>
       </c>
       <c r="Q99">
-        <v>4.4</v>
+        <v>2.81</v>
       </c>
       <c r="R99">
-        <v>2.34</v>
+        <v>2.03</v>
       </c>
       <c r="S99">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T99">
-        <v>3.2</v>
+        <v>2.77</v>
       </c>
       <c r="U99">
-        <v>2.54</v>
+        <v>2.61</v>
       </c>
       <c r="V99">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="W99">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X99">
         <v>1.01</v>
       </c>
       <c r="Y99">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z99">
-        <v>3.82</v>
+        <v>3.52</v>
       </c>
       <c r="AA99">
+        <v>1.85</v>
+      </c>
+      <c r="AB99">
+        <v>1.85</v>
+      </c>
+      <c r="AC99">
+        <v>3.4</v>
+      </c>
+      <c r="AD99">
+        <v>1.28</v>
+      </c>
+      <c r="AE99">
+        <v>1.11</v>
+      </c>
+      <c r="AF99">
         <v>1.73</v>
       </c>
-      <c r="AB99">
+      <c r="AG99">
         <v>2</v>
       </c>
-      <c r="AC99">
-        <v>2.83</v>
-      </c>
-      <c r="AD99">
-        <v>1.29</v>
-      </c>
-      <c r="AE99">
-        <v>1.14</v>
-      </c>
-      <c r="AF99">
-        <v>1.66</v>
-      </c>
-      <c r="AG99">
-        <v>2.07</v>
-      </c>
       <c r="AH99" t="inlineStr">
         <is>
           <t>[]</t>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK99">
-        <v>1.16</v>
+        <v>1.62</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.24</v>
+        <v>3.8</v>
       </c>
       <c r="O101">
+        <v>3.7</v>
+      </c>
+      <c r="P101">
+        <v>1.78</v>
+      </c>
+      <c r="Q101">
+        <v>4.4</v>
+      </c>
+      <c r="R101">
+        <v>2.34</v>
+      </c>
+      <c r="S101">
+        <v>1.34</v>
+      </c>
+      <c r="T101">
         <v>3.2</v>
       </c>
-      <c r="P101">
-        <v>3.1</v>
-      </c>
-      <c r="Q101">
-        <v>2.81</v>
-      </c>
-      <c r="R101">
-        <v>2.03</v>
-      </c>
-      <c r="S101">
-        <v>1.32</v>
-      </c>
-      <c r="T101">
-        <v>2.77</v>
-      </c>
       <c r="U101">
-        <v>2.61</v>
+        <v>2.54</v>
       </c>
       <c r="V101">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W101">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X101">
         <v>1.01</v>
       </c>
       <c r="Y101">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z101">
-        <v>3.52</v>
+        <v>3.82</v>
       </c>
       <c r="AA101">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AB101">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AC101">
-        <v>3.4</v>
+        <v>2.83</v>
       </c>
       <c r="AD101">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE101">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF101">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AG101">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK101">
-        <v>1.62</v>
+        <v>1.16</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -17605,10 +17605,10 @@
         <v>1.44</v>
       </c>
       <c r="T106">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="U106">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="V106">
         <v>1.3</v>
@@ -17629,13 +17629,13 @@
         <v>2.22</v>
       </c>
       <c r="AB106">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AC106">
         <v>4</v>
       </c>
       <c r="AD106">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE106">
         <v>1.02</v>
@@ -17657,7 +17657,7 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AK106">
         <v>1.75</v>
@@ -17765,10 +17765,10 @@
         <v>2.29</v>
       </c>
       <c r="S107">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T107">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U107">
         <v>2.26</v>
@@ -17783,7 +17783,7 @@
         <v>1.02</v>
       </c>
       <c r="Y107">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z107">
         <v>4.3</v>
@@ -17922,7 +17922,7 @@
         <v>5.5</v>
       </c>
       <c r="Q108">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="R108">
         <v>2.4</v>
@@ -17934,13 +17934,13 @@
         <v>3.08</v>
       </c>
       <c r="U108">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="V108">
         <v>1.44</v>
       </c>
       <c r="W108">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X108">
         <v>1.02</v>
@@ -17955,19 +17955,19 @@
         <v>1.62</v>
       </c>
       <c r="AB108">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="AC108">
         <v>2.54</v>
       </c>
       <c r="AD108">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE108">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AF108">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG108">
         <v>1.91</v>
@@ -17986,7 +17986,7 @@
         <v>1.08</v>
       </c>
       <c r="AK108">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AL108">
         <v>0</v>

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -938,36 +938,36 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="O4">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="P4">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="Q4">
         <v>4.53</v>
@@ -976,22 +976,22 @@
         <v>2.16</v>
       </c>
       <c r="S4">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T4">
-        <v>2.93</v>
+        <v>2.99</v>
       </c>
       <c r="U4">
         <v>2.57</v>
       </c>
       <c r="V4">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W4">
         <v>1.06</v>
       </c>
       <c r="X4">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y4">
         <v>1.21</v>
@@ -1009,7 +1009,7 @@
         <v>3.1</v>
       </c>
       <c r="AD4">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE4">
         <v>1.08</v>
@@ -1022,46 +1022,46 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+1"]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+1", "54"]</t>
         </is>
       </c>
       <c r="AJ4">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AK4">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1120,32 +1120,32 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="O5">
         <v>3.5</v>
       </c>
       <c r="P5">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q5">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="R5">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="S5">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T5">
         <v>3.2</v>
       </c>
       <c r="U5">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="V5">
         <v>1.4</v>
@@ -1163,10 +1163,10 @@
         <v>3.58</v>
       </c>
       <c r="AA5">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AB5">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC5">
         <v>2.99</v>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["28"]</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -1194,37 +1194,37 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK5">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1264,72 +1264,72 @@
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="O6">
         <v>3</v>
       </c>
       <c r="P6">
-        <v>2.96</v>
+        <v>2.59</v>
       </c>
       <c r="Q6">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R6">
         <v>2.1</v>
       </c>
       <c r="S6">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T6">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="U6">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="V6">
         <v>1.4</v>
       </c>
       <c r="W6">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X6">
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z6">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AA6">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AB6">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC6">
         <v>3.14</v>
@@ -1344,50 +1344,50 @@
         <v>1.68</v>
       </c>
       <c r="AG6">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["23", "60", "82"]</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["86"]</t>
         </is>
       </c>
       <c r="AJ6">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK6">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1442,66 +1442,66 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="O7">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="P7">
-        <v>3.39</v>
+        <v>4.31</v>
       </c>
       <c r="Q7">
-        <v>2.57</v>
+        <v>2.45</v>
       </c>
       <c r="R7">
-        <v>2.17</v>
+        <v>2.34</v>
       </c>
       <c r="S7">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T7">
-        <v>2.73</v>
+        <v>2.86</v>
       </c>
       <c r="U7">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="V7">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W7">
         <v>1.06</v>
       </c>
       <c r="X7">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z7">
-        <v>3.08</v>
+        <v>3.28</v>
       </c>
       <c r="AA7">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="AB7">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AC7">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AD7">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE7">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF7">
         <v>1.75</v>
@@ -1516,41 +1516,41 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["58"]</t>
         </is>
       </c>
       <c r="AJ7">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK7">
-        <v>1.67</v>
+        <v>2.09</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1590,26 +1590,26 @@
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["23", "45+7", "72"]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -1692,28 +1692,28 @@
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1753,26 +1753,26 @@
         </is>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
@@ -1782,13 +1782,13 @@
         <v>4.2</v>
       </c>
       <c r="P9">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q9">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R9">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="S9">
         <v>1.2</v>
@@ -1803,7 +1803,7 @@
         <v>1.9</v>
       </c>
       <c r="W9">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X9">
         <v>1.01</v>
@@ -1818,13 +1818,13 @@
         <v>1.27</v>
       </c>
       <c r="AB9">
-        <v>3.4</v>
+        <v>3.37</v>
       </c>
       <c r="AC9">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AD9">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AE9">
         <v>1.4</v>
@@ -1833,16 +1833,16 @@
         <v>1.29</v>
       </c>
       <c r="AG9">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["2", "14", "78", "80"]</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+5"]</t>
         </is>
       </c>
       <c r="AJ9">
@@ -1855,28 +1855,28 @@
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>27</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -2079,51 +2079,51 @@
         </is>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="O11">
         <v>3.2</v>
       </c>
       <c r="P11">
-        <v>3.3</v>
+        <v>2.87</v>
       </c>
       <c r="Q11">
-        <v>2.63</v>
+        <v>2.82</v>
       </c>
       <c r="R11">
         <v>2.07</v>
       </c>
       <c r="S11">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T11">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U11">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="V11">
         <v>1.39</v>
@@ -2144,10 +2144,10 @@
         <v>1.9</v>
       </c>
       <c r="AB11">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AC11">
-        <v>3.33</v>
+        <v>3.36</v>
       </c>
       <c r="AD11">
         <v>1.32</v>
@@ -2159,50 +2159,50 @@
         <v>1.68</v>
       </c>
       <c r="AG11">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["71", "73"]</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["15"]</t>
         </is>
       </c>
       <c r="AJ11">
         <v>1.24</v>
       </c>
       <c r="AK11">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP11">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -2257,115 +2257,115 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="O12">
         <v>3.25</v>
       </c>
       <c r="P12">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="Q12">
         <v>2.8</v>
       </c>
       <c r="R12">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="S12">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="T12">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="U12">
-        <v>2.73</v>
+        <v>2.48</v>
       </c>
       <c r="V12">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="W12">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X12">
         <v>1</v>
       </c>
       <c r="Y12">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="Z12">
-        <v>3.14</v>
+        <v>3.58</v>
       </c>
       <c r="AA12">
+        <v>1.8</v>
+      </c>
+      <c r="AB12">
+        <v>1.91</v>
+      </c>
+      <c r="AC12">
+        <v>2.92</v>
+      </c>
+      <c r="AD12">
+        <v>1.31</v>
+      </c>
+      <c r="AE12">
+        <v>1.08</v>
+      </c>
+      <c r="AF12">
+        <v>1.62</v>
+      </c>
+      <c r="AG12">
+        <v>2.15</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>["61"]</t>
+        </is>
+      </c>
+      <c r="AJ12">
+        <v>1.3</v>
+      </c>
+      <c r="AK12">
+        <v>1.58</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
         <v>2</v>
       </c>
-      <c r="AB12">
-        <v>1.73</v>
-      </c>
-      <c r="AC12">
-        <v>3.34</v>
-      </c>
-      <c r="AD12">
-        <v>1.24</v>
-      </c>
-      <c r="AE12">
-        <v>1.04</v>
-      </c>
-      <c r="AF12">
-        <v>1.73</v>
-      </c>
-      <c r="AG12">
+      <c r="AN12">
         <v>2</v>
       </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12">
-        <v>1.29</v>
-      </c>
-      <c r="AK12">
-        <v>1.57</v>
-      </c>
-      <c r="AL12">
-        <v>0</v>
-      </c>
-      <c r="AM12">
-        <v>-1</v>
-      </c>
-      <c r="AN12">
-        <v>-1</v>
-      </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>0.57</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -2405,16 +2405,16 @@
         </is>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -2424,17 +2424,17 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="O13">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="P13">
-        <v>2.9</v>
+        <v>1.55</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2489,12 +2489,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["34"]</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["7", "44"]</t>
         </is>
       </c>
       <c r="AJ13">
@@ -2507,28 +2507,28 @@
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -3086,13 +3086,13 @@
         <v>3.05</v>
       </c>
       <c r="P17">
-        <v>2.47</v>
+        <v>2.15</v>
       </c>
       <c r="Q17">
-        <v>3.66</v>
+        <v>3.57</v>
       </c>
       <c r="R17">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="S17">
         <v>1.45</v>
@@ -3101,10 +3101,10 @@
         <v>2.5</v>
       </c>
       <c r="U17">
-        <v>3.17</v>
+        <v>3.02</v>
       </c>
       <c r="V17">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W17">
         <v>1.02</v>
@@ -3119,13 +3119,13 @@
         <v>2.88</v>
       </c>
       <c r="AA17">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AB17">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AC17">
-        <v>3.82</v>
+        <v>3.58</v>
       </c>
       <c r="AD17">
         <v>1.21</v>
@@ -3153,7 +3153,7 @@
         <v>1.36</v>
       </c>
       <c r="AK17">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3249,19 +3249,19 @@
         <v>3.1</v>
       </c>
       <c r="P18">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q18">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="R18">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="S18">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T18">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="U18">
         <v>2.97</v>
@@ -3276,31 +3276,31 @@
         <v>1.03</v>
       </c>
       <c r="Y18">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z18">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AA18">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AB18">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AC18">
-        <v>4.03</v>
+        <v>4.07</v>
       </c>
       <c r="AD18">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE18">
         <v>1.03</v>
       </c>
       <c r="AF18">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AG18">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AK18">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3415,22 +3415,22 @@
         <v>5.76</v>
       </c>
       <c r="Q19">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="R19">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="S19">
         <v>1.34</v>
       </c>
       <c r="T19">
-        <v>3.08</v>
+        <v>3.22</v>
       </c>
       <c r="U19">
         <v>2.73</v>
       </c>
       <c r="V19">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W19">
         <v>1.08</v>
@@ -3448,13 +3448,13 @@
         <v>1.83</v>
       </c>
       <c r="AB19">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AC19">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AD19">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE19">
         <v>1.09</v>
@@ -3463,7 +3463,7 @@
         <v>1.99</v>
       </c>
       <c r="AG19">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="O23">
         <v>3.2</v>
@@ -4070,49 +4070,49 @@
         <v>2.7</v>
       </c>
       <c r="R23">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="S23">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="T23">
-        <v>2.51</v>
+        <v>2.61</v>
       </c>
       <c r="U23">
-        <v>2.99</v>
+        <v>2.85</v>
       </c>
       <c r="V23">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W23">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="Z23">
-        <v>2.94</v>
+        <v>3.08</v>
       </c>
       <c r="AA23">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB23">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AC23">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="AD23">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE23">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF23">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AG23">
         <v>1.91</v>
@@ -4710,25 +4710,25 @@
         </is>
       </c>
       <c r="N27">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="O27">
         <v>3.6</v>
       </c>
       <c r="P27">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="Q27">
-        <v>5.27</v>
+        <v>5.33</v>
       </c>
       <c r="R27">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="S27">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T27">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="U27">
         <v>2.92</v>
@@ -4743,22 +4743,22 @@
         <v>1</v>
       </c>
       <c r="Y27">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z27">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="AA27">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AB27">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AC27">
-        <v>3.71</v>
+        <v>3.79</v>
       </c>
       <c r="AD27">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AE27">
         <v>1.04</v>
@@ -5199,55 +5199,55 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="O30">
-        <v>4.18</v>
+        <v>4.07</v>
       </c>
       <c r="P30">
-        <v>6.25</v>
+        <v>5.99</v>
       </c>
       <c r="Q30">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="R30">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="S30">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T30">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="U30">
-        <v>2.48</v>
+        <v>2.57</v>
       </c>
       <c r="V30">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W30">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X30">
         <v>1</v>
       </c>
       <c r="Y30">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z30">
-        <v>3.78</v>
+        <v>3.58</v>
       </c>
       <c r="AA30">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AB30">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="AC30">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="AD30">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE30">
         <v>1.13</v>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AK30">
-        <v>2.39</v>
+        <v>2.29</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5371,55 +5371,55 @@
         <v>3.45</v>
       </c>
       <c r="Q31">
-        <v>2.59</v>
+        <v>2.78</v>
       </c>
       <c r="R31">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="S31">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="T31">
-        <v>2.54</v>
+        <v>2.45</v>
       </c>
       <c r="U31">
-        <v>2.97</v>
+        <v>3.34</v>
       </c>
       <c r="V31">
         <v>1.32</v>
       </c>
       <c r="W31">
+        <v>1.04</v>
+      </c>
+      <c r="X31">
         <v>1.05</v>
       </c>
-      <c r="X31">
-        <v>1.04</v>
-      </c>
       <c r="Y31">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z31">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AA31">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AB31">
         <v>1.62</v>
       </c>
       <c r="AC31">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="AD31">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE31">
         <v>1.03</v>
       </c>
       <c r="AF31">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AG31">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AK31">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.34</v>
+        <v>3.2</v>
       </c>
       <c r="O37">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="P37">
-        <v>7.2</v>
+        <v>2</v>
       </c>
       <c r="Q37">
-        <v>1.75</v>
+        <v>3.75</v>
       </c>
       <c r="R37">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="S37">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="T37">
-        <v>3.9</v>
+        <v>2.76</v>
       </c>
       <c r="U37">
-        <v>2.04</v>
+        <v>2.64</v>
       </c>
       <c r="V37">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="W37">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="X37">
         <v>1.01</v>
       </c>
       <c r="Y37">
+        <v>1.24</v>
+      </c>
+      <c r="Z37">
+        <v>3.8</v>
+      </c>
+      <c r="AA37">
+        <v>1.82</v>
+      </c>
+      <c r="AB37">
+        <v>1.85</v>
+      </c>
+      <c r="AC37">
+        <v>2.97</v>
+      </c>
+      <c r="AD37">
+        <v>1.3</v>
+      </c>
+      <c r="AE37">
         <v>1.08</v>
       </c>
-      <c r="Z37">
-        <v>6</v>
-      </c>
-      <c r="AA37">
-        <v>1.4</v>
-      </c>
-      <c r="AB37">
-        <v>2.75</v>
-      </c>
-      <c r="AC37">
-        <v>2.12</v>
-      </c>
-      <c r="AD37">
-        <v>1.67</v>
-      </c>
-      <c r="AE37">
-        <v>1.25</v>
-      </c>
       <c r="AF37">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="AG37">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.06</v>
+        <v>1.7</v>
       </c>
       <c r="AK37">
-        <v>2.92</v>
+        <v>1.22</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>3.2</v>
+        <v>1.34</v>
       </c>
       <c r="O38">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="P38">
-        <v>2</v>
+        <v>7.2</v>
       </c>
       <c r="Q38">
-        <v>3.75</v>
+        <v>1.75</v>
       </c>
       <c r="R38">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="S38">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="T38">
-        <v>2.76</v>
+        <v>3.9</v>
       </c>
       <c r="U38">
-        <v>2.64</v>
+        <v>2.04</v>
       </c>
       <c r="V38">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="W38">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="X38">
         <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="Z38">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="AA38">
-        <v>1.82</v>
+        <v>1.4</v>
       </c>
       <c r="AB38">
-        <v>1.85</v>
+        <v>2.75</v>
       </c>
       <c r="AC38">
-        <v>2.97</v>
+        <v>2.12</v>
       </c>
       <c r="AD38">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="AE38">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AF38">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="AG38">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.7</v>
+        <v>1.06</v>
       </c>
       <c r="AK38">
-        <v>1.22</v>
+        <v>2.92</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.47</v>
+        <v>3.5</v>
       </c>
       <c r="O40">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P40">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="Q40">
-        <v>2.88</v>
+        <v>3.44</v>
       </c>
       <c r="R40">
-        <v>2.41</v>
+        <v>2.49</v>
       </c>
       <c r="S40">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T40">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="U40">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="V40">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="W40">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="Z40">
-        <v>4.64</v>
+        <v>4.7</v>
       </c>
       <c r="AA40">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AB40">
-        <v>2.21</v>
+        <v>2.36</v>
       </c>
       <c r="AC40">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="AD40">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AE40">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF40">
         <v>1.55</v>
       </c>
       <c r="AG40">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK40">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>3.5</v>
+        <v>2.47</v>
       </c>
       <c r="O41">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P41">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="Q41">
-        <v>3.44</v>
+        <v>2.88</v>
       </c>
       <c r="R41">
-        <v>2.49</v>
+        <v>2.41</v>
       </c>
       <c r="S41">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T41">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="U41">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="V41">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="W41">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X41">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="Z41">
-        <v>4.7</v>
+        <v>4.64</v>
       </c>
       <c r="AA41">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AB41">
-        <v>2.36</v>
+        <v>2.21</v>
       </c>
       <c r="AC41">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="AD41">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AE41">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF41">
         <v>1.55</v>
       </c>
       <c r="AG41">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK41">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,34 +7318,34 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.45</v>
+        <v>1.59</v>
       </c>
       <c r="O43">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="P43">
-        <v>2.18</v>
+        <v>4.65</v>
       </c>
       <c r="Q43">
-        <v>3.42</v>
+        <v>2</v>
       </c>
       <c r="R43">
-        <v>2.34</v>
+        <v>2.41</v>
       </c>
       <c r="S43">
         <v>1.22</v>
       </c>
       <c r="T43">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U43">
         <v>2.01</v>
       </c>
       <c r="V43">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="W43">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X43">
         <v>1.02</v>
@@ -7357,25 +7357,25 @@
         <v>5.3</v>
       </c>
       <c r="AA43">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AB43">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AC43">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AD43">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AE43">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AF43">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AG43">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.62</v>
+        <v>1.19</v>
       </c>
       <c r="AK43">
-        <v>1.38</v>
+        <v>2.27</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,34 +7481,34 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.59</v>
+        <v>2.45</v>
       </c>
       <c r="O44">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="P44">
-        <v>4.65</v>
+        <v>2.18</v>
       </c>
       <c r="Q44">
-        <v>2</v>
+        <v>3.42</v>
       </c>
       <c r="R44">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
       <c r="S44">
         <v>1.22</v>
       </c>
       <c r="T44">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U44">
         <v>2.01</v>
       </c>
       <c r="V44">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="W44">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X44">
         <v>1.02</v>
@@ -7520,25 +7520,25 @@
         <v>5.3</v>
       </c>
       <c r="AA44">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AB44">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AC44">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AD44">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AE44">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AF44">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AG44">
-        <v>2.5</v>
+        <v>2.81</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.19</v>
+        <v>1.62</v>
       </c>
       <c r="AK44">
-        <v>2.27</v>
+        <v>1.38</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="O61">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="P61">
+        <v>3.35</v>
+      </c>
+      <c r="Q61">
+        <v>2.3</v>
+      </c>
+      <c r="R61">
+        <v>2.62</v>
+      </c>
+      <c r="S61">
+        <v>1.17</v>
+      </c>
+      <c r="T61">
         <v>4</v>
       </c>
-      <c r="Q61">
-        <v>2.18</v>
-      </c>
-      <c r="R61">
-        <v>2.32</v>
-      </c>
-      <c r="S61">
-        <v>1.25</v>
-      </c>
-      <c r="T61">
-        <v>3.24</v>
-      </c>
       <c r="U61">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="V61">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="W61">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X61">
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="Z61">
-        <v>4.8</v>
+        <v>6.57</v>
       </c>
       <c r="AA61">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AB61">
-        <v>2.35</v>
+        <v>3</v>
       </c>
       <c r="AC61">
-        <v>2.47</v>
+        <v>1.89</v>
       </c>
       <c r="AD61">
-        <v>1.48</v>
+        <v>1.78</v>
       </c>
       <c r="AE61">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AF61">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="AG61">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>1.17</v>
       </c>
       <c r="AK61">
-        <v>1.99</v>
+        <v>1.83</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.35</v>
+        <v>1.65</v>
       </c>
       <c r="O62">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="P62">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="Q62">
-        <v>2.7</v>
+        <v>2.18</v>
       </c>
       <c r="R62">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="S62">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="T62">
-        <v>4.2</v>
+        <v>3.24</v>
       </c>
       <c r="U62">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="V62">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="W62">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="Z62">
-        <v>6.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA62">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AB62">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="AC62">
-        <v>1.98</v>
+        <v>2.47</v>
       </c>
       <c r="AD62">
-        <v>1.68</v>
+        <v>1.48</v>
       </c>
       <c r="AE62">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AF62">
-        <v>1.35</v>
+        <v>1.56</v>
       </c>
       <c r="AG62">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK62">
-        <v>1.44</v>
+        <v>1.99</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.84</v>
+        <v>2.35</v>
       </c>
       <c r="O63">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="P63">
-        <v>3.35</v>
+        <v>2.4</v>
       </c>
       <c r="Q63">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="R63">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="S63">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T63">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="U63">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V63">
         <v>1.72</v>
       </c>
       <c r="W63">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X63">
         <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z63">
-        <v>6.57</v>
+        <v>6.5</v>
       </c>
       <c r="AA63">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB63">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AC63">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="AD63">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="AE63">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF63">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AG63">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK63">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,80 +11067,80 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="O66">
-        <v>3.23</v>
+        <v>3.4</v>
       </c>
       <c r="P66">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="Q66">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="R66">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S66">
+        <v>1.31</v>
+      </c>
+      <c r="T66">
+        <v>3.08</v>
+      </c>
+      <c r="U66">
+        <v>2.45</v>
+      </c>
+      <c r="V66">
+        <v>1.44</v>
+      </c>
+      <c r="W66">
+        <v>1.08</v>
+      </c>
+      <c r="X66">
+        <v>1.02</v>
+      </c>
+      <c r="Y66">
+        <v>1.21</v>
+      </c>
+      <c r="Z66">
+        <v>3.76</v>
+      </c>
+      <c r="AA66">
+        <v>1.78</v>
+      </c>
+      <c r="AB66">
+        <v>1.95</v>
+      </c>
+      <c r="AC66">
+        <v>3.15</v>
+      </c>
+      <c r="AD66">
+        <v>1.36</v>
+      </c>
+      <c r="AE66">
+        <v>1.13</v>
+      </c>
+      <c r="AF66">
+        <v>1.65</v>
+      </c>
+      <c r="AG66">
+        <v>2.15</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ66">
         <v>1.38</v>
       </c>
-      <c r="T66">
-        <v>2.92</v>
-      </c>
-      <c r="U66">
-        <v>2.89</v>
-      </c>
-      <c r="V66">
-        <v>1.4</v>
-      </c>
-      <c r="W66">
-        <v>1.05</v>
-      </c>
-      <c r="X66">
-        <v>1.04</v>
-      </c>
-      <c r="Y66">
-        <v>1.22</v>
-      </c>
-      <c r="Z66">
-        <v>3.48</v>
-      </c>
-      <c r="AA66">
-        <v>1.83</v>
-      </c>
-      <c r="AB66">
-        <v>1.88</v>
-      </c>
-      <c r="AC66">
-        <v>2.97</v>
-      </c>
-      <c r="AD66">
-        <v>1.33</v>
-      </c>
-      <c r="AE66">
-        <v>1.08</v>
-      </c>
-      <c r="AF66">
-        <v>1.75</v>
-      </c>
-      <c r="AG66">
-        <v>1.95</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ66">
-        <v>1.23</v>
-      </c>
       <c r="AK66">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="O67">
-        <v>3.15</v>
+        <v>3.36</v>
       </c>
       <c r="P67">
-        <v>3</v>
+        <v>2.52</v>
       </c>
       <c r="Q67">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="R67">
-        <v>1.95</v>
+        <v>2.13</v>
       </c>
       <c r="S67">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="T67">
-        <v>2.57</v>
+        <v>3.21</v>
       </c>
       <c r="U67">
-        <v>2.95</v>
+        <v>2.5</v>
       </c>
       <c r="V67">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="W67">
+        <v>1.07</v>
+      </c>
+      <c r="X67">
         <v>1.03</v>
       </c>
-      <c r="X67">
-        <v>1.04</v>
-      </c>
       <c r="Y67">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="Z67">
-        <v>2.84</v>
+        <v>3.94</v>
       </c>
       <c r="AA67">
-        <v>2.23</v>
+        <v>1.74</v>
       </c>
       <c r="AB67">
-        <v>1.61</v>
+        <v>1.98</v>
       </c>
       <c r="AC67">
-        <v>4.55</v>
+        <v>3.04</v>
       </c>
       <c r="AD67">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="AE67">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AF67">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AG67">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK67">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,80 +11393,80 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="O68">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="P68">
-        <v>3.25</v>
+        <v>3.82</v>
       </c>
       <c r="Q68">
-        <v>2.95</v>
+        <v>2.4</v>
       </c>
       <c r="R68">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="S68">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T68">
-        <v>2.51</v>
+        <v>3.1</v>
       </c>
       <c r="U68">
-        <v>2.86</v>
+        <v>2.74</v>
       </c>
       <c r="V68">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W68">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X68">
         <v>1.02</v>
       </c>
       <c r="Y68">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z68">
-        <v>3.04</v>
+        <v>3.92</v>
       </c>
       <c r="AA68">
-        <v>2.18</v>
+        <v>1.8</v>
       </c>
       <c r="AB68">
-        <v>1.67</v>
+        <v>2.01</v>
       </c>
       <c r="AC68">
-        <v>3.42</v>
+        <v>3.13</v>
       </c>
       <c r="AD68">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AE68">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AF68">
-        <v>1.78</v>
+        <v>1.64</v>
       </c>
       <c r="AG68">
+        <v>2.05</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ68">
+        <v>1.26</v>
+      </c>
+      <c r="AK68">
         <v>1.93</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ68">
-        <v>1.28</v>
-      </c>
-      <c r="AK68">
-        <v>1.6</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="O69">
-        <v>3.36</v>
+        <v>3.23</v>
       </c>
       <c r="P69">
-        <v>2.52</v>
+        <v>2.78</v>
       </c>
       <c r="Q69">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="R69">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="S69">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="T69">
-        <v>3.21</v>
+        <v>2.92</v>
       </c>
       <c r="U69">
-        <v>2.5</v>
+        <v>2.89</v>
       </c>
       <c r="V69">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W69">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X69">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y69">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z69">
-        <v>3.94</v>
+        <v>3.48</v>
       </c>
       <c r="AA69">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AB69">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="AC69">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AD69">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AE69">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF69">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG69">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AK69">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="O70">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="P70">
         <v>3</v>
       </c>
       <c r="Q70">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="R70">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="S70">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="T70">
-        <v>3.08</v>
+        <v>2.57</v>
       </c>
       <c r="U70">
-        <v>2.45</v>
+        <v>2.95</v>
       </c>
       <c r="V70">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="W70">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X70">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y70">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="Z70">
-        <v>3.76</v>
+        <v>2.84</v>
       </c>
       <c r="AA70">
-        <v>1.78</v>
+        <v>2.23</v>
       </c>
       <c r="AB70">
+        <v>1.61</v>
+      </c>
+      <c r="AC70">
+        <v>4.55</v>
+      </c>
+      <c r="AD70">
+        <v>1.18</v>
+      </c>
+      <c r="AE70">
+        <v>1.03</v>
+      </c>
+      <c r="AF70">
         <v>1.95</v>
       </c>
-      <c r="AC70">
-        <v>3.15</v>
-      </c>
-      <c r="AD70">
-        <v>1.36</v>
-      </c>
-      <c r="AE70">
-        <v>1.13</v>
-      </c>
-      <c r="AF70">
-        <v>1.65</v>
-      </c>
       <c r="AG70">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AK70">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="O71">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="P71">
-        <v>3.82</v>
+        <v>3.25</v>
       </c>
       <c r="Q71">
-        <v>2.4</v>
+        <v>2.95</v>
       </c>
       <c r="R71">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="S71">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T71">
-        <v>3.1</v>
+        <v>2.51</v>
       </c>
       <c r="U71">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="V71">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W71">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X71">
         <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z71">
-        <v>3.92</v>
+        <v>3.04</v>
       </c>
       <c r="AA71">
-        <v>1.8</v>
+        <v>2.18</v>
       </c>
       <c r="AB71">
-        <v>2.01</v>
+        <v>1.67</v>
       </c>
       <c r="AC71">
-        <v>3.13</v>
+        <v>3.42</v>
       </c>
       <c r="AD71">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AE71">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF71">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="AG71">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK71">
-        <v>1.93</v>
+        <v>1.6</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,34 +13186,34 @@
         </is>
       </c>
       <c r="N79">
+        <v>2.62</v>
+      </c>
+      <c r="O79">
+        <v>3.7</v>
+      </c>
+      <c r="P79">
+        <v>2.1</v>
+      </c>
+      <c r="Q79">
         <v>2.9</v>
       </c>
-      <c r="O79">
-        <v>3.75</v>
-      </c>
-      <c r="P79">
-        <v>1.95</v>
-      </c>
-      <c r="Q79">
-        <v>3.3</v>
-      </c>
       <c r="R79">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="S79">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T79">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="U79">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="V79">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="W79">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X79">
         <v>1.01</v>
@@ -13222,44 +13222,44 @@
         <v>1.05</v>
       </c>
       <c r="Z79">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AA79">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AB79">
-        <v>3.5</v>
+        <v>2.97</v>
       </c>
       <c r="AC79">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AD79">
-        <v>1.99</v>
+        <v>1.88</v>
       </c>
       <c r="AE79">
+        <v>1.41</v>
+      </c>
+      <c r="AF79">
+        <v>1.31</v>
+      </c>
+      <c r="AG79">
+        <v>3.1</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ79">
+        <v>1.25</v>
+      </c>
+      <c r="AK79">
         <v>1.4</v>
-      </c>
-      <c r="AF79">
-        <v>1.33</v>
-      </c>
-      <c r="AG79">
-        <v>3.4</v>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ79">
-        <v>1.2</v>
-      </c>
-      <c r="AK79">
-        <v>1.33</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.21</v>
+        <v>2.9</v>
       </c>
       <c r="O80">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P80">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="Q80">
-        <v>2.85</v>
+        <v>3.3</v>
       </c>
       <c r="R80">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="S80">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T80">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="U80">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="V80">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="W80">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="X80">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y80">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Z80">
-        <v>5.55</v>
+        <v>8</v>
       </c>
       <c r="AA80">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AB80">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="AC80">
-        <v>2.09</v>
+        <v>1.79</v>
       </c>
       <c r="AD80">
-        <v>1.68</v>
+        <v>1.99</v>
       </c>
       <c r="AE80">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AF80">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AG80">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK80">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="O81">
+        <v>3.72</v>
+      </c>
+      <c r="P81">
+        <v>2.55</v>
+      </c>
+      <c r="Q81">
+        <v>2.76</v>
+      </c>
+      <c r="R81">
+        <v>2.38</v>
+      </c>
+      <c r="S81">
+        <v>1.28</v>
+      </c>
+      <c r="T81">
         <v>3.6</v>
       </c>
-      <c r="P81">
-        <v>1.91</v>
-      </c>
-      <c r="Q81">
-        <v>3.4</v>
-      </c>
-      <c r="R81">
-        <v>2.5</v>
-      </c>
-      <c r="S81">
-        <v>1.22</v>
-      </c>
-      <c r="T81">
-        <v>3.55</v>
-      </c>
       <c r="U81">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="V81">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="W81">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X81">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Z81">
-        <v>5.25</v>
+        <v>4.6</v>
       </c>
       <c r="AA81">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="AB81">
-        <v>2.56</v>
+        <v>2.25</v>
       </c>
       <c r="AC81">
-        <v>2.03</v>
+        <v>2.38</v>
       </c>
       <c r="AD81">
-        <v>1.69</v>
+        <v>1.46</v>
       </c>
       <c r="AE81">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AF81">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AG81">
-        <v>2.69</v>
+        <v>2.45</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK81">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,19 +13675,19 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.62</v>
+        <v>1.67</v>
       </c>
       <c r="O82">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="P82">
-        <v>2.1</v>
+        <v>3.75</v>
       </c>
       <c r="Q82">
-        <v>2.9</v>
+        <v>2.04</v>
       </c>
       <c r="R82">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="S82">
         <v>1.18</v>
@@ -13708,31 +13708,31 @@
         <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z82">
-        <v>7.5</v>
+        <v>6.63</v>
       </c>
       <c r="AA82">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB82">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="AC82">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AD82">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AE82">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AF82">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AG82">
-        <v>3.1</v>
+        <v>2.76</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK82">
-        <v>1.4</v>
+        <v>2.07</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="O83">
-        <v>3.72</v>
+        <v>3.5</v>
       </c>
       <c r="P83">
-        <v>2.55</v>
+        <v>2.03</v>
       </c>
       <c r="Q83">
-        <v>2.76</v>
+        <v>3.18</v>
       </c>
       <c r="R83">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="S83">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="T83">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U83">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="V83">
-        <v>1.52</v>
+        <v>1.71</v>
       </c>
       <c r="W83">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="X83">
         <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Z83">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="AA83">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="AB83">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="AC83">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="AD83">
-        <v>1.46</v>
+        <v>1.69</v>
       </c>
       <c r="AE83">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AF83">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AG83">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.3</v>
+        <v>1.77</v>
       </c>
       <c r="AK83">
-        <v>1.53</v>
+        <v>1.26</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
+        <v>2.21</v>
+      </c>
+      <c r="O84">
+        <v>3.6</v>
+      </c>
+      <c r="P84">
+        <v>2.5</v>
+      </c>
+      <c r="Q84">
+        <v>2.85</v>
+      </c>
+      <c r="R84">
+        <v>2.3</v>
+      </c>
+      <c r="S84">
+        <v>1.22</v>
+      </c>
+      <c r="T84">
+        <v>4</v>
+      </c>
+      <c r="U84">
+        <v>2.04</v>
+      </c>
+      <c r="V84">
         <v>1.67</v>
       </c>
-      <c r="O84">
-        <v>4</v>
-      </c>
-      <c r="P84">
-        <v>3.75</v>
-      </c>
-      <c r="Q84">
-        <v>2.04</v>
-      </c>
-      <c r="R84">
-        <v>2.52</v>
-      </c>
-      <c r="S84">
-        <v>1.18</v>
-      </c>
-      <c r="T84">
-        <v>4.4</v>
-      </c>
-      <c r="U84">
-        <v>1.91</v>
-      </c>
-      <c r="V84">
-        <v>1.8</v>
-      </c>
       <c r="W84">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="X84">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y84">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Z84">
-        <v>6.63</v>
+        <v>5.55</v>
       </c>
       <c r="AA84">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AB84">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AC84">
-        <v>1.92</v>
+        <v>2.09</v>
       </c>
       <c r="AD84">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AE84">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AF84">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AG84">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK84">
-        <v>2.07</v>
+        <v>1.51</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G85">
@@ -14167,49 +14167,49 @@
         <v>3.1</v>
       </c>
       <c r="O85">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P85">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="Q85">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="R85">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S85">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T85">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="U85">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="V85">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="W85">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X85">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y85">
         <v>1.09</v>
       </c>
       <c r="Z85">
-        <v>5.4</v>
+        <v>5.25</v>
       </c>
       <c r="AA85">
         <v>1.4</v>
       </c>
       <c r="AB85">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="AC85">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AD85">
         <v>1.69</v>
@@ -14218,10 +14218,10 @@
         <v>1.25</v>
       </c>
       <c r="AF85">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG85">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.77</v>
+        <v>1.22</v>
       </c>
       <c r="AK85">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.15</v>
+        <v>1.43</v>
       </c>
       <c r="O98">
-        <v>3.25</v>
+        <v>4.7</v>
       </c>
       <c r="P98">
-        <v>3.05</v>
+        <v>5.5</v>
       </c>
       <c r="Q98">
-        <v>2.64</v>
+        <v>1.88</v>
       </c>
       <c r="R98">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="S98">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="T98">
-        <v>2.76</v>
+        <v>3.75</v>
       </c>
       <c r="U98">
-        <v>2.63</v>
+        <v>2.17</v>
       </c>
       <c r="V98">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="W98">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X98">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y98">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z98">
-        <v>3.58</v>
+        <v>5.5</v>
       </c>
       <c r="AA98">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AB98">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="AC98">
-        <v>2.88</v>
+        <v>2.24</v>
       </c>
       <c r="AD98">
-        <v>1.32</v>
+        <v>1.55</v>
       </c>
       <c r="AE98">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="AF98">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AG98">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="AK98">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.43</v>
+        <v>2.15</v>
       </c>
       <c r="O100">
-        <v>4.7</v>
+        <v>3.25</v>
       </c>
       <c r="P100">
-        <v>5.5</v>
+        <v>3.05</v>
       </c>
       <c r="Q100">
-        <v>1.88</v>
+        <v>2.64</v>
       </c>
       <c r="R100">
-        <v>2.5</v>
+        <v>2.08</v>
       </c>
       <c r="S100">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="T100">
-        <v>3.75</v>
+        <v>2.76</v>
       </c>
       <c r="U100">
-        <v>2.17</v>
+        <v>2.63</v>
       </c>
       <c r="V100">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="W100">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X100">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y100">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Z100">
-        <v>5.5</v>
+        <v>3.58</v>
       </c>
       <c r="AA100">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AB100">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="AC100">
-        <v>2.24</v>
+        <v>2.88</v>
       </c>
       <c r="AD100">
-        <v>1.55</v>
+        <v>1.32</v>
       </c>
       <c r="AE100">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="AF100">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AG100">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="AK100">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
+        <v>1.47</v>
+      </c>
+      <c r="O101">
+        <v>4.1</v>
+      </c>
+      <c r="P101">
+        <v>5.4</v>
+      </c>
+      <c r="Q101">
+        <v>2</v>
+      </c>
+      <c r="R101">
+        <v>2.67</v>
+      </c>
+      <c r="S101">
+        <v>1.22</v>
+      </c>
+      <c r="T101">
         <v>3.8</v>
       </c>
-      <c r="O101">
-        <v>3.7</v>
-      </c>
-      <c r="P101">
-        <v>1.78</v>
-      </c>
-      <c r="Q101">
-        <v>4.4</v>
-      </c>
-      <c r="R101">
-        <v>2.34</v>
-      </c>
-      <c r="S101">
-        <v>1.34</v>
-      </c>
-      <c r="T101">
-        <v>3.2</v>
-      </c>
       <c r="U101">
-        <v>2.54</v>
+        <v>2.2</v>
       </c>
       <c r="V101">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="W101">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X101">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y101">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z101">
-        <v>3.82</v>
+        <v>4.6</v>
       </c>
       <c r="AA101">
-        <v>1.73</v>
+        <v>1.49</v>
       </c>
       <c r="AB101">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="AC101">
-        <v>2.83</v>
+        <v>2.22</v>
       </c>
       <c r="AD101">
-        <v>1.29</v>
+        <v>1.56</v>
       </c>
       <c r="AE101">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AF101">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AG101">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK101">
-        <v>1.16</v>
+        <v>2.29</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,80 +16935,80 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.47</v>
+        <v>3.8</v>
       </c>
       <c r="O102">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="P102">
-        <v>5.4</v>
+        <v>1.78</v>
       </c>
       <c r="Q102">
+        <v>4.4</v>
+      </c>
+      <c r="R102">
+        <v>2.34</v>
+      </c>
+      <c r="S102">
+        <v>1.34</v>
+      </c>
+      <c r="T102">
+        <v>3.2</v>
+      </c>
+      <c r="U102">
+        <v>2.54</v>
+      </c>
+      <c r="V102">
+        <v>1.44</v>
+      </c>
+      <c r="W102">
+        <v>1.05</v>
+      </c>
+      <c r="X102">
+        <v>1.01</v>
+      </c>
+      <c r="Y102">
+        <v>1.19</v>
+      </c>
+      <c r="Z102">
+        <v>3.82</v>
+      </c>
+      <c r="AA102">
+        <v>1.73</v>
+      </c>
+      <c r="AB102">
         <v>2</v>
       </c>
-      <c r="R102">
-        <v>2.67</v>
-      </c>
-      <c r="S102">
-        <v>1.22</v>
-      </c>
-      <c r="T102">
-        <v>3.8</v>
-      </c>
-      <c r="U102">
-        <v>2.2</v>
-      </c>
-      <c r="V102">
-        <v>1.61</v>
-      </c>
-      <c r="W102">
+      <c r="AC102">
+        <v>2.83</v>
+      </c>
+      <c r="AD102">
+        <v>1.29</v>
+      </c>
+      <c r="AE102">
         <v>1.14</v>
       </c>
-      <c r="X102">
-        <v>1.02</v>
-      </c>
-      <c r="Y102">
+      <c r="AF102">
+        <v>1.66</v>
+      </c>
+      <c r="AG102">
+        <v>2.07</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ102">
+        <v>1.2</v>
+      </c>
+      <c r="AK102">
         <v>1.16</v>
-      </c>
-      <c r="Z102">
-        <v>4.6</v>
-      </c>
-      <c r="AA102">
-        <v>1.49</v>
-      </c>
-      <c r="AB102">
-        <v>2.55</v>
-      </c>
-      <c r="AC102">
-        <v>2.22</v>
-      </c>
-      <c r="AD102">
-        <v>1.56</v>
-      </c>
-      <c r="AE102">
-        <v>1.21</v>
-      </c>
-      <c r="AF102">
-        <v>1.55</v>
-      </c>
-      <c r="AG102">
-        <v>2.14</v>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ102">
-        <v>1.17</v>
-      </c>
-      <c r="AK102">
-        <v>2.29</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="O107">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="P107">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="Q107">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="R107">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="S107">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="T107">
-        <v>3.6</v>
+        <v>3.08</v>
       </c>
       <c r="U107">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="V107">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="W107">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X107">
         <v>1.02</v>
       </c>
       <c r="Y107">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z107">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AA107">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AB107">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AC107">
-        <v>2.61</v>
+        <v>2.54</v>
       </c>
       <c r="AD107">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AE107">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AF107">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="AG107">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="AK107">
-        <v>2.46</v>
+        <v>2.67</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="O108">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="P108">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="Q108">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="R108">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="S108">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="T108">
-        <v>3.08</v>
+        <v>3.6</v>
       </c>
       <c r="U108">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="V108">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="W108">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X108">
         <v>1.02</v>
       </c>
       <c r="Y108">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z108">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AA108">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AB108">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AC108">
-        <v>2.54</v>
+        <v>2.61</v>
       </c>
       <c r="AD108">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AE108">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AF108">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AG108">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="AK108">
-        <v>2.67</v>
+        <v>2.46</v>
       </c>
       <c r="AL108">
         <v>0</v>

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -1916,10 +1916,10 @@
         </is>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -1928,118 +1928,118 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
-        <v>2.65</v>
+        <v>2.35</v>
       </c>
       <c r="O10">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="P10">
-        <v>3.01</v>
+        <v>3.12</v>
       </c>
       <c r="Q10">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="R10">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="S10">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T10">
-        <v>2.8</v>
+        <v>3.02</v>
       </c>
       <c r="U10">
-        <v>2.89</v>
+        <v>2.72</v>
       </c>
       <c r="V10">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W10">
+        <v>1.04</v>
+      </c>
+      <c r="X10">
         <v>1.02</v>
       </c>
-      <c r="X10">
-        <v>1.03</v>
-      </c>
       <c r="Y10">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z10">
-        <v>2.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA10">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AB10">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="AC10">
-        <v>3.28</v>
+        <v>2.92</v>
       </c>
       <c r="AD10">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE10">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF10">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AG10">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["59"]</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["62", "90+1"]</t>
         </is>
       </c>
       <c r="AJ10">
         <v>1.1</v>
       </c>
       <c r="AK10">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2568,54 +2568,54 @@
         </is>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14">
         <v>0</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="O14">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="P14">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="Q14">
         <v>1.73</v>
       </c>
       <c r="R14">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S14">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T14">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="U14">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="V14">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="W14">
         <v>1.12</v>
@@ -2627,71 +2627,71 @@
         <v>1.17</v>
       </c>
       <c r="Z14">
-        <v>4.1</v>
+        <v>3.98</v>
       </c>
       <c r="AA14">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AB14">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AC14">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AD14">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE14">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF14">
         <v>1.95</v>
       </c>
       <c r="AG14">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
+          <t>["10", "18", "55"]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ14">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AK14">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="AL14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN14">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO14">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AP14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -2746,72 +2746,72 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="O15">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P15">
         <v>4.15</v>
       </c>
       <c r="Q15">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="R15">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S15">
+        <v>1.33</v>
+      </c>
+      <c r="T15">
+        <v>2.95</v>
+      </c>
+      <c r="U15">
+        <v>2.58</v>
+      </c>
+      <c r="V15">
         <v>1.4</v>
       </c>
-      <c r="T15">
-        <v>2.69</v>
-      </c>
-      <c r="U15">
-        <v>2.73</v>
-      </c>
-      <c r="V15">
-        <v>1.36</v>
-      </c>
       <c r="W15">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X15">
         <v>1.01</v>
       </c>
       <c r="Y15">
+        <v>1.22</v>
+      </c>
+      <c r="Z15">
+        <v>3.5</v>
+      </c>
+      <c r="AA15">
+        <v>1.82</v>
+      </c>
+      <c r="AB15">
+        <v>1.85</v>
+      </c>
+      <c r="AC15">
+        <v>3.14</v>
+      </c>
+      <c r="AD15">
         <v>1.29</v>
       </c>
-      <c r="Z15">
-        <v>3.04</v>
-      </c>
-      <c r="AA15">
-        <v>1.99</v>
-      </c>
-      <c r="AB15">
-        <v>1.7</v>
-      </c>
-      <c r="AC15">
-        <v>3.46</v>
-      </c>
-      <c r="AD15">
-        <v>1.22</v>
-      </c>
       <c r="AE15">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF15">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AG15">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2820,41 +2820,41 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["88"]</t>
         </is>
       </c>
       <c r="AJ15">
         <v>1.2</v>
       </c>
       <c r="AK15">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AL15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN15">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
@@ -2897,23 +2897,23 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
@@ -2926,19 +2926,19 @@
         <v>1.4</v>
       </c>
       <c r="Q16">
-        <v>6.34</v>
+        <v>4.94</v>
       </c>
       <c r="R16">
         <v>2.16</v>
       </c>
       <c r="S16">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T16">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="U16">
-        <v>2.64</v>
+        <v>2.46</v>
       </c>
       <c r="V16">
         <v>1.38</v>
@@ -2950,16 +2950,16 @@
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z16">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AA16">
         <v>1.83</v>
       </c>
       <c r="AB16">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AC16">
         <v>3.25</v>
@@ -2968,10 +2968,10 @@
         <v>1.33</v>
       </c>
       <c r="AE16">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF16">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG16">
         <v>1.7</v>
@@ -2983,11 +2983,11 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["25", "86", "90+2"]</t>
         </is>
       </c>
       <c r="AJ16">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AK16">
         <v>1.11</v>
@@ -2996,28 +2996,28 @@
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO16">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP16">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
@@ -3060,13 +3060,13 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["7"]</t>
         </is>
       </c>
       <c r="AJ17">
@@ -3159,16 +3159,16 @@
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN17">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP17">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ17">
         <v>0</v>
@@ -3220,26 +3220,26 @@
         </is>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["69", "81"]</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["31"]</t>
         </is>
       </c>
       <c r="AJ18">
@@ -3322,28 +3322,28 @@
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO18">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
@@ -3383,16 +3383,16 @@
         </is>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19">
         <v>0</v>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N19">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["3"]</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["12"]</t>
         </is>
       </c>
       <c r="AJ19">
@@ -3485,16 +3485,16 @@
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ19">
         <v>0</v>
@@ -3565,111 +3565,111 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N20">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="O20">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P20">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="Q20">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="R20">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S20">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T20">
-        <v>3.3</v>
+        <v>2.78</v>
       </c>
       <c r="U20">
-        <v>2.44</v>
+        <v>2.88</v>
       </c>
       <c r="V20">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W20">
         <v>1.08</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z20">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AA20">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="AB20">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AC20">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="AD20">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE20">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF20">
+        <v>1.66</v>
+      </c>
+      <c r="AG20">
+        <v>2</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20">
+        <v>1.3</v>
+      </c>
+      <c r="AK20">
         <v>1.6</v>
       </c>
-      <c r="AG20">
-        <v>2.15</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20">
-        <v>1.23</v>
-      </c>
-      <c r="AK20">
-        <v>1.56</v>
-      </c>
       <c r="AL20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN20">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
@@ -3709,36 +3709,36 @@
         </is>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N21">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="O21">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="P21">
-        <v>16.04</v>
+        <v>20</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3771,10 +3771,10 @@
         <v>0</v>
       </c>
       <c r="AA21">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AB21">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AC21">
         <v>0</v>
@@ -3793,12 +3793,12 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["16", "45+3", "72", "88"]</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["42"]</t>
         </is>
       </c>
       <c r="AJ21">
@@ -3811,28 +3811,28 @@
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN21">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO21">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP21">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
@@ -3872,42 +3872,42 @@
         </is>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22">
         <v>0</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N22">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O22">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P22">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q22">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="R22">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="S22">
         <v>1.36</v>
@@ -3916,10 +3916,10 @@
         <v>2.88</v>
       </c>
       <c r="U22">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="V22">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W22">
         <v>1.05</v>
@@ -3931,13 +3931,13 @@
         <v>1.33</v>
       </c>
       <c r="Z22">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AA22">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="AB22">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AC22">
         <v>3.9</v>
@@ -3949,53 +3949,53 @@
         <v>1.05</v>
       </c>
       <c r="AF22">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AG22">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["7"]</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["22", "86", "90"]</t>
         </is>
       </c>
       <c r="AJ22">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK22">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AL22">
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN22">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP22">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
@@ -4035,13 +4035,13 @@
         </is>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -4050,11 +4050,11 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N23">
@@ -4119,12 +4119,12 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["23"]</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["85"]</t>
         </is>
       </c>
       <c r="AJ23">
@@ -4137,28 +4137,28 @@
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP23">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
@@ -4198,16 +4198,16 @@
         </is>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -4217,59 +4217,59 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N24">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="O24">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P24">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="Q24">
-        <v>2.67</v>
+        <v>2.72</v>
       </c>
       <c r="R24">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="S24">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="T24">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="U24">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="V24">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W24">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X24">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y24">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="Z24">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AA24">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB24">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC24">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AD24">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE24">
         <v>1.03</v>
@@ -4282,46 +4282,46 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["15"]</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["12", "27"]</t>
         </is>
       </c>
       <c r="AJ24">
         <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="AL24">
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN24">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
@@ -4361,10 +4361,10 @@
         </is>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -4373,118 +4373,118 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N25">
         <v>2.2</v>
       </c>
       <c r="O25">
+        <v>2.85</v>
+      </c>
+      <c r="P25">
+        <v>3.4</v>
+      </c>
+      <c r="Q25">
+        <v>2.84</v>
+      </c>
+      <c r="R25">
+        <v>1.79</v>
+      </c>
+      <c r="S25">
+        <v>1.59</v>
+      </c>
+      <c r="T25">
+        <v>2.17</v>
+      </c>
+      <c r="U25">
+        <v>3.58</v>
+      </c>
+      <c r="V25">
+        <v>1.21</v>
+      </c>
+      <c r="W25">
+        <v>1.04</v>
+      </c>
+      <c r="X25">
+        <v>1.07</v>
+      </c>
+      <c r="Y25">
+        <v>1.54</v>
+      </c>
+      <c r="Z25">
+        <v>2.3</v>
+      </c>
+      <c r="AA25">
+        <v>2.55</v>
+      </c>
+      <c r="AB25">
+        <v>1.43</v>
+      </c>
+      <c r="AC25">
+        <v>4.95</v>
+      </c>
+      <c r="AD25">
+        <v>1.11</v>
+      </c>
+      <c r="AE25">
+        <v>1.04</v>
+      </c>
+      <c r="AF25">
+        <v>2.15</v>
+      </c>
+      <c r="AG25">
+        <v>1.6</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>["62"]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>["84"]</t>
+        </is>
+      </c>
+      <c r="AJ25">
+        <v>1.19</v>
+      </c>
+      <c r="AK25">
+        <v>1.57</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>5</v>
+      </c>
+      <c r="AN25">
         <v>3</v>
       </c>
-      <c r="P25">
-        <v>3.2</v>
-      </c>
-      <c r="Q25">
-        <v>2.73</v>
-      </c>
-      <c r="R25">
-        <v>2.05</v>
-      </c>
-      <c r="S25">
-        <v>1.48</v>
-      </c>
-      <c r="T25">
-        <v>2.34</v>
-      </c>
-      <c r="U25">
-        <v>3.24</v>
-      </c>
-      <c r="V25">
-        <v>1.26</v>
-      </c>
-      <c r="W25">
-        <v>1.06</v>
-      </c>
-      <c r="X25">
-        <v>1.04</v>
-      </c>
-      <c r="Y25">
-        <v>1.38</v>
-      </c>
-      <c r="Z25">
-        <v>2.81</v>
-      </c>
-      <c r="AA25">
-        <v>2.22</v>
-      </c>
-      <c r="AB25">
-        <v>1.56</v>
-      </c>
-      <c r="AC25">
-        <v>4.1</v>
-      </c>
-      <c r="AD25">
-        <v>1.16</v>
-      </c>
-      <c r="AE25">
-        <v>1.02</v>
-      </c>
-      <c r="AF25">
-        <v>1.95</v>
-      </c>
-      <c r="AG25">
-        <v>1.8</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ25">
-        <v>1.11</v>
-      </c>
-      <c r="AK25">
-        <v>1.59</v>
-      </c>
-      <c r="AL25">
-        <v>0</v>
-      </c>
-      <c r="AM25">
-        <v>-1</v>
-      </c>
-      <c r="AN25">
-        <v>-1</v>
-      </c>
       <c r="AO25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ25">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AR25">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AT25">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
@@ -4547,28 +4547,28 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="O26">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P26">
         <v>2.4</v>
       </c>
       <c r="Q26">
-        <v>3.51</v>
+        <v>3.4</v>
       </c>
       <c r="R26">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="S26">
         <v>1.49</v>
       </c>
       <c r="T26">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="U26">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="V26">
         <v>1.25</v>
@@ -4580,31 +4580,31 @@
         <v>1.06</v>
       </c>
       <c r="Y26">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="Z26">
         <v>2.28</v>
       </c>
       <c r="AA26">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="AB26">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AC26">
-        <v>5.1</v>
+        <v>5.05</v>
       </c>
       <c r="AD26">
         <v>1.1</v>
       </c>
       <c r="AE26">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AF26">
         <v>2.15</v>
       </c>
       <c r="AG26">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>1.36</v>
       </c>
       <c r="AK26">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4690,7 +4690,7 @@
         <v>0</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -4702,11 +4702,11 @@
         <v>0</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N27">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["75"]</t>
         </is>
       </c>
       <c r="AJ27">
@@ -4789,28 +4789,28 @@
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN27">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO27">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
@@ -4869,68 +4869,68 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N28">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="O28">
         <v>3.15</v>
       </c>
       <c r="P28">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA28">
         <v>2.1</v>
       </c>
       <c r="AB28">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,37 +4943,37 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL28">
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN28">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AS28">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         </is>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -5025,118 +5025,118 @@
         <v>0</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29">
         <v>0</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N29">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="O29">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P29">
         <v>4</v>
       </c>
       <c r="Q29">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="R29">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="S29">
         <v>1.36</v>
       </c>
       <c r="T29">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="U29">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V29">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W29">
+        <v>1.02</v>
+      </c>
+      <c r="X29">
+        <v>1.04</v>
+      </c>
+      <c r="Y29">
+        <v>1.31</v>
+      </c>
+      <c r="Z29">
+        <v>2.92</v>
+      </c>
+      <c r="AA29">
+        <v>2.07</v>
+      </c>
+      <c r="AB29">
+        <v>1.75</v>
+      </c>
+      <c r="AC29">
+        <v>3.58</v>
+      </c>
+      <c r="AD29">
+        <v>1.27</v>
+      </c>
+      <c r="AE29">
         <v>1.03</v>
       </c>
-      <c r="X29">
-        <v>1.03</v>
-      </c>
-      <c r="Y29">
-        <v>1.28</v>
-      </c>
-      <c r="Z29">
-        <v>3.08</v>
-      </c>
-      <c r="AA29">
-        <v>1.98</v>
-      </c>
-      <c r="AB29">
-        <v>1.82</v>
-      </c>
-      <c r="AC29">
-        <v>3.34</v>
-      </c>
-      <c r="AD29">
-        <v>1.29</v>
-      </c>
-      <c r="AE29">
-        <v>1.05</v>
-      </c>
       <c r="AF29">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG29">
         <v>1.91</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
+          <t>["90+1"]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ29">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK29">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AL29">
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN29">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO29">
-        <v>-1</v>
+        <v>28</v>
       </c>
       <c r="AP29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ29">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AR29">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="AS29">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AT29">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
@@ -5176,26 +5176,26 @@
         </is>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30">
         <v>0</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N30">
@@ -5260,12 +5260,12 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["17", "90+5"]</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["23", "43"]</t>
         </is>
       </c>
       <c r="AJ30">
@@ -5278,28 +5278,28 @@
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO30">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ30">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AR30">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AS30">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AT30">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
@@ -5365,22 +5365,22 @@
         <v>1.9</v>
       </c>
       <c r="O31">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="P31">
         <v>3.45</v>
       </c>
       <c r="Q31">
-        <v>2.78</v>
+        <v>2.64</v>
       </c>
       <c r="R31">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="S31">
         <v>1.48</v>
       </c>
       <c r="T31">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="U31">
         <v>3.34</v>
@@ -5395,13 +5395,13 @@
         <v>1.05</v>
       </c>
       <c r="Y31">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z31">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AA31">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AB31">
         <v>1.62</v>
@@ -5410,16 +5410,16 @@
         <v>4.25</v>
       </c>
       <c r="AD31">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE31">
         <v>1.03</v>
       </c>
       <c r="AF31">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AG31">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AK31">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="O32">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="P32">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q32">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="R32">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="S32">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="T32">
-        <v>4.15</v>
+        <v>4.3</v>
       </c>
       <c r="U32">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="V32">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="W32">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X32">
         <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z32">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="AA32">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AB32">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AC32">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AD32">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AE32">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF32">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="AG32">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AK32">
-        <v>5.1</v>
+        <v>5.55</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O33">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P33">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="Q33">
-        <v>2.59</v>
+        <v>2.64</v>
       </c>
       <c r="R33">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="S33">
+        <v>1.28</v>
+      </c>
+      <c r="T33">
+        <v>3.14</v>
+      </c>
+      <c r="U33">
+        <v>2.62</v>
+      </c>
+      <c r="V33">
+        <v>1.44</v>
+      </c>
+      <c r="W33">
+        <v>1.1</v>
+      </c>
+      <c r="X33">
+        <v>1.01</v>
+      </c>
+      <c r="Y33">
         <v>1.26</v>
       </c>
-      <c r="T33">
-        <v>3.29</v>
-      </c>
-      <c r="U33">
-        <v>2.45</v>
-      </c>
-      <c r="V33">
-        <v>1.48</v>
-      </c>
-      <c r="W33">
-        <v>1.11</v>
-      </c>
-      <c r="X33">
-        <v>1.03</v>
-      </c>
-      <c r="Y33">
-        <v>1.23</v>
-      </c>
       <c r="Z33">
-        <v>4.11</v>
+        <v>3.83</v>
       </c>
       <c r="AA33">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB33">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC33">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="AD33">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AE33">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF33">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AG33">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>1.22</v>
       </c>
       <c r="AK33">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5809,22 +5809,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="O34">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P34">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q34">
-        <v>2.34</v>
+        <v>2.78</v>
       </c>
       <c r="R34">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="S34">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="T34">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U34">
-        <v>2.21</v>
+        <v>1.88</v>
       </c>
       <c r="V34">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W34">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X34">
         <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z34">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AA34">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="AB34">
-        <v>2.33</v>
+        <v>2.48</v>
       </c>
       <c r="AC34">
-        <v>2.53</v>
+        <v>2.2</v>
       </c>
       <c r="AD34">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AE34">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AF34">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AG34">
-        <v>2.38</v>
+        <v>2.57</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK34">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5972,35 +5972,35 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35">
         <v>0</v>
@@ -6010,111 +6010,111 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N35">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="O35">
         <v>3.6</v>
       </c>
       <c r="P35">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="Q35">
-        <v>2.52</v>
+        <v>2.25</v>
       </c>
       <c r="R35">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="S35">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="T35">
-        <v>3.42</v>
+        <v>2.94</v>
       </c>
       <c r="U35">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="V35">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="W35">
+        <v>1.06</v>
+      </c>
+      <c r="X35">
+        <v>1.03</v>
+      </c>
+      <c r="Y35">
         <v>1.17</v>
       </c>
-      <c r="X35">
-        <v>1.01</v>
-      </c>
-      <c r="Y35">
+      <c r="Z35">
+        <v>3.95</v>
+      </c>
+      <c r="AA35">
+        <v>1.68</v>
+      </c>
+      <c r="AB35">
+        <v>2.02</v>
+      </c>
+      <c r="AC35">
+        <v>2.66</v>
+      </c>
+      <c r="AD35">
+        <v>1.37</v>
+      </c>
+      <c r="AE35">
         <v>1.11</v>
       </c>
-      <c r="Z35">
-        <v>4.9</v>
-      </c>
-      <c r="AA35">
-        <v>1.45</v>
-      </c>
-      <c r="AB35">
-        <v>2.48</v>
-      </c>
-      <c r="AC35">
-        <v>2.22</v>
-      </c>
-      <c r="AD35">
-        <v>1.56</v>
-      </c>
-      <c r="AE35">
-        <v>1.17</v>
-      </c>
       <c r="AF35">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AG35">
-        <v>2.51</v>
+        <v>2.08</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["17", "35"]</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["37"]</t>
         </is>
       </c>
       <c r="AJ35">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AK35">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="AL35">
         <v>0</v>
       </c>
       <c r="AM35">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP35">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ35">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="AR35">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AS35">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT35">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
@@ -6145,139 +6145,139 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J36">
         <v>0</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N36">
-        <v>1.76</v>
+        <v>1.29</v>
       </c>
       <c r="O36">
-        <v>3.6</v>
+        <v>5.8</v>
       </c>
       <c r="P36">
-        <v>3.9</v>
+        <v>8</v>
       </c>
       <c r="Q36">
-        <v>2.26</v>
+        <v>1.67</v>
       </c>
       <c r="R36">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="S36">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="T36">
-        <v>2.94</v>
+        <v>4.5</v>
       </c>
       <c r="U36">
-        <v>2.45</v>
+        <v>1.94</v>
       </c>
       <c r="V36">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="W36">
+        <v>1.2</v>
+      </c>
+      <c r="X36">
+        <v>1.01</v>
+      </c>
+      <c r="Y36">
         <v>1.06</v>
       </c>
-      <c r="X36">
-        <v>1.03</v>
-      </c>
-      <c r="Y36">
-        <v>1.17</v>
-      </c>
       <c r="Z36">
-        <v>3.95</v>
+        <v>6.25</v>
       </c>
       <c r="AA36">
-        <v>1.68</v>
+        <v>1.33</v>
       </c>
       <c r="AB36">
-        <v>2.02</v>
+        <v>3</v>
       </c>
       <c r="AC36">
-        <v>2.66</v>
+        <v>1.96</v>
       </c>
       <c r="AD36">
-        <v>1.37</v>
+        <v>1.83</v>
       </c>
       <c r="AE36">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="AF36">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG36">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["23", "37", "77"]</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["56", "85"]</t>
         </is>
       </c>
       <c r="AJ36">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="AK36">
-        <v>2.05</v>
+        <v>3.18</v>
       </c>
       <c r="AL36">
         <v>0</v>
       </c>
       <c r="AM36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO36">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ36">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AR36">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AS36">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT36">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
@@ -6317,30 +6317,30 @@
         </is>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I37">
         <v>0</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N37">
-        <v>3.2</v>
+        <v>3.27</v>
       </c>
       <c r="O37">
         <v>3.4</v>
@@ -6370,19 +6370,19 @@
         <v>1.1</v>
       </c>
       <c r="X37">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y37">
         <v>1.24</v>
       </c>
       <c r="Z37">
-        <v>3.8</v>
+        <v>3.34</v>
       </c>
       <c r="AA37">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AB37">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC37">
         <v>2.97</v>
@@ -6401,46 +6401,46 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["48", "70"]</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5", "67"]</t>
         </is>
       </c>
       <c r="AJ37">
         <v>1.7</v>
       </c>
       <c r="AK37">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AL37">
         <v>0</v>
       </c>
       <c r="AM37">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO37">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP37">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ37">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AR37">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS37">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AT37">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
@@ -6471,139 +6471,139 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J38">
         <v>0</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N38">
-        <v>1.34</v>
+        <v>1.84</v>
       </c>
       <c r="O38">
-        <v>5.4</v>
+        <v>3.75</v>
       </c>
       <c r="P38">
-        <v>7.2</v>
+        <v>3.6</v>
       </c>
       <c r="Q38">
-        <v>1.75</v>
+        <v>2.31</v>
       </c>
       <c r="R38">
-        <v>2.7</v>
+        <v>2.42</v>
       </c>
       <c r="S38">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T38">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="U38">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="V38">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="W38">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X38">
         <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z38">
-        <v>6</v>
+        <v>5.05</v>
       </c>
       <c r="AA38">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AB38">
-        <v>2.75</v>
+        <v>2.51</v>
       </c>
       <c r="AC38">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="AD38">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AE38">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF38">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AG38">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["18", "21", "56"]</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["71", "75"]</t>
         </is>
       </c>
       <c r="AJ38">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AK38">
-        <v>2.92</v>
+        <v>1.81</v>
       </c>
       <c r="AL38">
         <v>0</v>
       </c>
       <c r="AM38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN38">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AO38">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AP38">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ38">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AR38">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AS38">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT38">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
@@ -6619,12 +6619,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.93</v>
+        <v>2.47</v>
       </c>
       <c r="O39">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P39">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q39">
-        <v>2.46</v>
+        <v>2.88</v>
       </c>
       <c r="R39">
-        <v>2.24</v>
+        <v>2.41</v>
       </c>
       <c r="S39">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T39">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="U39">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="V39">
+        <v>1.51</v>
+      </c>
+      <c r="W39">
+        <v>1.11</v>
+      </c>
+      <c r="X39">
+        <v>1.02</v>
+      </c>
+      <c r="Y39">
+        <v>1.19</v>
+      </c>
+      <c r="Z39">
+        <v>4.64</v>
+      </c>
+      <c r="AA39">
         <v>1.62</v>
       </c>
-      <c r="W39">
+      <c r="AB39">
+        <v>2.21</v>
+      </c>
+      <c r="AC39">
+        <v>2.43</v>
+      </c>
+      <c r="AD39">
+        <v>1.49</v>
+      </c>
+      <c r="AE39">
         <v>1.15</v>
       </c>
-      <c r="X39">
-        <v>1.01</v>
-      </c>
-      <c r="Y39">
-        <v>1.12</v>
-      </c>
-      <c r="Z39">
-        <v>5</v>
-      </c>
-      <c r="AA39">
-        <v>1.57</v>
-      </c>
-      <c r="AB39">
-        <v>2.35</v>
-      </c>
-      <c r="AC39">
-        <v>2.33</v>
-      </c>
-      <c r="AD39">
-        <v>1.48</v>
-      </c>
-      <c r="AE39">
-        <v>1.18</v>
-      </c>
       <c r="AF39">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AG39">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK39">
-        <v>1.69</v>
+        <v>1.41</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>2026-09-18 13:00:00</t>
+          <t>2026-09-18 13:30:00</t>
         </is>
       </c>
     </row>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
+        <v>3.45</v>
+      </c>
+      <c r="O40">
         <v>3.5</v>
-      </c>
-      <c r="O40">
-        <v>3.6</v>
       </c>
       <c r="P40">
         <v>1.85</v>
       </c>
       <c r="Q40">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="R40">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="S40">
         <v>1.25</v>
       </c>
       <c r="T40">
-        <v>3.32</v>
+        <v>3.5</v>
       </c>
       <c r="U40">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="V40">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W40">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X40">
         <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="Z40">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AA40">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AB40">
-        <v>2.36</v>
+        <v>2.15</v>
       </c>
       <c r="AC40">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="AD40">
+        <v>1.49</v>
+      </c>
+      <c r="AE40">
+        <v>1.14</v>
+      </c>
+      <c r="AF40">
         <v>1.53</v>
       </c>
-      <c r="AE40">
-        <v>1.16</v>
-      </c>
-      <c r="AF40">
-        <v>1.55</v>
-      </c>
       <c r="AG40">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK40">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.47</v>
+        <v>3.5</v>
       </c>
       <c r="O41">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P41">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="Q41">
-        <v>2.88</v>
+        <v>3.44</v>
       </c>
       <c r="R41">
-        <v>2.41</v>
+        <v>2.49</v>
       </c>
       <c r="S41">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T41">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="U41">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="V41">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="W41">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X41">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="Z41">
-        <v>4.64</v>
+        <v>4.7</v>
       </c>
       <c r="AA41">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AB41">
-        <v>2.21</v>
+        <v>2.36</v>
       </c>
       <c r="AC41">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="AD41">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AE41">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF41">
         <v>1.55</v>
       </c>
       <c r="AG41">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK41">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>3.45</v>
+        <v>1.85</v>
       </c>
       <c r="O42">
+        <v>3.75</v>
+      </c>
+      <c r="P42">
         <v>3.5</v>
       </c>
-      <c r="P42">
-        <v>1.85</v>
-      </c>
       <c r="Q42">
-        <v>3.45</v>
+        <v>2.33</v>
       </c>
       <c r="R42">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S42">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T42">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U42">
         <v>2.25</v>
       </c>
       <c r="V42">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W42">
         <v>1.11</v>
       </c>
       <c r="X42">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z42">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AA42">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AB42">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="AC42">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="AD42">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AE42">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF42">
         <v>1.53</v>
       </c>
       <c r="AG42">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AK42">
-        <v>1.18</v>
+        <v>1.91</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -8459,16 +8459,16 @@
         </is>
       </c>
       <c r="N50">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="O50">
         <v>3</v>
       </c>
       <c r="P50">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q50">
-        <v>3.84</v>
+        <v>3.86</v>
       </c>
       <c r="R50">
         <v>1.83</v>
@@ -8483,7 +8483,7 @@
         <v>2.89</v>
       </c>
       <c r="V50">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W50">
         <v>1.03</v>
@@ -8516,7 +8516,7 @@
         <v>1.8</v>
       </c>
       <c r="AG50">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8622,80 +8622,80 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="O51">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="P51">
-        <v>3.25</v>
+        <v>3.03</v>
       </c>
       <c r="Q51">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="R51">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S51">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T51">
         <v>3.8</v>
       </c>
       <c r="U51">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="V51">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W51">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
         <v>1.12</v>
       </c>
       <c r="Z51">
-        <v>4.75</v>
+        <v>4.65</v>
       </c>
       <c r="AA51">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AB51">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="AC51">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AD51">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AE51">
+        <v>1.2</v>
+      </c>
+      <c r="AF51">
+        <v>1.5</v>
+      </c>
+      <c r="AG51">
+        <v>2.45</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
         <v>1.22</v>
       </c>
-      <c r="AF51">
-        <v>1.48</v>
-      </c>
-      <c r="AG51">
-        <v>2.5</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>1.2</v>
-      </c>
       <c r="AK51">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,7 +8785,7 @@
         </is>
       </c>
       <c r="N52">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O52">
         <v>3.3</v>
@@ -8794,22 +8794,22 @@
         <v>1.75</v>
       </c>
       <c r="Q52">
-        <v>5.19</v>
+        <v>5.25</v>
       </c>
       <c r="R52">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="S52">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="T52">
-        <v>2.84</v>
+        <v>2.77</v>
       </c>
       <c r="U52">
         <v>2.79</v>
       </c>
       <c r="V52">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W52">
         <v>1.06</v>
@@ -8824,22 +8824,22 @@
         <v>3.1</v>
       </c>
       <c r="AA52">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AB52">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AC52">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="AD52">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE52">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF52">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AG52">
         <v>1.82</v>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK52">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,25 +8948,25 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O53">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="P53">
         <v>3.2</v>
       </c>
       <c r="Q53">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="R53">
         <v>1.87</v>
       </c>
       <c r="S53">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="T53">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="U53">
         <v>3.3</v>
@@ -8975,22 +8975,22 @@
         <v>1.29</v>
       </c>
       <c r="W53">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X53">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y53">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="Z53">
         <v>2.55</v>
       </c>
       <c r="AA53">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AB53">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AC53">
         <v>4.8</v>
@@ -8999,10 +8999,10 @@
         <v>1.14</v>
       </c>
       <c r="AE53">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF53">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AG53">
         <v>1.7</v>
@@ -9114,61 +9114,61 @@
         <v>1.4</v>
       </c>
       <c r="O54">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="P54">
-        <v>6.25</v>
+        <v>5.93</v>
       </c>
       <c r="Q54">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="R54">
-        <v>2.44</v>
+        <v>2.61</v>
       </c>
       <c r="S54">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T54">
-        <v>2.96</v>
+        <v>3.4</v>
       </c>
       <c r="U54">
-        <v>2.57</v>
+        <v>2.3</v>
       </c>
       <c r="V54">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="W54">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X54">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y54">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="Z54">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA54">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AB54">
-        <v>1.98</v>
+        <v>2.21</v>
       </c>
       <c r="AC54">
-        <v>2.78</v>
+        <v>2.43</v>
       </c>
       <c r="AD54">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="AE54">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF54">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AG54">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AK54">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="O55">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="P55">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="Q55">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="R55">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S55">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T55">
         <v>3.09</v>
       </c>
       <c r="U55">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V55">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W55">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X55">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y55">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z55">
-        <v>3.78</v>
+        <v>4.2</v>
       </c>
       <c r="AA55">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AB55">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AC55">
-        <v>2.74</v>
+        <v>2.49</v>
       </c>
       <c r="AD55">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AE55">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AF55">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AG55">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AK55">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="O57">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="P57">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q57">
         <v>1.97</v>
@@ -9615,28 +9615,28 @@
         <v>2.17</v>
       </c>
       <c r="S57">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T57">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="U57">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="V57">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W57">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X57">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y57">
         <v>1.25</v>
       </c>
       <c r="Z57">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AA57">
         <v>1.85</v>
@@ -9648,16 +9648,16 @@
         <v>3.08</v>
       </c>
       <c r="AD57">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE57">
         <v>1.07</v>
       </c>
       <c r="AF57">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG57">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>1.2</v>
       </c>
       <c r="AK57">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.84</v>
+        <v>1.47</v>
       </c>
       <c r="O61">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="P61">
-        <v>3.35</v>
+        <v>5.6</v>
       </c>
       <c r="Q61">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="R61">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="S61">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T61">
-        <v>4</v>
+        <v>3.74</v>
       </c>
       <c r="U61">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="V61">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="W61">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X61">
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Z61">
-        <v>6.57</v>
+        <v>5.53</v>
       </c>
       <c r="AA61">
         <v>1.4</v>
       </c>
       <c r="AB61">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AC61">
-        <v>1.89</v>
+        <v>2.21</v>
       </c>
       <c r="AD61">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AE61">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AF61">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AG61">
-        <v>3</v>
+        <v>2.32</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AK61">
-        <v>1.83</v>
+        <v>2.43</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
+        <v>2.35</v>
+      </c>
+      <c r="O62">
+        <v>3.95</v>
+      </c>
+      <c r="P62">
+        <v>2.4</v>
+      </c>
+      <c r="Q62">
+        <v>2.7</v>
+      </c>
+      <c r="R62">
+        <v>2.4</v>
+      </c>
+      <c r="S62">
+        <v>1.18</v>
+      </c>
+      <c r="T62">
+        <v>3.85</v>
+      </c>
+      <c r="U62">
+        <v>2.06</v>
+      </c>
+      <c r="V62">
         <v>1.65</v>
       </c>
-      <c r="O62">
-        <v>3.7</v>
-      </c>
-      <c r="P62">
-        <v>4</v>
-      </c>
-      <c r="Q62">
-        <v>2.18</v>
-      </c>
-      <c r="R62">
-        <v>2.32</v>
-      </c>
-      <c r="S62">
-        <v>1.25</v>
-      </c>
-      <c r="T62">
-        <v>3.24</v>
-      </c>
-      <c r="U62">
-        <v>2.25</v>
-      </c>
-      <c r="V62">
-        <v>1.57</v>
-      </c>
       <c r="W62">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X62">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y62">
         <v>1.14</v>
       </c>
       <c r="Z62">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AA62">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AB62">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="AC62">
-        <v>2.47</v>
+        <v>2.15</v>
       </c>
       <c r="AD62">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="AE62">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AF62">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AG62">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK62">
-        <v>1.99</v>
+        <v>1.44</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,34 +10578,34 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.35</v>
+        <v>1.84</v>
       </c>
       <c r="O63">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="P63">
-        <v>2.4</v>
+        <v>3.35</v>
       </c>
       <c r="Q63">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="R63">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="S63">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="T63">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="U63">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="V63">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="W63">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X63">
         <v>1.01</v>
@@ -10614,25 +10614,25 @@
         <v>1.07</v>
       </c>
       <c r="Z63">
-        <v>6.5</v>
+        <v>6.68</v>
       </c>
       <c r="AA63">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AB63">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AC63">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AD63">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="AE63">
+        <v>1.3</v>
+      </c>
+      <c r="AF63">
         <v>1.33</v>
-      </c>
-      <c r="AF63">
-        <v>1.35</v>
       </c>
       <c r="AG63">
         <v>2.9</v>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK63">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10904,7 +10904,7 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="O65">
         <v>4.2</v>
@@ -10913,55 +10913,55 @@
         <v>8.44</v>
       </c>
       <c r="Q65">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="R65">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="S65">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="T65">
-        <v>2.75</v>
+        <v>2.31</v>
       </c>
       <c r="U65">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="V65">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W65">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X65">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y65">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="Z65">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
       <c r="AA65">
-        <v>2.17</v>
+        <v>2.51</v>
       </c>
       <c r="AB65">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AC65">
-        <v>3.86</v>
+        <v>4.55</v>
       </c>
       <c r="AD65">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AE65">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AF65">
-        <v>2.63</v>
+        <v>3.04</v>
       </c>
       <c r="AG65">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,52 +11067,52 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="O66">
         <v>3.4</v>
       </c>
       <c r="P66">
-        <v>3</v>
+        <v>3.82</v>
       </c>
       <c r="Q66">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="R66">
         <v>2.2</v>
       </c>
       <c r="S66">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T66">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="U66">
-        <v>2.45</v>
+        <v>2.74</v>
       </c>
       <c r="V66">
         <v>1.44</v>
       </c>
       <c r="W66">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X66">
         <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="Z66">
-        <v>3.76</v>
+        <v>3.92</v>
       </c>
       <c r="AA66">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AB66">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AC66">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="AD66">
         <v>1.36</v>
@@ -11121,10 +11121,10 @@
         <v>1.13</v>
       </c>
       <c r="AF66">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG66">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AK66">
-        <v>1.57</v>
+        <v>1.93</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="O67">
-        <v>3.36</v>
+        <v>3.23</v>
       </c>
       <c r="P67">
-        <v>2.52</v>
+        <v>2.78</v>
       </c>
       <c r="Q67">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="R67">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="S67">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="T67">
-        <v>3.21</v>
+        <v>2.92</v>
       </c>
       <c r="U67">
-        <v>2.5</v>
+        <v>2.89</v>
       </c>
       <c r="V67">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W67">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X67">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y67">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z67">
-        <v>3.94</v>
+        <v>3.48</v>
       </c>
       <c r="AA67">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AB67">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="AC67">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AD67">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AE67">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF67">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG67">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AK67">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,65 +11393,65 @@
         </is>
       </c>
       <c r="N68">
+        <v>2.2</v>
+      </c>
+      <c r="O68">
+        <v>3.15</v>
+      </c>
+      <c r="P68">
+        <v>3</v>
+      </c>
+      <c r="Q68">
+        <v>2.75</v>
+      </c>
+      <c r="R68">
+        <v>1.95</v>
+      </c>
+      <c r="S68">
+        <v>1.5</v>
+      </c>
+      <c r="T68">
+        <v>2.57</v>
+      </c>
+      <c r="U68">
+        <v>2.95</v>
+      </c>
+      <c r="V68">
+        <v>1.3</v>
+      </c>
+      <c r="W68">
+        <v>1.03</v>
+      </c>
+      <c r="X68">
+        <v>1.04</v>
+      </c>
+      <c r="Y68">
+        <v>1.37</v>
+      </c>
+      <c r="Z68">
+        <v>2.84</v>
+      </c>
+      <c r="AA68">
+        <v>2.23</v>
+      </c>
+      <c r="AB68">
+        <v>1.61</v>
+      </c>
+      <c r="AC68">
+        <v>4.55</v>
+      </c>
+      <c r="AD68">
+        <v>1.18</v>
+      </c>
+      <c r="AE68">
+        <v>1.03</v>
+      </c>
+      <c r="AF68">
+        <v>1.95</v>
+      </c>
+      <c r="AG68">
         <v>1.75</v>
       </c>
-      <c r="O68">
-        <v>3.4</v>
-      </c>
-      <c r="P68">
-        <v>3.82</v>
-      </c>
-      <c r="Q68">
-        <v>2.4</v>
-      </c>
-      <c r="R68">
-        <v>2.2</v>
-      </c>
-      <c r="S68">
-        <v>1.33</v>
-      </c>
-      <c r="T68">
-        <v>3.1</v>
-      </c>
-      <c r="U68">
-        <v>2.74</v>
-      </c>
-      <c r="V68">
-        <v>1.44</v>
-      </c>
-      <c r="W68">
-        <v>1.06</v>
-      </c>
-      <c r="X68">
-        <v>1.02</v>
-      </c>
-      <c r="Y68">
-        <v>1.26</v>
-      </c>
-      <c r="Z68">
-        <v>3.92</v>
-      </c>
-      <c r="AA68">
-        <v>1.8</v>
-      </c>
-      <c r="AB68">
-        <v>2.01</v>
-      </c>
-      <c r="AC68">
-        <v>3.13</v>
-      </c>
-      <c r="AD68">
-        <v>1.36</v>
-      </c>
-      <c r="AE68">
-        <v>1.13</v>
-      </c>
-      <c r="AF68">
-        <v>1.64</v>
-      </c>
-      <c r="AG68">
-        <v>2.05</v>
-      </c>
       <c r="AH68" t="inlineStr">
         <is>
           <t>[]</t>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK68">
-        <v>1.93</v>
+        <v>1.54</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="O69">
-        <v>3.23</v>
+        <v>3.05</v>
       </c>
       <c r="P69">
-        <v>2.78</v>
+        <v>3.25</v>
       </c>
       <c r="Q69">
-        <v>2.77</v>
+        <v>2.95</v>
       </c>
       <c r="R69">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S69">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T69">
-        <v>2.92</v>
+        <v>2.51</v>
       </c>
       <c r="U69">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="V69">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W69">
         <v>1.05</v>
       </c>
       <c r="X69">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y69">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="Z69">
-        <v>3.48</v>
+        <v>3.04</v>
       </c>
       <c r="AA69">
-        <v>1.83</v>
+        <v>2.18</v>
       </c>
       <c r="AB69">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AC69">
-        <v>2.97</v>
+        <v>3.42</v>
       </c>
       <c r="AD69">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AE69">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF69">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG69">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AK69">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="O70">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="P70">
         <v>3</v>
       </c>
       <c r="Q70">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="R70">
+        <v>2.2</v>
+      </c>
+      <c r="S70">
+        <v>1.31</v>
+      </c>
+      <c r="T70">
+        <v>3.08</v>
+      </c>
+      <c r="U70">
+        <v>2.45</v>
+      </c>
+      <c r="V70">
+        <v>1.44</v>
+      </c>
+      <c r="W70">
+        <v>1.08</v>
+      </c>
+      <c r="X70">
+        <v>1.02</v>
+      </c>
+      <c r="Y70">
+        <v>1.21</v>
+      </c>
+      <c r="Z70">
+        <v>3.76</v>
+      </c>
+      <c r="AA70">
+        <v>1.78</v>
+      </c>
+      <c r="AB70">
         <v>1.95</v>
       </c>
-      <c r="S70">
-        <v>1.5</v>
-      </c>
-      <c r="T70">
-        <v>2.57</v>
-      </c>
-      <c r="U70">
-        <v>2.95</v>
-      </c>
-      <c r="V70">
-        <v>1.3</v>
-      </c>
-      <c r="W70">
-        <v>1.03</v>
-      </c>
-      <c r="X70">
-        <v>1.04</v>
-      </c>
-      <c r="Y70">
-        <v>1.37</v>
-      </c>
-      <c r="Z70">
-        <v>2.84</v>
-      </c>
-      <c r="AA70">
-        <v>2.23</v>
-      </c>
-      <c r="AB70">
-        <v>1.61</v>
-      </c>
       <c r="AC70">
-        <v>4.55</v>
+        <v>3.15</v>
       </c>
       <c r="AD70">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AE70">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AF70">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AG70">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AK70">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="O71">
-        <v>3.05</v>
+        <v>3.36</v>
       </c>
       <c r="P71">
-        <v>3.25</v>
+        <v>2.52</v>
       </c>
       <c r="Q71">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="R71">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="S71">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="T71">
-        <v>2.51</v>
+        <v>3.21</v>
       </c>
       <c r="U71">
-        <v>2.86</v>
+        <v>2.5</v>
       </c>
       <c r="V71">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="W71">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X71">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y71">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z71">
+        <v>3.94</v>
+      </c>
+      <c r="AA71">
+        <v>1.74</v>
+      </c>
+      <c r="AB71">
+        <v>1.98</v>
+      </c>
+      <c r="AC71">
         <v>3.04</v>
       </c>
-      <c r="AA71">
-        <v>2.18</v>
-      </c>
-      <c r="AB71">
-        <v>1.67</v>
-      </c>
-      <c r="AC71">
-        <v>3.42</v>
-      </c>
       <c r="AD71">
-        <v>1.23</v>
+        <v>1.39</v>
       </c>
       <c r="AE71">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AF71">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AG71">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK71">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12250,16 +12250,16 @@
         <v>1.53</v>
       </c>
       <c r="AB73">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AC73">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="AD73">
         <v>1.53</v>
       </c>
       <c r="AE73">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF73">
         <v>1.83</v>
@@ -12278,7 +12278,7 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK73">
         <v>3.22</v>
@@ -12380,55 +12380,55 @@
         <v>0</v>
       </c>
       <c r="Q74">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="R74">
-        <v>4.65</v>
+        <v>4.33</v>
       </c>
       <c r="S74">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="T74">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="U74">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="V74">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="W74">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="X74">
         <v>1.01</v>
       </c>
       <c r="Y74">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Z74">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AA74">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AB74">
         <v>4.33</v>
       </c>
       <c r="AC74">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AD74">
-        <v>2.42</v>
+        <v>2.59</v>
       </c>
       <c r="AE74">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AF74">
-        <v>2.67</v>
+        <v>2.92</v>
       </c>
       <c r="AG74">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G75">
@@ -12543,52 +12543,52 @@
         <v>0</v>
       </c>
       <c r="Q75">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="R75">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="S75">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T75">
         <v>3.25</v>
       </c>
       <c r="U75">
-        <v>2.46</v>
+        <v>2.32</v>
       </c>
       <c r="V75">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W75">
         <v>1.12</v>
       </c>
       <c r="X75">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y75">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z75">
-        <v>4.05</v>
+        <v>4.47</v>
       </c>
       <c r="AA75">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AB75">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="AC75">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AD75">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AE75">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AF75">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG75">
         <v>2.3</v>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK75">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G76">
@@ -12706,52 +12706,52 @@
         <v>0</v>
       </c>
       <c r="Q76">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="R76">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="S76">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T76">
         <v>3.25</v>
       </c>
       <c r="U76">
-        <v>2.32</v>
+        <v>2.46</v>
       </c>
       <c r="V76">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W76">
         <v>1.12</v>
       </c>
       <c r="X76">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y76">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z76">
-        <v>4.47</v>
+        <v>4.05</v>
       </c>
       <c r="AA76">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AB76">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="AC76">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AD76">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AE76">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AF76">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG76">
         <v>2.3</v>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK76">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12860,31 +12860,31 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="O77">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P77">
         <v>5.35</v>
       </c>
       <c r="Q77">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="R77">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S77">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T77">
-        <v>2.49</v>
+        <v>2.53</v>
       </c>
       <c r="U77">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="V77">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W77">
         <v>1.05</v>
@@ -12893,31 +12893,31 @@
         <v>1.02</v>
       </c>
       <c r="Y77">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z77">
-        <v>2.96</v>
+        <v>3.08</v>
       </c>
       <c r="AA77">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="AB77">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AC77">
-        <v>4.1</v>
+        <v>3.98</v>
       </c>
       <c r="AD77">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE77">
         <v>1.03</v>
       </c>
       <c r="AF77">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AG77">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AK77">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13023,25 +13023,25 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="O78">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="P78">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="Q78">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="R78">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="S78">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T78">
-        <v>3.55</v>
+        <v>3.74</v>
       </c>
       <c r="U78">
         <v>2.1</v>
@@ -13056,32 +13056,32 @@
         <v>1.01</v>
       </c>
       <c r="Y78">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Z78">
-        <v>5.35</v>
+        <v>5.75</v>
       </c>
       <c r="AA78">
+        <v>1.36</v>
+      </c>
+      <c r="AB78">
+        <v>2.78</v>
+      </c>
+      <c r="AC78">
+        <v>1.9</v>
+      </c>
+      <c r="AD78">
+        <v>1.88</v>
+      </c>
+      <c r="AE78">
+        <v>1.33</v>
+      </c>
+      <c r="AF78">
         <v>1.4</v>
       </c>
-      <c r="AB78">
+      <c r="AG78">
         <v>2.62</v>
       </c>
-      <c r="AC78">
-        <v>1.99</v>
-      </c>
-      <c r="AD78">
-        <v>1.81</v>
-      </c>
-      <c r="AE78">
-        <v>1.29</v>
-      </c>
-      <c r="AF78">
-        <v>1.44</v>
-      </c>
-      <c r="AG78">
-        <v>2.5</v>
-      </c>
       <c r="AH78" t="inlineStr">
         <is>
           <t>[]</t>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AK78">
-        <v>2.31</v>
+        <v>2.49</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13201,16 +13201,16 @@
         <v>2.55</v>
       </c>
       <c r="S79">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="T79">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="U79">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="V79">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="W79">
         <v>1.22</v>
@@ -13222,7 +13222,7 @@
         <v>1.05</v>
       </c>
       <c r="Z79">
-        <v>7.5</v>
+        <v>6.45</v>
       </c>
       <c r="AA79">
         <v>1.36</v>
@@ -13240,10 +13240,10 @@
         <v>1.41</v>
       </c>
       <c r="AF79">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AG79">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,80 +13349,80 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="O80">
-        <v>3.75</v>
+        <v>3.68</v>
       </c>
       <c r="P80">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="Q80">
+        <v>2.83</v>
+      </c>
+      <c r="R80">
+        <v>2.25</v>
+      </c>
+      <c r="S80">
+        <v>1.28</v>
+      </c>
+      <c r="T80">
         <v>3.3</v>
       </c>
-      <c r="R80">
-        <v>2.62</v>
-      </c>
-      <c r="S80">
-        <v>1.17</v>
-      </c>
-      <c r="T80">
-        <v>4.1</v>
-      </c>
       <c r="U80">
-        <v>1.98</v>
+        <v>2.38</v>
       </c>
       <c r="V80">
-        <v>1.93</v>
+        <v>1.54</v>
       </c>
       <c r="W80">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="X80">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y80">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="Z80">
-        <v>8</v>
+        <v>4.4</v>
       </c>
       <c r="AA80">
+        <v>1.62</v>
+      </c>
+      <c r="AB80">
+        <v>2.17</v>
+      </c>
+      <c r="AC80">
+        <v>2.46</v>
+      </c>
+      <c r="AD80">
+        <v>1.43</v>
+      </c>
+      <c r="AE80">
+        <v>1.19</v>
+      </c>
+      <c r="AF80">
+        <v>1.5</v>
+      </c>
+      <c r="AG80">
+        <v>2.4</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ80">
         <v>1.3</v>
       </c>
-      <c r="AB80">
-        <v>3.5</v>
-      </c>
-      <c r="AC80">
-        <v>1.79</v>
-      </c>
-      <c r="AD80">
-        <v>1.99</v>
-      </c>
-      <c r="AE80">
-        <v>1.4</v>
-      </c>
-      <c r="AF80">
-        <v>1.33</v>
-      </c>
-      <c r="AG80">
-        <v>3.4</v>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI80" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ80">
-        <v>1.2</v>
-      </c>
       <c r="AK80">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.4</v>
+        <v>1.75</v>
       </c>
       <c r="O81">
-        <v>3.72</v>
+        <v>3.8</v>
       </c>
       <c r="P81">
-        <v>2.55</v>
+        <v>3.4</v>
       </c>
       <c r="Q81">
-        <v>2.76</v>
+        <v>2.19</v>
       </c>
       <c r="R81">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="S81">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="T81">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="U81">
-        <v>2.32</v>
+        <v>1.85</v>
       </c>
       <c r="V81">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="W81">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="X81">
         <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="Z81">
-        <v>4.6</v>
+        <v>6.58</v>
       </c>
       <c r="AA81">
-        <v>1.58</v>
+        <v>1.33</v>
       </c>
       <c r="AB81">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="AC81">
-        <v>2.38</v>
+        <v>1.96</v>
       </c>
       <c r="AD81">
-        <v>1.46</v>
+        <v>1.88</v>
       </c>
       <c r="AE81">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AF81">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AG81">
-        <v>2.45</v>
+        <v>2.84</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK81">
-        <v>1.53</v>
+        <v>1.92</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,80 +13675,80 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.67</v>
+        <v>3.6</v>
       </c>
       <c r="O82">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P82">
-        <v>3.75</v>
+        <v>1.83</v>
       </c>
       <c r="Q82">
-        <v>2.04</v>
+        <v>3.49</v>
       </c>
       <c r="R82">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="S82">
+        <v>1.17</v>
+      </c>
+      <c r="T82">
+        <v>4.2</v>
+      </c>
+      <c r="U82">
+        <v>2</v>
+      </c>
+      <c r="V82">
+        <v>1.73</v>
+      </c>
+      <c r="W82">
         <v>1.18</v>
-      </c>
-      <c r="T82">
-        <v>4.4</v>
-      </c>
-      <c r="U82">
-        <v>1.91</v>
-      </c>
-      <c r="V82">
-        <v>1.8</v>
-      </c>
-      <c r="W82">
-        <v>1.22</v>
       </c>
       <c r="X82">
         <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Z82">
-        <v>6.63</v>
+        <v>5.65</v>
       </c>
       <c r="AA82">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AB82">
-        <v>3.1</v>
+        <v>2.66</v>
       </c>
       <c r="AC82">
+        <v>1.97</v>
+      </c>
+      <c r="AD82">
+        <v>1.72</v>
+      </c>
+      <c r="AE82">
+        <v>1.26</v>
+      </c>
+      <c r="AF82">
+        <v>1.4</v>
+      </c>
+      <c r="AG82">
+        <v>2.8</v>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ82">
         <v>1.92</v>
       </c>
-      <c r="AD82">
-        <v>1.9</v>
-      </c>
-      <c r="AE82">
-        <v>1.33</v>
-      </c>
-      <c r="AF82">
-        <v>1.38</v>
-      </c>
-      <c r="AG82">
-        <v>2.76</v>
-      </c>
-      <c r="AH82" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI82" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ82">
-        <v>1.22</v>
-      </c>
       <c r="AK82">
-        <v>2.07</v>
+        <v>1.19</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,34 +13838,34 @@
         </is>
       </c>
       <c r="N83">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="O83">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P83">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="Q83">
-        <v>3.18</v>
+        <v>2.88</v>
       </c>
       <c r="R83">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="S83">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T83">
-        <v>3.8</v>
+        <v>3.48</v>
       </c>
       <c r="U83">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V83">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="W83">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X83">
         <v>1.01</v>
@@ -13874,28 +13874,28 @@
         <v>1.09</v>
       </c>
       <c r="Z83">
-        <v>5.4</v>
+        <v>6.5</v>
       </c>
       <c r="AA83">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB83">
         <v>2.7</v>
       </c>
       <c r="AC83">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="AD83">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AE83">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AF83">
         <v>1.4</v>
       </c>
       <c r="AG83">
-        <v>2.75</v>
+        <v